--- a/Market Fundamentals/Transelectrica_data/Cons_Prod_final/Weekly_Consumption_2026.xlsx
+++ b/Market Fundamentals/Transelectrica_data/Cons_Prod_final/Weekly_Consumption_2026.xlsx
@@ -44272,7 +44272,7 @@
         <v>1</v>
       </c>
       <c r="C2498">
-        <v>5880</v>
+        <v>5700</v>
       </c>
       <c r="D2498" t="s">
         <v>2500</v>
@@ -44286,7 +44286,7 @@
         <v>2</v>
       </c>
       <c r="C2499">
-        <v>5820</v>
+        <v>5650</v>
       </c>
       <c r="D2499" t="s">
         <v>2501</v>
@@ -44300,7 +44300,7 @@
         <v>3</v>
       </c>
       <c r="C2500">
-        <v>5770</v>
+        <v>5590</v>
       </c>
       <c r="D2500" t="s">
         <v>2502</v>
@@ -44314,7 +44314,7 @@
         <v>4</v>
       </c>
       <c r="C2501">
-        <v>5720</v>
+        <v>5540</v>
       </c>
       <c r="D2501" t="s">
         <v>2503</v>
@@ -44328,7 +44328,7 @@
         <v>5</v>
       </c>
       <c r="C2502">
-        <v>5660</v>
+        <v>5500</v>
       </c>
       <c r="D2502" t="s">
         <v>2504</v>
@@ -44342,7 +44342,7 @@
         <v>6</v>
       </c>
       <c r="C2503">
-        <v>5620</v>
+        <v>5460</v>
       </c>
       <c r="D2503" t="s">
         <v>2505</v>
@@ -44356,7 +44356,7 @@
         <v>7</v>
       </c>
       <c r="C2504">
-        <v>5600</v>
+        <v>5430</v>
       </c>
       <c r="D2504" t="s">
         <v>2506</v>
@@ -44370,7 +44370,7 @@
         <v>8</v>
       </c>
       <c r="C2505">
-        <v>5570</v>
+        <v>5410</v>
       </c>
       <c r="D2505" t="s">
         <v>2507</v>
@@ -44384,7 +44384,7 @@
         <v>9</v>
       </c>
       <c r="C2506">
-        <v>5550</v>
+        <v>5400</v>
       </c>
       <c r="D2506" t="s">
         <v>2508</v>
@@ -44398,7 +44398,7 @@
         <v>10</v>
       </c>
       <c r="C2507">
-        <v>5530</v>
+        <v>5400</v>
       </c>
       <c r="D2507" t="s">
         <v>2509</v>
@@ -44412,7 +44412,7 @@
         <v>11</v>
       </c>
       <c r="C2508">
-        <v>5510</v>
+        <v>5380</v>
       </c>
       <c r="D2508" t="s">
         <v>2510</v>
@@ -44426,7 +44426,7 @@
         <v>12</v>
       </c>
       <c r="C2509">
-        <v>5490</v>
+        <v>5380</v>
       </c>
       <c r="D2509" t="s">
         <v>2511</v>
@@ -44440,7 +44440,7 @@
         <v>13</v>
       </c>
       <c r="C2510">
-        <v>5480</v>
+        <v>5370</v>
       </c>
       <c r="D2510" t="s">
         <v>2512</v>
@@ -44454,7 +44454,7 @@
         <v>14</v>
       </c>
       <c r="C2511">
-        <v>5460</v>
+        <v>5370</v>
       </c>
       <c r="D2511" t="s">
         <v>2513</v>
@@ -44468,7 +44468,7 @@
         <v>15</v>
       </c>
       <c r="C2512">
-        <v>5450</v>
+        <v>5380</v>
       </c>
       <c r="D2512" t="s">
         <v>2514</v>
@@ -44482,7 +44482,7 @@
         <v>16</v>
       </c>
       <c r="C2513">
-        <v>5450</v>
+        <v>5390</v>
       </c>
       <c r="D2513" t="s">
         <v>2515</v>
@@ -44496,7 +44496,7 @@
         <v>17</v>
       </c>
       <c r="C2514">
-        <v>5460</v>
+        <v>5400</v>
       </c>
       <c r="D2514" t="s">
         <v>2516</v>
@@ -44510,7 +44510,7 @@
         <v>18</v>
       </c>
       <c r="C2515">
-        <v>5480</v>
+        <v>5420</v>
       </c>
       <c r="D2515" t="s">
         <v>2517</v>
@@ -44524,7 +44524,7 @@
         <v>19</v>
       </c>
       <c r="C2516">
-        <v>5500</v>
+        <v>5440</v>
       </c>
       <c r="D2516" t="s">
         <v>2518</v>
@@ -44538,7 +44538,7 @@
         <v>20</v>
       </c>
       <c r="C2517">
-        <v>5540</v>
+        <v>5480</v>
       </c>
       <c r="D2517" t="s">
         <v>2519</v>
@@ -44552,7 +44552,7 @@
         <v>21</v>
       </c>
       <c r="C2518">
-        <v>5590</v>
+        <v>5540</v>
       </c>
       <c r="D2518" t="s">
         <v>2520</v>
@@ -44566,7 +44566,7 @@
         <v>22</v>
       </c>
       <c r="C2519">
-        <v>5650</v>
+        <v>5620</v>
       </c>
       <c r="D2519" t="s">
         <v>2521</v>
@@ -44580,7 +44580,7 @@
         <v>23</v>
       </c>
       <c r="C2520">
-        <v>5730</v>
+        <v>5720</v>
       </c>
       <c r="D2520" t="s">
         <v>2522</v>
@@ -44608,7 +44608,7 @@
         <v>25</v>
       </c>
       <c r="C2522">
-        <v>5940</v>
+        <v>5970</v>
       </c>
       <c r="D2522" t="s">
         <v>2524</v>
@@ -44622,7 +44622,7 @@
         <v>26</v>
       </c>
       <c r="C2523">
-        <v>6070</v>
+        <v>6100</v>
       </c>
       <c r="D2523" t="s">
         <v>2525</v>
@@ -44636,7 +44636,7 @@
         <v>27</v>
       </c>
       <c r="C2524">
-        <v>6210</v>
+        <v>6230</v>
       </c>
       <c r="D2524" t="s">
         <v>2526</v>
@@ -44650,7 +44650,7 @@
         <v>28</v>
       </c>
       <c r="C2525">
-        <v>6350</v>
+        <v>6360</v>
       </c>
       <c r="D2525" t="s">
         <v>2527</v>
@@ -44664,7 +44664,7 @@
         <v>29</v>
       </c>
       <c r="C2526">
-        <v>6500</v>
+        <v>6470</v>
       </c>
       <c r="D2526" t="s">
         <v>2528</v>
@@ -44678,7 +44678,7 @@
         <v>30</v>
       </c>
       <c r="C2527">
-        <v>6630</v>
+        <v>6570</v>
       </c>
       <c r="D2527" t="s">
         <v>2529</v>
@@ -44692,7 +44692,7 @@
         <v>31</v>
       </c>
       <c r="C2528">
-        <v>6750</v>
+        <v>6660</v>
       </c>
       <c r="D2528" t="s">
         <v>2530</v>
@@ -44706,7 +44706,7 @@
         <v>32</v>
       </c>
       <c r="C2529">
-        <v>6850</v>
+        <v>6720</v>
       </c>
       <c r="D2529" t="s">
         <v>2531</v>
@@ -44720,7 +44720,7 @@
         <v>33</v>
       </c>
       <c r="C2530">
-        <v>6950</v>
+        <v>6760</v>
       </c>
       <c r="D2530" t="s">
         <v>2532</v>
@@ -44734,7 +44734,7 @@
         <v>34</v>
       </c>
       <c r="C2531">
-        <v>7000</v>
+        <v>6770</v>
       </c>
       <c r="D2531" t="s">
         <v>2533</v>
@@ -44748,7 +44748,7 @@
         <v>35</v>
       </c>
       <c r="C2532">
-        <v>7000</v>
+        <v>6760</v>
       </c>
       <c r="D2532" t="s">
         <v>2534</v>
@@ -44762,7 +44762,7 @@
         <v>36</v>
       </c>
       <c r="C2533">
-        <v>6970</v>
+        <v>6740</v>
       </c>
       <c r="D2533" t="s">
         <v>2535</v>
@@ -44776,7 +44776,7 @@
         <v>37</v>
       </c>
       <c r="C2534">
-        <v>6900</v>
+        <v>6680</v>
       </c>
       <c r="D2534" t="s">
         <v>2536</v>
@@ -44790,7 +44790,7 @@
         <v>38</v>
       </c>
       <c r="C2535">
-        <v>6820</v>
+        <v>6630</v>
       </c>
       <c r="D2535" t="s">
         <v>2537</v>
@@ -44804,7 +44804,7 @@
         <v>39</v>
       </c>
       <c r="C2536">
-        <v>6730</v>
+        <v>6560</v>
       </c>
       <c r="D2536" t="s">
         <v>2538</v>
@@ -44818,7 +44818,7 @@
         <v>40</v>
       </c>
       <c r="C2537">
-        <v>6630</v>
+        <v>6480</v>
       </c>
       <c r="D2537" t="s">
         <v>2539</v>
@@ -44832,7 +44832,7 @@
         <v>41</v>
       </c>
       <c r="C2538">
-        <v>6530</v>
+        <v>6400</v>
       </c>
       <c r="D2538" t="s">
         <v>2540</v>
@@ -44846,7 +44846,7 @@
         <v>42</v>
       </c>
       <c r="C2539">
-        <v>6430</v>
+        <v>6320</v>
       </c>
       <c r="D2539" t="s">
         <v>2541</v>
@@ -44860,7 +44860,7 @@
         <v>43</v>
       </c>
       <c r="C2540">
-        <v>6340</v>
+        <v>6240</v>
       </c>
       <c r="D2540" t="s">
         <v>2542</v>
@@ -44874,7 +44874,7 @@
         <v>44</v>
       </c>
       <c r="C2541">
-        <v>6260</v>
+        <v>6170</v>
       </c>
       <c r="D2541" t="s">
         <v>2543</v>
@@ -44888,7 +44888,7 @@
         <v>45</v>
       </c>
       <c r="C2542">
-        <v>6190</v>
+        <v>6110</v>
       </c>
       <c r="D2542" t="s">
         <v>2544</v>
@@ -44902,7 +44902,7 @@
         <v>46</v>
       </c>
       <c r="C2543">
-        <v>6140</v>
+        <v>6050</v>
       </c>
       <c r="D2543" t="s">
         <v>2545</v>
@@ -44916,7 +44916,7 @@
         <v>47</v>
       </c>
       <c r="C2544">
-        <v>6100</v>
+        <v>6010</v>
       </c>
       <c r="D2544" t="s">
         <v>2546</v>
@@ -44930,7 +44930,7 @@
         <v>48</v>
       </c>
       <c r="C2545">
-        <v>6070</v>
+        <v>5980</v>
       </c>
       <c r="D2545" t="s">
         <v>2547</v>
@@ -44944,7 +44944,7 @@
         <v>49</v>
       </c>
       <c r="C2546">
-        <v>6060</v>
+        <v>5960</v>
       </c>
       <c r="D2546" t="s">
         <v>2548</v>
@@ -44958,7 +44958,7 @@
         <v>50</v>
       </c>
       <c r="C2547">
-        <v>6040</v>
+        <v>5950</v>
       </c>
       <c r="D2547" t="s">
         <v>2549</v>
@@ -44972,7 +44972,7 @@
         <v>51</v>
       </c>
       <c r="C2548">
-        <v>6030</v>
+        <v>5960</v>
       </c>
       <c r="D2548" t="s">
         <v>2550</v>
@@ -44986,7 +44986,7 @@
         <v>52</v>
       </c>
       <c r="C2549">
-        <v>6020</v>
+        <v>5970</v>
       </c>
       <c r="D2549" t="s">
         <v>2551</v>
@@ -45000,7 +45000,7 @@
         <v>53</v>
       </c>
       <c r="C2550">
-        <v>6030</v>
+        <v>5990</v>
       </c>
       <c r="D2550" t="s">
         <v>2552</v>
@@ -45014,7 +45014,7 @@
         <v>54</v>
       </c>
       <c r="C2551">
-        <v>6060</v>
+        <v>6020</v>
       </c>
       <c r="D2551" t="s">
         <v>2553</v>
@@ -45028,7 +45028,7 @@
         <v>55</v>
       </c>
       <c r="C2552">
-        <v>6130</v>
+        <v>6060</v>
       </c>
       <c r="D2552" t="s">
         <v>2554</v>
@@ -45042,7 +45042,7 @@
         <v>56</v>
       </c>
       <c r="C2553">
-        <v>6200</v>
+        <v>6100</v>
       </c>
       <c r="D2553" t="s">
         <v>2555</v>
@@ -45056,7 +45056,7 @@
         <v>57</v>
       </c>
       <c r="C2554">
-        <v>6260</v>
+        <v>6150</v>
       </c>
       <c r="D2554" t="s">
         <v>2556</v>
@@ -45070,7 +45070,7 @@
         <v>58</v>
       </c>
       <c r="C2555">
-        <v>6330</v>
+        <v>6200</v>
       </c>
       <c r="D2555" t="s">
         <v>2557</v>
@@ -45084,7 +45084,7 @@
         <v>59</v>
       </c>
       <c r="C2556">
-        <v>6380</v>
+        <v>6240</v>
       </c>
       <c r="D2556" t="s">
         <v>2558</v>
@@ -45098,7 +45098,7 @@
         <v>60</v>
       </c>
       <c r="C2557">
-        <v>6430</v>
+        <v>6290</v>
       </c>
       <c r="D2557" t="s">
         <v>2559</v>
@@ -45112,7 +45112,7 @@
         <v>61</v>
       </c>
       <c r="C2558">
-        <v>6480</v>
+        <v>6330</v>
       </c>
       <c r="D2558" t="s">
         <v>2560</v>
@@ -45126,7 +45126,7 @@
         <v>62</v>
       </c>
       <c r="C2559">
-        <v>6530</v>
+        <v>6380</v>
       </c>
       <c r="D2559" t="s">
         <v>2561</v>
@@ -45140,7 +45140,7 @@
         <v>63</v>
       </c>
       <c r="C2560">
-        <v>6570</v>
+        <v>6430</v>
       </c>
       <c r="D2560" t="s">
         <v>2562</v>
@@ -45154,7 +45154,7 @@
         <v>64</v>
       </c>
       <c r="C2561">
-        <v>6630</v>
+        <v>6490</v>
       </c>
       <c r="D2561" t="s">
         <v>2563</v>
@@ -45168,7 +45168,7 @@
         <v>65</v>
       </c>
       <c r="C2562">
-        <v>6690</v>
+        <v>6550</v>
       </c>
       <c r="D2562" t="s">
         <v>2564</v>
@@ -45182,7 +45182,7 @@
         <v>66</v>
       </c>
       <c r="C2563">
-        <v>6770</v>
+        <v>6630</v>
       </c>
       <c r="D2563" t="s">
         <v>2565</v>
@@ -45196,7 +45196,7 @@
         <v>67</v>
       </c>
       <c r="C2564">
-        <v>6850</v>
+        <v>6700</v>
       </c>
       <c r="D2564" t="s">
         <v>2566</v>
@@ -45210,7 +45210,7 @@
         <v>68</v>
       </c>
       <c r="C2565">
-        <v>6930</v>
+        <v>6790</v>
       </c>
       <c r="D2565" t="s">
         <v>2567</v>
@@ -45224,7 +45224,7 @@
         <v>69</v>
       </c>
       <c r="C2566">
-        <v>7020</v>
+        <v>6870</v>
       </c>
       <c r="D2566" t="s">
         <v>2568</v>
@@ -45238,7 +45238,7 @@
         <v>70</v>
       </c>
       <c r="C2567">
-        <v>7090</v>
+        <v>6960</v>
       </c>
       <c r="D2567" t="s">
         <v>2569</v>
@@ -45252,7 +45252,7 @@
         <v>71</v>
       </c>
       <c r="C2568">
-        <v>7160</v>
+        <v>7030</v>
       </c>
       <c r="D2568" t="s">
         <v>2570</v>
@@ -45266,7 +45266,7 @@
         <v>72</v>
       </c>
       <c r="C2569">
-        <v>7220</v>
+        <v>7100</v>
       </c>
       <c r="D2569" t="s">
         <v>2571</v>
@@ -45280,7 +45280,7 @@
         <v>73</v>
       </c>
       <c r="C2570">
-        <v>7310</v>
+        <v>7170</v>
       </c>
       <c r="D2570" t="s">
         <v>2572</v>
@@ -45294,7 +45294,7 @@
         <v>74</v>
       </c>
       <c r="C2571">
-        <v>7380</v>
+        <v>7240</v>
       </c>
       <c r="D2571" t="s">
         <v>2573</v>
@@ -45308,7 +45308,7 @@
         <v>75</v>
       </c>
       <c r="C2572">
-        <v>7440</v>
+        <v>7330</v>
       </c>
       <c r="D2572" t="s">
         <v>2574</v>
@@ -45322,7 +45322,7 @@
         <v>76</v>
       </c>
       <c r="C2573">
-        <v>7520</v>
+        <v>7420</v>
       </c>
       <c r="D2573" t="s">
         <v>2575</v>
@@ -45336,7 +45336,7 @@
         <v>77</v>
       </c>
       <c r="C2574">
-        <v>7610</v>
+        <v>7490</v>
       </c>
       <c r="D2574" t="s">
         <v>2576</v>
@@ -45350,7 +45350,7 @@
         <v>78</v>
       </c>
       <c r="C2575">
-        <v>7680</v>
+        <v>7570</v>
       </c>
       <c r="D2575" t="s">
         <v>2577</v>
@@ -45364,7 +45364,7 @@
         <v>79</v>
       </c>
       <c r="C2576">
-        <v>7700</v>
+        <v>7600</v>
       </c>
       <c r="D2576" t="s">
         <v>2578</v>
@@ -45378,7 +45378,7 @@
         <v>80</v>
       </c>
       <c r="C2577">
-        <v>7700</v>
+        <v>7630</v>
       </c>
       <c r="D2577" t="s">
         <v>2579</v>
@@ -45392,7 +45392,7 @@
         <v>81</v>
       </c>
       <c r="C2578">
-        <v>7680</v>
+        <v>7610</v>
       </c>
       <c r="D2578" t="s">
         <v>2580</v>
@@ -45406,7 +45406,7 @@
         <v>82</v>
       </c>
       <c r="C2579">
-        <v>7630</v>
+        <v>7580</v>
       </c>
       <c r="D2579" t="s">
         <v>2581</v>
@@ -45420,7 +45420,7 @@
         <v>83</v>
       </c>
       <c r="C2580">
-        <v>7570</v>
+        <v>7510</v>
       </c>
       <c r="D2580" t="s">
         <v>2582</v>
@@ -45434,7 +45434,7 @@
         <v>84</v>
       </c>
       <c r="C2581">
-        <v>7480</v>
+        <v>7420</v>
       </c>
       <c r="D2581" t="s">
         <v>2583</v>
@@ -45448,7 +45448,7 @@
         <v>85</v>
       </c>
       <c r="C2582">
-        <v>7370</v>
+        <v>7330</v>
       </c>
       <c r="D2582" t="s">
         <v>2584</v>
@@ -45462,7 +45462,7 @@
         <v>86</v>
       </c>
       <c r="C2583">
-        <v>7270</v>
+        <v>7220</v>
       </c>
       <c r="D2583" t="s">
         <v>2585</v>
@@ -45476,7 +45476,7 @@
         <v>87</v>
       </c>
       <c r="C2584">
-        <v>7180</v>
+        <v>7110</v>
       </c>
       <c r="D2584" t="s">
         <v>2586</v>
@@ -45490,7 +45490,7 @@
         <v>88</v>
       </c>
       <c r="C2585">
-        <v>7040</v>
+        <v>7000</v>
       </c>
       <c r="D2585" t="s">
         <v>2587</v>
@@ -45504,7 +45504,7 @@
         <v>89</v>
       </c>
       <c r="C2586">
-        <v>6890</v>
+        <v>6870</v>
       </c>
       <c r="D2586" t="s">
         <v>2588</v>
@@ -45518,7 +45518,7 @@
         <v>90</v>
       </c>
       <c r="C2587">
-        <v>6760</v>
+        <v>6730</v>
       </c>
       <c r="D2587" t="s">
         <v>2589</v>
@@ -45532,7 +45532,7 @@
         <v>91</v>
       </c>
       <c r="C2588">
-        <v>6600</v>
+        <v>6580</v>
       </c>
       <c r="D2588" t="s">
         <v>2590</v>
@@ -45546,7 +45546,7 @@
         <v>92</v>
       </c>
       <c r="C2589">
-        <v>6460</v>
+        <v>6420</v>
       </c>
       <c r="D2589" t="s">
         <v>2591</v>
@@ -45560,7 +45560,7 @@
         <v>93</v>
       </c>
       <c r="C2590">
-        <v>6300</v>
+        <v>6280</v>
       </c>
       <c r="D2590" t="s">
         <v>2592</v>
@@ -45574,7 +45574,7 @@
         <v>94</v>
       </c>
       <c r="C2591">
-        <v>6150</v>
+        <v>6140</v>
       </c>
       <c r="D2591" t="s">
         <v>2593</v>
@@ -45588,7 +45588,7 @@
         <v>95</v>
       </c>
       <c r="C2592">
-        <v>6030</v>
+        <v>6000</v>
       </c>
       <c r="D2592" t="s">
         <v>2594</v>
@@ -45616,7 +45616,7 @@
         <v>1</v>
       </c>
       <c r="C2594">
-        <v>5760</v>
+        <v>5880</v>
       </c>
       <c r="D2594" t="s">
         <v>2596</v>
@@ -45630,7 +45630,7 @@
         <v>2</v>
       </c>
       <c r="C2595">
-        <v>5680</v>
+        <v>5830</v>
       </c>
       <c r="D2595" t="s">
         <v>2597</v>
@@ -45644,7 +45644,7 @@
         <v>3</v>
       </c>
       <c r="C2596">
-        <v>5610</v>
+        <v>5770</v>
       </c>
       <c r="D2596" t="s">
         <v>2598</v>
@@ -45658,7 +45658,7 @@
         <v>4</v>
       </c>
       <c r="C2597">
-        <v>5560</v>
+        <v>5710</v>
       </c>
       <c r="D2597" t="s">
         <v>2599</v>
@@ -45672,7 +45672,7 @@
         <v>5</v>
       </c>
       <c r="C2598">
-        <v>5520</v>
+        <v>5650</v>
       </c>
       <c r="D2598" t="s">
         <v>2600</v>
@@ -45686,7 +45686,7 @@
         <v>6</v>
       </c>
       <c r="C2599">
-        <v>5490</v>
+        <v>5610</v>
       </c>
       <c r="D2599" t="s">
         <v>2601</v>
@@ -45700,7 +45700,7 @@
         <v>7</v>
       </c>
       <c r="C2600">
-        <v>5460</v>
+        <v>5570</v>
       </c>
       <c r="D2600" t="s">
         <v>2602</v>
@@ -45714,7 +45714,7 @@
         <v>8</v>
       </c>
       <c r="C2601">
-        <v>5430</v>
+        <v>5540</v>
       </c>
       <c r="D2601" t="s">
         <v>2603</v>
@@ -45728,7 +45728,7 @@
         <v>9</v>
       </c>
       <c r="C2602">
-        <v>5410</v>
+        <v>5510</v>
       </c>
       <c r="D2602" t="s">
         <v>2604</v>
@@ -45742,7 +45742,7 @@
         <v>10</v>
       </c>
       <c r="C2603">
-        <v>5390</v>
+        <v>5490</v>
       </c>
       <c r="D2603" t="s">
         <v>2605</v>
@@ -45756,7 +45756,7 @@
         <v>11</v>
       </c>
       <c r="C2604">
-        <v>5360</v>
+        <v>5470</v>
       </c>
       <c r="D2604" t="s">
         <v>2606</v>
@@ -45770,7 +45770,7 @@
         <v>12</v>
       </c>
       <c r="C2605">
-        <v>5340</v>
+        <v>5450</v>
       </c>
       <c r="D2605" t="s">
         <v>2607</v>
@@ -45784,7 +45784,7 @@
         <v>13</v>
       </c>
       <c r="C2606">
-        <v>5320</v>
+        <v>5430</v>
       </c>
       <c r="D2606" t="s">
         <v>2608</v>
@@ -45798,7 +45798,7 @@
         <v>14</v>
       </c>
       <c r="C2607">
-        <v>5300</v>
+        <v>5400</v>
       </c>
       <c r="D2607" t="s">
         <v>2609</v>
@@ -45812,7 +45812,7 @@
         <v>15</v>
       </c>
       <c r="C2608">
-        <v>5290</v>
+        <v>5410</v>
       </c>
       <c r="D2608" t="s">
         <v>2610</v>
@@ -45826,7 +45826,7 @@
         <v>16</v>
       </c>
       <c r="C2609">
-        <v>5290</v>
+        <v>5410</v>
       </c>
       <c r="D2609" t="s">
         <v>2611</v>
@@ -45840,7 +45840,7 @@
         <v>17</v>
       </c>
       <c r="C2610">
-        <v>5300</v>
+        <v>5420</v>
       </c>
       <c r="D2610" t="s">
         <v>2612</v>
@@ -45854,7 +45854,7 @@
         <v>18</v>
       </c>
       <c r="C2611">
-        <v>5310</v>
+        <v>5430</v>
       </c>
       <c r="D2611" t="s">
         <v>2613</v>
@@ -45868,7 +45868,7 @@
         <v>19</v>
       </c>
       <c r="C2612">
-        <v>5340</v>
+        <v>5450</v>
       </c>
       <c r="D2612" t="s">
         <v>2614</v>
@@ -45882,7 +45882,7 @@
         <v>20</v>
       </c>
       <c r="C2613">
-        <v>5380</v>
+        <v>5470</v>
       </c>
       <c r="D2613" t="s">
         <v>2615</v>
@@ -45896,7 +45896,7 @@
         <v>21</v>
       </c>
       <c r="C2614">
-        <v>5420</v>
+        <v>5500</v>
       </c>
       <c r="D2614" t="s">
         <v>2616</v>
@@ -45910,7 +45910,7 @@
         <v>22</v>
       </c>
       <c r="C2615">
-        <v>5450</v>
+        <v>5530</v>
       </c>
       <c r="D2615" t="s">
         <v>2617</v>
@@ -45924,7 +45924,7 @@
         <v>23</v>
       </c>
       <c r="C2616">
-        <v>5460</v>
+        <v>5550</v>
       </c>
       <c r="D2616" t="s">
         <v>2618</v>
@@ -45938,7 +45938,7 @@
         <v>24</v>
       </c>
       <c r="C2617">
-        <v>5450</v>
+        <v>5560</v>
       </c>
       <c r="D2617" t="s">
         <v>2619</v>
@@ -45952,7 +45952,7 @@
         <v>25</v>
       </c>
       <c r="C2618">
-        <v>5430</v>
+        <v>5580</v>
       </c>
       <c r="D2618" t="s">
         <v>2620</v>
@@ -45966,7 +45966,7 @@
         <v>26</v>
       </c>
       <c r="C2619">
-        <v>5430</v>
+        <v>5600</v>
       </c>
       <c r="D2619" t="s">
         <v>2621</v>
@@ -45980,7 +45980,7 @@
         <v>27</v>
       </c>
       <c r="C2620">
-        <v>5450</v>
+        <v>5650</v>
       </c>
       <c r="D2620" t="s">
         <v>2622</v>
@@ -45994,7 +45994,7 @@
         <v>28</v>
       </c>
       <c r="C2621">
-        <v>5500</v>
+        <v>5710</v>
       </c>
       <c r="D2621" t="s">
         <v>2623</v>
@@ -46008,7 +46008,7 @@
         <v>29</v>
       </c>
       <c r="C2622">
-        <v>5570</v>
+        <v>5780</v>
       </c>
       <c r="D2622" t="s">
         <v>2624</v>
@@ -46022,7 +46022,7 @@
         <v>30</v>
       </c>
       <c r="C2623">
-        <v>5620</v>
+        <v>5860</v>
       </c>
       <c r="D2623" t="s">
         <v>2625</v>
@@ -46036,7 +46036,7 @@
         <v>31</v>
       </c>
       <c r="C2624">
-        <v>5660</v>
+        <v>5940</v>
       </c>
       <c r="D2624" t="s">
         <v>2626</v>
@@ -46050,7 +46050,7 @@
         <v>32</v>
       </c>
       <c r="C2625">
-        <v>5690</v>
+        <v>6030</v>
       </c>
       <c r="D2625" t="s">
         <v>2627</v>
@@ -46064,7 +46064,7 @@
         <v>33</v>
       </c>
       <c r="C2626">
-        <v>5700</v>
+        <v>6110</v>
       </c>
       <c r="D2626" t="s">
         <v>2628</v>
@@ -46078,7 +46078,7 @@
         <v>34</v>
       </c>
       <c r="C2627">
-        <v>5700</v>
+        <v>6180</v>
       </c>
       <c r="D2627" t="s">
         <v>2629</v>
@@ -46092,7 +46092,7 @@
         <v>35</v>
       </c>
       <c r="C2628">
-        <v>5710</v>
+        <v>6230</v>
       </c>
       <c r="D2628" t="s">
         <v>2630</v>
@@ -46106,7 +46106,7 @@
         <v>36</v>
       </c>
       <c r="C2629">
-        <v>5710</v>
+        <v>6270</v>
       </c>
       <c r="D2629" t="s">
         <v>2631</v>
@@ -46120,7 +46120,7 @@
         <v>37</v>
       </c>
       <c r="C2630">
-        <v>5710</v>
+        <v>6290</v>
       </c>
       <c r="D2630" t="s">
         <v>2632</v>
@@ -46134,7 +46134,7 @@
         <v>38</v>
       </c>
       <c r="C2631">
-        <v>5700</v>
+        <v>6300</v>
       </c>
       <c r="D2631" t="s">
         <v>2633</v>
@@ -46148,7 +46148,7 @@
         <v>39</v>
       </c>
       <c r="C2632">
-        <v>5680</v>
+        <v>6300</v>
       </c>
       <c r="D2632" t="s">
         <v>2634</v>
@@ -46162,7 +46162,7 @@
         <v>40</v>
       </c>
       <c r="C2633">
-        <v>5660</v>
+        <v>6300</v>
       </c>
       <c r="D2633" t="s">
         <v>2635</v>
@@ -46176,7 +46176,7 @@
         <v>41</v>
       </c>
       <c r="C2634">
-        <v>5620</v>
+        <v>6300</v>
       </c>
       <c r="D2634" t="s">
         <v>2636</v>
@@ -46190,7 +46190,7 @@
         <v>42</v>
       </c>
       <c r="C2635">
-        <v>5580</v>
+        <v>6300</v>
       </c>
       <c r="D2635" t="s">
         <v>2637</v>
@@ -46204,7 +46204,7 @@
         <v>43</v>
       </c>
       <c r="C2636">
-        <v>5540</v>
+        <v>6300</v>
       </c>
       <c r="D2636" t="s">
         <v>2638</v>
@@ -46218,7 +46218,7 @@
         <v>44</v>
       </c>
       <c r="C2637">
-        <v>5490</v>
+        <v>6290</v>
       </c>
       <c r="D2637" t="s">
         <v>2639</v>
@@ -46232,7 +46232,7 @@
         <v>45</v>
       </c>
       <c r="C2638">
-        <v>5450</v>
+        <v>6260</v>
       </c>
       <c r="D2638" t="s">
         <v>2640</v>
@@ -46246,7 +46246,7 @@
         <v>46</v>
       </c>
       <c r="C2639">
-        <v>5400</v>
+        <v>6230</v>
       </c>
       <c r="D2639" t="s">
         <v>2641</v>
@@ -46260,7 +46260,7 @@
         <v>47</v>
       </c>
       <c r="C2640">
-        <v>5360</v>
+        <v>6210</v>
       </c>
       <c r="D2640" t="s">
         <v>2642</v>
@@ -46274,7 +46274,7 @@
         <v>48</v>
       </c>
       <c r="C2641">
-        <v>5320</v>
+        <v>6200</v>
       </c>
       <c r="D2641" t="s">
         <v>2643</v>
@@ -46288,7 +46288,7 @@
         <v>49</v>
       </c>
       <c r="C2642">
-        <v>5280</v>
+        <v>6190</v>
       </c>
       <c r="D2642" t="s">
         <v>2644</v>
@@ -46302,7 +46302,7 @@
         <v>50</v>
       </c>
       <c r="C2643">
-        <v>5250</v>
+        <v>6180</v>
       </c>
       <c r="D2643" t="s">
         <v>2645</v>
@@ -46316,7 +46316,7 @@
         <v>51</v>
       </c>
       <c r="C2644">
-        <v>5230</v>
+        <v>6170</v>
       </c>
       <c r="D2644" t="s">
         <v>2646</v>
@@ -46330,7 +46330,7 @@
         <v>52</v>
       </c>
       <c r="C2645">
-        <v>5220</v>
+        <v>6160</v>
       </c>
       <c r="D2645" t="s">
         <v>2647</v>
@@ -46344,7 +46344,7 @@
         <v>53</v>
       </c>
       <c r="C2646">
-        <v>5220</v>
+        <v>6150</v>
       </c>
       <c r="D2646" t="s">
         <v>2648</v>
@@ -46358,7 +46358,7 @@
         <v>54</v>
       </c>
       <c r="C2647">
-        <v>5220</v>
+        <v>6140</v>
       </c>
       <c r="D2647" t="s">
         <v>2649</v>
@@ -46372,7 +46372,7 @@
         <v>55</v>
       </c>
       <c r="C2648">
-        <v>5240</v>
+        <v>6140</v>
       </c>
       <c r="D2648" t="s">
         <v>2650</v>
@@ -46386,7 +46386,7 @@
         <v>56</v>
       </c>
       <c r="C2649">
-        <v>5260</v>
+        <v>6140</v>
       </c>
       <c r="D2649" t="s">
         <v>2651</v>
@@ -46400,7 +46400,7 @@
         <v>57</v>
       </c>
       <c r="C2650">
-        <v>5290</v>
+        <v>6140</v>
       </c>
       <c r="D2650" t="s">
         <v>2652</v>
@@ -46414,7 +46414,7 @@
         <v>58</v>
       </c>
       <c r="C2651">
-        <v>5320</v>
+        <v>6140</v>
       </c>
       <c r="D2651" t="s">
         <v>2653</v>
@@ -46428,7 +46428,7 @@
         <v>59</v>
       </c>
       <c r="C2652">
-        <v>5350</v>
+        <v>6140</v>
       </c>
       <c r="D2652" t="s">
         <v>2654</v>
@@ -46442,7 +46442,7 @@
         <v>60</v>
       </c>
       <c r="C2653">
-        <v>5370</v>
+        <v>6140</v>
       </c>
       <c r="D2653" t="s">
         <v>2655</v>
@@ -46456,7 +46456,7 @@
         <v>61</v>
       </c>
       <c r="C2654">
-        <v>5390</v>
+        <v>6140</v>
       </c>
       <c r="D2654" t="s">
         <v>2656</v>
@@ -46470,7 +46470,7 @@
         <v>62</v>
       </c>
       <c r="C2655">
-        <v>5420</v>
+        <v>6160</v>
       </c>
       <c r="D2655" t="s">
         <v>2657</v>
@@ -46484,7 +46484,7 @@
         <v>63</v>
       </c>
       <c r="C2656">
-        <v>5480</v>
+        <v>6180</v>
       </c>
       <c r="D2656" t="s">
         <v>2658</v>
@@ -46498,7 +46498,7 @@
         <v>64</v>
       </c>
       <c r="C2657">
-        <v>5560</v>
+        <v>6220</v>
       </c>
       <c r="D2657" t="s">
         <v>2659</v>
@@ -46512,7 +46512,7 @@
         <v>65</v>
       </c>
       <c r="C2658">
-        <v>5660</v>
+        <v>6280</v>
       </c>
       <c r="D2658" t="s">
         <v>2660</v>
@@ -46526,7 +46526,7 @@
         <v>66</v>
       </c>
       <c r="C2659">
-        <v>5760</v>
+        <v>6340</v>
       </c>
       <c r="D2659" t="s">
         <v>2661</v>
@@ -46540,7 +46540,7 @@
         <v>67</v>
       </c>
       <c r="C2660">
-        <v>5870</v>
+        <v>6410</v>
       </c>
       <c r="D2660" t="s">
         <v>2662</v>
@@ -46554,7 +46554,7 @@
         <v>68</v>
       </c>
       <c r="C2661">
-        <v>5970</v>
+        <v>6490</v>
       </c>
       <c r="D2661" t="s">
         <v>2663</v>
@@ -46568,7 +46568,7 @@
         <v>69</v>
       </c>
       <c r="C2662">
-        <v>6080</v>
+        <v>6580</v>
       </c>
       <c r="D2662" t="s">
         <v>2664</v>
@@ -46582,7 +46582,7 @@
         <v>70</v>
       </c>
       <c r="C2663">
-        <v>6180</v>
+        <v>6660</v>
       </c>
       <c r="D2663" t="s">
         <v>2665</v>
@@ -46596,7 +46596,7 @@
         <v>71</v>
       </c>
       <c r="C2664">
-        <v>6260</v>
+        <v>6740</v>
       </c>
       <c r="D2664" t="s">
         <v>2666</v>
@@ -46610,7 +46610,7 @@
         <v>72</v>
       </c>
       <c r="C2665">
-        <v>6340</v>
+        <v>6800</v>
       </c>
       <c r="D2665" t="s">
         <v>2667</v>
@@ -46624,7 +46624,7 @@
         <v>73</v>
       </c>
       <c r="C2666">
-        <v>6410</v>
+        <v>6860</v>
       </c>
       <c r="D2666" t="s">
         <v>2668</v>
@@ -46638,7 +46638,7 @@
         <v>74</v>
       </c>
       <c r="C2667">
-        <v>6500</v>
+        <v>6900</v>
       </c>
       <c r="D2667" t="s">
         <v>2669</v>
@@ -46652,7 +46652,7 @@
         <v>75</v>
       </c>
       <c r="C2668">
-        <v>6610</v>
+        <v>6960</v>
       </c>
       <c r="D2668" t="s">
         <v>2670</v>
@@ -46666,7 +46666,7 @@
         <v>76</v>
       </c>
       <c r="C2669">
-        <v>6760</v>
+        <v>6980</v>
       </c>
       <c r="D2669" t="s">
         <v>2671</v>
@@ -46680,7 +46680,7 @@
         <v>77</v>
       </c>
       <c r="C2670">
-        <v>6910</v>
+        <v>7050</v>
       </c>
       <c r="D2670" t="s">
         <v>2672</v>
@@ -46694,7 +46694,7 @@
         <v>78</v>
       </c>
       <c r="C2671">
-        <v>7020</v>
+        <v>7090</v>
       </c>
       <c r="D2671" t="s">
         <v>2673</v>
@@ -46708,7 +46708,7 @@
         <v>79</v>
       </c>
       <c r="C2672">
-        <v>7080</v>
+        <v>7100</v>
       </c>
       <c r="D2672" t="s">
         <v>2674</v>
@@ -46722,7 +46722,7 @@
         <v>80</v>
       </c>
       <c r="C2673">
-        <v>7080</v>
+        <v>7140</v>
       </c>
       <c r="D2673" t="s">
         <v>2675</v>
@@ -46736,7 +46736,7 @@
         <v>81</v>
       </c>
       <c r="C2674">
-        <v>7030</v>
+        <v>7150</v>
       </c>
       <c r="D2674" t="s">
         <v>2676</v>
@@ -46750,7 +46750,7 @@
         <v>82</v>
       </c>
       <c r="C2675">
-        <v>6970</v>
+        <v>7130</v>
       </c>
       <c r="D2675" t="s">
         <v>2677</v>
@@ -46764,7 +46764,7 @@
         <v>83</v>
       </c>
       <c r="C2676">
-        <v>6920</v>
+        <v>7110</v>
       </c>
       <c r="D2676" t="s">
         <v>2678</v>
@@ -46778,7 +46778,7 @@
         <v>84</v>
       </c>
       <c r="C2677">
-        <v>6870</v>
+        <v>7080</v>
       </c>
       <c r="D2677" t="s">
         <v>2679</v>
@@ -46792,7 +46792,7 @@
         <v>85</v>
       </c>
       <c r="C2678">
-        <v>6820</v>
+        <v>6990</v>
       </c>
       <c r="D2678" t="s">
         <v>2680</v>
@@ -46806,7 +46806,7 @@
         <v>86</v>
       </c>
       <c r="C2679">
-        <v>6740</v>
+        <v>6890</v>
       </c>
       <c r="D2679" t="s">
         <v>2681</v>
@@ -46820,7 +46820,7 @@
         <v>87</v>
       </c>
       <c r="C2680">
-        <v>6640</v>
+        <v>6790</v>
       </c>
       <c r="D2680" t="s">
         <v>2682</v>
@@ -46834,7 +46834,7 @@
         <v>88</v>
       </c>
       <c r="C2681">
-        <v>6500</v>
+        <v>6670</v>
       </c>
       <c r="D2681" t="s">
         <v>2683</v>
@@ -46848,7 +46848,7 @@
         <v>89</v>
       </c>
       <c r="C2682">
-        <v>6350</v>
+        <v>6550</v>
       </c>
       <c r="D2682" t="s">
         <v>2684</v>
@@ -46862,7 +46862,7 @@
         <v>90</v>
       </c>
       <c r="C2683">
-        <v>6200</v>
+        <v>6430</v>
       </c>
       <c r="D2683" t="s">
         <v>2685</v>
@@ -46876,7 +46876,7 @@
         <v>91</v>
       </c>
       <c r="C2684">
-        <v>6060</v>
+        <v>6300</v>
       </c>
       <c r="D2684" t="s">
         <v>2686</v>
@@ -46890,7 +46890,7 @@
         <v>92</v>
       </c>
       <c r="C2685">
-        <v>5940</v>
+        <v>6180</v>
       </c>
       <c r="D2685" t="s">
         <v>2687</v>
@@ -46904,7 +46904,7 @@
         <v>93</v>
       </c>
       <c r="C2686">
-        <v>5830</v>
+        <v>6050</v>
       </c>
       <c r="D2686" t="s">
         <v>2688</v>
@@ -46918,7 +46918,7 @@
         <v>94</v>
       </c>
       <c r="C2687">
-        <v>5720</v>
+        <v>5930</v>
       </c>
       <c r="D2687" t="s">
         <v>2689</v>
@@ -46932,7 +46932,7 @@
         <v>95</v>
       </c>
       <c r="C2688">
-        <v>5630</v>
+        <v>5830</v>
       </c>
       <c r="D2688" t="s">
         <v>2690</v>
@@ -46946,7 +46946,7 @@
         <v>96</v>
       </c>
       <c r="C2689">
-        <v>5540</v>
+        <v>5730</v>
       </c>
       <c r="D2689" t="s">
         <v>2691</v>
@@ -46960,7 +46960,7 @@
         <v>1</v>
       </c>
       <c r="C2690">
-        <v>5460</v>
+        <v>5610</v>
       </c>
       <c r="D2690" t="s">
         <v>2692</v>
@@ -46974,7 +46974,7 @@
         <v>2</v>
       </c>
       <c r="C2691">
-        <v>5390</v>
+        <v>5530</v>
       </c>
       <c r="D2691" t="s">
         <v>2693</v>
@@ -46988,7 +46988,7 @@
         <v>3</v>
       </c>
       <c r="C2692">
-        <v>5320</v>
+        <v>5460</v>
       </c>
       <c r="D2692" t="s">
         <v>2694</v>
@@ -47002,7 +47002,7 @@
         <v>4</v>
       </c>
       <c r="C2693">
-        <v>5260</v>
+        <v>5390</v>
       </c>
       <c r="D2693" t="s">
         <v>2695</v>
@@ -47016,7 +47016,7 @@
         <v>5</v>
       </c>
       <c r="C2694">
-        <v>5210</v>
+        <v>5330</v>
       </c>
       <c r="D2694" t="s">
         <v>2696</v>
@@ -47030,7 +47030,7 @@
         <v>6</v>
       </c>
       <c r="C2695">
-        <v>5160</v>
+        <v>5280</v>
       </c>
       <c r="D2695" t="s">
         <v>2697</v>
@@ -47044,7 +47044,7 @@
         <v>7</v>
       </c>
       <c r="C2696">
-        <v>5120</v>
+        <v>5240</v>
       </c>
       <c r="D2696" t="s">
         <v>2698</v>
@@ -47058,7 +47058,7 @@
         <v>8</v>
       </c>
       <c r="C2697">
-        <v>5090</v>
+        <v>5210</v>
       </c>
       <c r="D2697" t="s">
         <v>2699</v>
@@ -47072,7 +47072,7 @@
         <v>9</v>
       </c>
       <c r="C2698">
-        <v>5070</v>
+        <v>5180</v>
       </c>
       <c r="D2698" t="s">
         <v>2700</v>
@@ -47086,7 +47086,7 @@
         <v>10</v>
       </c>
       <c r="C2699">
-        <v>5050</v>
+        <v>5110</v>
       </c>
       <c r="D2699" t="s">
         <v>2701</v>
@@ -47100,7 +47100,7 @@
         <v>11</v>
       </c>
       <c r="C2700">
-        <v>5020</v>
+        <v>5060</v>
       </c>
       <c r="D2700" t="s">
         <v>2702</v>
@@ -47128,7 +47128,7 @@
         <v>17</v>
       </c>
       <c r="C2702">
-        <v>4980</v>
+        <v>5000</v>
       </c>
       <c r="D2702" t="s">
         <v>2704</v>
@@ -47142,7 +47142,7 @@
         <v>18</v>
       </c>
       <c r="C2703">
-        <v>4970</v>
+        <v>5020</v>
       </c>
       <c r="D2703" t="s">
         <v>2705</v>
@@ -47156,7 +47156,7 @@
         <v>19</v>
       </c>
       <c r="C2704">
-        <v>4970</v>
+        <v>5050</v>
       </c>
       <c r="D2704" t="s">
         <v>2706</v>
@@ -47170,7 +47170,7 @@
         <v>20</v>
       </c>
       <c r="C2705">
-        <v>4980</v>
+        <v>5080</v>
       </c>
       <c r="D2705" t="s">
         <v>2707</v>
@@ -47184,7 +47184,7 @@
         <v>21</v>
       </c>
       <c r="C2706">
-        <v>5000</v>
+        <v>5120</v>
       </c>
       <c r="D2706" t="s">
         <v>2708</v>
@@ -47198,7 +47198,7 @@
         <v>22</v>
       </c>
       <c r="C2707">
-        <v>5020</v>
+        <v>5140</v>
       </c>
       <c r="D2707" t="s">
         <v>2709</v>
@@ -47212,7 +47212,7 @@
         <v>23</v>
       </c>
       <c r="C2708">
-        <v>5050</v>
+        <v>5160</v>
       </c>
       <c r="D2708" t="s">
         <v>2710</v>
@@ -47226,7 +47226,7 @@
         <v>24</v>
       </c>
       <c r="C2709">
-        <v>5070</v>
+        <v>5180</v>
       </c>
       <c r="D2709" t="s">
         <v>2711</v>
@@ -47240,7 +47240,7 @@
         <v>25</v>
       </c>
       <c r="C2710">
-        <v>5090</v>
+        <v>5190</v>
       </c>
       <c r="D2710" t="s">
         <v>2712</v>
@@ -47254,7 +47254,7 @@
         <v>26</v>
       </c>
       <c r="C2711">
-        <v>5100</v>
+        <v>5210</v>
       </c>
       <c r="D2711" t="s">
         <v>2713</v>
@@ -47268,7 +47268,7 @@
         <v>27</v>
       </c>
       <c r="C2712">
-        <v>5100</v>
+        <v>5220</v>
       </c>
       <c r="D2712" t="s">
         <v>2714</v>
@@ -47282,7 +47282,7 @@
         <v>28</v>
       </c>
       <c r="C2713">
-        <v>5090</v>
+        <v>5240</v>
       </c>
       <c r="D2713" t="s">
         <v>2715</v>
@@ -47296,7 +47296,7 @@
         <v>29</v>
       </c>
       <c r="C2714">
-        <v>5080</v>
+        <v>5250</v>
       </c>
       <c r="D2714" t="s">
         <v>2716</v>
@@ -47310,7 +47310,7 @@
         <v>30</v>
       </c>
       <c r="C2715">
-        <v>5080</v>
+        <v>5280</v>
       </c>
       <c r="D2715" t="s">
         <v>2717</v>
@@ -47324,7 +47324,7 @@
         <v>31</v>
       </c>
       <c r="C2716">
-        <v>5110</v>
+        <v>5320</v>
       </c>
       <c r="D2716" t="s">
         <v>2718</v>
@@ -47338,7 +47338,7 @@
         <v>32</v>
       </c>
       <c r="C2717">
-        <v>5160</v>
+        <v>5380</v>
       </c>
       <c r="D2717" t="s">
         <v>2719</v>
@@ -47352,7 +47352,7 @@
         <v>33</v>
       </c>
       <c r="C2718">
-        <v>5230</v>
+        <v>5450</v>
       </c>
       <c r="D2718" t="s">
         <v>2720</v>
@@ -47366,7 +47366,7 @@
         <v>34</v>
       </c>
       <c r="C2719">
-        <v>5280</v>
+        <v>5470</v>
       </c>
       <c r="D2719" t="s">
         <v>2721</v>
@@ -47380,7 +47380,7 @@
         <v>35</v>
       </c>
       <c r="C2720">
-        <v>5300</v>
+        <v>5480</v>
       </c>
       <c r="D2720" t="s">
         <v>2722</v>
@@ -47394,7 +47394,7 @@
         <v>36</v>
       </c>
       <c r="C2721">
-        <v>5290</v>
+        <v>5490</v>
       </c>
       <c r="D2721" t="s">
         <v>2723</v>
@@ -47408,7 +47408,7 @@
         <v>37</v>
       </c>
       <c r="C2722">
-        <v>5250</v>
+        <v>5500</v>
       </c>
       <c r="D2722" t="s">
         <v>2724</v>
@@ -47422,7 +47422,7 @@
         <v>38</v>
       </c>
       <c r="C2723">
-        <v>5210</v>
+        <v>5520</v>
       </c>
       <c r="D2723" t="s">
         <v>2725</v>
@@ -47436,7 +47436,7 @@
         <v>39</v>
       </c>
       <c r="C2724">
-        <v>5180</v>
+        <v>5550</v>
       </c>
       <c r="D2724" t="s">
         <v>2726</v>
@@ -47450,7 +47450,7 @@
         <v>40</v>
       </c>
       <c r="C2725">
-        <v>5150</v>
+        <v>5550</v>
       </c>
       <c r="D2725" t="s">
         <v>2727</v>
@@ -47464,7 +47464,7 @@
         <v>41</v>
       </c>
       <c r="C2726">
-        <v>5120</v>
+        <v>5550</v>
       </c>
       <c r="D2726" t="s">
         <v>2728</v>
@@ -47478,7 +47478,7 @@
         <v>42</v>
       </c>
       <c r="C2727">
-        <v>5090</v>
+        <v>5530</v>
       </c>
       <c r="D2727" t="s">
         <v>2729</v>
@@ -47492,7 +47492,7 @@
         <v>43</v>
       </c>
       <c r="C2728">
-        <v>5050</v>
+        <v>5520</v>
       </c>
       <c r="D2728" t="s">
         <v>2730</v>
@@ -47506,7 +47506,7 @@
         <v>44</v>
       </c>
       <c r="C2729">
-        <v>5000</v>
+        <v>5500</v>
       </c>
       <c r="D2729" t="s">
         <v>2731</v>
@@ -47520,7 +47520,7 @@
         <v>45</v>
       </c>
       <c r="C2730">
-        <v>4950</v>
+        <v>5480</v>
       </c>
       <c r="D2730" t="s">
         <v>2732</v>
@@ -47534,7 +47534,7 @@
         <v>46</v>
       </c>
       <c r="C2731">
-        <v>4900</v>
+        <v>5490</v>
       </c>
       <c r="D2731" t="s">
         <v>2733</v>
@@ -47548,7 +47548,7 @@
         <v>47</v>
       </c>
       <c r="C2732">
-        <v>4850</v>
+        <v>5460</v>
       </c>
       <c r="D2732" t="s">
         <v>2734</v>
@@ -47562,7 +47562,7 @@
         <v>48</v>
       </c>
       <c r="C2733">
-        <v>4810</v>
+        <v>5410</v>
       </c>
       <c r="D2733" t="s">
         <v>2735</v>
@@ -47576,7 +47576,7 @@
         <v>49</v>
       </c>
       <c r="C2734">
-        <v>4780</v>
+        <v>5370</v>
       </c>
       <c r="D2734" t="s">
         <v>2736</v>
@@ -47590,7 +47590,7 @@
         <v>50</v>
       </c>
       <c r="C2735">
-        <v>4750</v>
+        <v>5330</v>
       </c>
       <c r="D2735" t="s">
         <v>2737</v>
@@ -47604,7 +47604,7 @@
         <v>51</v>
       </c>
       <c r="C2736">
-        <v>4730</v>
+        <v>5310</v>
       </c>
       <c r="D2736" t="s">
         <v>2738</v>
@@ -47618,7 +47618,7 @@
         <v>52</v>
       </c>
       <c r="C2737">
-        <v>4720</v>
+        <v>5310</v>
       </c>
       <c r="D2737" t="s">
         <v>2739</v>
@@ -47632,7 +47632,7 @@
         <v>53</v>
       </c>
       <c r="C2738">
-        <v>4720</v>
+        <v>5330</v>
       </c>
       <c r="D2738" t="s">
         <v>2740</v>
@@ -47646,7 +47646,7 @@
         <v>54</v>
       </c>
       <c r="C2739">
-        <v>4710</v>
+        <v>5330</v>
       </c>
       <c r="D2739" t="s">
         <v>2741</v>
@@ -47660,7 +47660,7 @@
         <v>55</v>
       </c>
       <c r="C2740">
-        <v>4690</v>
+        <v>5310</v>
       </c>
       <c r="D2740" t="s">
         <v>2742</v>
@@ -47674,7 +47674,7 @@
         <v>56</v>
       </c>
       <c r="C2741">
-        <v>4660</v>
+        <v>5280</v>
       </c>
       <c r="D2741" t="s">
         <v>2743</v>
@@ -47688,7 +47688,7 @@
         <v>57</v>
       </c>
       <c r="C2742">
-        <v>4630</v>
+        <v>5240</v>
       </c>
       <c r="D2742" t="s">
         <v>2744</v>
@@ -47702,7 +47702,7 @@
         <v>58</v>
       </c>
       <c r="C2743">
-        <v>4610</v>
+        <v>5210</v>
       </c>
       <c r="D2743" t="s">
         <v>2745</v>
@@ -47716,7 +47716,7 @@
         <v>59</v>
       </c>
       <c r="C2744">
-        <v>4600</v>
+        <v>5210</v>
       </c>
       <c r="D2744" t="s">
         <v>2746</v>
@@ -47730,7 +47730,7 @@
         <v>60</v>
       </c>
       <c r="C2745">
-        <v>4590</v>
+        <v>5230</v>
       </c>
       <c r="D2745" t="s">
         <v>2747</v>
@@ -47744,7 +47744,7 @@
         <v>61</v>
       </c>
       <c r="C2746">
-        <v>4610</v>
+        <v>5270</v>
       </c>
       <c r="D2746" t="s">
         <v>2748</v>
@@ -47758,7 +47758,7 @@
         <v>62</v>
       </c>
       <c r="C2747">
-        <v>4630</v>
+        <v>5320</v>
       </c>
       <c r="D2747" t="s">
         <v>2749</v>
@@ -47772,7 +47772,7 @@
         <v>63</v>
       </c>
       <c r="C2748">
-        <v>4680</v>
+        <v>5370</v>
       </c>
       <c r="D2748" t="s">
         <v>2750</v>
@@ -47786,7 +47786,7 @@
         <v>64</v>
       </c>
       <c r="C2749">
-        <v>4750</v>
+        <v>5420</v>
       </c>
       <c r="D2749" t="s">
         <v>2751</v>
@@ -47800,7 +47800,7 @@
         <v>65</v>
       </c>
       <c r="C2750">
-        <v>4830</v>
+        <v>5480</v>
       </c>
       <c r="D2750" t="s">
         <v>2752</v>
@@ -47814,7 +47814,7 @@
         <v>66</v>
       </c>
       <c r="C2751">
-        <v>4920</v>
+        <v>5550</v>
       </c>
       <c r="D2751" t="s">
         <v>2753</v>
@@ -47828,7 +47828,7 @@
         <v>67</v>
       </c>
       <c r="C2752">
-        <v>5010</v>
+        <v>5620</v>
       </c>
       <c r="D2752" t="s">
         <v>2754</v>
@@ -47842,7 +47842,7 @@
         <v>68</v>
       </c>
       <c r="C2753">
-        <v>5100</v>
+        <v>5690</v>
       </c>
       <c r="D2753" t="s">
         <v>2755</v>
@@ -47856,7 +47856,7 @@
         <v>69</v>
       </c>
       <c r="C2754">
-        <v>5190</v>
+        <v>5770</v>
       </c>
       <c r="D2754" t="s">
         <v>2756</v>
@@ -47870,7 +47870,7 @@
         <v>70</v>
       </c>
       <c r="C2755">
-        <v>5280</v>
+        <v>5840</v>
       </c>
       <c r="D2755" t="s">
         <v>2757</v>
@@ -47884,7 +47884,7 @@
         <v>71</v>
       </c>
       <c r="C2756">
-        <v>5380</v>
+        <v>5910</v>
       </c>
       <c r="D2756" t="s">
         <v>2758</v>
@@ -47898,7 +47898,7 @@
         <v>72</v>
       </c>
       <c r="C2757">
-        <v>5480</v>
+        <v>5980</v>
       </c>
       <c r="D2757" t="s">
         <v>2759</v>
@@ -47912,7 +47912,7 @@
         <v>73</v>
       </c>
       <c r="C2758">
-        <v>5590</v>
+        <v>6040</v>
       </c>
       <c r="D2758" t="s">
         <v>2760</v>
@@ -47926,7 +47926,7 @@
         <v>74</v>
       </c>
       <c r="C2759">
-        <v>5690</v>
+        <v>6110</v>
       </c>
       <c r="D2759" t="s">
         <v>2761</v>
@@ -47940,7 +47940,7 @@
         <v>75</v>
       </c>
       <c r="C2760">
-        <v>5780</v>
+        <v>6180</v>
       </c>
       <c r="D2760" t="s">
         <v>2762</v>
@@ -47954,7 +47954,7 @@
         <v>76</v>
       </c>
       <c r="C2761">
-        <v>5870</v>
+        <v>6260</v>
       </c>
       <c r="D2761" t="s">
         <v>2763</v>
@@ -47968,7 +47968,7 @@
         <v>77</v>
       </c>
       <c r="C2762">
-        <v>5950</v>
+        <v>6340</v>
       </c>
       <c r="D2762" t="s">
         <v>2764</v>
@@ -47982,7 +47982,7 @@
         <v>78</v>
       </c>
       <c r="C2763">
-        <v>6040</v>
+        <v>6420</v>
       </c>
       <c r="D2763" t="s">
         <v>2765</v>
@@ -47996,7 +47996,7 @@
         <v>79</v>
       </c>
       <c r="C2764">
-        <v>6160</v>
+        <v>6500</v>
       </c>
       <c r="D2764" t="s">
         <v>2766</v>
@@ -48010,7 +48010,7 @@
         <v>80</v>
       </c>
       <c r="C2765">
-        <v>6290</v>
+        <v>6550</v>
       </c>
       <c r="D2765" t="s">
         <v>2767</v>
@@ -48024,7 +48024,7 @@
         <v>81</v>
       </c>
       <c r="C2766">
-        <v>6440</v>
+        <v>6580</v>
       </c>
       <c r="D2766" t="s">
         <v>2768</v>
@@ -48038,7 +48038,7 @@
         <v>82</v>
       </c>
       <c r="C2767">
-        <v>6530</v>
+        <v>6590</v>
       </c>
       <c r="D2767" t="s">
         <v>2769</v>
@@ -48052,7 +48052,7 @@
         <v>83</v>
       </c>
       <c r="C2768">
-        <v>6560</v>
+        <v>6600</v>
       </c>
       <c r="D2768" t="s">
         <v>2770</v>
@@ -48066,7 +48066,7 @@
         <v>84</v>
       </c>
       <c r="C2769">
-        <v>6530</v>
+        <v>6600</v>
       </c>
       <c r="D2769" t="s">
         <v>2771</v>
@@ -48080,7 +48080,7 @@
         <v>85</v>
       </c>
       <c r="C2770">
-        <v>6450</v>
+        <v>6580</v>
       </c>
       <c r="D2770" t="s">
         <v>2772</v>
@@ -48094,7 +48094,7 @@
         <v>86</v>
       </c>
       <c r="C2771">
-        <v>6360</v>
+        <v>6520</v>
       </c>
       <c r="D2771" t="s">
         <v>2773</v>
@@ -48108,7 +48108,7 @@
         <v>87</v>
       </c>
       <c r="C2772">
-        <v>6260</v>
+        <v>6420</v>
       </c>
       <c r="D2772" t="s">
         <v>2774</v>
@@ -48122,7 +48122,7 @@
         <v>88</v>
       </c>
       <c r="C2773">
-        <v>6160</v>
+        <v>6320</v>
       </c>
       <c r="D2773" t="s">
         <v>2775</v>
@@ -48136,7 +48136,7 @@
         <v>89</v>
       </c>
       <c r="C2774">
-        <v>6050</v>
+        <v>6210</v>
       </c>
       <c r="D2774" t="s">
         <v>2776</v>
@@ -48150,7 +48150,7 @@
         <v>90</v>
       </c>
       <c r="C2775">
-        <v>5940</v>
+        <v>6090</v>
       </c>
       <c r="D2775" t="s">
         <v>2777</v>
@@ -48164,7 +48164,7 @@
         <v>91</v>
       </c>
       <c r="C2776">
-        <v>5830</v>
+        <v>5970</v>
       </c>
       <c r="D2776" t="s">
         <v>2778</v>
@@ -48178,7 +48178,7 @@
         <v>92</v>
       </c>
       <c r="C2777">
-        <v>5710</v>
+        <v>5860</v>
       </c>
       <c r="D2777" t="s">
         <v>2779</v>
@@ -48192,7 +48192,7 @@
         <v>93</v>
       </c>
       <c r="C2778">
-        <v>5600</v>
+        <v>5740</v>
       </c>
       <c r="D2778" t="s">
         <v>2780</v>
@@ -48206,7 +48206,7 @@
         <v>94</v>
       </c>
       <c r="C2779">
-        <v>5490</v>
+        <v>5640</v>
       </c>
       <c r="D2779" t="s">
         <v>2781</v>
@@ -48220,7 +48220,7 @@
         <v>95</v>
       </c>
       <c r="C2780">
-        <v>5400</v>
+        <v>5550</v>
       </c>
       <c r="D2780" t="s">
         <v>2782</v>
@@ -48234,7 +48234,7 @@
         <v>96</v>
       </c>
       <c r="C2781">
-        <v>5320</v>
+        <v>5470</v>
       </c>
       <c r="D2781" t="s">
         <v>2783</v>
@@ -48248,7 +48248,7 @@
         <v>1</v>
       </c>
       <c r="C2782">
-        <v>5230</v>
+        <v>5420</v>
       </c>
       <c r="D2782" t="s">
         <v>2784</v>
@@ -48262,7 +48262,7 @@
         <v>2</v>
       </c>
       <c r="C2783">
-        <v>5160</v>
+        <v>5360</v>
       </c>
       <c r="D2783" t="s">
         <v>2785</v>
@@ -48276,7 +48276,7 @@
         <v>3</v>
       </c>
       <c r="C2784">
-        <v>5110</v>
+        <v>5300</v>
       </c>
       <c r="D2784" t="s">
         <v>2786</v>
@@ -48290,7 +48290,7 @@
         <v>4</v>
       </c>
       <c r="C2785">
-        <v>5060</v>
+        <v>5250</v>
       </c>
       <c r="D2785" t="s">
         <v>2787</v>
@@ -48304,7 +48304,7 @@
         <v>5</v>
       </c>
       <c r="C2786">
-        <v>5020</v>
+        <v>5200</v>
       </c>
       <c r="D2786" t="s">
         <v>2788</v>
@@ -48318,7 +48318,7 @@
         <v>6</v>
       </c>
       <c r="C2787">
-        <v>4990</v>
+        <v>5160</v>
       </c>
       <c r="D2787" t="s">
         <v>2789</v>
@@ -48332,7 +48332,7 @@
         <v>7</v>
       </c>
       <c r="C2788">
-        <v>4960</v>
+        <v>5130</v>
       </c>
       <c r="D2788" t="s">
         <v>2790</v>
@@ -48346,7 +48346,7 @@
         <v>8</v>
       </c>
       <c r="C2789">
-        <v>4930</v>
+        <v>5110</v>
       </c>
       <c r="D2789" t="s">
         <v>2791</v>
@@ -48360,7 +48360,7 @@
         <v>9</v>
       </c>
       <c r="C2790">
-        <v>4910</v>
+        <v>5100</v>
       </c>
       <c r="D2790" t="s">
         <v>2792</v>
@@ -48374,7 +48374,7 @@
         <v>10</v>
       </c>
       <c r="C2791">
-        <v>4900</v>
+        <v>5080</v>
       </c>
       <c r="D2791" t="s">
         <v>2793</v>
@@ -48388,7 +48388,7 @@
         <v>11</v>
       </c>
       <c r="C2792">
-        <v>4890</v>
+        <v>5050</v>
       </c>
       <c r="D2792" t="s">
         <v>2794</v>
@@ -48402,7 +48402,7 @@
         <v>12</v>
       </c>
       <c r="C2793">
-        <v>4890</v>
+        <v>5020</v>
       </c>
       <c r="D2793" t="s">
         <v>2795</v>
@@ -48416,7 +48416,7 @@
         <v>13</v>
       </c>
       <c r="C2794">
-        <v>4890</v>
+        <v>5010</v>
       </c>
       <c r="D2794" t="s">
         <v>2796</v>
@@ -48430,7 +48430,7 @@
         <v>14</v>
       </c>
       <c r="C2795">
-        <v>4900</v>
+        <v>5000</v>
       </c>
       <c r="D2795" t="s">
         <v>2797</v>
@@ -48444,7 +48444,7 @@
         <v>15</v>
       </c>
       <c r="C2796">
-        <v>4900</v>
+        <v>5020</v>
       </c>
       <c r="D2796" t="s">
         <v>2798</v>
@@ -48458,7 +48458,7 @@
         <v>16</v>
       </c>
       <c r="C2797">
-        <v>4910</v>
+        <v>5060</v>
       </c>
       <c r="D2797" t="s">
         <v>2799</v>
@@ -48472,7 +48472,7 @@
         <v>17</v>
       </c>
       <c r="C2798">
-        <v>4920</v>
+        <v>5110</v>
       </c>
       <c r="D2798" t="s">
         <v>2800</v>
@@ -48486,7 +48486,7 @@
         <v>18</v>
       </c>
       <c r="C2799">
-        <v>4940</v>
+        <v>5130</v>
       </c>
       <c r="D2799" t="s">
         <v>2801</v>
@@ -48500,7 +48500,7 @@
         <v>19</v>
       </c>
       <c r="C2800">
-        <v>4980</v>
+        <v>5150</v>
       </c>
       <c r="D2800" t="s">
         <v>2802</v>
@@ -48514,7 +48514,7 @@
         <v>20</v>
       </c>
       <c r="C2801">
-        <v>5020</v>
+        <v>5190</v>
       </c>
       <c r="D2801" t="s">
         <v>2803</v>
@@ -48528,7 +48528,7 @@
         <v>21</v>
       </c>
       <c r="C2802">
-        <v>5080</v>
+        <v>5230</v>
       </c>
       <c r="D2802" t="s">
         <v>2804</v>
@@ -48542,7 +48542,7 @@
         <v>22</v>
       </c>
       <c r="C2803">
-        <v>5160</v>
+        <v>5300</v>
       </c>
       <c r="D2803" t="s">
         <v>2805</v>
@@ -48556,7 +48556,7 @@
         <v>23</v>
       </c>
       <c r="C2804">
-        <v>5270</v>
+        <v>5390</v>
       </c>
       <c r="D2804" t="s">
         <v>2806</v>
@@ -48570,7 +48570,7 @@
         <v>24</v>
       </c>
       <c r="C2805">
-        <v>5400</v>
+        <v>5510</v>
       </c>
       <c r="D2805" t="s">
         <v>2807</v>
@@ -48584,7 +48584,7 @@
         <v>25</v>
       </c>
       <c r="C2806">
-        <v>5550</v>
+        <v>5650</v>
       </c>
       <c r="D2806" t="s">
         <v>2808</v>
@@ -48598,7 +48598,7 @@
         <v>26</v>
       </c>
       <c r="C2807">
-        <v>5710</v>
+        <v>5820</v>
       </c>
       <c r="D2807" t="s">
         <v>2809</v>
@@ -48612,7 +48612,7 @@
         <v>27</v>
       </c>
       <c r="C2808">
-        <v>5890</v>
+        <v>6000</v>
       </c>
       <c r="D2808" t="s">
         <v>2810</v>
@@ -48626,7 +48626,7 @@
         <v>28</v>
       </c>
       <c r="C2809">
-        <v>6080</v>
+        <v>6150</v>
       </c>
       <c r="D2809" t="s">
         <v>2811</v>
@@ -48640,7 +48640,7 @@
         <v>29</v>
       </c>
       <c r="C2810">
-        <v>6280</v>
+        <v>6330</v>
       </c>
       <c r="D2810" t="s">
         <v>2812</v>
@@ -48654,7 +48654,7 @@
         <v>30</v>
       </c>
       <c r="C2811">
-        <v>6470</v>
+        <v>6550</v>
       </c>
       <c r="D2811" t="s">
         <v>2813</v>
@@ -48668,7 +48668,7 @@
         <v>31</v>
       </c>
       <c r="C2812">
-        <v>6640</v>
+        <v>6700</v>
       </c>
       <c r="D2812" t="s">
         <v>2814</v>
@@ -48696,7 +48696,7 @@
         <v>33</v>
       </c>
       <c r="C2814">
-        <v>6940</v>
+        <v>6900</v>
       </c>
       <c r="D2814" t="s">
         <v>2816</v>
@@ -48710,7 +48710,7 @@
         <v>34</v>
       </c>
       <c r="C2815">
-        <v>7040</v>
+        <v>6950</v>
       </c>
       <c r="D2815" t="s">
         <v>2817</v>
@@ -48724,7 +48724,7 @@
         <v>35</v>
       </c>
       <c r="C2816">
-        <v>7100</v>
+        <v>6990</v>
       </c>
       <c r="D2816" t="s">
         <v>2818</v>
@@ -48738,7 +48738,7 @@
         <v>36</v>
       </c>
       <c r="C2817">
-        <v>7110</v>
+        <v>7000</v>
       </c>
       <c r="D2817" t="s">
         <v>2819</v>
@@ -48752,7 +48752,7 @@
         <v>37</v>
       </c>
       <c r="C2818">
-        <v>7090</v>
+        <v>7000</v>
       </c>
       <c r="D2818" t="s">
         <v>2820</v>
@@ -48766,7 +48766,7 @@
         <v>38</v>
       </c>
       <c r="C2819">
-        <v>7060</v>
+        <v>7000</v>
       </c>
       <c r="D2819" t="s">
         <v>2821</v>
@@ -48780,7 +48780,7 @@
         <v>39</v>
       </c>
       <c r="C2820">
-        <v>7020</v>
+        <v>7000</v>
       </c>
       <c r="D2820" t="s">
         <v>2822</v>
@@ -48794,7 +48794,7 @@
         <v>40</v>
       </c>
       <c r="C2821">
-        <v>6970</v>
+        <v>7000</v>
       </c>
       <c r="D2821" t="s">
         <v>2823</v>
@@ -48808,7 +48808,7 @@
         <v>41</v>
       </c>
       <c r="C2822">
-        <v>6910</v>
+        <v>6950</v>
       </c>
       <c r="D2822" t="s">
         <v>2824</v>
@@ -48822,7 +48822,7 @@
         <v>42</v>
       </c>
       <c r="C2823">
-        <v>6840</v>
+        <v>6920</v>
       </c>
       <c r="D2823" t="s">
         <v>2825</v>
@@ -48836,7 +48836,7 @@
         <v>43</v>
       </c>
       <c r="C2824">
-        <v>6760</v>
+        <v>6900</v>
       </c>
       <c r="D2824" t="s">
         <v>2826</v>
@@ -48850,7 +48850,7 @@
         <v>44</v>
       </c>
       <c r="C2825">
-        <v>6670</v>
+        <v>6840</v>
       </c>
       <c r="D2825" t="s">
         <v>2827</v>
@@ -48864,7 +48864,7 @@
         <v>45</v>
       </c>
       <c r="C2826">
-        <v>6570</v>
+        <v>6820</v>
       </c>
       <c r="D2826" t="s">
         <v>2828</v>
@@ -48878,7 +48878,7 @@
         <v>46</v>
       </c>
       <c r="C2827">
-        <v>6480</v>
+        <v>6770</v>
       </c>
       <c r="D2827" t="s">
         <v>2829</v>
@@ -48892,7 +48892,7 @@
         <v>47</v>
       </c>
       <c r="C2828">
-        <v>6390</v>
+        <v>6690</v>
       </c>
       <c r="D2828" t="s">
         <v>2830</v>
@@ -48906,7 +48906,7 @@
         <v>48</v>
       </c>
       <c r="C2829">
-        <v>6320</v>
+        <v>6610</v>
       </c>
       <c r="D2829" t="s">
         <v>2831</v>
@@ -48920,7 +48920,7 @@
         <v>49</v>
       </c>
       <c r="C2830">
-        <v>6260</v>
+        <v>6530</v>
       </c>
       <c r="D2830" t="s">
         <v>2832</v>
@@ -48934,7 +48934,7 @@
         <v>50</v>
       </c>
       <c r="C2831">
-        <v>6210</v>
+        <v>6470</v>
       </c>
       <c r="D2831" t="s">
         <v>2833</v>
@@ -48948,7 +48948,7 @@
         <v>51</v>
       </c>
       <c r="C2832">
-        <v>6180</v>
+        <v>6430</v>
       </c>
       <c r="D2832" t="s">
         <v>2834</v>
@@ -48962,7 +48962,7 @@
         <v>52</v>
       </c>
       <c r="C2833">
-        <v>6170</v>
+        <v>6410</v>
       </c>
       <c r="D2833" t="s">
         <v>2835</v>
@@ -48976,7 +48976,7 @@
         <v>53</v>
       </c>
       <c r="C2834">
-        <v>6170</v>
+        <v>6410</v>
       </c>
       <c r="D2834" t="s">
         <v>2836</v>
@@ -48990,7 +48990,7 @@
         <v>54</v>
       </c>
       <c r="C2835">
-        <v>6160</v>
+        <v>6390</v>
       </c>
       <c r="D2835" t="s">
         <v>2837</v>
@@ -49004,7 +49004,7 @@
         <v>55</v>
       </c>
       <c r="C2836">
-        <v>6130</v>
+        <v>6370</v>
       </c>
       <c r="D2836" t="s">
         <v>2838</v>
@@ -49018,7 +49018,7 @@
         <v>56</v>
       </c>
       <c r="C2837">
-        <v>6080</v>
+        <v>6340</v>
       </c>
       <c r="D2837" t="s">
         <v>2839</v>
@@ -49032,7 +49032,7 @@
         <v>57</v>
       </c>
       <c r="C2838">
-        <v>6030</v>
+        <v>6310</v>
       </c>
       <c r="D2838" t="s">
         <v>2840</v>
@@ -49046,7 +49046,7 @@
         <v>58</v>
       </c>
       <c r="C2839">
-        <v>6000</v>
+        <v>6280</v>
       </c>
       <c r="D2839" t="s">
         <v>2841</v>
@@ -49060,7 +49060,7 @@
         <v>59</v>
       </c>
       <c r="C2840">
-        <v>6010</v>
+        <v>6280</v>
       </c>
       <c r="D2840" t="s">
         <v>2842</v>
@@ -49074,7 +49074,7 @@
         <v>60</v>
       </c>
       <c r="C2841">
-        <v>6070</v>
+        <v>6300</v>
       </c>
       <c r="D2841" t="s">
         <v>2843</v>
@@ -49088,7 +49088,7 @@
         <v>61</v>
       </c>
       <c r="C2842">
-        <v>6150</v>
+        <v>6330</v>
       </c>
       <c r="D2842" t="s">
         <v>2844</v>
@@ -49102,7 +49102,7 @@
         <v>62</v>
       </c>
       <c r="C2843">
-        <v>6230</v>
+        <v>6360</v>
       </c>
       <c r="D2843" t="s">
         <v>2845</v>
@@ -49116,7 +49116,7 @@
         <v>63</v>
       </c>
       <c r="C2844">
-        <v>6280</v>
+        <v>6390</v>
       </c>
       <c r="D2844" t="s">
         <v>2846</v>
@@ -49130,7 +49130,7 @@
         <v>64</v>
       </c>
       <c r="C2845">
-        <v>6310</v>
+        <v>6420</v>
       </c>
       <c r="D2845" t="s">
         <v>2847</v>
@@ -49144,7 +49144,7 @@
         <v>65</v>
       </c>
       <c r="C2846">
-        <v>6320</v>
+        <v>6440</v>
       </c>
       <c r="D2846" t="s">
         <v>2848</v>
@@ -49158,7 +49158,7 @@
         <v>66</v>
       </c>
       <c r="C2847">
-        <v>6350</v>
+        <v>6480</v>
       </c>
       <c r="D2847" t="s">
         <v>2849</v>
@@ -49172,7 +49172,7 @@
         <v>67</v>
       </c>
       <c r="C2848">
-        <v>6400</v>
+        <v>6530</v>
       </c>
       <c r="D2848" t="s">
         <v>2850</v>
@@ -49186,7 +49186,7 @@
         <v>68</v>
       </c>
       <c r="C2849">
-        <v>6460</v>
+        <v>6600</v>
       </c>
       <c r="D2849" t="s">
         <v>2851</v>
@@ -49200,7 +49200,7 @@
         <v>69</v>
       </c>
       <c r="C2850">
-        <v>6530</v>
+        <v>6680</v>
       </c>
       <c r="D2850" t="s">
         <v>2852</v>
@@ -49214,7 +49214,7 @@
         <v>70</v>
       </c>
       <c r="C2851">
-        <v>6610</v>
+        <v>6760</v>
       </c>
       <c r="D2851" t="s">
         <v>2853</v>
@@ -49228,7 +49228,7 @@
         <v>71</v>
       </c>
       <c r="C2852">
-        <v>6680</v>
+        <v>6840</v>
       </c>
       <c r="D2852" t="s">
         <v>2854</v>
@@ -49242,7 +49242,7 @@
         <v>72</v>
       </c>
       <c r="C2853">
-        <v>6750</v>
+        <v>6910</v>
       </c>
       <c r="D2853" t="s">
         <v>2855</v>
@@ -49256,7 +49256,7 @@
         <v>73</v>
       </c>
       <c r="C2854">
-        <v>6810</v>
+        <v>6990</v>
       </c>
       <c r="D2854" t="s">
         <v>2856</v>
@@ -49270,7 +49270,7 @@
         <v>74</v>
       </c>
       <c r="C2855">
-        <v>6880</v>
+        <v>7060</v>
       </c>
       <c r="D2855" t="s">
         <v>2857</v>
@@ -49284,7 +49284,7 @@
         <v>75</v>
       </c>
       <c r="C2856">
-        <v>6940</v>
+        <v>7130</v>
       </c>
       <c r="D2856" t="s">
         <v>2858</v>
@@ -49298,7 +49298,7 @@
         <v>76</v>
       </c>
       <c r="C2857">
-        <v>7010</v>
+        <v>7200</v>
       </c>
       <c r="D2857" t="s">
         <v>2859</v>
@@ -49312,7 +49312,7 @@
         <v>77</v>
       </c>
       <c r="C2858">
-        <v>7070</v>
+        <v>7260</v>
       </c>
       <c r="D2858" t="s">
         <v>2860</v>
@@ -49326,7 +49326,7 @@
         <v>78</v>
       </c>
       <c r="C2859">
-        <v>7150</v>
+        <v>7340</v>
       </c>
       <c r="D2859" t="s">
         <v>2861</v>
@@ -49340,7 +49340,7 @@
         <v>79</v>
       </c>
       <c r="C2860">
-        <v>7240</v>
+        <v>7430</v>
       </c>
       <c r="D2860" t="s">
         <v>2862</v>
@@ -49354,7 +49354,7 @@
         <v>80</v>
       </c>
       <c r="C2861">
-        <v>7350</v>
+        <v>7530</v>
       </c>
       <c r="D2861" t="s">
         <v>2863</v>
@@ -49368,7 +49368,7 @@
         <v>81</v>
       </c>
       <c r="C2862">
-        <v>7460</v>
+        <v>7600</v>
       </c>
       <c r="D2862" t="s">
         <v>2864</v>
@@ -49382,7 +49382,7 @@
         <v>82</v>
       </c>
       <c r="C2863">
-        <v>7530</v>
+        <v>7620</v>
       </c>
       <c r="D2863" t="s">
         <v>2865</v>
@@ -49396,7 +49396,7 @@
         <v>83</v>
       </c>
       <c r="C2864">
-        <v>7540</v>
+        <v>7650</v>
       </c>
       <c r="D2864" t="s">
         <v>2866</v>
@@ -49410,7 +49410,7 @@
         <v>84</v>
       </c>
       <c r="C2865">
-        <v>7500</v>
+        <v>7650</v>
       </c>
       <c r="D2865" t="s">
         <v>2867</v>
@@ -49424,7 +49424,7 @@
         <v>85</v>
       </c>
       <c r="C2866">
-        <v>7400</v>
+        <v>7600</v>
       </c>
       <c r="D2866" t="s">
         <v>2868</v>
@@ -49438,7 +49438,7 @@
         <v>86</v>
       </c>
       <c r="C2867">
-        <v>7290</v>
+        <v>7430</v>
       </c>
       <c r="D2867" t="s">
         <v>2869</v>
@@ -49452,7 +49452,7 @@
         <v>87</v>
       </c>
       <c r="C2868">
-        <v>7150</v>
+        <v>7300</v>
       </c>
       <c r="D2868" t="s">
         <v>2870</v>
@@ -49466,7 +49466,7 @@
         <v>88</v>
       </c>
       <c r="C2869">
-        <v>7000</v>
+        <v>7160</v>
       </c>
       <c r="D2869" t="s">
         <v>2871</v>
@@ -49480,7 +49480,7 @@
         <v>89</v>
       </c>
       <c r="C2870">
-        <v>6840</v>
+        <v>7000</v>
       </c>
       <c r="D2870" t="s">
         <v>2872</v>
@@ -49494,7 +49494,7 @@
         <v>90</v>
       </c>
       <c r="C2871">
-        <v>6680</v>
+        <v>6840</v>
       </c>
       <c r="D2871" t="s">
         <v>2873</v>
@@ -49508,7 +49508,7 @@
         <v>91</v>
       </c>
       <c r="C2872">
-        <v>6520</v>
+        <v>6690</v>
       </c>
       <c r="D2872" t="s">
         <v>2874</v>
@@ -49522,7 +49522,7 @@
         <v>92</v>
       </c>
       <c r="C2873">
-        <v>6370</v>
+        <v>6530</v>
       </c>
       <c r="D2873" t="s">
         <v>2875</v>
@@ -49536,7 +49536,7 @@
         <v>93</v>
       </c>
       <c r="C2874">
-        <v>6230</v>
+        <v>6370</v>
       </c>
       <c r="D2874" t="s">
         <v>2876</v>
@@ -49550,7 +49550,7 @@
         <v>94</v>
       </c>
       <c r="C2875">
-        <v>6100</v>
+        <v>6240</v>
       </c>
       <c r="D2875" t="s">
         <v>2877</v>
@@ -49564,7 +49564,7 @@
         <v>95</v>
       </c>
       <c r="C2876">
-        <v>5980</v>
+        <v>6120</v>
       </c>
       <c r="D2876" t="s">
         <v>2878</v>
@@ -49578,7 +49578,7 @@
         <v>96</v>
       </c>
       <c r="C2877">
-        <v>5880</v>
+        <v>6030</v>
       </c>
       <c r="D2877" t="s">
         <v>2879</v>
@@ -49592,7 +49592,7 @@
         <v>1</v>
       </c>
       <c r="C2878">
-        <v>5800</v>
+        <v>5950</v>
       </c>
       <c r="D2878" t="s">
         <v>2880</v>
@@ -49606,7 +49606,7 @@
         <v>2</v>
       </c>
       <c r="C2879">
-        <v>5730</v>
+        <v>5880</v>
       </c>
       <c r="D2879" t="s">
         <v>2881</v>
@@ -49620,7 +49620,7 @@
         <v>3</v>
       </c>
       <c r="C2880">
-        <v>5670</v>
+        <v>5820</v>
       </c>
       <c r="D2880" t="s">
         <v>2882</v>
@@ -49634,7 +49634,7 @@
         <v>4</v>
       </c>
       <c r="C2881">
-        <v>5620</v>
+        <v>5760</v>
       </c>
       <c r="D2881" t="s">
         <v>2883</v>
@@ -49648,7 +49648,7 @@
         <v>5</v>
       </c>
       <c r="C2882">
-        <v>5580</v>
+        <v>5710</v>
       </c>
       <c r="D2882" t="s">
         <v>2884</v>
@@ -49662,7 +49662,7 @@
         <v>6</v>
       </c>
       <c r="C2883">
-        <v>5550</v>
+        <v>5670</v>
       </c>
       <c r="D2883" t="s">
         <v>2885</v>
@@ -49676,7 +49676,7 @@
         <v>7</v>
       </c>
       <c r="C2884">
-        <v>5510</v>
+        <v>5630</v>
       </c>
       <c r="D2884" t="s">
         <v>2886</v>
@@ -49690,7 +49690,7 @@
         <v>8</v>
       </c>
       <c r="C2885">
-        <v>5480</v>
+        <v>5600</v>
       </c>
       <c r="D2885" t="s">
         <v>2887</v>
@@ -49704,7 +49704,7 @@
         <v>9</v>
       </c>
       <c r="C2886">
-        <v>5450</v>
+        <v>5580</v>
       </c>
       <c r="D2886" t="s">
         <v>2888</v>
@@ -49718,7 +49718,7 @@
         <v>10</v>
       </c>
       <c r="C2887">
-        <v>5430</v>
+        <v>5560</v>
       </c>
       <c r="D2887" t="s">
         <v>2889</v>
@@ -49732,7 +49732,7 @@
         <v>11</v>
       </c>
       <c r="C2888">
-        <v>5410</v>
+        <v>5550</v>
       </c>
       <c r="D2888" t="s">
         <v>2890</v>
@@ -49746,7 +49746,7 @@
         <v>12</v>
       </c>
       <c r="C2889">
-        <v>5400</v>
+        <v>5540</v>
       </c>
       <c r="D2889" t="s">
         <v>2891</v>
@@ -49760,7 +49760,7 @@
         <v>13</v>
       </c>
       <c r="C2890">
-        <v>5400</v>
+        <v>5520</v>
       </c>
       <c r="D2890" t="s">
         <v>2892</v>
@@ -49774,7 +49774,7 @@
         <v>14</v>
       </c>
       <c r="C2891">
-        <v>5400</v>
+        <v>5500</v>
       </c>
       <c r="D2891" t="s">
         <v>2893</v>
@@ -49788,7 +49788,7 @@
         <v>15</v>
       </c>
       <c r="C2892">
-        <v>5410</v>
+        <v>5520</v>
       </c>
       <c r="D2892" t="s">
         <v>2894</v>
@@ -49802,7 +49802,7 @@
         <v>16</v>
       </c>
       <c r="C2893">
-        <v>5420</v>
+        <v>5530</v>
       </c>
       <c r="D2893" t="s">
         <v>2895</v>
@@ -49816,7 +49816,7 @@
         <v>17</v>
       </c>
       <c r="C2894">
-        <v>5440</v>
+        <v>5550</v>
       </c>
       <c r="D2894" t="s">
         <v>2896</v>
@@ -49830,7 +49830,7 @@
         <v>18</v>
       </c>
       <c r="C2895">
-        <v>5460</v>
+        <v>5590</v>
       </c>
       <c r="D2895" t="s">
         <v>2897</v>
@@ -49844,7 +49844,7 @@
         <v>19</v>
       </c>
       <c r="C2896">
-        <v>5490</v>
+        <v>5620</v>
       </c>
       <c r="D2896" t="s">
         <v>2898</v>
@@ -49858,7 +49858,7 @@
         <v>20</v>
       </c>
       <c r="C2897">
-        <v>5520</v>
+        <v>5650</v>
       </c>
       <c r="D2897" t="s">
         <v>2899</v>
@@ -49872,7 +49872,7 @@
         <v>21</v>
       </c>
       <c r="C2898">
-        <v>5560</v>
+        <v>5690</v>
       </c>
       <c r="D2898" t="s">
         <v>2900</v>
@@ -49886,7 +49886,7 @@
         <v>22</v>
       </c>
       <c r="C2899">
-        <v>5610</v>
+        <v>5750</v>
       </c>
       <c r="D2899" t="s">
         <v>2901</v>
@@ -49900,7 +49900,7 @@
         <v>23</v>
       </c>
       <c r="C2900">
-        <v>5690</v>
+        <v>5820</v>
       </c>
       <c r="D2900" t="s">
         <v>2902</v>
@@ -49914,7 +49914,7 @@
         <v>24</v>
       </c>
       <c r="C2901">
-        <v>5790</v>
+        <v>5900</v>
       </c>
       <c r="D2901" t="s">
         <v>2903</v>
@@ -49928,7 +49928,7 @@
         <v>25</v>
       </c>
       <c r="C2902">
-        <v>5900</v>
+        <v>5990</v>
       </c>
       <c r="D2902" t="s">
         <v>2904</v>
@@ -49942,7 +49942,7 @@
         <v>26</v>
       </c>
       <c r="C2903">
-        <v>6030</v>
+        <v>6110</v>
       </c>
       <c r="D2903" t="s">
         <v>2905</v>
@@ -49956,7 +49956,7 @@
         <v>27</v>
       </c>
       <c r="C2904">
-        <v>6190</v>
+        <v>6260</v>
       </c>
       <c r="D2904" t="s">
         <v>2906</v>
@@ -49970,7 +49970,7 @@
         <v>28</v>
       </c>
       <c r="C2905">
-        <v>6360</v>
+        <v>6430</v>
       </c>
       <c r="D2905" t="s">
         <v>2907</v>
@@ -49984,7 +49984,7 @@
         <v>29</v>
       </c>
       <c r="C2906">
-        <v>6540</v>
+        <v>6620</v>
       </c>
       <c r="D2906" t="s">
         <v>2908</v>
@@ -49998,7 +49998,7 @@
         <v>30</v>
       </c>
       <c r="C2907">
-        <v>6710</v>
+        <v>6750</v>
       </c>
       <c r="D2907" t="s">
         <v>2909</v>
@@ -50012,7 +50012,7 @@
         <v>31</v>
       </c>
       <c r="C2908">
-        <v>6850</v>
+        <v>6780</v>
       </c>
       <c r="D2908" t="s">
         <v>2910</v>
@@ -50026,7 +50026,7 @@
         <v>32</v>
       </c>
       <c r="C2909">
-        <v>6980</v>
+        <v>6850</v>
       </c>
       <c r="D2909" t="s">
         <v>2911</v>
@@ -50040,7 +50040,7 @@
         <v>33</v>
       </c>
       <c r="C2910">
-        <v>7080</v>
+        <v>6950</v>
       </c>
       <c r="D2910" t="s">
         <v>2912</v>
@@ -50054,7 +50054,7 @@
         <v>34</v>
       </c>
       <c r="C2911">
-        <v>7150</v>
+        <v>7000</v>
       </c>
       <c r="D2911" t="s">
         <v>2913</v>
@@ -50068,7 +50068,7 @@
         <v>35</v>
       </c>
       <c r="C2912">
-        <v>7200</v>
+        <v>7060</v>
       </c>
       <c r="D2912" t="s">
         <v>2914</v>
@@ -50082,7 +50082,7 @@
         <v>36</v>
       </c>
       <c r="C2913">
-        <v>7200</v>
+        <v>7080</v>
       </c>
       <c r="D2913" t="s">
         <v>2915</v>
@@ -50096,7 +50096,7 @@
         <v>37</v>
       </c>
       <c r="C2914">
-        <v>7190</v>
+        <v>7100</v>
       </c>
       <c r="D2914" t="s">
         <v>2916</v>
@@ -50110,7 +50110,7 @@
         <v>38</v>
       </c>
       <c r="C2915">
-        <v>7150</v>
+        <v>7100</v>
       </c>
       <c r="D2915" t="s">
         <v>2917</v>
@@ -50124,7 +50124,7 @@
         <v>39</v>
       </c>
       <c r="C2916">
-        <v>7110</v>
+        <v>7100</v>
       </c>
       <c r="D2916" t="s">
         <v>2918</v>
@@ -50138,7 +50138,7 @@
         <v>40</v>
       </c>
       <c r="C2917">
-        <v>7050</v>
+        <v>7080</v>
       </c>
       <c r="D2917" t="s">
         <v>2919</v>
@@ -50152,7 +50152,7 @@
         <v>41</v>
       </c>
       <c r="C2918">
-        <v>6980</v>
+        <v>7020</v>
       </c>
       <c r="D2918" t="s">
         <v>2920</v>
@@ -50166,7 +50166,7 @@
         <v>42</v>
       </c>
       <c r="C2919">
-        <v>6900</v>
+        <v>6930</v>
       </c>
       <c r="D2919" t="s">
         <v>2921</v>
@@ -50180,7 +50180,7 @@
         <v>43</v>
       </c>
       <c r="C2920">
-        <v>6820</v>
+        <v>6850</v>
       </c>
       <c r="D2920" t="s">
         <v>2922</v>
@@ -50194,7 +50194,7 @@
         <v>44</v>
       </c>
       <c r="C2921">
-        <v>6720</v>
+        <v>6750</v>
       </c>
       <c r="D2921" t="s">
         <v>2923</v>
@@ -50208,7 +50208,7 @@
         <v>45</v>
       </c>
       <c r="C2922">
-        <v>6610</v>
+        <v>6640</v>
       </c>
       <c r="D2922" t="s">
         <v>2924</v>
@@ -50222,7 +50222,7 @@
         <v>46</v>
       </c>
       <c r="C2923">
-        <v>6520</v>
+        <v>6540</v>
       </c>
       <c r="D2923" t="s">
         <v>2925</v>
@@ -50236,7 +50236,7 @@
         <v>47</v>
       </c>
       <c r="C2924">
-        <v>6430</v>
+        <v>6460</v>
       </c>
       <c r="D2924" t="s">
         <v>2926</v>
@@ -50250,7 +50250,7 @@
         <v>48</v>
       </c>
       <c r="C2925">
-        <v>6360</v>
+        <v>6380</v>
       </c>
       <c r="D2925" t="s">
         <v>2927</v>
@@ -50264,7 +50264,7 @@
         <v>49</v>
       </c>
       <c r="C2926">
-        <v>6300</v>
+        <v>6320</v>
       </c>
       <c r="D2926" t="s">
         <v>2928</v>
@@ -50278,7 +50278,7 @@
         <v>50</v>
       </c>
       <c r="C2927">
-        <v>6250</v>
+        <v>6270</v>
       </c>
       <c r="D2927" t="s">
         <v>2929</v>
@@ -50292,7 +50292,7 @@
         <v>51</v>
       </c>
       <c r="C2928">
-        <v>6220</v>
+        <v>6240</v>
       </c>
       <c r="D2928" t="s">
         <v>2930</v>
@@ -50306,7 +50306,7 @@
         <v>52</v>
       </c>
       <c r="C2929">
-        <v>6200</v>
+        <v>6230</v>
       </c>
       <c r="D2929" t="s">
         <v>2931</v>
@@ -50320,7 +50320,7 @@
         <v>53</v>
       </c>
       <c r="C2930">
-        <v>6200</v>
+        <v>6220</v>
       </c>
       <c r="D2930" t="s">
         <v>2932</v>
@@ -50334,7 +50334,7 @@
         <v>54</v>
       </c>
       <c r="C2931">
-        <v>6180</v>
+        <v>6210</v>
       </c>
       <c r="D2931" t="s">
         <v>2933</v>
@@ -50348,7 +50348,7 @@
         <v>55</v>
       </c>
       <c r="C2932">
-        <v>6160</v>
+        <v>6190</v>
       </c>
       <c r="D2932" t="s">
         <v>2934</v>
@@ -50362,7 +50362,7 @@
         <v>56</v>
       </c>
       <c r="C2933">
-        <v>6120</v>
+        <v>6160</v>
       </c>
       <c r="D2933" t="s">
         <v>2935</v>
@@ -50376,7 +50376,7 @@
         <v>57</v>
       </c>
       <c r="C2934">
-        <v>6080</v>
+        <v>6130</v>
       </c>
       <c r="D2934" t="s">
         <v>2936</v>
@@ -50390,7 +50390,7 @@
         <v>58</v>
       </c>
       <c r="C2935">
-        <v>6050</v>
+        <v>6110</v>
       </c>
       <c r="D2935" t="s">
         <v>2937</v>
@@ -50404,7 +50404,7 @@
         <v>59</v>
       </c>
       <c r="C2936">
-        <v>6050</v>
+        <v>6100</v>
       </c>
       <c r="D2936" t="s">
         <v>2938</v>
@@ -50418,7 +50418,7 @@
         <v>60</v>
       </c>
       <c r="C2937">
-        <v>6080</v>
+        <v>6110</v>
       </c>
       <c r="D2937" t="s">
         <v>2939</v>
@@ -50446,7 +50446,7 @@
         <v>62</v>
       </c>
       <c r="C2939">
-        <v>6170</v>
+        <v>6160</v>
       </c>
       <c r="D2939" t="s">
         <v>2941</v>
@@ -50460,7 +50460,7 @@
         <v>63</v>
       </c>
       <c r="C2940">
-        <v>6210</v>
+        <v>6190</v>
       </c>
       <c r="D2940" t="s">
         <v>2942</v>
@@ -50474,7 +50474,7 @@
         <v>64</v>
       </c>
       <c r="C2941">
-        <v>6250</v>
+        <v>6230</v>
       </c>
       <c r="D2941" t="s">
         <v>2943</v>
@@ -50488,7 +50488,7 @@
         <v>65</v>
       </c>
       <c r="C2942">
-        <v>6270</v>
+        <v>6280</v>
       </c>
       <c r="D2942" t="s">
         <v>2944</v>
@@ -50502,7 +50502,7 @@
         <v>66</v>
       </c>
       <c r="C2943">
-        <v>6310</v>
+        <v>6330</v>
       </c>
       <c r="D2943" t="s">
         <v>2945</v>
@@ -50516,7 +50516,7 @@
         <v>67</v>
       </c>
       <c r="C2944">
-        <v>6360</v>
+        <v>6400</v>
       </c>
       <c r="D2944" t="s">
         <v>2946</v>
@@ -50530,7 +50530,7 @@
         <v>68</v>
       </c>
       <c r="C2945">
-        <v>6420</v>
+        <v>6480</v>
       </c>
       <c r="D2945" t="s">
         <v>2947</v>
@@ -50544,7 +50544,7 @@
         <v>69</v>
       </c>
       <c r="C2946">
-        <v>6500</v>
+        <v>6580</v>
       </c>
       <c r="D2946" t="s">
         <v>2948</v>
@@ -50558,7 +50558,7 @@
         <v>70</v>
       </c>
       <c r="C2947">
-        <v>6570</v>
+        <v>6670</v>
       </c>
       <c r="D2947" t="s">
         <v>2949</v>
@@ -50572,7 +50572,7 @@
         <v>71</v>
       </c>
       <c r="C2948">
-        <v>6650</v>
+        <v>6760</v>
       </c>
       <c r="D2948" t="s">
         <v>2950</v>
@@ -50586,7 +50586,7 @@
         <v>72</v>
       </c>
       <c r="C2949">
-        <v>6720</v>
+        <v>6860</v>
       </c>
       <c r="D2949" t="s">
         <v>2951</v>
@@ -50600,7 +50600,7 @@
         <v>73</v>
       </c>
       <c r="C2950">
-        <v>6800</v>
+        <v>6950</v>
       </c>
       <c r="D2950" t="s">
         <v>2952</v>
@@ -50614,7 +50614,7 @@
         <v>74</v>
       </c>
       <c r="C2951">
-        <v>6870</v>
+        <v>7030</v>
       </c>
       <c r="D2951" t="s">
         <v>2953</v>
@@ -50628,7 +50628,7 @@
         <v>75</v>
       </c>
       <c r="C2952">
-        <v>6940</v>
+        <v>7110</v>
       </c>
       <c r="D2952" t="s">
         <v>2954</v>
@@ -50642,7 +50642,7 @@
         <v>76</v>
       </c>
       <c r="C2953">
-        <v>7010</v>
+        <v>7180</v>
       </c>
       <c r="D2953" t="s">
         <v>2955</v>
@@ -50656,7 +50656,7 @@
         <v>77</v>
       </c>
       <c r="C2954">
-        <v>7080</v>
+        <v>7250</v>
       </c>
       <c r="D2954" t="s">
         <v>2956</v>
@@ -50670,7 +50670,7 @@
         <v>78</v>
       </c>
       <c r="C2955">
-        <v>7150</v>
+        <v>7330</v>
       </c>
       <c r="D2955" t="s">
         <v>2957</v>
@@ -50684,7 +50684,7 @@
         <v>79</v>
       </c>
       <c r="C2956">
-        <v>7250</v>
+        <v>7440</v>
       </c>
       <c r="D2956" t="s">
         <v>2958</v>
@@ -50698,7 +50698,7 @@
         <v>80</v>
       </c>
       <c r="C2957">
-        <v>7360</v>
+        <v>7550</v>
       </c>
       <c r="D2957" t="s">
         <v>2959</v>
@@ -50712,7 +50712,7 @@
         <v>81</v>
       </c>
       <c r="C2958">
-        <v>7480</v>
+        <v>7580</v>
       </c>
       <c r="D2958" t="s">
         <v>2960</v>
@@ -50726,7 +50726,7 @@
         <v>82</v>
       </c>
       <c r="C2959">
-        <v>7550</v>
+        <v>7650</v>
       </c>
       <c r="D2959" t="s">
         <v>2961</v>
@@ -50740,7 +50740,7 @@
         <v>83</v>
       </c>
       <c r="C2960">
-        <v>7560</v>
+        <v>7700</v>
       </c>
       <c r="D2960" t="s">
         <v>2962</v>
@@ -50754,7 +50754,7 @@
         <v>84</v>
       </c>
       <c r="C2961">
-        <v>7520</v>
+        <v>7700</v>
       </c>
       <c r="D2961" t="s">
         <v>2963</v>
@@ -50768,7 +50768,7 @@
         <v>85</v>
       </c>
       <c r="C2962">
-        <v>7430</v>
+        <v>7620</v>
       </c>
       <c r="D2962" t="s">
         <v>2964</v>
@@ -50782,7 +50782,7 @@
         <v>86</v>
       </c>
       <c r="C2963">
-        <v>7310</v>
+        <v>7500</v>
       </c>
       <c r="D2963" t="s">
         <v>2965</v>
@@ -50796,7 +50796,7 @@
         <v>87</v>
       </c>
       <c r="C2964">
-        <v>7180</v>
+        <v>7370</v>
       </c>
       <c r="D2964" t="s">
         <v>2966</v>
@@ -50810,7 +50810,7 @@
         <v>88</v>
       </c>
       <c r="C2965">
-        <v>7030</v>
+        <v>7220</v>
       </c>
       <c r="D2965" t="s">
         <v>2967</v>
@@ -50824,7 +50824,7 @@
         <v>89</v>
       </c>
       <c r="C2966">
-        <v>6870</v>
+        <v>7070</v>
       </c>
       <c r="D2966" t="s">
         <v>2968</v>
@@ -50838,7 +50838,7 @@
         <v>90</v>
       </c>
       <c r="C2967">
-        <v>6710</v>
+        <v>6910</v>
       </c>
       <c r="D2967" t="s">
         <v>2969</v>
@@ -50852,7 +50852,7 @@
         <v>91</v>
       </c>
       <c r="C2968">
-        <v>6560</v>
+        <v>6760</v>
       </c>
       <c r="D2968" t="s">
         <v>2970</v>
@@ -50866,7 +50866,7 @@
         <v>92</v>
       </c>
       <c r="C2969">
-        <v>6410</v>
+        <v>6600</v>
       </c>
       <c r="D2969" t="s">
         <v>2971</v>
@@ -50880,7 +50880,7 @@
         <v>93</v>
       </c>
       <c r="C2970">
-        <v>6260</v>
+        <v>6450</v>
       </c>
       <c r="D2970" t="s">
         <v>2972</v>
@@ -50894,7 +50894,7 @@
         <v>94</v>
       </c>
       <c r="C2971">
-        <v>6130</v>
+        <v>6310</v>
       </c>
       <c r="D2971" t="s">
         <v>2973</v>
@@ -50908,7 +50908,7 @@
         <v>95</v>
       </c>
       <c r="C2972">
-        <v>6010</v>
+        <v>6190</v>
       </c>
       <c r="D2972" t="s">
         <v>2974</v>
@@ -50922,7 +50922,7 @@
         <v>96</v>
       </c>
       <c r="C2973">
-        <v>5910</v>
+        <v>6090</v>
       </c>
       <c r="D2973" t="s">
         <v>2975</v>

--- a/Market Fundamentals/Transelectrica_data/Cons_Prod_final/Weekly_Consumption_2026.xlsx
+++ b/Market Fundamentals/Transelectrica_data/Cons_Prod_final/Weekly_Consumption_2026.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2788" uniqueCount="2788">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2884" uniqueCount="2884">
   <si>
     <t>Date</t>
   </si>
@@ -8378,6 +8378,294 @@
   </si>
   <si>
     <t>29.04.202696.0</t>
+  </si>
+  <si>
+    <t>30.04.20261.0</t>
+  </si>
+  <si>
+    <t>30.04.20262.0</t>
+  </si>
+  <si>
+    <t>30.04.20263.0</t>
+  </si>
+  <si>
+    <t>30.04.20264.0</t>
+  </si>
+  <si>
+    <t>30.04.20265.0</t>
+  </si>
+  <si>
+    <t>30.04.20266.0</t>
+  </si>
+  <si>
+    <t>30.04.20267.0</t>
+  </si>
+  <si>
+    <t>30.04.20268.0</t>
+  </si>
+  <si>
+    <t>30.04.20269.0</t>
+  </si>
+  <si>
+    <t>30.04.202610.0</t>
+  </si>
+  <si>
+    <t>30.04.202611.0</t>
+  </si>
+  <si>
+    <t>30.04.202612.0</t>
+  </si>
+  <si>
+    <t>30.04.202613.0</t>
+  </si>
+  <si>
+    <t>30.04.202614.0</t>
+  </si>
+  <si>
+    <t>30.04.202615.0</t>
+  </si>
+  <si>
+    <t>30.04.202616.0</t>
+  </si>
+  <si>
+    <t>30.04.202617.0</t>
+  </si>
+  <si>
+    <t>30.04.202618.0</t>
+  </si>
+  <si>
+    <t>30.04.202619.0</t>
+  </si>
+  <si>
+    <t>30.04.202620.0</t>
+  </si>
+  <si>
+    <t>30.04.202621.0</t>
+  </si>
+  <si>
+    <t>30.04.202622.0</t>
+  </si>
+  <si>
+    <t>30.04.202623.0</t>
+  </si>
+  <si>
+    <t>30.04.202624.0</t>
+  </si>
+  <si>
+    <t>30.04.202625.0</t>
+  </si>
+  <si>
+    <t>30.04.202626.0</t>
+  </si>
+  <si>
+    <t>30.04.202627.0</t>
+  </si>
+  <si>
+    <t>30.04.202628.0</t>
+  </si>
+  <si>
+    <t>30.04.202629.0</t>
+  </si>
+  <si>
+    <t>30.04.202630.0</t>
+  </si>
+  <si>
+    <t>30.04.202631.0</t>
+  </si>
+  <si>
+    <t>30.04.202632.0</t>
+  </si>
+  <si>
+    <t>30.04.202633.0</t>
+  </si>
+  <si>
+    <t>30.04.202634.0</t>
+  </si>
+  <si>
+    <t>30.04.202635.0</t>
+  </si>
+  <si>
+    <t>30.04.202636.0</t>
+  </si>
+  <si>
+    <t>30.04.202637.0</t>
+  </si>
+  <si>
+    <t>30.04.202638.0</t>
+  </si>
+  <si>
+    <t>30.04.202639.0</t>
+  </si>
+  <si>
+    <t>30.04.202640.0</t>
+  </si>
+  <si>
+    <t>30.04.202641.0</t>
+  </si>
+  <si>
+    <t>30.04.202642.0</t>
+  </si>
+  <si>
+    <t>30.04.202643.0</t>
+  </si>
+  <si>
+    <t>30.04.202644.0</t>
+  </si>
+  <si>
+    <t>30.04.202645.0</t>
+  </si>
+  <si>
+    <t>30.04.202646.0</t>
+  </si>
+  <si>
+    <t>30.04.202647.0</t>
+  </si>
+  <si>
+    <t>30.04.202648.0</t>
+  </si>
+  <si>
+    <t>30.04.202649.0</t>
+  </si>
+  <si>
+    <t>30.04.202650.0</t>
+  </si>
+  <si>
+    <t>30.04.202651.0</t>
+  </si>
+  <si>
+    <t>30.04.202652.0</t>
+  </si>
+  <si>
+    <t>30.04.202653.0</t>
+  </si>
+  <si>
+    <t>30.04.202654.0</t>
+  </si>
+  <si>
+    <t>30.04.202655.0</t>
+  </si>
+  <si>
+    <t>30.04.202656.0</t>
+  </si>
+  <si>
+    <t>30.04.202657.0</t>
+  </si>
+  <si>
+    <t>30.04.202658.0</t>
+  </si>
+  <si>
+    <t>30.04.202659.0</t>
+  </si>
+  <si>
+    <t>30.04.202660.0</t>
+  </si>
+  <si>
+    <t>30.04.202661.0</t>
+  </si>
+  <si>
+    <t>30.04.202662.0</t>
+  </si>
+  <si>
+    <t>30.04.202663.0</t>
+  </si>
+  <si>
+    <t>30.04.202664.0</t>
+  </si>
+  <si>
+    <t>30.04.202665.0</t>
+  </si>
+  <si>
+    <t>30.04.202666.0</t>
+  </si>
+  <si>
+    <t>30.04.202667.0</t>
+  </si>
+  <si>
+    <t>30.04.202668.0</t>
+  </si>
+  <si>
+    <t>30.04.202669.0</t>
+  </si>
+  <si>
+    <t>30.04.202670.0</t>
+  </si>
+  <si>
+    <t>30.04.202671.0</t>
+  </si>
+  <si>
+    <t>30.04.202672.0</t>
+  </si>
+  <si>
+    <t>30.04.202673.0</t>
+  </si>
+  <si>
+    <t>30.04.202674.0</t>
+  </si>
+  <si>
+    <t>30.04.202675.0</t>
+  </si>
+  <si>
+    <t>30.04.202676.0</t>
+  </si>
+  <si>
+    <t>30.04.202677.0</t>
+  </si>
+  <si>
+    <t>30.04.202678.0</t>
+  </si>
+  <si>
+    <t>30.04.202679.0</t>
+  </si>
+  <si>
+    <t>30.04.202680.0</t>
+  </si>
+  <si>
+    <t>30.04.202681.0</t>
+  </si>
+  <si>
+    <t>30.04.202682.0</t>
+  </si>
+  <si>
+    <t>30.04.202683.0</t>
+  </si>
+  <si>
+    <t>30.04.202684.0</t>
+  </si>
+  <si>
+    <t>30.04.202685.0</t>
+  </si>
+  <si>
+    <t>30.04.202686.0</t>
+  </si>
+  <si>
+    <t>30.04.202687.0</t>
+  </si>
+  <si>
+    <t>30.04.202688.0</t>
+  </si>
+  <si>
+    <t>30.04.202689.0</t>
+  </si>
+  <si>
+    <t>30.04.202690.0</t>
+  </si>
+  <si>
+    <t>30.04.202691.0</t>
+  </si>
+  <si>
+    <t>30.04.202692.0</t>
+  </si>
+  <si>
+    <t>30.04.202693.0</t>
+  </si>
+  <si>
+    <t>30.04.202694.0</t>
+  </si>
+  <si>
+    <t>30.04.202695.0</t>
+  </si>
+  <si>
+    <t>30.04.202696.0</t>
   </si>
 </sst>
 </file>
@@ -8739,7 +9027,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D2785"/>
+  <dimension ref="A1:D2881"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -38332,7 +38620,7 @@
         <v>1</v>
       </c>
       <c r="C2114">
-        <v>5600</v>
+        <v>5700</v>
       </c>
       <c r="D2114" t="s">
         <v>2116</v>
@@ -38346,7 +38634,7 @@
         <v>2</v>
       </c>
       <c r="C2115">
-        <v>5540</v>
+        <v>5630</v>
       </c>
       <c r="D2115" t="s">
         <v>2117</v>
@@ -38360,7 +38648,7 @@
         <v>3</v>
       </c>
       <c r="C2116">
-        <v>5490</v>
+        <v>5570</v>
       </c>
       <c r="D2116" t="s">
         <v>2118</v>
@@ -38374,7 +38662,7 @@
         <v>4</v>
       </c>
       <c r="C2117">
-        <v>5430</v>
+        <v>5510</v>
       </c>
       <c r="D2117" t="s">
         <v>2119</v>
@@ -38388,7 +38676,7 @@
         <v>5</v>
       </c>
       <c r="C2118">
-        <v>5370</v>
+        <v>5460</v>
       </c>
       <c r="D2118" t="s">
         <v>2120</v>
@@ -38402,7 +38690,7 @@
         <v>6</v>
       </c>
       <c r="C2119">
-        <v>5330</v>
+        <v>5410</v>
       </c>
       <c r="D2119" t="s">
         <v>2121</v>
@@ -38416,7 +38704,7 @@
         <v>7</v>
       </c>
       <c r="C2120">
-        <v>5290</v>
+        <v>5370</v>
       </c>
       <c r="D2120" t="s">
         <v>2122</v>
@@ -38430,7 +38718,7 @@
         <v>8</v>
       </c>
       <c r="C2121">
-        <v>5270</v>
+        <v>5340</v>
       </c>
       <c r="D2121" t="s">
         <v>2123</v>
@@ -38444,7 +38732,7 @@
         <v>9</v>
       </c>
       <c r="C2122">
-        <v>5240</v>
+        <v>5310</v>
       </c>
       <c r="D2122" t="s">
         <v>2124</v>
@@ -38458,7 +38746,7 @@
         <v>10</v>
       </c>
       <c r="C2123">
-        <v>5230</v>
+        <v>5290</v>
       </c>
       <c r="D2123" t="s">
         <v>2125</v>
@@ -38472,7 +38760,7 @@
         <v>11</v>
       </c>
       <c r="C2124">
-        <v>5220</v>
+        <v>5280</v>
       </c>
       <c r="D2124" t="s">
         <v>2126</v>
@@ -38486,7 +38774,7 @@
         <v>12</v>
       </c>
       <c r="C2125">
-        <v>5210</v>
+        <v>5270</v>
       </c>
       <c r="D2125" t="s">
         <v>2127</v>
@@ -38500,7 +38788,7 @@
         <v>13</v>
       </c>
       <c r="C2126">
-        <v>5210</v>
+        <v>5260</v>
       </c>
       <c r="D2126" t="s">
         <v>2128</v>
@@ -38514,7 +38802,7 @@
         <v>14</v>
       </c>
       <c r="C2127">
-        <v>5200</v>
+        <v>5260</v>
       </c>
       <c r="D2127" t="s">
         <v>2129</v>
@@ -38528,7 +38816,7 @@
         <v>15</v>
       </c>
       <c r="C2128">
-        <v>5210</v>
+        <v>5260</v>
       </c>
       <c r="D2128" t="s">
         <v>2130</v>
@@ -38542,7 +38830,7 @@
         <v>16</v>
       </c>
       <c r="C2129">
-        <v>5220</v>
+        <v>5280</v>
       </c>
       <c r="D2129" t="s">
         <v>2131</v>
@@ -38556,7 +38844,7 @@
         <v>17</v>
       </c>
       <c r="C2130">
-        <v>5230</v>
+        <v>5300</v>
       </c>
       <c r="D2130" t="s">
         <v>2132</v>
@@ -38570,7 +38858,7 @@
         <v>18</v>
       </c>
       <c r="C2131">
-        <v>5250</v>
+        <v>5330</v>
       </c>
       <c r="D2131" t="s">
         <v>2133</v>
@@ -38584,7 +38872,7 @@
         <v>19</v>
       </c>
       <c r="C2132">
-        <v>5280</v>
+        <v>5360</v>
       </c>
       <c r="D2132" t="s">
         <v>2134</v>
@@ -38598,7 +38886,7 @@
         <v>20</v>
       </c>
       <c r="C2133">
-        <v>5310</v>
+        <v>5390</v>
       </c>
       <c r="D2133" t="s">
         <v>2135</v>
@@ -38612,7 +38900,7 @@
         <v>21</v>
       </c>
       <c r="C2134">
-        <v>5370</v>
+        <v>5440</v>
       </c>
       <c r="D2134" t="s">
         <v>2136</v>
@@ -38626,7 +38914,7 @@
         <v>22</v>
       </c>
       <c r="C2135">
-        <v>5430</v>
+        <v>5490</v>
       </c>
       <c r="D2135" t="s">
         <v>2137</v>
@@ -38640,7 +38928,7 @@
         <v>23</v>
       </c>
       <c r="C2136">
-        <v>5500</v>
+        <v>5560</v>
       </c>
       <c r="D2136" t="s">
         <v>2138</v>
@@ -38654,7 +38942,7 @@
         <v>24</v>
       </c>
       <c r="C2137">
-        <v>5580</v>
+        <v>5640</v>
       </c>
       <c r="D2137" t="s">
         <v>2139</v>
@@ -38668,7 +38956,7 @@
         <v>25</v>
       </c>
       <c r="C2138">
-        <v>5680</v>
+        <v>5740</v>
       </c>
       <c r="D2138" t="s">
         <v>2140</v>
@@ -38682,7 +38970,7 @@
         <v>26</v>
       </c>
       <c r="C2139">
-        <v>5770</v>
+        <v>5830</v>
       </c>
       <c r="D2139" t="s">
         <v>2141</v>
@@ -38696,7 +38984,7 @@
         <v>27</v>
       </c>
       <c r="C2140">
-        <v>5870</v>
+        <v>5930</v>
       </c>
       <c r="D2140" t="s">
         <v>2142</v>
@@ -38710,7 +38998,7 @@
         <v>28</v>
       </c>
       <c r="C2141">
-        <v>5960</v>
+        <v>6030</v>
       </c>
       <c r="D2141" t="s">
         <v>2143</v>
@@ -38724,7 +39012,7 @@
         <v>29</v>
       </c>
       <c r="C2142">
-        <v>6040</v>
+        <v>6110</v>
       </c>
       <c r="D2142" t="s">
         <v>2144</v>
@@ -38738,7 +39026,7 @@
         <v>30</v>
       </c>
       <c r="C2143">
-        <v>6110</v>
+        <v>6180</v>
       </c>
       <c r="D2143" t="s">
         <v>2145</v>
@@ -38752,7 +39040,7 @@
         <v>31</v>
       </c>
       <c r="C2144">
-        <v>6150</v>
+        <v>6220</v>
       </c>
       <c r="D2144" t="s">
         <v>2146</v>
@@ -38766,7 +39054,7 @@
         <v>32</v>
       </c>
       <c r="C2145">
-        <v>6150</v>
+        <v>6230</v>
       </c>
       <c r="D2145" t="s">
         <v>2147</v>
@@ -38780,7 +39068,7 @@
         <v>33</v>
       </c>
       <c r="C2146">
-        <v>6150</v>
+        <v>6220</v>
       </c>
       <c r="D2146" t="s">
         <v>2148</v>
@@ -38794,7 +39082,7 @@
         <v>34</v>
       </c>
       <c r="C2147">
-        <v>6150</v>
+        <v>6170</v>
       </c>
       <c r="D2147" t="s">
         <v>2149</v>
@@ -38808,7 +39096,7 @@
         <v>35</v>
       </c>
       <c r="C2148">
-        <v>6100</v>
+        <v>6090</v>
       </c>
       <c r="D2148" t="s">
         <v>2150</v>
@@ -38822,7 +39110,7 @@
         <v>36</v>
       </c>
       <c r="C2149">
-        <v>6020</v>
+        <v>6000</v>
       </c>
       <c r="D2149" t="s">
         <v>2151</v>
@@ -38836,7 +39124,7 @@
         <v>37</v>
       </c>
       <c r="C2150">
-        <v>5910</v>
+        <v>5880</v>
       </c>
       <c r="D2150" t="s">
         <v>2152</v>
@@ -38850,7 +39138,7 @@
         <v>38</v>
       </c>
       <c r="C2151">
-        <v>5780</v>
+        <v>5750</v>
       </c>
       <c r="D2151" t="s">
         <v>2153</v>
@@ -38864,7 +39152,7 @@
         <v>39</v>
       </c>
       <c r="C2152">
-        <v>5640</v>
+        <v>5610</v>
       </c>
       <c r="D2152" t="s">
         <v>2154</v>
@@ -38878,7 +39166,7 @@
         <v>40</v>
       </c>
       <c r="C2153">
-        <v>5480</v>
+        <v>5470</v>
       </c>
       <c r="D2153" t="s">
         <v>2155</v>
@@ -38892,7 +39180,7 @@
         <v>41</v>
       </c>
       <c r="C2154">
-        <v>5330</v>
+        <v>5340</v>
       </c>
       <c r="D2154" t="s">
         <v>2156</v>
@@ -38906,7 +39194,7 @@
         <v>42</v>
       </c>
       <c r="C2155">
-        <v>5180</v>
+        <v>5220</v>
       </c>
       <c r="D2155" t="s">
         <v>2157</v>
@@ -38920,7 +39208,7 @@
         <v>43</v>
       </c>
       <c r="C2156">
-        <v>5040</v>
+        <v>5120</v>
       </c>
       <c r="D2156" t="s">
         <v>2158</v>
@@ -38934,7 +39222,7 @@
         <v>44</v>
       </c>
       <c r="C2157">
-        <v>4920</v>
+        <v>5030</v>
       </c>
       <c r="D2157" t="s">
         <v>2159</v>
@@ -38948,7 +39236,7 @@
         <v>45</v>
       </c>
       <c r="C2158">
-        <v>4820</v>
+        <v>4950</v>
       </c>
       <c r="D2158" t="s">
         <v>2160</v>
@@ -38962,7 +39250,7 @@
         <v>46</v>
       </c>
       <c r="C2159">
-        <v>4730</v>
+        <v>4890</v>
       </c>
       <c r="D2159" t="s">
         <v>2161</v>
@@ -38976,7 +39264,7 @@
         <v>47</v>
       </c>
       <c r="C2160">
-        <v>4670</v>
+        <v>4840</v>
       </c>
       <c r="D2160" t="s">
         <v>2162</v>
@@ -38990,7 +39278,7 @@
         <v>48</v>
       </c>
       <c r="C2161">
-        <v>4620</v>
+        <v>4800</v>
       </c>
       <c r="D2161" t="s">
         <v>2163</v>
@@ -39004,7 +39292,7 @@
         <v>49</v>
       </c>
       <c r="C2162">
-        <v>4580</v>
+        <v>4770</v>
       </c>
       <c r="D2162" t="s">
         <v>2164</v>
@@ -39018,7 +39306,7 @@
         <v>50</v>
       </c>
       <c r="C2163">
-        <v>4550</v>
+        <v>4740</v>
       </c>
       <c r="D2163" t="s">
         <v>2165</v>
@@ -39032,7 +39320,7 @@
         <v>51</v>
       </c>
       <c r="C2164">
-        <v>4540</v>
+        <v>4730</v>
       </c>
       <c r="D2164" t="s">
         <v>2166</v>
@@ -39046,7 +39334,7 @@
         <v>52</v>
       </c>
       <c r="C2165">
-        <v>4530</v>
+        <v>4720</v>
       </c>
       <c r="D2165" t="s">
         <v>2167</v>
@@ -39060,7 +39348,7 @@
         <v>53</v>
       </c>
       <c r="C2166">
-        <v>4520</v>
+        <v>4710</v>
       </c>
       <c r="D2166" t="s">
         <v>2168</v>
@@ -39074,7 +39362,7 @@
         <v>54</v>
       </c>
       <c r="C2167">
-        <v>4520</v>
+        <v>4720</v>
       </c>
       <c r="D2167" t="s">
         <v>2169</v>
@@ -39088,7 +39376,7 @@
         <v>55</v>
       </c>
       <c r="C2168">
-        <v>4520</v>
+        <v>4730</v>
       </c>
       <c r="D2168" t="s">
         <v>2170</v>
@@ -39102,7 +39390,7 @@
         <v>56</v>
       </c>
       <c r="C2169">
-        <v>4520</v>
+        <v>4740</v>
       </c>
       <c r="D2169" t="s">
         <v>2171</v>
@@ -39116,7 +39404,7 @@
         <v>57</v>
       </c>
       <c r="C2170">
-        <v>4520</v>
+        <v>4760</v>
       </c>
       <c r="D2170" t="s">
         <v>2172</v>
@@ -39130,7 +39418,7 @@
         <v>58</v>
       </c>
       <c r="C2171">
-        <v>4520</v>
+        <v>4770</v>
       </c>
       <c r="D2171" t="s">
         <v>2173</v>
@@ -39144,7 +39432,7 @@
         <v>59</v>
       </c>
       <c r="C2172">
-        <v>4520</v>
+        <v>4790</v>
       </c>
       <c r="D2172" t="s">
         <v>2174</v>
@@ -39158,7 +39446,7 @@
         <v>60</v>
       </c>
       <c r="C2173">
-        <v>4530</v>
+        <v>4810</v>
       </c>
       <c r="D2173" t="s">
         <v>2175</v>
@@ -39172,7 +39460,7 @@
         <v>61</v>
       </c>
       <c r="C2174">
-        <v>4540</v>
+        <v>4830</v>
       </c>
       <c r="D2174" t="s">
         <v>2176</v>
@@ -39186,7 +39474,7 @@
         <v>62</v>
       </c>
       <c r="C2175">
-        <v>4560</v>
+        <v>4860</v>
       </c>
       <c r="D2175" t="s">
         <v>2177</v>
@@ -39200,7 +39488,7 @@
         <v>63</v>
       </c>
       <c r="C2176">
-        <v>4600</v>
+        <v>4900</v>
       </c>
       <c r="D2176" t="s">
         <v>2178</v>
@@ -39214,7 +39502,7 @@
         <v>64</v>
       </c>
       <c r="C2177">
-        <v>4650</v>
+        <v>4960</v>
       </c>
       <c r="D2177" t="s">
         <v>2179</v>
@@ -39228,7 +39516,7 @@
         <v>65</v>
       </c>
       <c r="C2178">
-        <v>4730</v>
+        <v>5030</v>
       </c>
       <c r="D2178" t="s">
         <v>2180</v>
@@ -39242,7 +39530,7 @@
         <v>66</v>
       </c>
       <c r="C2179">
-        <v>4830</v>
+        <v>5120</v>
       </c>
       <c r="D2179" t="s">
         <v>2181</v>
@@ -39256,7 +39544,7 @@
         <v>67</v>
       </c>
       <c r="C2180">
-        <v>4950</v>
+        <v>5220</v>
       </c>
       <c r="D2180" t="s">
         <v>2182</v>
@@ -39270,7 +39558,7 @@
         <v>68</v>
       </c>
       <c r="C2181">
-        <v>5090</v>
+        <v>5330</v>
       </c>
       <c r="D2181" t="s">
         <v>2183</v>
@@ -39284,7 +39572,7 @@
         <v>69</v>
       </c>
       <c r="C2182">
-        <v>5230</v>
+        <v>5450</v>
       </c>
       <c r="D2182" t="s">
         <v>2184</v>
@@ -39298,7 +39586,7 @@
         <v>70</v>
       </c>
       <c r="C2183">
-        <v>5370</v>
+        <v>5570</v>
       </c>
       <c r="D2183" t="s">
         <v>2185</v>
@@ -39312,7 +39600,7 @@
         <v>71</v>
       </c>
       <c r="C2184">
-        <v>5500</v>
+        <v>5680</v>
       </c>
       <c r="D2184" t="s">
         <v>2186</v>
@@ -39326,7 +39614,7 @@
         <v>72</v>
       </c>
       <c r="C2185">
-        <v>5620</v>
+        <v>5800</v>
       </c>
       <c r="D2185" t="s">
         <v>2187</v>
@@ -39340,7 +39628,7 @@
         <v>73</v>
       </c>
       <c r="C2186">
-        <v>5740</v>
+        <v>5900</v>
       </c>
       <c r="D2186" t="s">
         <v>2188</v>
@@ -39354,7 +39642,7 @@
         <v>74</v>
       </c>
       <c r="C2187">
-        <v>5860</v>
+        <v>6020</v>
       </c>
       <c r="D2187" t="s">
         <v>2189</v>
@@ -39368,7 +39656,7 @@
         <v>75</v>
       </c>
       <c r="C2188">
-        <v>6000</v>
+        <v>6120</v>
       </c>
       <c r="D2188" t="s">
         <v>2190</v>
@@ -39382,7 +39670,7 @@
         <v>76</v>
       </c>
       <c r="C2189">
-        <v>6150</v>
+        <v>6250</v>
       </c>
       <c r="D2189" t="s">
         <v>2191</v>
@@ -39396,7 +39684,7 @@
         <v>77</v>
       </c>
       <c r="C2190">
-        <v>6320</v>
+        <v>6380</v>
       </c>
       <c r="D2190" t="s">
         <v>2192</v>
@@ -39410,7 +39698,7 @@
         <v>78</v>
       </c>
       <c r="C2191">
-        <v>6500</v>
+        <v>6520</v>
       </c>
       <c r="D2191" t="s">
         <v>2193</v>
@@ -39424,7 +39712,7 @@
         <v>79</v>
       </c>
       <c r="C2192">
-        <v>6670</v>
+        <v>6660</v>
       </c>
       <c r="D2192" t="s">
         <v>2194</v>
@@ -39438,7 +39726,7 @@
         <v>80</v>
       </c>
       <c r="C2193">
-        <v>6820</v>
+        <v>6800</v>
       </c>
       <c r="D2193" t="s">
         <v>2195</v>
@@ -39452,7 +39740,7 @@
         <v>81</v>
       </c>
       <c r="C2194">
-        <v>6970</v>
+        <v>6910</v>
       </c>
       <c r="D2194" t="s">
         <v>2196</v>
@@ -39466,7 +39754,7 @@
         <v>82</v>
       </c>
       <c r="C2195">
-        <v>7070</v>
+        <v>7020</v>
       </c>
       <c r="D2195" t="s">
         <v>2197</v>
@@ -39480,7 +39768,7 @@
         <v>83</v>
       </c>
       <c r="C2196">
-        <v>7100</v>
+        <v>7080</v>
       </c>
       <c r="D2196" t="s">
         <v>2198</v>
@@ -39494,7 +39782,7 @@
         <v>84</v>
       </c>
       <c r="C2197">
-        <v>7140</v>
+        <v>7120</v>
       </c>
       <c r="D2197" t="s">
         <v>2199</v>
@@ -39508,7 +39796,7 @@
         <v>85</v>
       </c>
       <c r="C2198">
-        <v>7150</v>
+        <v>7090</v>
       </c>
       <c r="D2198" t="s">
         <v>2200</v>
@@ -39522,7 +39810,7 @@
         <v>86</v>
       </c>
       <c r="C2199">
-        <v>7140</v>
+        <v>7040</v>
       </c>
       <c r="D2199" t="s">
         <v>2201</v>
@@ -39536,7 +39824,7 @@
         <v>87</v>
       </c>
       <c r="C2200">
-        <v>7080</v>
+        <v>6960</v>
       </c>
       <c r="D2200" t="s">
         <v>2202</v>
@@ -39550,7 +39838,7 @@
         <v>88</v>
       </c>
       <c r="C2201">
-        <v>6980</v>
+        <v>6850</v>
       </c>
       <c r="D2201" t="s">
         <v>2203</v>
@@ -39564,7 +39852,7 @@
         <v>89</v>
       </c>
       <c r="C2202">
-        <v>6840</v>
+        <v>6700</v>
       </c>
       <c r="D2202" t="s">
         <v>2204</v>
@@ -39578,7 +39866,7 @@
         <v>90</v>
       </c>
       <c r="C2203">
-        <v>6750</v>
+        <v>6580</v>
       </c>
       <c r="D2203" t="s">
         <v>2205</v>
@@ -39592,7 +39880,7 @@
         <v>91</v>
       </c>
       <c r="C2204">
-        <v>6580</v>
+        <v>6420</v>
       </c>
       <c r="D2204" t="s">
         <v>2206</v>
@@ -39606,7 +39894,7 @@
         <v>92</v>
       </c>
       <c r="C2205">
-        <v>6380</v>
+        <v>6260</v>
       </c>
       <c r="D2205" t="s">
         <v>2207</v>
@@ -39620,7 +39908,7 @@
         <v>93</v>
       </c>
       <c r="C2206">
-        <v>6120</v>
+        <v>6090</v>
       </c>
       <c r="D2206" t="s">
         <v>2208</v>
@@ -39634,7 +39922,7 @@
         <v>94</v>
       </c>
       <c r="C2207">
-        <v>5900</v>
+        <v>5950</v>
       </c>
       <c r="D2207" t="s">
         <v>2209</v>
@@ -39648,7 +39936,7 @@
         <v>95</v>
       </c>
       <c r="C2208">
-        <v>5830</v>
+        <v>5800</v>
       </c>
       <c r="D2208" t="s">
         <v>2210</v>
@@ -39662,7 +39950,7 @@
         <v>96</v>
       </c>
       <c r="C2209">
-        <v>5720</v>
+        <v>5660</v>
       </c>
       <c r="D2209" t="s">
         <v>2211</v>
@@ -39676,7 +39964,7 @@
         <v>1</v>
       </c>
       <c r="C2210">
-        <v>5680</v>
+        <v>5600</v>
       </c>
       <c r="D2210" t="s">
         <v>2212</v>
@@ -39690,7 +39978,7 @@
         <v>2</v>
       </c>
       <c r="C2211">
-        <v>5610</v>
+        <v>5530</v>
       </c>
       <c r="D2211" t="s">
         <v>2213</v>
@@ -39704,7 +39992,7 @@
         <v>3</v>
       </c>
       <c r="C2212">
-        <v>5540</v>
+        <v>5480</v>
       </c>
       <c r="D2212" t="s">
         <v>2214</v>
@@ -39718,7 +40006,7 @@
         <v>4</v>
       </c>
       <c r="C2213">
-        <v>5470</v>
+        <v>5420</v>
       </c>
       <c r="D2213" t="s">
         <v>2215</v>
@@ -39732,7 +40020,7 @@
         <v>5</v>
       </c>
       <c r="C2214">
-        <v>5420</v>
+        <v>5360</v>
       </c>
       <c r="D2214" t="s">
         <v>2216</v>
@@ -39746,7 +40034,7 @@
         <v>6</v>
       </c>
       <c r="C2215">
-        <v>5370</v>
+        <v>5310</v>
       </c>
       <c r="D2215" t="s">
         <v>2217</v>
@@ -39760,7 +40048,7 @@
         <v>7</v>
       </c>
       <c r="C2216">
-        <v>5330</v>
+        <v>5280</v>
       </c>
       <c r="D2216" t="s">
         <v>2218</v>
@@ -39774,7 +40062,7 @@
         <v>8</v>
       </c>
       <c r="C2217">
-        <v>5310</v>
+        <v>5250</v>
       </c>
       <c r="D2217" t="s">
         <v>2219</v>
@@ -39788,7 +40076,7 @@
         <v>9</v>
       </c>
       <c r="C2218">
-        <v>5290</v>
+        <v>5240</v>
       </c>
       <c r="D2218" t="s">
         <v>2220</v>
@@ -39802,7 +40090,7 @@
         <v>10</v>
       </c>
       <c r="C2219">
-        <v>5270</v>
+        <v>5220</v>
       </c>
       <c r="D2219" t="s">
         <v>2221</v>
@@ -39816,7 +40104,7 @@
         <v>11</v>
       </c>
       <c r="C2220">
-        <v>5260</v>
+        <v>5210</v>
       </c>
       <c r="D2220" t="s">
         <v>2222</v>
@@ -39830,7 +40118,7 @@
         <v>12</v>
       </c>
       <c r="C2221">
-        <v>5250</v>
+        <v>5200</v>
       </c>
       <c r="D2221" t="s">
         <v>2223</v>
@@ -39844,7 +40132,7 @@
         <v>13</v>
       </c>
       <c r="C2222">
-        <v>5240</v>
+        <v>5200</v>
       </c>
       <c r="D2222" t="s">
         <v>2224</v>
@@ -39858,7 +40146,7 @@
         <v>14</v>
       </c>
       <c r="C2223">
-        <v>5240</v>
+        <v>5200</v>
       </c>
       <c r="D2223" t="s">
         <v>2225</v>
@@ -39872,7 +40160,7 @@
         <v>15</v>
       </c>
       <c r="C2224">
-        <v>5240</v>
+        <v>5210</v>
       </c>
       <c r="D2224" t="s">
         <v>2226</v>
@@ -39886,7 +40174,7 @@
         <v>16</v>
       </c>
       <c r="C2225">
-        <v>5240</v>
+        <v>5220</v>
       </c>
       <c r="D2225" t="s">
         <v>2227</v>
@@ -39900,7 +40188,7 @@
         <v>17</v>
       </c>
       <c r="C2226">
-        <v>5250</v>
+        <v>5230</v>
       </c>
       <c r="D2226" t="s">
         <v>2228</v>
@@ -39914,7 +40202,7 @@
         <v>18</v>
       </c>
       <c r="C2227">
-        <v>5260</v>
+        <v>5240</v>
       </c>
       <c r="D2227" t="s">
         <v>2229</v>
@@ -39928,7 +40216,7 @@
         <v>19</v>
       </c>
       <c r="C2228">
-        <v>5280</v>
+        <v>5250</v>
       </c>
       <c r="D2228" t="s">
         <v>2230</v>
@@ -39942,7 +40230,7 @@
         <v>20</v>
       </c>
       <c r="C2229">
-        <v>5310</v>
+        <v>5280</v>
       </c>
       <c r="D2229" t="s">
         <v>2231</v>
@@ -39956,7 +40244,7 @@
         <v>21</v>
       </c>
       <c r="C2230">
-        <v>5350</v>
+        <v>5330</v>
       </c>
       <c r="D2230" t="s">
         <v>2232</v>
@@ -39970,7 +40258,7 @@
         <v>22</v>
       </c>
       <c r="C2231">
-        <v>5400</v>
+        <v>5380</v>
       </c>
       <c r="D2231" t="s">
         <v>2233</v>
@@ -39998,7 +40286,7 @@
         <v>24</v>
       </c>
       <c r="C2233">
-        <v>5550</v>
+        <v>5540</v>
       </c>
       <c r="D2233" t="s">
         <v>2235</v>
@@ -40026,7 +40314,7 @@
         <v>26</v>
       </c>
       <c r="C2235">
-        <v>5750</v>
+        <v>5740</v>
       </c>
       <c r="D2235" t="s">
         <v>2237</v>
@@ -40040,7 +40328,7 @@
         <v>27</v>
       </c>
       <c r="C2236">
-        <v>5870</v>
+        <v>5840</v>
       </c>
       <c r="D2236" t="s">
         <v>2238</v>
@@ -40054,7 +40342,7 @@
         <v>28</v>
       </c>
       <c r="C2237">
-        <v>5990</v>
+        <v>5930</v>
       </c>
       <c r="D2237" t="s">
         <v>2239</v>
@@ -40068,7 +40356,7 @@
         <v>29</v>
       </c>
       <c r="C2238">
-        <v>6120</v>
+        <v>6000</v>
       </c>
       <c r="D2238" t="s">
         <v>2240</v>
@@ -40082,7 +40370,7 @@
         <v>30</v>
       </c>
       <c r="C2239">
-        <v>6240</v>
+        <v>6050</v>
       </c>
       <c r="D2239" t="s">
         <v>2241</v>
@@ -40096,7 +40384,7 @@
         <v>31</v>
       </c>
       <c r="C2240">
-        <v>6330</v>
+        <v>6080</v>
       </c>
       <c r="D2240" t="s">
         <v>2242</v>
@@ -40110,7 +40398,7 @@
         <v>32</v>
       </c>
       <c r="C2241">
-        <v>6400</v>
+        <v>6080</v>
       </c>
       <c r="D2241" t="s">
         <v>2243</v>
@@ -40124,7 +40412,7 @@
         <v>33</v>
       </c>
       <c r="C2242">
-        <v>6440</v>
+        <v>6050</v>
       </c>
       <c r="D2242" t="s">
         <v>2244</v>
@@ -40138,7 +40426,7 @@
         <v>34</v>
       </c>
       <c r="C2243">
-        <v>6450</v>
+        <v>5990</v>
       </c>
       <c r="D2243" t="s">
         <v>2245</v>
@@ -40152,7 +40440,7 @@
         <v>35</v>
       </c>
       <c r="C2244">
-        <v>6420</v>
+        <v>5890</v>
       </c>
       <c r="D2244" t="s">
         <v>2246</v>
@@ -40166,7 +40454,7 @@
         <v>36</v>
       </c>
       <c r="C2245">
-        <v>6360</v>
+        <v>5770</v>
       </c>
       <c r="D2245" t="s">
         <v>2247</v>
@@ -40180,7 +40468,7 @@
         <v>37</v>
       </c>
       <c r="C2246">
-        <v>6270</v>
+        <v>5630</v>
       </c>
       <c r="D2246" t="s">
         <v>2248</v>
@@ -40194,7 +40482,7 @@
         <v>38</v>
       </c>
       <c r="C2247">
-        <v>6180</v>
+        <v>5460</v>
       </c>
       <c r="D2247" t="s">
         <v>2249</v>
@@ -40208,7 +40496,7 @@
         <v>39</v>
       </c>
       <c r="C2248">
-        <v>6090</v>
+        <v>5290</v>
       </c>
       <c r="D2248" t="s">
         <v>2250</v>
@@ -40222,7 +40510,7 @@
         <v>40</v>
       </c>
       <c r="C2249">
-        <v>6010</v>
+        <v>5120</v>
       </c>
       <c r="D2249" t="s">
         <v>2251</v>
@@ -40236,7 +40524,7 @@
         <v>41</v>
       </c>
       <c r="C2250">
-        <v>5920</v>
+        <v>4950</v>
       </c>
       <c r="D2250" t="s">
         <v>2252</v>
@@ -40250,7 +40538,7 @@
         <v>42</v>
       </c>
       <c r="C2251">
-        <v>5830</v>
+        <v>4800</v>
       </c>
       <c r="D2251" t="s">
         <v>2253</v>
@@ -40264,7 +40552,7 @@
         <v>43</v>
       </c>
       <c r="C2252">
-        <v>5740</v>
+        <v>4660</v>
       </c>
       <c r="D2252" t="s">
         <v>2254</v>
@@ -40278,7 +40566,7 @@
         <v>44</v>
       </c>
       <c r="C2253">
-        <v>5630</v>
+        <v>4540</v>
       </c>
       <c r="D2253" t="s">
         <v>2255</v>
@@ -40292,7 +40580,7 @@
         <v>45</v>
       </c>
       <c r="C2254">
-        <v>5520</v>
+        <v>4450</v>
       </c>
       <c r="D2254" t="s">
         <v>2256</v>
@@ -40306,7 +40594,7 @@
         <v>46</v>
       </c>
       <c r="C2255">
-        <v>5410</v>
+        <v>4380</v>
       </c>
       <c r="D2255" t="s">
         <v>2257</v>
@@ -40320,7 +40608,7 @@
         <v>47</v>
       </c>
       <c r="C2256">
-        <v>5330</v>
+        <v>4330</v>
       </c>
       <c r="D2256" t="s">
         <v>2258</v>
@@ -40334,7 +40622,7 @@
         <v>48</v>
       </c>
       <c r="C2257">
-        <v>5250</v>
+        <v>4300</v>
       </c>
       <c r="D2257" t="s">
         <v>2259</v>
@@ -40348,7 +40636,7 @@
         <v>49</v>
       </c>
       <c r="C2258">
-        <v>5200</v>
+        <v>4280</v>
       </c>
       <c r="D2258" t="s">
         <v>2260</v>
@@ -40362,7 +40650,7 @@
         <v>50</v>
       </c>
       <c r="C2259">
-        <v>5150</v>
+        <v>4280</v>
       </c>
       <c r="D2259" t="s">
         <v>2261</v>
@@ -40376,7 +40664,7 @@
         <v>51</v>
       </c>
       <c r="C2260">
-        <v>5130</v>
+        <v>4280</v>
       </c>
       <c r="D2260" t="s">
         <v>2262</v>
@@ -40390,7 +40678,7 @@
         <v>52</v>
       </c>
       <c r="C2261">
-        <v>5120</v>
+        <v>4300</v>
       </c>
       <c r="D2261" t="s">
         <v>2263</v>
@@ -40404,7 +40692,7 @@
         <v>53</v>
       </c>
       <c r="C2262">
-        <v>5120</v>
+        <v>4310</v>
       </c>
       <c r="D2262" t="s">
         <v>2264</v>
@@ -40418,7 +40706,7 @@
         <v>54</v>
       </c>
       <c r="C2263">
-        <v>5120</v>
+        <v>4340</v>
       </c>
       <c r="D2263" t="s">
         <v>2265</v>
@@ -40432,7 +40720,7 @@
         <v>55</v>
       </c>
       <c r="C2264">
-        <v>5090</v>
+        <v>4370</v>
       </c>
       <c r="D2264" t="s">
         <v>2266</v>
@@ -40446,7 +40734,7 @@
         <v>56</v>
       </c>
       <c r="C2265">
-        <v>5050</v>
+        <v>4400</v>
       </c>
       <c r="D2265" t="s">
         <v>2267</v>
@@ -40460,7 +40748,7 @@
         <v>57</v>
       </c>
       <c r="C2266">
-        <v>5010</v>
+        <v>4440</v>
       </c>
       <c r="D2266" t="s">
         <v>2268</v>
@@ -40474,7 +40762,7 @@
         <v>58</v>
       </c>
       <c r="C2267">
-        <v>4980</v>
+        <v>4480</v>
       </c>
       <c r="D2267" t="s">
         <v>2269</v>
@@ -40488,7 +40776,7 @@
         <v>59</v>
       </c>
       <c r="C2268">
-        <v>5000</v>
+        <v>4530</v>
       </c>
       <c r="D2268" t="s">
         <v>2270</v>
@@ -40502,7 +40790,7 @@
         <v>60</v>
       </c>
       <c r="C2269">
-        <v>5050</v>
+        <v>4570</v>
       </c>
       <c r="D2269" t="s">
         <v>2271</v>
@@ -40516,7 +40804,7 @@
         <v>61</v>
       </c>
       <c r="C2270">
-        <v>5130</v>
+        <v>4630</v>
       </c>
       <c r="D2270" t="s">
         <v>2272</v>
@@ -40530,7 +40818,7 @@
         <v>62</v>
       </c>
       <c r="C2271">
-        <v>5200</v>
+        <v>4690</v>
       </c>
       <c r="D2271" t="s">
         <v>2273</v>
@@ -40544,7 +40832,7 @@
         <v>63</v>
       </c>
       <c r="C2272">
-        <v>5250</v>
+        <v>4750</v>
       </c>
       <c r="D2272" t="s">
         <v>2274</v>
@@ -40558,7 +40846,7 @@
         <v>64</v>
       </c>
       <c r="C2273">
-        <v>5300</v>
+        <v>4810</v>
       </c>
       <c r="D2273" t="s">
         <v>2275</v>
@@ -40572,7 +40860,7 @@
         <v>65</v>
       </c>
       <c r="C2274">
-        <v>5330</v>
+        <v>4900</v>
       </c>
       <c r="D2274" t="s">
         <v>2276</v>
@@ -40586,7 +40874,7 @@
         <v>66</v>
       </c>
       <c r="C2275">
-        <v>5380</v>
+        <v>4990</v>
       </c>
       <c r="D2275" t="s">
         <v>2277</v>
@@ -40600,7 +40888,7 @@
         <v>67</v>
       </c>
       <c r="C2276">
-        <v>5440</v>
+        <v>5100</v>
       </c>
       <c r="D2276" t="s">
         <v>2278</v>
@@ -40614,7 +40902,7 @@
         <v>68</v>
       </c>
       <c r="C2277">
-        <v>5520</v>
+        <v>5220</v>
       </c>
       <c r="D2277" t="s">
         <v>2279</v>
@@ -40628,7 +40916,7 @@
         <v>69</v>
       </c>
       <c r="C2278">
-        <v>5620</v>
+        <v>5330</v>
       </c>
       <c r="D2278" t="s">
         <v>2280</v>
@@ -40642,7 +40930,7 @@
         <v>70</v>
       </c>
       <c r="C2279">
-        <v>5730</v>
+        <v>5450</v>
       </c>
       <c r="D2279" t="s">
         <v>2281</v>
@@ -40656,7 +40944,7 @@
         <v>71</v>
       </c>
       <c r="C2280">
-        <v>5840</v>
+        <v>5560</v>
       </c>
       <c r="D2280" t="s">
         <v>2282</v>
@@ -40670,7 +40958,7 @@
         <v>72</v>
       </c>
       <c r="C2281">
-        <v>5960</v>
+        <v>5680</v>
       </c>
       <c r="D2281" t="s">
         <v>2283</v>
@@ -40684,7 +40972,7 @@
         <v>73</v>
       </c>
       <c r="C2282">
-        <v>6090</v>
+        <v>5800</v>
       </c>
       <c r="D2282" t="s">
         <v>2284</v>
@@ -40698,7 +40986,7 @@
         <v>74</v>
       </c>
       <c r="C2283">
-        <v>6200</v>
+        <v>5920</v>
       </c>
       <c r="D2283" t="s">
         <v>2285</v>
@@ -40712,7 +41000,7 @@
         <v>75</v>
       </c>
       <c r="C2284">
-        <v>6300</v>
+        <v>6040</v>
       </c>
       <c r="D2284" t="s">
         <v>2286</v>
@@ -40726,7 +41014,7 @@
         <v>76</v>
       </c>
       <c r="C2285">
-        <v>6400</v>
+        <v>6170</v>
       </c>
       <c r="D2285" t="s">
         <v>2287</v>
@@ -40740,7 +41028,7 @@
         <v>77</v>
       </c>
       <c r="C2286">
-        <v>6480</v>
+        <v>6310</v>
       </c>
       <c r="D2286" t="s">
         <v>2288</v>
@@ -40754,7 +41042,7 @@
         <v>78</v>
       </c>
       <c r="C2287">
-        <v>6570</v>
+        <v>6450</v>
       </c>
       <c r="D2287" t="s">
         <v>2289</v>
@@ -40768,7 +41056,7 @@
         <v>79</v>
       </c>
       <c r="C2288">
-        <v>6680</v>
+        <v>6580</v>
       </c>
       <c r="D2288" t="s">
         <v>2290</v>
@@ -40782,7 +41070,7 @@
         <v>80</v>
       </c>
       <c r="C2289">
-        <v>6810</v>
+        <v>6700</v>
       </c>
       <c r="D2289" t="s">
         <v>2291</v>
@@ -40796,7 +41084,7 @@
         <v>81</v>
       </c>
       <c r="C2290">
-        <v>6940</v>
+        <v>6820</v>
       </c>
       <c r="D2290" t="s">
         <v>2292</v>
@@ -40810,7 +41098,7 @@
         <v>82</v>
       </c>
       <c r="C2291">
-        <v>7040</v>
+        <v>6920</v>
       </c>
       <c r="D2291" t="s">
         <v>2293</v>
@@ -40824,7 +41112,7 @@
         <v>83</v>
       </c>
       <c r="C2292">
-        <v>7110</v>
+        <v>7000</v>
       </c>
       <c r="D2292" t="s">
         <v>2294</v>
@@ -40838,7 +41126,7 @@
         <v>84</v>
       </c>
       <c r="C2293">
-        <v>7130</v>
+        <v>7050</v>
       </c>
       <c r="D2293" t="s">
         <v>2295</v>
@@ -40852,7 +41140,7 @@
         <v>85</v>
       </c>
       <c r="C2294">
-        <v>7110</v>
+        <v>7050</v>
       </c>
       <c r="D2294" t="s">
         <v>2296</v>
@@ -40866,7 +41154,7 @@
         <v>86</v>
       </c>
       <c r="C2295">
-        <v>7060</v>
+        <v>7000</v>
       </c>
       <c r="D2295" t="s">
         <v>2297</v>
@@ -40880,7 +41168,7 @@
         <v>87</v>
       </c>
       <c r="C2296">
-        <v>6980</v>
+        <v>6920</v>
       </c>
       <c r="D2296" t="s">
         <v>2298</v>
@@ -40894,7 +41182,7 @@
         <v>88</v>
       </c>
       <c r="C2297">
-        <v>6870</v>
+        <v>6800</v>
       </c>
       <c r="D2297" t="s">
         <v>2299</v>
@@ -40908,7 +41196,7 @@
         <v>89</v>
       </c>
       <c r="C2298">
-        <v>6730</v>
+        <v>6650</v>
       </c>
       <c r="D2298" t="s">
         <v>2300</v>
@@ -40922,7 +41210,7 @@
         <v>90</v>
       </c>
       <c r="C2299">
-        <v>6580</v>
+        <v>6500</v>
       </c>
       <c r="D2299" t="s">
         <v>2301</v>
@@ -40936,7 +41224,7 @@
         <v>91</v>
       </c>
       <c r="C2300">
-        <v>6430</v>
+        <v>6340</v>
       </c>
       <c r="D2300" t="s">
         <v>2302</v>
@@ -40950,7 +41238,7 @@
         <v>92</v>
       </c>
       <c r="C2301">
-        <v>6280</v>
+        <v>6160</v>
       </c>
       <c r="D2301" t="s">
         <v>2303</v>
@@ -40964,7 +41252,7 @@
         <v>93</v>
       </c>
       <c r="C2302">
-        <v>6140</v>
+        <v>6000</v>
       </c>
       <c r="D2302" t="s">
         <v>2304</v>
@@ -40978,7 +41266,7 @@
         <v>94</v>
       </c>
       <c r="C2303">
-        <v>6000</v>
+        <v>5850</v>
       </c>
       <c r="D2303" t="s">
         <v>2305</v>
@@ -40992,7 +41280,7 @@
         <v>95</v>
       </c>
       <c r="C2304">
-        <v>5880</v>
+        <v>5720</v>
       </c>
       <c r="D2304" t="s">
         <v>2306</v>
@@ -41006,7 +41294,7 @@
         <v>96</v>
       </c>
       <c r="C2305">
-        <v>5770</v>
+        <v>5600</v>
       </c>
       <c r="D2305" t="s">
         <v>2307</v>
@@ -41020,7 +41308,7 @@
         <v>1</v>
       </c>
       <c r="C2306">
-        <v>5610</v>
+        <v>5560</v>
       </c>
       <c r="D2306" t="s">
         <v>2308</v>
@@ -41034,7 +41322,7 @@
         <v>2</v>
       </c>
       <c r="C2307">
-        <v>5530</v>
+        <v>5520</v>
       </c>
       <c r="D2307" t="s">
         <v>2309</v>
@@ -41062,7 +41350,7 @@
         <v>4</v>
       </c>
       <c r="C2309">
-        <v>5380</v>
+        <v>5370</v>
       </c>
       <c r="D2309" t="s">
         <v>2311</v>
@@ -41076,7 +41364,7 @@
         <v>5</v>
       </c>
       <c r="C2310">
-        <v>5320</v>
+        <v>5280</v>
       </c>
       <c r="D2310" t="s">
         <v>2312</v>
@@ -41090,7 +41378,7 @@
         <v>6</v>
       </c>
       <c r="C2311">
-        <v>5270</v>
+        <v>5220</v>
       </c>
       <c r="D2311" t="s">
         <v>2313</v>
@@ -41104,7 +41392,7 @@
         <v>7</v>
       </c>
       <c r="C2312">
-        <v>5230</v>
+        <v>5200</v>
       </c>
       <c r="D2312" t="s">
         <v>2314</v>
@@ -41118,7 +41406,7 @@
         <v>8</v>
       </c>
       <c r="C2313">
-        <v>5200</v>
+        <v>5180</v>
       </c>
       <c r="D2313" t="s">
         <v>2315</v>
@@ -41146,7 +41434,7 @@
         <v>10</v>
       </c>
       <c r="C2315">
-        <v>5150</v>
+        <v>5160</v>
       </c>
       <c r="D2315" t="s">
         <v>2317</v>
@@ -41160,7 +41448,7 @@
         <v>11</v>
       </c>
       <c r="C2316">
-        <v>5130</v>
+        <v>5150</v>
       </c>
       <c r="D2316" t="s">
         <v>2318</v>
@@ -41174,7 +41462,7 @@
         <v>12</v>
       </c>
       <c r="C2317">
-        <v>5110</v>
+        <v>5150</v>
       </c>
       <c r="D2317" t="s">
         <v>2319</v>
@@ -41188,7 +41476,7 @@
         <v>13</v>
       </c>
       <c r="C2318">
-        <v>5080</v>
+        <v>5150</v>
       </c>
       <c r="D2318" t="s">
         <v>2320</v>
@@ -41202,7 +41490,7 @@
         <v>14</v>
       </c>
       <c r="C2319">
-        <v>5070</v>
+        <v>5150</v>
       </c>
       <c r="D2319" t="s">
         <v>2321</v>
@@ -41216,7 +41504,7 @@
         <v>15</v>
       </c>
       <c r="C2320">
-        <v>5060</v>
+        <v>5150</v>
       </c>
       <c r="D2320" t="s">
         <v>2322</v>
@@ -41230,7 +41518,7 @@
         <v>16</v>
       </c>
       <c r="C2321">
-        <v>5060</v>
+        <v>5150</v>
       </c>
       <c r="D2321" t="s">
         <v>2323</v>
@@ -41244,7 +41532,7 @@
         <v>17</v>
       </c>
       <c r="C2322">
-        <v>5060</v>
+        <v>5170</v>
       </c>
       <c r="D2322" t="s">
         <v>2324</v>
@@ -41258,7 +41546,7 @@
         <v>18</v>
       </c>
       <c r="C2323">
-        <v>5070</v>
+        <v>5180</v>
       </c>
       <c r="D2323" t="s">
         <v>2325</v>
@@ -41272,7 +41560,7 @@
         <v>19</v>
       </c>
       <c r="C2324">
-        <v>5090</v>
+        <v>5190</v>
       </c>
       <c r="D2324" t="s">
         <v>2326</v>
@@ -41286,7 +41574,7 @@
         <v>20</v>
       </c>
       <c r="C2325">
-        <v>5110</v>
+        <v>5220</v>
       </c>
       <c r="D2325" t="s">
         <v>2327</v>
@@ -41300,7 +41588,7 @@
         <v>21</v>
       </c>
       <c r="C2326">
-        <v>5140</v>
+        <v>5230</v>
       </c>
       <c r="D2326" t="s">
         <v>2328</v>
@@ -41314,7 +41602,7 @@
         <v>22</v>
       </c>
       <c r="C2327">
-        <v>5150</v>
+        <v>5240</v>
       </c>
       <c r="D2327" t="s">
         <v>2329</v>
@@ -41328,7 +41616,7 @@
         <v>23</v>
       </c>
       <c r="C2328">
-        <v>5160</v>
+        <v>5250</v>
       </c>
       <c r="D2328" t="s">
         <v>2330</v>
@@ -41342,7 +41630,7 @@
         <v>24</v>
       </c>
       <c r="C2329">
-        <v>5150</v>
+        <v>5250</v>
       </c>
       <c r="D2329" t="s">
         <v>2331</v>
@@ -41356,7 +41644,7 @@
         <v>25</v>
       </c>
       <c r="C2330">
-        <v>5130</v>
+        <v>5240</v>
       </c>
       <c r="D2330" t="s">
         <v>2332</v>
@@ -41370,7 +41658,7 @@
         <v>26</v>
       </c>
       <c r="C2331">
-        <v>5130</v>
+        <v>5220</v>
       </c>
       <c r="D2331" t="s">
         <v>2333</v>
@@ -41384,7 +41672,7 @@
         <v>27</v>
       </c>
       <c r="C2332">
-        <v>5140</v>
+        <v>5170</v>
       </c>
       <c r="D2332" t="s">
         <v>2334</v>
@@ -41398,7 +41686,7 @@
         <v>28</v>
       </c>
       <c r="C2333">
-        <v>5180</v>
+        <v>5170</v>
       </c>
       <c r="D2333" t="s">
         <v>2335</v>
@@ -41412,7 +41700,7 @@
         <v>29</v>
       </c>
       <c r="C2334">
-        <v>5230</v>
+        <v>5180</v>
       </c>
       <c r="D2334" t="s">
         <v>2336</v>
@@ -41426,7 +41714,7 @@
         <v>30</v>
       </c>
       <c r="C2335">
-        <v>5270</v>
+        <v>5180</v>
       </c>
       <c r="D2335" t="s">
         <v>2337</v>
@@ -41440,7 +41728,7 @@
         <v>31</v>
       </c>
       <c r="C2336">
-        <v>5310</v>
+        <v>5180</v>
       </c>
       <c r="D2336" t="s">
         <v>2338</v>
@@ -41454,7 +41742,7 @@
         <v>32</v>
       </c>
       <c r="C2337">
-        <v>5350</v>
+        <v>5170</v>
       </c>
       <c r="D2337" t="s">
         <v>2339</v>
@@ -41468,7 +41756,7 @@
         <v>33</v>
       </c>
       <c r="C2338">
-        <v>5370</v>
+        <v>5150</v>
       </c>
       <c r="D2338" t="s">
         <v>2340</v>
@@ -41482,7 +41770,7 @@
         <v>34</v>
       </c>
       <c r="C2339">
-        <v>5370</v>
+        <v>5100</v>
       </c>
       <c r="D2339" t="s">
         <v>2341</v>
@@ -41496,7 +41784,7 @@
         <v>35</v>
       </c>
       <c r="C2340">
-        <v>5340</v>
+        <v>5010</v>
       </c>
       <c r="D2340" t="s">
         <v>2342</v>
@@ -41510,7 +41798,7 @@
         <v>36</v>
       </c>
       <c r="C2341">
-        <v>5270</v>
+        <v>4890</v>
       </c>
       <c r="D2341" t="s">
         <v>2343</v>
@@ -41524,7 +41812,7 @@
         <v>37</v>
       </c>
       <c r="C2342">
-        <v>5180</v>
+        <v>4730</v>
       </c>
       <c r="D2342" t="s">
         <v>2344</v>
@@ -41538,7 +41826,7 @@
         <v>38</v>
       </c>
       <c r="C2343">
-        <v>5090</v>
+        <v>4600</v>
       </c>
       <c r="D2343" t="s">
         <v>2345</v>
@@ -41552,7 +41840,7 @@
         <v>39</v>
       </c>
       <c r="C2344">
-        <v>5010</v>
+        <v>4490</v>
       </c>
       <c r="D2344" t="s">
         <v>2346</v>
@@ -41566,7 +41854,7 @@
         <v>40</v>
       </c>
       <c r="C2345">
-        <v>4950</v>
+        <v>4410</v>
       </c>
       <c r="D2345" t="s">
         <v>2347</v>
@@ -41580,7 +41868,7 @@
         <v>41</v>
       </c>
       <c r="C2346">
-        <v>4890</v>
+        <v>4350</v>
       </c>
       <c r="D2346" t="s">
         <v>2348</v>
@@ -41594,7 +41882,7 @@
         <v>42</v>
       </c>
       <c r="C2347">
-        <v>4830</v>
+        <v>4270</v>
       </c>
       <c r="D2347" t="s">
         <v>2349</v>
@@ -41608,7 +41896,7 @@
         <v>43</v>
       </c>
       <c r="C2348">
-        <v>4760</v>
+        <v>4170</v>
       </c>
       <c r="D2348" t="s">
         <v>2350</v>
@@ -41622,7 +41910,7 @@
         <v>44</v>
       </c>
       <c r="C2349">
-        <v>4680</v>
+        <v>4040</v>
       </c>
       <c r="D2349" t="s">
         <v>2351</v>
@@ -41636,7 +41924,7 @@
         <v>45</v>
       </c>
       <c r="C2350">
-        <v>4590</v>
+        <v>3900</v>
       </c>
       <c r="D2350" t="s">
         <v>2352</v>
@@ -41650,7 +41938,7 @@
         <v>46</v>
       </c>
       <c r="C2351">
-        <v>4510</v>
+        <v>3800</v>
       </c>
       <c r="D2351" t="s">
         <v>2353</v>
@@ -41664,7 +41952,7 @@
         <v>47</v>
       </c>
       <c r="C2352">
-        <v>4450</v>
+        <v>3760</v>
       </c>
       <c r="D2352" t="s">
         <v>2354</v>
@@ -41678,7 +41966,7 @@
         <v>48</v>
       </c>
       <c r="C2353">
-        <v>4390</v>
+        <v>3780</v>
       </c>
       <c r="D2353" t="s">
         <v>2355</v>
@@ -41692,7 +41980,7 @@
         <v>49</v>
       </c>
       <c r="C2354">
-        <v>4340</v>
+        <v>3840</v>
       </c>
       <c r="D2354" t="s">
         <v>2356</v>
@@ -41706,7 +41994,7 @@
         <v>50</v>
       </c>
       <c r="C2355">
-        <v>4300</v>
+        <v>3880</v>
       </c>
       <c r="D2355" t="s">
         <v>2357</v>
@@ -41720,7 +42008,7 @@
         <v>51</v>
       </c>
       <c r="C2356">
-        <v>4270</v>
+        <v>3900</v>
       </c>
       <c r="D2356" t="s">
         <v>2358</v>
@@ -41734,7 +42022,7 @@
         <v>52</v>
       </c>
       <c r="C2357">
-        <v>4250</v>
+        <v>3870</v>
       </c>
       <c r="D2357" t="s">
         <v>2359</v>
@@ -41748,7 +42036,7 @@
         <v>53</v>
       </c>
       <c r="C2358">
-        <v>4240</v>
+        <v>3830</v>
       </c>
       <c r="D2358" t="s">
         <v>2360</v>
@@ -41762,7 +42050,7 @@
         <v>54</v>
       </c>
       <c r="C2359">
-        <v>4220</v>
+        <v>3780</v>
       </c>
       <c r="D2359" t="s">
         <v>2361</v>
@@ -41776,7 +42064,7 @@
         <v>55</v>
       </c>
       <c r="C2360">
-        <v>4190</v>
+        <v>3740</v>
       </c>
       <c r="D2360" t="s">
         <v>2362</v>
@@ -41790,7 +42078,7 @@
         <v>56</v>
       </c>
       <c r="C2361">
-        <v>4150</v>
+        <v>3710</v>
       </c>
       <c r="D2361" t="s">
         <v>2363</v>
@@ -41804,7 +42092,7 @@
         <v>57</v>
       </c>
       <c r="C2362">
-        <v>4110</v>
+        <v>3690</v>
       </c>
       <c r="D2362" t="s">
         <v>2364</v>
@@ -41818,7 +42106,7 @@
         <v>58</v>
       </c>
       <c r="C2363">
-        <v>4100</v>
+        <v>3700</v>
       </c>
       <c r="D2363" t="s">
         <v>2365</v>
@@ -41832,7 +42120,7 @@
         <v>59</v>
       </c>
       <c r="C2364">
-        <v>4120</v>
+        <v>3740</v>
       </c>
       <c r="D2364" t="s">
         <v>2366</v>
@@ -41846,7 +42134,7 @@
         <v>60</v>
       </c>
       <c r="C2365">
-        <v>4170</v>
+        <v>3810</v>
       </c>
       <c r="D2365" t="s">
         <v>2367</v>
@@ -41860,7 +42148,7 @@
         <v>61</v>
       </c>
       <c r="C2366">
-        <v>4260</v>
+        <v>3910</v>
       </c>
       <c r="D2366" t="s">
         <v>2368</v>
@@ -41874,7 +42162,7 @@
         <v>62</v>
       </c>
       <c r="C2367">
-        <v>4340</v>
+        <v>4010</v>
       </c>
       <c r="D2367" t="s">
         <v>2369</v>
@@ -41888,7 +42176,7 @@
         <v>63</v>
       </c>
       <c r="C2368">
-        <v>4400</v>
+        <v>4100</v>
       </c>
       <c r="D2368" t="s">
         <v>2370</v>
@@ -41902,7 +42190,7 @@
         <v>64</v>
       </c>
       <c r="C2369">
-        <v>4460</v>
+        <v>4190</v>
       </c>
       <c r="D2369" t="s">
         <v>2371</v>
@@ -41916,7 +42204,7 @@
         <v>65</v>
       </c>
       <c r="C2370">
-        <v>4510</v>
+        <v>4270</v>
       </c>
       <c r="D2370" t="s">
         <v>2372</v>
@@ -41930,7 +42218,7 @@
         <v>66</v>
       </c>
       <c r="C2371">
-        <v>4580</v>
+        <v>4350</v>
       </c>
       <c r="D2371" t="s">
         <v>2373</v>
@@ -41944,7 +42232,7 @@
         <v>67</v>
       </c>
       <c r="C2372">
-        <v>4660</v>
+        <v>4460</v>
       </c>
       <c r="D2372" t="s">
         <v>2374</v>
@@ -41958,7 +42246,7 @@
         <v>68</v>
       </c>
       <c r="C2373">
-        <v>4750</v>
+        <v>4570</v>
       </c>
       <c r="D2373" t="s">
         <v>2375</v>
@@ -41972,7 +42260,7 @@
         <v>69</v>
       </c>
       <c r="C2374">
-        <v>4870</v>
+        <v>4690</v>
       </c>
       <c r="D2374" t="s">
         <v>2376</v>
@@ -41986,7 +42274,7 @@
         <v>70</v>
       </c>
       <c r="C2375">
-        <v>4980</v>
+        <v>4820</v>
       </c>
       <c r="D2375" t="s">
         <v>2377</v>
@@ -42000,7 +42288,7 @@
         <v>71</v>
       </c>
       <c r="C2376">
-        <v>5110</v>
+        <v>4950</v>
       </c>
       <c r="D2376" t="s">
         <v>2378</v>
@@ -42014,7 +42302,7 @@
         <v>72</v>
       </c>
       <c r="C2377">
-        <v>5230</v>
+        <v>5090</v>
       </c>
       <c r="D2377" t="s">
         <v>2379</v>
@@ -42028,7 +42316,7 @@
         <v>73</v>
       </c>
       <c r="C2378">
-        <v>5360</v>
+        <v>5230</v>
       </c>
       <c r="D2378" t="s">
         <v>2380</v>
@@ -42042,7 +42330,7 @@
         <v>74</v>
       </c>
       <c r="C2379">
-        <v>5480</v>
+        <v>5360</v>
       </c>
       <c r="D2379" t="s">
         <v>2381</v>
@@ -42056,7 +42344,7 @@
         <v>75</v>
       </c>
       <c r="C2380">
-        <v>5600</v>
+        <v>5480</v>
       </c>
       <c r="D2380" t="s">
         <v>2382</v>
@@ -42070,7 +42358,7 @@
         <v>76</v>
       </c>
       <c r="C2381">
-        <v>5700</v>
+        <v>5580</v>
       </c>
       <c r="D2381" t="s">
         <v>2383</v>
@@ -42084,7 +42372,7 @@
         <v>77</v>
       </c>
       <c r="C2382">
-        <v>5800</v>
+        <v>5670</v>
       </c>
       <c r="D2382" t="s">
         <v>2384</v>
@@ -42098,7 +42386,7 @@
         <v>78</v>
       </c>
       <c r="C2383">
-        <v>5900</v>
+        <v>5770</v>
       </c>
       <c r="D2383" t="s">
         <v>2385</v>
@@ -42112,7 +42400,7 @@
         <v>79</v>
       </c>
       <c r="C2384">
-        <v>6030</v>
+        <v>5900</v>
       </c>
       <c r="D2384" t="s">
         <v>2386</v>
@@ -42126,7 +42414,7 @@
         <v>80</v>
       </c>
       <c r="C2385">
-        <v>6160</v>
+        <v>6040</v>
       </c>
       <c r="D2385" t="s">
         <v>2387</v>
@@ -42140,7 +42428,7 @@
         <v>81</v>
       </c>
       <c r="C2386">
-        <v>6300</v>
+        <v>6190</v>
       </c>
       <c r="D2386" t="s">
         <v>2388</v>
@@ -42154,7 +42442,7 @@
         <v>82</v>
       </c>
       <c r="C2387">
-        <v>6420</v>
+        <v>6310</v>
       </c>
       <c r="D2387" t="s">
         <v>2389</v>
@@ -42168,7 +42456,7 @@
         <v>83</v>
       </c>
       <c r="C2388">
-        <v>6490</v>
+        <v>6410</v>
       </c>
       <c r="D2388" t="s">
         <v>2390</v>
@@ -42182,7 +42470,7 @@
         <v>84</v>
       </c>
       <c r="C2389">
-        <v>6520</v>
+        <v>6470</v>
       </c>
       <c r="D2389" t="s">
         <v>2391</v>
@@ -42196,7 +42484,7 @@
         <v>85</v>
       </c>
       <c r="C2390">
-        <v>6520</v>
+        <v>6500</v>
       </c>
       <c r="D2390" t="s">
         <v>2392</v>
@@ -42210,7 +42498,7 @@
         <v>86</v>
       </c>
       <c r="C2391">
-        <v>6480</v>
+        <v>6490</v>
       </c>
       <c r="D2391" t="s">
         <v>2393</v>
@@ -42224,7 +42512,7 @@
         <v>87</v>
       </c>
       <c r="C2392">
-        <v>6410</v>
+        <v>6430</v>
       </c>
       <c r="D2392" t="s">
         <v>2394</v>
@@ -42238,7 +42526,7 @@
         <v>88</v>
       </c>
       <c r="C2393">
-        <v>6320</v>
+        <v>6330</v>
       </c>
       <c r="D2393" t="s">
         <v>2395</v>
@@ -42252,7 +42540,7 @@
         <v>89</v>
       </c>
       <c r="C2394">
-        <v>6190</v>
+        <v>6200</v>
       </c>
       <c r="D2394" t="s">
         <v>2396</v>
@@ -42266,7 +42554,7 @@
         <v>90</v>
       </c>
       <c r="C2395">
-        <v>6070</v>
+        <v>6060</v>
       </c>
       <c r="D2395" t="s">
         <v>2397</v>
@@ -42280,7 +42568,7 @@
         <v>91</v>
       </c>
       <c r="C2396">
-        <v>5950</v>
+        <v>5930</v>
       </c>
       <c r="D2396" t="s">
         <v>2398</v>
@@ -42294,7 +42582,7 @@
         <v>92</v>
       </c>
       <c r="C2397">
-        <v>5830</v>
+        <v>5800</v>
       </c>
       <c r="D2397" t="s">
         <v>2399</v>
@@ -42308,7 +42596,7 @@
         <v>93</v>
       </c>
       <c r="C2398">
-        <v>5710</v>
+        <v>5690</v>
       </c>
       <c r="D2398" t="s">
         <v>2400</v>
@@ -42322,7 +42610,7 @@
         <v>94</v>
       </c>
       <c r="C2399">
-        <v>5590</v>
+        <v>5570</v>
       </c>
       <c r="D2399" t="s">
         <v>2401</v>
@@ -42336,7 +42624,7 @@
         <v>95</v>
       </c>
       <c r="C2400">
-        <v>5480</v>
+        <v>5450</v>
       </c>
       <c r="D2400" t="s">
         <v>2402</v>
@@ -42350,7 +42638,7 @@
         <v>96</v>
       </c>
       <c r="C2401">
-        <v>5370</v>
+        <v>5340</v>
       </c>
       <c r="D2401" t="s">
         <v>2403</v>
@@ -42364,7 +42652,7 @@
         <v>1</v>
       </c>
       <c r="C2402">
-        <v>5260</v>
+        <v>5230</v>
       </c>
       <c r="D2402" t="s">
         <v>2404</v>
@@ -42378,7 +42666,7 @@
         <v>2</v>
       </c>
       <c r="C2403">
-        <v>5160</v>
+        <v>5130</v>
       </c>
       <c r="D2403" t="s">
         <v>2405</v>
@@ -42392,7 +42680,7 @@
         <v>3</v>
       </c>
       <c r="C2404">
-        <v>5080</v>
+        <v>5050</v>
       </c>
       <c r="D2404" t="s">
         <v>2406</v>
@@ -42406,7 +42694,7 @@
         <v>4</v>
       </c>
       <c r="C2405">
-        <v>5010</v>
+        <v>4980</v>
       </c>
       <c r="D2405" t="s">
         <v>2407</v>
@@ -42420,7 +42708,7 @@
         <v>5</v>
       </c>
       <c r="C2406">
-        <v>4950</v>
+        <v>4930</v>
       </c>
       <c r="D2406" t="s">
         <v>2408</v>
@@ -42434,7 +42722,7 @@
         <v>6</v>
       </c>
       <c r="C2407">
-        <v>4900</v>
+        <v>4880</v>
       </c>
       <c r="D2407" t="s">
         <v>2409</v>
@@ -42448,7 +42736,7 @@
         <v>7</v>
       </c>
       <c r="C2408">
-        <v>4860</v>
+        <v>4840</v>
       </c>
       <c r="D2408" t="s">
         <v>2410</v>
@@ -42476,7 +42764,7 @@
         <v>9</v>
       </c>
       <c r="C2410">
-        <v>4790</v>
+        <v>4800</v>
       </c>
       <c r="D2410" t="s">
         <v>2412</v>
@@ -42504,7 +42792,7 @@
         <v>11</v>
       </c>
       <c r="C2412">
-        <v>4740</v>
+        <v>4750</v>
       </c>
       <c r="D2412" t="s">
         <v>2414</v>
@@ -42518,7 +42806,7 @@
         <v>12</v>
       </c>
       <c r="C2413">
-        <v>4710</v>
+        <v>4750</v>
       </c>
       <c r="D2413" t="s">
         <v>2415</v>
@@ -42532,7 +42820,7 @@
         <v>13</v>
       </c>
       <c r="C2414">
-        <v>4690</v>
+        <v>4750</v>
       </c>
       <c r="D2414" t="s">
         <v>2416</v>
@@ -42546,7 +42834,7 @@
         <v>14</v>
       </c>
       <c r="C2415">
-        <v>4670</v>
+        <v>4750</v>
       </c>
       <c r="D2415" t="s">
         <v>2417</v>
@@ -42560,7 +42848,7 @@
         <v>15</v>
       </c>
       <c r="C2416">
-        <v>4660</v>
+        <v>4750</v>
       </c>
       <c r="D2416" t="s">
         <v>2418</v>
@@ -42574,7 +42862,7 @@
         <v>16</v>
       </c>
       <c r="C2417">
-        <v>4660</v>
+        <v>4750</v>
       </c>
       <c r="D2417" t="s">
         <v>2419</v>
@@ -42588,7 +42876,7 @@
         <v>17</v>
       </c>
       <c r="C2418">
-        <v>4660</v>
+        <v>4730</v>
       </c>
       <c r="D2418" t="s">
         <v>2420</v>
@@ -42602,7 +42890,7 @@
         <v>18</v>
       </c>
       <c r="C2419">
-        <v>4670</v>
+        <v>4720</v>
       </c>
       <c r="D2419" t="s">
         <v>2421</v>
@@ -42616,7 +42904,7 @@
         <v>19</v>
       </c>
       <c r="C2420">
-        <v>4680</v>
+        <v>4700</v>
       </c>
       <c r="D2420" t="s">
         <v>2422</v>
@@ -42630,7 +42918,7 @@
         <v>20</v>
       </c>
       <c r="C2421">
-        <v>4700</v>
+        <v>4720</v>
       </c>
       <c r="D2421" t="s">
         <v>2423</v>
@@ -42644,7 +42932,7 @@
         <v>21</v>
       </c>
       <c r="C2422">
-        <v>4720</v>
+        <v>4750</v>
       </c>
       <c r="D2422" t="s">
         <v>2424</v>
@@ -42658,7 +42946,7 @@
         <v>22</v>
       </c>
       <c r="C2423">
-        <v>4730</v>
+        <v>4750</v>
       </c>
       <c r="D2423" t="s">
         <v>2425</v>
@@ -42672,7 +42960,7 @@
         <v>23</v>
       </c>
       <c r="C2424">
-        <v>4720</v>
+        <v>4750</v>
       </c>
       <c r="D2424" t="s">
         <v>2426</v>
@@ -42686,7 +42974,7 @@
         <v>24</v>
       </c>
       <c r="C2425">
-        <v>4690</v>
+        <v>4730</v>
       </c>
       <c r="D2425" t="s">
         <v>2427</v>
@@ -42700,7 +42988,7 @@
         <v>25</v>
       </c>
       <c r="C2426">
-        <v>4660</v>
+        <v>4680</v>
       </c>
       <c r="D2426" t="s">
         <v>2428</v>
@@ -42714,7 +43002,7 @@
         <v>26</v>
       </c>
       <c r="C2427">
-        <v>4630</v>
+        <v>4600</v>
       </c>
       <c r="D2427" t="s">
         <v>2429</v>
@@ -42728,7 +43016,7 @@
         <v>27</v>
       </c>
       <c r="C2428">
-        <v>4610</v>
+        <v>4580</v>
       </c>
       <c r="D2428" t="s">
         <v>2430</v>
@@ -42742,7 +43030,7 @@
         <v>28</v>
       </c>
       <c r="C2429">
-        <v>4590</v>
+        <v>4570</v>
       </c>
       <c r="D2429" t="s">
         <v>2431</v>
@@ -42756,7 +43044,7 @@
         <v>29</v>
       </c>
       <c r="C2430">
-        <v>4590</v>
+        <v>4520</v>
       </c>
       <c r="D2430" t="s">
         <v>2432</v>
@@ -42770,7 +43058,7 @@
         <v>30</v>
       </c>
       <c r="C2431">
-        <v>4590</v>
+        <v>4510</v>
       </c>
       <c r="D2431" t="s">
         <v>2433</v>
@@ -42784,7 +43072,7 @@
         <v>31</v>
       </c>
       <c r="C2432">
-        <v>4580</v>
+        <v>4500</v>
       </c>
       <c r="D2432" t="s">
         <v>2434</v>
@@ -42798,7 +43086,7 @@
         <v>32</v>
       </c>
       <c r="C2433">
-        <v>4580</v>
+        <v>4480</v>
       </c>
       <c r="D2433" t="s">
         <v>2435</v>
@@ -42812,7 +43100,7 @@
         <v>33</v>
       </c>
       <c r="C2434">
-        <v>4570</v>
+        <v>4380</v>
       </c>
       <c r="D2434" t="s">
         <v>2436</v>
@@ -42826,7 +43114,7 @@
         <v>34</v>
       </c>
       <c r="C2435">
-        <v>4550</v>
+        <v>4280</v>
       </c>
       <c r="D2435" t="s">
         <v>2437</v>
@@ -42840,7 +43128,7 @@
         <v>35</v>
       </c>
       <c r="C2436">
-        <v>4500</v>
+        <v>4180</v>
       </c>
       <c r="D2436" t="s">
         <v>2438</v>
@@ -42854,7 +43142,7 @@
         <v>36</v>
       </c>
       <c r="C2437">
-        <v>4430</v>
+        <v>4060</v>
       </c>
       <c r="D2437" t="s">
         <v>2439</v>
@@ -42868,7 +43156,7 @@
         <v>37</v>
       </c>
       <c r="C2438">
-        <v>4340</v>
+        <v>3940</v>
       </c>
       <c r="D2438" t="s">
         <v>2440</v>
@@ -42882,7 +43170,7 @@
         <v>38</v>
       </c>
       <c r="C2439">
-        <v>4250</v>
+        <v>3830</v>
       </c>
       <c r="D2439" t="s">
         <v>2441</v>
@@ -42896,7 +43184,7 @@
         <v>39</v>
       </c>
       <c r="C2440">
-        <v>4170</v>
+        <v>3720</v>
       </c>
       <c r="D2440" t="s">
         <v>2442</v>
@@ -42910,7 +43198,7 @@
         <v>40</v>
       </c>
       <c r="C2441">
-        <v>4100</v>
+        <v>3630</v>
       </c>
       <c r="D2441" t="s">
         <v>2443</v>
@@ -42924,7 +43212,7 @@
         <v>41</v>
       </c>
       <c r="C2442">
-        <v>4030</v>
+        <v>3540</v>
       </c>
       <c r="D2442" t="s">
         <v>2444</v>
@@ -42938,7 +43226,7 @@
         <v>42</v>
       </c>
       <c r="C2443">
-        <v>3960</v>
+        <v>3450</v>
       </c>
       <c r="D2443" t="s">
         <v>2445</v>
@@ -42952,7 +43240,7 @@
         <v>43</v>
       </c>
       <c r="C2444">
-        <v>3890</v>
+        <v>3370</v>
       </c>
       <c r="D2444" t="s">
         <v>2446</v>
@@ -42966,7 +43254,7 @@
         <v>44</v>
       </c>
       <c r="C2445">
-        <v>3830</v>
+        <v>3280</v>
       </c>
       <c r="D2445" t="s">
         <v>2447</v>
@@ -42980,7 +43268,7 @@
         <v>45</v>
       </c>
       <c r="C2446">
-        <v>3760</v>
+        <v>3200</v>
       </c>
       <c r="D2446" t="s">
         <v>2448</v>
@@ -42994,7 +43282,7 @@
         <v>46</v>
       </c>
       <c r="C2447">
-        <v>3690</v>
+        <v>3140</v>
       </c>
       <c r="D2447" t="s">
         <v>2449</v>
@@ -43008,7 +43296,7 @@
         <v>47</v>
       </c>
       <c r="C2448">
-        <v>3630</v>
+        <v>3110</v>
       </c>
       <c r="D2448" t="s">
         <v>2450</v>
@@ -43022,7 +43310,7 @@
         <v>48</v>
       </c>
       <c r="C2449">
-        <v>3580</v>
+        <v>3100</v>
       </c>
       <c r="D2449" t="s">
         <v>2451</v>
@@ -43036,7 +43324,7 @@
         <v>49</v>
       </c>
       <c r="C2450">
-        <v>3540</v>
+        <v>3120</v>
       </c>
       <c r="D2450" t="s">
         <v>2452</v>
@@ -43050,7 +43338,7 @@
         <v>50</v>
       </c>
       <c r="C2451">
-        <v>3510</v>
+        <v>3140</v>
       </c>
       <c r="D2451" t="s">
         <v>2453</v>
@@ -43064,7 +43352,7 @@
         <v>51</v>
       </c>
       <c r="C2452">
-        <v>3490</v>
+        <v>3140</v>
       </c>
       <c r="D2452" t="s">
         <v>2454</v>
@@ -43078,7 +43366,7 @@
         <v>52</v>
       </c>
       <c r="C2453">
-        <v>3490</v>
+        <v>3130</v>
       </c>
       <c r="D2453" t="s">
         <v>2455</v>
@@ -43092,7 +43380,7 @@
         <v>53</v>
       </c>
       <c r="C2454">
-        <v>3500</v>
+        <v>3110</v>
       </c>
       <c r="D2454" t="s">
         <v>2456</v>
@@ -43106,7 +43394,7 @@
         <v>54</v>
       </c>
       <c r="C2455">
-        <v>3500</v>
+        <v>3100</v>
       </c>
       <c r="D2455" t="s">
         <v>2457</v>
@@ -43120,7 +43408,7 @@
         <v>55</v>
       </c>
       <c r="C2456">
-        <v>3490</v>
+        <v>3080</v>
       </c>
       <c r="D2456" t="s">
         <v>2458</v>
@@ -43134,7 +43422,7 @@
         <v>56</v>
       </c>
       <c r="C2457">
-        <v>3460</v>
+        <v>3080</v>
       </c>
       <c r="D2457" t="s">
         <v>2459</v>
@@ -43148,7 +43436,7 @@
         <v>57</v>
       </c>
       <c r="C2458">
-        <v>3420</v>
+        <v>3080</v>
       </c>
       <c r="D2458" t="s">
         <v>2460</v>
@@ -43162,7 +43450,7 @@
         <v>58</v>
       </c>
       <c r="C2459">
-        <v>3410</v>
+        <v>3090</v>
       </c>
       <c r="D2459" t="s">
         <v>2461</v>
@@ -43176,7 +43464,7 @@
         <v>59</v>
       </c>
       <c r="C2460">
-        <v>3440</v>
+        <v>3110</v>
       </c>
       <c r="D2460" t="s">
         <v>2462</v>
@@ -43190,7 +43478,7 @@
         <v>60</v>
       </c>
       <c r="C2461">
-        <v>3490</v>
+        <v>3140</v>
       </c>
       <c r="D2461" t="s">
         <v>2463</v>
@@ -43204,7 +43492,7 @@
         <v>61</v>
       </c>
       <c r="C2462">
-        <v>3570</v>
+        <v>3180</v>
       </c>
       <c r="D2462" t="s">
         <v>2464</v>
@@ -43218,7 +43506,7 @@
         <v>62</v>
       </c>
       <c r="C2463">
-        <v>3650</v>
+        <v>3240</v>
       </c>
       <c r="D2463" t="s">
         <v>2465</v>
@@ -43232,7 +43520,7 @@
         <v>63</v>
       </c>
       <c r="C2464">
-        <v>3720</v>
+        <v>3300</v>
       </c>
       <c r="D2464" t="s">
         <v>2466</v>
@@ -43246,7 +43534,7 @@
         <v>64</v>
       </c>
       <c r="C2465">
-        <v>3790</v>
+        <v>3370</v>
       </c>
       <c r="D2465" t="s">
         <v>2467</v>
@@ -43260,7 +43548,7 @@
         <v>65</v>
       </c>
       <c r="C2466">
-        <v>3850</v>
+        <v>3450</v>
       </c>
       <c r="D2466" t="s">
         <v>2468</v>
@@ -43274,7 +43562,7 @@
         <v>66</v>
       </c>
       <c r="C2467">
-        <v>3930</v>
+        <v>3540</v>
       </c>
       <c r="D2467" t="s">
         <v>2469</v>
@@ -43288,7 +43576,7 @@
         <v>67</v>
       </c>
       <c r="C2468">
-        <v>4020</v>
+        <v>3660</v>
       </c>
       <c r="D2468" t="s">
         <v>2470</v>
@@ -43302,7 +43590,7 @@
         <v>68</v>
       </c>
       <c r="C2469">
-        <v>4120</v>
+        <v>3790</v>
       </c>
       <c r="D2469" t="s">
         <v>2471</v>
@@ -43316,7 +43604,7 @@
         <v>69</v>
       </c>
       <c r="C2470">
-        <v>4240</v>
+        <v>3950</v>
       </c>
       <c r="D2470" t="s">
         <v>2472</v>
@@ -43330,7 +43618,7 @@
         <v>70</v>
       </c>
       <c r="C2471">
-        <v>4360</v>
+        <v>4100</v>
       </c>
       <c r="D2471" t="s">
         <v>2473</v>
@@ -43344,7 +43632,7 @@
         <v>71</v>
       </c>
       <c r="C2472">
-        <v>4490</v>
+        <v>4260</v>
       </c>
       <c r="D2472" t="s">
         <v>2474</v>
@@ -43358,7 +43646,7 @@
         <v>72</v>
       </c>
       <c r="C2473">
-        <v>4630</v>
+        <v>4430</v>
       </c>
       <c r="D2473" t="s">
         <v>2475</v>
@@ -43372,7 +43660,7 @@
         <v>73</v>
       </c>
       <c r="C2474">
-        <v>4760</v>
+        <v>4600</v>
       </c>
       <c r="D2474" t="s">
         <v>2476</v>
@@ -43386,7 +43674,7 @@
         <v>74</v>
       </c>
       <c r="C2475">
-        <v>4890</v>
+        <v>4760</v>
       </c>
       <c r="D2475" t="s">
         <v>2477</v>
@@ -43400,7 +43688,7 @@
         <v>75</v>
       </c>
       <c r="C2476">
-        <v>5010</v>
+        <v>4920</v>
       </c>
       <c r="D2476" t="s">
         <v>2478</v>
@@ -43414,7 +43702,7 @@
         <v>76</v>
       </c>
       <c r="C2477">
-        <v>5130</v>
+        <v>5070</v>
       </c>
       <c r="D2477" t="s">
         <v>2479</v>
@@ -43428,7 +43716,7 @@
         <v>77</v>
       </c>
       <c r="C2478">
-        <v>5240</v>
+        <v>5220</v>
       </c>
       <c r="D2478" t="s">
         <v>2480</v>
@@ -43456,7 +43744,7 @@
         <v>79</v>
       </c>
       <c r="C2480">
-        <v>5480</v>
+        <v>5500</v>
       </c>
       <c r="D2480" t="s">
         <v>2482</v>
@@ -43470,7 +43758,7 @@
         <v>80</v>
       </c>
       <c r="C2481">
-        <v>5610</v>
+        <v>5640</v>
       </c>
       <c r="D2481" t="s">
         <v>2483</v>
@@ -43484,7 +43772,7 @@
         <v>81</v>
       </c>
       <c r="C2482">
-        <v>5750</v>
+        <v>5780</v>
       </c>
       <c r="D2482" t="s">
         <v>2484</v>
@@ -43498,7 +43786,7 @@
         <v>82</v>
       </c>
       <c r="C2483">
-        <v>5860</v>
+        <v>5900</v>
       </c>
       <c r="D2483" t="s">
         <v>2485</v>
@@ -43512,7 +43800,7 @@
         <v>83</v>
       </c>
       <c r="C2484">
-        <v>5950</v>
+        <v>6010</v>
       </c>
       <c r="D2484" t="s">
         <v>2486</v>
@@ -43526,7 +43814,7 @@
         <v>84</v>
       </c>
       <c r="C2485">
-        <v>6010</v>
+        <v>6090</v>
       </c>
       <c r="D2485" t="s">
         <v>2487</v>
@@ -43540,7 +43828,7 @@
         <v>85</v>
       </c>
       <c r="C2486">
-        <v>6050</v>
+        <v>6100</v>
       </c>
       <c r="D2486" t="s">
         <v>2488</v>
@@ -43554,7 +43842,7 @@
         <v>86</v>
       </c>
       <c r="C2487">
-        <v>6050</v>
+        <v>6100</v>
       </c>
       <c r="D2487" t="s">
         <v>2489</v>
@@ -43568,7 +43856,7 @@
         <v>87</v>
       </c>
       <c r="C2488">
-        <v>6010</v>
+        <v>6100</v>
       </c>
       <c r="D2488" t="s">
         <v>2490</v>
@@ -43582,7 +43870,7 @@
         <v>88</v>
       </c>
       <c r="C2489">
-        <v>5930</v>
+        <v>6070</v>
       </c>
       <c r="D2489" t="s">
         <v>2491</v>
@@ -43596,7 +43884,7 @@
         <v>89</v>
       </c>
       <c r="C2490">
-        <v>5820</v>
+        <v>5950</v>
       </c>
       <c r="D2490" t="s">
         <v>2492</v>
@@ -43610,7 +43898,7 @@
         <v>90</v>
       </c>
       <c r="C2491">
-        <v>5700</v>
+        <v>5820</v>
       </c>
       <c r="D2491" t="s">
         <v>2493</v>
@@ -43708,7 +43996,7 @@
         <v>1</v>
       </c>
       <c r="C2498">
-        <v>5040</v>
+        <v>5070</v>
       </c>
       <c r="D2498" t="s">
         <v>2500</v>
@@ -43722,7 +44010,7 @@
         <v>2</v>
       </c>
       <c r="C2499">
-        <v>4970</v>
+        <v>4990</v>
       </c>
       <c r="D2499" t="s">
         <v>2501</v>
@@ -43736,7 +44024,7 @@
         <v>3</v>
       </c>
       <c r="C2500">
-        <v>4910</v>
+        <v>4920</v>
       </c>
       <c r="D2500" t="s">
         <v>2502</v>
@@ -43750,7 +44038,7 @@
         <v>4</v>
       </c>
       <c r="C2501">
-        <v>4850</v>
+        <v>4860</v>
       </c>
       <c r="D2501" t="s">
         <v>2503</v>
@@ -43764,7 +44052,7 @@
         <v>5</v>
       </c>
       <c r="C2502">
-        <v>4790</v>
+        <v>4800</v>
       </c>
       <c r="D2502" t="s">
         <v>2504</v>
@@ -43778,7 +44066,7 @@
         <v>6</v>
       </c>
       <c r="C2503">
-        <v>4750</v>
+        <v>4760</v>
       </c>
       <c r="D2503" t="s">
         <v>2505</v>
@@ -43806,7 +44094,7 @@
         <v>8</v>
       </c>
       <c r="C2505">
-        <v>4690</v>
+        <v>4700</v>
       </c>
       <c r="D2505" t="s">
         <v>2507</v>
@@ -43820,7 +44108,7 @@
         <v>9</v>
       </c>
       <c r="C2506">
-        <v>4670</v>
+        <v>4700</v>
       </c>
       <c r="D2506" t="s">
         <v>2508</v>
@@ -43834,7 +44122,7 @@
         <v>10</v>
       </c>
       <c r="C2507">
-        <v>4660</v>
+        <v>4700</v>
       </c>
       <c r="D2507" t="s">
         <v>2509</v>
@@ -43848,7 +44136,7 @@
         <v>11</v>
       </c>
       <c r="C2508">
-        <v>4650</v>
+        <v>4700</v>
       </c>
       <c r="D2508" t="s">
         <v>2510</v>
@@ -43862,7 +44150,7 @@
         <v>12</v>
       </c>
       <c r="C2509">
-        <v>4650</v>
+        <v>4700</v>
       </c>
       <c r="D2509" t="s">
         <v>2511</v>
@@ -43876,7 +44164,7 @@
         <v>13</v>
       </c>
       <c r="C2510">
-        <v>4640</v>
+        <v>4700</v>
       </c>
       <c r="D2510" t="s">
         <v>2512</v>
@@ -43890,7 +44178,7 @@
         <v>14</v>
       </c>
       <c r="C2511">
-        <v>4650</v>
+        <v>4700</v>
       </c>
       <c r="D2511" t="s">
         <v>2513</v>
@@ -43904,7 +44192,7 @@
         <v>15</v>
       </c>
       <c r="C2512">
-        <v>4650</v>
+        <v>4700</v>
       </c>
       <c r="D2512" t="s">
         <v>2514</v>
@@ -43918,7 +44206,7 @@
         <v>16</v>
       </c>
       <c r="C2513">
-        <v>4660</v>
+        <v>4700</v>
       </c>
       <c r="D2513" t="s">
         <v>2515</v>
@@ -43932,7 +44220,7 @@
         <v>17</v>
       </c>
       <c r="C2514">
-        <v>4680</v>
+        <v>4710</v>
       </c>
       <c r="D2514" t="s">
         <v>2516</v>
@@ -43946,7 +44234,7 @@
         <v>18</v>
       </c>
       <c r="C2515">
-        <v>4700</v>
+        <v>4730</v>
       </c>
       <c r="D2515" t="s">
         <v>2517</v>
@@ -43960,7 +44248,7 @@
         <v>19</v>
       </c>
       <c r="C2516">
-        <v>4720</v>
+        <v>4760</v>
       </c>
       <c r="D2516" t="s">
         <v>2518</v>
@@ -43974,7 +44262,7 @@
         <v>20</v>
       </c>
       <c r="C2517">
-        <v>4750</v>
+        <v>4800</v>
       </c>
       <c r="D2517" t="s">
         <v>2519</v>
@@ -43988,7 +44276,7 @@
         <v>21</v>
       </c>
       <c r="C2518">
-        <v>4790</v>
+        <v>4860</v>
       </c>
       <c r="D2518" t="s">
         <v>2520</v>
@@ -44002,7 +44290,7 @@
         <v>22</v>
       </c>
       <c r="C2519">
-        <v>4850</v>
+        <v>4930</v>
       </c>
       <c r="D2519" t="s">
         <v>2521</v>
@@ -44016,7 +44304,7 @@
         <v>23</v>
       </c>
       <c r="C2520">
-        <v>4930</v>
+        <v>5010</v>
       </c>
       <c r="D2520" t="s">
         <v>2522</v>
@@ -44030,7 +44318,7 @@
         <v>24</v>
       </c>
       <c r="C2521">
-        <v>5030</v>
+        <v>5100</v>
       </c>
       <c r="D2521" t="s">
         <v>2523</v>
@@ -44044,7 +44332,7 @@
         <v>25</v>
       </c>
       <c r="C2522">
-        <v>5150</v>
+        <v>5210</v>
       </c>
       <c r="D2522" t="s">
         <v>2524</v>
@@ -44058,7 +44346,7 @@
         <v>26</v>
       </c>
       <c r="C2523">
-        <v>5290</v>
+        <v>5330</v>
       </c>
       <c r="D2523" t="s">
         <v>2525</v>
@@ -44072,7 +44360,7 @@
         <v>27</v>
       </c>
       <c r="C2524">
-        <v>5430</v>
+        <v>5460</v>
       </c>
       <c r="D2524" t="s">
         <v>2526</v>
@@ -44086,7 +44374,7 @@
         <v>28</v>
       </c>
       <c r="C2525">
-        <v>5590</v>
+        <v>5600</v>
       </c>
       <c r="D2525" t="s">
         <v>2527</v>
@@ -44100,7 +44388,7 @@
         <v>29</v>
       </c>
       <c r="C2526">
-        <v>5750</v>
+        <v>5740</v>
       </c>
       <c r="D2526" t="s">
         <v>2528</v>
@@ -44114,7 +44402,7 @@
         <v>30</v>
       </c>
       <c r="C2527">
-        <v>5890</v>
+        <v>5850</v>
       </c>
       <c r="D2527" t="s">
         <v>2529</v>
@@ -44128,7 +44416,7 @@
         <v>31</v>
       </c>
       <c r="C2528">
-        <v>5990</v>
+        <v>5930</v>
       </c>
       <c r="D2528" t="s">
         <v>2530</v>
@@ -44142,7 +44430,7 @@
         <v>32</v>
       </c>
       <c r="C2529">
-        <v>6050</v>
+        <v>6020</v>
       </c>
       <c r="D2529" t="s">
         <v>2531</v>
@@ -44156,7 +44444,7 @@
         <v>33</v>
       </c>
       <c r="C2530">
-        <v>6080</v>
+        <v>6100</v>
       </c>
       <c r="D2530" t="s">
         <v>2532</v>
@@ -44170,7 +44458,7 @@
         <v>34</v>
       </c>
       <c r="C2531">
-        <v>6080</v>
+        <v>6150</v>
       </c>
       <c r="D2531" t="s">
         <v>2533</v>
@@ -44184,7 +44472,7 @@
         <v>35</v>
       </c>
       <c r="C2532">
-        <v>6040</v>
+        <v>6200</v>
       </c>
       <c r="D2532" t="s">
         <v>2534</v>
@@ -44198,7 +44486,7 @@
         <v>36</v>
       </c>
       <c r="C2533">
-        <v>5980</v>
+        <v>6100</v>
       </c>
       <c r="D2533" t="s">
         <v>2535</v>
@@ -44212,7 +44500,7 @@
         <v>37</v>
       </c>
       <c r="C2534">
-        <v>5880</v>
+        <v>5900</v>
       </c>
       <c r="D2534" t="s">
         <v>2536</v>
@@ -44226,7 +44514,7 @@
         <v>38</v>
       </c>
       <c r="C2535">
-        <v>5780</v>
+        <v>5600</v>
       </c>
       <c r="D2535" t="s">
         <v>2537</v>
@@ -44240,7 +44528,7 @@
         <v>39</v>
       </c>
       <c r="C2536">
-        <v>5680</v>
+        <v>5500</v>
       </c>
       <c r="D2536" t="s">
         <v>2538</v>
@@ -44254,7 +44542,7 @@
         <v>40</v>
       </c>
       <c r="C2537">
-        <v>5570</v>
+        <v>5300</v>
       </c>
       <c r="D2537" t="s">
         <v>2539</v>
@@ -44268,7 +44556,7 @@
         <v>41</v>
       </c>
       <c r="C2538">
-        <v>5460</v>
+        <v>5100</v>
       </c>
       <c r="D2538" t="s">
         <v>2540</v>
@@ -44282,7 +44570,7 @@
         <v>42</v>
       </c>
       <c r="C2539">
-        <v>5350</v>
+        <v>4970</v>
       </c>
       <c r="D2539" t="s">
         <v>2541</v>
@@ -44296,7 +44584,7 @@
         <v>43</v>
       </c>
       <c r="C2540">
-        <v>5240</v>
+        <v>4840</v>
       </c>
       <c r="D2540" t="s">
         <v>2542</v>
@@ -44310,7 +44598,7 @@
         <v>44</v>
       </c>
       <c r="C2541">
-        <v>5120</v>
+        <v>4720</v>
       </c>
       <c r="D2541" t="s">
         <v>2543</v>
@@ -44324,7 +44612,7 @@
         <v>45</v>
       </c>
       <c r="C2542">
-        <v>5010</v>
+        <v>4590</v>
       </c>
       <c r="D2542" t="s">
         <v>2544</v>
@@ -44338,7 +44626,7 @@
         <v>46</v>
       </c>
       <c r="C2543">
-        <v>4910</v>
+        <v>4490</v>
       </c>
       <c r="D2543" t="s">
         <v>2545</v>
@@ -44352,7 +44640,7 @@
         <v>47</v>
       </c>
       <c r="C2544">
-        <v>4820</v>
+        <v>4420</v>
       </c>
       <c r="D2544" t="s">
         <v>2546</v>
@@ -44366,7 +44654,7 @@
         <v>48</v>
       </c>
       <c r="C2545">
-        <v>4760</v>
+        <v>4380</v>
       </c>
       <c r="D2545" t="s">
         <v>2547</v>
@@ -44380,7 +44668,7 @@
         <v>49</v>
       </c>
       <c r="C2546">
-        <v>4710</v>
+        <v>4360</v>
       </c>
       <c r="D2546" t="s">
         <v>2548</v>
@@ -44394,7 +44682,7 @@
         <v>50</v>
       </c>
       <c r="C2547">
-        <v>4670</v>
+        <v>4350</v>
       </c>
       <c r="D2547" t="s">
         <v>2549</v>
@@ -44408,7 +44696,7 @@
         <v>51</v>
       </c>
       <c r="C2548">
-        <v>4660</v>
+        <v>4340</v>
       </c>
       <c r="D2548" t="s">
         <v>2550</v>
@@ -44422,7 +44710,7 @@
         <v>52</v>
       </c>
       <c r="C2549">
-        <v>4650</v>
+        <v>4320</v>
       </c>
       <c r="D2549" t="s">
         <v>2551</v>
@@ -44436,7 +44724,7 @@
         <v>53</v>
       </c>
       <c r="C2550">
-        <v>4660</v>
+        <v>4310</v>
       </c>
       <c r="D2550" t="s">
         <v>2552</v>
@@ -44450,7 +44738,7 @@
         <v>54</v>
       </c>
       <c r="C2551">
-        <v>4660</v>
+        <v>4290</v>
       </c>
       <c r="D2551" t="s">
         <v>2553</v>
@@ -44464,7 +44752,7 @@
         <v>55</v>
       </c>
       <c r="C2552">
-        <v>4640</v>
+        <v>4270</v>
       </c>
       <c r="D2552" t="s">
         <v>2554</v>
@@ -44478,7 +44766,7 @@
         <v>56</v>
       </c>
       <c r="C2553">
-        <v>4610</v>
+        <v>4240</v>
       </c>
       <c r="D2553" t="s">
         <v>2555</v>
@@ -44492,7 +44780,7 @@
         <v>57</v>
       </c>
       <c r="C2554">
-        <v>4570</v>
+        <v>4220</v>
       </c>
       <c r="D2554" t="s">
         <v>2556</v>
@@ -44506,7 +44794,7 @@
         <v>58</v>
       </c>
       <c r="C2555">
-        <v>4570</v>
+        <v>4210</v>
       </c>
       <c r="D2555" t="s">
         <v>2557</v>
@@ -44520,7 +44808,7 @@
         <v>59</v>
       </c>
       <c r="C2556">
-        <v>4600</v>
+        <v>4230</v>
       </c>
       <c r="D2556" t="s">
         <v>2558</v>
@@ -44534,7 +44822,7 @@
         <v>60</v>
       </c>
       <c r="C2557">
-        <v>4680</v>
+        <v>4270</v>
       </c>
       <c r="D2557" t="s">
         <v>2559</v>
@@ -44548,7 +44836,7 @@
         <v>61</v>
       </c>
       <c r="C2558">
-        <v>4800</v>
+        <v>4330</v>
       </c>
       <c r="D2558" t="s">
         <v>2560</v>
@@ -44562,7 +44850,7 @@
         <v>62</v>
       </c>
       <c r="C2559">
-        <v>4900</v>
+        <v>4390</v>
       </c>
       <c r="D2559" t="s">
         <v>2561</v>
@@ -44576,7 +44864,7 @@
         <v>63</v>
       </c>
       <c r="C2560">
-        <v>4980</v>
+        <v>4460</v>
       </c>
       <c r="D2560" t="s">
         <v>2562</v>
@@ -44590,7 +44878,7 @@
         <v>64</v>
       </c>
       <c r="C2561">
-        <v>5030</v>
+        <v>4520</v>
       </c>
       <c r="D2561" t="s">
         <v>2563</v>
@@ -44604,7 +44892,7 @@
         <v>65</v>
       </c>
       <c r="C2562">
-        <v>5070</v>
+        <v>4580</v>
       </c>
       <c r="D2562" t="s">
         <v>2564</v>
@@ -44618,7 +44906,7 @@
         <v>66</v>
       </c>
       <c r="C2563">
-        <v>5110</v>
+        <v>4660</v>
       </c>
       <c r="D2563" t="s">
         <v>2565</v>
@@ -44632,7 +44920,7 @@
         <v>67</v>
       </c>
       <c r="C2564">
-        <v>5180</v>
+        <v>4740</v>
       </c>
       <c r="D2564" t="s">
         <v>2566</v>
@@ -44646,7 +44934,7 @@
         <v>68</v>
       </c>
       <c r="C2565">
-        <v>5260</v>
+        <v>4840</v>
       </c>
       <c r="D2565" t="s">
         <v>2567</v>
@@ -44660,7 +44948,7 @@
         <v>69</v>
       </c>
       <c r="C2566">
-        <v>5360</v>
+        <v>4960</v>
       </c>
       <c r="D2566" t="s">
         <v>2568</v>
@@ -44674,7 +44962,7 @@
         <v>70</v>
       </c>
       <c r="C2567">
-        <v>5470</v>
+        <v>5100</v>
       </c>
       <c r="D2567" t="s">
         <v>2569</v>
@@ -44688,7 +44976,7 @@
         <v>71</v>
       </c>
       <c r="C2568">
-        <v>5580</v>
+        <v>5260</v>
       </c>
       <c r="D2568" t="s">
         <v>2570</v>
@@ -44702,7 +44990,7 @@
         <v>72</v>
       </c>
       <c r="C2569">
-        <v>5700</v>
+        <v>5440</v>
       </c>
       <c r="D2569" t="s">
         <v>2571</v>
@@ -44716,7 +45004,7 @@
         <v>73</v>
       </c>
       <c r="C2570">
-        <v>5830</v>
+        <v>5640</v>
       </c>
       <c r="D2570" t="s">
         <v>2572</v>
@@ -44730,7 +45018,7 @@
         <v>74</v>
       </c>
       <c r="C2571">
-        <v>5940</v>
+        <v>5830</v>
       </c>
       <c r="D2571" t="s">
         <v>2573</v>
@@ -44744,7 +45032,7 @@
         <v>75</v>
       </c>
       <c r="C2572">
-        <v>6050</v>
+        <v>5990</v>
       </c>
       <c r="D2572" t="s">
         <v>2574</v>
@@ -44758,7 +45046,7 @@
         <v>76</v>
       </c>
       <c r="C2573">
-        <v>6160</v>
+        <v>6130</v>
       </c>
       <c r="D2573" t="s">
         <v>2575</v>
@@ -44772,7 +45060,7 @@
         <v>77</v>
       </c>
       <c r="C2574">
-        <v>6250</v>
+        <v>6260</v>
       </c>
       <c r="D2574" t="s">
         <v>2576</v>
@@ -44786,7 +45074,7 @@
         <v>78</v>
       </c>
       <c r="C2575">
-        <v>6360</v>
+        <v>6380</v>
       </c>
       <c r="D2575" t="s">
         <v>2577</v>
@@ -44800,7 +45088,7 @@
         <v>79</v>
       </c>
       <c r="C2576">
-        <v>6480</v>
+        <v>6510</v>
       </c>
       <c r="D2576" t="s">
         <v>2578</v>
@@ -44814,7 +45102,7 @@
         <v>80</v>
       </c>
       <c r="C2577">
-        <v>6620</v>
+        <v>6640</v>
       </c>
       <c r="D2577" t="s">
         <v>2579</v>
@@ -44828,7 +45116,7 @@
         <v>81</v>
       </c>
       <c r="C2578">
-        <v>6760</v>
+        <v>6770</v>
       </c>
       <c r="D2578" t="s">
         <v>2580</v>
@@ -44842,7 +45130,7 @@
         <v>82</v>
       </c>
       <c r="C2579">
-        <v>6870</v>
+        <v>6880</v>
       </c>
       <c r="D2579" t="s">
         <v>2581</v>
@@ -44856,7 +45144,7 @@
         <v>83</v>
       </c>
       <c r="C2580">
-        <v>6950</v>
+        <v>6970</v>
       </c>
       <c r="D2580" t="s">
         <v>2582</v>
@@ -44870,7 +45158,7 @@
         <v>84</v>
       </c>
       <c r="C2581">
-        <v>7000</v>
+        <v>7040</v>
       </c>
       <c r="D2581" t="s">
         <v>2583</v>
@@ -44884,7 +45172,7 @@
         <v>85</v>
       </c>
       <c r="C2582">
-        <v>7010</v>
+        <v>7100</v>
       </c>
       <c r="D2582" t="s">
         <v>2584</v>
@@ -44898,7 +45186,7 @@
         <v>86</v>
       </c>
       <c r="C2583">
-        <v>6980</v>
+        <v>7070</v>
       </c>
       <c r="D2583" t="s">
         <v>2585</v>
@@ -44912,7 +45200,7 @@
         <v>87</v>
       </c>
       <c r="C2584">
-        <v>6900</v>
+        <v>7000</v>
       </c>
       <c r="D2584" t="s">
         <v>2586</v>
@@ -44926,7 +45214,7 @@
         <v>88</v>
       </c>
       <c r="C2585">
-        <v>6790</v>
+        <v>6880</v>
       </c>
       <c r="D2585" t="s">
         <v>2587</v>
@@ -44940,7 +45228,7 @@
         <v>89</v>
       </c>
       <c r="C2586">
-        <v>6640</v>
+        <v>6720</v>
       </c>
       <c r="D2586" t="s">
         <v>2588</v>
@@ -44954,7 +45242,7 @@
         <v>90</v>
       </c>
       <c r="C2587">
-        <v>6480</v>
+        <v>6560</v>
       </c>
       <c r="D2587" t="s">
         <v>2589</v>
@@ -45052,7 +45340,7 @@
         <v>1</v>
       </c>
       <c r="C2594">
-        <v>5500</v>
+        <v>5600</v>
       </c>
       <c r="D2594" t="s">
         <v>2596</v>
@@ -45066,7 +45354,7 @@
         <v>2</v>
       </c>
       <c r="C2595">
-        <v>5420</v>
+        <v>5510</v>
       </c>
       <c r="D2595" t="s">
         <v>2597</v>
@@ -45080,7 +45368,7 @@
         <v>3</v>
       </c>
       <c r="C2596">
-        <v>5350</v>
+        <v>5430</v>
       </c>
       <c r="D2596" t="s">
         <v>2598</v>
@@ -45094,7 +45382,7 @@
         <v>4</v>
       </c>
       <c r="C2597">
-        <v>5280</v>
+        <v>5360</v>
       </c>
       <c r="D2597" t="s">
         <v>2599</v>
@@ -45108,7 +45396,7 @@
         <v>5</v>
       </c>
       <c r="C2598">
-        <v>5220</v>
+        <v>5310</v>
       </c>
       <c r="D2598" t="s">
         <v>2600</v>
@@ -45122,7 +45410,7 @@
         <v>6</v>
       </c>
       <c r="C2599">
-        <v>5180</v>
+        <v>5270</v>
       </c>
       <c r="D2599" t="s">
         <v>2601</v>
@@ -45136,7 +45424,7 @@
         <v>7</v>
       </c>
       <c r="C2600">
-        <v>5140</v>
+        <v>5230</v>
       </c>
       <c r="D2600" t="s">
         <v>2602</v>
@@ -45150,7 +45438,7 @@
         <v>8</v>
       </c>
       <c r="C2601">
-        <v>5110</v>
+        <v>5210</v>
       </c>
       <c r="D2601" t="s">
         <v>2603</v>
@@ -45164,7 +45452,7 @@
         <v>9</v>
       </c>
       <c r="C2602">
-        <v>5080</v>
+        <v>5200</v>
       </c>
       <c r="D2602" t="s">
         <v>2604</v>
@@ -45178,7 +45466,7 @@
         <v>10</v>
       </c>
       <c r="C2603">
-        <v>5070</v>
+        <v>5200</v>
       </c>
       <c r="D2603" t="s">
         <v>2605</v>
@@ -45192,7 +45480,7 @@
         <v>11</v>
       </c>
       <c r="C2604">
-        <v>5050</v>
+        <v>5200</v>
       </c>
       <c r="D2604" t="s">
         <v>2606</v>
@@ -45206,7 +45494,7 @@
         <v>12</v>
       </c>
       <c r="C2605">
-        <v>5040</v>
+        <v>5200</v>
       </c>
       <c r="D2605" t="s">
         <v>2607</v>
@@ -45220,7 +45508,7 @@
         <v>13</v>
       </c>
       <c r="C2606">
-        <v>5030</v>
+        <v>5200</v>
       </c>
       <c r="D2606" t="s">
         <v>2608</v>
@@ -45234,7 +45522,7 @@
         <v>14</v>
       </c>
       <c r="C2607">
-        <v>5030</v>
+        <v>5200</v>
       </c>
       <c r="D2607" t="s">
         <v>2609</v>
@@ -45248,7 +45536,7 @@
         <v>15</v>
       </c>
       <c r="C2608">
-        <v>5030</v>
+        <v>5210</v>
       </c>
       <c r="D2608" t="s">
         <v>2610</v>
@@ -45262,7 +45550,7 @@
         <v>16</v>
       </c>
       <c r="C2609">
-        <v>5030</v>
+        <v>5220</v>
       </c>
       <c r="D2609" t="s">
         <v>2611</v>
@@ -45276,7 +45564,7 @@
         <v>17</v>
       </c>
       <c r="C2610">
-        <v>5040</v>
+        <v>5230</v>
       </c>
       <c r="D2610" t="s">
         <v>2612</v>
@@ -45290,7 +45578,7 @@
         <v>18</v>
       </c>
       <c r="C2611">
-        <v>5060</v>
+        <v>5250</v>
       </c>
       <c r="D2611" t="s">
         <v>2613</v>
@@ -45304,7 +45592,7 @@
         <v>19</v>
       </c>
       <c r="C2612">
-        <v>5080</v>
+        <v>5260</v>
       </c>
       <c r="D2612" t="s">
         <v>2614</v>
@@ -45318,7 +45606,7 @@
         <v>20</v>
       </c>
       <c r="C2613">
-        <v>5110</v>
+        <v>5250</v>
       </c>
       <c r="D2613" t="s">
         <v>2615</v>
@@ -45332,7 +45620,7 @@
         <v>21</v>
       </c>
       <c r="C2614">
-        <v>5150</v>
+        <v>5280</v>
       </c>
       <c r="D2614" t="s">
         <v>2616</v>
@@ -45346,7 +45634,7 @@
         <v>22</v>
       </c>
       <c r="C2615">
-        <v>5190</v>
+        <v>5320</v>
       </c>
       <c r="D2615" t="s">
         <v>2617</v>
@@ -45360,7 +45648,7 @@
         <v>23</v>
       </c>
       <c r="C2616">
-        <v>5250</v>
+        <v>5380</v>
       </c>
       <c r="D2616" t="s">
         <v>2618</v>
@@ -45374,7 +45662,7 @@
         <v>24</v>
       </c>
       <c r="C2617">
-        <v>5310</v>
+        <v>5450</v>
       </c>
       <c r="D2617" t="s">
         <v>2619</v>
@@ -45388,7 +45676,7 @@
         <v>25</v>
       </c>
       <c r="C2618">
-        <v>5380</v>
+        <v>5530</v>
       </c>
       <c r="D2618" t="s">
         <v>2620</v>
@@ -45402,7 +45690,7 @@
         <v>26</v>
       </c>
       <c r="C2619">
-        <v>5470</v>
+        <v>5620</v>
       </c>
       <c r="D2619" t="s">
         <v>2621</v>
@@ -45416,7 +45704,7 @@
         <v>27</v>
       </c>
       <c r="C2620">
-        <v>5580</v>
+        <v>5730</v>
       </c>
       <c r="D2620" t="s">
         <v>2622</v>
@@ -45430,7 +45718,7 @@
         <v>28</v>
       </c>
       <c r="C2621">
-        <v>5720</v>
+        <v>5860</v>
       </c>
       <c r="D2621" t="s">
         <v>2623</v>
@@ -45444,7 +45732,7 @@
         <v>29</v>
       </c>
       <c r="C2622">
-        <v>5870</v>
+        <v>5990</v>
       </c>
       <c r="D2622" t="s">
         <v>2624</v>
@@ -45458,7 +45746,7 @@
         <v>30</v>
       </c>
       <c r="C2623">
-        <v>6000</v>
+        <v>6080</v>
       </c>
       <c r="D2623" t="s">
         <v>2625</v>
@@ -45472,7 +45760,7 @@
         <v>31</v>
       </c>
       <c r="C2624">
-        <v>6080</v>
+        <v>6140</v>
       </c>
       <c r="D2624" t="s">
         <v>2626</v>
@@ -45486,7 +45774,7 @@
         <v>32</v>
       </c>
       <c r="C2625">
-        <v>6130</v>
+        <v>6160</v>
       </c>
       <c r="D2625" t="s">
         <v>2627</v>
@@ -45500,7 +45788,7 @@
         <v>33</v>
       </c>
       <c r="C2626">
-        <v>6140</v>
+        <v>6220</v>
       </c>
       <c r="D2626" t="s">
         <v>2628</v>
@@ -45514,7 +45802,7 @@
         <v>34</v>
       </c>
       <c r="C2627">
-        <v>6120</v>
+        <v>6250</v>
       </c>
       <c r="D2627" t="s">
         <v>2629</v>
@@ -45528,7 +45816,7 @@
         <v>35</v>
       </c>
       <c r="C2628">
-        <v>6070</v>
+        <v>6300</v>
       </c>
       <c r="D2628" t="s">
         <v>2630</v>
@@ -45542,7 +45830,7 @@
         <v>36</v>
       </c>
       <c r="C2629">
-        <v>6000</v>
+        <v>6200</v>
       </c>
       <c r="D2629" t="s">
         <v>2631</v>
@@ -45556,7 +45844,7 @@
         <v>37</v>
       </c>
       <c r="C2630">
-        <v>5910</v>
+        <v>6150</v>
       </c>
       <c r="D2630" t="s">
         <v>2632</v>
@@ -45570,7 +45858,7 @@
         <v>38</v>
       </c>
       <c r="C2631">
-        <v>5810</v>
+        <v>6000</v>
       </c>
       <c r="D2631" t="s">
         <v>2633</v>
@@ -45584,7 +45872,7 @@
         <v>39</v>
       </c>
       <c r="C2632">
-        <v>5720</v>
+        <v>5700</v>
       </c>
       <c r="D2632" t="s">
         <v>2634</v>
@@ -45598,7 +45886,7 @@
         <v>40</v>
       </c>
       <c r="C2633">
-        <v>5620</v>
+        <v>5460</v>
       </c>
       <c r="D2633" t="s">
         <v>2635</v>
@@ -45612,7 +45900,7 @@
         <v>41</v>
       </c>
       <c r="C2634">
-        <v>5520</v>
+        <v>5350</v>
       </c>
       <c r="D2634" t="s">
         <v>2636</v>
@@ -45626,7 +45914,7 @@
         <v>42</v>
       </c>
       <c r="C2635">
-        <v>5410</v>
+        <v>5230</v>
       </c>
       <c r="D2635" t="s">
         <v>2637</v>
@@ -45640,7 +45928,7 @@
         <v>43</v>
       </c>
       <c r="C2636">
-        <v>5300</v>
+        <v>5100</v>
       </c>
       <c r="D2636" t="s">
         <v>2638</v>
@@ -45654,7 +45942,7 @@
         <v>44</v>
       </c>
       <c r="C2637">
-        <v>5190</v>
+        <v>4960</v>
       </c>
       <c r="D2637" t="s">
         <v>2639</v>
@@ -45668,7 +45956,7 @@
         <v>45</v>
       </c>
       <c r="C2638">
-        <v>5070</v>
+        <v>4820</v>
       </c>
       <c r="D2638" t="s">
         <v>2640</v>
@@ -45682,7 +45970,7 @@
         <v>46</v>
       </c>
       <c r="C2639">
-        <v>4970</v>
+        <v>4690</v>
       </c>
       <c r="D2639" t="s">
         <v>2641</v>
@@ -45696,7 +45984,7 @@
         <v>47</v>
       </c>
       <c r="C2640">
-        <v>4880</v>
+        <v>4600</v>
       </c>
       <c r="D2640" t="s">
         <v>2642</v>
@@ -45710,7 +45998,7 @@
         <v>48</v>
       </c>
       <c r="C2641">
-        <v>4820</v>
+        <v>4530</v>
       </c>
       <c r="D2641" t="s">
         <v>2643</v>
@@ -45724,7 +46012,7 @@
         <v>49</v>
       </c>
       <c r="C2642">
-        <v>4770</v>
+        <v>4490</v>
       </c>
       <c r="D2642" t="s">
         <v>2644</v>
@@ -45738,7 +46026,7 @@
         <v>50</v>
       </c>
       <c r="C2643">
-        <v>4730</v>
+        <v>4460</v>
       </c>
       <c r="D2643" t="s">
         <v>2645</v>
@@ -45752,7 +46040,7 @@
         <v>51</v>
       </c>
       <c r="C2644">
-        <v>4720</v>
+        <v>4450</v>
       </c>
       <c r="D2644" t="s">
         <v>2646</v>
@@ -45766,7 +46054,7 @@
         <v>52</v>
       </c>
       <c r="C2645">
-        <v>4710</v>
+        <v>4440</v>
       </c>
       <c r="D2645" t="s">
         <v>2647</v>
@@ -45780,7 +46068,7 @@
         <v>53</v>
       </c>
       <c r="C2646">
-        <v>4720</v>
+        <v>4440</v>
       </c>
       <c r="D2646" t="s">
         <v>2648</v>
@@ -45794,7 +46082,7 @@
         <v>54</v>
       </c>
       <c r="C2647">
-        <v>4720</v>
+        <v>4430</v>
       </c>
       <c r="D2647" t="s">
         <v>2649</v>
@@ -45808,7 +46096,7 @@
         <v>55</v>
       </c>
       <c r="C2648">
-        <v>4700</v>
+        <v>4400</v>
       </c>
       <c r="D2648" t="s">
         <v>2650</v>
@@ -45822,7 +46110,7 @@
         <v>56</v>
       </c>
       <c r="C2649">
-        <v>4670</v>
+        <v>4360</v>
       </c>
       <c r="D2649" t="s">
         <v>2651</v>
@@ -45836,7 +46124,7 @@
         <v>57</v>
       </c>
       <c r="C2650">
-        <v>4630</v>
+        <v>4310</v>
       </c>
       <c r="D2650" t="s">
         <v>2652</v>
@@ -45850,7 +46138,7 @@
         <v>58</v>
       </c>
       <c r="C2651">
-        <v>4620</v>
+        <v>4300</v>
       </c>
       <c r="D2651" t="s">
         <v>2653</v>
@@ -45864,7 +46152,7 @@
         <v>59</v>
       </c>
       <c r="C2652">
-        <v>4650</v>
+        <v>4350</v>
       </c>
       <c r="D2652" t="s">
         <v>2654</v>
@@ -45878,7 +46166,7 @@
         <v>60</v>
       </c>
       <c r="C2653">
-        <v>4720</v>
+        <v>4440</v>
       </c>
       <c r="D2653" t="s">
         <v>2655</v>
@@ -45892,7 +46180,7 @@
         <v>61</v>
       </c>
       <c r="C2654">
-        <v>4820</v>
+        <v>4580</v>
       </c>
       <c r="D2654" t="s">
         <v>2656</v>
@@ -45906,7 +46194,7 @@
         <v>62</v>
       </c>
       <c r="C2655">
-        <v>4910</v>
+        <v>4700</v>
       </c>
       <c r="D2655" t="s">
         <v>2657</v>
@@ -45920,7 +46208,7 @@
         <v>63</v>
       </c>
       <c r="C2656">
-        <v>4980</v>
+        <v>4790</v>
       </c>
       <c r="D2656" t="s">
         <v>2658</v>
@@ -45934,7 +46222,7 @@
         <v>64</v>
       </c>
       <c r="C2657">
-        <v>5030</v>
+        <v>4860</v>
       </c>
       <c r="D2657" t="s">
         <v>2659</v>
@@ -45948,7 +46236,7 @@
         <v>65</v>
       </c>
       <c r="C2658">
-        <v>5070</v>
+        <v>4900</v>
       </c>
       <c r="D2658" t="s">
         <v>2660</v>
@@ -45962,7 +46250,7 @@
         <v>66</v>
       </c>
       <c r="C2659">
-        <v>5120</v>
+        <v>4960</v>
       </c>
       <c r="D2659" t="s">
         <v>2661</v>
@@ -45976,7 +46264,7 @@
         <v>67</v>
       </c>
       <c r="C2660">
-        <v>5200</v>
+        <v>5040</v>
       </c>
       <c r="D2660" t="s">
         <v>2662</v>
@@ -45990,7 +46278,7 @@
         <v>68</v>
       </c>
       <c r="C2661">
-        <v>5290</v>
+        <v>5130</v>
       </c>
       <c r="D2661" t="s">
         <v>2663</v>
@@ -46004,7 +46292,7 @@
         <v>69</v>
       </c>
       <c r="C2662">
-        <v>5400</v>
+        <v>5250</v>
       </c>
       <c r="D2662" t="s">
         <v>2664</v>
@@ -46018,7 +46306,7 @@
         <v>70</v>
       </c>
       <c r="C2663">
-        <v>5520</v>
+        <v>5380</v>
       </c>
       <c r="D2663" t="s">
         <v>2665</v>
@@ -46032,7 +46320,7 @@
         <v>71</v>
       </c>
       <c r="C2664">
-        <v>5640</v>
+        <v>5510</v>
       </c>
       <c r="D2664" t="s">
         <v>2666</v>
@@ -46046,7 +46334,7 @@
         <v>72</v>
       </c>
       <c r="C2665">
-        <v>5750</v>
+        <v>5650</v>
       </c>
       <c r="D2665" t="s">
         <v>2667</v>
@@ -46060,7 +46348,7 @@
         <v>73</v>
       </c>
       <c r="C2666">
-        <v>5870</v>
+        <v>5790</v>
       </c>
       <c r="D2666" t="s">
         <v>2668</v>
@@ -46074,7 +46362,7 @@
         <v>74</v>
       </c>
       <c r="C2667">
-        <v>5980</v>
+        <v>5930</v>
       </c>
       <c r="D2667" t="s">
         <v>2669</v>
@@ -46088,7 +46376,7 @@
         <v>75</v>
       </c>
       <c r="C2668">
-        <v>6080</v>
+        <v>6070</v>
       </c>
       <c r="D2668" t="s">
         <v>2670</v>
@@ -46102,7 +46390,7 @@
         <v>76</v>
       </c>
       <c r="C2669">
-        <v>6180</v>
+        <v>6200</v>
       </c>
       <c r="D2669" t="s">
         <v>2671</v>
@@ -46116,7 +46404,7 @@
         <v>77</v>
       </c>
       <c r="C2670">
-        <v>6270</v>
+        <v>6330</v>
       </c>
       <c r="D2670" t="s">
         <v>2672</v>
@@ -46130,7 +46418,7 @@
         <v>78</v>
       </c>
       <c r="C2671">
-        <v>6380</v>
+        <v>6450</v>
       </c>
       <c r="D2671" t="s">
         <v>2673</v>
@@ -46144,7 +46432,7 @@
         <v>79</v>
       </c>
       <c r="C2672">
-        <v>6490</v>
+        <v>6580</v>
       </c>
       <c r="D2672" t="s">
         <v>2674</v>
@@ -46158,7 +46446,7 @@
         <v>80</v>
       </c>
       <c r="C2673">
-        <v>6620</v>
+        <v>6710</v>
       </c>
       <c r="D2673" t="s">
         <v>2675</v>
@@ -46172,7 +46460,7 @@
         <v>81</v>
       </c>
       <c r="C2674">
-        <v>6740</v>
+        <v>6840</v>
       </c>
       <c r="D2674" t="s">
         <v>2676</v>
@@ -46186,7 +46474,7 @@
         <v>82</v>
       </c>
       <c r="C2675">
-        <v>6850</v>
+        <v>6940</v>
       </c>
       <c r="D2675" t="s">
         <v>2677</v>
@@ -46200,7 +46488,7 @@
         <v>83</v>
       </c>
       <c r="C2676">
-        <v>6930</v>
+        <v>7030</v>
       </c>
       <c r="D2676" t="s">
         <v>2678</v>
@@ -46214,7 +46502,7 @@
         <v>84</v>
       </c>
       <c r="C2677">
-        <v>6980</v>
+        <v>7150</v>
       </c>
       <c r="D2677" t="s">
         <v>2679</v>
@@ -46228,7 +46516,7 @@
         <v>85</v>
       </c>
       <c r="C2678">
-        <v>6990</v>
+        <v>7180</v>
       </c>
       <c r="D2678" t="s">
         <v>2680</v>
@@ -46242,7 +46530,7 @@
         <v>86</v>
       </c>
       <c r="C2679">
-        <v>6970</v>
+        <v>7200</v>
       </c>
       <c r="D2679" t="s">
         <v>2681</v>
@@ -46256,7 +46544,7 @@
         <v>87</v>
       </c>
       <c r="C2680">
-        <v>6900</v>
+        <v>7050</v>
       </c>
       <c r="D2680" t="s">
         <v>2682</v>
@@ -46270,7 +46558,7 @@
         <v>88</v>
       </c>
       <c r="C2681">
-        <v>6790</v>
+        <v>6930</v>
       </c>
       <c r="D2681" t="s">
         <v>2683</v>
@@ -46284,7 +46572,7 @@
         <v>89</v>
       </c>
       <c r="C2682">
-        <v>6640</v>
+        <v>6770</v>
       </c>
       <c r="D2682" t="s">
         <v>2684</v>
@@ -46298,7 +46586,7 @@
         <v>90</v>
       </c>
       <c r="C2683">
-        <v>6480</v>
+        <v>6600</v>
       </c>
       <c r="D2683" t="s">
         <v>2685</v>
@@ -47730,6 +48018,1350 @@
       </c>
       <c r="D2785" t="s">
         <v>2787</v>
+      </c>
+    </row>
+    <row r="2786" spans="1:4">
+      <c r="A2786" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2786">
+        <v>1</v>
+      </c>
+      <c r="C2786">
+        <v>5540</v>
+      </c>
+      <c r="D2786" t="s">
+        <v>2788</v>
+      </c>
+    </row>
+    <row r="2787" spans="1:4">
+      <c r="A2787" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2787">
+        <v>2</v>
+      </c>
+      <c r="C2787">
+        <v>5500</v>
+      </c>
+      <c r="D2787" t="s">
+        <v>2789</v>
+      </c>
+    </row>
+    <row r="2788" spans="1:4">
+      <c r="A2788" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2788">
+        <v>3</v>
+      </c>
+      <c r="C2788">
+        <v>5440</v>
+      </c>
+      <c r="D2788" t="s">
+        <v>2790</v>
+      </c>
+    </row>
+    <row r="2789" spans="1:4">
+      <c r="A2789" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2789">
+        <v>4</v>
+      </c>
+      <c r="C2789">
+        <v>5360</v>
+      </c>
+      <c r="D2789" t="s">
+        <v>2791</v>
+      </c>
+    </row>
+    <row r="2790" spans="1:4">
+      <c r="A2790" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2790">
+        <v>5</v>
+      </c>
+      <c r="C2790">
+        <v>5290</v>
+      </c>
+      <c r="D2790" t="s">
+        <v>2792</v>
+      </c>
+    </row>
+    <row r="2791" spans="1:4">
+      <c r="A2791" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2791">
+        <v>6</v>
+      </c>
+      <c r="C2791">
+        <v>5240</v>
+      </c>
+      <c r="D2791" t="s">
+        <v>2793</v>
+      </c>
+    </row>
+    <row r="2792" spans="1:4">
+      <c r="A2792" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2792">
+        <v>7</v>
+      </c>
+      <c r="C2792">
+        <v>5190</v>
+      </c>
+      <c r="D2792" t="s">
+        <v>2794</v>
+      </c>
+    </row>
+    <row r="2793" spans="1:4">
+      <c r="A2793" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2793">
+        <v>8</v>
+      </c>
+      <c r="C2793">
+        <v>5150</v>
+      </c>
+      <c r="D2793" t="s">
+        <v>2795</v>
+      </c>
+    </row>
+    <row r="2794" spans="1:4">
+      <c r="A2794" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2794">
+        <v>9</v>
+      </c>
+      <c r="C2794">
+        <v>5110</v>
+      </c>
+      <c r="D2794" t="s">
+        <v>2796</v>
+      </c>
+    </row>
+    <row r="2795" spans="1:4">
+      <c r="A2795" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2795">
+        <v>10</v>
+      </c>
+      <c r="C2795">
+        <v>5080</v>
+      </c>
+      <c r="D2795" t="s">
+        <v>2797</v>
+      </c>
+    </row>
+    <row r="2796" spans="1:4">
+      <c r="A2796" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2796">
+        <v>11</v>
+      </c>
+      <c r="C2796">
+        <v>5060</v>
+      </c>
+      <c r="D2796" t="s">
+        <v>2798</v>
+      </c>
+    </row>
+    <row r="2797" spans="1:4">
+      <c r="A2797" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2797">
+        <v>12</v>
+      </c>
+      <c r="C2797">
+        <v>5050</v>
+      </c>
+      <c r="D2797" t="s">
+        <v>2799</v>
+      </c>
+    </row>
+    <row r="2798" spans="1:4">
+      <c r="A2798" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2798">
+        <v>13</v>
+      </c>
+      <c r="C2798">
+        <v>5060</v>
+      </c>
+      <c r="D2798" t="s">
+        <v>2800</v>
+      </c>
+    </row>
+    <row r="2799" spans="1:4">
+      <c r="A2799" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2799">
+        <v>14</v>
+      </c>
+      <c r="C2799">
+        <v>5060</v>
+      </c>
+      <c r="D2799" t="s">
+        <v>2801</v>
+      </c>
+    </row>
+    <row r="2800" spans="1:4">
+      <c r="A2800" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2800">
+        <v>15</v>
+      </c>
+      <c r="C2800">
+        <v>5070</v>
+      </c>
+      <c r="D2800" t="s">
+        <v>2802</v>
+      </c>
+    </row>
+    <row r="2801" spans="1:4">
+      <c r="A2801" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2801">
+        <v>16</v>
+      </c>
+      <c r="C2801">
+        <v>5080</v>
+      </c>
+      <c r="D2801" t="s">
+        <v>2803</v>
+      </c>
+    </row>
+    <row r="2802" spans="1:4">
+      <c r="A2802" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2802">
+        <v>17</v>
+      </c>
+      <c r="C2802">
+        <v>5080</v>
+      </c>
+      <c r="D2802" t="s">
+        <v>2804</v>
+      </c>
+    </row>
+    <row r="2803" spans="1:4">
+      <c r="A2803" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2803">
+        <v>18</v>
+      </c>
+      <c r="C2803">
+        <v>5080</v>
+      </c>
+      <c r="D2803" t="s">
+        <v>2805</v>
+      </c>
+    </row>
+    <row r="2804" spans="1:4">
+      <c r="A2804" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2804">
+        <v>19</v>
+      </c>
+      <c r="C2804">
+        <v>5080</v>
+      </c>
+      <c r="D2804" t="s">
+        <v>2806</v>
+      </c>
+    </row>
+    <row r="2805" spans="1:4">
+      <c r="A2805" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2805">
+        <v>20</v>
+      </c>
+      <c r="C2805">
+        <v>5090</v>
+      </c>
+      <c r="D2805" t="s">
+        <v>2807</v>
+      </c>
+    </row>
+    <row r="2806" spans="1:4">
+      <c r="A2806" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2806">
+        <v>21</v>
+      </c>
+      <c r="C2806">
+        <v>5120</v>
+      </c>
+      <c r="D2806" t="s">
+        <v>2808</v>
+      </c>
+    </row>
+    <row r="2807" spans="1:4">
+      <c r="A2807" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2807">
+        <v>22</v>
+      </c>
+      <c r="C2807">
+        <v>5160</v>
+      </c>
+      <c r="D2807" t="s">
+        <v>2809</v>
+      </c>
+    </row>
+    <row r="2808" spans="1:4">
+      <c r="A2808" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2808">
+        <v>23</v>
+      </c>
+      <c r="C2808">
+        <v>5230</v>
+      </c>
+      <c r="D2808" t="s">
+        <v>2810</v>
+      </c>
+    </row>
+    <row r="2809" spans="1:4">
+      <c r="A2809" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2809">
+        <v>24</v>
+      </c>
+      <c r="C2809">
+        <v>5310</v>
+      </c>
+      <c r="D2809" t="s">
+        <v>2811</v>
+      </c>
+    </row>
+    <row r="2810" spans="1:4">
+      <c r="A2810" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2810">
+        <v>25</v>
+      </c>
+      <c r="C2810">
+        <v>5420</v>
+      </c>
+      <c r="D2810" t="s">
+        <v>2812</v>
+      </c>
+    </row>
+    <row r="2811" spans="1:4">
+      <c r="A2811" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2811">
+        <v>26</v>
+      </c>
+      <c r="C2811">
+        <v>5540</v>
+      </c>
+      <c r="D2811" t="s">
+        <v>2813</v>
+      </c>
+    </row>
+    <row r="2812" spans="1:4">
+      <c r="A2812" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2812">
+        <v>27</v>
+      </c>
+      <c r="C2812">
+        <v>5680</v>
+      </c>
+      <c r="D2812" t="s">
+        <v>2814</v>
+      </c>
+    </row>
+    <row r="2813" spans="1:4">
+      <c r="A2813" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2813">
+        <v>28</v>
+      </c>
+      <c r="C2813">
+        <v>5810</v>
+      </c>
+      <c r="D2813" t="s">
+        <v>2815</v>
+      </c>
+    </row>
+    <row r="2814" spans="1:4">
+      <c r="A2814" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2814">
+        <v>29</v>
+      </c>
+      <c r="C2814">
+        <v>5930</v>
+      </c>
+      <c r="D2814" t="s">
+        <v>2816</v>
+      </c>
+    </row>
+    <row r="2815" spans="1:4">
+      <c r="A2815" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2815">
+        <v>30</v>
+      </c>
+      <c r="C2815">
+        <v>6040</v>
+      </c>
+      <c r="D2815" t="s">
+        <v>2817</v>
+      </c>
+    </row>
+    <row r="2816" spans="1:4">
+      <c r="A2816" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2816">
+        <v>31</v>
+      </c>
+      <c r="C2816">
+        <v>6120</v>
+      </c>
+      <c r="D2816" t="s">
+        <v>2818</v>
+      </c>
+    </row>
+    <row r="2817" spans="1:4">
+      <c r="A2817" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2817">
+        <v>32</v>
+      </c>
+      <c r="C2817">
+        <v>6180</v>
+      </c>
+      <c r="D2817" t="s">
+        <v>2819</v>
+      </c>
+    </row>
+    <row r="2818" spans="1:4">
+      <c r="A2818" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2818">
+        <v>33</v>
+      </c>
+      <c r="C2818">
+        <v>6190</v>
+      </c>
+      <c r="D2818" t="s">
+        <v>2820</v>
+      </c>
+    </row>
+    <row r="2819" spans="1:4">
+      <c r="A2819" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2819">
+        <v>34</v>
+      </c>
+      <c r="C2819">
+        <v>6180</v>
+      </c>
+      <c r="D2819" t="s">
+        <v>2821</v>
+      </c>
+    </row>
+    <row r="2820" spans="1:4">
+      <c r="A2820" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2820">
+        <v>35</v>
+      </c>
+      <c r="C2820">
+        <v>6130</v>
+      </c>
+      <c r="D2820" t="s">
+        <v>2822</v>
+      </c>
+    </row>
+    <row r="2821" spans="1:4">
+      <c r="A2821" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2821">
+        <v>36</v>
+      </c>
+      <c r="C2821">
+        <v>6050</v>
+      </c>
+      <c r="D2821" t="s">
+        <v>2823</v>
+      </c>
+    </row>
+    <row r="2822" spans="1:4">
+      <c r="A2822" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2822">
+        <v>37</v>
+      </c>
+      <c r="C2822">
+        <v>5950</v>
+      </c>
+      <c r="D2822" t="s">
+        <v>2824</v>
+      </c>
+    </row>
+    <row r="2823" spans="1:4">
+      <c r="A2823" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2823">
+        <v>38</v>
+      </c>
+      <c r="C2823">
+        <v>5830</v>
+      </c>
+      <c r="D2823" t="s">
+        <v>2825</v>
+      </c>
+    </row>
+    <row r="2824" spans="1:4">
+      <c r="A2824" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2824">
+        <v>39</v>
+      </c>
+      <c r="C2824">
+        <v>5700</v>
+      </c>
+      <c r="D2824" t="s">
+        <v>2826</v>
+      </c>
+    </row>
+    <row r="2825" spans="1:4">
+      <c r="A2825" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2825">
+        <v>40</v>
+      </c>
+      <c r="C2825">
+        <v>5570</v>
+      </c>
+      <c r="D2825" t="s">
+        <v>2827</v>
+      </c>
+    </row>
+    <row r="2826" spans="1:4">
+      <c r="A2826" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2826">
+        <v>41</v>
+      </c>
+      <c r="C2826">
+        <v>5450</v>
+      </c>
+      <c r="D2826" t="s">
+        <v>2828</v>
+      </c>
+    </row>
+    <row r="2827" spans="1:4">
+      <c r="A2827" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2827">
+        <v>42</v>
+      </c>
+      <c r="C2827">
+        <v>5340</v>
+      </c>
+      <c r="D2827" t="s">
+        <v>2829</v>
+      </c>
+    </row>
+    <row r="2828" spans="1:4">
+      <c r="A2828" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2828">
+        <v>43</v>
+      </c>
+      <c r="C2828">
+        <v>5230</v>
+      </c>
+      <c r="D2828" t="s">
+        <v>2830</v>
+      </c>
+    </row>
+    <row r="2829" spans="1:4">
+      <c r="A2829" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2829">
+        <v>44</v>
+      </c>
+      <c r="C2829">
+        <v>5150</v>
+      </c>
+      <c r="D2829" t="s">
+        <v>2831</v>
+      </c>
+    </row>
+    <row r="2830" spans="1:4">
+      <c r="A2830" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2830">
+        <v>45</v>
+      </c>
+      <c r="C2830">
+        <v>5070</v>
+      </c>
+      <c r="D2830" t="s">
+        <v>2832</v>
+      </c>
+    </row>
+    <row r="2831" spans="1:4">
+      <c r="A2831" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2831">
+        <v>46</v>
+      </c>
+      <c r="C2831">
+        <v>5010</v>
+      </c>
+      <c r="D2831" t="s">
+        <v>2833</v>
+      </c>
+    </row>
+    <row r="2832" spans="1:4">
+      <c r="A2832" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2832">
+        <v>47</v>
+      </c>
+      <c r="C2832">
+        <v>4950</v>
+      </c>
+      <c r="D2832" t="s">
+        <v>2834</v>
+      </c>
+    </row>
+    <row r="2833" spans="1:4">
+      <c r="A2833" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2833">
+        <v>48</v>
+      </c>
+      <c r="C2833">
+        <v>4910</v>
+      </c>
+      <c r="D2833" t="s">
+        <v>2835</v>
+      </c>
+    </row>
+    <row r="2834" spans="1:4">
+      <c r="A2834" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2834">
+        <v>49</v>
+      </c>
+      <c r="C2834">
+        <v>4870</v>
+      </c>
+      <c r="D2834" t="s">
+        <v>2836</v>
+      </c>
+    </row>
+    <row r="2835" spans="1:4">
+      <c r="A2835" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2835">
+        <v>50</v>
+      </c>
+      <c r="C2835">
+        <v>4830</v>
+      </c>
+      <c r="D2835" t="s">
+        <v>2837</v>
+      </c>
+    </row>
+    <row r="2836" spans="1:4">
+      <c r="A2836" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2836">
+        <v>51</v>
+      </c>
+      <c r="C2836">
+        <v>4800</v>
+      </c>
+      <c r="D2836" t="s">
+        <v>2838</v>
+      </c>
+    </row>
+    <row r="2837" spans="1:4">
+      <c r="A2837" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2837">
+        <v>52</v>
+      </c>
+      <c r="C2837">
+        <v>4780</v>
+      </c>
+      <c r="D2837" t="s">
+        <v>2839</v>
+      </c>
+    </row>
+    <row r="2838" spans="1:4">
+      <c r="A2838" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2838">
+        <v>53</v>
+      </c>
+      <c r="C2838">
+        <v>4760</v>
+      </c>
+      <c r="D2838" t="s">
+        <v>2840</v>
+      </c>
+    </row>
+    <row r="2839" spans="1:4">
+      <c r="A2839" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2839">
+        <v>54</v>
+      </c>
+      <c r="C2839">
+        <v>4740</v>
+      </c>
+      <c r="D2839" t="s">
+        <v>2841</v>
+      </c>
+    </row>
+    <row r="2840" spans="1:4">
+      <c r="A2840" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2840">
+        <v>55</v>
+      </c>
+      <c r="C2840">
+        <v>4730</v>
+      </c>
+      <c r="D2840" t="s">
+        <v>2842</v>
+      </c>
+    </row>
+    <row r="2841" spans="1:4">
+      <c r="A2841" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2841">
+        <v>56</v>
+      </c>
+      <c r="C2841">
+        <v>4720</v>
+      </c>
+      <c r="D2841" t="s">
+        <v>2843</v>
+      </c>
+    </row>
+    <row r="2842" spans="1:4">
+      <c r="A2842" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2842">
+        <v>57</v>
+      </c>
+      <c r="C2842">
+        <v>4720</v>
+      </c>
+      <c r="D2842" t="s">
+        <v>2844</v>
+      </c>
+    </row>
+    <row r="2843" spans="1:4">
+      <c r="A2843" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2843">
+        <v>58</v>
+      </c>
+      <c r="C2843">
+        <v>4720</v>
+      </c>
+      <c r="D2843" t="s">
+        <v>2845</v>
+      </c>
+    </row>
+    <row r="2844" spans="1:4">
+      <c r="A2844" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2844">
+        <v>59</v>
+      </c>
+      <c r="C2844">
+        <v>4720</v>
+      </c>
+      <c r="D2844" t="s">
+        <v>2846</v>
+      </c>
+    </row>
+    <row r="2845" spans="1:4">
+      <c r="A2845" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2845">
+        <v>60</v>
+      </c>
+      <c r="C2845">
+        <v>4730</v>
+      </c>
+      <c r="D2845" t="s">
+        <v>2847</v>
+      </c>
+    </row>
+    <row r="2846" spans="1:4">
+      <c r="A2846" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2846">
+        <v>61</v>
+      </c>
+      <c r="C2846">
+        <v>4740</v>
+      </c>
+      <c r="D2846" t="s">
+        <v>2848</v>
+      </c>
+    </row>
+    <row r="2847" spans="1:4">
+      <c r="A2847" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2847">
+        <v>62</v>
+      </c>
+      <c r="C2847">
+        <v>4750</v>
+      </c>
+      <c r="D2847" t="s">
+        <v>2849</v>
+      </c>
+    </row>
+    <row r="2848" spans="1:4">
+      <c r="A2848" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2848">
+        <v>63</v>
+      </c>
+      <c r="C2848">
+        <v>4780</v>
+      </c>
+      <c r="D2848" t="s">
+        <v>2850</v>
+      </c>
+    </row>
+    <row r="2849" spans="1:4">
+      <c r="A2849" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2849">
+        <v>64</v>
+      </c>
+      <c r="C2849">
+        <v>4820</v>
+      </c>
+      <c r="D2849" t="s">
+        <v>2851</v>
+      </c>
+    </row>
+    <row r="2850" spans="1:4">
+      <c r="A2850" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2850">
+        <v>65</v>
+      </c>
+      <c r="C2850">
+        <v>4880</v>
+      </c>
+      <c r="D2850" t="s">
+        <v>2852</v>
+      </c>
+    </row>
+    <row r="2851" spans="1:4">
+      <c r="A2851" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2851">
+        <v>66</v>
+      </c>
+      <c r="C2851">
+        <v>4950</v>
+      </c>
+      <c r="D2851" t="s">
+        <v>2853</v>
+      </c>
+    </row>
+    <row r="2852" spans="1:4">
+      <c r="A2852" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2852">
+        <v>67</v>
+      </c>
+      <c r="C2852">
+        <v>5040</v>
+      </c>
+      <c r="D2852" t="s">
+        <v>2854</v>
+      </c>
+    </row>
+    <row r="2853" spans="1:4">
+      <c r="A2853" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2853">
+        <v>68</v>
+      </c>
+      <c r="C2853">
+        <v>5150</v>
+      </c>
+      <c r="D2853" t="s">
+        <v>2855</v>
+      </c>
+    </row>
+    <row r="2854" spans="1:4">
+      <c r="A2854" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2854">
+        <v>69</v>
+      </c>
+      <c r="C2854">
+        <v>5260</v>
+      </c>
+      <c r="D2854" t="s">
+        <v>2856</v>
+      </c>
+    </row>
+    <row r="2855" spans="1:4">
+      <c r="A2855" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2855">
+        <v>70</v>
+      </c>
+      <c r="C2855">
+        <v>5380</v>
+      </c>
+      <c r="D2855" t="s">
+        <v>2857</v>
+      </c>
+    </row>
+    <row r="2856" spans="1:4">
+      <c r="A2856" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2856">
+        <v>71</v>
+      </c>
+      <c r="C2856">
+        <v>5490</v>
+      </c>
+      <c r="D2856" t="s">
+        <v>2858</v>
+      </c>
+    </row>
+    <row r="2857" spans="1:4">
+      <c r="A2857" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2857">
+        <v>72</v>
+      </c>
+      <c r="C2857">
+        <v>5610</v>
+      </c>
+      <c r="D2857" t="s">
+        <v>2859</v>
+      </c>
+    </row>
+    <row r="2858" spans="1:4">
+      <c r="A2858" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2858">
+        <v>73</v>
+      </c>
+      <c r="C2858">
+        <v>5730</v>
+      </c>
+      <c r="D2858" t="s">
+        <v>2860</v>
+      </c>
+    </row>
+    <row r="2859" spans="1:4">
+      <c r="A2859" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2859">
+        <v>74</v>
+      </c>
+      <c r="C2859">
+        <v>5860</v>
+      </c>
+      <c r="D2859" t="s">
+        <v>2861</v>
+      </c>
+    </row>
+    <row r="2860" spans="1:4">
+      <c r="A2860" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2860">
+        <v>75</v>
+      </c>
+      <c r="C2860">
+        <v>6000</v>
+      </c>
+      <c r="D2860" t="s">
+        <v>2862</v>
+      </c>
+    </row>
+    <row r="2861" spans="1:4">
+      <c r="A2861" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2861">
+        <v>76</v>
+      </c>
+      <c r="C2861">
+        <v>6160</v>
+      </c>
+      <c r="D2861" t="s">
+        <v>2863</v>
+      </c>
+    </row>
+    <row r="2862" spans="1:4">
+      <c r="A2862" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2862">
+        <v>77</v>
+      </c>
+      <c r="C2862">
+        <v>6330</v>
+      </c>
+      <c r="D2862" t="s">
+        <v>2864</v>
+      </c>
+    </row>
+    <row r="2863" spans="1:4">
+      <c r="A2863" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2863">
+        <v>78</v>
+      </c>
+      <c r="C2863">
+        <v>6500</v>
+      </c>
+      <c r="D2863" t="s">
+        <v>2865</v>
+      </c>
+    </row>
+    <row r="2864" spans="1:4">
+      <c r="A2864" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2864">
+        <v>79</v>
+      </c>
+      <c r="C2864">
+        <v>6670</v>
+      </c>
+      <c r="D2864" t="s">
+        <v>2866</v>
+      </c>
+    </row>
+    <row r="2865" spans="1:4">
+      <c r="A2865" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2865">
+        <v>80</v>
+      </c>
+      <c r="C2865">
+        <v>6830</v>
+      </c>
+      <c r="D2865" t="s">
+        <v>2867</v>
+      </c>
+    </row>
+    <row r="2866" spans="1:4">
+      <c r="A2866" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2866">
+        <v>81</v>
+      </c>
+      <c r="C2866">
+        <v>6990</v>
+      </c>
+      <c r="D2866" t="s">
+        <v>2868</v>
+      </c>
+    </row>
+    <row r="2867" spans="1:4">
+      <c r="A2867" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2867">
+        <v>82</v>
+      </c>
+      <c r="C2867">
+        <v>7140</v>
+      </c>
+      <c r="D2867" t="s">
+        <v>2869</v>
+      </c>
+    </row>
+    <row r="2868" spans="1:4">
+      <c r="A2868" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2868">
+        <v>83</v>
+      </c>
+      <c r="C2868">
+        <v>7240</v>
+      </c>
+      <c r="D2868" t="s">
+        <v>2870</v>
+      </c>
+    </row>
+    <row r="2869" spans="1:4">
+      <c r="A2869" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2869">
+        <v>84</v>
+      </c>
+      <c r="C2869">
+        <v>7310</v>
+      </c>
+      <c r="D2869" t="s">
+        <v>2871</v>
+      </c>
+    </row>
+    <row r="2870" spans="1:4">
+      <c r="A2870" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2870">
+        <v>85</v>
+      </c>
+      <c r="C2870">
+        <v>7290</v>
+      </c>
+      <c r="D2870" t="s">
+        <v>2872</v>
+      </c>
+    </row>
+    <row r="2871" spans="1:4">
+      <c r="A2871" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2871">
+        <v>86</v>
+      </c>
+      <c r="C2871">
+        <v>7210</v>
+      </c>
+      <c r="D2871" t="s">
+        <v>2873</v>
+      </c>
+    </row>
+    <row r="2872" spans="1:4">
+      <c r="A2872" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2872">
+        <v>87</v>
+      </c>
+      <c r="C2872">
+        <v>7150</v>
+      </c>
+      <c r="D2872" t="s">
+        <v>2874</v>
+      </c>
+    </row>
+    <row r="2873" spans="1:4">
+      <c r="A2873" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2873">
+        <v>88</v>
+      </c>
+      <c r="C2873">
+        <v>7080</v>
+      </c>
+      <c r="D2873" t="s">
+        <v>2875</v>
+      </c>
+    </row>
+    <row r="2874" spans="1:4">
+      <c r="A2874" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2874">
+        <v>89</v>
+      </c>
+      <c r="C2874">
+        <v>6980</v>
+      </c>
+      <c r="D2874" t="s">
+        <v>2876</v>
+      </c>
+    </row>
+    <row r="2875" spans="1:4">
+      <c r="A2875" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2875">
+        <v>90</v>
+      </c>
+      <c r="C2875">
+        <v>6900</v>
+      </c>
+      <c r="D2875" t="s">
+        <v>2877</v>
+      </c>
+    </row>
+    <row r="2876" spans="1:4">
+      <c r="A2876" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2876">
+        <v>91</v>
+      </c>
+      <c r="C2876">
+        <v>6730</v>
+      </c>
+      <c r="D2876" t="s">
+        <v>2878</v>
+      </c>
+    </row>
+    <row r="2877" spans="1:4">
+      <c r="A2877" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2877">
+        <v>92</v>
+      </c>
+      <c r="C2877">
+        <v>6530</v>
+      </c>
+      <c r="D2877" t="s">
+        <v>2879</v>
+      </c>
+    </row>
+    <row r="2878" spans="1:4">
+      <c r="A2878" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2878">
+        <v>93</v>
+      </c>
+      <c r="C2878">
+        <v>6280</v>
+      </c>
+      <c r="D2878" t="s">
+        <v>2880</v>
+      </c>
+    </row>
+    <row r="2879" spans="1:4">
+      <c r="A2879" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2879">
+        <v>94</v>
+      </c>
+      <c r="C2879">
+        <v>6050</v>
+      </c>
+      <c r="D2879" t="s">
+        <v>2881</v>
+      </c>
+    </row>
+    <row r="2880" spans="1:4">
+      <c r="A2880" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2880">
+        <v>95</v>
+      </c>
+      <c r="C2880">
+        <v>5980</v>
+      </c>
+      <c r="D2880" t="s">
+        <v>2882</v>
+      </c>
+    </row>
+    <row r="2881" spans="1:4">
+      <c r="A2881" s="2">
+        <v>46142</v>
+      </c>
+      <c r="B2881">
+        <v>96</v>
+      </c>
+      <c r="C2881">
+        <v>5870</v>
+      </c>
+      <c r="D2881" t="s">
+        <v>2883</v>
       </c>
     </row>
   </sheetData>

--- a/Market Fundamentals/Transelectrica_data/Cons_Prod_final/Weekly_Consumption_2026.xlsx
+++ b/Market Fundamentals/Transelectrica_data/Cons_Prod_final/Weekly_Consumption_2026.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1828" uniqueCount="1828">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1924" uniqueCount="1924">
   <si>
     <t>Date</t>
   </si>
@@ -5498,6 +5498,294 @@
   </si>
   <si>
     <t>19.05.202696.0</t>
+  </si>
+  <si>
+    <t>20.05.20261.0</t>
+  </si>
+  <si>
+    <t>20.05.20262.0</t>
+  </si>
+  <si>
+    <t>20.05.20263.0</t>
+  </si>
+  <si>
+    <t>20.05.20264.0</t>
+  </si>
+  <si>
+    <t>20.05.20265.0</t>
+  </si>
+  <si>
+    <t>20.05.20266.0</t>
+  </si>
+  <si>
+    <t>20.05.20267.0</t>
+  </si>
+  <si>
+    <t>20.05.20268.0</t>
+  </si>
+  <si>
+    <t>20.05.20269.0</t>
+  </si>
+  <si>
+    <t>20.05.202610.0</t>
+  </si>
+  <si>
+    <t>20.05.202611.0</t>
+  </si>
+  <si>
+    <t>20.05.202612.0</t>
+  </si>
+  <si>
+    <t>20.05.202613.0</t>
+  </si>
+  <si>
+    <t>20.05.202614.0</t>
+  </si>
+  <si>
+    <t>20.05.202615.0</t>
+  </si>
+  <si>
+    <t>20.05.202616.0</t>
+  </si>
+  <si>
+    <t>20.05.202617.0</t>
+  </si>
+  <si>
+    <t>20.05.202618.0</t>
+  </si>
+  <si>
+    <t>20.05.202619.0</t>
+  </si>
+  <si>
+    <t>20.05.202620.0</t>
+  </si>
+  <si>
+    <t>20.05.202621.0</t>
+  </si>
+  <si>
+    <t>20.05.202622.0</t>
+  </si>
+  <si>
+    <t>20.05.202623.0</t>
+  </si>
+  <si>
+    <t>20.05.202624.0</t>
+  </si>
+  <si>
+    <t>20.05.202625.0</t>
+  </si>
+  <si>
+    <t>20.05.202626.0</t>
+  </si>
+  <si>
+    <t>20.05.202627.0</t>
+  </si>
+  <si>
+    <t>20.05.202628.0</t>
+  </si>
+  <si>
+    <t>20.05.202629.0</t>
+  </si>
+  <si>
+    <t>20.05.202630.0</t>
+  </si>
+  <si>
+    <t>20.05.202631.0</t>
+  </si>
+  <si>
+    <t>20.05.202632.0</t>
+  </si>
+  <si>
+    <t>20.05.202633.0</t>
+  </si>
+  <si>
+    <t>20.05.202634.0</t>
+  </si>
+  <si>
+    <t>20.05.202635.0</t>
+  </si>
+  <si>
+    <t>20.05.202636.0</t>
+  </si>
+  <si>
+    <t>20.05.202637.0</t>
+  </si>
+  <si>
+    <t>20.05.202638.0</t>
+  </si>
+  <si>
+    <t>20.05.202639.0</t>
+  </si>
+  <si>
+    <t>20.05.202640.0</t>
+  </si>
+  <si>
+    <t>20.05.202641.0</t>
+  </si>
+  <si>
+    <t>20.05.202642.0</t>
+  </si>
+  <si>
+    <t>20.05.202643.0</t>
+  </si>
+  <si>
+    <t>20.05.202644.0</t>
+  </si>
+  <si>
+    <t>20.05.202645.0</t>
+  </si>
+  <si>
+    <t>20.05.202646.0</t>
+  </si>
+  <si>
+    <t>20.05.202647.0</t>
+  </si>
+  <si>
+    <t>20.05.202648.0</t>
+  </si>
+  <si>
+    <t>20.05.202649.0</t>
+  </si>
+  <si>
+    <t>20.05.202650.0</t>
+  </si>
+  <si>
+    <t>20.05.202651.0</t>
+  </si>
+  <si>
+    <t>20.05.202652.0</t>
+  </si>
+  <si>
+    <t>20.05.202653.0</t>
+  </si>
+  <si>
+    <t>20.05.202654.0</t>
+  </si>
+  <si>
+    <t>20.05.202655.0</t>
+  </si>
+  <si>
+    <t>20.05.202656.0</t>
+  </si>
+  <si>
+    <t>20.05.202657.0</t>
+  </si>
+  <si>
+    <t>20.05.202658.0</t>
+  </si>
+  <si>
+    <t>20.05.202659.0</t>
+  </si>
+  <si>
+    <t>20.05.202660.0</t>
+  </si>
+  <si>
+    <t>20.05.202661.0</t>
+  </si>
+  <si>
+    <t>20.05.202662.0</t>
+  </si>
+  <si>
+    <t>20.05.202663.0</t>
+  </si>
+  <si>
+    <t>20.05.202664.0</t>
+  </si>
+  <si>
+    <t>20.05.202665.0</t>
+  </si>
+  <si>
+    <t>20.05.202666.0</t>
+  </si>
+  <si>
+    <t>20.05.202667.0</t>
+  </si>
+  <si>
+    <t>20.05.202668.0</t>
+  </si>
+  <si>
+    <t>20.05.202669.0</t>
+  </si>
+  <si>
+    <t>20.05.202670.0</t>
+  </si>
+  <si>
+    <t>20.05.202671.0</t>
+  </si>
+  <si>
+    <t>20.05.202672.0</t>
+  </si>
+  <si>
+    <t>20.05.202673.0</t>
+  </si>
+  <si>
+    <t>20.05.202674.0</t>
+  </si>
+  <si>
+    <t>20.05.202675.0</t>
+  </si>
+  <si>
+    <t>20.05.202676.0</t>
+  </si>
+  <si>
+    <t>20.05.202677.0</t>
+  </si>
+  <si>
+    <t>20.05.202678.0</t>
+  </si>
+  <si>
+    <t>20.05.202679.0</t>
+  </si>
+  <si>
+    <t>20.05.202680.0</t>
+  </si>
+  <si>
+    <t>20.05.202681.0</t>
+  </si>
+  <si>
+    <t>20.05.202682.0</t>
+  </si>
+  <si>
+    <t>20.05.202683.0</t>
+  </si>
+  <si>
+    <t>20.05.202684.0</t>
+  </si>
+  <si>
+    <t>20.05.202685.0</t>
+  </si>
+  <si>
+    <t>20.05.202686.0</t>
+  </si>
+  <si>
+    <t>20.05.202687.0</t>
+  </si>
+  <si>
+    <t>20.05.202688.0</t>
+  </si>
+  <si>
+    <t>20.05.202689.0</t>
+  </si>
+  <si>
+    <t>20.05.202690.0</t>
+  </si>
+  <si>
+    <t>20.05.202691.0</t>
+  </si>
+  <si>
+    <t>20.05.202692.0</t>
+  </si>
+  <si>
+    <t>20.05.202693.0</t>
+  </si>
+  <si>
+    <t>20.05.202694.0</t>
+  </si>
+  <si>
+    <t>20.05.202695.0</t>
+  </si>
+  <si>
+    <t>20.05.202696.0</t>
   </si>
 </sst>
 </file>
@@ -5859,7 +6147,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1825"/>
+  <dimension ref="A1:D1921"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -22012,7 +22300,7 @@
         <v>1</v>
       </c>
       <c r="C1154">
-        <v>5500</v>
+        <v>5470</v>
       </c>
       <c r="D1154" t="s">
         <v>1156</v>
@@ -22026,7 +22314,7 @@
         <v>2</v>
       </c>
       <c r="C1155">
-        <v>5450</v>
+        <v>5410</v>
       </c>
       <c r="D1155" t="s">
         <v>1157</v>
@@ -22040,7 +22328,7 @@
         <v>3</v>
       </c>
       <c r="C1156">
-        <v>5390</v>
+        <v>5350</v>
       </c>
       <c r="D1156" t="s">
         <v>1158</v>
@@ -22054,7 +22342,7 @@
         <v>4</v>
       </c>
       <c r="C1157">
-        <v>5320</v>
+        <v>5300</v>
       </c>
       <c r="D1157" t="s">
         <v>1159</v>
@@ -22068,7 +22356,7 @@
         <v>5</v>
       </c>
       <c r="C1158">
-        <v>5260</v>
+        <v>5220</v>
       </c>
       <c r="D1158" t="s">
         <v>1160</v>
@@ -22082,7 +22370,7 @@
         <v>6</v>
       </c>
       <c r="C1159">
-        <v>5220</v>
+        <v>5190</v>
       </c>
       <c r="D1159" t="s">
         <v>1161</v>
@@ -22110,7 +22398,7 @@
         <v>8</v>
       </c>
       <c r="C1161">
-        <v>5130</v>
+        <v>5150</v>
       </c>
       <c r="D1161" t="s">
         <v>1163</v>
@@ -22124,7 +22412,7 @@
         <v>9</v>
       </c>
       <c r="C1162">
-        <v>5100</v>
+        <v>5090</v>
       </c>
       <c r="D1162" t="s">
         <v>1164</v>
@@ -22152,7 +22440,7 @@
         <v>11</v>
       </c>
       <c r="C1164">
-        <v>5070</v>
+        <v>5080</v>
       </c>
       <c r="D1164" t="s">
         <v>1166</v>
@@ -22166,7 +22454,7 @@
         <v>12</v>
       </c>
       <c r="C1165">
-        <v>5060</v>
+        <v>5080</v>
       </c>
       <c r="D1165" t="s">
         <v>1167</v>
@@ -22180,7 +22468,7 @@
         <v>13</v>
       </c>
       <c r="C1166">
-        <v>5050</v>
+        <v>5070</v>
       </c>
       <c r="D1166" t="s">
         <v>1168</v>
@@ -22194,7 +22482,7 @@
         <v>14</v>
       </c>
       <c r="C1167">
-        <v>5050</v>
+        <v>5070</v>
       </c>
       <c r="D1167" t="s">
         <v>1169</v>
@@ -22208,7 +22496,7 @@
         <v>15</v>
       </c>
       <c r="C1168">
-        <v>5050</v>
+        <v>5070</v>
       </c>
       <c r="D1168" t="s">
         <v>1170</v>
@@ -22222,7 +22510,7 @@
         <v>16</v>
       </c>
       <c r="C1169">
-        <v>5060</v>
+        <v>5080</v>
       </c>
       <c r="D1169" t="s">
         <v>1171</v>
@@ -22236,7 +22524,7 @@
         <v>17</v>
       </c>
       <c r="C1170">
-        <v>5070</v>
+        <v>5100</v>
       </c>
       <c r="D1170" t="s">
         <v>1172</v>
@@ -22250,7 +22538,7 @@
         <v>18</v>
       </c>
       <c r="C1171">
-        <v>5080</v>
+        <v>5100</v>
       </c>
       <c r="D1171" t="s">
         <v>1173</v>
@@ -22264,7 +22552,7 @@
         <v>19</v>
       </c>
       <c r="C1172">
-        <v>5090</v>
+        <v>5100</v>
       </c>
       <c r="D1172" t="s">
         <v>1174</v>
@@ -22278,7 +22566,7 @@
         <v>20</v>
       </c>
       <c r="C1173">
-        <v>5120</v>
+        <v>5100</v>
       </c>
       <c r="D1173" t="s">
         <v>1175</v>
@@ -22292,7 +22580,7 @@
         <v>21</v>
       </c>
       <c r="C1174">
-        <v>5150</v>
+        <v>5110</v>
       </c>
       <c r="D1174" t="s">
         <v>1176</v>
@@ -22306,7 +22594,7 @@
         <v>22</v>
       </c>
       <c r="C1175">
-        <v>5200</v>
+        <v>5140</v>
       </c>
       <c r="D1175" t="s">
         <v>1177</v>
@@ -22320,7 +22608,7 @@
         <v>23</v>
       </c>
       <c r="C1176">
-        <v>5260</v>
+        <v>5180</v>
       </c>
       <c r="D1176" t="s">
         <v>1178</v>
@@ -22334,7 +22622,7 @@
         <v>24</v>
       </c>
       <c r="C1177">
-        <v>5320</v>
+        <v>5250</v>
       </c>
       <c r="D1177" t="s">
         <v>1179</v>
@@ -22348,7 +22636,7 @@
         <v>25</v>
       </c>
       <c r="C1178">
-        <v>5400</v>
+        <v>5310</v>
       </c>
       <c r="D1178" t="s">
         <v>1180</v>
@@ -22362,7 +22650,7 @@
         <v>26</v>
       </c>
       <c r="C1179">
-        <v>5480</v>
+        <v>5410</v>
       </c>
       <c r="D1179" t="s">
         <v>1181</v>
@@ -22376,7 +22664,7 @@
         <v>27</v>
       </c>
       <c r="C1180">
-        <v>5570</v>
+        <v>5510</v>
       </c>
       <c r="D1180" t="s">
         <v>1182</v>
@@ -22390,7 +22678,7 @@
         <v>28</v>
       </c>
       <c r="C1181">
-        <v>5650</v>
+        <v>5620</v>
       </c>
       <c r="D1181" t="s">
         <v>1183</v>
@@ -22404,7 +22692,7 @@
         <v>29</v>
       </c>
       <c r="C1182">
-        <v>5740</v>
+        <v>5820</v>
       </c>
       <c r="D1182" t="s">
         <v>1184</v>
@@ -22418,7 +22706,7 @@
         <v>30</v>
       </c>
       <c r="C1183">
-        <v>5820</v>
+        <v>5950</v>
       </c>
       <c r="D1183" t="s">
         <v>1185</v>
@@ -22432,7 +22720,7 @@
         <v>31</v>
       </c>
       <c r="C1184">
-        <v>5900</v>
+        <v>6030</v>
       </c>
       <c r="D1184" t="s">
         <v>1186</v>
@@ -22446,7 +22734,7 @@
         <v>32</v>
       </c>
       <c r="C1185">
-        <v>5970</v>
+        <v>6080</v>
       </c>
       <c r="D1185" t="s">
         <v>1187</v>
@@ -22460,7 +22748,7 @@
         <v>33</v>
       </c>
       <c r="C1186">
-        <v>6030</v>
+        <v>6110</v>
       </c>
       <c r="D1186" t="s">
         <v>1188</v>
@@ -22474,7 +22762,7 @@
         <v>34</v>
       </c>
       <c r="C1187">
-        <v>6080</v>
+        <v>6100</v>
       </c>
       <c r="D1187" t="s">
         <v>1189</v>
@@ -22502,7 +22790,7 @@
         <v>36</v>
       </c>
       <c r="C1189">
-        <v>6100</v>
+        <v>6090</v>
       </c>
       <c r="D1189" t="s">
         <v>1191</v>
@@ -22516,7 +22804,7 @@
         <v>37</v>
       </c>
       <c r="C1190">
-        <v>6090</v>
+        <v>6060</v>
       </c>
       <c r="D1190" t="s">
         <v>1192</v>
@@ -22530,7 +22818,7 @@
         <v>38</v>
       </c>
       <c r="C1191">
-        <v>6060</v>
+        <v>6020</v>
       </c>
       <c r="D1191" t="s">
         <v>1193</v>
@@ -22544,7 +22832,7 @@
         <v>39</v>
       </c>
       <c r="C1192">
-        <v>6010</v>
+        <v>5990</v>
       </c>
       <c r="D1192" t="s">
         <v>1194</v>
@@ -22558,7 +22846,7 @@
         <v>40</v>
       </c>
       <c r="C1193">
-        <v>5950</v>
+        <v>5910</v>
       </c>
       <c r="D1193" t="s">
         <v>1195</v>
@@ -22572,7 +22860,7 @@
         <v>41</v>
       </c>
       <c r="C1194">
-        <v>5870</v>
+        <v>5830</v>
       </c>
       <c r="D1194" t="s">
         <v>1196</v>
@@ -22586,7 +22874,7 @@
         <v>42</v>
       </c>
       <c r="C1195">
-        <v>5800</v>
+        <v>5740</v>
       </c>
       <c r="D1195" t="s">
         <v>1197</v>
@@ -22600,7 +22888,7 @@
         <v>43</v>
       </c>
       <c r="C1196">
-        <v>5720</v>
+        <v>5650</v>
       </c>
       <c r="D1196" t="s">
         <v>1198</v>
@@ -22614,7 +22902,7 @@
         <v>44</v>
       </c>
       <c r="C1197">
-        <v>5650</v>
+        <v>5570</v>
       </c>
       <c r="D1197" t="s">
         <v>1199</v>
@@ -22628,7 +22916,7 @@
         <v>45</v>
       </c>
       <c r="C1198">
-        <v>5590</v>
+        <v>5460</v>
       </c>
       <c r="D1198" t="s">
         <v>1200</v>
@@ -22642,7 +22930,7 @@
         <v>46</v>
       </c>
       <c r="C1199">
-        <v>5540</v>
+        <v>5400</v>
       </c>
       <c r="D1199" t="s">
         <v>1201</v>
@@ -22656,7 +22944,7 @@
         <v>47</v>
       </c>
       <c r="C1200">
-        <v>5500</v>
+        <v>5350</v>
       </c>
       <c r="D1200" t="s">
         <v>1202</v>
@@ -22670,7 +22958,7 @@
         <v>48</v>
       </c>
       <c r="C1201">
-        <v>5470</v>
+        <v>5310</v>
       </c>
       <c r="D1201" t="s">
         <v>1203</v>
@@ -22684,7 +22972,7 @@
         <v>49</v>
       </c>
       <c r="C1202">
-        <v>5440</v>
+        <v>5280</v>
       </c>
       <c r="D1202" t="s">
         <v>1204</v>
@@ -22698,7 +22986,7 @@
         <v>50</v>
       </c>
       <c r="C1203">
-        <v>5420</v>
+        <v>5260</v>
       </c>
       <c r="D1203" t="s">
         <v>1205</v>
@@ -22712,7 +23000,7 @@
         <v>51</v>
       </c>
       <c r="C1204">
-        <v>5410</v>
+        <v>5240</v>
       </c>
       <c r="D1204" t="s">
         <v>1206</v>
@@ -22726,7 +23014,7 @@
         <v>52</v>
       </c>
       <c r="C1205">
-        <v>5390</v>
+        <v>5240</v>
       </c>
       <c r="D1205" t="s">
         <v>1207</v>
@@ -22740,7 +23028,7 @@
         <v>53</v>
       </c>
       <c r="C1206">
-        <v>5380</v>
+        <v>5240</v>
       </c>
       <c r="D1206" t="s">
         <v>1208</v>
@@ -22754,7 +23042,7 @@
         <v>54</v>
       </c>
       <c r="C1207">
-        <v>5380</v>
+        <v>5240</v>
       </c>
       <c r="D1207" t="s">
         <v>1209</v>
@@ -22768,7 +23056,7 @@
         <v>55</v>
       </c>
       <c r="C1208">
-        <v>5370</v>
+        <v>5240</v>
       </c>
       <c r="D1208" t="s">
         <v>1210</v>
@@ -22782,7 +23070,7 @@
         <v>56</v>
       </c>
       <c r="C1209">
-        <v>5370</v>
+        <v>5230</v>
       </c>
       <c r="D1209" t="s">
         <v>1211</v>
@@ -22796,7 +23084,7 @@
         <v>57</v>
       </c>
       <c r="C1210">
-        <v>5380</v>
+        <v>5210</v>
       </c>
       <c r="D1210" t="s">
         <v>1212</v>
@@ -22810,7 +23098,7 @@
         <v>58</v>
       </c>
       <c r="C1211">
-        <v>5390</v>
+        <v>5200</v>
       </c>
       <c r="D1211" t="s">
         <v>1213</v>
@@ -22824,7 +23112,7 @@
         <v>59</v>
       </c>
       <c r="C1212">
-        <v>5390</v>
+        <v>5200</v>
       </c>
       <c r="D1212" t="s">
         <v>1214</v>
@@ -22838,7 +23126,7 @@
         <v>60</v>
       </c>
       <c r="C1213">
-        <v>5400</v>
+        <v>5210</v>
       </c>
       <c r="D1213" t="s">
         <v>1215</v>
@@ -22852,7 +23140,7 @@
         <v>61</v>
       </c>
       <c r="C1214">
-        <v>5410</v>
+        <v>5240</v>
       </c>
       <c r="D1214" t="s">
         <v>1216</v>
@@ -22866,7 +23154,7 @@
         <v>62</v>
       </c>
       <c r="C1215">
-        <v>5410</v>
+        <v>5260</v>
       </c>
       <c r="D1215" t="s">
         <v>1217</v>
@@ -22880,7 +23168,7 @@
         <v>63</v>
       </c>
       <c r="C1216">
-        <v>5420</v>
+        <v>5280</v>
       </c>
       <c r="D1216" t="s">
         <v>1218</v>
@@ -22894,7 +23182,7 @@
         <v>64</v>
       </c>
       <c r="C1217">
-        <v>5440</v>
+        <v>5310</v>
       </c>
       <c r="D1217" t="s">
         <v>1219</v>
@@ -22908,7 +23196,7 @@
         <v>65</v>
       </c>
       <c r="C1218">
-        <v>5470</v>
+        <v>5370</v>
       </c>
       <c r="D1218" t="s">
         <v>1220</v>
@@ -22922,7 +23210,7 @@
         <v>66</v>
       </c>
       <c r="C1219">
-        <v>5510</v>
+        <v>5430</v>
       </c>
       <c r="D1219" t="s">
         <v>1221</v>
@@ -22936,7 +23224,7 @@
         <v>67</v>
       </c>
       <c r="C1220">
-        <v>5580</v>
+        <v>5500</v>
       </c>
       <c r="D1220" t="s">
         <v>1222</v>
@@ -22950,7 +23238,7 @@
         <v>68</v>
       </c>
       <c r="C1221">
-        <v>5650</v>
+        <v>5570</v>
       </c>
       <c r="D1221" t="s">
         <v>1223</v>
@@ -22964,7 +23252,7 @@
         <v>69</v>
       </c>
       <c r="C1222">
-        <v>5740</v>
+        <v>5660</v>
       </c>
       <c r="D1222" t="s">
         <v>1224</v>
@@ -22978,7 +23266,7 @@
         <v>70</v>
       </c>
       <c r="C1223">
-        <v>5840</v>
+        <v>5740</v>
       </c>
       <c r="D1223" t="s">
         <v>1225</v>
@@ -22992,7 +23280,7 @@
         <v>71</v>
       </c>
       <c r="C1224">
-        <v>5930</v>
+        <v>5810</v>
       </c>
       <c r="D1224" t="s">
         <v>1226</v>
@@ -23006,7 +23294,7 @@
         <v>72</v>
       </c>
       <c r="C1225">
-        <v>6010</v>
+        <v>5900</v>
       </c>
       <c r="D1225" t="s">
         <v>1227</v>
@@ -23020,7 +23308,7 @@
         <v>73</v>
       </c>
       <c r="C1226">
-        <v>6080</v>
+        <v>6010</v>
       </c>
       <c r="D1226" t="s">
         <v>1228</v>
@@ -23034,7 +23322,7 @@
         <v>74</v>
       </c>
       <c r="C1227">
-        <v>6160</v>
+        <v>6100</v>
       </c>
       <c r="D1227" t="s">
         <v>1229</v>
@@ -23048,7 +23336,7 @@
         <v>75</v>
       </c>
       <c r="C1228">
-        <v>6240</v>
+        <v>6190</v>
       </c>
       <c r="D1228" t="s">
         <v>1230</v>
@@ -23062,7 +23350,7 @@
         <v>76</v>
       </c>
       <c r="C1229">
-        <v>6330</v>
+        <v>6300</v>
       </c>
       <c r="D1229" t="s">
         <v>1231</v>
@@ -23076,7 +23364,7 @@
         <v>77</v>
       </c>
       <c r="C1230">
-        <v>6430</v>
+        <v>6390</v>
       </c>
       <c r="D1230" t="s">
         <v>1232</v>
@@ -23090,7 +23378,7 @@
         <v>78</v>
       </c>
       <c r="C1231">
-        <v>6540</v>
+        <v>6510</v>
       </c>
       <c r="D1231" t="s">
         <v>1233</v>
@@ -23104,7 +23392,7 @@
         <v>79</v>
       </c>
       <c r="C1232">
-        <v>6640</v>
+        <v>6610</v>
       </c>
       <c r="D1232" t="s">
         <v>1234</v>
@@ -23118,7 +23406,7 @@
         <v>80</v>
       </c>
       <c r="C1233">
-        <v>6720</v>
+        <v>6690</v>
       </c>
       <c r="D1233" t="s">
         <v>1235</v>
@@ -23132,7 +23420,7 @@
         <v>81</v>
       </c>
       <c r="C1234">
-        <v>6810</v>
+        <v>6780</v>
       </c>
       <c r="D1234" t="s">
         <v>1236</v>
@@ -23146,7 +23434,7 @@
         <v>82</v>
       </c>
       <c r="C1235">
-        <v>6910</v>
+        <v>6860</v>
       </c>
       <c r="D1235" t="s">
         <v>1237</v>
@@ -23160,7 +23448,7 @@
         <v>83</v>
       </c>
       <c r="C1236">
-        <v>6980</v>
+        <v>6910</v>
       </c>
       <c r="D1236" t="s">
         <v>1238</v>
@@ -23174,7 +23462,7 @@
         <v>84</v>
       </c>
       <c r="C1237">
-        <v>7030</v>
+        <v>6970</v>
       </c>
       <c r="D1237" t="s">
         <v>1239</v>
@@ -23188,7 +23476,7 @@
         <v>85</v>
       </c>
       <c r="C1238">
-        <v>7050</v>
+        <v>7010</v>
       </c>
       <c r="D1238" t="s">
         <v>1240</v>
@@ -23202,7 +23490,7 @@
         <v>86</v>
       </c>
       <c r="C1239">
-        <v>7050</v>
+        <v>6980</v>
       </c>
       <c r="D1239" t="s">
         <v>1241</v>
@@ -23216,7 +23504,7 @@
         <v>87</v>
       </c>
       <c r="C1240">
-        <v>7030</v>
+        <v>6920</v>
       </c>
       <c r="D1240" t="s">
         <v>1242</v>
@@ -23230,7 +23518,7 @@
         <v>88</v>
       </c>
       <c r="C1241">
-        <v>6980</v>
+        <v>6810</v>
       </c>
       <c r="D1241" t="s">
         <v>1243</v>
@@ -23244,7 +23532,7 @@
         <v>89</v>
       </c>
       <c r="C1242">
-        <v>6860</v>
+        <v>6650</v>
       </c>
       <c r="D1242" t="s">
         <v>1244</v>
@@ -23258,7 +23546,7 @@
         <v>90</v>
       </c>
       <c r="C1243">
-        <v>6730</v>
+        <v>6500</v>
       </c>
       <c r="D1243" t="s">
         <v>1245</v>
@@ -23272,7 +23560,7 @@
         <v>91</v>
       </c>
       <c r="C1244">
-        <v>6550</v>
+        <v>6350</v>
       </c>
       <c r="D1244" t="s">
         <v>1246</v>
@@ -23286,7 +23574,7 @@
         <v>92</v>
       </c>
       <c r="C1245">
-        <v>6360</v>
+        <v>6190</v>
       </c>
       <c r="D1245" t="s">
         <v>1247</v>
@@ -23300,7 +23588,7 @@
         <v>93</v>
       </c>
       <c r="C1246">
-        <v>6180</v>
+        <v>6020</v>
       </c>
       <c r="D1246" t="s">
         <v>1248</v>
@@ -23314,7 +23602,7 @@
         <v>94</v>
       </c>
       <c r="C1247">
-        <v>6020</v>
+        <v>5860</v>
       </c>
       <c r="D1247" t="s">
         <v>1249</v>
@@ -23328,7 +23616,7 @@
         <v>95</v>
       </c>
       <c r="C1248">
-        <v>5880</v>
+        <v>5750</v>
       </c>
       <c r="D1248" t="s">
         <v>1250</v>
@@ -23342,7 +23630,7 @@
         <v>96</v>
       </c>
       <c r="C1249">
-        <v>5740</v>
+        <v>5640</v>
       </c>
       <c r="D1249" t="s">
         <v>1251</v>
@@ -23356,7 +23644,7 @@
         <v>1</v>
       </c>
       <c r="C1250">
-        <v>5480</v>
+        <v>5430</v>
       </c>
       <c r="D1250" t="s">
         <v>1252</v>
@@ -23370,7 +23658,7 @@
         <v>2</v>
       </c>
       <c r="C1251">
-        <v>5420</v>
+        <v>5330</v>
       </c>
       <c r="D1251" t="s">
         <v>1253</v>
@@ -23384,7 +23672,7 @@
         <v>3</v>
       </c>
       <c r="C1252">
-        <v>5350</v>
+        <v>5260</v>
       </c>
       <c r="D1252" t="s">
         <v>1254</v>
@@ -23398,7 +23686,7 @@
         <v>4</v>
       </c>
       <c r="C1253">
-        <v>5300</v>
+        <v>5200</v>
       </c>
       <c r="D1253" t="s">
         <v>1255</v>
@@ -23412,7 +23700,7 @@
         <v>5</v>
       </c>
       <c r="C1254">
-        <v>5240</v>
+        <v>5150</v>
       </c>
       <c r="D1254" t="s">
         <v>1256</v>
@@ -23426,7 +23714,7 @@
         <v>6</v>
       </c>
       <c r="C1255">
-        <v>5210</v>
+        <v>5100</v>
       </c>
       <c r="D1255" t="s">
         <v>1257</v>
@@ -23440,7 +23728,7 @@
         <v>7</v>
       </c>
       <c r="C1256">
-        <v>5180</v>
+        <v>5090</v>
       </c>
       <c r="D1256" t="s">
         <v>1258</v>
@@ -23454,7 +23742,7 @@
         <v>8</v>
       </c>
       <c r="C1257">
-        <v>5130</v>
+        <v>5060</v>
       </c>
       <c r="D1257" t="s">
         <v>1259</v>
@@ -23468,7 +23756,7 @@
         <v>9</v>
       </c>
       <c r="C1258">
-        <v>5090</v>
+        <v>5050</v>
       </c>
       <c r="D1258" t="s">
         <v>1260</v>
@@ -23482,7 +23770,7 @@
         <v>10</v>
       </c>
       <c r="C1259">
-        <v>5050</v>
+        <v>5040</v>
       </c>
       <c r="D1259" t="s">
         <v>1261</v>
@@ -23496,7 +23784,7 @@
         <v>11</v>
       </c>
       <c r="C1260">
-        <v>5030</v>
+        <v>5040</v>
       </c>
       <c r="D1260" t="s">
         <v>1262</v>
@@ -23510,7 +23798,7 @@
         <v>12</v>
       </c>
       <c r="C1261">
-        <v>5020</v>
+        <v>5040</v>
       </c>
       <c r="D1261" t="s">
         <v>1263</v>
@@ -23524,7 +23812,7 @@
         <v>13</v>
       </c>
       <c r="C1262">
-        <v>5020</v>
+        <v>5030</v>
       </c>
       <c r="D1262" t="s">
         <v>1264</v>
@@ -23538,7 +23826,7 @@
         <v>14</v>
       </c>
       <c r="C1263">
-        <v>5030</v>
+        <v>5020</v>
       </c>
       <c r="D1263" t="s">
         <v>1265</v>
@@ -23552,7 +23840,7 @@
         <v>15</v>
       </c>
       <c r="C1264">
-        <v>5040</v>
+        <v>5020</v>
       </c>
       <c r="D1264" t="s">
         <v>1266</v>
@@ -23566,7 +23854,7 @@
         <v>16</v>
       </c>
       <c r="C1265">
-        <v>5050</v>
+        <v>5030</v>
       </c>
       <c r="D1265" t="s">
         <v>1267</v>
@@ -23580,7 +23868,7 @@
         <v>17</v>
       </c>
       <c r="C1266">
-        <v>5050</v>
+        <v>5060</v>
       </c>
       <c r="D1266" t="s">
         <v>1268</v>
@@ -23594,7 +23882,7 @@
         <v>18</v>
       </c>
       <c r="C1267">
-        <v>5060</v>
+        <v>5070</v>
       </c>
       <c r="D1267" t="s">
         <v>1269</v>
@@ -23622,7 +23910,7 @@
         <v>20</v>
       </c>
       <c r="C1269">
-        <v>5090</v>
+        <v>5100</v>
       </c>
       <c r="D1269" t="s">
         <v>1271</v>
@@ -23636,7 +23924,7 @@
         <v>21</v>
       </c>
       <c r="C1270">
-        <v>5120</v>
+        <v>5110</v>
       </c>
       <c r="D1270" t="s">
         <v>1272</v>
@@ -23650,7 +23938,7 @@
         <v>22</v>
       </c>
       <c r="C1271">
-        <v>5170</v>
+        <v>5120</v>
       </c>
       <c r="D1271" t="s">
         <v>1273</v>
@@ -23664,7 +23952,7 @@
         <v>23</v>
       </c>
       <c r="C1272">
-        <v>5240</v>
+        <v>5150</v>
       </c>
       <c r="D1272" t="s">
         <v>1274</v>
@@ -23678,7 +23966,7 @@
         <v>24</v>
       </c>
       <c r="C1273">
-        <v>5330</v>
+        <v>5210</v>
       </c>
       <c r="D1273" t="s">
         <v>1275</v>
@@ -23692,7 +23980,7 @@
         <v>25</v>
       </c>
       <c r="C1274">
-        <v>5430</v>
+        <v>5290</v>
       </c>
       <c r="D1274" t="s">
         <v>1276</v>
@@ -23706,7 +23994,7 @@
         <v>26</v>
       </c>
       <c r="C1275">
-        <v>5540</v>
+        <v>5360</v>
       </c>
       <c r="D1275" t="s">
         <v>1277</v>
@@ -23720,7 +24008,7 @@
         <v>27</v>
       </c>
       <c r="C1276">
-        <v>5650</v>
+        <v>5470</v>
       </c>
       <c r="D1276" t="s">
         <v>1278</v>
@@ -23734,7 +24022,7 @@
         <v>28</v>
       </c>
       <c r="C1277">
-        <v>5750</v>
+        <v>5590</v>
       </c>
       <c r="D1277" t="s">
         <v>1279</v>
@@ -23748,7 +24036,7 @@
         <v>29</v>
       </c>
       <c r="C1278">
-        <v>5840</v>
+        <v>5730</v>
       </c>
       <c r="D1278" t="s">
         <v>1280</v>
@@ -23762,7 +24050,7 @@
         <v>30</v>
       </c>
       <c r="C1279">
-        <v>5920</v>
+        <v>5840</v>
       </c>
       <c r="D1279" t="s">
         <v>1281</v>
@@ -23776,7 +24064,7 @@
         <v>31</v>
       </c>
       <c r="C1280">
-        <v>5970</v>
+        <v>5900</v>
       </c>
       <c r="D1280" t="s">
         <v>1282</v>
@@ -23790,7 +24078,7 @@
         <v>32</v>
       </c>
       <c r="C1281">
-        <v>6010</v>
+        <v>5920</v>
       </c>
       <c r="D1281" t="s">
         <v>1283</v>
@@ -23804,7 +24092,7 @@
         <v>33</v>
       </c>
       <c r="C1282">
-        <v>6010</v>
+        <v>5920</v>
       </c>
       <c r="D1282" t="s">
         <v>1284</v>
@@ -23818,7 +24106,7 @@
         <v>34</v>
       </c>
       <c r="C1283">
-        <v>5990</v>
+        <v>5900</v>
       </c>
       <c r="D1283" t="s">
         <v>1285</v>
@@ -23832,7 +24120,7 @@
         <v>35</v>
       </c>
       <c r="C1284">
-        <v>5950</v>
+        <v>5840</v>
       </c>
       <c r="D1284" t="s">
         <v>1286</v>
@@ -23846,7 +24134,7 @@
         <v>36</v>
       </c>
       <c r="C1285">
-        <v>5880</v>
+        <v>5730</v>
       </c>
       <c r="D1285" t="s">
         <v>1287</v>
@@ -23860,7 +24148,7 @@
         <v>37</v>
       </c>
       <c r="C1286">
-        <v>5790</v>
+        <v>5610</v>
       </c>
       <c r="D1286" t="s">
         <v>1288</v>
@@ -23874,7 +24162,7 @@
         <v>38</v>
       </c>
       <c r="C1287">
-        <v>5690</v>
+        <v>5500</v>
       </c>
       <c r="D1287" t="s">
         <v>1289</v>
@@ -23888,7 +24176,7 @@
         <v>39</v>
       </c>
       <c r="C1288">
-        <v>5570</v>
+        <v>5370</v>
       </c>
       <c r="D1288" t="s">
         <v>1290</v>
@@ -23902,7 +24190,7 @@
         <v>40</v>
       </c>
       <c r="C1289">
-        <v>5450</v>
+        <v>5230</v>
       </c>
       <c r="D1289" t="s">
         <v>1291</v>
@@ -23916,7 +24204,7 @@
         <v>41</v>
       </c>
       <c r="C1290">
-        <v>5330</v>
+        <v>5120</v>
       </c>
       <c r="D1290" t="s">
         <v>1292</v>
@@ -23930,7 +24218,7 @@
         <v>42</v>
       </c>
       <c r="C1291">
-        <v>5220</v>
+        <v>5000</v>
       </c>
       <c r="D1291" t="s">
         <v>1293</v>
@@ -23944,7 +24232,7 @@
         <v>43</v>
       </c>
       <c r="C1292">
-        <v>5110</v>
+        <v>4890</v>
       </c>
       <c r="D1292" t="s">
         <v>1294</v>
@@ -23958,7 +24246,7 @@
         <v>44</v>
       </c>
       <c r="C1293">
-        <v>5020</v>
+        <v>4790</v>
       </c>
       <c r="D1293" t="s">
         <v>1295</v>
@@ -23972,7 +24260,7 @@
         <v>45</v>
       </c>
       <c r="C1294">
-        <v>4940</v>
+        <v>4670</v>
       </c>
       <c r="D1294" t="s">
         <v>1296</v>
@@ -23986,7 +24274,7 @@
         <v>46</v>
       </c>
       <c r="C1295">
-        <v>4880</v>
+        <v>4600</v>
       </c>
       <c r="D1295" t="s">
         <v>1297</v>
@@ -24000,7 +24288,7 @@
         <v>47</v>
       </c>
       <c r="C1296">
-        <v>4830</v>
+        <v>4550</v>
       </c>
       <c r="D1296" t="s">
         <v>1298</v>
@@ -24014,7 +24302,7 @@
         <v>48</v>
       </c>
       <c r="C1297">
-        <v>4790</v>
+        <v>4500</v>
       </c>
       <c r="D1297" t="s">
         <v>1299</v>
@@ -24028,7 +24316,7 @@
         <v>49</v>
       </c>
       <c r="C1298">
-        <v>4770</v>
+        <v>4440</v>
       </c>
       <c r="D1298" t="s">
         <v>1300</v>
@@ -24042,7 +24330,7 @@
         <v>50</v>
       </c>
       <c r="C1299">
-        <v>4750</v>
+        <v>4410</v>
       </c>
       <c r="D1299" t="s">
         <v>1301</v>
@@ -24056,7 +24344,7 @@
         <v>51</v>
       </c>
       <c r="C1300">
-        <v>4740</v>
+        <v>4390</v>
       </c>
       <c r="D1300" t="s">
         <v>1302</v>
@@ -24070,7 +24358,7 @@
         <v>52</v>
       </c>
       <c r="C1301">
-        <v>4740</v>
+        <v>4380</v>
       </c>
       <c r="D1301" t="s">
         <v>1303</v>
@@ -24084,7 +24372,7 @@
         <v>53</v>
       </c>
       <c r="C1302">
-        <v>4740</v>
+        <v>4390</v>
       </c>
       <c r="D1302" t="s">
         <v>1304</v>
@@ -24098,7 +24386,7 @@
         <v>54</v>
       </c>
       <c r="C1303">
-        <v>4750</v>
+        <v>4390</v>
       </c>
       <c r="D1303" t="s">
         <v>1305</v>
@@ -24112,7 +24400,7 @@
         <v>55</v>
       </c>
       <c r="C1304">
-        <v>4760</v>
+        <v>4400</v>
       </c>
       <c r="D1304" t="s">
         <v>1306</v>
@@ -24126,7 +24414,7 @@
         <v>56</v>
       </c>
       <c r="C1305">
-        <v>4780</v>
+        <v>4400</v>
       </c>
       <c r="D1305" t="s">
         <v>1307</v>
@@ -24140,7 +24428,7 @@
         <v>57</v>
       </c>
       <c r="C1306">
-        <v>4810</v>
+        <v>4420</v>
       </c>
       <c r="D1306" t="s">
         <v>1308</v>
@@ -24154,7 +24442,7 @@
         <v>58</v>
       </c>
       <c r="C1307">
-        <v>4840</v>
+        <v>4430</v>
       </c>
       <c r="D1307" t="s">
         <v>1309</v>
@@ -24168,7 +24456,7 @@
         <v>59</v>
       </c>
       <c r="C1308">
-        <v>4870</v>
+        <v>4440</v>
       </c>
       <c r="D1308" t="s">
         <v>1310</v>
@@ -24182,7 +24470,7 @@
         <v>60</v>
       </c>
       <c r="C1309">
-        <v>4900</v>
+        <v>4450</v>
       </c>
       <c r="D1309" t="s">
         <v>1311</v>
@@ -24196,7 +24484,7 @@
         <v>61</v>
       </c>
       <c r="C1310">
-        <v>4940</v>
+        <v>4490</v>
       </c>
       <c r="D1310" t="s">
         <v>1312</v>
@@ -24210,7 +24498,7 @@
         <v>62</v>
       </c>
       <c r="C1311">
-        <v>4980</v>
+        <v>4520</v>
       </c>
       <c r="D1311" t="s">
         <v>1313</v>
@@ -24224,7 +24512,7 @@
         <v>63</v>
       </c>
       <c r="C1312">
-        <v>5020</v>
+        <v>4550</v>
       </c>
       <c r="D1312" t="s">
         <v>1314</v>
@@ -24238,7 +24526,7 @@
         <v>64</v>
       </c>
       <c r="C1313">
-        <v>5080</v>
+        <v>4600</v>
       </c>
       <c r="D1313" t="s">
         <v>1315</v>
@@ -24252,7 +24540,7 @@
         <v>65</v>
       </c>
       <c r="C1314">
-        <v>5150</v>
+        <v>4660</v>
       </c>
       <c r="D1314" t="s">
         <v>1316</v>
@@ -24266,7 +24554,7 @@
         <v>66</v>
       </c>
       <c r="C1315">
-        <v>5240</v>
+        <v>4730</v>
       </c>
       <c r="D1315" t="s">
         <v>1317</v>
@@ -24280,7 +24568,7 @@
         <v>67</v>
       </c>
       <c r="C1316">
-        <v>5340</v>
+        <v>4830</v>
       </c>
       <c r="D1316" t="s">
         <v>1318</v>
@@ -24294,7 +24582,7 @@
         <v>68</v>
       </c>
       <c r="C1317">
-        <v>5440</v>
+        <v>4920</v>
       </c>
       <c r="D1317" t="s">
         <v>1319</v>
@@ -24308,7 +24596,7 @@
         <v>69</v>
       </c>
       <c r="C1318">
-        <v>5550</v>
+        <v>5020</v>
       </c>
       <c r="D1318" t="s">
         <v>1320</v>
@@ -24322,7 +24610,7 @@
         <v>70</v>
       </c>
       <c r="C1319">
-        <v>5660</v>
+        <v>5110</v>
       </c>
       <c r="D1319" t="s">
         <v>1321</v>
@@ -24336,7 +24624,7 @@
         <v>71</v>
       </c>
       <c r="C1320">
-        <v>5770</v>
+        <v>5220</v>
       </c>
       <c r="D1320" t="s">
         <v>1322</v>
@@ -24350,7 +24638,7 @@
         <v>72</v>
       </c>
       <c r="C1321">
-        <v>5880</v>
+        <v>5350</v>
       </c>
       <c r="D1321" t="s">
         <v>1323</v>
@@ -24364,7 +24652,7 @@
         <v>73</v>
       </c>
       <c r="C1322">
-        <v>5970</v>
+        <v>5500</v>
       </c>
       <c r="D1322" t="s">
         <v>1324</v>
@@ -24378,7 +24666,7 @@
         <v>74</v>
       </c>
       <c r="C1323">
-        <v>6060</v>
+        <v>5650</v>
       </c>
       <c r="D1323" t="s">
         <v>1325</v>
@@ -24392,7 +24680,7 @@
         <v>75</v>
       </c>
       <c r="C1324">
-        <v>6160</v>
+        <v>5800</v>
       </c>
       <c r="D1324" t="s">
         <v>1326</v>
@@ -24406,7 +24694,7 @@
         <v>76</v>
       </c>
       <c r="C1325">
-        <v>6270</v>
+        <v>5940</v>
       </c>
       <c r="D1325" t="s">
         <v>1327</v>
@@ -24420,7 +24708,7 @@
         <v>77</v>
       </c>
       <c r="C1326">
-        <v>6390</v>
+        <v>6100</v>
       </c>
       <c r="D1326" t="s">
         <v>1328</v>
@@ -24434,7 +24722,7 @@
         <v>78</v>
       </c>
       <c r="C1327">
-        <v>6500</v>
+        <v>6250</v>
       </c>
       <c r="D1327" t="s">
         <v>1329</v>
@@ -24448,7 +24736,7 @@
         <v>79</v>
       </c>
       <c r="C1328">
-        <v>6600</v>
+        <v>6390</v>
       </c>
       <c r="D1328" t="s">
         <v>1330</v>
@@ -24462,7 +24750,7 @@
         <v>80</v>
       </c>
       <c r="C1329">
-        <v>6670</v>
+        <v>6530</v>
       </c>
       <c r="D1329" t="s">
         <v>1331</v>
@@ -24476,7 +24764,7 @@
         <v>81</v>
       </c>
       <c r="C1330">
-        <v>6740</v>
+        <v>6630</v>
       </c>
       <c r="D1330" t="s">
         <v>1332</v>
@@ -24490,7 +24778,7 @@
         <v>82</v>
       </c>
       <c r="C1331">
-        <v>6820</v>
+        <v>6720</v>
       </c>
       <c r="D1331" t="s">
         <v>1333</v>
@@ -24504,7 +24792,7 @@
         <v>83</v>
       </c>
       <c r="C1332">
-        <v>6890</v>
+        <v>6790</v>
       </c>
       <c r="D1332" t="s">
         <v>1334</v>
@@ -24518,7 +24806,7 @@
         <v>84</v>
       </c>
       <c r="C1333">
-        <v>6980</v>
+        <v>6880</v>
       </c>
       <c r="D1333" t="s">
         <v>1335</v>
@@ -24532,7 +24820,7 @@
         <v>85</v>
       </c>
       <c r="C1334">
-        <v>7020</v>
+        <v>6940</v>
       </c>
       <c r="D1334" t="s">
         <v>1336</v>
@@ -24546,7 +24834,7 @@
         <v>86</v>
       </c>
       <c r="C1335">
-        <v>7010</v>
+        <v>6940</v>
       </c>
       <c r="D1335" t="s">
         <v>1337</v>
@@ -24560,7 +24848,7 @@
         <v>87</v>
       </c>
       <c r="C1336">
-        <v>6990</v>
+        <v>6930</v>
       </c>
       <c r="D1336" t="s">
         <v>1338</v>
@@ -24574,7 +24862,7 @@
         <v>88</v>
       </c>
       <c r="C1337">
-        <v>6890</v>
+        <v>6870</v>
       </c>
       <c r="D1337" t="s">
         <v>1339</v>
@@ -24588,7 +24876,7 @@
         <v>89</v>
       </c>
       <c r="C1338">
-        <v>6750</v>
+        <v>6720</v>
       </c>
       <c r="D1338" t="s">
         <v>1340</v>
@@ -24602,7 +24890,7 @@
         <v>90</v>
       </c>
       <c r="C1339">
-        <v>6620</v>
+        <v>6520</v>
       </c>
       <c r="D1339" t="s">
         <v>1341</v>
@@ -24616,7 +24904,7 @@
         <v>91</v>
       </c>
       <c r="C1340">
-        <v>6460</v>
+        <v>6350</v>
       </c>
       <c r="D1340" t="s">
         <v>1342</v>
@@ -24630,7 +24918,7 @@
         <v>92</v>
       </c>
       <c r="C1341">
-        <v>6280</v>
+        <v>6170</v>
       </c>
       <c r="D1341" t="s">
         <v>1343</v>
@@ -24644,7 +24932,7 @@
         <v>93</v>
       </c>
       <c r="C1342">
-        <v>6120</v>
+        <v>6030</v>
       </c>
       <c r="D1342" t="s">
         <v>1344</v>
@@ -24658,7 +24946,7 @@
         <v>94</v>
       </c>
       <c r="C1343">
-        <v>5970</v>
+        <v>5890</v>
       </c>
       <c r="D1343" t="s">
         <v>1345</v>
@@ -24672,7 +24960,7 @@
         <v>95</v>
       </c>
       <c r="C1344">
-        <v>5850</v>
+        <v>5780</v>
       </c>
       <c r="D1344" t="s">
         <v>1346</v>
@@ -24686,7 +24974,7 @@
         <v>96</v>
       </c>
       <c r="C1345">
-        <v>5720</v>
+        <v>5660</v>
       </c>
       <c r="D1345" t="s">
         <v>1347</v>
@@ -24700,7 +24988,7 @@
         <v>1</v>
       </c>
       <c r="C1346">
-        <v>5470</v>
+        <v>5460</v>
       </c>
       <c r="D1346" t="s">
         <v>1348</v>
@@ -24728,7 +25016,7 @@
         <v>3</v>
       </c>
       <c r="C1348">
-        <v>5340</v>
+        <v>5360</v>
       </c>
       <c r="D1348" t="s">
         <v>1350</v>
@@ -24742,7 +25030,7 @@
         <v>4</v>
       </c>
       <c r="C1349">
-        <v>5280</v>
+        <v>5290</v>
       </c>
       <c r="D1349" t="s">
         <v>1351</v>
@@ -24756,7 +25044,7 @@
         <v>5</v>
       </c>
       <c r="C1350">
-        <v>5230</v>
+        <v>5240</v>
       </c>
       <c r="D1350" t="s">
         <v>1352</v>
@@ -24784,7 +25072,7 @@
         <v>7</v>
       </c>
       <c r="C1352">
-        <v>5160</v>
+        <v>5140</v>
       </c>
       <c r="D1352" t="s">
         <v>1354</v>
@@ -24798,7 +25086,7 @@
         <v>8</v>
       </c>
       <c r="C1353">
-        <v>5120</v>
+        <v>5100</v>
       </c>
       <c r="D1353" t="s">
         <v>1355</v>
@@ -24812,7 +25100,7 @@
         <v>9</v>
       </c>
       <c r="C1354">
-        <v>5080</v>
+        <v>5060</v>
       </c>
       <c r="D1354" t="s">
         <v>1356</v>
@@ -24826,7 +25114,7 @@
         <v>10</v>
       </c>
       <c r="C1355">
-        <v>5050</v>
+        <v>5030</v>
       </c>
       <c r="D1355" t="s">
         <v>1357</v>
@@ -24840,7 +25128,7 @@
         <v>11</v>
       </c>
       <c r="C1356">
-        <v>5040</v>
+        <v>5010</v>
       </c>
       <c r="D1356" t="s">
         <v>1358</v>
@@ -24854,7 +25142,7 @@
         <v>12</v>
       </c>
       <c r="C1357">
-        <v>5030</v>
+        <v>5010</v>
       </c>
       <c r="D1357" t="s">
         <v>1359</v>
@@ -24868,7 +25156,7 @@
         <v>13</v>
       </c>
       <c r="C1358">
-        <v>5030</v>
+        <v>5000</v>
       </c>
       <c r="D1358" t="s">
         <v>1360</v>
@@ -24882,7 +25170,7 @@
         <v>14</v>
       </c>
       <c r="C1359">
-        <v>5030</v>
+        <v>5020</v>
       </c>
       <c r="D1359" t="s">
         <v>1361</v>
@@ -24896,7 +25184,7 @@
         <v>15</v>
       </c>
       <c r="C1360">
-        <v>5040</v>
+        <v>5030</v>
       </c>
       <c r="D1360" t="s">
         <v>1362</v>
@@ -24910,7 +25198,7 @@
         <v>16</v>
       </c>
       <c r="C1361">
-        <v>5040</v>
+        <v>5030</v>
       </c>
       <c r="D1361" t="s">
         <v>1363</v>
@@ -24924,7 +25212,7 @@
         <v>17</v>
       </c>
       <c r="C1362">
-        <v>5050</v>
+        <v>5040</v>
       </c>
       <c r="D1362" t="s">
         <v>1364</v>
@@ -25008,7 +25296,7 @@
         <v>23</v>
       </c>
       <c r="C1368">
-        <v>5240</v>
+        <v>5250</v>
       </c>
       <c r="D1368" t="s">
         <v>1370</v>
@@ -25022,7 +25310,7 @@
         <v>24</v>
       </c>
       <c r="C1369">
-        <v>5310</v>
+        <v>5330</v>
       </c>
       <c r="D1369" t="s">
         <v>1371</v>
@@ -25036,7 +25324,7 @@
         <v>25</v>
       </c>
       <c r="C1370">
-        <v>5390</v>
+        <v>5410</v>
       </c>
       <c r="D1370" t="s">
         <v>1372</v>
@@ -25050,7 +25338,7 @@
         <v>26</v>
       </c>
       <c r="C1371">
-        <v>5480</v>
+        <v>5500</v>
       </c>
       <c r="D1371" t="s">
         <v>1373</v>
@@ -25064,7 +25352,7 @@
         <v>27</v>
       </c>
       <c r="C1372">
-        <v>5560</v>
+        <v>5590</v>
       </c>
       <c r="D1372" t="s">
         <v>1374</v>
@@ -25078,7 +25366,7 @@
         <v>28</v>
       </c>
       <c r="C1373">
-        <v>5640</v>
+        <v>5660</v>
       </c>
       <c r="D1373" t="s">
         <v>1375</v>
@@ -25092,7 +25380,7 @@
         <v>29</v>
       </c>
       <c r="C1374">
-        <v>5710</v>
+        <v>5720</v>
       </c>
       <c r="D1374" t="s">
         <v>1376</v>
@@ -25106,7 +25394,7 @@
         <v>30</v>
       </c>
       <c r="C1375">
-        <v>5770</v>
+        <v>5760</v>
       </c>
       <c r="D1375" t="s">
         <v>1377</v>
@@ -25120,7 +25408,7 @@
         <v>31</v>
       </c>
       <c r="C1376">
-        <v>5810</v>
+        <v>5780</v>
       </c>
       <c r="D1376" t="s">
         <v>1378</v>
@@ -25134,7 +25422,7 @@
         <v>32</v>
       </c>
       <c r="C1377">
-        <v>5830</v>
+        <v>5800</v>
       </c>
       <c r="D1377" t="s">
         <v>1379</v>
@@ -25148,7 +25436,7 @@
         <v>33</v>
       </c>
       <c r="C1378">
-        <v>5830</v>
+        <v>5750</v>
       </c>
       <c r="D1378" t="s">
         <v>1380</v>
@@ -25162,7 +25450,7 @@
         <v>34</v>
       </c>
       <c r="C1379">
-        <v>5810</v>
+        <v>5700</v>
       </c>
       <c r="D1379" t="s">
         <v>1381</v>
@@ -25176,7 +25464,7 @@
         <v>35</v>
       </c>
       <c r="C1380">
-        <v>5760</v>
+        <v>5630</v>
       </c>
       <c r="D1380" t="s">
         <v>1382</v>
@@ -25190,7 +25478,7 @@
         <v>36</v>
       </c>
       <c r="C1381">
-        <v>5700</v>
+        <v>5550</v>
       </c>
       <c r="D1381" t="s">
         <v>1383</v>
@@ -25204,7 +25492,7 @@
         <v>37</v>
       </c>
       <c r="C1382">
-        <v>5610</v>
+        <v>5460</v>
       </c>
       <c r="D1382" t="s">
         <v>1384</v>
@@ -25218,7 +25506,7 @@
         <v>38</v>
       </c>
       <c r="C1383">
-        <v>5510</v>
+        <v>5360</v>
       </c>
       <c r="D1383" t="s">
         <v>1385</v>
@@ -25232,7 +25520,7 @@
         <v>39</v>
       </c>
       <c r="C1384">
-        <v>5390</v>
+        <v>5260</v>
       </c>
       <c r="D1384" t="s">
         <v>1386</v>
@@ -25246,7 +25534,7 @@
         <v>40</v>
       </c>
       <c r="C1385">
-        <v>5270</v>
+        <v>5170</v>
       </c>
       <c r="D1385" t="s">
         <v>1387</v>
@@ -25260,7 +25548,7 @@
         <v>41</v>
       </c>
       <c r="C1386">
-        <v>5150</v>
+        <v>5080</v>
       </c>
       <c r="D1386" t="s">
         <v>1388</v>
@@ -25274,7 +25562,7 @@
         <v>42</v>
       </c>
       <c r="C1387">
-        <v>5030</v>
+        <v>4990</v>
       </c>
       <c r="D1387" t="s">
         <v>1389</v>
@@ -25288,7 +25576,7 @@
         <v>43</v>
       </c>
       <c r="C1388">
-        <v>4930</v>
+        <v>4910</v>
       </c>
       <c r="D1388" t="s">
         <v>1390</v>
@@ -25302,7 +25590,7 @@
         <v>44</v>
       </c>
       <c r="C1389">
-        <v>4840</v>
+        <v>4850</v>
       </c>
       <c r="D1389" t="s">
         <v>1391</v>
@@ -25316,7 +25604,7 @@
         <v>45</v>
       </c>
       <c r="C1390">
-        <v>4770</v>
+        <v>4780</v>
       </c>
       <c r="D1390" t="s">
         <v>1392</v>
@@ -25330,7 +25618,7 @@
         <v>46</v>
       </c>
       <c r="C1391">
-        <v>4720</v>
+        <v>4730</v>
       </c>
       <c r="D1391" t="s">
         <v>1393</v>
@@ -25358,7 +25646,7 @@
         <v>48</v>
       </c>
       <c r="C1393">
-        <v>4650</v>
+        <v>4630</v>
       </c>
       <c r="D1393" t="s">
         <v>1395</v>
@@ -25372,7 +25660,7 @@
         <v>49</v>
       </c>
       <c r="C1394">
-        <v>4630</v>
+        <v>4590</v>
       </c>
       <c r="D1394" t="s">
         <v>1396</v>
@@ -25386,7 +25674,7 @@
         <v>50</v>
       </c>
       <c r="C1395">
-        <v>4610</v>
+        <v>4550</v>
       </c>
       <c r="D1395" t="s">
         <v>1397</v>
@@ -25400,7 +25688,7 @@
         <v>51</v>
       </c>
       <c r="C1396">
-        <v>4590</v>
+        <v>4510</v>
       </c>
       <c r="D1396" t="s">
         <v>1398</v>
@@ -25414,7 +25702,7 @@
         <v>52</v>
       </c>
       <c r="C1397">
-        <v>4580</v>
+        <v>4480</v>
       </c>
       <c r="D1397" t="s">
         <v>1399</v>
@@ -25428,7 +25716,7 @@
         <v>53</v>
       </c>
       <c r="C1398">
-        <v>4560</v>
+        <v>4450</v>
       </c>
       <c r="D1398" t="s">
         <v>1400</v>
@@ -25442,7 +25730,7 @@
         <v>54</v>
       </c>
       <c r="C1399">
-        <v>4540</v>
+        <v>4430</v>
       </c>
       <c r="D1399" t="s">
         <v>1401</v>
@@ -25456,7 +25744,7 @@
         <v>55</v>
       </c>
       <c r="C1400">
-        <v>4540</v>
+        <v>4420</v>
       </c>
       <c r="D1400" t="s">
         <v>1402</v>
@@ -25470,7 +25758,7 @@
         <v>56</v>
       </c>
       <c r="C1401">
-        <v>4540</v>
+        <v>4420</v>
       </c>
       <c r="D1401" t="s">
         <v>1403</v>
@@ -25484,7 +25772,7 @@
         <v>57</v>
       </c>
       <c r="C1402">
-        <v>4550</v>
+        <v>4430</v>
       </c>
       <c r="D1402" t="s">
         <v>1404</v>
@@ -25498,7 +25786,7 @@
         <v>58</v>
       </c>
       <c r="C1403">
-        <v>4570</v>
+        <v>4450</v>
       </c>
       <c r="D1403" t="s">
         <v>1405</v>
@@ -25512,7 +25800,7 @@
         <v>59</v>
       </c>
       <c r="C1404">
-        <v>4600</v>
+        <v>4480</v>
       </c>
       <c r="D1404" t="s">
         <v>1406</v>
@@ -25526,7 +25814,7 @@
         <v>60</v>
       </c>
       <c r="C1405">
-        <v>4650</v>
+        <v>4510</v>
       </c>
       <c r="D1405" t="s">
         <v>1407</v>
@@ -25540,7 +25828,7 @@
         <v>61</v>
       </c>
       <c r="C1406">
-        <v>4700</v>
+        <v>4550</v>
       </c>
       <c r="D1406" t="s">
         <v>1408</v>
@@ -25554,7 +25842,7 @@
         <v>62</v>
       </c>
       <c r="C1407">
-        <v>4770</v>
+        <v>4590</v>
       </c>
       <c r="D1407" t="s">
         <v>1409</v>
@@ -25568,7 +25856,7 @@
         <v>63</v>
       </c>
       <c r="C1408">
-        <v>4840</v>
+        <v>4640</v>
       </c>
       <c r="D1408" t="s">
         <v>1410</v>
@@ -25582,7 +25870,7 @@
         <v>64</v>
       </c>
       <c r="C1409">
-        <v>4910</v>
+        <v>4700</v>
       </c>
       <c r="D1409" t="s">
         <v>1411</v>
@@ -25596,7 +25884,7 @@
         <v>65</v>
       </c>
       <c r="C1410">
-        <v>5000</v>
+        <v>4770</v>
       </c>
       <c r="D1410" t="s">
         <v>1412</v>
@@ -25610,7 +25898,7 @@
         <v>66</v>
       </c>
       <c r="C1411">
-        <v>5100</v>
+        <v>4850</v>
       </c>
       <c r="D1411" t="s">
         <v>1413</v>
@@ -25624,7 +25912,7 @@
         <v>67</v>
       </c>
       <c r="C1412">
-        <v>5210</v>
+        <v>4940</v>
       </c>
       <c r="D1412" t="s">
         <v>1414</v>
@@ -25638,7 +25926,7 @@
         <v>68</v>
       </c>
       <c r="C1413">
-        <v>5320</v>
+        <v>5050</v>
       </c>
       <c r="D1413" t="s">
         <v>1415</v>
@@ -25652,7 +25940,7 @@
         <v>69</v>
       </c>
       <c r="C1414">
-        <v>5440</v>
+        <v>5160</v>
       </c>
       <c r="D1414" t="s">
         <v>1416</v>
@@ -25666,7 +25954,7 @@
         <v>70</v>
       </c>
       <c r="C1415">
-        <v>5550</v>
+        <v>5270</v>
       </c>
       <c r="D1415" t="s">
         <v>1417</v>
@@ -25680,7 +25968,7 @@
         <v>71</v>
       </c>
       <c r="C1416">
-        <v>5650</v>
+        <v>5380</v>
       </c>
       <c r="D1416" t="s">
         <v>1418</v>
@@ -25694,7 +25982,7 @@
         <v>72</v>
       </c>
       <c r="C1417">
-        <v>5750</v>
+        <v>5490</v>
       </c>
       <c r="D1417" t="s">
         <v>1419</v>
@@ -25708,7 +25996,7 @@
         <v>73</v>
       </c>
       <c r="C1418">
-        <v>5840</v>
+        <v>5610</v>
       </c>
       <c r="D1418" t="s">
         <v>1420</v>
@@ -25722,7 +26010,7 @@
         <v>74</v>
       </c>
       <c r="C1419">
-        <v>5930</v>
+        <v>5720</v>
       </c>
       <c r="D1419" t="s">
         <v>1421</v>
@@ -25736,7 +26024,7 @@
         <v>75</v>
       </c>
       <c r="C1420">
-        <v>6040</v>
+        <v>5850</v>
       </c>
       <c r="D1420" t="s">
         <v>1422</v>
@@ -25750,7 +26038,7 @@
         <v>76</v>
       </c>
       <c r="C1421">
-        <v>6150</v>
+        <v>5980</v>
       </c>
       <c r="D1421" t="s">
         <v>1423</v>
@@ -25764,7 +26052,7 @@
         <v>77</v>
       </c>
       <c r="C1422">
-        <v>6280</v>
+        <v>6120</v>
       </c>
       <c r="D1422" t="s">
         <v>1424</v>
@@ -25778,7 +26066,7 @@
         <v>78</v>
       </c>
       <c r="C1423">
-        <v>6400</v>
+        <v>6260</v>
       </c>
       <c r="D1423" t="s">
         <v>1425</v>
@@ -25792,7 +26080,7 @@
         <v>79</v>
       </c>
       <c r="C1424">
-        <v>6500</v>
+        <v>6390</v>
       </c>
       <c r="D1424" t="s">
         <v>1426</v>
@@ -25806,7 +26094,7 @@
         <v>80</v>
       </c>
       <c r="C1425">
-        <v>6570</v>
+        <v>6490</v>
       </c>
       <c r="D1425" t="s">
         <v>1427</v>
@@ -25820,7 +26108,7 @@
         <v>81</v>
       </c>
       <c r="C1426">
-        <v>6650</v>
+        <v>6600</v>
       </c>
       <c r="D1426" t="s">
         <v>1428</v>
@@ -25834,7 +26122,7 @@
         <v>82</v>
       </c>
       <c r="C1427">
-        <v>6720</v>
+        <v>6660</v>
       </c>
       <c r="D1427" t="s">
         <v>1429</v>
@@ -25848,7 +26136,7 @@
         <v>83</v>
       </c>
       <c r="C1428">
-        <v>6790</v>
+        <v>6720</v>
       </c>
       <c r="D1428" t="s">
         <v>1430</v>
@@ -25862,7 +26150,7 @@
         <v>84</v>
       </c>
       <c r="C1429">
-        <v>6880</v>
+        <v>6750</v>
       </c>
       <c r="D1429" t="s">
         <v>1431</v>
@@ -25876,7 +26164,7 @@
         <v>85</v>
       </c>
       <c r="C1430">
-        <v>6920</v>
+        <v>6750</v>
       </c>
       <c r="D1430" t="s">
         <v>1432</v>
@@ -25890,7 +26178,7 @@
         <v>86</v>
       </c>
       <c r="C1431">
-        <v>6910</v>
+        <v>6750</v>
       </c>
       <c r="D1431" t="s">
         <v>1433</v>
@@ -25904,7 +26192,7 @@
         <v>87</v>
       </c>
       <c r="C1432">
-        <v>6890</v>
+        <v>6720</v>
       </c>
       <c r="D1432" t="s">
         <v>1434</v>
@@ -25918,7 +26206,7 @@
         <v>88</v>
       </c>
       <c r="C1433">
-        <v>6790</v>
+        <v>6650</v>
       </c>
       <c r="D1433" t="s">
         <v>1435</v>
@@ -25932,7 +26220,7 @@
         <v>89</v>
       </c>
       <c r="C1434">
-        <v>6650</v>
+        <v>6520</v>
       </c>
       <c r="D1434" t="s">
         <v>1436</v>
@@ -25946,7 +26234,7 @@
         <v>90</v>
       </c>
       <c r="C1435">
-        <v>6520</v>
+        <v>6430</v>
       </c>
       <c r="D1435" t="s">
         <v>1437</v>
@@ -25960,7 +26248,7 @@
         <v>91</v>
       </c>
       <c r="C1436">
-        <v>6360</v>
+        <v>6270</v>
       </c>
       <c r="D1436" t="s">
         <v>1438</v>
@@ -25974,7 +26262,7 @@
         <v>92</v>
       </c>
       <c r="C1437">
-        <v>6190</v>
+        <v>6140</v>
       </c>
       <c r="D1437" t="s">
         <v>1439</v>
@@ -25988,7 +26276,7 @@
         <v>93</v>
       </c>
       <c r="C1438">
-        <v>6030</v>
+        <v>5980</v>
       </c>
       <c r="D1438" t="s">
         <v>1440</v>
@@ -26002,7 +26290,7 @@
         <v>94</v>
       </c>
       <c r="C1439">
-        <v>5880</v>
+        <v>5820</v>
       </c>
       <c r="D1439" t="s">
         <v>1441</v>
@@ -26016,7 +26304,7 @@
         <v>95</v>
       </c>
       <c r="C1440">
-        <v>5750</v>
+        <v>5730</v>
       </c>
       <c r="D1440" t="s">
         <v>1442</v>
@@ -31410,6 +31698,1350 @@
       </c>
       <c r="D1825" t="s">
         <v>1827</v>
+      </c>
+    </row>
+    <row r="1826" spans="1:4">
+      <c r="A1826" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1826">
+        <v>1</v>
+      </c>
+      <c r="C1826">
+        <v>5620</v>
+      </c>
+      <c r="D1826" t="s">
+        <v>1828</v>
+      </c>
+    </row>
+    <row r="1827" spans="1:4">
+      <c r="A1827" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1827">
+        <v>2</v>
+      </c>
+      <c r="C1827">
+        <v>5580</v>
+      </c>
+      <c r="D1827" t="s">
+        <v>1829</v>
+      </c>
+    </row>
+    <row r="1828" spans="1:4">
+      <c r="A1828" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1828">
+        <v>3</v>
+      </c>
+      <c r="C1828">
+        <v>5520</v>
+      </c>
+      <c r="D1828" t="s">
+        <v>1830</v>
+      </c>
+    </row>
+    <row r="1829" spans="1:4">
+      <c r="A1829" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1829">
+        <v>4</v>
+      </c>
+      <c r="C1829">
+        <v>5440</v>
+      </c>
+      <c r="D1829" t="s">
+        <v>1831</v>
+      </c>
+    </row>
+    <row r="1830" spans="1:4">
+      <c r="A1830" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1830">
+        <v>5</v>
+      </c>
+      <c r="C1830">
+        <v>5370</v>
+      </c>
+      <c r="D1830" t="s">
+        <v>1832</v>
+      </c>
+    </row>
+    <row r="1831" spans="1:4">
+      <c r="A1831" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1831">
+        <v>6</v>
+      </c>
+      <c r="C1831">
+        <v>5320</v>
+      </c>
+      <c r="D1831" t="s">
+        <v>1833</v>
+      </c>
+    </row>
+    <row r="1832" spans="1:4">
+      <c r="A1832" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1832">
+        <v>7</v>
+      </c>
+      <c r="C1832">
+        <v>5280</v>
+      </c>
+      <c r="D1832" t="s">
+        <v>1834</v>
+      </c>
+    </row>
+    <row r="1833" spans="1:4">
+      <c r="A1833" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1833">
+        <v>8</v>
+      </c>
+      <c r="C1833">
+        <v>5240</v>
+      </c>
+      <c r="D1833" t="s">
+        <v>1835</v>
+      </c>
+    </row>
+    <row r="1834" spans="1:4">
+      <c r="A1834" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1834">
+        <v>9</v>
+      </c>
+      <c r="C1834">
+        <v>5210</v>
+      </c>
+      <c r="D1834" t="s">
+        <v>1836</v>
+      </c>
+    </row>
+    <row r="1835" spans="1:4">
+      <c r="A1835" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1835">
+        <v>10</v>
+      </c>
+      <c r="C1835">
+        <v>5190</v>
+      </c>
+      <c r="D1835" t="s">
+        <v>1837</v>
+      </c>
+    </row>
+    <row r="1836" spans="1:4">
+      <c r="A1836" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1836">
+        <v>11</v>
+      </c>
+      <c r="C1836">
+        <v>5170</v>
+      </c>
+      <c r="D1836" t="s">
+        <v>1838</v>
+      </c>
+    </row>
+    <row r="1837" spans="1:4">
+      <c r="A1837" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1837">
+        <v>12</v>
+      </c>
+      <c r="C1837">
+        <v>5150</v>
+      </c>
+      <c r="D1837" t="s">
+        <v>1839</v>
+      </c>
+    </row>
+    <row r="1838" spans="1:4">
+      <c r="A1838" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1838">
+        <v>13</v>
+      </c>
+      <c r="C1838">
+        <v>5150</v>
+      </c>
+      <c r="D1838" t="s">
+        <v>1840</v>
+      </c>
+    </row>
+    <row r="1839" spans="1:4">
+      <c r="A1839" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1839">
+        <v>14</v>
+      </c>
+      <c r="C1839">
+        <v>5150</v>
+      </c>
+      <c r="D1839" t="s">
+        <v>1841</v>
+      </c>
+    </row>
+    <row r="1840" spans="1:4">
+      <c r="A1840" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1840">
+        <v>15</v>
+      </c>
+      <c r="C1840">
+        <v>5150</v>
+      </c>
+      <c r="D1840" t="s">
+        <v>1842</v>
+      </c>
+    </row>
+    <row r="1841" spans="1:4">
+      <c r="A1841" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1841">
+        <v>16</v>
+      </c>
+      <c r="C1841">
+        <v>5160</v>
+      </c>
+      <c r="D1841" t="s">
+        <v>1843</v>
+      </c>
+    </row>
+    <row r="1842" spans="1:4">
+      <c r="A1842" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1842">
+        <v>17</v>
+      </c>
+      <c r="C1842">
+        <v>5160</v>
+      </c>
+      <c r="D1842" t="s">
+        <v>1844</v>
+      </c>
+    </row>
+    <row r="1843" spans="1:4">
+      <c r="A1843" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1843">
+        <v>18</v>
+      </c>
+      <c r="C1843">
+        <v>5160</v>
+      </c>
+      <c r="D1843" t="s">
+        <v>1845</v>
+      </c>
+    </row>
+    <row r="1844" spans="1:4">
+      <c r="A1844" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1844">
+        <v>19</v>
+      </c>
+      <c r="C1844">
+        <v>5170</v>
+      </c>
+      <c r="D1844" t="s">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="1845" spans="1:4">
+      <c r="A1845" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1845">
+        <v>20</v>
+      </c>
+      <c r="C1845">
+        <v>5180</v>
+      </c>
+      <c r="D1845" t="s">
+        <v>1847</v>
+      </c>
+    </row>
+    <row r="1846" spans="1:4">
+      <c r="A1846" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1846">
+        <v>21</v>
+      </c>
+      <c r="C1846">
+        <v>5200</v>
+      </c>
+      <c r="D1846" t="s">
+        <v>1848</v>
+      </c>
+    </row>
+    <row r="1847" spans="1:4">
+      <c r="A1847" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1847">
+        <v>22</v>
+      </c>
+      <c r="C1847">
+        <v>5230</v>
+      </c>
+      <c r="D1847" t="s">
+        <v>1849</v>
+      </c>
+    </row>
+    <row r="1848" spans="1:4">
+      <c r="A1848" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1848">
+        <v>23</v>
+      </c>
+      <c r="C1848">
+        <v>5290</v>
+      </c>
+      <c r="D1848" t="s">
+        <v>1850</v>
+      </c>
+    </row>
+    <row r="1849" spans="1:4">
+      <c r="A1849" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1849">
+        <v>24</v>
+      </c>
+      <c r="C1849">
+        <v>5360</v>
+      </c>
+      <c r="D1849" t="s">
+        <v>1851</v>
+      </c>
+    </row>
+    <row r="1850" spans="1:4">
+      <c r="A1850" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1850">
+        <v>25</v>
+      </c>
+      <c r="C1850">
+        <v>5460</v>
+      </c>
+      <c r="D1850" t="s">
+        <v>1852</v>
+      </c>
+    </row>
+    <row r="1851" spans="1:4">
+      <c r="A1851" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1851">
+        <v>26</v>
+      </c>
+      <c r="C1851">
+        <v>5570</v>
+      </c>
+      <c r="D1851" t="s">
+        <v>1853</v>
+      </c>
+    </row>
+    <row r="1852" spans="1:4">
+      <c r="A1852" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1852">
+        <v>27</v>
+      </c>
+      <c r="C1852">
+        <v>5690</v>
+      </c>
+      <c r="D1852" t="s">
+        <v>1854</v>
+      </c>
+    </row>
+    <row r="1853" spans="1:4">
+      <c r="A1853" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1853">
+        <v>28</v>
+      </c>
+      <c r="C1853">
+        <v>5810</v>
+      </c>
+      <c r="D1853" t="s">
+        <v>1855</v>
+      </c>
+    </row>
+    <row r="1854" spans="1:4">
+      <c r="A1854" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1854">
+        <v>29</v>
+      </c>
+      <c r="C1854">
+        <v>5930</v>
+      </c>
+      <c r="D1854" t="s">
+        <v>1856</v>
+      </c>
+    </row>
+    <row r="1855" spans="1:4">
+      <c r="A1855" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1855">
+        <v>30</v>
+      </c>
+      <c r="C1855">
+        <v>6040</v>
+      </c>
+      <c r="D1855" t="s">
+        <v>1857</v>
+      </c>
+    </row>
+    <row r="1856" spans="1:4">
+      <c r="A1856" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1856">
+        <v>31</v>
+      </c>
+      <c r="C1856">
+        <v>6120</v>
+      </c>
+      <c r="D1856" t="s">
+        <v>1858</v>
+      </c>
+    </row>
+    <row r="1857" spans="1:4">
+      <c r="A1857" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1857">
+        <v>32</v>
+      </c>
+      <c r="C1857">
+        <v>6170</v>
+      </c>
+      <c r="D1857" t="s">
+        <v>1859</v>
+      </c>
+    </row>
+    <row r="1858" spans="1:4">
+      <c r="A1858" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1858">
+        <v>33</v>
+      </c>
+      <c r="C1858">
+        <v>6200</v>
+      </c>
+      <c r="D1858" t="s">
+        <v>1860</v>
+      </c>
+    </row>
+    <row r="1859" spans="1:4">
+      <c r="A1859" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1859">
+        <v>34</v>
+      </c>
+      <c r="C1859">
+        <v>6190</v>
+      </c>
+      <c r="D1859" t="s">
+        <v>1861</v>
+      </c>
+    </row>
+    <row r="1860" spans="1:4">
+      <c r="A1860" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1860">
+        <v>35</v>
+      </c>
+      <c r="C1860">
+        <v>6150</v>
+      </c>
+      <c r="D1860" t="s">
+        <v>1862</v>
+      </c>
+    </row>
+    <row r="1861" spans="1:4">
+      <c r="A1861" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1861">
+        <v>36</v>
+      </c>
+      <c r="C1861">
+        <v>6090</v>
+      </c>
+      <c r="D1861" t="s">
+        <v>1863</v>
+      </c>
+    </row>
+    <row r="1862" spans="1:4">
+      <c r="A1862" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1862">
+        <v>37</v>
+      </c>
+      <c r="C1862">
+        <v>6010</v>
+      </c>
+      <c r="D1862" t="s">
+        <v>1864</v>
+      </c>
+    </row>
+    <row r="1863" spans="1:4">
+      <c r="A1863" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1863">
+        <v>38</v>
+      </c>
+      <c r="C1863">
+        <v>5910</v>
+      </c>
+      <c r="D1863" t="s">
+        <v>1865</v>
+      </c>
+    </row>
+    <row r="1864" spans="1:4">
+      <c r="A1864" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1864">
+        <v>39</v>
+      </c>
+      <c r="C1864">
+        <v>5810</v>
+      </c>
+      <c r="D1864" t="s">
+        <v>1866</v>
+      </c>
+    </row>
+    <row r="1865" spans="1:4">
+      <c r="A1865" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1865">
+        <v>40</v>
+      </c>
+      <c r="C1865">
+        <v>5700</v>
+      </c>
+      <c r="D1865" t="s">
+        <v>1867</v>
+      </c>
+    </row>
+    <row r="1866" spans="1:4">
+      <c r="A1866" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1866">
+        <v>41</v>
+      </c>
+      <c r="C1866">
+        <v>5590</v>
+      </c>
+      <c r="D1866" t="s">
+        <v>1868</v>
+      </c>
+    </row>
+    <row r="1867" spans="1:4">
+      <c r="A1867" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1867">
+        <v>42</v>
+      </c>
+      <c r="C1867">
+        <v>5500</v>
+      </c>
+      <c r="D1867" t="s">
+        <v>1869</v>
+      </c>
+    </row>
+    <row r="1868" spans="1:4">
+      <c r="A1868" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1868">
+        <v>43</v>
+      </c>
+      <c r="C1868">
+        <v>5410</v>
+      </c>
+      <c r="D1868" t="s">
+        <v>1870</v>
+      </c>
+    </row>
+    <row r="1869" spans="1:4">
+      <c r="A1869" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1869">
+        <v>44</v>
+      </c>
+      <c r="C1869">
+        <v>5330</v>
+      </c>
+      <c r="D1869" t="s">
+        <v>1871</v>
+      </c>
+    </row>
+    <row r="1870" spans="1:4">
+      <c r="A1870" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1870">
+        <v>45</v>
+      </c>
+      <c r="C1870">
+        <v>5250</v>
+      </c>
+      <c r="D1870" t="s">
+        <v>1872</v>
+      </c>
+    </row>
+    <row r="1871" spans="1:4">
+      <c r="A1871" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1871">
+        <v>46</v>
+      </c>
+      <c r="C1871">
+        <v>5190</v>
+      </c>
+      <c r="D1871" t="s">
+        <v>1873</v>
+      </c>
+    </row>
+    <row r="1872" spans="1:4">
+      <c r="A1872" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1872">
+        <v>47</v>
+      </c>
+      <c r="C1872">
+        <v>5140</v>
+      </c>
+      <c r="D1872" t="s">
+        <v>1874</v>
+      </c>
+    </row>
+    <row r="1873" spans="1:4">
+      <c r="A1873" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1873">
+        <v>48</v>
+      </c>
+      <c r="C1873">
+        <v>5090</v>
+      </c>
+      <c r="D1873" t="s">
+        <v>1875</v>
+      </c>
+    </row>
+    <row r="1874" spans="1:4">
+      <c r="A1874" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1874">
+        <v>49</v>
+      </c>
+      <c r="C1874">
+        <v>5050</v>
+      </c>
+      <c r="D1874" t="s">
+        <v>1876</v>
+      </c>
+    </row>
+    <row r="1875" spans="1:4">
+      <c r="A1875" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1875">
+        <v>50</v>
+      </c>
+      <c r="C1875">
+        <v>5010</v>
+      </c>
+      <c r="D1875" t="s">
+        <v>1877</v>
+      </c>
+    </row>
+    <row r="1876" spans="1:4">
+      <c r="A1876" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1876">
+        <v>51</v>
+      </c>
+      <c r="C1876">
+        <v>4990</v>
+      </c>
+      <c r="D1876" t="s">
+        <v>1878</v>
+      </c>
+    </row>
+    <row r="1877" spans="1:4">
+      <c r="A1877" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1877">
+        <v>52</v>
+      </c>
+      <c r="C1877">
+        <v>4970</v>
+      </c>
+      <c r="D1877" t="s">
+        <v>1879</v>
+      </c>
+    </row>
+    <row r="1878" spans="1:4">
+      <c r="A1878" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1878">
+        <v>53</v>
+      </c>
+      <c r="C1878">
+        <v>4960</v>
+      </c>
+      <c r="D1878" t="s">
+        <v>1880</v>
+      </c>
+    </row>
+    <row r="1879" spans="1:4">
+      <c r="A1879" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1879">
+        <v>54</v>
+      </c>
+      <c r="C1879">
+        <v>4960</v>
+      </c>
+      <c r="D1879" t="s">
+        <v>1881</v>
+      </c>
+    </row>
+    <row r="1880" spans="1:4">
+      <c r="A1880" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1880">
+        <v>55</v>
+      </c>
+      <c r="C1880">
+        <v>4960</v>
+      </c>
+      <c r="D1880" t="s">
+        <v>1882</v>
+      </c>
+    </row>
+    <row r="1881" spans="1:4">
+      <c r="A1881" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1881">
+        <v>56</v>
+      </c>
+      <c r="C1881">
+        <v>4970</v>
+      </c>
+      <c r="D1881" t="s">
+        <v>1883</v>
+      </c>
+    </row>
+    <row r="1882" spans="1:4">
+      <c r="A1882" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1882">
+        <v>57</v>
+      </c>
+      <c r="C1882">
+        <v>4990</v>
+      </c>
+      <c r="D1882" t="s">
+        <v>1884</v>
+      </c>
+    </row>
+    <row r="1883" spans="1:4">
+      <c r="A1883" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1883">
+        <v>58</v>
+      </c>
+      <c r="C1883">
+        <v>5000</v>
+      </c>
+      <c r="D1883" t="s">
+        <v>1885</v>
+      </c>
+    </row>
+    <row r="1884" spans="1:4">
+      <c r="A1884" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1884">
+        <v>59</v>
+      </c>
+      <c r="C1884">
+        <v>5020</v>
+      </c>
+      <c r="D1884" t="s">
+        <v>1886</v>
+      </c>
+    </row>
+    <row r="1885" spans="1:4">
+      <c r="A1885" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1885">
+        <v>60</v>
+      </c>
+      <c r="C1885">
+        <v>5040</v>
+      </c>
+      <c r="D1885" t="s">
+        <v>1887</v>
+      </c>
+    </row>
+    <row r="1886" spans="1:4">
+      <c r="A1886" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1886">
+        <v>61</v>
+      </c>
+      <c r="C1886">
+        <v>5070</v>
+      </c>
+      <c r="D1886" t="s">
+        <v>1888</v>
+      </c>
+    </row>
+    <row r="1887" spans="1:4">
+      <c r="A1887" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1887">
+        <v>62</v>
+      </c>
+      <c r="C1887">
+        <v>5110</v>
+      </c>
+      <c r="D1887" t="s">
+        <v>1889</v>
+      </c>
+    </row>
+    <row r="1888" spans="1:4">
+      <c r="A1888" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1888">
+        <v>63</v>
+      </c>
+      <c r="C1888">
+        <v>5160</v>
+      </c>
+      <c r="D1888" t="s">
+        <v>1890</v>
+      </c>
+    </row>
+    <row r="1889" spans="1:4">
+      <c r="A1889" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1889">
+        <v>64</v>
+      </c>
+      <c r="C1889">
+        <v>5220</v>
+      </c>
+      <c r="D1889" t="s">
+        <v>1891</v>
+      </c>
+    </row>
+    <row r="1890" spans="1:4">
+      <c r="A1890" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1890">
+        <v>65</v>
+      </c>
+      <c r="C1890">
+        <v>5300</v>
+      </c>
+      <c r="D1890" t="s">
+        <v>1892</v>
+      </c>
+    </row>
+    <row r="1891" spans="1:4">
+      <c r="A1891" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1891">
+        <v>66</v>
+      </c>
+      <c r="C1891">
+        <v>5380</v>
+      </c>
+      <c r="D1891" t="s">
+        <v>1893</v>
+      </c>
+    </row>
+    <row r="1892" spans="1:4">
+      <c r="A1892" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1892">
+        <v>67</v>
+      </c>
+      <c r="C1892">
+        <v>5470</v>
+      </c>
+      <c r="D1892" t="s">
+        <v>1894</v>
+      </c>
+    </row>
+    <row r="1893" spans="1:4">
+      <c r="A1893" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1893">
+        <v>68</v>
+      </c>
+      <c r="C1893">
+        <v>5560</v>
+      </c>
+      <c r="D1893" t="s">
+        <v>1895</v>
+      </c>
+    </row>
+    <row r="1894" spans="1:4">
+      <c r="A1894" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1894">
+        <v>69</v>
+      </c>
+      <c r="C1894">
+        <v>5640</v>
+      </c>
+      <c r="D1894" t="s">
+        <v>1896</v>
+      </c>
+    </row>
+    <row r="1895" spans="1:4">
+      <c r="A1895" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1895">
+        <v>70</v>
+      </c>
+      <c r="C1895">
+        <v>5720</v>
+      </c>
+      <c r="D1895" t="s">
+        <v>1897</v>
+      </c>
+    </row>
+    <row r="1896" spans="1:4">
+      <c r="A1896" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1896">
+        <v>71</v>
+      </c>
+      <c r="C1896">
+        <v>5800</v>
+      </c>
+      <c r="D1896" t="s">
+        <v>1898</v>
+      </c>
+    </row>
+    <row r="1897" spans="1:4">
+      <c r="A1897" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1897">
+        <v>72</v>
+      </c>
+      <c r="C1897">
+        <v>5880</v>
+      </c>
+      <c r="D1897" t="s">
+        <v>1899</v>
+      </c>
+    </row>
+    <row r="1898" spans="1:4">
+      <c r="A1898" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1898">
+        <v>73</v>
+      </c>
+      <c r="C1898">
+        <v>5970</v>
+      </c>
+      <c r="D1898" t="s">
+        <v>1900</v>
+      </c>
+    </row>
+    <row r="1899" spans="1:4">
+      <c r="A1899" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1899">
+        <v>74</v>
+      </c>
+      <c r="C1899">
+        <v>6070</v>
+      </c>
+      <c r="D1899" t="s">
+        <v>1901</v>
+      </c>
+    </row>
+    <row r="1900" spans="1:4">
+      <c r="A1900" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1900">
+        <v>75</v>
+      </c>
+      <c r="C1900">
+        <v>6180</v>
+      </c>
+      <c r="D1900" t="s">
+        <v>1902</v>
+      </c>
+    </row>
+    <row r="1901" spans="1:4">
+      <c r="A1901" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1901">
+        <v>76</v>
+      </c>
+      <c r="C1901">
+        <v>6300</v>
+      </c>
+      <c r="D1901" t="s">
+        <v>1903</v>
+      </c>
+    </row>
+    <row r="1902" spans="1:4">
+      <c r="A1902" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1902">
+        <v>77</v>
+      </c>
+      <c r="C1902">
+        <v>6430</v>
+      </c>
+      <c r="D1902" t="s">
+        <v>1904</v>
+      </c>
+    </row>
+    <row r="1903" spans="1:4">
+      <c r="A1903" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1903">
+        <v>78</v>
+      </c>
+      <c r="C1903">
+        <v>6560</v>
+      </c>
+      <c r="D1903" t="s">
+        <v>1905</v>
+      </c>
+    </row>
+    <row r="1904" spans="1:4">
+      <c r="A1904" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1904">
+        <v>79</v>
+      </c>
+      <c r="C1904">
+        <v>6660</v>
+      </c>
+      <c r="D1904" t="s">
+        <v>1906</v>
+      </c>
+    </row>
+    <row r="1905" spans="1:4">
+      <c r="A1905" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1905">
+        <v>80</v>
+      </c>
+      <c r="C1905">
+        <v>6750</v>
+      </c>
+      <c r="D1905" t="s">
+        <v>1907</v>
+      </c>
+    </row>
+    <row r="1906" spans="1:4">
+      <c r="A1906" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1906">
+        <v>81</v>
+      </c>
+      <c r="C1906">
+        <v>6850</v>
+      </c>
+      <c r="D1906" t="s">
+        <v>1908</v>
+      </c>
+    </row>
+    <row r="1907" spans="1:4">
+      <c r="A1907" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1907">
+        <v>82</v>
+      </c>
+      <c r="C1907">
+        <v>6950</v>
+      </c>
+      <c r="D1907" t="s">
+        <v>1909</v>
+      </c>
+    </row>
+    <row r="1908" spans="1:4">
+      <c r="A1908" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1908">
+        <v>83</v>
+      </c>
+      <c r="C1908">
+        <v>7030</v>
+      </c>
+      <c r="D1908" t="s">
+        <v>1910</v>
+      </c>
+    </row>
+    <row r="1909" spans="1:4">
+      <c r="A1909" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1909">
+        <v>84</v>
+      </c>
+      <c r="C1909">
+        <v>7090</v>
+      </c>
+      <c r="D1909" t="s">
+        <v>1911</v>
+      </c>
+    </row>
+    <row r="1910" spans="1:4">
+      <c r="A1910" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1910">
+        <v>85</v>
+      </c>
+      <c r="C1910">
+        <v>7080</v>
+      </c>
+      <c r="D1910" t="s">
+        <v>1912</v>
+      </c>
+    </row>
+    <row r="1911" spans="1:4">
+      <c r="A1911" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1911">
+        <v>86</v>
+      </c>
+      <c r="C1911">
+        <v>7020</v>
+      </c>
+      <c r="D1911" t="s">
+        <v>1913</v>
+      </c>
+    </row>
+    <row r="1912" spans="1:4">
+      <c r="A1912" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1912">
+        <v>87</v>
+      </c>
+      <c r="C1912">
+        <v>7000</v>
+      </c>
+      <c r="D1912" t="s">
+        <v>1914</v>
+      </c>
+    </row>
+    <row r="1913" spans="1:4">
+      <c r="A1913" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1913">
+        <v>88</v>
+      </c>
+      <c r="C1913">
+        <v>6960</v>
+      </c>
+      <c r="D1913" t="s">
+        <v>1915</v>
+      </c>
+    </row>
+    <row r="1914" spans="1:4">
+      <c r="A1914" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1914">
+        <v>89</v>
+      </c>
+      <c r="C1914">
+        <v>6890</v>
+      </c>
+      <c r="D1914" t="s">
+        <v>1916</v>
+      </c>
+    </row>
+    <row r="1915" spans="1:4">
+      <c r="A1915" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1915">
+        <v>90</v>
+      </c>
+      <c r="C1915">
+        <v>6840</v>
+      </c>
+      <c r="D1915" t="s">
+        <v>1917</v>
+      </c>
+    </row>
+    <row r="1916" spans="1:4">
+      <c r="A1916" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1916">
+        <v>91</v>
+      </c>
+      <c r="C1916">
+        <v>6690</v>
+      </c>
+      <c r="D1916" t="s">
+        <v>1918</v>
+      </c>
+    </row>
+    <row r="1917" spans="1:4">
+      <c r="A1917" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1917">
+        <v>92</v>
+      </c>
+      <c r="C1917">
+        <v>6500</v>
+      </c>
+      <c r="D1917" t="s">
+        <v>1919</v>
+      </c>
+    </row>
+    <row r="1918" spans="1:4">
+      <c r="A1918" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1918">
+        <v>93</v>
+      </c>
+      <c r="C1918">
+        <v>6280</v>
+      </c>
+      <c r="D1918" t="s">
+        <v>1920</v>
+      </c>
+    </row>
+    <row r="1919" spans="1:4">
+      <c r="A1919" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1919">
+        <v>94</v>
+      </c>
+      <c r="C1919">
+        <v>6090</v>
+      </c>
+      <c r="D1919" t="s">
+        <v>1921</v>
+      </c>
+    </row>
+    <row r="1920" spans="1:4">
+      <c r="A1920" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1920">
+        <v>95</v>
+      </c>
+      <c r="C1920">
+        <v>6010</v>
+      </c>
+      <c r="D1920" t="s">
+        <v>1922</v>
+      </c>
+    </row>
+    <row r="1921" spans="1:4">
+      <c r="A1921" s="2">
+        <v>46162</v>
+      </c>
+      <c r="B1921">
+        <v>96</v>
+      </c>
+      <c r="C1921">
+        <v>5900</v>
+      </c>
+      <c r="D1921" t="s">
+        <v>1923</v>
       </c>
     </row>
   </sheetData>

--- a/Market Fundamentals/Transelectrica_data/Cons_Prod_final/Weekly_Consumption_2026.xlsx
+++ b/Market Fundamentals/Transelectrica_data/Cons_Prod_final/Weekly_Consumption_2026.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1924" uniqueCount="1924">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2116" uniqueCount="2116">
   <si>
     <t>Date</t>
   </si>
@@ -5786,6 +5786,582 @@
   </si>
   <si>
     <t>20.05.202696.0</t>
+  </si>
+  <si>
+    <t>21.05.20261.0</t>
+  </si>
+  <si>
+    <t>21.05.20262.0</t>
+  </si>
+  <si>
+    <t>21.05.20263.0</t>
+  </si>
+  <si>
+    <t>21.05.20264.0</t>
+  </si>
+  <si>
+    <t>21.05.20265.0</t>
+  </si>
+  <si>
+    <t>21.05.20266.0</t>
+  </si>
+  <si>
+    <t>21.05.20267.0</t>
+  </si>
+  <si>
+    <t>21.05.20268.0</t>
+  </si>
+  <si>
+    <t>21.05.20269.0</t>
+  </si>
+  <si>
+    <t>21.05.202610.0</t>
+  </si>
+  <si>
+    <t>21.05.202611.0</t>
+  </si>
+  <si>
+    <t>21.05.202612.0</t>
+  </si>
+  <si>
+    <t>21.05.202613.0</t>
+  </si>
+  <si>
+    <t>21.05.202614.0</t>
+  </si>
+  <si>
+    <t>21.05.202615.0</t>
+  </si>
+  <si>
+    <t>21.05.202616.0</t>
+  </si>
+  <si>
+    <t>21.05.202617.0</t>
+  </si>
+  <si>
+    <t>21.05.202618.0</t>
+  </si>
+  <si>
+    <t>21.05.202619.0</t>
+  </si>
+  <si>
+    <t>21.05.202620.0</t>
+  </si>
+  <si>
+    <t>21.05.202621.0</t>
+  </si>
+  <si>
+    <t>21.05.202622.0</t>
+  </si>
+  <si>
+    <t>21.05.202623.0</t>
+  </si>
+  <si>
+    <t>21.05.202624.0</t>
+  </si>
+  <si>
+    <t>21.05.202625.0</t>
+  </si>
+  <si>
+    <t>21.05.202626.0</t>
+  </si>
+  <si>
+    <t>21.05.202627.0</t>
+  </si>
+  <si>
+    <t>21.05.202628.0</t>
+  </si>
+  <si>
+    <t>21.05.202629.0</t>
+  </si>
+  <si>
+    <t>21.05.202630.0</t>
+  </si>
+  <si>
+    <t>21.05.202631.0</t>
+  </si>
+  <si>
+    <t>21.05.202632.0</t>
+  </si>
+  <si>
+    <t>21.05.202633.0</t>
+  </si>
+  <si>
+    <t>21.05.202634.0</t>
+  </si>
+  <si>
+    <t>21.05.202635.0</t>
+  </si>
+  <si>
+    <t>21.05.202636.0</t>
+  </si>
+  <si>
+    <t>21.05.202637.0</t>
+  </si>
+  <si>
+    <t>21.05.202638.0</t>
+  </si>
+  <si>
+    <t>21.05.202639.0</t>
+  </si>
+  <si>
+    <t>21.05.202640.0</t>
+  </si>
+  <si>
+    <t>21.05.202641.0</t>
+  </si>
+  <si>
+    <t>21.05.202642.0</t>
+  </si>
+  <si>
+    <t>21.05.202643.0</t>
+  </si>
+  <si>
+    <t>21.05.202644.0</t>
+  </si>
+  <si>
+    <t>21.05.202645.0</t>
+  </si>
+  <si>
+    <t>21.05.202646.0</t>
+  </si>
+  <si>
+    <t>21.05.202647.0</t>
+  </si>
+  <si>
+    <t>21.05.202648.0</t>
+  </si>
+  <si>
+    <t>21.05.202649.0</t>
+  </si>
+  <si>
+    <t>21.05.202650.0</t>
+  </si>
+  <si>
+    <t>21.05.202651.0</t>
+  </si>
+  <si>
+    <t>21.05.202652.0</t>
+  </si>
+  <si>
+    <t>21.05.202653.0</t>
+  </si>
+  <si>
+    <t>21.05.202654.0</t>
+  </si>
+  <si>
+    <t>21.05.202655.0</t>
+  </si>
+  <si>
+    <t>21.05.202656.0</t>
+  </si>
+  <si>
+    <t>21.05.202657.0</t>
+  </si>
+  <si>
+    <t>21.05.202658.0</t>
+  </si>
+  <si>
+    <t>21.05.202659.0</t>
+  </si>
+  <si>
+    <t>21.05.202660.0</t>
+  </si>
+  <si>
+    <t>21.05.202661.0</t>
+  </si>
+  <si>
+    <t>21.05.202662.0</t>
+  </si>
+  <si>
+    <t>21.05.202663.0</t>
+  </si>
+  <si>
+    <t>21.05.202664.0</t>
+  </si>
+  <si>
+    <t>21.05.202665.0</t>
+  </si>
+  <si>
+    <t>21.05.202666.0</t>
+  </si>
+  <si>
+    <t>21.05.202667.0</t>
+  </si>
+  <si>
+    <t>21.05.202668.0</t>
+  </si>
+  <si>
+    <t>21.05.202669.0</t>
+  </si>
+  <si>
+    <t>21.05.202670.0</t>
+  </si>
+  <si>
+    <t>21.05.202671.0</t>
+  </si>
+  <si>
+    <t>21.05.202672.0</t>
+  </si>
+  <si>
+    <t>21.05.202673.0</t>
+  </si>
+  <si>
+    <t>21.05.202674.0</t>
+  </si>
+  <si>
+    <t>21.05.202675.0</t>
+  </si>
+  <si>
+    <t>21.05.202676.0</t>
+  </si>
+  <si>
+    <t>21.05.202677.0</t>
+  </si>
+  <si>
+    <t>21.05.202678.0</t>
+  </si>
+  <si>
+    <t>21.05.202679.0</t>
+  </si>
+  <si>
+    <t>21.05.202680.0</t>
+  </si>
+  <si>
+    <t>21.05.202681.0</t>
+  </si>
+  <si>
+    <t>21.05.202682.0</t>
+  </si>
+  <si>
+    <t>21.05.202683.0</t>
+  </si>
+  <si>
+    <t>21.05.202684.0</t>
+  </si>
+  <si>
+    <t>21.05.202685.0</t>
+  </si>
+  <si>
+    <t>21.05.202686.0</t>
+  </si>
+  <si>
+    <t>21.05.202687.0</t>
+  </si>
+  <si>
+    <t>21.05.202688.0</t>
+  </si>
+  <si>
+    <t>21.05.202689.0</t>
+  </si>
+  <si>
+    <t>21.05.202690.0</t>
+  </si>
+  <si>
+    <t>21.05.202691.0</t>
+  </si>
+  <si>
+    <t>21.05.202692.0</t>
+  </si>
+  <si>
+    <t>21.05.202693.0</t>
+  </si>
+  <si>
+    <t>21.05.202694.0</t>
+  </si>
+  <si>
+    <t>21.05.202695.0</t>
+  </si>
+  <si>
+    <t>21.05.202696.0</t>
+  </si>
+  <si>
+    <t>22.05.20261.0</t>
+  </si>
+  <si>
+    <t>22.05.20262.0</t>
+  </si>
+  <si>
+    <t>22.05.20263.0</t>
+  </si>
+  <si>
+    <t>22.05.20264.0</t>
+  </si>
+  <si>
+    <t>22.05.20265.0</t>
+  </si>
+  <si>
+    <t>22.05.20266.0</t>
+  </si>
+  <si>
+    <t>22.05.20267.0</t>
+  </si>
+  <si>
+    <t>22.05.20268.0</t>
+  </si>
+  <si>
+    <t>22.05.20269.0</t>
+  </si>
+  <si>
+    <t>22.05.202610.0</t>
+  </si>
+  <si>
+    <t>22.05.202611.0</t>
+  </si>
+  <si>
+    <t>22.05.202612.0</t>
+  </si>
+  <si>
+    <t>22.05.202613.0</t>
+  </si>
+  <si>
+    <t>22.05.202614.0</t>
+  </si>
+  <si>
+    <t>22.05.202615.0</t>
+  </si>
+  <si>
+    <t>22.05.202616.0</t>
+  </si>
+  <si>
+    <t>22.05.202617.0</t>
+  </si>
+  <si>
+    <t>22.05.202618.0</t>
+  </si>
+  <si>
+    <t>22.05.202619.0</t>
+  </si>
+  <si>
+    <t>22.05.202620.0</t>
+  </si>
+  <si>
+    <t>22.05.202621.0</t>
+  </si>
+  <si>
+    <t>22.05.202622.0</t>
+  </si>
+  <si>
+    <t>22.05.202623.0</t>
+  </si>
+  <si>
+    <t>22.05.202624.0</t>
+  </si>
+  <si>
+    <t>22.05.202625.0</t>
+  </si>
+  <si>
+    <t>22.05.202626.0</t>
+  </si>
+  <si>
+    <t>22.05.202627.0</t>
+  </si>
+  <si>
+    <t>22.05.202628.0</t>
+  </si>
+  <si>
+    <t>22.05.202629.0</t>
+  </si>
+  <si>
+    <t>22.05.202630.0</t>
+  </si>
+  <si>
+    <t>22.05.202631.0</t>
+  </si>
+  <si>
+    <t>22.05.202632.0</t>
+  </si>
+  <si>
+    <t>22.05.202633.0</t>
+  </si>
+  <si>
+    <t>22.05.202634.0</t>
+  </si>
+  <si>
+    <t>22.05.202635.0</t>
+  </si>
+  <si>
+    <t>22.05.202636.0</t>
+  </si>
+  <si>
+    <t>22.05.202637.0</t>
+  </si>
+  <si>
+    <t>22.05.202638.0</t>
+  </si>
+  <si>
+    <t>22.05.202639.0</t>
+  </si>
+  <si>
+    <t>22.05.202640.0</t>
+  </si>
+  <si>
+    <t>22.05.202641.0</t>
+  </si>
+  <si>
+    <t>22.05.202642.0</t>
+  </si>
+  <si>
+    <t>22.05.202643.0</t>
+  </si>
+  <si>
+    <t>22.05.202644.0</t>
+  </si>
+  <si>
+    <t>22.05.202645.0</t>
+  </si>
+  <si>
+    <t>22.05.202646.0</t>
+  </si>
+  <si>
+    <t>22.05.202647.0</t>
+  </si>
+  <si>
+    <t>22.05.202648.0</t>
+  </si>
+  <si>
+    <t>22.05.202649.0</t>
+  </si>
+  <si>
+    <t>22.05.202650.0</t>
+  </si>
+  <si>
+    <t>22.05.202651.0</t>
+  </si>
+  <si>
+    <t>22.05.202652.0</t>
+  </si>
+  <si>
+    <t>22.05.202653.0</t>
+  </si>
+  <si>
+    <t>22.05.202654.0</t>
+  </si>
+  <si>
+    <t>22.05.202655.0</t>
+  </si>
+  <si>
+    <t>22.05.202656.0</t>
+  </si>
+  <si>
+    <t>22.05.202657.0</t>
+  </si>
+  <si>
+    <t>22.05.202658.0</t>
+  </si>
+  <si>
+    <t>22.05.202659.0</t>
+  </si>
+  <si>
+    <t>22.05.202660.0</t>
+  </si>
+  <si>
+    <t>22.05.202661.0</t>
+  </si>
+  <si>
+    <t>22.05.202662.0</t>
+  </si>
+  <si>
+    <t>22.05.202663.0</t>
+  </si>
+  <si>
+    <t>22.05.202664.0</t>
+  </si>
+  <si>
+    <t>22.05.202665.0</t>
+  </si>
+  <si>
+    <t>22.05.202666.0</t>
+  </si>
+  <si>
+    <t>22.05.202667.0</t>
+  </si>
+  <si>
+    <t>22.05.202668.0</t>
+  </si>
+  <si>
+    <t>22.05.202669.0</t>
+  </si>
+  <si>
+    <t>22.05.202670.0</t>
+  </si>
+  <si>
+    <t>22.05.202671.0</t>
+  </si>
+  <si>
+    <t>22.05.202672.0</t>
+  </si>
+  <si>
+    <t>22.05.202673.0</t>
+  </si>
+  <si>
+    <t>22.05.202674.0</t>
+  </si>
+  <si>
+    <t>22.05.202675.0</t>
+  </si>
+  <si>
+    <t>22.05.202676.0</t>
+  </si>
+  <si>
+    <t>22.05.202677.0</t>
+  </si>
+  <si>
+    <t>22.05.202678.0</t>
+  </si>
+  <si>
+    <t>22.05.202679.0</t>
+  </si>
+  <si>
+    <t>22.05.202680.0</t>
+  </si>
+  <si>
+    <t>22.05.202681.0</t>
+  </si>
+  <si>
+    <t>22.05.202682.0</t>
+  </si>
+  <si>
+    <t>22.05.202683.0</t>
+  </si>
+  <si>
+    <t>22.05.202684.0</t>
+  </si>
+  <si>
+    <t>22.05.202685.0</t>
+  </si>
+  <si>
+    <t>22.05.202686.0</t>
+  </si>
+  <si>
+    <t>22.05.202687.0</t>
+  </si>
+  <si>
+    <t>22.05.202688.0</t>
+  </si>
+  <si>
+    <t>22.05.202689.0</t>
+  </si>
+  <si>
+    <t>22.05.202690.0</t>
+  </si>
+  <si>
+    <t>22.05.202691.0</t>
+  </si>
+  <si>
+    <t>22.05.202692.0</t>
+  </si>
+  <si>
+    <t>22.05.202693.0</t>
+  </si>
+  <si>
+    <t>22.05.202694.0</t>
+  </si>
+  <si>
+    <t>22.05.202695.0</t>
+  </si>
+  <si>
+    <t>22.05.202696.0</t>
   </si>
 </sst>
 </file>
@@ -6147,7 +6723,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1921"/>
+  <dimension ref="A1:D2113"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -24988,7 +25564,7 @@
         <v>1</v>
       </c>
       <c r="C1346">
-        <v>5460</v>
+        <v>5490</v>
       </c>
       <c r="D1346" t="s">
         <v>1348</v>
@@ -25002,7 +25578,7 @@
         <v>2</v>
       </c>
       <c r="C1347">
-        <v>5420</v>
+        <v>5430</v>
       </c>
       <c r="D1347" t="s">
         <v>1349</v>
@@ -25016,7 +25592,7 @@
         <v>3</v>
       </c>
       <c r="C1348">
-        <v>5360</v>
+        <v>5370</v>
       </c>
       <c r="D1348" t="s">
         <v>1350</v>
@@ -25030,7 +25606,7 @@
         <v>4</v>
       </c>
       <c r="C1349">
-        <v>5290</v>
+        <v>5310</v>
       </c>
       <c r="D1349" t="s">
         <v>1351</v>
@@ -25044,7 +25620,7 @@
         <v>5</v>
       </c>
       <c r="C1350">
-        <v>5240</v>
+        <v>5230</v>
       </c>
       <c r="D1350" t="s">
         <v>1352</v>
@@ -25058,7 +25634,7 @@
         <v>6</v>
       </c>
       <c r="C1351">
-        <v>5190</v>
+        <v>5180</v>
       </c>
       <c r="D1351" t="s">
         <v>1353</v>
@@ -25072,7 +25648,7 @@
         <v>7</v>
       </c>
       <c r="C1352">
-        <v>5140</v>
+        <v>5150</v>
       </c>
       <c r="D1352" t="s">
         <v>1354</v>
@@ -25086,7 +25662,7 @@
         <v>8</v>
       </c>
       <c r="C1353">
-        <v>5100</v>
+        <v>5130</v>
       </c>
       <c r="D1353" t="s">
         <v>1355</v>
@@ -25100,7 +25676,7 @@
         <v>9</v>
       </c>
       <c r="C1354">
-        <v>5060</v>
+        <v>5110</v>
       </c>
       <c r="D1354" t="s">
         <v>1356</v>
@@ -25114,7 +25690,7 @@
         <v>10</v>
       </c>
       <c r="C1355">
-        <v>5030</v>
+        <v>5100</v>
       </c>
       <c r="D1355" t="s">
         <v>1357</v>
@@ -25128,7 +25704,7 @@
         <v>11</v>
       </c>
       <c r="C1356">
-        <v>5010</v>
+        <v>5100</v>
       </c>
       <c r="D1356" t="s">
         <v>1358</v>
@@ -25142,7 +25718,7 @@
         <v>12</v>
       </c>
       <c r="C1357">
-        <v>5010</v>
+        <v>5090</v>
       </c>
       <c r="D1357" t="s">
         <v>1359</v>
@@ -25156,7 +25732,7 @@
         <v>13</v>
       </c>
       <c r="C1358">
-        <v>5000</v>
+        <v>5080</v>
       </c>
       <c r="D1358" t="s">
         <v>1360</v>
@@ -25170,7 +25746,7 @@
         <v>14</v>
       </c>
       <c r="C1359">
-        <v>5020</v>
+        <v>5080</v>
       </c>
       <c r="D1359" t="s">
         <v>1361</v>
@@ -25184,7 +25760,7 @@
         <v>15</v>
       </c>
       <c r="C1360">
-        <v>5030</v>
+        <v>5080</v>
       </c>
       <c r="D1360" t="s">
         <v>1362</v>
@@ -25198,7 +25774,7 @@
         <v>16</v>
       </c>
       <c r="C1361">
-        <v>5030</v>
+        <v>5090</v>
       </c>
       <c r="D1361" t="s">
         <v>1363</v>
@@ -25212,7 +25788,7 @@
         <v>17</v>
       </c>
       <c r="C1362">
-        <v>5040</v>
+        <v>5100</v>
       </c>
       <c r="D1362" t="s">
         <v>1364</v>
@@ -25226,7 +25802,7 @@
         <v>18</v>
       </c>
       <c r="C1363">
-        <v>5050</v>
+        <v>5110</v>
       </c>
       <c r="D1363" t="s">
         <v>1365</v>
@@ -25240,7 +25816,7 @@
         <v>19</v>
       </c>
       <c r="C1364">
-        <v>5070</v>
+        <v>5120</v>
       </c>
       <c r="D1364" t="s">
         <v>1366</v>
@@ -25254,7 +25830,7 @@
         <v>20</v>
       </c>
       <c r="C1365">
-        <v>5090</v>
+        <v>5140</v>
       </c>
       <c r="D1365" t="s">
         <v>1367</v>
@@ -25268,7 +25844,7 @@
         <v>21</v>
       </c>
       <c r="C1366">
-        <v>5130</v>
+        <v>5160</v>
       </c>
       <c r="D1366" t="s">
         <v>1368</v>
@@ -25282,7 +25858,7 @@
         <v>22</v>
       </c>
       <c r="C1367">
-        <v>5180</v>
+        <v>5200</v>
       </c>
       <c r="D1367" t="s">
         <v>1369</v>
@@ -25310,7 +25886,7 @@
         <v>24</v>
       </c>
       <c r="C1369">
-        <v>5330</v>
+        <v>5320</v>
       </c>
       <c r="D1369" t="s">
         <v>1371</v>
@@ -25324,7 +25900,7 @@
         <v>25</v>
       </c>
       <c r="C1370">
-        <v>5410</v>
+        <v>5380</v>
       </c>
       <c r="D1370" t="s">
         <v>1372</v>
@@ -25338,7 +25914,7 @@
         <v>26</v>
       </c>
       <c r="C1371">
-        <v>5500</v>
+        <v>5470</v>
       </c>
       <c r="D1371" t="s">
         <v>1373</v>
@@ -25352,7 +25928,7 @@
         <v>27</v>
       </c>
       <c r="C1372">
-        <v>5590</v>
+        <v>5540</v>
       </c>
       <c r="D1372" t="s">
         <v>1374</v>
@@ -25366,7 +25942,7 @@
         <v>28</v>
       </c>
       <c r="C1373">
-        <v>5660</v>
+        <v>5630</v>
       </c>
       <c r="D1373" t="s">
         <v>1375</v>
@@ -25380,7 +25956,7 @@
         <v>29</v>
       </c>
       <c r="C1374">
-        <v>5720</v>
+        <v>5790</v>
       </c>
       <c r="D1374" t="s">
         <v>1376</v>
@@ -25394,7 +25970,7 @@
         <v>30</v>
       </c>
       <c r="C1375">
-        <v>5760</v>
+        <v>5830</v>
       </c>
       <c r="D1375" t="s">
         <v>1377</v>
@@ -25408,7 +25984,7 @@
         <v>31</v>
       </c>
       <c r="C1376">
-        <v>5780</v>
+        <v>5840</v>
       </c>
       <c r="D1376" t="s">
         <v>1378</v>
@@ -25422,7 +25998,7 @@
         <v>32</v>
       </c>
       <c r="C1377">
-        <v>5800</v>
+        <v>5810</v>
       </c>
       <c r="D1377" t="s">
         <v>1379</v>
@@ -25436,7 +26012,7 @@
         <v>33</v>
       </c>
       <c r="C1378">
-        <v>5750</v>
+        <v>5740</v>
       </c>
       <c r="D1378" t="s">
         <v>1380</v>
@@ -25450,7 +26026,7 @@
         <v>34</v>
       </c>
       <c r="C1379">
-        <v>5700</v>
+        <v>5660</v>
       </c>
       <c r="D1379" t="s">
         <v>1381</v>
@@ -25464,7 +26040,7 @@
         <v>35</v>
       </c>
       <c r="C1380">
-        <v>5630</v>
+        <v>5580</v>
       </c>
       <c r="D1380" t="s">
         <v>1382</v>
@@ -25478,7 +26054,7 @@
         <v>36</v>
       </c>
       <c r="C1381">
-        <v>5550</v>
+        <v>5480</v>
       </c>
       <c r="D1381" t="s">
         <v>1383</v>
@@ -25492,7 +26068,7 @@
         <v>37</v>
       </c>
       <c r="C1382">
-        <v>5460</v>
+        <v>5320</v>
       </c>
       <c r="D1382" t="s">
         <v>1384</v>
@@ -25506,7 +26082,7 @@
         <v>38</v>
       </c>
       <c r="C1383">
-        <v>5360</v>
+        <v>5180</v>
       </c>
       <c r="D1383" t="s">
         <v>1385</v>
@@ -25520,7 +26096,7 @@
         <v>39</v>
       </c>
       <c r="C1384">
-        <v>5260</v>
+        <v>5030</v>
       </c>
       <c r="D1384" t="s">
         <v>1386</v>
@@ -25534,7 +26110,7 @@
         <v>40</v>
       </c>
       <c r="C1385">
-        <v>5170</v>
+        <v>4900</v>
       </c>
       <c r="D1385" t="s">
         <v>1387</v>
@@ -25548,7 +26124,7 @@
         <v>41</v>
       </c>
       <c r="C1386">
-        <v>5080</v>
+        <v>4780</v>
       </c>
       <c r="D1386" t="s">
         <v>1388</v>
@@ -25562,7 +26138,7 @@
         <v>42</v>
       </c>
       <c r="C1387">
-        <v>4990</v>
+        <v>4650</v>
       </c>
       <c r="D1387" t="s">
         <v>1389</v>
@@ -25576,7 +26152,7 @@
         <v>43</v>
       </c>
       <c r="C1388">
-        <v>4910</v>
+        <v>4530</v>
       </c>
       <c r="D1388" t="s">
         <v>1390</v>
@@ -25590,7 +26166,7 @@
         <v>44</v>
       </c>
       <c r="C1389">
-        <v>4850</v>
+        <v>4420</v>
       </c>
       <c r="D1389" t="s">
         <v>1391</v>
@@ -25604,7 +26180,7 @@
         <v>45</v>
       </c>
       <c r="C1390">
-        <v>4780</v>
+        <v>4270</v>
       </c>
       <c r="D1390" t="s">
         <v>1392</v>
@@ -25618,7 +26194,7 @@
         <v>46</v>
       </c>
       <c r="C1391">
-        <v>4730</v>
+        <v>4170</v>
       </c>
       <c r="D1391" t="s">
         <v>1393</v>
@@ -25632,7 +26208,7 @@
         <v>47</v>
       </c>
       <c r="C1392">
-        <v>4680</v>
+        <v>4130</v>
       </c>
       <c r="D1392" t="s">
         <v>1394</v>
@@ -25646,7 +26222,7 @@
         <v>48</v>
       </c>
       <c r="C1393">
-        <v>4630</v>
+        <v>4110</v>
       </c>
       <c r="D1393" t="s">
         <v>1395</v>
@@ -25660,7 +26236,7 @@
         <v>49</v>
       </c>
       <c r="C1394">
-        <v>4590</v>
+        <v>4090</v>
       </c>
       <c r="D1394" t="s">
         <v>1396</v>
@@ -25674,7 +26250,7 @@
         <v>50</v>
       </c>
       <c r="C1395">
-        <v>4550</v>
+        <v>4080</v>
       </c>
       <c r="D1395" t="s">
         <v>1397</v>
@@ -25688,7 +26264,7 @@
         <v>51</v>
       </c>
       <c r="C1396">
-        <v>4510</v>
+        <v>4080</v>
       </c>
       <c r="D1396" t="s">
         <v>1398</v>
@@ -25702,7 +26278,7 @@
         <v>52</v>
       </c>
       <c r="C1397">
-        <v>4480</v>
+        <v>4070</v>
       </c>
       <c r="D1397" t="s">
         <v>1399</v>
@@ -25716,7 +26292,7 @@
         <v>53</v>
       </c>
       <c r="C1398">
-        <v>4450</v>
+        <v>4070</v>
       </c>
       <c r="D1398" t="s">
         <v>1400</v>
@@ -25730,7 +26306,7 @@
         <v>54</v>
       </c>
       <c r="C1399">
-        <v>4430</v>
+        <v>4080</v>
       </c>
       <c r="D1399" t="s">
         <v>1401</v>
@@ -25744,7 +26320,7 @@
         <v>55</v>
       </c>
       <c r="C1400">
-        <v>4420</v>
+        <v>4080</v>
       </c>
       <c r="D1400" t="s">
         <v>1402</v>
@@ -25758,7 +26334,7 @@
         <v>56</v>
       </c>
       <c r="C1401">
-        <v>4420</v>
+        <v>4080</v>
       </c>
       <c r="D1401" t="s">
         <v>1403</v>
@@ -25772,7 +26348,7 @@
         <v>57</v>
       </c>
       <c r="C1402">
-        <v>4430</v>
+        <v>4080</v>
       </c>
       <c r="D1402" t="s">
         <v>1404</v>
@@ -25786,7 +26362,7 @@
         <v>58</v>
       </c>
       <c r="C1403">
-        <v>4450</v>
+        <v>4100</v>
       </c>
       <c r="D1403" t="s">
         <v>1405</v>
@@ -25800,7 +26376,7 @@
         <v>59</v>
       </c>
       <c r="C1404">
-        <v>4480</v>
+        <v>4100</v>
       </c>
       <c r="D1404" t="s">
         <v>1406</v>
@@ -25814,7 +26390,7 @@
         <v>60</v>
       </c>
       <c r="C1405">
-        <v>4510</v>
+        <v>4120</v>
       </c>
       <c r="D1405" t="s">
         <v>1407</v>
@@ -25828,7 +26404,7 @@
         <v>61</v>
       </c>
       <c r="C1406">
-        <v>4550</v>
+        <v>4180</v>
       </c>
       <c r="D1406" t="s">
         <v>1408</v>
@@ -25842,7 +26418,7 @@
         <v>62</v>
       </c>
       <c r="C1407">
-        <v>4590</v>
+        <v>4220</v>
       </c>
       <c r="D1407" t="s">
         <v>1409</v>
@@ -25856,7 +26432,7 @@
         <v>63</v>
       </c>
       <c r="C1408">
-        <v>4640</v>
+        <v>4270</v>
       </c>
       <c r="D1408" t="s">
         <v>1410</v>
@@ -25870,7 +26446,7 @@
         <v>64</v>
       </c>
       <c r="C1409">
-        <v>4700</v>
+        <v>4330</v>
       </c>
       <c r="D1409" t="s">
         <v>1411</v>
@@ -25884,7 +26460,7 @@
         <v>65</v>
       </c>
       <c r="C1410">
-        <v>4770</v>
+        <v>4400</v>
       </c>
       <c r="D1410" t="s">
         <v>1412</v>
@@ -25898,7 +26474,7 @@
         <v>66</v>
       </c>
       <c r="C1411">
-        <v>4850</v>
+        <v>4490</v>
       </c>
       <c r="D1411" t="s">
         <v>1413</v>
@@ -25912,7 +26488,7 @@
         <v>67</v>
       </c>
       <c r="C1412">
-        <v>4940</v>
+        <v>4600</v>
       </c>
       <c r="D1412" t="s">
         <v>1414</v>
@@ -25926,7 +26502,7 @@
         <v>68</v>
       </c>
       <c r="C1413">
-        <v>5050</v>
+        <v>4710</v>
       </c>
       <c r="D1413" t="s">
         <v>1415</v>
@@ -25940,7 +26516,7 @@
         <v>69</v>
       </c>
       <c r="C1414">
-        <v>5160</v>
+        <v>4830</v>
       </c>
       <c r="D1414" t="s">
         <v>1416</v>
@@ -25954,7 +26530,7 @@
         <v>70</v>
       </c>
       <c r="C1415">
-        <v>5270</v>
+        <v>4960</v>
       </c>
       <c r="D1415" t="s">
         <v>1417</v>
@@ -25968,7 +26544,7 @@
         <v>71</v>
       </c>
       <c r="C1416">
-        <v>5380</v>
+        <v>5100</v>
       </c>
       <c r="D1416" t="s">
         <v>1418</v>
@@ -25982,7 +26558,7 @@
         <v>72</v>
       </c>
       <c r="C1417">
-        <v>5490</v>
+        <v>5240</v>
       </c>
       <c r="D1417" t="s">
         <v>1419</v>
@@ -25996,7 +26572,7 @@
         <v>73</v>
       </c>
       <c r="C1418">
-        <v>5610</v>
+        <v>5430</v>
       </c>
       <c r="D1418" t="s">
         <v>1420</v>
@@ -26010,7 +26586,7 @@
         <v>74</v>
       </c>
       <c r="C1419">
-        <v>5720</v>
+        <v>5580</v>
       </c>
       <c r="D1419" t="s">
         <v>1421</v>
@@ -26024,7 +26600,7 @@
         <v>75</v>
       </c>
       <c r="C1420">
-        <v>5850</v>
+        <v>5740</v>
       </c>
       <c r="D1420" t="s">
         <v>1422</v>
@@ -26038,7 +26614,7 @@
         <v>76</v>
       </c>
       <c r="C1421">
-        <v>5980</v>
+        <v>5890</v>
       </c>
       <c r="D1421" t="s">
         <v>1423</v>
@@ -26052,7 +26628,7 @@
         <v>77</v>
       </c>
       <c r="C1422">
-        <v>6120</v>
+        <v>6040</v>
       </c>
       <c r="D1422" t="s">
         <v>1424</v>
@@ -26066,7 +26642,7 @@
         <v>78</v>
       </c>
       <c r="C1423">
-        <v>6260</v>
+        <v>6180</v>
       </c>
       <c r="D1423" t="s">
         <v>1425</v>
@@ -26080,7 +26656,7 @@
         <v>79</v>
       </c>
       <c r="C1424">
-        <v>6390</v>
+        <v>6280</v>
       </c>
       <c r="D1424" t="s">
         <v>1426</v>
@@ -26094,7 +26670,7 @@
         <v>80</v>
       </c>
       <c r="C1425">
-        <v>6490</v>
+        <v>6380</v>
       </c>
       <c r="D1425" t="s">
         <v>1427</v>
@@ -26108,7 +26684,7 @@
         <v>81</v>
       </c>
       <c r="C1426">
-        <v>6600</v>
+        <v>6460</v>
       </c>
       <c r="D1426" t="s">
         <v>1428</v>
@@ -26122,7 +26698,7 @@
         <v>82</v>
       </c>
       <c r="C1427">
-        <v>6660</v>
+        <v>6540</v>
       </c>
       <c r="D1427" t="s">
         <v>1429</v>
@@ -26136,7 +26712,7 @@
         <v>83</v>
       </c>
       <c r="C1428">
-        <v>6720</v>
+        <v>6620</v>
       </c>
       <c r="D1428" t="s">
         <v>1430</v>
@@ -26150,7 +26726,7 @@
         <v>84</v>
       </c>
       <c r="C1429">
-        <v>6750</v>
+        <v>6700</v>
       </c>
       <c r="D1429" t="s">
         <v>1431</v>
@@ -26164,7 +26740,7 @@
         <v>85</v>
       </c>
       <c r="C1430">
-        <v>6750</v>
+        <v>6760</v>
       </c>
       <c r="D1430" t="s">
         <v>1432</v>
@@ -26178,7 +26754,7 @@
         <v>86</v>
       </c>
       <c r="C1431">
-        <v>6750</v>
+        <v>6760</v>
       </c>
       <c r="D1431" t="s">
         <v>1433</v>
@@ -26192,7 +26768,7 @@
         <v>87</v>
       </c>
       <c r="C1432">
-        <v>6720</v>
+        <v>6750</v>
       </c>
       <c r="D1432" t="s">
         <v>1434</v>
@@ -26206,7 +26782,7 @@
         <v>88</v>
       </c>
       <c r="C1433">
-        <v>6650</v>
+        <v>6690</v>
       </c>
       <c r="D1433" t="s">
         <v>1435</v>
@@ -26234,7 +26810,7 @@
         <v>90</v>
       </c>
       <c r="C1435">
-        <v>6430</v>
+        <v>6400</v>
       </c>
       <c r="D1435" t="s">
         <v>1437</v>
@@ -26248,7 +26824,7 @@
         <v>91</v>
       </c>
       <c r="C1436">
-        <v>6270</v>
+        <v>6250</v>
       </c>
       <c r="D1436" t="s">
         <v>1438</v>
@@ -26262,7 +26838,7 @@
         <v>92</v>
       </c>
       <c r="C1437">
-        <v>6140</v>
+        <v>6110</v>
       </c>
       <c r="D1437" t="s">
         <v>1439</v>
@@ -26276,7 +26852,7 @@
         <v>93</v>
       </c>
       <c r="C1438">
-        <v>5980</v>
+        <v>5950</v>
       </c>
       <c r="D1438" t="s">
         <v>1440</v>
@@ -26290,7 +26866,7 @@
         <v>94</v>
       </c>
       <c r="C1439">
-        <v>5820</v>
+        <v>5810</v>
       </c>
       <c r="D1439" t="s">
         <v>1441</v>
@@ -26304,7 +26880,7 @@
         <v>95</v>
       </c>
       <c r="C1440">
-        <v>5730</v>
+        <v>5700</v>
       </c>
       <c r="D1440" t="s">
         <v>1442</v>
@@ -26318,7 +26894,7 @@
         <v>96</v>
       </c>
       <c r="C1441">
-        <v>5620</v>
+        <v>5590</v>
       </c>
       <c r="D1441" t="s">
         <v>1443</v>
@@ -26332,7 +26908,7 @@
         <v>1</v>
       </c>
       <c r="C1442">
-        <v>5570</v>
+        <v>5480</v>
       </c>
       <c r="D1442" t="s">
         <v>1444</v>
@@ -26346,7 +26922,7 @@
         <v>2</v>
       </c>
       <c r="C1443">
-        <v>5490</v>
+        <v>5440</v>
       </c>
       <c r="D1443" t="s">
         <v>1445</v>
@@ -26360,7 +26936,7 @@
         <v>3</v>
       </c>
       <c r="C1444">
-        <v>5400</v>
+        <v>5380</v>
       </c>
       <c r="D1444" t="s">
         <v>1446</v>
@@ -26374,7 +26950,7 @@
         <v>4</v>
       </c>
       <c r="C1445">
-        <v>5330</v>
+        <v>5300</v>
       </c>
       <c r="D1445" t="s">
         <v>1447</v>
@@ -26388,7 +26964,7 @@
         <v>5</v>
       </c>
       <c r="C1446">
-        <v>5250</v>
+        <v>5240</v>
       </c>
       <c r="D1446" t="s">
         <v>1448</v>
@@ -26416,7 +26992,7 @@
         <v>7</v>
       </c>
       <c r="C1448">
-        <v>5150</v>
+        <v>5140</v>
       </c>
       <c r="D1448" t="s">
         <v>1450</v>
@@ -26430,7 +27006,7 @@
         <v>8</v>
       </c>
       <c r="C1449">
-        <v>5110</v>
+        <v>5100</v>
       </c>
       <c r="D1449" t="s">
         <v>1451</v>
@@ -26444,7 +27020,7 @@
         <v>9</v>
       </c>
       <c r="C1450">
-        <v>5090</v>
+        <v>5060</v>
       </c>
       <c r="D1450" t="s">
         <v>1452</v>
@@ -26458,7 +27034,7 @@
         <v>10</v>
       </c>
       <c r="C1451">
-        <v>5070</v>
+        <v>5030</v>
       </c>
       <c r="D1451" t="s">
         <v>1453</v>
@@ -26472,7 +27048,7 @@
         <v>11</v>
       </c>
       <c r="C1452">
-        <v>5050</v>
+        <v>5000</v>
       </c>
       <c r="D1452" t="s">
         <v>1454</v>
@@ -26486,7 +27062,7 @@
         <v>12</v>
       </c>
       <c r="C1453">
-        <v>5040</v>
+        <v>4990</v>
       </c>
       <c r="D1453" t="s">
         <v>1455</v>
@@ -26500,7 +27076,7 @@
         <v>13</v>
       </c>
       <c r="C1454">
-        <v>5040</v>
+        <v>4980</v>
       </c>
       <c r="D1454" t="s">
         <v>1456</v>
@@ -26514,7 +27090,7 @@
         <v>14</v>
       </c>
       <c r="C1455">
-        <v>5030</v>
+        <v>4970</v>
       </c>
       <c r="D1455" t="s">
         <v>1457</v>
@@ -26528,7 +27104,7 @@
         <v>15</v>
       </c>
       <c r="C1456">
-        <v>5030</v>
+        <v>4970</v>
       </c>
       <c r="D1456" t="s">
         <v>1458</v>
@@ -26542,7 +27118,7 @@
         <v>16</v>
       </c>
       <c r="C1457">
-        <v>5020</v>
+        <v>4960</v>
       </c>
       <c r="D1457" t="s">
         <v>1459</v>
@@ -26556,7 +27132,7 @@
         <v>17</v>
       </c>
       <c r="C1458">
-        <v>5010</v>
+        <v>4960</v>
       </c>
       <c r="D1458" t="s">
         <v>1460</v>
@@ -26570,7 +27146,7 @@
         <v>18</v>
       </c>
       <c r="C1459">
-        <v>5020</v>
+        <v>4950</v>
       </c>
       <c r="D1459" t="s">
         <v>1461</v>
@@ -26584,7 +27160,7 @@
         <v>19</v>
       </c>
       <c r="C1460">
-        <v>5030</v>
+        <v>4950</v>
       </c>
       <c r="D1460" t="s">
         <v>1462</v>
@@ -26598,7 +27174,7 @@
         <v>20</v>
       </c>
       <c r="C1461">
-        <v>5040</v>
+        <v>4950</v>
       </c>
       <c r="D1461" t="s">
         <v>1463</v>
@@ -26612,7 +27188,7 @@
         <v>21</v>
       </c>
       <c r="C1462">
-        <v>5070</v>
+        <v>4950</v>
       </c>
       <c r="D1462" t="s">
         <v>1464</v>
@@ -26626,7 +27202,7 @@
         <v>22</v>
       </c>
       <c r="C1463">
-        <v>5080</v>
+        <v>4950</v>
       </c>
       <c r="D1463" t="s">
         <v>1465</v>
@@ -26640,7 +27216,7 @@
         <v>23</v>
       </c>
       <c r="C1464">
-        <v>5070</v>
+        <v>4950</v>
       </c>
       <c r="D1464" t="s">
         <v>1466</v>
@@ -26654,7 +27230,7 @@
         <v>24</v>
       </c>
       <c r="C1465">
-        <v>5050</v>
+        <v>4970</v>
       </c>
       <c r="D1465" t="s">
         <v>1467</v>
@@ -26668,7 +27244,7 @@
         <v>25</v>
       </c>
       <c r="C1466">
-        <v>5020</v>
+        <v>4980</v>
       </c>
       <c r="D1466" t="s">
         <v>1468</v>
@@ -26682,7 +27258,7 @@
         <v>26</v>
       </c>
       <c r="C1467">
-        <v>5000</v>
+        <v>4990</v>
       </c>
       <c r="D1467" t="s">
         <v>1469</v>
@@ -26710,7 +27286,7 @@
         <v>28</v>
       </c>
       <c r="C1469">
-        <v>5020</v>
+        <v>5000</v>
       </c>
       <c r="D1469" t="s">
         <v>1471</v>
@@ -26724,7 +27300,7 @@
         <v>29</v>
       </c>
       <c r="C1470">
-        <v>5060</v>
+        <v>5000</v>
       </c>
       <c r="D1470" t="s">
         <v>1472</v>
@@ -26738,7 +27314,7 @@
         <v>30</v>
       </c>
       <c r="C1471">
-        <v>5090</v>
+        <v>4980</v>
       </c>
       <c r="D1471" t="s">
         <v>1473</v>
@@ -26752,7 +27328,7 @@
         <v>31</v>
       </c>
       <c r="C1472">
-        <v>5120</v>
+        <v>4950</v>
       </c>
       <c r="D1472" t="s">
         <v>1474</v>
@@ -26766,7 +27342,7 @@
         <v>32</v>
       </c>
       <c r="C1473">
-        <v>5130</v>
+        <v>4920</v>
       </c>
       <c r="D1473" t="s">
         <v>1475</v>
@@ -26780,7 +27356,7 @@
         <v>33</v>
       </c>
       <c r="C1474">
-        <v>5130</v>
+        <v>4870</v>
       </c>
       <c r="D1474" t="s">
         <v>1476</v>
@@ -26794,7 +27370,7 @@
         <v>34</v>
       </c>
       <c r="C1475">
-        <v>5110</v>
+        <v>4800</v>
       </c>
       <c r="D1475" t="s">
         <v>1477</v>
@@ -26808,7 +27384,7 @@
         <v>35</v>
       </c>
       <c r="C1476">
-        <v>5070</v>
+        <v>4730</v>
       </c>
       <c r="D1476" t="s">
         <v>1478</v>
@@ -26822,7 +27398,7 @@
         <v>36</v>
       </c>
       <c r="C1477">
-        <v>5020</v>
+        <v>4650</v>
       </c>
       <c r="D1477" t="s">
         <v>1479</v>
@@ -26836,7 +27412,7 @@
         <v>37</v>
       </c>
       <c r="C1478">
-        <v>4950</v>
+        <v>4560</v>
       </c>
       <c r="D1478" t="s">
         <v>1480</v>
@@ -26850,7 +27426,7 @@
         <v>38</v>
       </c>
       <c r="C1479">
-        <v>4880</v>
+        <v>4470</v>
       </c>
       <c r="D1479" t="s">
         <v>1481</v>
@@ -26864,7 +27440,7 @@
         <v>39</v>
       </c>
       <c r="C1480">
-        <v>4810</v>
+        <v>4370</v>
       </c>
       <c r="D1480" t="s">
         <v>1482</v>
@@ -26878,7 +27454,7 @@
         <v>40</v>
       </c>
       <c r="C1481">
-        <v>4750</v>
+        <v>4280</v>
       </c>
       <c r="D1481" t="s">
         <v>1483</v>
@@ -26892,7 +27468,7 @@
         <v>41</v>
       </c>
       <c r="C1482">
-        <v>4690</v>
+        <v>4190</v>
       </c>
       <c r="D1482" t="s">
         <v>1484</v>
@@ -26906,7 +27482,7 @@
         <v>42</v>
       </c>
       <c r="C1483">
-        <v>4610</v>
+        <v>4110</v>
       </c>
       <c r="D1483" t="s">
         <v>1485</v>
@@ -26920,7 +27496,7 @@
         <v>43</v>
       </c>
       <c r="C1484">
-        <v>4530</v>
+        <v>4040</v>
       </c>
       <c r="D1484" t="s">
         <v>1486</v>
@@ -26934,7 +27510,7 @@
         <v>44</v>
       </c>
       <c r="C1485">
-        <v>4440</v>
+        <v>3980</v>
       </c>
       <c r="D1485" t="s">
         <v>1487</v>
@@ -26948,7 +27524,7 @@
         <v>45</v>
       </c>
       <c r="C1486">
-        <v>4340</v>
+        <v>3930</v>
       </c>
       <c r="D1486" t="s">
         <v>1488</v>
@@ -26962,7 +27538,7 @@
         <v>46</v>
       </c>
       <c r="C1487">
-        <v>4260</v>
+        <v>3890</v>
       </c>
       <c r="D1487" t="s">
         <v>1489</v>
@@ -26976,7 +27552,7 @@
         <v>47</v>
       </c>
       <c r="C1488">
-        <v>4190</v>
+        <v>3860</v>
       </c>
       <c r="D1488" t="s">
         <v>1490</v>
@@ -26990,7 +27566,7 @@
         <v>48</v>
       </c>
       <c r="C1489">
-        <v>4140</v>
+        <v>3830</v>
       </c>
       <c r="D1489" t="s">
         <v>1491</v>
@@ -27004,7 +27580,7 @@
         <v>49</v>
       </c>
       <c r="C1490">
-        <v>4110</v>
+        <v>3810</v>
       </c>
       <c r="D1490" t="s">
         <v>1492</v>
@@ -27018,7 +27594,7 @@
         <v>50</v>
       </c>
       <c r="C1491">
-        <v>4090</v>
+        <v>3790</v>
       </c>
       <c r="D1491" t="s">
         <v>1493</v>
@@ -27032,7 +27608,7 @@
         <v>51</v>
       </c>
       <c r="C1492">
-        <v>4070</v>
+        <v>3770</v>
       </c>
       <c r="D1492" t="s">
         <v>1494</v>
@@ -27046,7 +27622,7 @@
         <v>52</v>
       </c>
       <c r="C1493">
-        <v>4060</v>
+        <v>3760</v>
       </c>
       <c r="D1493" t="s">
         <v>1495</v>
@@ -27060,7 +27636,7 @@
         <v>53</v>
       </c>
       <c r="C1494">
-        <v>4040</v>
+        <v>3750</v>
       </c>
       <c r="D1494" t="s">
         <v>1496</v>
@@ -27074,7 +27650,7 @@
         <v>54</v>
       </c>
       <c r="C1495">
-        <v>4030</v>
+        <v>3740</v>
       </c>
       <c r="D1495" t="s">
         <v>1497</v>
@@ -27088,7 +27664,7 @@
         <v>55</v>
       </c>
       <c r="C1496">
-        <v>4010</v>
+        <v>3740</v>
       </c>
       <c r="D1496" t="s">
         <v>1498</v>
@@ -27102,7 +27678,7 @@
         <v>56</v>
       </c>
       <c r="C1497">
-        <v>3980</v>
+        <v>3750</v>
       </c>
       <c r="D1497" t="s">
         <v>1499</v>
@@ -27116,7 +27692,7 @@
         <v>57</v>
       </c>
       <c r="C1498">
-        <v>3960</v>
+        <v>3780</v>
       </c>
       <c r="D1498" t="s">
         <v>1500</v>
@@ -27130,7 +27706,7 @@
         <v>58</v>
       </c>
       <c r="C1499">
-        <v>3960</v>
+        <v>3810</v>
       </c>
       <c r="D1499" t="s">
         <v>1501</v>
@@ -27144,7 +27720,7 @@
         <v>59</v>
       </c>
       <c r="C1500">
-        <v>4010</v>
+        <v>3850</v>
       </c>
       <c r="D1500" t="s">
         <v>1502</v>
@@ -27158,7 +27734,7 @@
         <v>60</v>
       </c>
       <c r="C1501">
-        <v>4090</v>
+        <v>3900</v>
       </c>
       <c r="D1501" t="s">
         <v>1503</v>
@@ -27172,7 +27748,7 @@
         <v>61</v>
       </c>
       <c r="C1502">
-        <v>4190</v>
+        <v>3960</v>
       </c>
       <c r="D1502" t="s">
         <v>1504</v>
@@ -27186,7 +27762,7 @@
         <v>62</v>
       </c>
       <c r="C1503">
-        <v>4300</v>
+        <v>4020</v>
       </c>
       <c r="D1503" t="s">
         <v>1505</v>
@@ -27200,7 +27776,7 @@
         <v>63</v>
       </c>
       <c r="C1504">
-        <v>4390</v>
+        <v>4090</v>
       </c>
       <c r="D1504" t="s">
         <v>1506</v>
@@ -27214,7 +27790,7 @@
         <v>64</v>
       </c>
       <c r="C1505">
-        <v>4470</v>
+        <v>4180</v>
       </c>
       <c r="D1505" t="s">
         <v>1507</v>
@@ -27228,7 +27804,7 @@
         <v>65</v>
       </c>
       <c r="C1506">
-        <v>4540</v>
+        <v>4270</v>
       </c>
       <c r="D1506" t="s">
         <v>1508</v>
@@ -27242,7 +27818,7 @@
         <v>66</v>
       </c>
       <c r="C1507">
-        <v>4620</v>
+        <v>4380</v>
       </c>
       <c r="D1507" t="s">
         <v>1509</v>
@@ -27256,7 +27832,7 @@
         <v>67</v>
       </c>
       <c r="C1508">
-        <v>4710</v>
+        <v>4490</v>
       </c>
       <c r="D1508" t="s">
         <v>1510</v>
@@ -27270,7 +27846,7 @@
         <v>68</v>
       </c>
       <c r="C1509">
-        <v>4820</v>
+        <v>4620</v>
       </c>
       <c r="D1509" t="s">
         <v>1511</v>
@@ -27284,7 +27860,7 @@
         <v>69</v>
       </c>
       <c r="C1510">
-        <v>4940</v>
+        <v>4760</v>
       </c>
       <c r="D1510" t="s">
         <v>1512</v>
@@ -27298,7 +27874,7 @@
         <v>70</v>
       </c>
       <c r="C1511">
-        <v>5050</v>
+        <v>4900</v>
       </c>
       <c r="D1511" t="s">
         <v>1513</v>
@@ -27312,7 +27888,7 @@
         <v>71</v>
       </c>
       <c r="C1512">
-        <v>5160</v>
+        <v>5040</v>
       </c>
       <c r="D1512" t="s">
         <v>1514</v>
@@ -27326,7 +27902,7 @@
         <v>72</v>
       </c>
       <c r="C1513">
-        <v>5260</v>
+        <v>5170</v>
       </c>
       <c r="D1513" t="s">
         <v>1515</v>
@@ -27340,7 +27916,7 @@
         <v>73</v>
       </c>
       <c r="C1514">
-        <v>5360</v>
+        <v>5300</v>
       </c>
       <c r="D1514" t="s">
         <v>1516</v>
@@ -27354,7 +27930,7 @@
         <v>74</v>
       </c>
       <c r="C1515">
-        <v>5470</v>
+        <v>5420</v>
       </c>
       <c r="D1515" t="s">
         <v>1517</v>
@@ -27368,7 +27944,7 @@
         <v>75</v>
       </c>
       <c r="C1516">
-        <v>5580</v>
+        <v>5540</v>
       </c>
       <c r="D1516" t="s">
         <v>1518</v>
@@ -27382,7 +27958,7 @@
         <v>76</v>
       </c>
       <c r="C1517">
-        <v>5690</v>
+        <v>5670</v>
       </c>
       <c r="D1517" t="s">
         <v>1519</v>
@@ -27396,7 +27972,7 @@
         <v>77</v>
       </c>
       <c r="C1518">
-        <v>5800</v>
+        <v>5790</v>
       </c>
       <c r="D1518" t="s">
         <v>1520</v>
@@ -27410,7 +27986,7 @@
         <v>78</v>
       </c>
       <c r="C1519">
-        <v>5900</v>
+        <v>5920</v>
       </c>
       <c r="D1519" t="s">
         <v>1521</v>
@@ -27424,7 +28000,7 @@
         <v>79</v>
       </c>
       <c r="C1520">
-        <v>5980</v>
+        <v>6030</v>
       </c>
       <c r="D1520" t="s">
         <v>1522</v>
@@ -27438,7 +28014,7 @@
         <v>80</v>
       </c>
       <c r="C1521">
-        <v>6060</v>
+        <v>6130</v>
       </c>
       <c r="D1521" t="s">
         <v>1523</v>
@@ -27452,7 +28028,7 @@
         <v>81</v>
       </c>
       <c r="C1522">
-        <v>6120</v>
+        <v>6230</v>
       </c>
       <c r="D1522" t="s">
         <v>1524</v>
@@ -27466,7 +28042,7 @@
         <v>82</v>
       </c>
       <c r="C1523">
-        <v>6180</v>
+        <v>6330</v>
       </c>
       <c r="D1523" t="s">
         <v>1525</v>
@@ -27480,7 +28056,7 @@
         <v>83</v>
       </c>
       <c r="C1524">
-        <v>6260</v>
+        <v>6390</v>
       </c>
       <c r="D1524" t="s">
         <v>1526</v>
@@ -27494,7 +28070,7 @@
         <v>84</v>
       </c>
       <c r="C1525">
-        <v>6340</v>
+        <v>6400</v>
       </c>
       <c r="D1525" t="s">
         <v>1527</v>
@@ -27508,7 +28084,7 @@
         <v>85</v>
       </c>
       <c r="C1526">
-        <v>6430</v>
+        <v>6400</v>
       </c>
       <c r="D1526" t="s">
         <v>1528</v>
@@ -27522,7 +28098,7 @@
         <v>86</v>
       </c>
       <c r="C1527">
-        <v>6460</v>
+        <v>6400</v>
       </c>
       <c r="D1527" t="s">
         <v>1529</v>
@@ -27536,7 +28112,7 @@
         <v>87</v>
       </c>
       <c r="C1528">
-        <v>6440</v>
+        <v>6380</v>
       </c>
       <c r="D1528" t="s">
         <v>1530</v>
@@ -27550,7 +28126,7 @@
         <v>88</v>
       </c>
       <c r="C1529">
-        <v>6360</v>
+        <v>6320</v>
       </c>
       <c r="D1529" t="s">
         <v>1531</v>
@@ -27564,7 +28140,7 @@
         <v>89</v>
       </c>
       <c r="C1530">
-        <v>6230</v>
+        <v>6200</v>
       </c>
       <c r="D1530" t="s">
         <v>1532</v>
@@ -27578,7 +28154,7 @@
         <v>90</v>
       </c>
       <c r="C1531">
-        <v>6090</v>
+        <v>6100</v>
       </c>
       <c r="D1531" t="s">
         <v>1533</v>
@@ -27606,7 +28182,7 @@
         <v>92</v>
       </c>
       <c r="C1533">
-        <v>5820</v>
+        <v>5830</v>
       </c>
       <c r="D1533" t="s">
         <v>1535</v>
@@ -27620,7 +28196,7 @@
         <v>93</v>
       </c>
       <c r="C1534">
-        <v>5680</v>
+        <v>5690</v>
       </c>
       <c r="D1534" t="s">
         <v>1536</v>
@@ -27634,7 +28210,7 @@
         <v>94</v>
       </c>
       <c r="C1535">
-        <v>5560</v>
+        <v>5540</v>
       </c>
       <c r="D1535" t="s">
         <v>1537</v>
@@ -27648,7 +28224,7 @@
         <v>95</v>
       </c>
       <c r="C1536">
-        <v>5460</v>
+        <v>5450</v>
       </c>
       <c r="D1536" t="s">
         <v>1538</v>
@@ -27662,7 +28238,7 @@
         <v>96</v>
       </c>
       <c r="C1537">
-        <v>5360</v>
+        <v>5340</v>
       </c>
       <c r="D1537" t="s">
         <v>1539</v>
@@ -27676,7 +28252,7 @@
         <v>1</v>
       </c>
       <c r="C1538">
-        <v>5280</v>
+        <v>5210</v>
       </c>
       <c r="D1538" t="s">
         <v>1540</v>
@@ -27690,7 +28266,7 @@
         <v>2</v>
       </c>
       <c r="C1539">
-        <v>5200</v>
+        <v>5140</v>
       </c>
       <c r="D1539" t="s">
         <v>1541</v>
@@ -27704,7 +28280,7 @@
         <v>3</v>
       </c>
       <c r="C1540">
-        <v>5130</v>
+        <v>5110</v>
       </c>
       <c r="D1540" t="s">
         <v>1542</v>
@@ -27718,7 +28294,7 @@
         <v>4</v>
       </c>
       <c r="C1541">
-        <v>5050</v>
+        <v>5040</v>
       </c>
       <c r="D1541" t="s">
         <v>1543</v>
@@ -27732,7 +28308,7 @@
         <v>5</v>
       </c>
       <c r="C1542">
-        <v>4990</v>
+        <v>4960</v>
       </c>
       <c r="D1542" t="s">
         <v>1544</v>
@@ -27746,7 +28322,7 @@
         <v>6</v>
       </c>
       <c r="C1543">
-        <v>4930</v>
+        <v>4900</v>
       </c>
       <c r="D1543" t="s">
         <v>1545</v>
@@ -27760,7 +28336,7 @@
         <v>7</v>
       </c>
       <c r="C1544">
-        <v>4880</v>
+        <v>4850</v>
       </c>
       <c r="D1544" t="s">
         <v>1546</v>
@@ -27774,7 +28350,7 @@
         <v>8</v>
       </c>
       <c r="C1545">
-        <v>4850</v>
+        <v>4810</v>
       </c>
       <c r="D1545" t="s">
         <v>1547</v>
@@ -27788,7 +28364,7 @@
         <v>9</v>
       </c>
       <c r="C1546">
-        <v>4820</v>
+        <v>4790</v>
       </c>
       <c r="D1546" t="s">
         <v>1548</v>
@@ -27802,7 +28378,7 @@
         <v>10</v>
       </c>
       <c r="C1547">
-        <v>4800</v>
+        <v>4770</v>
       </c>
       <c r="D1547" t="s">
         <v>1549</v>
@@ -27816,7 +28392,7 @@
         <v>11</v>
       </c>
       <c r="C1548">
-        <v>4770</v>
+        <v>4760</v>
       </c>
       <c r="D1548" t="s">
         <v>1550</v>
@@ -27844,7 +28420,7 @@
         <v>13</v>
       </c>
       <c r="C1550">
-        <v>4720</v>
+        <v>4730</v>
       </c>
       <c r="D1550" t="s">
         <v>1552</v>
@@ -27858,7 +28434,7 @@
         <v>14</v>
       </c>
       <c r="C1551">
-        <v>4700</v>
+        <v>4710</v>
       </c>
       <c r="D1551" t="s">
         <v>1553</v>
@@ -27886,7 +28462,7 @@
         <v>16</v>
       </c>
       <c r="C1553">
-        <v>4690</v>
+        <v>4680</v>
       </c>
       <c r="D1553" t="s">
         <v>1555</v>
@@ -27900,7 +28476,7 @@
         <v>17</v>
       </c>
       <c r="C1554">
-        <v>4690</v>
+        <v>4670</v>
       </c>
       <c r="D1554" t="s">
         <v>1556</v>
@@ -27914,7 +28490,7 @@
         <v>18</v>
       </c>
       <c r="C1555">
-        <v>4700</v>
+        <v>4660</v>
       </c>
       <c r="D1555" t="s">
         <v>1557</v>
@@ -27928,7 +28504,7 @@
         <v>19</v>
       </c>
       <c r="C1556">
-        <v>4690</v>
+        <v>4650</v>
       </c>
       <c r="D1556" t="s">
         <v>1558</v>
@@ -27942,7 +28518,7 @@
         <v>20</v>
       </c>
       <c r="C1557">
-        <v>4680</v>
+        <v>4650</v>
       </c>
       <c r="D1557" t="s">
         <v>1559</v>
@@ -27956,7 +28532,7 @@
         <v>21</v>
       </c>
       <c r="C1558">
-        <v>4670</v>
+        <v>4640</v>
       </c>
       <c r="D1558" t="s">
         <v>1560</v>
@@ -27970,7 +28546,7 @@
         <v>22</v>
       </c>
       <c r="C1559">
-        <v>4650</v>
+        <v>4640</v>
       </c>
       <c r="D1559" t="s">
         <v>1561</v>
@@ -27984,7 +28560,7 @@
         <v>23</v>
       </c>
       <c r="C1560">
-        <v>4640</v>
+        <v>4630</v>
       </c>
       <c r="D1560" t="s">
         <v>1562</v>
@@ -28026,7 +28602,7 @@
         <v>26</v>
       </c>
       <c r="C1563">
-        <v>4590</v>
+        <v>4610</v>
       </c>
       <c r="D1563" t="s">
         <v>1565</v>
@@ -28040,7 +28616,7 @@
         <v>27</v>
       </c>
       <c r="C1564">
-        <v>4590</v>
+        <v>4610</v>
       </c>
       <c r="D1564" t="s">
         <v>1566</v>
@@ -28054,7 +28630,7 @@
         <v>28</v>
       </c>
       <c r="C1565">
-        <v>4580</v>
+        <v>4620</v>
       </c>
       <c r="D1565" t="s">
         <v>1567</v>
@@ -28068,7 +28644,7 @@
         <v>29</v>
       </c>
       <c r="C1566">
-        <v>4580</v>
+        <v>4630</v>
       </c>
       <c r="D1566" t="s">
         <v>1568</v>
@@ -28082,7 +28658,7 @@
         <v>30</v>
       </c>
       <c r="C1567">
-        <v>4590</v>
+        <v>4660</v>
       </c>
       <c r="D1567" t="s">
         <v>1569</v>
@@ -28096,7 +28672,7 @@
         <v>31</v>
       </c>
       <c r="C1568">
-        <v>4590</v>
+        <v>4690</v>
       </c>
       <c r="D1568" t="s">
         <v>1570</v>
@@ -28110,7 +28686,7 @@
         <v>32</v>
       </c>
       <c r="C1569">
-        <v>4590</v>
+        <v>4730</v>
       </c>
       <c r="D1569" t="s">
         <v>1571</v>
@@ -28124,7 +28700,7 @@
         <v>33</v>
       </c>
       <c r="C1570">
-        <v>4580</v>
+        <v>4760</v>
       </c>
       <c r="D1570" t="s">
         <v>1572</v>
@@ -28138,7 +28714,7 @@
         <v>34</v>
       </c>
       <c r="C1571">
-        <v>4570</v>
+        <v>4820</v>
       </c>
       <c r="D1571" t="s">
         <v>1573</v>
@@ -28152,7 +28728,7 @@
         <v>35</v>
       </c>
       <c r="C1572">
-        <v>4540</v>
+        <v>4850</v>
       </c>
       <c r="D1572" t="s">
         <v>1574</v>
@@ -28166,7 +28742,7 @@
         <v>36</v>
       </c>
       <c r="C1573">
-        <v>4490</v>
+        <v>4840</v>
       </c>
       <c r="D1573" t="s">
         <v>1575</v>
@@ -28180,7 +28756,7 @@
         <v>37</v>
       </c>
       <c r="C1574">
-        <v>4430</v>
+        <v>4830</v>
       </c>
       <c r="D1574" t="s">
         <v>1576</v>
@@ -28194,7 +28770,7 @@
         <v>38</v>
       </c>
       <c r="C1575">
-        <v>4370</v>
+        <v>4820</v>
       </c>
       <c r="D1575" t="s">
         <v>1577</v>
@@ -28208,7 +28784,7 @@
         <v>39</v>
       </c>
       <c r="C1576">
-        <v>4310</v>
+        <v>4790</v>
       </c>
       <c r="D1576" t="s">
         <v>1578</v>
@@ -28222,7 +28798,7 @@
         <v>40</v>
       </c>
       <c r="C1577">
-        <v>4260</v>
+        <v>4750</v>
       </c>
       <c r="D1577" t="s">
         <v>1579</v>
@@ -28236,7 +28812,7 @@
         <v>41</v>
       </c>
       <c r="C1578">
-        <v>4210</v>
+        <v>4700</v>
       </c>
       <c r="D1578" t="s">
         <v>1580</v>
@@ -28250,7 +28826,7 @@
         <v>42</v>
       </c>
       <c r="C1579">
-        <v>4160</v>
+        <v>4660</v>
       </c>
       <c r="D1579" t="s">
         <v>1581</v>
@@ -28264,7 +28840,7 @@
         <v>43</v>
       </c>
       <c r="C1580">
-        <v>4100</v>
+        <v>4610</v>
       </c>
       <c r="D1580" t="s">
         <v>1582</v>
@@ -28278,7 +28854,7 @@
         <v>44</v>
       </c>
       <c r="C1581">
-        <v>4030</v>
+        <v>4570</v>
       </c>
       <c r="D1581" t="s">
         <v>1583</v>
@@ -28292,7 +28868,7 @@
         <v>45</v>
       </c>
       <c r="C1582">
-        <v>3970</v>
+        <v>4530</v>
       </c>
       <c r="D1582" t="s">
         <v>1584</v>
@@ -28306,7 +28882,7 @@
         <v>46</v>
       </c>
       <c r="C1583">
-        <v>3910</v>
+        <v>4500</v>
       </c>
       <c r="D1583" t="s">
         <v>1585</v>
@@ -28320,7 +28896,7 @@
         <v>47</v>
       </c>
       <c r="C1584">
-        <v>3860</v>
+        <v>4480</v>
       </c>
       <c r="D1584" t="s">
         <v>1586</v>
@@ -28334,7 +28910,7 @@
         <v>48</v>
       </c>
       <c r="C1585">
-        <v>3830</v>
+        <v>4460</v>
       </c>
       <c r="D1585" t="s">
         <v>1587</v>
@@ -28348,7 +28924,7 @@
         <v>49</v>
       </c>
       <c r="C1586">
-        <v>3810</v>
+        <v>4450</v>
       </c>
       <c r="D1586" t="s">
         <v>1588</v>
@@ -28362,7 +28938,7 @@
         <v>50</v>
       </c>
       <c r="C1587">
-        <v>3790</v>
+        <v>4440</v>
       </c>
       <c r="D1587" t="s">
         <v>1589</v>
@@ -28376,7 +28952,7 @@
         <v>51</v>
       </c>
       <c r="C1588">
-        <v>3780</v>
+        <v>4430</v>
       </c>
       <c r="D1588" t="s">
         <v>1590</v>
@@ -28390,7 +28966,7 @@
         <v>52</v>
       </c>
       <c r="C1589">
-        <v>3780</v>
+        <v>4420</v>
       </c>
       <c r="D1589" t="s">
         <v>1591</v>
@@ -28404,7 +28980,7 @@
         <v>53</v>
       </c>
       <c r="C1590">
-        <v>3780</v>
+        <v>4410</v>
       </c>
       <c r="D1590" t="s">
         <v>1592</v>
@@ -28418,7 +28994,7 @@
         <v>54</v>
       </c>
       <c r="C1591">
-        <v>3780</v>
+        <v>4400</v>
       </c>
       <c r="D1591" t="s">
         <v>1593</v>
@@ -28432,7 +29008,7 @@
         <v>55</v>
       </c>
       <c r="C1592">
-        <v>3770</v>
+        <v>4390</v>
       </c>
       <c r="D1592" t="s">
         <v>1594</v>
@@ -28446,7 +29022,7 @@
         <v>56</v>
       </c>
       <c r="C1593">
-        <v>3750</v>
+        <v>4390</v>
       </c>
       <c r="D1593" t="s">
         <v>1595</v>
@@ -28460,7 +29036,7 @@
         <v>57</v>
       </c>
       <c r="C1594">
-        <v>3730</v>
+        <v>4380</v>
       </c>
       <c r="D1594" t="s">
         <v>1596</v>
@@ -28474,7 +29050,7 @@
         <v>58</v>
       </c>
       <c r="C1595">
-        <v>3730</v>
+        <v>4370</v>
       </c>
       <c r="D1595" t="s">
         <v>1597</v>
@@ -28488,7 +29064,7 @@
         <v>59</v>
       </c>
       <c r="C1596">
-        <v>3750</v>
+        <v>4360</v>
       </c>
       <c r="D1596" t="s">
         <v>1598</v>
@@ -28502,7 +29078,7 @@
         <v>60</v>
       </c>
       <c r="C1597">
-        <v>3790</v>
+        <v>4360</v>
       </c>
       <c r="D1597" t="s">
         <v>1599</v>
@@ -28516,7 +29092,7 @@
         <v>61</v>
       </c>
       <c r="C1598">
-        <v>3840</v>
+        <v>4360</v>
       </c>
       <c r="D1598" t="s">
         <v>1600</v>
@@ -28530,7 +29106,7 @@
         <v>62</v>
       </c>
       <c r="C1599">
-        <v>3910</v>
+        <v>4360</v>
       </c>
       <c r="D1599" t="s">
         <v>1601</v>
@@ -28544,7 +29120,7 @@
         <v>63</v>
       </c>
       <c r="C1600">
-        <v>3980</v>
+        <v>4380</v>
       </c>
       <c r="D1600" t="s">
         <v>1602</v>
@@ -28558,7 +29134,7 @@
         <v>64</v>
       </c>
       <c r="C1601">
-        <v>4050</v>
+        <v>4420</v>
       </c>
       <c r="D1601" t="s">
         <v>1603</v>
@@ -28572,7 +29148,7 @@
         <v>65</v>
       </c>
       <c r="C1602">
-        <v>4130</v>
+        <v>4470</v>
       </c>
       <c r="D1602" t="s">
         <v>1604</v>
@@ -28586,7 +29162,7 @@
         <v>66</v>
       </c>
       <c r="C1603">
-        <v>4220</v>
+        <v>4550</v>
       </c>
       <c r="D1603" t="s">
         <v>1605</v>
@@ -28600,7 +29176,7 @@
         <v>67</v>
       </c>
       <c r="C1604">
-        <v>4310</v>
+        <v>4650</v>
       </c>
       <c r="D1604" t="s">
         <v>1606</v>
@@ -28614,7 +29190,7 @@
         <v>68</v>
       </c>
       <c r="C1605">
-        <v>4420</v>
+        <v>4760</v>
       </c>
       <c r="D1605" t="s">
         <v>1607</v>
@@ -28628,7 +29204,7 @@
         <v>69</v>
       </c>
       <c r="C1606">
-        <v>4540</v>
+        <v>4870</v>
       </c>
       <c r="D1606" t="s">
         <v>1608</v>
@@ -28642,7 +29218,7 @@
         <v>70</v>
       </c>
       <c r="C1607">
-        <v>4650</v>
+        <v>4970</v>
       </c>
       <c r="D1607" t="s">
         <v>1609</v>
@@ -28656,7 +29232,7 @@
         <v>71</v>
       </c>
       <c r="C1608">
-        <v>4760</v>
+        <v>5060</v>
       </c>
       <c r="D1608" t="s">
         <v>1610</v>
@@ -28670,7 +29246,7 @@
         <v>72</v>
       </c>
       <c r="C1609">
-        <v>4860</v>
+        <v>5130</v>
       </c>
       <c r="D1609" t="s">
         <v>1611</v>
@@ -28684,7 +29260,7 @@
         <v>73</v>
       </c>
       <c r="C1610">
-        <v>4960</v>
+        <v>5190</v>
       </c>
       <c r="D1610" t="s">
         <v>1612</v>
@@ -28698,7 +29274,7 @@
         <v>74</v>
       </c>
       <c r="C1611">
-        <v>5060</v>
+        <v>5260</v>
       </c>
       <c r="D1611" t="s">
         <v>1613</v>
@@ -28712,7 +29288,7 @@
         <v>75</v>
       </c>
       <c r="C1612">
-        <v>5160</v>
+        <v>5330</v>
       </c>
       <c r="D1612" t="s">
         <v>1614</v>
@@ -28726,7 +29302,7 @@
         <v>76</v>
       </c>
       <c r="C1613">
-        <v>5270</v>
+        <v>5420</v>
       </c>
       <c r="D1613" t="s">
         <v>1615</v>
@@ -28740,7 +29316,7 @@
         <v>77</v>
       </c>
       <c r="C1614">
-        <v>5380</v>
+        <v>5530</v>
       </c>
       <c r="D1614" t="s">
         <v>1616</v>
@@ -28754,7 +29330,7 @@
         <v>78</v>
       </c>
       <c r="C1615">
-        <v>5480</v>
+        <v>5640</v>
       </c>
       <c r="D1615" t="s">
         <v>1617</v>
@@ -28768,7 +29344,7 @@
         <v>79</v>
       </c>
       <c r="C1616">
-        <v>5570</v>
+        <v>5740</v>
       </c>
       <c r="D1616" t="s">
         <v>1618</v>
@@ -28782,7 +29358,7 @@
         <v>80</v>
       </c>
       <c r="C1617">
-        <v>5640</v>
+        <v>5810</v>
       </c>
       <c r="D1617" t="s">
         <v>1619</v>
@@ -28796,7 +29372,7 @@
         <v>81</v>
       </c>
       <c r="C1618">
-        <v>5700</v>
+        <v>5870</v>
       </c>
       <c r="D1618" t="s">
         <v>1620</v>
@@ -28810,7 +29386,7 @@
         <v>82</v>
       </c>
       <c r="C1619">
-        <v>5770</v>
+        <v>5940</v>
       </c>
       <c r="D1619" t="s">
         <v>1621</v>
@@ -28824,7 +29400,7 @@
         <v>83</v>
       </c>
       <c r="C1620">
-        <v>5850</v>
+        <v>5970</v>
       </c>
       <c r="D1620" t="s">
         <v>1622</v>
@@ -28838,7 +29414,7 @@
         <v>84</v>
       </c>
       <c r="C1621">
-        <v>5930</v>
+        <v>6000</v>
       </c>
       <c r="D1621" t="s">
         <v>1623</v>
@@ -28852,7 +29428,7 @@
         <v>85</v>
       </c>
       <c r="C1622">
-        <v>6010</v>
+        <v>6000</v>
       </c>
       <c r="D1622" t="s">
         <v>1624</v>
@@ -28866,7 +29442,7 @@
         <v>86</v>
       </c>
       <c r="C1623">
-        <v>6050</v>
+        <v>5990</v>
       </c>
       <c r="D1623" t="s">
         <v>1625</v>
@@ -28880,7 +29456,7 @@
         <v>87</v>
       </c>
       <c r="C1624">
-        <v>6040</v>
+        <v>5980</v>
       </c>
       <c r="D1624" t="s">
         <v>1626</v>
@@ -28894,7 +29470,7 @@
         <v>88</v>
       </c>
       <c r="C1625">
-        <v>5980</v>
+        <v>5930</v>
       </c>
       <c r="D1625" t="s">
         <v>1627</v>
@@ -28908,7 +29484,7 @@
         <v>89</v>
       </c>
       <c r="C1626">
-        <v>5880</v>
+        <v>5810</v>
       </c>
       <c r="D1626" t="s">
         <v>1628</v>
@@ -28922,7 +29498,7 @@
         <v>90</v>
       </c>
       <c r="C1627">
-        <v>5770</v>
+        <v>5730</v>
       </c>
       <c r="D1627" t="s">
         <v>1629</v>
@@ -28936,7 +29512,7 @@
         <v>91</v>
       </c>
       <c r="C1628">
-        <v>5650</v>
+        <v>5600</v>
       </c>
       <c r="D1628" t="s">
         <v>1630</v>
@@ -28950,7 +29526,7 @@
         <v>92</v>
       </c>
       <c r="C1629">
-        <v>5520</v>
+        <v>5480</v>
       </c>
       <c r="D1629" t="s">
         <v>1631</v>
@@ -28964,7 +29540,7 @@
         <v>93</v>
       </c>
       <c r="C1630">
-        <v>5380</v>
+        <v>5330</v>
       </c>
       <c r="D1630" t="s">
         <v>1632</v>
@@ -28978,7 +29554,7 @@
         <v>94</v>
       </c>
       <c r="C1631">
-        <v>5260</v>
+        <v>5230</v>
       </c>
       <c r="D1631" t="s">
         <v>1633</v>
@@ -28992,7 +29568,7 @@
         <v>95</v>
       </c>
       <c r="C1632">
-        <v>5160</v>
+        <v>5110</v>
       </c>
       <c r="D1632" t="s">
         <v>1634</v>
@@ -29006,7 +29582,7 @@
         <v>96</v>
       </c>
       <c r="C1633">
-        <v>5080</v>
+        <v>5010</v>
       </c>
       <c r="D1633" t="s">
         <v>1635</v>
@@ -29020,7 +29596,7 @@
         <v>1</v>
       </c>
       <c r="C1634">
-        <v>5000</v>
+        <v>4990</v>
       </c>
       <c r="D1634" t="s">
         <v>1636</v>
@@ -29034,7 +29610,7 @@
         <v>2</v>
       </c>
       <c r="C1635">
-        <v>4940</v>
+        <v>4950</v>
       </c>
       <c r="D1635" t="s">
         <v>1637</v>
@@ -29048,7 +29624,7 @@
         <v>3</v>
       </c>
       <c r="C1636">
-        <v>4860</v>
+        <v>4890</v>
       </c>
       <c r="D1636" t="s">
         <v>1638</v>
@@ -29062,7 +29638,7 @@
         <v>4</v>
       </c>
       <c r="C1637">
-        <v>4810</v>
+        <v>4820</v>
       </c>
       <c r="D1637" t="s">
         <v>1639</v>
@@ -29090,7 +29666,7 @@
         <v>6</v>
       </c>
       <c r="C1639">
-        <v>4740</v>
+        <v>4730</v>
       </c>
       <c r="D1639" t="s">
         <v>1641</v>
@@ -29104,7 +29680,7 @@
         <v>7</v>
       </c>
       <c r="C1640">
-        <v>4710</v>
+        <v>4690</v>
       </c>
       <c r="D1640" t="s">
         <v>1642</v>
@@ -29118,7 +29694,7 @@
         <v>8</v>
       </c>
       <c r="C1641">
-        <v>4680</v>
+        <v>4660</v>
       </c>
       <c r="D1641" t="s">
         <v>1643</v>
@@ -29132,7 +29708,7 @@
         <v>9</v>
       </c>
       <c r="C1642">
-        <v>4650</v>
+        <v>4630</v>
       </c>
       <c r="D1642" t="s">
         <v>1644</v>
@@ -29146,7 +29722,7 @@
         <v>10</v>
       </c>
       <c r="C1643">
-        <v>4630</v>
+        <v>4620</v>
       </c>
       <c r="D1643" t="s">
         <v>1645</v>
@@ -29160,7 +29736,7 @@
         <v>11</v>
       </c>
       <c r="C1644">
-        <v>4620</v>
+        <v>4600</v>
       </c>
       <c r="D1644" t="s">
         <v>1646</v>
@@ -29174,7 +29750,7 @@
         <v>12</v>
       </c>
       <c r="C1645">
-        <v>4620</v>
+        <v>4600</v>
       </c>
       <c r="D1645" t="s">
         <v>1647</v>
@@ -29188,7 +29764,7 @@
         <v>13</v>
       </c>
       <c r="C1646">
-        <v>4620</v>
+        <v>4600</v>
       </c>
       <c r="D1646" t="s">
         <v>1648</v>
@@ -29202,7 +29778,7 @@
         <v>14</v>
       </c>
       <c r="C1647">
-        <v>4630</v>
+        <v>4610</v>
       </c>
       <c r="D1647" t="s">
         <v>1649</v>
@@ -29216,7 +29792,7 @@
         <v>15</v>
       </c>
       <c r="C1648">
-        <v>4630</v>
+        <v>4620</v>
       </c>
       <c r="D1648" t="s">
         <v>1650</v>
@@ -29230,7 +29806,7 @@
         <v>16</v>
       </c>
       <c r="C1649">
-        <v>4640</v>
+        <v>4630</v>
       </c>
       <c r="D1649" t="s">
         <v>1651</v>
@@ -29244,7 +29820,7 @@
         <v>17</v>
       </c>
       <c r="C1650">
-        <v>4640</v>
+        <v>4630</v>
       </c>
       <c r="D1650" t="s">
         <v>1652</v>
@@ -29258,7 +29834,7 @@
         <v>18</v>
       </c>
       <c r="C1651">
-        <v>4650</v>
+        <v>4640</v>
       </c>
       <c r="D1651" t="s">
         <v>1653</v>
@@ -29272,7 +29848,7 @@
         <v>19</v>
       </c>
       <c r="C1652">
-        <v>4660</v>
+        <v>4650</v>
       </c>
       <c r="D1652" t="s">
         <v>1654</v>
@@ -29286,7 +29862,7 @@
         <v>20</v>
       </c>
       <c r="C1653">
-        <v>4690</v>
+        <v>4670</v>
       </c>
       <c r="D1653" t="s">
         <v>1655</v>
@@ -29300,7 +29876,7 @@
         <v>21</v>
       </c>
       <c r="C1654">
-        <v>4740</v>
+        <v>4710</v>
       </c>
       <c r="D1654" t="s">
         <v>1656</v>
@@ -29314,7 +29890,7 @@
         <v>22</v>
       </c>
       <c r="C1655">
-        <v>4810</v>
+        <v>4780</v>
       </c>
       <c r="D1655" t="s">
         <v>1657</v>
@@ -29328,7 +29904,7 @@
         <v>23</v>
       </c>
       <c r="C1656">
-        <v>4900</v>
+        <v>4860</v>
       </c>
       <c r="D1656" t="s">
         <v>1658</v>
@@ -29342,7 +29918,7 @@
         <v>24</v>
       </c>
       <c r="C1657">
-        <v>5000</v>
+        <v>4960</v>
       </c>
       <c r="D1657" t="s">
         <v>1659</v>
@@ -29356,7 +29932,7 @@
         <v>25</v>
       </c>
       <c r="C1658">
-        <v>5120</v>
+        <v>5070</v>
       </c>
       <c r="D1658" t="s">
         <v>1660</v>
@@ -29370,7 +29946,7 @@
         <v>26</v>
       </c>
       <c r="C1659">
-        <v>5240</v>
+        <v>5200</v>
       </c>
       <c r="D1659" t="s">
         <v>1661</v>
@@ -29384,7 +29960,7 @@
         <v>27</v>
       </c>
       <c r="C1660">
-        <v>5370</v>
+        <v>5340</v>
       </c>
       <c r="D1660" t="s">
         <v>1662</v>
@@ -29398,7 +29974,7 @@
         <v>28</v>
       </c>
       <c r="C1661">
-        <v>5500</v>
+        <v>5470</v>
       </c>
       <c r="D1661" t="s">
         <v>1663</v>
@@ -29412,7 +29988,7 @@
         <v>29</v>
       </c>
       <c r="C1662">
-        <v>5610</v>
+        <v>5600</v>
       </c>
       <c r="D1662" t="s">
         <v>1664</v>
@@ -29426,7 +30002,7 @@
         <v>30</v>
       </c>
       <c r="C1663">
-        <v>5710</v>
+        <v>5720</v>
       </c>
       <c r="D1663" t="s">
         <v>1665</v>
@@ -29440,7 +30016,7 @@
         <v>31</v>
       </c>
       <c r="C1664">
-        <v>5790</v>
+        <v>5830</v>
       </c>
       <c r="D1664" t="s">
         <v>1666</v>
@@ -29454,7 +30030,7 @@
         <v>32</v>
       </c>
       <c r="C1665">
-        <v>5840</v>
+        <v>5920</v>
       </c>
       <c r="D1665" t="s">
         <v>1667</v>
@@ -29468,7 +30044,7 @@
         <v>33</v>
       </c>
       <c r="C1666">
-        <v>5870</v>
+        <v>5990</v>
       </c>
       <c r="D1666" t="s">
         <v>1668</v>
@@ -29482,7 +30058,7 @@
         <v>34</v>
       </c>
       <c r="C1667">
-        <v>5870</v>
+        <v>6030</v>
       </c>
       <c r="D1667" t="s">
         <v>1669</v>
@@ -29496,7 +30072,7 @@
         <v>35</v>
       </c>
       <c r="C1668">
-        <v>5840</v>
+        <v>6050</v>
       </c>
       <c r="D1668" t="s">
         <v>1670</v>
@@ -29510,7 +30086,7 @@
         <v>36</v>
       </c>
       <c r="C1669">
-        <v>5780</v>
+        <v>6050</v>
       </c>
       <c r="D1669" t="s">
         <v>1671</v>
@@ -29524,7 +30100,7 @@
         <v>37</v>
       </c>
       <c r="C1670">
-        <v>5700</v>
+        <v>6050</v>
       </c>
       <c r="D1670" t="s">
         <v>1672</v>
@@ -29538,7 +30114,7 @@
         <v>38</v>
       </c>
       <c r="C1671">
-        <v>5600</v>
+        <v>6020</v>
       </c>
       <c r="D1671" t="s">
         <v>1673</v>
@@ -29552,7 +30128,7 @@
         <v>39</v>
       </c>
       <c r="C1672">
-        <v>5490</v>
+        <v>5970</v>
       </c>
       <c r="D1672" t="s">
         <v>1674</v>
@@ -29566,7 +30142,7 @@
         <v>40</v>
       </c>
       <c r="C1673">
-        <v>5370</v>
+        <v>5910</v>
       </c>
       <c r="D1673" t="s">
         <v>1675</v>
@@ -29580,7 +30156,7 @@
         <v>41</v>
       </c>
       <c r="C1674">
-        <v>5250</v>
+        <v>5830</v>
       </c>
       <c r="D1674" t="s">
         <v>1676</v>
@@ -29594,7 +30170,7 @@
         <v>42</v>
       </c>
       <c r="C1675">
-        <v>5130</v>
+        <v>5750</v>
       </c>
       <c r="D1675" t="s">
         <v>1677</v>
@@ -29608,7 +30184,7 @@
         <v>43</v>
       </c>
       <c r="C1676">
-        <v>5030</v>
+        <v>5660</v>
       </c>
       <c r="D1676" t="s">
         <v>1678</v>
@@ -29622,7 +30198,7 @@
         <v>44</v>
       </c>
       <c r="C1677">
-        <v>4950</v>
+        <v>5560</v>
       </c>
       <c r="D1677" t="s">
         <v>1679</v>
@@ -29636,7 +30212,7 @@
         <v>45</v>
       </c>
       <c r="C1678">
-        <v>4880</v>
+        <v>5470</v>
       </c>
       <c r="D1678" t="s">
         <v>1680</v>
@@ -29650,7 +30226,7 @@
         <v>46</v>
       </c>
       <c r="C1679">
-        <v>4830</v>
+        <v>5390</v>
       </c>
       <c r="D1679" t="s">
         <v>1681</v>
@@ -29664,7 +30240,7 @@
         <v>47</v>
       </c>
       <c r="C1680">
-        <v>4790</v>
+        <v>5310</v>
       </c>
       <c r="D1680" t="s">
         <v>1682</v>
@@ -29678,7 +30254,7 @@
         <v>48</v>
       </c>
       <c r="C1681">
-        <v>4760</v>
+        <v>5230</v>
       </c>
       <c r="D1681" t="s">
         <v>1683</v>
@@ -29692,7 +30268,7 @@
         <v>49</v>
       </c>
       <c r="C1682">
-        <v>4740</v>
+        <v>5170</v>
       </c>
       <c r="D1682" t="s">
         <v>1684</v>
@@ -29706,7 +30282,7 @@
         <v>50</v>
       </c>
       <c r="C1683">
-        <v>4720</v>
+        <v>5110</v>
       </c>
       <c r="D1683" t="s">
         <v>1685</v>
@@ -29720,7 +30296,7 @@
         <v>51</v>
       </c>
       <c r="C1684">
-        <v>4700</v>
+        <v>5070</v>
       </c>
       <c r="D1684" t="s">
         <v>1686</v>
@@ -29734,7 +30310,7 @@
         <v>52</v>
       </c>
       <c r="C1685">
-        <v>4680</v>
+        <v>5040</v>
       </c>
       <c r="D1685" t="s">
         <v>1687</v>
@@ -29748,7 +30324,7 @@
         <v>53</v>
       </c>
       <c r="C1686">
-        <v>4660</v>
+        <v>5010</v>
       </c>
       <c r="D1686" t="s">
         <v>1688</v>
@@ -29762,7 +30338,7 @@
         <v>54</v>
       </c>
       <c r="C1687">
-        <v>4650</v>
+        <v>5000</v>
       </c>
       <c r="D1687" t="s">
         <v>1689</v>
@@ -29776,7 +30352,7 @@
         <v>55</v>
       </c>
       <c r="C1688">
-        <v>4640</v>
+        <v>5000</v>
       </c>
       <c r="D1688" t="s">
         <v>1690</v>
@@ -29790,7 +30366,7 @@
         <v>56</v>
       </c>
       <c r="C1689">
-        <v>4640</v>
+        <v>5000</v>
       </c>
       <c r="D1689" t="s">
         <v>1691</v>
@@ -29804,7 +30380,7 @@
         <v>57</v>
       </c>
       <c r="C1690">
-        <v>4660</v>
+        <v>5010</v>
       </c>
       <c r="D1690" t="s">
         <v>1692</v>
@@ -29818,7 +30394,7 @@
         <v>58</v>
       </c>
       <c r="C1691">
-        <v>4680</v>
+        <v>5020</v>
       </c>
       <c r="D1691" t="s">
         <v>1693</v>
@@ -29832,7 +30408,7 @@
         <v>59</v>
       </c>
       <c r="C1692">
-        <v>4720</v>
+        <v>5020</v>
       </c>
       <c r="D1692" t="s">
         <v>1694</v>
@@ -29846,7 +30422,7 @@
         <v>60</v>
       </c>
       <c r="C1693">
-        <v>4760</v>
+        <v>5030</v>
       </c>
       <c r="D1693" t="s">
         <v>1695</v>
@@ -29860,7 +30436,7 @@
         <v>61</v>
       </c>
       <c r="C1694">
-        <v>4810</v>
+        <v>5040</v>
       </c>
       <c r="D1694" t="s">
         <v>1696</v>
@@ -29874,7 +30450,7 @@
         <v>62</v>
       </c>
       <c r="C1695">
-        <v>4870</v>
+        <v>5060</v>
       </c>
       <c r="D1695" t="s">
         <v>1697</v>
@@ -29888,7 +30464,7 @@
         <v>63</v>
       </c>
       <c r="C1696">
-        <v>4930</v>
+        <v>5080</v>
       </c>
       <c r="D1696" t="s">
         <v>1698</v>
@@ -29902,7 +30478,7 @@
         <v>64</v>
       </c>
       <c r="C1697">
-        <v>5000</v>
+        <v>5120</v>
       </c>
       <c r="D1697" t="s">
         <v>1699</v>
@@ -29916,7 +30492,7 @@
         <v>65</v>
       </c>
       <c r="C1698">
-        <v>5080</v>
+        <v>5180</v>
       </c>
       <c r="D1698" t="s">
         <v>1700</v>
@@ -29930,7 +30506,7 @@
         <v>66</v>
       </c>
       <c r="C1699">
-        <v>5170</v>
+        <v>5250</v>
       </c>
       <c r="D1699" t="s">
         <v>1701</v>
@@ -29944,7 +30520,7 @@
         <v>67</v>
       </c>
       <c r="C1700">
-        <v>5280</v>
+        <v>5330</v>
       </c>
       <c r="D1700" t="s">
         <v>1702</v>
@@ -29958,7 +30534,7 @@
         <v>68</v>
       </c>
       <c r="C1701">
-        <v>5380</v>
+        <v>5420</v>
       </c>
       <c r="D1701" t="s">
         <v>1703</v>
@@ -29972,7 +30548,7 @@
         <v>69</v>
       </c>
       <c r="C1702">
-        <v>5500</v>
+        <v>5520</v>
       </c>
       <c r="D1702" t="s">
         <v>1704</v>
@@ -30000,7 +30576,7 @@
         <v>71</v>
       </c>
       <c r="C1704">
-        <v>5710</v>
+        <v>5700</v>
       </c>
       <c r="D1704" t="s">
         <v>1706</v>
@@ -30014,7 +30590,7 @@
         <v>72</v>
       </c>
       <c r="C1705">
-        <v>5810</v>
+        <v>5790</v>
       </c>
       <c r="D1705" t="s">
         <v>1707</v>
@@ -30028,7 +30604,7 @@
         <v>73</v>
       </c>
       <c r="C1706">
-        <v>5900</v>
+        <v>5870</v>
       </c>
       <c r="D1706" t="s">
         <v>1708</v>
@@ -30042,7 +30618,7 @@
         <v>74</v>
       </c>
       <c r="C1707">
-        <v>5990</v>
+        <v>5970</v>
       </c>
       <c r="D1707" t="s">
         <v>1709</v>
@@ -30056,7 +30632,7 @@
         <v>75</v>
       </c>
       <c r="C1708">
-        <v>6090</v>
+        <v>6080</v>
       </c>
       <c r="D1708" t="s">
         <v>1710</v>
@@ -30084,7 +30660,7 @@
         <v>77</v>
       </c>
       <c r="C1710">
-        <v>6310</v>
+        <v>6320</v>
       </c>
       <c r="D1710" t="s">
         <v>1712</v>
@@ -30098,7 +30674,7 @@
         <v>78</v>
       </c>
       <c r="C1711">
-        <v>6420</v>
+        <v>6440</v>
       </c>
       <c r="D1711" t="s">
         <v>1713</v>
@@ -30112,7 +30688,7 @@
         <v>79</v>
       </c>
       <c r="C1712">
-        <v>6520</v>
+        <v>6540</v>
       </c>
       <c r="D1712" t="s">
         <v>1714</v>
@@ -30126,7 +30702,7 @@
         <v>80</v>
       </c>
       <c r="C1713">
-        <v>6590</v>
+        <v>6600</v>
       </c>
       <c r="D1713" t="s">
         <v>1715</v>
@@ -30140,7 +30716,7 @@
         <v>81</v>
       </c>
       <c r="C1714">
-        <v>6660</v>
+        <v>6670</v>
       </c>
       <c r="D1714" t="s">
         <v>1716</v>
@@ -30154,7 +30730,7 @@
         <v>82</v>
       </c>
       <c r="C1715">
-        <v>6740</v>
+        <v>6750</v>
       </c>
       <c r="D1715" t="s">
         <v>1717</v>
@@ -30168,7 +30744,7 @@
         <v>83</v>
       </c>
       <c r="C1716">
-        <v>6810</v>
+        <v>6820</v>
       </c>
       <c r="D1716" t="s">
         <v>1718</v>
@@ -30196,7 +30772,7 @@
         <v>85</v>
       </c>
       <c r="C1718">
-        <v>6930</v>
+        <v>6900</v>
       </c>
       <c r="D1718" t="s">
         <v>1720</v>
@@ -30210,7 +30786,7 @@
         <v>86</v>
       </c>
       <c r="C1719">
-        <v>6910</v>
+        <v>6900</v>
       </c>
       <c r="D1719" t="s">
         <v>1721</v>
@@ -30224,7 +30800,7 @@
         <v>87</v>
       </c>
       <c r="C1720">
-        <v>6890</v>
+        <v>6880</v>
       </c>
       <c r="D1720" t="s">
         <v>1722</v>
@@ -30238,7 +30814,7 @@
         <v>88</v>
       </c>
       <c r="C1721">
-        <v>6790</v>
+        <v>6770</v>
       </c>
       <c r="D1721" t="s">
         <v>1723</v>
@@ -30252,7 +30828,7 @@
         <v>89</v>
       </c>
       <c r="C1722">
-        <v>6630</v>
+        <v>6600</v>
       </c>
       <c r="D1722" t="s">
         <v>1724</v>
@@ -30266,7 +30842,7 @@
         <v>90</v>
       </c>
       <c r="C1723">
-        <v>6500</v>
+        <v>6480</v>
       </c>
       <c r="D1723" t="s">
         <v>1725</v>
@@ -30294,7 +30870,7 @@
         <v>92</v>
       </c>
       <c r="C1725">
-        <v>6150</v>
+        <v>6170</v>
       </c>
       <c r="D1725" t="s">
         <v>1727</v>
@@ -30308,7 +30884,7 @@
         <v>93</v>
       </c>
       <c r="C1726">
-        <v>5990</v>
+        <v>5940</v>
       </c>
       <c r="D1726" t="s">
         <v>1728</v>
@@ -30322,7 +30898,7 @@
         <v>94</v>
       </c>
       <c r="C1727">
-        <v>5840</v>
+        <v>5760</v>
       </c>
       <c r="D1727" t="s">
         <v>1729</v>
@@ -30336,7 +30912,7 @@
         <v>95</v>
       </c>
       <c r="C1728">
-        <v>5710</v>
+        <v>5680</v>
       </c>
       <c r="D1728" t="s">
         <v>1730</v>
@@ -30364,7 +30940,7 @@
         <v>1</v>
       </c>
       <c r="C1730">
-        <v>5540</v>
+        <v>5450</v>
       </c>
       <c r="D1730" t="s">
         <v>1732</v>
@@ -30378,7 +30954,7 @@
         <v>2</v>
       </c>
       <c r="C1731">
-        <v>5520</v>
+        <v>5410</v>
       </c>
       <c r="D1731" t="s">
         <v>1733</v>
@@ -30392,7 +30968,7 @@
         <v>3</v>
       </c>
       <c r="C1732">
-        <v>5430</v>
+        <v>5350</v>
       </c>
       <c r="D1732" t="s">
         <v>1734</v>
@@ -30406,7 +30982,7 @@
         <v>4</v>
       </c>
       <c r="C1733">
-        <v>5340</v>
+        <v>5280</v>
       </c>
       <c r="D1733" t="s">
         <v>1735</v>
@@ -30420,7 +30996,7 @@
         <v>5</v>
       </c>
       <c r="C1734">
-        <v>5290</v>
+        <v>5230</v>
       </c>
       <c r="D1734" t="s">
         <v>1736</v>
@@ -30434,7 +31010,7 @@
         <v>6</v>
       </c>
       <c r="C1735">
-        <v>5250</v>
+        <v>5190</v>
       </c>
       <c r="D1735" t="s">
         <v>1737</v>
@@ -30448,7 +31024,7 @@
         <v>7</v>
       </c>
       <c r="C1736">
-        <v>5210</v>
+        <v>5150</v>
       </c>
       <c r="D1736" t="s">
         <v>1738</v>
@@ -30462,7 +31038,7 @@
         <v>8</v>
       </c>
       <c r="C1737">
-        <v>5160</v>
+        <v>5110</v>
       </c>
       <c r="D1737" t="s">
         <v>1739</v>
@@ -30476,7 +31052,7 @@
         <v>9</v>
       </c>
       <c r="C1738">
-        <v>5120</v>
+        <v>5080</v>
       </c>
       <c r="D1738" t="s">
         <v>1740</v>
@@ -30490,7 +31066,7 @@
         <v>10</v>
       </c>
       <c r="C1739">
-        <v>5090</v>
+        <v>5060</v>
       </c>
       <c r="D1739" t="s">
         <v>1741</v>
@@ -30504,7 +31080,7 @@
         <v>11</v>
       </c>
       <c r="C1740">
-        <v>5080</v>
+        <v>5050</v>
       </c>
       <c r="D1740" t="s">
         <v>1742</v>
@@ -30518,7 +31094,7 @@
         <v>12</v>
       </c>
       <c r="C1741">
-        <v>5070</v>
+        <v>5050</v>
       </c>
       <c r="D1741" t="s">
         <v>1743</v>
@@ -30532,7 +31108,7 @@
         <v>13</v>
       </c>
       <c r="C1742">
-        <v>5080</v>
+        <v>5050</v>
       </c>
       <c r="D1742" t="s">
         <v>1744</v>
@@ -30546,7 +31122,7 @@
         <v>14</v>
       </c>
       <c r="C1743">
-        <v>5080</v>
+        <v>5060</v>
       </c>
       <c r="D1743" t="s">
         <v>1745</v>
@@ -30560,7 +31136,7 @@
         <v>15</v>
       </c>
       <c r="C1744">
-        <v>5090</v>
+        <v>5070</v>
       </c>
       <c r="D1744" t="s">
         <v>1746</v>
@@ -30574,7 +31150,7 @@
         <v>16</v>
       </c>
       <c r="C1745">
-        <v>5080</v>
+        <v>5070</v>
       </c>
       <c r="D1745" t="s">
         <v>1747</v>
@@ -30588,7 +31164,7 @@
         <v>17</v>
       </c>
       <c r="C1746">
-        <v>5080</v>
+        <v>5070</v>
       </c>
       <c r="D1746" t="s">
         <v>1748</v>
@@ -30644,7 +31220,7 @@
         <v>21</v>
       </c>
       <c r="C1750">
-        <v>5110</v>
+        <v>5100</v>
       </c>
       <c r="D1750" t="s">
         <v>1752</v>
@@ -30658,7 +31234,7 @@
         <v>22</v>
       </c>
       <c r="C1751">
-        <v>5150</v>
+        <v>5140</v>
       </c>
       <c r="D1751" t="s">
         <v>1753</v>
@@ -30672,7 +31248,7 @@
         <v>23</v>
       </c>
       <c r="C1752">
-        <v>5220</v>
+        <v>5190</v>
       </c>
       <c r="D1752" t="s">
         <v>1754</v>
@@ -30686,7 +31262,7 @@
         <v>24</v>
       </c>
       <c r="C1753">
-        <v>5300</v>
+        <v>5260</v>
       </c>
       <c r="D1753" t="s">
         <v>1755</v>
@@ -30700,7 +31276,7 @@
         <v>25</v>
       </c>
       <c r="C1754">
-        <v>5400</v>
+        <v>5340</v>
       </c>
       <c r="D1754" t="s">
         <v>1756</v>
@@ -30714,7 +31290,7 @@
         <v>26</v>
       </c>
       <c r="C1755">
-        <v>5510</v>
+        <v>5440</v>
       </c>
       <c r="D1755" t="s">
         <v>1757</v>
@@ -30728,7 +31304,7 @@
         <v>27</v>
       </c>
       <c r="C1756">
-        <v>5620</v>
+        <v>5550</v>
       </c>
       <c r="D1756" t="s">
         <v>1758</v>
@@ -30742,7 +31318,7 @@
         <v>28</v>
       </c>
       <c r="C1757">
-        <v>5730</v>
+        <v>5650</v>
       </c>
       <c r="D1757" t="s">
         <v>1759</v>
@@ -30756,7 +31332,7 @@
         <v>29</v>
       </c>
       <c r="C1758">
-        <v>5830</v>
+        <v>5760</v>
       </c>
       <c r="D1758" t="s">
         <v>1760</v>
@@ -30770,7 +31346,7 @@
         <v>30</v>
       </c>
       <c r="C1759">
-        <v>5920</v>
+        <v>5860</v>
       </c>
       <c r="D1759" t="s">
         <v>1761</v>
@@ -30784,7 +31360,7 @@
         <v>31</v>
       </c>
       <c r="C1760">
-        <v>5990</v>
+        <v>5950</v>
       </c>
       <c r="D1760" t="s">
         <v>1762</v>
@@ -30798,7 +31374,7 @@
         <v>32</v>
       </c>
       <c r="C1761">
-        <v>6040</v>
+        <v>6020</v>
       </c>
       <c r="D1761" t="s">
         <v>1763</v>
@@ -30826,7 +31402,7 @@
         <v>34</v>
       </c>
       <c r="C1763">
-        <v>6070</v>
+        <v>6100</v>
       </c>
       <c r="D1763" t="s">
         <v>1765</v>
@@ -30840,7 +31416,7 @@
         <v>35</v>
       </c>
       <c r="C1764">
-        <v>6060</v>
+        <v>6100</v>
       </c>
       <c r="D1764" t="s">
         <v>1766</v>
@@ -30854,7 +31430,7 @@
         <v>36</v>
       </c>
       <c r="C1765">
-        <v>6020</v>
+        <v>6080</v>
       </c>
       <c r="D1765" t="s">
         <v>1767</v>
@@ -30868,7 +31444,7 @@
         <v>37</v>
       </c>
       <c r="C1766">
-        <v>5960</v>
+        <v>6040</v>
       </c>
       <c r="D1766" t="s">
         <v>1768</v>
@@ -30882,7 +31458,7 @@
         <v>38</v>
       </c>
       <c r="C1767">
-        <v>5880</v>
+        <v>5980</v>
       </c>
       <c r="D1767" t="s">
         <v>1769</v>
@@ -30896,7 +31472,7 @@
         <v>39</v>
       </c>
       <c r="C1768">
-        <v>5790</v>
+        <v>5900</v>
       </c>
       <c r="D1768" t="s">
         <v>1770</v>
@@ -30910,7 +31486,7 @@
         <v>40</v>
       </c>
       <c r="C1769">
-        <v>5690</v>
+        <v>5810</v>
       </c>
       <c r="D1769" t="s">
         <v>1771</v>
@@ -30924,7 +31500,7 @@
         <v>41</v>
       </c>
       <c r="C1770">
-        <v>5580</v>
+        <v>5720</v>
       </c>
       <c r="D1770" t="s">
         <v>1772</v>
@@ -30938,7 +31514,7 @@
         <v>42</v>
       </c>
       <c r="C1771">
-        <v>5470</v>
+        <v>5620</v>
       </c>
       <c r="D1771" t="s">
         <v>1773</v>
@@ -30952,7 +31528,7 @@
         <v>43</v>
       </c>
       <c r="C1772">
-        <v>5360</v>
+        <v>5530</v>
       </c>
       <c r="D1772" t="s">
         <v>1774</v>
@@ -30966,7 +31542,7 @@
         <v>44</v>
       </c>
       <c r="C1773">
-        <v>5260</v>
+        <v>5450</v>
       </c>
       <c r="D1773" t="s">
         <v>1775</v>
@@ -30980,7 +31556,7 @@
         <v>45</v>
       </c>
       <c r="C1774">
-        <v>5170</v>
+        <v>5370</v>
       </c>
       <c r="D1774" t="s">
         <v>1776</v>
@@ -30994,7 +31570,7 @@
         <v>46</v>
       </c>
       <c r="C1775">
-        <v>5100</v>
+        <v>5300</v>
       </c>
       <c r="D1775" t="s">
         <v>1777</v>
@@ -31008,7 +31584,7 @@
         <v>47</v>
       </c>
       <c r="C1776">
-        <v>5040</v>
+        <v>5250</v>
       </c>
       <c r="D1776" t="s">
         <v>1778</v>
@@ -31022,7 +31598,7 @@
         <v>48</v>
       </c>
       <c r="C1777">
-        <v>4990</v>
+        <v>5200</v>
       </c>
       <c r="D1777" t="s">
         <v>1779</v>
@@ -31036,7 +31612,7 @@
         <v>49</v>
       </c>
       <c r="C1778">
-        <v>4950</v>
+        <v>5170</v>
       </c>
       <c r="D1778" t="s">
         <v>1780</v>
@@ -31050,7 +31626,7 @@
         <v>50</v>
       </c>
       <c r="C1779">
-        <v>4930</v>
+        <v>5140</v>
       </c>
       <c r="D1779" t="s">
         <v>1781</v>
@@ -31064,7 +31640,7 @@
         <v>51</v>
       </c>
       <c r="C1780">
-        <v>4910</v>
+        <v>5110</v>
       </c>
       <c r="D1780" t="s">
         <v>1782</v>
@@ -31078,7 +31654,7 @@
         <v>52</v>
       </c>
       <c r="C1781">
-        <v>4900</v>
+        <v>5100</v>
       </c>
       <c r="D1781" t="s">
         <v>1783</v>
@@ -31092,7 +31668,7 @@
         <v>53</v>
       </c>
       <c r="C1782">
-        <v>4890</v>
+        <v>5080</v>
       </c>
       <c r="D1782" t="s">
         <v>1784</v>
@@ -31106,7 +31682,7 @@
         <v>54</v>
       </c>
       <c r="C1783">
-        <v>4890</v>
+        <v>5080</v>
       </c>
       <c r="D1783" t="s">
         <v>1785</v>
@@ -31120,7 +31696,7 @@
         <v>55</v>
       </c>
       <c r="C1784">
-        <v>4890</v>
+        <v>5070</v>
       </c>
       <c r="D1784" t="s">
         <v>1786</v>
@@ -31134,7 +31710,7 @@
         <v>56</v>
       </c>
       <c r="C1785">
-        <v>4890</v>
+        <v>5070</v>
       </c>
       <c r="D1785" t="s">
         <v>1787</v>
@@ -31148,7 +31724,7 @@
         <v>57</v>
       </c>
       <c r="C1786">
-        <v>4900</v>
+        <v>5070</v>
       </c>
       <c r="D1786" t="s">
         <v>1788</v>
@@ -31162,7 +31738,7 @@
         <v>58</v>
       </c>
       <c r="C1787">
-        <v>4910</v>
+        <v>5080</v>
       </c>
       <c r="D1787" t="s">
         <v>1789</v>
@@ -31176,7 +31752,7 @@
         <v>59</v>
       </c>
       <c r="C1788">
-        <v>4930</v>
+        <v>5090</v>
       </c>
       <c r="D1788" t="s">
         <v>1790</v>
@@ -31190,7 +31766,7 @@
         <v>60</v>
       </c>
       <c r="C1789">
-        <v>4960</v>
+        <v>5100</v>
       </c>
       <c r="D1789" t="s">
         <v>1791</v>
@@ -31204,7 +31780,7 @@
         <v>61</v>
       </c>
       <c r="C1790">
-        <v>4990</v>
+        <v>5120</v>
       </c>
       <c r="D1790" t="s">
         <v>1792</v>
@@ -31218,7 +31794,7 @@
         <v>62</v>
       </c>
       <c r="C1791">
-        <v>5040</v>
+        <v>5140</v>
       </c>
       <c r="D1791" t="s">
         <v>1793</v>
@@ -31232,7 +31808,7 @@
         <v>63</v>
       </c>
       <c r="C1792">
-        <v>5090</v>
+        <v>5170</v>
       </c>
       <c r="D1792" t="s">
         <v>1794</v>
@@ -31246,7 +31822,7 @@
         <v>64</v>
       </c>
       <c r="C1793">
-        <v>5150</v>
+        <v>5220</v>
       </c>
       <c r="D1793" t="s">
         <v>1795</v>
@@ -31260,7 +31836,7 @@
         <v>65</v>
       </c>
       <c r="C1794">
-        <v>5220</v>
+        <v>5280</v>
       </c>
       <c r="D1794" t="s">
         <v>1796</v>
@@ -31274,7 +31850,7 @@
         <v>66</v>
       </c>
       <c r="C1795">
-        <v>5300</v>
+        <v>5360</v>
       </c>
       <c r="D1795" t="s">
         <v>1797</v>
@@ -31288,7 +31864,7 @@
         <v>67</v>
       </c>
       <c r="C1796">
-        <v>5380</v>
+        <v>5440</v>
       </c>
       <c r="D1796" t="s">
         <v>1798</v>
@@ -31302,7 +31878,7 @@
         <v>68</v>
       </c>
       <c r="C1797">
-        <v>5470</v>
+        <v>5530</v>
       </c>
       <c r="D1797" t="s">
         <v>1799</v>
@@ -31316,7 +31892,7 @@
         <v>69</v>
       </c>
       <c r="C1798">
-        <v>5560</v>
+        <v>5630</v>
       </c>
       <c r="D1798" t="s">
         <v>1800</v>
@@ -31330,7 +31906,7 @@
         <v>70</v>
       </c>
       <c r="C1799">
-        <v>5640</v>
+        <v>5720</v>
       </c>
       <c r="D1799" t="s">
         <v>1801</v>
@@ -31344,7 +31920,7 @@
         <v>71</v>
       </c>
       <c r="C1800">
-        <v>5720</v>
+        <v>5800</v>
       </c>
       <c r="D1800" t="s">
         <v>1802</v>
@@ -31358,7 +31934,7 @@
         <v>72</v>
       </c>
       <c r="C1801">
-        <v>5800</v>
+        <v>5880</v>
       </c>
       <c r="D1801" t="s">
         <v>1803</v>
@@ -31372,7 +31948,7 @@
         <v>73</v>
       </c>
       <c r="C1802">
-        <v>5890</v>
+        <v>5960</v>
       </c>
       <c r="D1802" t="s">
         <v>1804</v>
@@ -31386,7 +31962,7 @@
         <v>74</v>
       </c>
       <c r="C1803">
-        <v>5990</v>
+        <v>6050</v>
       </c>
       <c r="D1803" t="s">
         <v>1805</v>
@@ -31400,7 +31976,7 @@
         <v>75</v>
       </c>
       <c r="C1804">
-        <v>6100</v>
+        <v>6150</v>
       </c>
       <c r="D1804" t="s">
         <v>1806</v>
@@ -31414,7 +31990,7 @@
         <v>76</v>
       </c>
       <c r="C1805">
-        <v>6220</v>
+        <v>6260</v>
       </c>
       <c r="D1805" t="s">
         <v>1807</v>
@@ -31428,7 +32004,7 @@
         <v>77</v>
       </c>
       <c r="C1806">
-        <v>6350</v>
+        <v>6380</v>
       </c>
       <c r="D1806" t="s">
         <v>1808</v>
@@ -31442,7 +32018,7 @@
         <v>78</v>
       </c>
       <c r="C1807">
-        <v>6480</v>
+        <v>6490</v>
       </c>
       <c r="D1807" t="s">
         <v>1809</v>
@@ -31456,7 +32032,7 @@
         <v>79</v>
       </c>
       <c r="C1808">
-        <v>6590</v>
+        <v>6580</v>
       </c>
       <c r="D1808" t="s">
         <v>1810</v>
@@ -31470,7 +32046,7 @@
         <v>80</v>
       </c>
       <c r="C1809">
-        <v>6680</v>
+        <v>6630</v>
       </c>
       <c r="D1809" t="s">
         <v>1811</v>
@@ -31484,7 +32060,7 @@
         <v>81</v>
       </c>
       <c r="C1810">
-        <v>6770</v>
+        <v>6690</v>
       </c>
       <c r="D1810" t="s">
         <v>1812</v>
@@ -31498,7 +32074,7 @@
         <v>82</v>
       </c>
       <c r="C1811">
-        <v>6870</v>
+        <v>6760</v>
       </c>
       <c r="D1811" t="s">
         <v>1813</v>
@@ -31512,7 +32088,7 @@
         <v>83</v>
       </c>
       <c r="C1812">
-        <v>6950</v>
+        <v>6820</v>
       </c>
       <c r="D1812" t="s">
         <v>1814</v>
@@ -31526,7 +32102,7 @@
         <v>84</v>
       </c>
       <c r="C1813">
-        <v>7040</v>
+        <v>6900</v>
       </c>
       <c r="D1813" t="s">
         <v>1815</v>
@@ -31540,7 +32116,7 @@
         <v>85</v>
       </c>
       <c r="C1814">
-        <v>7070</v>
+        <v>6900</v>
       </c>
       <c r="D1814" t="s">
         <v>1816</v>
@@ -31554,7 +32130,7 @@
         <v>86</v>
       </c>
       <c r="C1815">
-        <v>7050</v>
+        <v>6900</v>
       </c>
       <c r="D1815" t="s">
         <v>1817</v>
@@ -31568,7 +32144,7 @@
         <v>87</v>
       </c>
       <c r="C1816">
-        <v>7030</v>
+        <v>6880</v>
       </c>
       <c r="D1816" t="s">
         <v>1818</v>
@@ -31582,7 +32158,7 @@
         <v>88</v>
       </c>
       <c r="C1817">
-        <v>6950</v>
+        <v>6780</v>
       </c>
       <c r="D1817" t="s">
         <v>1819</v>
@@ -31596,7 +32172,7 @@
         <v>89</v>
       </c>
       <c r="C1818">
-        <v>6820</v>
+        <v>6610</v>
       </c>
       <c r="D1818" t="s">
         <v>1820</v>
@@ -31610,7 +32186,7 @@
         <v>90</v>
       </c>
       <c r="C1819">
-        <v>6730</v>
+        <v>6490</v>
       </c>
       <c r="D1819" t="s">
         <v>1821</v>
@@ -31624,7 +32200,7 @@
         <v>91</v>
       </c>
       <c r="C1820">
-        <v>6580</v>
+        <v>6350</v>
       </c>
       <c r="D1820" t="s">
         <v>1822</v>
@@ -31638,7 +32214,7 @@
         <v>92</v>
       </c>
       <c r="C1821">
-        <v>6420</v>
+        <v>6190</v>
       </c>
       <c r="D1821" t="s">
         <v>1823</v>
@@ -31652,7 +32228,7 @@
         <v>93</v>
       </c>
       <c r="C1822">
-        <v>6190</v>
+        <v>5970</v>
       </c>
       <c r="D1822" t="s">
         <v>1824</v>
@@ -31666,7 +32242,7 @@
         <v>94</v>
       </c>
       <c r="C1823">
-        <v>6010</v>
+        <v>5790</v>
       </c>
       <c r="D1823" t="s">
         <v>1825</v>
@@ -31680,7 +32256,7 @@
         <v>95</v>
       </c>
       <c r="C1824">
-        <v>5930</v>
+        <v>5710</v>
       </c>
       <c r="D1824" t="s">
         <v>1826</v>
@@ -31694,7 +32270,7 @@
         <v>96</v>
       </c>
       <c r="C1825">
-        <v>5820</v>
+        <v>5600</v>
       </c>
       <c r="D1825" t="s">
         <v>1827</v>
@@ -31708,7 +32284,7 @@
         <v>1</v>
       </c>
       <c r="C1826">
-        <v>5620</v>
+        <v>5520</v>
       </c>
       <c r="D1826" t="s">
         <v>1828</v>
@@ -31722,7 +32298,7 @@
         <v>2</v>
       </c>
       <c r="C1827">
-        <v>5580</v>
+        <v>5440</v>
       </c>
       <c r="D1827" t="s">
         <v>1829</v>
@@ -31736,7 +32312,7 @@
         <v>3</v>
       </c>
       <c r="C1828">
-        <v>5520</v>
+        <v>5360</v>
       </c>
       <c r="D1828" t="s">
         <v>1830</v>
@@ -31750,7 +32326,7 @@
         <v>4</v>
       </c>
       <c r="C1829">
-        <v>5440</v>
+        <v>5300</v>
       </c>
       <c r="D1829" t="s">
         <v>1831</v>
@@ -31764,7 +32340,7 @@
         <v>5</v>
       </c>
       <c r="C1830">
-        <v>5370</v>
+        <v>5250</v>
       </c>
       <c r="D1830" t="s">
         <v>1832</v>
@@ -31778,7 +32354,7 @@
         <v>6</v>
       </c>
       <c r="C1831">
-        <v>5320</v>
+        <v>5210</v>
       </c>
       <c r="D1831" t="s">
         <v>1833</v>
@@ -31792,7 +32368,7 @@
         <v>7</v>
       </c>
       <c r="C1832">
-        <v>5280</v>
+        <v>5170</v>
       </c>
       <c r="D1832" t="s">
         <v>1834</v>
@@ -31806,7 +32382,7 @@
         <v>8</v>
       </c>
       <c r="C1833">
-        <v>5240</v>
+        <v>5140</v>
       </c>
       <c r="D1833" t="s">
         <v>1835</v>
@@ -31820,7 +32396,7 @@
         <v>9</v>
       </c>
       <c r="C1834">
-        <v>5210</v>
+        <v>5110</v>
       </c>
       <c r="D1834" t="s">
         <v>1836</v>
@@ -31834,7 +32410,7 @@
         <v>10</v>
       </c>
       <c r="C1835">
-        <v>5190</v>
+        <v>5090</v>
       </c>
       <c r="D1835" t="s">
         <v>1837</v>
@@ -31848,7 +32424,7 @@
         <v>11</v>
       </c>
       <c r="C1836">
-        <v>5170</v>
+        <v>5070</v>
       </c>
       <c r="D1836" t="s">
         <v>1838</v>
@@ -31862,7 +32438,7 @@
         <v>12</v>
       </c>
       <c r="C1837">
-        <v>5150</v>
+        <v>5070</v>
       </c>
       <c r="D1837" t="s">
         <v>1839</v>
@@ -31876,7 +32452,7 @@
         <v>13</v>
       </c>
       <c r="C1838">
-        <v>5150</v>
+        <v>5060</v>
       </c>
       <c r="D1838" t="s">
         <v>1840</v>
@@ -31890,7 +32466,7 @@
         <v>14</v>
       </c>
       <c r="C1839">
-        <v>5150</v>
+        <v>5060</v>
       </c>
       <c r="D1839" t="s">
         <v>1841</v>
@@ -31904,7 +32480,7 @@
         <v>15</v>
       </c>
       <c r="C1840">
-        <v>5150</v>
+        <v>5060</v>
       </c>
       <c r="D1840" t="s">
         <v>1842</v>
@@ -31918,7 +32494,7 @@
         <v>16</v>
       </c>
       <c r="C1841">
-        <v>5160</v>
+        <v>5060</v>
       </c>
       <c r="D1841" t="s">
         <v>1843</v>
@@ -31932,7 +32508,7 @@
         <v>17</v>
       </c>
       <c r="C1842">
-        <v>5160</v>
+        <v>5070</v>
       </c>
       <c r="D1842" t="s">
         <v>1844</v>
@@ -31946,7 +32522,7 @@
         <v>18</v>
       </c>
       <c r="C1843">
-        <v>5160</v>
+        <v>5070</v>
       </c>
       <c r="D1843" t="s">
         <v>1845</v>
@@ -31960,7 +32536,7 @@
         <v>19</v>
       </c>
       <c r="C1844">
-        <v>5170</v>
+        <v>5090</v>
       </c>
       <c r="D1844" t="s">
         <v>1846</v>
@@ -31974,7 +32550,7 @@
         <v>20</v>
       </c>
       <c r="C1845">
-        <v>5180</v>
+        <v>5110</v>
       </c>
       <c r="D1845" t="s">
         <v>1847</v>
@@ -31988,7 +32564,7 @@
         <v>21</v>
       </c>
       <c r="C1846">
-        <v>5200</v>
+        <v>5140</v>
       </c>
       <c r="D1846" t="s">
         <v>1848</v>
@@ -32002,7 +32578,7 @@
         <v>22</v>
       </c>
       <c r="C1847">
-        <v>5230</v>
+        <v>5170</v>
       </c>
       <c r="D1847" t="s">
         <v>1849</v>
@@ -32016,7 +32592,7 @@
         <v>23</v>
       </c>
       <c r="C1848">
-        <v>5290</v>
+        <v>5220</v>
       </c>
       <c r="D1848" t="s">
         <v>1850</v>
@@ -32030,7 +32606,7 @@
         <v>24</v>
       </c>
       <c r="C1849">
-        <v>5360</v>
+        <v>5280</v>
       </c>
       <c r="D1849" t="s">
         <v>1851</v>
@@ -32044,7 +32620,7 @@
         <v>25</v>
       </c>
       <c r="C1850">
-        <v>5460</v>
+        <v>5350</v>
       </c>
       <c r="D1850" t="s">
         <v>1852</v>
@@ -32058,7 +32634,7 @@
         <v>26</v>
       </c>
       <c r="C1851">
-        <v>5570</v>
+        <v>5440</v>
       </c>
       <c r="D1851" t="s">
         <v>1853</v>
@@ -32072,7 +32648,7 @@
         <v>27</v>
       </c>
       <c r="C1852">
-        <v>5690</v>
+        <v>5550</v>
       </c>
       <c r="D1852" t="s">
         <v>1854</v>
@@ -32086,7 +32662,7 @@
         <v>28</v>
       </c>
       <c r="C1853">
-        <v>5810</v>
+        <v>5670</v>
       </c>
       <c r="D1853" t="s">
         <v>1855</v>
@@ -32100,7 +32676,7 @@
         <v>29</v>
       </c>
       <c r="C1854">
-        <v>5930</v>
+        <v>5800</v>
       </c>
       <c r="D1854" t="s">
         <v>1856</v>
@@ -32114,7 +32690,7 @@
         <v>30</v>
       </c>
       <c r="C1855">
-        <v>6040</v>
+        <v>5910</v>
       </c>
       <c r="D1855" t="s">
         <v>1857</v>
@@ -32128,7 +32704,7 @@
         <v>31</v>
       </c>
       <c r="C1856">
-        <v>6120</v>
+        <v>6010</v>
       </c>
       <c r="D1856" t="s">
         <v>1858</v>
@@ -32142,7 +32718,7 @@
         <v>32</v>
       </c>
       <c r="C1857">
-        <v>6170</v>
+        <v>6080</v>
       </c>
       <c r="D1857" t="s">
         <v>1859</v>
@@ -32156,7 +32732,7 @@
         <v>33</v>
       </c>
       <c r="C1858">
-        <v>6200</v>
+        <v>6130</v>
       </c>
       <c r="D1858" t="s">
         <v>1860</v>
@@ -32170,7 +32746,7 @@
         <v>34</v>
       </c>
       <c r="C1859">
-        <v>6190</v>
+        <v>6150</v>
       </c>
       <c r="D1859" t="s">
         <v>1861</v>
@@ -32184,7 +32760,7 @@
         <v>35</v>
       </c>
       <c r="C1860">
-        <v>6150</v>
+        <v>6140</v>
       </c>
       <c r="D1860" t="s">
         <v>1862</v>
@@ -32198,7 +32774,7 @@
         <v>36</v>
       </c>
       <c r="C1861">
-        <v>6090</v>
+        <v>6110</v>
       </c>
       <c r="D1861" t="s">
         <v>1863</v>
@@ -32212,7 +32788,7 @@
         <v>37</v>
       </c>
       <c r="C1862">
-        <v>6010</v>
+        <v>6040</v>
       </c>
       <c r="D1862" t="s">
         <v>1864</v>
@@ -32226,7 +32802,7 @@
         <v>38</v>
       </c>
       <c r="C1863">
-        <v>5910</v>
+        <v>5980</v>
       </c>
       <c r="D1863" t="s">
         <v>1865</v>
@@ -32240,7 +32816,7 @@
         <v>39</v>
       </c>
       <c r="C1864">
-        <v>5810</v>
+        <v>5920</v>
       </c>
       <c r="D1864" t="s">
         <v>1866</v>
@@ -32254,7 +32830,7 @@
         <v>40</v>
       </c>
       <c r="C1865">
-        <v>5700</v>
+        <v>5870</v>
       </c>
       <c r="D1865" t="s">
         <v>1867</v>
@@ -32268,7 +32844,7 @@
         <v>41</v>
       </c>
       <c r="C1866">
-        <v>5590</v>
+        <v>5820</v>
       </c>
       <c r="D1866" t="s">
         <v>1868</v>
@@ -32282,7 +32858,7 @@
         <v>42</v>
       </c>
       <c r="C1867">
-        <v>5500</v>
+        <v>5750</v>
       </c>
       <c r="D1867" t="s">
         <v>1869</v>
@@ -32296,7 +32872,7 @@
         <v>43</v>
       </c>
       <c r="C1868">
-        <v>5410</v>
+        <v>5670</v>
       </c>
       <c r="D1868" t="s">
         <v>1870</v>
@@ -32310,7 +32886,7 @@
         <v>44</v>
       </c>
       <c r="C1869">
-        <v>5330</v>
+        <v>5570</v>
       </c>
       <c r="D1869" t="s">
         <v>1871</v>
@@ -32324,7 +32900,7 @@
         <v>45</v>
       </c>
       <c r="C1870">
-        <v>5250</v>
+        <v>5450</v>
       </c>
       <c r="D1870" t="s">
         <v>1872</v>
@@ -32338,7 +32914,7 @@
         <v>46</v>
       </c>
       <c r="C1871">
-        <v>5190</v>
+        <v>5350</v>
       </c>
       <c r="D1871" t="s">
         <v>1873</v>
@@ -32352,7 +32928,7 @@
         <v>47</v>
       </c>
       <c r="C1872">
-        <v>5140</v>
+        <v>5280</v>
       </c>
       <c r="D1872" t="s">
         <v>1874</v>
@@ -32366,7 +32942,7 @@
         <v>48</v>
       </c>
       <c r="C1873">
-        <v>5090</v>
+        <v>5230</v>
       </c>
       <c r="D1873" t="s">
         <v>1875</v>
@@ -32380,7 +32956,7 @@
         <v>49</v>
       </c>
       <c r="C1874">
-        <v>5050</v>
+        <v>5200</v>
       </c>
       <c r="D1874" t="s">
         <v>1876</v>
@@ -32394,7 +32970,7 @@
         <v>50</v>
       </c>
       <c r="C1875">
-        <v>5010</v>
+        <v>5180</v>
       </c>
       <c r="D1875" t="s">
         <v>1877</v>
@@ -32408,7 +32984,7 @@
         <v>51</v>
       </c>
       <c r="C1876">
-        <v>4990</v>
+        <v>5170</v>
       </c>
       <c r="D1876" t="s">
         <v>1878</v>
@@ -32422,7 +32998,7 @@
         <v>52</v>
       </c>
       <c r="C1877">
-        <v>4970</v>
+        <v>5170</v>
       </c>
       <c r="D1877" t="s">
         <v>1879</v>
@@ -32436,7 +33012,7 @@
         <v>53</v>
       </c>
       <c r="C1878">
-        <v>4960</v>
+        <v>5180</v>
       </c>
       <c r="D1878" t="s">
         <v>1880</v>
@@ -32450,7 +33026,7 @@
         <v>54</v>
       </c>
       <c r="C1879">
-        <v>4960</v>
+        <v>5180</v>
       </c>
       <c r="D1879" t="s">
         <v>1881</v>
@@ -32464,7 +33040,7 @@
         <v>55</v>
       </c>
       <c r="C1880">
-        <v>4960</v>
+        <v>5180</v>
       </c>
       <c r="D1880" t="s">
         <v>1882</v>
@@ -32478,7 +33054,7 @@
         <v>56</v>
       </c>
       <c r="C1881">
-        <v>4970</v>
+        <v>5170</v>
       </c>
       <c r="D1881" t="s">
         <v>1883</v>
@@ -32492,7 +33068,7 @@
         <v>57</v>
       </c>
       <c r="C1882">
-        <v>4990</v>
+        <v>5160</v>
       </c>
       <c r="D1882" t="s">
         <v>1884</v>
@@ -32506,7 +33082,7 @@
         <v>58</v>
       </c>
       <c r="C1883">
-        <v>5000</v>
+        <v>5150</v>
       </c>
       <c r="D1883" t="s">
         <v>1885</v>
@@ -32520,7 +33096,7 @@
         <v>59</v>
       </c>
       <c r="C1884">
-        <v>5020</v>
+        <v>5140</v>
       </c>
       <c r="D1884" t="s">
         <v>1886</v>
@@ -32534,7 +33110,7 @@
         <v>60</v>
       </c>
       <c r="C1885">
-        <v>5040</v>
+        <v>5140</v>
       </c>
       <c r="D1885" t="s">
         <v>1887</v>
@@ -32548,7 +33124,7 @@
         <v>61</v>
       </c>
       <c r="C1886">
-        <v>5070</v>
+        <v>5150</v>
       </c>
       <c r="D1886" t="s">
         <v>1888</v>
@@ -32562,7 +33138,7 @@
         <v>62</v>
       </c>
       <c r="C1887">
-        <v>5110</v>
+        <v>5170</v>
       </c>
       <c r="D1887" t="s">
         <v>1889</v>
@@ -32576,7 +33152,7 @@
         <v>63</v>
       </c>
       <c r="C1888">
-        <v>5160</v>
+        <v>5210</v>
       </c>
       <c r="D1888" t="s">
         <v>1890</v>
@@ -32590,7 +33166,7 @@
         <v>64</v>
       </c>
       <c r="C1889">
-        <v>5220</v>
+        <v>5260</v>
       </c>
       <c r="D1889" t="s">
         <v>1891</v>
@@ -32604,7 +33180,7 @@
         <v>65</v>
       </c>
       <c r="C1890">
-        <v>5300</v>
+        <v>5320</v>
       </c>
       <c r="D1890" t="s">
         <v>1892</v>
@@ -32618,7 +33194,7 @@
         <v>66</v>
       </c>
       <c r="C1891">
-        <v>5380</v>
+        <v>5390</v>
       </c>
       <c r="D1891" t="s">
         <v>1893</v>
@@ -32632,7 +33208,7 @@
         <v>67</v>
       </c>
       <c r="C1892">
-        <v>5470</v>
+        <v>5460</v>
       </c>
       <c r="D1892" t="s">
         <v>1894</v>
@@ -32646,7 +33222,7 @@
         <v>68</v>
       </c>
       <c r="C1893">
-        <v>5560</v>
+        <v>5530</v>
       </c>
       <c r="D1893" t="s">
         <v>1895</v>
@@ -32660,7 +33236,7 @@
         <v>69</v>
       </c>
       <c r="C1894">
-        <v>5640</v>
+        <v>5610</v>
       </c>
       <c r="D1894" t="s">
         <v>1896</v>
@@ -32674,7 +33250,7 @@
         <v>70</v>
       </c>
       <c r="C1895">
-        <v>5720</v>
+        <v>5690</v>
       </c>
       <c r="D1895" t="s">
         <v>1897</v>
@@ -32688,7 +33264,7 @@
         <v>71</v>
       </c>
       <c r="C1896">
-        <v>5800</v>
+        <v>5770</v>
       </c>
       <c r="D1896" t="s">
         <v>1898</v>
@@ -32702,7 +33278,7 @@
         <v>72</v>
       </c>
       <c r="C1897">
-        <v>5880</v>
+        <v>5860</v>
       </c>
       <c r="D1897" t="s">
         <v>1899</v>
@@ -32716,7 +33292,7 @@
         <v>73</v>
       </c>
       <c r="C1898">
-        <v>5970</v>
+        <v>5940</v>
       </c>
       <c r="D1898" t="s">
         <v>1900</v>
@@ -32730,7 +33306,7 @@
         <v>74</v>
       </c>
       <c r="C1899">
-        <v>6070</v>
+        <v>6030</v>
       </c>
       <c r="D1899" t="s">
         <v>1901</v>
@@ -32744,7 +33320,7 @@
         <v>75</v>
       </c>
       <c r="C1900">
-        <v>6180</v>
+        <v>6130</v>
       </c>
       <c r="D1900" t="s">
         <v>1902</v>
@@ -32758,7 +33334,7 @@
         <v>76</v>
       </c>
       <c r="C1901">
-        <v>6300</v>
+        <v>6230</v>
       </c>
       <c r="D1901" t="s">
         <v>1903</v>
@@ -32772,7 +33348,7 @@
         <v>77</v>
       </c>
       <c r="C1902">
-        <v>6430</v>
+        <v>6340</v>
       </c>
       <c r="D1902" t="s">
         <v>1904</v>
@@ -32786,7 +33362,7 @@
         <v>78</v>
       </c>
       <c r="C1903">
-        <v>6560</v>
+        <v>6430</v>
       </c>
       <c r="D1903" t="s">
         <v>1905</v>
@@ -32800,7 +33376,7 @@
         <v>79</v>
       </c>
       <c r="C1904">
-        <v>6660</v>
+        <v>6510</v>
       </c>
       <c r="D1904" t="s">
         <v>1906</v>
@@ -32814,7 +33390,7 @@
         <v>80</v>
       </c>
       <c r="C1905">
-        <v>6750</v>
+        <v>6580</v>
       </c>
       <c r="D1905" t="s">
         <v>1907</v>
@@ -32828,7 +33404,7 @@
         <v>81</v>
       </c>
       <c r="C1906">
-        <v>6850</v>
+        <v>6640</v>
       </c>
       <c r="D1906" t="s">
         <v>1908</v>
@@ -32842,7 +33418,7 @@
         <v>82</v>
       </c>
       <c r="C1907">
-        <v>6950</v>
+        <v>6700</v>
       </c>
       <c r="D1907" t="s">
         <v>1909</v>
@@ -32856,7 +33432,7 @@
         <v>83</v>
       </c>
       <c r="C1908">
-        <v>7030</v>
+        <v>6760</v>
       </c>
       <c r="D1908" t="s">
         <v>1910</v>
@@ -32870,7 +33446,7 @@
         <v>84</v>
       </c>
       <c r="C1909">
-        <v>7090</v>
+        <v>6830</v>
       </c>
       <c r="D1909" t="s">
         <v>1911</v>
@@ -32884,7 +33460,7 @@
         <v>85</v>
       </c>
       <c r="C1910">
-        <v>7080</v>
+        <v>6880</v>
       </c>
       <c r="D1910" t="s">
         <v>1912</v>
@@ -32898,7 +33474,7 @@
         <v>86</v>
       </c>
       <c r="C1911">
-        <v>7020</v>
+        <v>6890</v>
       </c>
       <c r="D1911" t="s">
         <v>1913</v>
@@ -32912,7 +33488,7 @@
         <v>87</v>
       </c>
       <c r="C1912">
-        <v>7000</v>
+        <v>6850</v>
       </c>
       <c r="D1912" t="s">
         <v>1914</v>
@@ -32926,7 +33502,7 @@
         <v>88</v>
       </c>
       <c r="C1913">
-        <v>6960</v>
+        <v>6750</v>
       </c>
       <c r="D1913" t="s">
         <v>1915</v>
@@ -32940,7 +33516,7 @@
         <v>89</v>
       </c>
       <c r="C1914">
-        <v>6890</v>
+        <v>6600</v>
       </c>
       <c r="D1914" t="s">
         <v>1916</v>
@@ -32954,7 +33530,7 @@
         <v>90</v>
       </c>
       <c r="C1915">
-        <v>6840</v>
+        <v>6450</v>
       </c>
       <c r="D1915" t="s">
         <v>1917</v>
@@ -32968,7 +33544,7 @@
         <v>91</v>
       </c>
       <c r="C1916">
-        <v>6690</v>
+        <v>6290</v>
       </c>
       <c r="D1916" t="s">
         <v>1918</v>
@@ -32982,7 +33558,7 @@
         <v>92</v>
       </c>
       <c r="C1917">
-        <v>6500</v>
+        <v>6140</v>
       </c>
       <c r="D1917" t="s">
         <v>1919</v>
@@ -32996,7 +33572,7 @@
         <v>93</v>
       </c>
       <c r="C1918">
-        <v>6280</v>
+        <v>5990</v>
       </c>
       <c r="D1918" t="s">
         <v>1920</v>
@@ -33010,7 +33586,7 @@
         <v>94</v>
       </c>
       <c r="C1919">
-        <v>6090</v>
+        <v>5850</v>
       </c>
       <c r="D1919" t="s">
         <v>1921</v>
@@ -33024,7 +33600,7 @@
         <v>95</v>
       </c>
       <c r="C1920">
-        <v>6010</v>
+        <v>5730</v>
       </c>
       <c r="D1920" t="s">
         <v>1922</v>
@@ -33038,10 +33614,2698 @@
         <v>96</v>
       </c>
       <c r="C1921">
-        <v>5900</v>
+        <v>5620</v>
       </c>
       <c r="D1921" t="s">
         <v>1923</v>
+      </c>
+    </row>
+    <row r="1922" spans="1:4">
+      <c r="A1922" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1922">
+        <v>1</v>
+      </c>
+      <c r="C1922">
+        <v>5530</v>
+      </c>
+      <c r="D1922" t="s">
+        <v>1924</v>
+      </c>
+    </row>
+    <row r="1923" spans="1:4">
+      <c r="A1923" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1923">
+        <v>2</v>
+      </c>
+      <c r="C1923">
+        <v>5440</v>
+      </c>
+      <c r="D1923" t="s">
+        <v>1925</v>
+      </c>
+    </row>
+    <row r="1924" spans="1:4">
+      <c r="A1924" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1924">
+        <v>3</v>
+      </c>
+      <c r="C1924">
+        <v>5370</v>
+      </c>
+      <c r="D1924" t="s">
+        <v>1926</v>
+      </c>
+    </row>
+    <row r="1925" spans="1:4">
+      <c r="A1925" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1925">
+        <v>4</v>
+      </c>
+      <c r="C1925">
+        <v>5310</v>
+      </c>
+      <c r="D1925" t="s">
+        <v>1927</v>
+      </c>
+    </row>
+    <row r="1926" spans="1:4">
+      <c r="A1926" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1926">
+        <v>5</v>
+      </c>
+      <c r="C1926">
+        <v>5260</v>
+      </c>
+      <c r="D1926" t="s">
+        <v>1928</v>
+      </c>
+    </row>
+    <row r="1927" spans="1:4">
+      <c r="A1927" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1927">
+        <v>6</v>
+      </c>
+      <c r="C1927">
+        <v>5210</v>
+      </c>
+      <c r="D1927" t="s">
+        <v>1929</v>
+      </c>
+    </row>
+    <row r="1928" spans="1:4">
+      <c r="A1928" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1928">
+        <v>7</v>
+      </c>
+      <c r="C1928">
+        <v>5170</v>
+      </c>
+      <c r="D1928" t="s">
+        <v>1930</v>
+      </c>
+    </row>
+    <row r="1929" spans="1:4">
+      <c r="A1929" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1929">
+        <v>8</v>
+      </c>
+      <c r="C1929">
+        <v>5140</v>
+      </c>
+      <c r="D1929" t="s">
+        <v>1931</v>
+      </c>
+    </row>
+    <row r="1930" spans="1:4">
+      <c r="A1930" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1930">
+        <v>9</v>
+      </c>
+      <c r="C1930">
+        <v>5110</v>
+      </c>
+      <c r="D1930" t="s">
+        <v>1932</v>
+      </c>
+    </row>
+    <row r="1931" spans="1:4">
+      <c r="A1931" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1931">
+        <v>10</v>
+      </c>
+      <c r="C1931">
+        <v>5090</v>
+      </c>
+      <c r="D1931" t="s">
+        <v>1933</v>
+      </c>
+    </row>
+    <row r="1932" spans="1:4">
+      <c r="A1932" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1932">
+        <v>11</v>
+      </c>
+      <c r="C1932">
+        <v>5080</v>
+      </c>
+      <c r="D1932" t="s">
+        <v>1934</v>
+      </c>
+    </row>
+    <row r="1933" spans="1:4">
+      <c r="A1933" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1933">
+        <v>12</v>
+      </c>
+      <c r="C1933">
+        <v>5070</v>
+      </c>
+      <c r="D1933" t="s">
+        <v>1935</v>
+      </c>
+    </row>
+    <row r="1934" spans="1:4">
+      <c r="A1934" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1934">
+        <v>13</v>
+      </c>
+      <c r="C1934">
+        <v>5060</v>
+      </c>
+      <c r="D1934" t="s">
+        <v>1936</v>
+      </c>
+    </row>
+    <row r="1935" spans="1:4">
+      <c r="A1935" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1935">
+        <v>14</v>
+      </c>
+      <c r="C1935">
+        <v>5060</v>
+      </c>
+      <c r="D1935" t="s">
+        <v>1937</v>
+      </c>
+    </row>
+    <row r="1936" spans="1:4">
+      <c r="A1936" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1936">
+        <v>15</v>
+      </c>
+      <c r="C1936">
+        <v>5060</v>
+      </c>
+      <c r="D1936" t="s">
+        <v>1938</v>
+      </c>
+    </row>
+    <row r="1937" spans="1:4">
+      <c r="A1937" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1937">
+        <v>16</v>
+      </c>
+      <c r="C1937">
+        <v>5060</v>
+      </c>
+      <c r="D1937" t="s">
+        <v>1939</v>
+      </c>
+    </row>
+    <row r="1938" spans="1:4">
+      <c r="A1938" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1938">
+        <v>17</v>
+      </c>
+      <c r="C1938">
+        <v>5060</v>
+      </c>
+      <c r="D1938" t="s">
+        <v>1940</v>
+      </c>
+    </row>
+    <row r="1939" spans="1:4">
+      <c r="A1939" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1939">
+        <v>18</v>
+      </c>
+      <c r="C1939">
+        <v>5060</v>
+      </c>
+      <c r="D1939" t="s">
+        <v>1941</v>
+      </c>
+    </row>
+    <row r="1940" spans="1:4">
+      <c r="A1940" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1940">
+        <v>19</v>
+      </c>
+      <c r="C1940">
+        <v>5070</v>
+      </c>
+      <c r="D1940" t="s">
+        <v>1942</v>
+      </c>
+    </row>
+    <row r="1941" spans="1:4">
+      <c r="A1941" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1941">
+        <v>20</v>
+      </c>
+      <c r="C1941">
+        <v>5080</v>
+      </c>
+      <c r="D1941" t="s">
+        <v>1943</v>
+      </c>
+    </row>
+    <row r="1942" spans="1:4">
+      <c r="A1942" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1942">
+        <v>21</v>
+      </c>
+      <c r="C1942">
+        <v>5090</v>
+      </c>
+      <c r="D1942" t="s">
+        <v>1944</v>
+      </c>
+    </row>
+    <row r="1943" spans="1:4">
+      <c r="A1943" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1943">
+        <v>22</v>
+      </c>
+      <c r="C1943">
+        <v>5120</v>
+      </c>
+      <c r="D1943" t="s">
+        <v>1945</v>
+      </c>
+    </row>
+    <row r="1944" spans="1:4">
+      <c r="A1944" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1944">
+        <v>23</v>
+      </c>
+      <c r="C1944">
+        <v>5180</v>
+      </c>
+      <c r="D1944" t="s">
+        <v>1946</v>
+      </c>
+    </row>
+    <row r="1945" spans="1:4">
+      <c r="A1945" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1945">
+        <v>24</v>
+      </c>
+      <c r="C1945">
+        <v>5240</v>
+      </c>
+      <c r="D1945" t="s">
+        <v>1947</v>
+      </c>
+    </row>
+    <row r="1946" spans="1:4">
+      <c r="A1946" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1946">
+        <v>25</v>
+      </c>
+      <c r="C1946">
+        <v>5330</v>
+      </c>
+      <c r="D1946" t="s">
+        <v>1948</v>
+      </c>
+    </row>
+    <row r="1947" spans="1:4">
+      <c r="A1947" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1947">
+        <v>26</v>
+      </c>
+      <c r="C1947">
+        <v>5420</v>
+      </c>
+      <c r="D1947" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="1948" spans="1:4">
+      <c r="A1948" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1948">
+        <v>27</v>
+      </c>
+      <c r="C1948">
+        <v>5510</v>
+      </c>
+      <c r="D1948" t="s">
+        <v>1950</v>
+      </c>
+    </row>
+    <row r="1949" spans="1:4">
+      <c r="A1949" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1949">
+        <v>28</v>
+      </c>
+      <c r="C1949">
+        <v>5610</v>
+      </c>
+      <c r="D1949" t="s">
+        <v>1951</v>
+      </c>
+    </row>
+    <row r="1950" spans="1:4">
+      <c r="A1950" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1950">
+        <v>29</v>
+      </c>
+      <c r="C1950">
+        <v>5700</v>
+      </c>
+      <c r="D1950" t="s">
+        <v>1952</v>
+      </c>
+    </row>
+    <row r="1951" spans="1:4">
+      <c r="A1951" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1951">
+        <v>30</v>
+      </c>
+      <c r="C1951">
+        <v>5790</v>
+      </c>
+      <c r="D1951" t="s">
+        <v>1953</v>
+      </c>
+    </row>
+    <row r="1952" spans="1:4">
+      <c r="A1952" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1952">
+        <v>31</v>
+      </c>
+      <c r="C1952">
+        <v>5860</v>
+      </c>
+      <c r="D1952" t="s">
+        <v>1954</v>
+      </c>
+    </row>
+    <row r="1953" spans="1:4">
+      <c r="A1953" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1953">
+        <v>32</v>
+      </c>
+      <c r="C1953">
+        <v>5930</v>
+      </c>
+      <c r="D1953" t="s">
+        <v>1955</v>
+      </c>
+    </row>
+    <row r="1954" spans="1:4">
+      <c r="A1954" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1954">
+        <v>33</v>
+      </c>
+      <c r="C1954">
+        <v>5980</v>
+      </c>
+      <c r="D1954" t="s">
+        <v>1956</v>
+      </c>
+    </row>
+    <row r="1955" spans="1:4">
+      <c r="A1955" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1955">
+        <v>34</v>
+      </c>
+      <c r="C1955">
+        <v>5990</v>
+      </c>
+      <c r="D1955" t="s">
+        <v>1957</v>
+      </c>
+    </row>
+    <row r="1956" spans="1:4">
+      <c r="A1956" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1956">
+        <v>35</v>
+      </c>
+      <c r="C1956">
+        <v>5970</v>
+      </c>
+      <c r="D1956" t="s">
+        <v>1958</v>
+      </c>
+    </row>
+    <row r="1957" spans="1:4">
+      <c r="A1957" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1957">
+        <v>36</v>
+      </c>
+      <c r="C1957">
+        <v>5920</v>
+      </c>
+      <c r="D1957" t="s">
+        <v>1959</v>
+      </c>
+    </row>
+    <row r="1958" spans="1:4">
+      <c r="A1958" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1958">
+        <v>37</v>
+      </c>
+      <c r="C1958">
+        <v>5830</v>
+      </c>
+      <c r="D1958" t="s">
+        <v>1960</v>
+      </c>
+    </row>
+    <row r="1959" spans="1:4">
+      <c r="A1959" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1959">
+        <v>38</v>
+      </c>
+      <c r="C1959">
+        <v>5750</v>
+      </c>
+      <c r="D1959" t="s">
+        <v>1961</v>
+      </c>
+    </row>
+    <row r="1960" spans="1:4">
+      <c r="A1960" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1960">
+        <v>39</v>
+      </c>
+      <c r="C1960">
+        <v>5670</v>
+      </c>
+      <c r="D1960" t="s">
+        <v>1962</v>
+      </c>
+    </row>
+    <row r="1961" spans="1:4">
+      <c r="A1961" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1961">
+        <v>40</v>
+      </c>
+      <c r="C1961">
+        <v>5590</v>
+      </c>
+      <c r="D1961" t="s">
+        <v>1963</v>
+      </c>
+    </row>
+    <row r="1962" spans="1:4">
+      <c r="A1962" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1962">
+        <v>41</v>
+      </c>
+      <c r="C1962">
+        <v>5520</v>
+      </c>
+      <c r="D1962" t="s">
+        <v>1964</v>
+      </c>
+    </row>
+    <row r="1963" spans="1:4">
+      <c r="A1963" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1963">
+        <v>42</v>
+      </c>
+      <c r="C1963">
+        <v>5430</v>
+      </c>
+      <c r="D1963" t="s">
+        <v>1965</v>
+      </c>
+    </row>
+    <row r="1964" spans="1:4">
+      <c r="A1964" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1964">
+        <v>43</v>
+      </c>
+      <c r="C1964">
+        <v>5330</v>
+      </c>
+      <c r="D1964" t="s">
+        <v>1966</v>
+      </c>
+    </row>
+    <row r="1965" spans="1:4">
+      <c r="A1965" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1965">
+        <v>44</v>
+      </c>
+      <c r="C1965">
+        <v>5220</v>
+      </c>
+      <c r="D1965" t="s">
+        <v>1967</v>
+      </c>
+    </row>
+    <row r="1966" spans="1:4">
+      <c r="A1966" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1966">
+        <v>45</v>
+      </c>
+      <c r="C1966">
+        <v>5090</v>
+      </c>
+      <c r="D1966" t="s">
+        <v>1968</v>
+      </c>
+    </row>
+    <row r="1967" spans="1:4">
+      <c r="A1967" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1967">
+        <v>46</v>
+      </c>
+      <c r="C1967">
+        <v>4990</v>
+      </c>
+      <c r="D1967" t="s">
+        <v>1969</v>
+      </c>
+    </row>
+    <row r="1968" spans="1:4">
+      <c r="A1968" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1968">
+        <v>47</v>
+      </c>
+      <c r="C1968">
+        <v>4920</v>
+      </c>
+      <c r="D1968" t="s">
+        <v>1970</v>
+      </c>
+    </row>
+    <row r="1969" spans="1:4">
+      <c r="A1969" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1969">
+        <v>48</v>
+      </c>
+      <c r="C1969">
+        <v>4870</v>
+      </c>
+      <c r="D1969" t="s">
+        <v>1971</v>
+      </c>
+    </row>
+    <row r="1970" spans="1:4">
+      <c r="A1970" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1970">
+        <v>49</v>
+      </c>
+      <c r="C1970">
+        <v>4850</v>
+      </c>
+      <c r="D1970" t="s">
+        <v>1972</v>
+      </c>
+    </row>
+    <row r="1971" spans="1:4">
+      <c r="A1971" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1971">
+        <v>50</v>
+      </c>
+      <c r="C1971">
+        <v>4840</v>
+      </c>
+      <c r="D1971" t="s">
+        <v>1973</v>
+      </c>
+    </row>
+    <row r="1972" spans="1:4">
+      <c r="A1972" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1972">
+        <v>51</v>
+      </c>
+      <c r="C1972">
+        <v>4830</v>
+      </c>
+      <c r="D1972" t="s">
+        <v>1974</v>
+      </c>
+    </row>
+    <row r="1973" spans="1:4">
+      <c r="A1973" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1973">
+        <v>52</v>
+      </c>
+      <c r="C1973">
+        <v>4830</v>
+      </c>
+      <c r="D1973" t="s">
+        <v>1975</v>
+      </c>
+    </row>
+    <row r="1974" spans="1:4">
+      <c r="A1974" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1974">
+        <v>53</v>
+      </c>
+      <c r="C1974">
+        <v>4830</v>
+      </c>
+      <c r="D1974" t="s">
+        <v>1976</v>
+      </c>
+    </row>
+    <row r="1975" spans="1:4">
+      <c r="A1975" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1975">
+        <v>54</v>
+      </c>
+      <c r="C1975">
+        <v>4830</v>
+      </c>
+      <c r="D1975" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="1976" spans="1:4">
+      <c r="A1976" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1976">
+        <v>55</v>
+      </c>
+      <c r="C1976">
+        <v>4830</v>
+      </c>
+      <c r="D1976" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="1977" spans="1:4">
+      <c r="A1977" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1977">
+        <v>56</v>
+      </c>
+      <c r="C1977">
+        <v>4820</v>
+      </c>
+      <c r="D1977" t="s">
+        <v>1979</v>
+      </c>
+    </row>
+    <row r="1978" spans="1:4">
+      <c r="A1978" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1978">
+        <v>57</v>
+      </c>
+      <c r="C1978">
+        <v>4810</v>
+      </c>
+      <c r="D1978" t="s">
+        <v>1980</v>
+      </c>
+    </row>
+    <row r="1979" spans="1:4">
+      <c r="A1979" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1979">
+        <v>58</v>
+      </c>
+      <c r="C1979">
+        <v>4810</v>
+      </c>
+      <c r="D1979" t="s">
+        <v>1981</v>
+      </c>
+    </row>
+    <row r="1980" spans="1:4">
+      <c r="A1980" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1980">
+        <v>59</v>
+      </c>
+      <c r="C1980">
+        <v>4820</v>
+      </c>
+      <c r="D1980" t="s">
+        <v>1982</v>
+      </c>
+    </row>
+    <row r="1981" spans="1:4">
+      <c r="A1981" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1981">
+        <v>60</v>
+      </c>
+      <c r="C1981">
+        <v>4830</v>
+      </c>
+      <c r="D1981" t="s">
+        <v>1983</v>
+      </c>
+    </row>
+    <row r="1982" spans="1:4">
+      <c r="A1982" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1982">
+        <v>61</v>
+      </c>
+      <c r="C1982">
+        <v>4850</v>
+      </c>
+      <c r="D1982" t="s">
+        <v>1984</v>
+      </c>
+    </row>
+    <row r="1983" spans="1:4">
+      <c r="A1983" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1983">
+        <v>62</v>
+      </c>
+      <c r="C1983">
+        <v>4890</v>
+      </c>
+      <c r="D1983" t="s">
+        <v>1985</v>
+      </c>
+    </row>
+    <row r="1984" spans="1:4">
+      <c r="A1984" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1984">
+        <v>63</v>
+      </c>
+      <c r="C1984">
+        <v>4930</v>
+      </c>
+      <c r="D1984" t="s">
+        <v>1986</v>
+      </c>
+    </row>
+    <row r="1985" spans="1:4">
+      <c r="A1985" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1985">
+        <v>64</v>
+      </c>
+      <c r="C1985">
+        <v>4980</v>
+      </c>
+      <c r="D1985" t="s">
+        <v>1987</v>
+      </c>
+    </row>
+    <row r="1986" spans="1:4">
+      <c r="A1986" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1986">
+        <v>65</v>
+      </c>
+      <c r="C1986">
+        <v>5040</v>
+      </c>
+      <c r="D1986" t="s">
+        <v>1988</v>
+      </c>
+    </row>
+    <row r="1987" spans="1:4">
+      <c r="A1987" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1987">
+        <v>66</v>
+      </c>
+      <c r="C1987">
+        <v>5110</v>
+      </c>
+      <c r="D1987" t="s">
+        <v>1989</v>
+      </c>
+    </row>
+    <row r="1988" spans="1:4">
+      <c r="A1988" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1988">
+        <v>67</v>
+      </c>
+      <c r="C1988">
+        <v>5190</v>
+      </c>
+      <c r="D1988" t="s">
+        <v>1990</v>
+      </c>
+    </row>
+    <row r="1989" spans="1:4">
+      <c r="A1989" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1989">
+        <v>68</v>
+      </c>
+      <c r="C1989">
+        <v>5280</v>
+      </c>
+      <c r="D1989" t="s">
+        <v>1991</v>
+      </c>
+    </row>
+    <row r="1990" spans="1:4">
+      <c r="A1990" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1990">
+        <v>69</v>
+      </c>
+      <c r="C1990">
+        <v>5380</v>
+      </c>
+      <c r="D1990" t="s">
+        <v>1992</v>
+      </c>
+    </row>
+    <row r="1991" spans="1:4">
+      <c r="A1991" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1991">
+        <v>70</v>
+      </c>
+      <c r="C1991">
+        <v>5480</v>
+      </c>
+      <c r="D1991" t="s">
+        <v>1993</v>
+      </c>
+    </row>
+    <row r="1992" spans="1:4">
+      <c r="A1992" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1992">
+        <v>71</v>
+      </c>
+      <c r="C1992">
+        <v>5580</v>
+      </c>
+      <c r="D1992" t="s">
+        <v>1994</v>
+      </c>
+    </row>
+    <row r="1993" spans="1:4">
+      <c r="A1993" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1993">
+        <v>72</v>
+      </c>
+      <c r="C1993">
+        <v>5670</v>
+      </c>
+      <c r="D1993" t="s">
+        <v>1995</v>
+      </c>
+    </row>
+    <row r="1994" spans="1:4">
+      <c r="A1994" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1994">
+        <v>73</v>
+      </c>
+      <c r="C1994">
+        <v>5760</v>
+      </c>
+      <c r="D1994" t="s">
+        <v>1996</v>
+      </c>
+    </row>
+    <row r="1995" spans="1:4">
+      <c r="A1995" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1995">
+        <v>74</v>
+      </c>
+      <c r="C1995">
+        <v>5860</v>
+      </c>
+      <c r="D1995" t="s">
+        <v>1997</v>
+      </c>
+    </row>
+    <row r="1996" spans="1:4">
+      <c r="A1996" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1996">
+        <v>75</v>
+      </c>
+      <c r="C1996">
+        <v>5970</v>
+      </c>
+      <c r="D1996" t="s">
+        <v>1998</v>
+      </c>
+    </row>
+    <row r="1997" spans="1:4">
+      <c r="A1997" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1997">
+        <v>76</v>
+      </c>
+      <c r="C1997">
+        <v>6090</v>
+      </c>
+      <c r="D1997" t="s">
+        <v>1999</v>
+      </c>
+    </row>
+    <row r="1998" spans="1:4">
+      <c r="A1998" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1998">
+        <v>77</v>
+      </c>
+      <c r="C1998">
+        <v>6210</v>
+      </c>
+      <c r="D1998" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="1999" spans="1:4">
+      <c r="A1999" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B1999">
+        <v>78</v>
+      </c>
+      <c r="C1999">
+        <v>6310</v>
+      </c>
+      <c r="D1999" t="s">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="2000" spans="1:4">
+      <c r="A2000" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B2000">
+        <v>79</v>
+      </c>
+      <c r="C2000">
+        <v>6400</v>
+      </c>
+      <c r="D2000" t="s">
+        <v>2002</v>
+      </c>
+    </row>
+    <row r="2001" spans="1:4">
+      <c r="A2001" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B2001">
+        <v>80</v>
+      </c>
+      <c r="C2001">
+        <v>6470</v>
+      </c>
+      <c r="D2001" t="s">
+        <v>2003</v>
+      </c>
+    </row>
+    <row r="2002" spans="1:4">
+      <c r="A2002" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B2002">
+        <v>81</v>
+      </c>
+      <c r="C2002">
+        <v>6520</v>
+      </c>
+      <c r="D2002" t="s">
+        <v>2004</v>
+      </c>
+    </row>
+    <row r="2003" spans="1:4">
+      <c r="A2003" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B2003">
+        <v>82</v>
+      </c>
+      <c r="C2003">
+        <v>6580</v>
+      </c>
+      <c r="D2003" t="s">
+        <v>2005</v>
+      </c>
+    </row>
+    <row r="2004" spans="1:4">
+      <c r="A2004" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B2004">
+        <v>83</v>
+      </c>
+      <c r="C2004">
+        <v>6640</v>
+      </c>
+      <c r="D2004" t="s">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="2005" spans="1:4">
+      <c r="A2005" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B2005">
+        <v>84</v>
+      </c>
+      <c r="C2005">
+        <v>6720</v>
+      </c>
+      <c r="D2005" t="s">
+        <v>2007</v>
+      </c>
+    </row>
+    <row r="2006" spans="1:4">
+      <c r="A2006" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B2006">
+        <v>85</v>
+      </c>
+      <c r="C2006">
+        <v>6790</v>
+      </c>
+      <c r="D2006" t="s">
+        <v>2008</v>
+      </c>
+    </row>
+    <row r="2007" spans="1:4">
+      <c r="A2007" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B2007">
+        <v>86</v>
+      </c>
+      <c r="C2007">
+        <v>6820</v>
+      </c>
+      <c r="D2007" t="s">
+        <v>2009</v>
+      </c>
+    </row>
+    <row r="2008" spans="1:4">
+      <c r="A2008" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B2008">
+        <v>87</v>
+      </c>
+      <c r="C2008">
+        <v>6790</v>
+      </c>
+      <c r="D2008" t="s">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="2009" spans="1:4">
+      <c r="A2009" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B2009">
+        <v>88</v>
+      </c>
+      <c r="C2009">
+        <v>6700</v>
+      </c>
+      <c r="D2009" t="s">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="2010" spans="1:4">
+      <c r="A2010" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B2010">
+        <v>89</v>
+      </c>
+      <c r="C2010">
+        <v>6560</v>
+      </c>
+      <c r="D2010" t="s">
+        <v>2012</v>
+      </c>
+    </row>
+    <row r="2011" spans="1:4">
+      <c r="A2011" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B2011">
+        <v>90</v>
+      </c>
+      <c r="C2011">
+        <v>6410</v>
+      </c>
+      <c r="D2011" t="s">
+        <v>2013</v>
+      </c>
+    </row>
+    <row r="2012" spans="1:4">
+      <c r="A2012" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B2012">
+        <v>91</v>
+      </c>
+      <c r="C2012">
+        <v>6250</v>
+      </c>
+      <c r="D2012" t="s">
+        <v>2014</v>
+      </c>
+    </row>
+    <row r="2013" spans="1:4">
+      <c r="A2013" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B2013">
+        <v>92</v>
+      </c>
+      <c r="C2013">
+        <v>6100</v>
+      </c>
+      <c r="D2013" t="s">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="2014" spans="1:4">
+      <c r="A2014" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B2014">
+        <v>93</v>
+      </c>
+      <c r="C2014">
+        <v>5950</v>
+      </c>
+      <c r="D2014" t="s">
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="2015" spans="1:4">
+      <c r="A2015" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B2015">
+        <v>94</v>
+      </c>
+      <c r="C2015">
+        <v>5810</v>
+      </c>
+      <c r="D2015" t="s">
+        <v>2017</v>
+      </c>
+    </row>
+    <row r="2016" spans="1:4">
+      <c r="A2016" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B2016">
+        <v>95</v>
+      </c>
+      <c r="C2016">
+        <v>5690</v>
+      </c>
+      <c r="D2016" t="s">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="2017" spans="1:4">
+      <c r="A2017" s="2">
+        <v>46163</v>
+      </c>
+      <c r="B2017">
+        <v>96</v>
+      </c>
+      <c r="C2017">
+        <v>5580</v>
+      </c>
+      <c r="D2017" t="s">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="2018" spans="1:4">
+      <c r="A2018" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2018">
+        <v>1</v>
+      </c>
+      <c r="C2018">
+        <v>5490</v>
+      </c>
+      <c r="D2018" t="s">
+        <v>2020</v>
+      </c>
+    </row>
+    <row r="2019" spans="1:4">
+      <c r="A2019" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2019">
+        <v>2</v>
+      </c>
+      <c r="C2019">
+        <v>5410</v>
+      </c>
+      <c r="D2019" t="s">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="2020" spans="1:4">
+      <c r="A2020" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2020">
+        <v>3</v>
+      </c>
+      <c r="C2020">
+        <v>5340</v>
+      </c>
+      <c r="D2020" t="s">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="2021" spans="1:4">
+      <c r="A2021" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2021">
+        <v>4</v>
+      </c>
+      <c r="C2021">
+        <v>5270</v>
+      </c>
+      <c r="D2021" t="s">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="2022" spans="1:4">
+      <c r="A2022" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2022">
+        <v>5</v>
+      </c>
+      <c r="C2022">
+        <v>5220</v>
+      </c>
+      <c r="D2022" t="s">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="2023" spans="1:4">
+      <c r="A2023" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2023">
+        <v>6</v>
+      </c>
+      <c r="C2023">
+        <v>5170</v>
+      </c>
+      <c r="D2023" t="s">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="2024" spans="1:4">
+      <c r="A2024" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2024">
+        <v>7</v>
+      </c>
+      <c r="C2024">
+        <v>5130</v>
+      </c>
+      <c r="D2024" t="s">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="2025" spans="1:4">
+      <c r="A2025" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2025">
+        <v>8</v>
+      </c>
+      <c r="C2025">
+        <v>5100</v>
+      </c>
+      <c r="D2025" t="s">
+        <v>2027</v>
+      </c>
+    </row>
+    <row r="2026" spans="1:4">
+      <c r="A2026" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2026">
+        <v>9</v>
+      </c>
+      <c r="C2026">
+        <v>5080</v>
+      </c>
+      <c r="D2026" t="s">
+        <v>2028</v>
+      </c>
+    </row>
+    <row r="2027" spans="1:4">
+      <c r="A2027" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2027">
+        <v>10</v>
+      </c>
+      <c r="C2027">
+        <v>5060</v>
+      </c>
+      <c r="D2027" t="s">
+        <v>2029</v>
+      </c>
+    </row>
+    <row r="2028" spans="1:4">
+      <c r="A2028" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2028">
+        <v>11</v>
+      </c>
+      <c r="C2028">
+        <v>5050</v>
+      </c>
+      <c r="D2028" t="s">
+        <v>2030</v>
+      </c>
+    </row>
+    <row r="2029" spans="1:4">
+      <c r="A2029" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2029">
+        <v>12</v>
+      </c>
+      <c r="C2029">
+        <v>5040</v>
+      </c>
+      <c r="D2029" t="s">
+        <v>2031</v>
+      </c>
+    </row>
+    <row r="2030" spans="1:4">
+      <c r="A2030" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2030">
+        <v>13</v>
+      </c>
+      <c r="C2030">
+        <v>5040</v>
+      </c>
+      <c r="D2030" t="s">
+        <v>2032</v>
+      </c>
+    </row>
+    <row r="2031" spans="1:4">
+      <c r="A2031" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2031">
+        <v>14</v>
+      </c>
+      <c r="C2031">
+        <v>5030</v>
+      </c>
+      <c r="D2031" t="s">
+        <v>2033</v>
+      </c>
+    </row>
+    <row r="2032" spans="1:4">
+      <c r="A2032" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2032">
+        <v>15</v>
+      </c>
+      <c r="C2032">
+        <v>5030</v>
+      </c>
+      <c r="D2032" t="s">
+        <v>2034</v>
+      </c>
+    </row>
+    <row r="2033" spans="1:4">
+      <c r="A2033" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2033">
+        <v>16</v>
+      </c>
+      <c r="C2033">
+        <v>5030</v>
+      </c>
+      <c r="D2033" t="s">
+        <v>2035</v>
+      </c>
+    </row>
+    <row r="2034" spans="1:4">
+      <c r="A2034" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2034">
+        <v>17</v>
+      </c>
+      <c r="C2034">
+        <v>5040</v>
+      </c>
+      <c r="D2034" t="s">
+        <v>2036</v>
+      </c>
+    </row>
+    <row r="2035" spans="1:4">
+      <c r="A2035" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2035">
+        <v>18</v>
+      </c>
+      <c r="C2035">
+        <v>5050</v>
+      </c>
+      <c r="D2035" t="s">
+        <v>2037</v>
+      </c>
+    </row>
+    <row r="2036" spans="1:4">
+      <c r="A2036" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2036">
+        <v>19</v>
+      </c>
+      <c r="C2036">
+        <v>5050</v>
+      </c>
+      <c r="D2036" t="s">
+        <v>2038</v>
+      </c>
+    </row>
+    <row r="2037" spans="1:4">
+      <c r="A2037" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2037">
+        <v>20</v>
+      </c>
+      <c r="C2037">
+        <v>5060</v>
+      </c>
+      <c r="D2037" t="s">
+        <v>2039</v>
+      </c>
+    </row>
+    <row r="2038" spans="1:4">
+      <c r="A2038" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2038">
+        <v>21</v>
+      </c>
+      <c r="C2038">
+        <v>5070</v>
+      </c>
+      <c r="D2038" t="s">
+        <v>2040</v>
+      </c>
+    </row>
+    <row r="2039" spans="1:4">
+      <c r="A2039" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2039">
+        <v>22</v>
+      </c>
+      <c r="C2039">
+        <v>5100</v>
+      </c>
+      <c r="D2039" t="s">
+        <v>2041</v>
+      </c>
+    </row>
+    <row r="2040" spans="1:4">
+      <c r="A2040" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2040">
+        <v>23</v>
+      </c>
+      <c r="C2040">
+        <v>5150</v>
+      </c>
+      <c r="D2040" t="s">
+        <v>2042</v>
+      </c>
+    </row>
+    <row r="2041" spans="1:4">
+      <c r="A2041" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2041">
+        <v>24</v>
+      </c>
+      <c r="C2041">
+        <v>5210</v>
+      </c>
+      <c r="D2041" t="s">
+        <v>2043</v>
+      </c>
+    </row>
+    <row r="2042" spans="1:4">
+      <c r="A2042" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2042">
+        <v>25</v>
+      </c>
+      <c r="C2042">
+        <v>5300</v>
+      </c>
+      <c r="D2042" t="s">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="2043" spans="1:4">
+      <c r="A2043" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2043">
+        <v>26</v>
+      </c>
+      <c r="C2043">
+        <v>5390</v>
+      </c>
+      <c r="D2043" t="s">
+        <v>2045</v>
+      </c>
+    </row>
+    <row r="2044" spans="1:4">
+      <c r="A2044" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2044">
+        <v>27</v>
+      </c>
+      <c r="C2044">
+        <v>5480</v>
+      </c>
+      <c r="D2044" t="s">
+        <v>2046</v>
+      </c>
+    </row>
+    <row r="2045" spans="1:4">
+      <c r="A2045" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2045">
+        <v>28</v>
+      </c>
+      <c r="C2045">
+        <v>5580</v>
+      </c>
+      <c r="D2045" t="s">
+        <v>2047</v>
+      </c>
+    </row>
+    <row r="2046" spans="1:4">
+      <c r="A2046" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2046">
+        <v>29</v>
+      </c>
+      <c r="C2046">
+        <v>5680</v>
+      </c>
+      <c r="D2046" t="s">
+        <v>2048</v>
+      </c>
+    </row>
+    <row r="2047" spans="1:4">
+      <c r="A2047" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2047">
+        <v>30</v>
+      </c>
+      <c r="C2047">
+        <v>5770</v>
+      </c>
+      <c r="D2047" t="s">
+        <v>2049</v>
+      </c>
+    </row>
+    <row r="2048" spans="1:4">
+      <c r="A2048" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2048">
+        <v>31</v>
+      </c>
+      <c r="C2048">
+        <v>5840</v>
+      </c>
+      <c r="D2048" t="s">
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="2049" spans="1:4">
+      <c r="A2049" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2049">
+        <v>32</v>
+      </c>
+      <c r="C2049">
+        <v>5900</v>
+      </c>
+      <c r="D2049" t="s">
+        <v>2051</v>
+      </c>
+    </row>
+    <row r="2050" spans="1:4">
+      <c r="A2050" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2050">
+        <v>33</v>
+      </c>
+      <c r="C2050">
+        <v>5930</v>
+      </c>
+      <c r="D2050" t="s">
+        <v>2052</v>
+      </c>
+    </row>
+    <row r="2051" spans="1:4">
+      <c r="A2051" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2051">
+        <v>34</v>
+      </c>
+      <c r="C2051">
+        <v>5940</v>
+      </c>
+      <c r="D2051" t="s">
+        <v>2053</v>
+      </c>
+    </row>
+    <row r="2052" spans="1:4">
+      <c r="A2052" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2052">
+        <v>35</v>
+      </c>
+      <c r="C2052">
+        <v>5910</v>
+      </c>
+      <c r="D2052" t="s">
+        <v>2054</v>
+      </c>
+    </row>
+    <row r="2053" spans="1:4">
+      <c r="A2053" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2053">
+        <v>36</v>
+      </c>
+      <c r="C2053">
+        <v>5840</v>
+      </c>
+      <c r="D2053" t="s">
+        <v>2055</v>
+      </c>
+    </row>
+    <row r="2054" spans="1:4">
+      <c r="A2054" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2054">
+        <v>37</v>
+      </c>
+      <c r="C2054">
+        <v>5750</v>
+      </c>
+      <c r="D2054" t="s">
+        <v>2056</v>
+      </c>
+    </row>
+    <row r="2055" spans="1:4">
+      <c r="A2055" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2055">
+        <v>38</v>
+      </c>
+      <c r="C2055">
+        <v>5660</v>
+      </c>
+      <c r="D2055" t="s">
+        <v>2057</v>
+      </c>
+    </row>
+    <row r="2056" spans="1:4">
+      <c r="A2056" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2056">
+        <v>39</v>
+      </c>
+      <c r="C2056">
+        <v>5580</v>
+      </c>
+      <c r="D2056" t="s">
+        <v>2058</v>
+      </c>
+    </row>
+    <row r="2057" spans="1:4">
+      <c r="A2057" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2057">
+        <v>40</v>
+      </c>
+      <c r="C2057">
+        <v>5490</v>
+      </c>
+      <c r="D2057" t="s">
+        <v>2059</v>
+      </c>
+    </row>
+    <row r="2058" spans="1:4">
+      <c r="A2058" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2058">
+        <v>41</v>
+      </c>
+      <c r="C2058">
+        <v>5410</v>
+      </c>
+      <c r="D2058" t="s">
+        <v>2060</v>
+      </c>
+    </row>
+    <row r="2059" spans="1:4">
+      <c r="A2059" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2059">
+        <v>42</v>
+      </c>
+      <c r="C2059">
+        <v>5320</v>
+      </c>
+      <c r="D2059" t="s">
+        <v>2061</v>
+      </c>
+    </row>
+    <row r="2060" spans="1:4">
+      <c r="A2060" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2060">
+        <v>43</v>
+      </c>
+      <c r="C2060">
+        <v>5230</v>
+      </c>
+      <c r="D2060" t="s">
+        <v>2062</v>
+      </c>
+    </row>
+    <row r="2061" spans="1:4">
+      <c r="A2061" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2061">
+        <v>44</v>
+      </c>
+      <c r="C2061">
+        <v>5120</v>
+      </c>
+      <c r="D2061" t="s">
+        <v>2063</v>
+      </c>
+    </row>
+    <row r="2062" spans="1:4">
+      <c r="A2062" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2062">
+        <v>45</v>
+      </c>
+      <c r="C2062">
+        <v>5000</v>
+      </c>
+      <c r="D2062" t="s">
+        <v>2064</v>
+      </c>
+    </row>
+    <row r="2063" spans="1:4">
+      <c r="A2063" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2063">
+        <v>46</v>
+      </c>
+      <c r="C2063">
+        <v>4910</v>
+      </c>
+      <c r="D2063" t="s">
+        <v>2065</v>
+      </c>
+    </row>
+    <row r="2064" spans="1:4">
+      <c r="A2064" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2064">
+        <v>47</v>
+      </c>
+      <c r="C2064">
+        <v>4830</v>
+      </c>
+      <c r="D2064" t="s">
+        <v>2066</v>
+      </c>
+    </row>
+    <row r="2065" spans="1:4">
+      <c r="A2065" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2065">
+        <v>48</v>
+      </c>
+      <c r="C2065">
+        <v>4780</v>
+      </c>
+      <c r="D2065" t="s">
+        <v>2067</v>
+      </c>
+    </row>
+    <row r="2066" spans="1:4">
+      <c r="A2066" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2066">
+        <v>49</v>
+      </c>
+      <c r="C2066">
+        <v>4750</v>
+      </c>
+      <c r="D2066" t="s">
+        <v>2068</v>
+      </c>
+    </row>
+    <row r="2067" spans="1:4">
+      <c r="A2067" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2067">
+        <v>50</v>
+      </c>
+      <c r="C2067">
+        <v>4730</v>
+      </c>
+      <c r="D2067" t="s">
+        <v>2069</v>
+      </c>
+    </row>
+    <row r="2068" spans="1:4">
+      <c r="A2068" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2068">
+        <v>51</v>
+      </c>
+      <c r="C2068">
+        <v>4720</v>
+      </c>
+      <c r="D2068" t="s">
+        <v>2070</v>
+      </c>
+    </row>
+    <row r="2069" spans="1:4">
+      <c r="A2069" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2069">
+        <v>52</v>
+      </c>
+      <c r="C2069">
+        <v>4720</v>
+      </c>
+      <c r="D2069" t="s">
+        <v>2071</v>
+      </c>
+    </row>
+    <row r="2070" spans="1:4">
+      <c r="A2070" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2070">
+        <v>53</v>
+      </c>
+      <c r="C2070">
+        <v>4730</v>
+      </c>
+      <c r="D2070" t="s">
+        <v>2072</v>
+      </c>
+    </row>
+    <row r="2071" spans="1:4">
+      <c r="A2071" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2071">
+        <v>54</v>
+      </c>
+      <c r="C2071">
+        <v>4730</v>
+      </c>
+      <c r="D2071" t="s">
+        <v>2073</v>
+      </c>
+    </row>
+    <row r="2072" spans="1:4">
+      <c r="A2072" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2072">
+        <v>55</v>
+      </c>
+      <c r="C2072">
+        <v>4720</v>
+      </c>
+      <c r="D2072" t="s">
+        <v>2074</v>
+      </c>
+    </row>
+    <row r="2073" spans="1:4">
+      <c r="A2073" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2073">
+        <v>56</v>
+      </c>
+      <c r="C2073">
+        <v>4720</v>
+      </c>
+      <c r="D2073" t="s">
+        <v>2075</v>
+      </c>
+    </row>
+    <row r="2074" spans="1:4">
+      <c r="A2074" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2074">
+        <v>57</v>
+      </c>
+      <c r="C2074">
+        <v>4700</v>
+      </c>
+      <c r="D2074" t="s">
+        <v>2076</v>
+      </c>
+    </row>
+    <row r="2075" spans="1:4">
+      <c r="A2075" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2075">
+        <v>58</v>
+      </c>
+      <c r="C2075">
+        <v>4700</v>
+      </c>
+      <c r="D2075" t="s">
+        <v>2077</v>
+      </c>
+    </row>
+    <row r="2076" spans="1:4">
+      <c r="A2076" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2076">
+        <v>59</v>
+      </c>
+      <c r="C2076">
+        <v>4720</v>
+      </c>
+      <c r="D2076" t="s">
+        <v>2078</v>
+      </c>
+    </row>
+    <row r="2077" spans="1:4">
+      <c r="A2077" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2077">
+        <v>60</v>
+      </c>
+      <c r="C2077">
+        <v>4740</v>
+      </c>
+      <c r="D2077" t="s">
+        <v>2079</v>
+      </c>
+    </row>
+    <row r="2078" spans="1:4">
+      <c r="A2078" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2078">
+        <v>61</v>
+      </c>
+      <c r="C2078">
+        <v>4780</v>
+      </c>
+      <c r="D2078" t="s">
+        <v>2080</v>
+      </c>
+    </row>
+    <row r="2079" spans="1:4">
+      <c r="A2079" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2079">
+        <v>62</v>
+      </c>
+      <c r="C2079">
+        <v>4830</v>
+      </c>
+      <c r="D2079" t="s">
+        <v>2081</v>
+      </c>
+    </row>
+    <row r="2080" spans="1:4">
+      <c r="A2080" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2080">
+        <v>63</v>
+      </c>
+      <c r="C2080">
+        <v>4890</v>
+      </c>
+      <c r="D2080" t="s">
+        <v>2082</v>
+      </c>
+    </row>
+    <row r="2081" spans="1:4">
+      <c r="A2081" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2081">
+        <v>64</v>
+      </c>
+      <c r="C2081">
+        <v>4950</v>
+      </c>
+      <c r="D2081" t="s">
+        <v>2083</v>
+      </c>
+    </row>
+    <row r="2082" spans="1:4">
+      <c r="A2082" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2082">
+        <v>65</v>
+      </c>
+      <c r="C2082">
+        <v>5010</v>
+      </c>
+      <c r="D2082" t="s">
+        <v>2084</v>
+      </c>
+    </row>
+    <row r="2083" spans="1:4">
+      <c r="A2083" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2083">
+        <v>66</v>
+      </c>
+      <c r="C2083">
+        <v>5090</v>
+      </c>
+      <c r="D2083" t="s">
+        <v>2085</v>
+      </c>
+    </row>
+    <row r="2084" spans="1:4">
+      <c r="A2084" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2084">
+        <v>67</v>
+      </c>
+      <c r="C2084">
+        <v>5160</v>
+      </c>
+      <c r="D2084" t="s">
+        <v>2086</v>
+      </c>
+    </row>
+    <row r="2085" spans="1:4">
+      <c r="A2085" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2085">
+        <v>68</v>
+      </c>
+      <c r="C2085">
+        <v>5250</v>
+      </c>
+      <c r="D2085" t="s">
+        <v>2087</v>
+      </c>
+    </row>
+    <row r="2086" spans="1:4">
+      <c r="A2086" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2086">
+        <v>69</v>
+      </c>
+      <c r="C2086">
+        <v>5340</v>
+      </c>
+      <c r="D2086" t="s">
+        <v>2088</v>
+      </c>
+    </row>
+    <row r="2087" spans="1:4">
+      <c r="A2087" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2087">
+        <v>70</v>
+      </c>
+      <c r="C2087">
+        <v>5430</v>
+      </c>
+      <c r="D2087" t="s">
+        <v>2089</v>
+      </c>
+    </row>
+    <row r="2088" spans="1:4">
+      <c r="A2088" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2088">
+        <v>71</v>
+      </c>
+      <c r="C2088">
+        <v>5530</v>
+      </c>
+      <c r="D2088" t="s">
+        <v>2090</v>
+      </c>
+    </row>
+    <row r="2089" spans="1:4">
+      <c r="A2089" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2089">
+        <v>72</v>
+      </c>
+      <c r="C2089">
+        <v>5630</v>
+      </c>
+      <c r="D2089" t="s">
+        <v>2091</v>
+      </c>
+    </row>
+    <row r="2090" spans="1:4">
+      <c r="A2090" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2090">
+        <v>73</v>
+      </c>
+      <c r="C2090">
+        <v>5730</v>
+      </c>
+      <c r="D2090" t="s">
+        <v>2092</v>
+      </c>
+    </row>
+    <row r="2091" spans="1:4">
+      <c r="A2091" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2091">
+        <v>74</v>
+      </c>
+      <c r="C2091">
+        <v>5830</v>
+      </c>
+      <c r="D2091" t="s">
+        <v>2093</v>
+      </c>
+    </row>
+    <row r="2092" spans="1:4">
+      <c r="A2092" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2092">
+        <v>75</v>
+      </c>
+      <c r="C2092">
+        <v>5940</v>
+      </c>
+      <c r="D2092" t="s">
+        <v>2094</v>
+      </c>
+    </row>
+    <row r="2093" spans="1:4">
+      <c r="A2093" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2093">
+        <v>76</v>
+      </c>
+      <c r="C2093">
+        <v>6060</v>
+      </c>
+      <c r="D2093" t="s">
+        <v>2095</v>
+      </c>
+    </row>
+    <row r="2094" spans="1:4">
+      <c r="A2094" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2094">
+        <v>77</v>
+      </c>
+      <c r="C2094">
+        <v>6170</v>
+      </c>
+      <c r="D2094" t="s">
+        <v>2096</v>
+      </c>
+    </row>
+    <row r="2095" spans="1:4">
+      <c r="A2095" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2095">
+        <v>78</v>
+      </c>
+      <c r="C2095">
+        <v>6270</v>
+      </c>
+      <c r="D2095" t="s">
+        <v>2097</v>
+      </c>
+    </row>
+    <row r="2096" spans="1:4">
+      <c r="A2096" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2096">
+        <v>79</v>
+      </c>
+      <c r="C2096">
+        <v>6350</v>
+      </c>
+      <c r="D2096" t="s">
+        <v>2098</v>
+      </c>
+    </row>
+    <row r="2097" spans="1:4">
+      <c r="A2097" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2097">
+        <v>80</v>
+      </c>
+      <c r="C2097">
+        <v>6420</v>
+      </c>
+      <c r="D2097" t="s">
+        <v>2099</v>
+      </c>
+    </row>
+    <row r="2098" spans="1:4">
+      <c r="A2098" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2098">
+        <v>81</v>
+      </c>
+      <c r="C2098">
+        <v>6470</v>
+      </c>
+      <c r="D2098" t="s">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="2099" spans="1:4">
+      <c r="A2099" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2099">
+        <v>82</v>
+      </c>
+      <c r="C2099">
+        <v>6530</v>
+      </c>
+      <c r="D2099" t="s">
+        <v>2101</v>
+      </c>
+    </row>
+    <row r="2100" spans="1:4">
+      <c r="A2100" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2100">
+        <v>83</v>
+      </c>
+      <c r="C2100">
+        <v>6590</v>
+      </c>
+      <c r="D2100" t="s">
+        <v>2102</v>
+      </c>
+    </row>
+    <row r="2101" spans="1:4">
+      <c r="A2101" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2101">
+        <v>84</v>
+      </c>
+      <c r="C2101">
+        <v>6650</v>
+      </c>
+      <c r="D2101" t="s">
+        <v>2103</v>
+      </c>
+    </row>
+    <row r="2102" spans="1:4">
+      <c r="A2102" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2102">
+        <v>85</v>
+      </c>
+      <c r="C2102">
+        <v>6710</v>
+      </c>
+      <c r="D2102" t="s">
+        <v>2104</v>
+      </c>
+    </row>
+    <row r="2103" spans="1:4">
+      <c r="A2103" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2103">
+        <v>86</v>
+      </c>
+      <c r="C2103">
+        <v>6730</v>
+      </c>
+      <c r="D2103" t="s">
+        <v>2105</v>
+      </c>
+    </row>
+    <row r="2104" spans="1:4">
+      <c r="A2104" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2104">
+        <v>87</v>
+      </c>
+      <c r="C2104">
+        <v>6700</v>
+      </c>
+      <c r="D2104" t="s">
+        <v>2106</v>
+      </c>
+    </row>
+    <row r="2105" spans="1:4">
+      <c r="A2105" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2105">
+        <v>88</v>
+      </c>
+      <c r="C2105">
+        <v>6620</v>
+      </c>
+      <c r="D2105" t="s">
+        <v>2107</v>
+      </c>
+    </row>
+    <row r="2106" spans="1:4">
+      <c r="A2106" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2106">
+        <v>89</v>
+      </c>
+      <c r="C2106">
+        <v>6500</v>
+      </c>
+      <c r="D2106" t="s">
+        <v>2108</v>
+      </c>
+    </row>
+    <row r="2107" spans="1:4">
+      <c r="A2107" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2107">
+        <v>90</v>
+      </c>
+      <c r="C2107">
+        <v>6370</v>
+      </c>
+      <c r="D2107" t="s">
+        <v>2109</v>
+      </c>
+    </row>
+    <row r="2108" spans="1:4">
+      <c r="A2108" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2108">
+        <v>91</v>
+      </c>
+      <c r="C2108">
+        <v>6230</v>
+      </c>
+      <c r="D2108" t="s">
+        <v>2110</v>
+      </c>
+    </row>
+    <row r="2109" spans="1:4">
+      <c r="A2109" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2109">
+        <v>92</v>
+      </c>
+      <c r="C2109">
+        <v>6080</v>
+      </c>
+      <c r="D2109" t="s">
+        <v>2111</v>
+      </c>
+    </row>
+    <row r="2110" spans="1:4">
+      <c r="A2110" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2110">
+        <v>93</v>
+      </c>
+      <c r="C2110">
+        <v>5940</v>
+      </c>
+      <c r="D2110" t="s">
+        <v>2112</v>
+      </c>
+    </row>
+    <row r="2111" spans="1:4">
+      <c r="A2111" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2111">
+        <v>94</v>
+      </c>
+      <c r="C2111">
+        <v>5800</v>
+      </c>
+      <c r="D2111" t="s">
+        <v>2113</v>
+      </c>
+    </row>
+    <row r="2112" spans="1:4">
+      <c r="A2112" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2112">
+        <v>95</v>
+      </c>
+      <c r="C2112">
+        <v>5670</v>
+      </c>
+      <c r="D2112" t="s">
+        <v>2114</v>
+      </c>
+    </row>
+    <row r="2113" spans="1:4">
+      <c r="A2113" s="2">
+        <v>46164</v>
+      </c>
+      <c r="B2113">
+        <v>96</v>
+      </c>
+      <c r="C2113">
+        <v>5550</v>
+      </c>
+      <c r="D2113" t="s">
+        <v>2115</v>
       </c>
     </row>
   </sheetData>

--- a/Market Fundamentals/Transelectrica_data/Cons_Prod_final/Weekly_Consumption_2026.xlsx
+++ b/Market Fundamentals/Transelectrica_data/Cons_Prod_final/Weekly_Consumption_2026.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2116" uniqueCount="2116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2500" uniqueCount="2500">
   <si>
     <t>Date</t>
   </si>
@@ -6362,6 +6362,1158 @@
   </si>
   <si>
     <t>22.05.202696.0</t>
+  </si>
+  <si>
+    <t>23.05.20261.0</t>
+  </si>
+  <si>
+    <t>23.05.20262.0</t>
+  </si>
+  <si>
+    <t>23.05.20263.0</t>
+  </si>
+  <si>
+    <t>23.05.20264.0</t>
+  </si>
+  <si>
+    <t>23.05.20265.0</t>
+  </si>
+  <si>
+    <t>23.05.20266.0</t>
+  </si>
+  <si>
+    <t>23.05.20267.0</t>
+  </si>
+  <si>
+    <t>23.05.20268.0</t>
+  </si>
+  <si>
+    <t>23.05.20269.0</t>
+  </si>
+  <si>
+    <t>23.05.202610.0</t>
+  </si>
+  <si>
+    <t>23.05.202611.0</t>
+  </si>
+  <si>
+    <t>23.05.202612.0</t>
+  </si>
+  <si>
+    <t>23.05.202613.0</t>
+  </si>
+  <si>
+    <t>23.05.202614.0</t>
+  </si>
+  <si>
+    <t>23.05.202615.0</t>
+  </si>
+  <si>
+    <t>23.05.202616.0</t>
+  </si>
+  <si>
+    <t>23.05.202617.0</t>
+  </si>
+  <si>
+    <t>23.05.202618.0</t>
+  </si>
+  <si>
+    <t>23.05.202619.0</t>
+  </si>
+  <si>
+    <t>23.05.202620.0</t>
+  </si>
+  <si>
+    <t>23.05.202621.0</t>
+  </si>
+  <si>
+    <t>23.05.202622.0</t>
+  </si>
+  <si>
+    <t>23.05.202623.0</t>
+  </si>
+  <si>
+    <t>23.05.202624.0</t>
+  </si>
+  <si>
+    <t>23.05.202625.0</t>
+  </si>
+  <si>
+    <t>23.05.202626.0</t>
+  </si>
+  <si>
+    <t>23.05.202627.0</t>
+  </si>
+  <si>
+    <t>23.05.202628.0</t>
+  </si>
+  <si>
+    <t>23.05.202629.0</t>
+  </si>
+  <si>
+    <t>23.05.202630.0</t>
+  </si>
+  <si>
+    <t>23.05.202631.0</t>
+  </si>
+  <si>
+    <t>23.05.202632.0</t>
+  </si>
+  <si>
+    <t>23.05.202633.0</t>
+  </si>
+  <si>
+    <t>23.05.202634.0</t>
+  </si>
+  <si>
+    <t>23.05.202635.0</t>
+  </si>
+  <si>
+    <t>23.05.202636.0</t>
+  </si>
+  <si>
+    <t>23.05.202637.0</t>
+  </si>
+  <si>
+    <t>23.05.202638.0</t>
+  </si>
+  <si>
+    <t>23.05.202639.0</t>
+  </si>
+  <si>
+    <t>23.05.202640.0</t>
+  </si>
+  <si>
+    <t>23.05.202641.0</t>
+  </si>
+  <si>
+    <t>23.05.202642.0</t>
+  </si>
+  <si>
+    <t>23.05.202643.0</t>
+  </si>
+  <si>
+    <t>23.05.202644.0</t>
+  </si>
+  <si>
+    <t>23.05.202645.0</t>
+  </si>
+  <si>
+    <t>23.05.202646.0</t>
+  </si>
+  <si>
+    <t>23.05.202647.0</t>
+  </si>
+  <si>
+    <t>23.05.202648.0</t>
+  </si>
+  <si>
+    <t>23.05.202649.0</t>
+  </si>
+  <si>
+    <t>23.05.202650.0</t>
+  </si>
+  <si>
+    <t>23.05.202651.0</t>
+  </si>
+  <si>
+    <t>23.05.202652.0</t>
+  </si>
+  <si>
+    <t>23.05.202653.0</t>
+  </si>
+  <si>
+    <t>23.05.202654.0</t>
+  </si>
+  <si>
+    <t>23.05.202655.0</t>
+  </si>
+  <si>
+    <t>23.05.202656.0</t>
+  </si>
+  <si>
+    <t>23.05.202657.0</t>
+  </si>
+  <si>
+    <t>23.05.202658.0</t>
+  </si>
+  <si>
+    <t>23.05.202659.0</t>
+  </si>
+  <si>
+    <t>23.05.202660.0</t>
+  </si>
+  <si>
+    <t>23.05.202661.0</t>
+  </si>
+  <si>
+    <t>23.05.202662.0</t>
+  </si>
+  <si>
+    <t>23.05.202663.0</t>
+  </si>
+  <si>
+    <t>23.05.202664.0</t>
+  </si>
+  <si>
+    <t>23.05.202665.0</t>
+  </si>
+  <si>
+    <t>23.05.202666.0</t>
+  </si>
+  <si>
+    <t>23.05.202667.0</t>
+  </si>
+  <si>
+    <t>23.05.202668.0</t>
+  </si>
+  <si>
+    <t>23.05.202669.0</t>
+  </si>
+  <si>
+    <t>23.05.202670.0</t>
+  </si>
+  <si>
+    <t>23.05.202671.0</t>
+  </si>
+  <si>
+    <t>23.05.202672.0</t>
+  </si>
+  <si>
+    <t>23.05.202673.0</t>
+  </si>
+  <si>
+    <t>23.05.202674.0</t>
+  </si>
+  <si>
+    <t>23.05.202675.0</t>
+  </si>
+  <si>
+    <t>23.05.202676.0</t>
+  </si>
+  <si>
+    <t>23.05.202677.0</t>
+  </si>
+  <si>
+    <t>23.05.202678.0</t>
+  </si>
+  <si>
+    <t>23.05.202679.0</t>
+  </si>
+  <si>
+    <t>23.05.202680.0</t>
+  </si>
+  <si>
+    <t>23.05.202681.0</t>
+  </si>
+  <si>
+    <t>23.05.202682.0</t>
+  </si>
+  <si>
+    <t>23.05.202683.0</t>
+  </si>
+  <si>
+    <t>23.05.202684.0</t>
+  </si>
+  <si>
+    <t>23.05.202685.0</t>
+  </si>
+  <si>
+    <t>23.05.202686.0</t>
+  </si>
+  <si>
+    <t>23.05.202687.0</t>
+  </si>
+  <si>
+    <t>23.05.202688.0</t>
+  </si>
+  <si>
+    <t>23.05.202689.0</t>
+  </si>
+  <si>
+    <t>23.05.202690.0</t>
+  </si>
+  <si>
+    <t>23.05.202691.0</t>
+  </si>
+  <si>
+    <t>23.05.202692.0</t>
+  </si>
+  <si>
+    <t>23.05.202693.0</t>
+  </si>
+  <si>
+    <t>23.05.202694.0</t>
+  </si>
+  <si>
+    <t>23.05.202695.0</t>
+  </si>
+  <si>
+    <t>23.05.202696.0</t>
+  </si>
+  <si>
+    <t>24.05.20261.0</t>
+  </si>
+  <si>
+    <t>24.05.20262.0</t>
+  </si>
+  <si>
+    <t>24.05.20263.0</t>
+  </si>
+  <si>
+    <t>24.05.20264.0</t>
+  </si>
+  <si>
+    <t>24.05.20265.0</t>
+  </si>
+  <si>
+    <t>24.05.20266.0</t>
+  </si>
+  <si>
+    <t>24.05.20267.0</t>
+  </si>
+  <si>
+    <t>24.05.20268.0</t>
+  </si>
+  <si>
+    <t>24.05.20269.0</t>
+  </si>
+  <si>
+    <t>24.05.202610.0</t>
+  </si>
+  <si>
+    <t>24.05.202611.0</t>
+  </si>
+  <si>
+    <t>24.05.202612.0</t>
+  </si>
+  <si>
+    <t>24.05.202613.0</t>
+  </si>
+  <si>
+    <t>24.05.202614.0</t>
+  </si>
+  <si>
+    <t>24.05.202615.0</t>
+  </si>
+  <si>
+    <t>24.05.202616.0</t>
+  </si>
+  <si>
+    <t>24.05.202617.0</t>
+  </si>
+  <si>
+    <t>24.05.202618.0</t>
+  </si>
+  <si>
+    <t>24.05.202619.0</t>
+  </si>
+  <si>
+    <t>24.05.202620.0</t>
+  </si>
+  <si>
+    <t>24.05.202621.0</t>
+  </si>
+  <si>
+    <t>24.05.202622.0</t>
+  </si>
+  <si>
+    <t>24.05.202623.0</t>
+  </si>
+  <si>
+    <t>24.05.202624.0</t>
+  </si>
+  <si>
+    <t>24.05.202625.0</t>
+  </si>
+  <si>
+    <t>24.05.202626.0</t>
+  </si>
+  <si>
+    <t>24.05.202627.0</t>
+  </si>
+  <si>
+    <t>24.05.202628.0</t>
+  </si>
+  <si>
+    <t>24.05.202629.0</t>
+  </si>
+  <si>
+    <t>24.05.202630.0</t>
+  </si>
+  <si>
+    <t>24.05.202631.0</t>
+  </si>
+  <si>
+    <t>24.05.202632.0</t>
+  </si>
+  <si>
+    <t>24.05.202633.0</t>
+  </si>
+  <si>
+    <t>24.05.202634.0</t>
+  </si>
+  <si>
+    <t>24.05.202635.0</t>
+  </si>
+  <si>
+    <t>24.05.202636.0</t>
+  </si>
+  <si>
+    <t>24.05.202637.0</t>
+  </si>
+  <si>
+    <t>24.05.202638.0</t>
+  </si>
+  <si>
+    <t>24.05.202639.0</t>
+  </si>
+  <si>
+    <t>24.05.202640.0</t>
+  </si>
+  <si>
+    <t>24.05.202641.0</t>
+  </si>
+  <si>
+    <t>24.05.202642.0</t>
+  </si>
+  <si>
+    <t>24.05.202643.0</t>
+  </si>
+  <si>
+    <t>24.05.202644.0</t>
+  </si>
+  <si>
+    <t>24.05.202645.0</t>
+  </si>
+  <si>
+    <t>24.05.202646.0</t>
+  </si>
+  <si>
+    <t>24.05.202647.0</t>
+  </si>
+  <si>
+    <t>24.05.202648.0</t>
+  </si>
+  <si>
+    <t>24.05.202649.0</t>
+  </si>
+  <si>
+    <t>24.05.202650.0</t>
+  </si>
+  <si>
+    <t>24.05.202651.0</t>
+  </si>
+  <si>
+    <t>24.05.202652.0</t>
+  </si>
+  <si>
+    <t>24.05.202653.0</t>
+  </si>
+  <si>
+    <t>24.05.202654.0</t>
+  </si>
+  <si>
+    <t>24.05.202655.0</t>
+  </si>
+  <si>
+    <t>24.05.202656.0</t>
+  </si>
+  <si>
+    <t>24.05.202657.0</t>
+  </si>
+  <si>
+    <t>24.05.202658.0</t>
+  </si>
+  <si>
+    <t>24.05.202659.0</t>
+  </si>
+  <si>
+    <t>24.05.202660.0</t>
+  </si>
+  <si>
+    <t>24.05.202661.0</t>
+  </si>
+  <si>
+    <t>24.05.202662.0</t>
+  </si>
+  <si>
+    <t>24.05.202663.0</t>
+  </si>
+  <si>
+    <t>24.05.202664.0</t>
+  </si>
+  <si>
+    <t>24.05.202665.0</t>
+  </si>
+  <si>
+    <t>24.05.202666.0</t>
+  </si>
+  <si>
+    <t>24.05.202667.0</t>
+  </si>
+  <si>
+    <t>24.05.202668.0</t>
+  </si>
+  <si>
+    <t>24.05.202669.0</t>
+  </si>
+  <si>
+    <t>24.05.202670.0</t>
+  </si>
+  <si>
+    <t>24.05.202671.0</t>
+  </si>
+  <si>
+    <t>24.05.202672.0</t>
+  </si>
+  <si>
+    <t>24.05.202673.0</t>
+  </si>
+  <si>
+    <t>24.05.202674.0</t>
+  </si>
+  <si>
+    <t>24.05.202675.0</t>
+  </si>
+  <si>
+    <t>24.05.202676.0</t>
+  </si>
+  <si>
+    <t>24.05.202677.0</t>
+  </si>
+  <si>
+    <t>24.05.202678.0</t>
+  </si>
+  <si>
+    <t>24.05.202679.0</t>
+  </si>
+  <si>
+    <t>24.05.202680.0</t>
+  </si>
+  <si>
+    <t>24.05.202681.0</t>
+  </si>
+  <si>
+    <t>24.05.202682.0</t>
+  </si>
+  <si>
+    <t>24.05.202683.0</t>
+  </si>
+  <si>
+    <t>24.05.202684.0</t>
+  </si>
+  <si>
+    <t>24.05.202685.0</t>
+  </si>
+  <si>
+    <t>24.05.202686.0</t>
+  </si>
+  <si>
+    <t>24.05.202687.0</t>
+  </si>
+  <si>
+    <t>24.05.202688.0</t>
+  </si>
+  <si>
+    <t>24.05.202689.0</t>
+  </si>
+  <si>
+    <t>24.05.202690.0</t>
+  </si>
+  <si>
+    <t>24.05.202691.0</t>
+  </si>
+  <si>
+    <t>24.05.202692.0</t>
+  </si>
+  <si>
+    <t>24.05.202693.0</t>
+  </si>
+  <si>
+    <t>24.05.202694.0</t>
+  </si>
+  <si>
+    <t>24.05.202695.0</t>
+  </si>
+  <si>
+    <t>24.05.202696.0</t>
+  </si>
+  <si>
+    <t>25.05.20261.0</t>
+  </si>
+  <si>
+    <t>25.05.20262.0</t>
+  </si>
+  <si>
+    <t>25.05.20263.0</t>
+  </si>
+  <si>
+    <t>25.05.20264.0</t>
+  </si>
+  <si>
+    <t>25.05.20265.0</t>
+  </si>
+  <si>
+    <t>25.05.20266.0</t>
+  </si>
+  <si>
+    <t>25.05.20267.0</t>
+  </si>
+  <si>
+    <t>25.05.20268.0</t>
+  </si>
+  <si>
+    <t>25.05.20269.0</t>
+  </si>
+  <si>
+    <t>25.05.202610.0</t>
+  </si>
+  <si>
+    <t>25.05.202611.0</t>
+  </si>
+  <si>
+    <t>25.05.202612.0</t>
+  </si>
+  <si>
+    <t>25.05.202613.0</t>
+  </si>
+  <si>
+    <t>25.05.202614.0</t>
+  </si>
+  <si>
+    <t>25.05.202615.0</t>
+  </si>
+  <si>
+    <t>25.05.202616.0</t>
+  </si>
+  <si>
+    <t>25.05.202617.0</t>
+  </si>
+  <si>
+    <t>25.05.202618.0</t>
+  </si>
+  <si>
+    <t>25.05.202619.0</t>
+  </si>
+  <si>
+    <t>25.05.202620.0</t>
+  </si>
+  <si>
+    <t>25.05.202621.0</t>
+  </si>
+  <si>
+    <t>25.05.202622.0</t>
+  </si>
+  <si>
+    <t>25.05.202623.0</t>
+  </si>
+  <si>
+    <t>25.05.202624.0</t>
+  </si>
+  <si>
+    <t>25.05.202625.0</t>
+  </si>
+  <si>
+    <t>25.05.202626.0</t>
+  </si>
+  <si>
+    <t>25.05.202627.0</t>
+  </si>
+  <si>
+    <t>25.05.202628.0</t>
+  </si>
+  <si>
+    <t>25.05.202629.0</t>
+  </si>
+  <si>
+    <t>25.05.202630.0</t>
+  </si>
+  <si>
+    <t>25.05.202631.0</t>
+  </si>
+  <si>
+    <t>25.05.202632.0</t>
+  </si>
+  <si>
+    <t>25.05.202633.0</t>
+  </si>
+  <si>
+    <t>25.05.202634.0</t>
+  </si>
+  <si>
+    <t>25.05.202635.0</t>
+  </si>
+  <si>
+    <t>25.05.202636.0</t>
+  </si>
+  <si>
+    <t>25.05.202637.0</t>
+  </si>
+  <si>
+    <t>25.05.202638.0</t>
+  </si>
+  <si>
+    <t>25.05.202639.0</t>
+  </si>
+  <si>
+    <t>25.05.202640.0</t>
+  </si>
+  <si>
+    <t>25.05.202641.0</t>
+  </si>
+  <si>
+    <t>25.05.202642.0</t>
+  </si>
+  <si>
+    <t>25.05.202643.0</t>
+  </si>
+  <si>
+    <t>25.05.202644.0</t>
+  </si>
+  <si>
+    <t>25.05.202645.0</t>
+  </si>
+  <si>
+    <t>25.05.202646.0</t>
+  </si>
+  <si>
+    <t>25.05.202647.0</t>
+  </si>
+  <si>
+    <t>25.05.202648.0</t>
+  </si>
+  <si>
+    <t>25.05.202649.0</t>
+  </si>
+  <si>
+    <t>25.05.202650.0</t>
+  </si>
+  <si>
+    <t>25.05.202651.0</t>
+  </si>
+  <si>
+    <t>25.05.202652.0</t>
+  </si>
+  <si>
+    <t>25.05.202653.0</t>
+  </si>
+  <si>
+    <t>25.05.202654.0</t>
+  </si>
+  <si>
+    <t>25.05.202655.0</t>
+  </si>
+  <si>
+    <t>25.05.202656.0</t>
+  </si>
+  <si>
+    <t>25.05.202657.0</t>
+  </si>
+  <si>
+    <t>25.05.202658.0</t>
+  </si>
+  <si>
+    <t>25.05.202659.0</t>
+  </si>
+  <si>
+    <t>25.05.202660.0</t>
+  </si>
+  <si>
+    <t>25.05.202661.0</t>
+  </si>
+  <si>
+    <t>25.05.202662.0</t>
+  </si>
+  <si>
+    <t>25.05.202663.0</t>
+  </si>
+  <si>
+    <t>25.05.202664.0</t>
+  </si>
+  <si>
+    <t>25.05.202665.0</t>
+  </si>
+  <si>
+    <t>25.05.202666.0</t>
+  </si>
+  <si>
+    <t>25.05.202667.0</t>
+  </si>
+  <si>
+    <t>25.05.202668.0</t>
+  </si>
+  <si>
+    <t>25.05.202669.0</t>
+  </si>
+  <si>
+    <t>25.05.202670.0</t>
+  </si>
+  <si>
+    <t>25.05.202671.0</t>
+  </si>
+  <si>
+    <t>25.05.202672.0</t>
+  </si>
+  <si>
+    <t>25.05.202673.0</t>
+  </si>
+  <si>
+    <t>25.05.202674.0</t>
+  </si>
+  <si>
+    <t>25.05.202675.0</t>
+  </si>
+  <si>
+    <t>25.05.202676.0</t>
+  </si>
+  <si>
+    <t>25.05.202677.0</t>
+  </si>
+  <si>
+    <t>25.05.202678.0</t>
+  </si>
+  <si>
+    <t>25.05.202679.0</t>
+  </si>
+  <si>
+    <t>25.05.202680.0</t>
+  </si>
+  <si>
+    <t>25.05.202681.0</t>
+  </si>
+  <si>
+    <t>25.05.202682.0</t>
+  </si>
+  <si>
+    <t>25.05.202683.0</t>
+  </si>
+  <si>
+    <t>25.05.202684.0</t>
+  </si>
+  <si>
+    <t>25.05.202685.0</t>
+  </si>
+  <si>
+    <t>25.05.202686.0</t>
+  </si>
+  <si>
+    <t>25.05.202687.0</t>
+  </si>
+  <si>
+    <t>25.05.202688.0</t>
+  </si>
+  <si>
+    <t>25.05.202689.0</t>
+  </si>
+  <si>
+    <t>25.05.202690.0</t>
+  </si>
+  <si>
+    <t>25.05.202691.0</t>
+  </si>
+  <si>
+    <t>25.05.202692.0</t>
+  </si>
+  <si>
+    <t>25.05.202693.0</t>
+  </si>
+  <si>
+    <t>25.05.202694.0</t>
+  </si>
+  <si>
+    <t>25.05.202695.0</t>
+  </si>
+  <si>
+    <t>25.05.202696.0</t>
+  </si>
+  <si>
+    <t>26.05.20261.0</t>
+  </si>
+  <si>
+    <t>26.05.20262.0</t>
+  </si>
+  <si>
+    <t>26.05.20263.0</t>
+  </si>
+  <si>
+    <t>26.05.20264.0</t>
+  </si>
+  <si>
+    <t>26.05.20265.0</t>
+  </si>
+  <si>
+    <t>26.05.20266.0</t>
+  </si>
+  <si>
+    <t>26.05.20267.0</t>
+  </si>
+  <si>
+    <t>26.05.20268.0</t>
+  </si>
+  <si>
+    <t>26.05.20269.0</t>
+  </si>
+  <si>
+    <t>26.05.202610.0</t>
+  </si>
+  <si>
+    <t>26.05.202611.0</t>
+  </si>
+  <si>
+    <t>26.05.202612.0</t>
+  </si>
+  <si>
+    <t>26.05.202613.0</t>
+  </si>
+  <si>
+    <t>26.05.202614.0</t>
+  </si>
+  <si>
+    <t>26.05.202615.0</t>
+  </si>
+  <si>
+    <t>26.05.202616.0</t>
+  </si>
+  <si>
+    <t>26.05.202617.0</t>
+  </si>
+  <si>
+    <t>26.05.202618.0</t>
+  </si>
+  <si>
+    <t>26.05.202619.0</t>
+  </si>
+  <si>
+    <t>26.05.202620.0</t>
+  </si>
+  <si>
+    <t>26.05.202621.0</t>
+  </si>
+  <si>
+    <t>26.05.202622.0</t>
+  </si>
+  <si>
+    <t>26.05.202623.0</t>
+  </si>
+  <si>
+    <t>26.05.202624.0</t>
+  </si>
+  <si>
+    <t>26.05.202625.0</t>
+  </si>
+  <si>
+    <t>26.05.202626.0</t>
+  </si>
+  <si>
+    <t>26.05.202627.0</t>
+  </si>
+  <si>
+    <t>26.05.202628.0</t>
+  </si>
+  <si>
+    <t>26.05.202629.0</t>
+  </si>
+  <si>
+    <t>26.05.202630.0</t>
+  </si>
+  <si>
+    <t>26.05.202631.0</t>
+  </si>
+  <si>
+    <t>26.05.202632.0</t>
+  </si>
+  <si>
+    <t>26.05.202633.0</t>
+  </si>
+  <si>
+    <t>26.05.202634.0</t>
+  </si>
+  <si>
+    <t>26.05.202635.0</t>
+  </si>
+  <si>
+    <t>26.05.202636.0</t>
+  </si>
+  <si>
+    <t>26.05.202637.0</t>
+  </si>
+  <si>
+    <t>26.05.202638.0</t>
+  </si>
+  <si>
+    <t>26.05.202639.0</t>
+  </si>
+  <si>
+    <t>26.05.202640.0</t>
+  </si>
+  <si>
+    <t>26.05.202641.0</t>
+  </si>
+  <si>
+    <t>26.05.202642.0</t>
+  </si>
+  <si>
+    <t>26.05.202643.0</t>
+  </si>
+  <si>
+    <t>26.05.202644.0</t>
+  </si>
+  <si>
+    <t>26.05.202645.0</t>
+  </si>
+  <si>
+    <t>26.05.202646.0</t>
+  </si>
+  <si>
+    <t>26.05.202647.0</t>
+  </si>
+  <si>
+    <t>26.05.202648.0</t>
+  </si>
+  <si>
+    <t>26.05.202649.0</t>
+  </si>
+  <si>
+    <t>26.05.202650.0</t>
+  </si>
+  <si>
+    <t>26.05.202651.0</t>
+  </si>
+  <si>
+    <t>26.05.202652.0</t>
+  </si>
+  <si>
+    <t>26.05.202653.0</t>
+  </si>
+  <si>
+    <t>26.05.202654.0</t>
+  </si>
+  <si>
+    <t>26.05.202655.0</t>
+  </si>
+  <si>
+    <t>26.05.202656.0</t>
+  </si>
+  <si>
+    <t>26.05.202657.0</t>
+  </si>
+  <si>
+    <t>26.05.202658.0</t>
+  </si>
+  <si>
+    <t>26.05.202659.0</t>
+  </si>
+  <si>
+    <t>26.05.202660.0</t>
+  </si>
+  <si>
+    <t>26.05.202661.0</t>
+  </si>
+  <si>
+    <t>26.05.202662.0</t>
+  </si>
+  <si>
+    <t>26.05.202663.0</t>
+  </si>
+  <si>
+    <t>26.05.202664.0</t>
+  </si>
+  <si>
+    <t>26.05.202665.0</t>
+  </si>
+  <si>
+    <t>26.05.202666.0</t>
+  </si>
+  <si>
+    <t>26.05.202667.0</t>
+  </si>
+  <si>
+    <t>26.05.202668.0</t>
+  </si>
+  <si>
+    <t>26.05.202669.0</t>
+  </si>
+  <si>
+    <t>26.05.202670.0</t>
+  </si>
+  <si>
+    <t>26.05.202671.0</t>
+  </si>
+  <si>
+    <t>26.05.202672.0</t>
+  </si>
+  <si>
+    <t>26.05.202673.0</t>
+  </si>
+  <si>
+    <t>26.05.202674.0</t>
+  </si>
+  <si>
+    <t>26.05.202675.0</t>
+  </si>
+  <si>
+    <t>26.05.202676.0</t>
+  </si>
+  <si>
+    <t>26.05.202677.0</t>
+  </si>
+  <si>
+    <t>26.05.202678.0</t>
+  </si>
+  <si>
+    <t>26.05.202679.0</t>
+  </si>
+  <si>
+    <t>26.05.202680.0</t>
+  </si>
+  <si>
+    <t>26.05.202681.0</t>
+  </si>
+  <si>
+    <t>26.05.202682.0</t>
+  </si>
+  <si>
+    <t>26.05.202683.0</t>
+  </si>
+  <si>
+    <t>26.05.202684.0</t>
+  </si>
+  <si>
+    <t>26.05.202685.0</t>
+  </si>
+  <si>
+    <t>26.05.202686.0</t>
+  </si>
+  <si>
+    <t>26.05.202687.0</t>
+  </si>
+  <si>
+    <t>26.05.202688.0</t>
+  </si>
+  <si>
+    <t>26.05.202689.0</t>
+  </si>
+  <si>
+    <t>26.05.202690.0</t>
+  </si>
+  <si>
+    <t>26.05.202691.0</t>
+  </si>
+  <si>
+    <t>26.05.202692.0</t>
+  </si>
+  <si>
+    <t>26.05.202693.0</t>
+  </si>
+  <si>
+    <t>26.05.202694.0</t>
+  </si>
+  <si>
+    <t>26.05.202695.0</t>
+  </si>
+  <si>
+    <t>26.05.202696.0</t>
   </si>
 </sst>
 </file>
@@ -6723,7 +7875,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D2113"/>
+  <dimension ref="A1:D2497"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -26908,7 +28060,7 @@
         <v>1</v>
       </c>
       <c r="C1442">
-        <v>5480</v>
+        <v>5470</v>
       </c>
       <c r="D1442" t="s">
         <v>1444</v>
@@ -26922,7 +28074,7 @@
         <v>2</v>
       </c>
       <c r="C1443">
-        <v>5440</v>
+        <v>5400</v>
       </c>
       <c r="D1443" t="s">
         <v>1445</v>
@@ -26936,7 +28088,7 @@
         <v>3</v>
       </c>
       <c r="C1444">
-        <v>5380</v>
+        <v>5350</v>
       </c>
       <c r="D1444" t="s">
         <v>1446</v>
@@ -26964,7 +28116,7 @@
         <v>5</v>
       </c>
       <c r="C1446">
-        <v>5240</v>
+        <v>5220</v>
       </c>
       <c r="D1446" t="s">
         <v>1448</v>
@@ -26978,7 +28130,7 @@
         <v>6</v>
       </c>
       <c r="C1447">
-        <v>5190</v>
+        <v>5170</v>
       </c>
       <c r="D1447" t="s">
         <v>1449</v>
@@ -27006,7 +28158,7 @@
         <v>8</v>
       </c>
       <c r="C1449">
-        <v>5100</v>
+        <v>5110</v>
       </c>
       <c r="D1449" t="s">
         <v>1451</v>
@@ -27020,7 +28172,7 @@
         <v>9</v>
       </c>
       <c r="C1450">
-        <v>5060</v>
+        <v>5070</v>
       </c>
       <c r="D1450" t="s">
         <v>1452</v>
@@ -27034,7 +28186,7 @@
         <v>10</v>
       </c>
       <c r="C1451">
-        <v>5030</v>
+        <v>5050</v>
       </c>
       <c r="D1451" t="s">
         <v>1453</v>
@@ -27048,7 +28200,7 @@
         <v>11</v>
       </c>
       <c r="C1452">
-        <v>5000</v>
+        <v>5040</v>
       </c>
       <c r="D1452" t="s">
         <v>1454</v>
@@ -27062,7 +28214,7 @@
         <v>12</v>
       </c>
       <c r="C1453">
-        <v>4990</v>
+        <v>5030</v>
       </c>
       <c r="D1453" t="s">
         <v>1455</v>
@@ -27076,7 +28228,7 @@
         <v>13</v>
       </c>
       <c r="C1454">
-        <v>4980</v>
+        <v>5010</v>
       </c>
       <c r="D1454" t="s">
         <v>1456</v>
@@ -27090,7 +28242,7 @@
         <v>14</v>
       </c>
       <c r="C1455">
-        <v>4970</v>
+        <v>5000</v>
       </c>
       <c r="D1455" t="s">
         <v>1457</v>
@@ -27104,7 +28256,7 @@
         <v>15</v>
       </c>
       <c r="C1456">
-        <v>4970</v>
+        <v>5000</v>
       </c>
       <c r="D1456" t="s">
         <v>1458</v>
@@ -27118,7 +28270,7 @@
         <v>16</v>
       </c>
       <c r="C1457">
-        <v>4960</v>
+        <v>5000</v>
       </c>
       <c r="D1457" t="s">
         <v>1459</v>
@@ -27132,7 +28284,7 @@
         <v>17</v>
       </c>
       <c r="C1458">
-        <v>4960</v>
+        <v>4980</v>
       </c>
       <c r="D1458" t="s">
         <v>1460</v>
@@ -27146,7 +28298,7 @@
         <v>18</v>
       </c>
       <c r="C1459">
-        <v>4950</v>
+        <v>4980</v>
       </c>
       <c r="D1459" t="s">
         <v>1461</v>
@@ -27160,7 +28312,7 @@
         <v>19</v>
       </c>
       <c r="C1460">
-        <v>4950</v>
+        <v>4980</v>
       </c>
       <c r="D1460" t="s">
         <v>1462</v>
@@ -27174,7 +28326,7 @@
         <v>20</v>
       </c>
       <c r="C1461">
-        <v>4950</v>
+        <v>4980</v>
       </c>
       <c r="D1461" t="s">
         <v>1463</v>
@@ -27188,7 +28340,7 @@
         <v>21</v>
       </c>
       <c r="C1462">
-        <v>4950</v>
+        <v>4980</v>
       </c>
       <c r="D1462" t="s">
         <v>1464</v>
@@ -27202,7 +28354,7 @@
         <v>22</v>
       </c>
       <c r="C1463">
-        <v>4950</v>
+        <v>4980</v>
       </c>
       <c r="D1463" t="s">
         <v>1465</v>
@@ -27216,7 +28368,7 @@
         <v>23</v>
       </c>
       <c r="C1464">
-        <v>4950</v>
+        <v>4980</v>
       </c>
       <c r="D1464" t="s">
         <v>1466</v>
@@ -27244,7 +28396,7 @@
         <v>25</v>
       </c>
       <c r="C1466">
-        <v>4980</v>
+        <v>4910</v>
       </c>
       <c r="D1466" t="s">
         <v>1468</v>
@@ -27258,7 +28410,7 @@
         <v>26</v>
       </c>
       <c r="C1467">
-        <v>4990</v>
+        <v>4900</v>
       </c>
       <c r="D1467" t="s">
         <v>1469</v>
@@ -27272,7 +28424,7 @@
         <v>27</v>
       </c>
       <c r="C1468">
-        <v>5000</v>
+        <v>4900</v>
       </c>
       <c r="D1468" t="s">
         <v>1470</v>
@@ -27286,7 +28438,7 @@
         <v>28</v>
       </c>
       <c r="C1469">
-        <v>5000</v>
+        <v>4900</v>
       </c>
       <c r="D1469" t="s">
         <v>1471</v>
@@ -27300,7 +28452,7 @@
         <v>29</v>
       </c>
       <c r="C1470">
-        <v>5000</v>
+        <v>4900</v>
       </c>
       <c r="D1470" t="s">
         <v>1472</v>
@@ -27314,7 +28466,7 @@
         <v>30</v>
       </c>
       <c r="C1471">
-        <v>4980</v>
+        <v>4880</v>
       </c>
       <c r="D1471" t="s">
         <v>1473</v>
@@ -27328,7 +28480,7 @@
         <v>31</v>
       </c>
       <c r="C1472">
-        <v>4950</v>
+        <v>4850</v>
       </c>
       <c r="D1472" t="s">
         <v>1474</v>
@@ -27342,7 +28494,7 @@
         <v>32</v>
       </c>
       <c r="C1473">
-        <v>4920</v>
+        <v>4770</v>
       </c>
       <c r="D1473" t="s">
         <v>1475</v>
@@ -27356,7 +28508,7 @@
         <v>33</v>
       </c>
       <c r="C1474">
-        <v>4870</v>
+        <v>4680</v>
       </c>
       <c r="D1474" t="s">
         <v>1476</v>
@@ -27370,7 +28522,7 @@
         <v>34</v>
       </c>
       <c r="C1475">
-        <v>4800</v>
+        <v>4590</v>
       </c>
       <c r="D1475" t="s">
         <v>1477</v>
@@ -27384,7 +28536,7 @@
         <v>35</v>
       </c>
       <c r="C1476">
-        <v>4730</v>
+        <v>4510</v>
       </c>
       <c r="D1476" t="s">
         <v>1478</v>
@@ -27398,7 +28550,7 @@
         <v>36</v>
       </c>
       <c r="C1477">
-        <v>4650</v>
+        <v>4430</v>
       </c>
       <c r="D1477" t="s">
         <v>1479</v>
@@ -27412,7 +28564,7 @@
         <v>37</v>
       </c>
       <c r="C1478">
-        <v>4560</v>
+        <v>4330</v>
       </c>
       <c r="D1478" t="s">
         <v>1480</v>
@@ -27426,7 +28578,7 @@
         <v>38</v>
       </c>
       <c r="C1479">
-        <v>4470</v>
+        <v>4240</v>
       </c>
       <c r="D1479" t="s">
         <v>1481</v>
@@ -27440,7 +28592,7 @@
         <v>39</v>
       </c>
       <c r="C1480">
-        <v>4370</v>
+        <v>4170</v>
       </c>
       <c r="D1480" t="s">
         <v>1482</v>
@@ -27454,7 +28606,7 @@
         <v>40</v>
       </c>
       <c r="C1481">
-        <v>4280</v>
+        <v>4070</v>
       </c>
       <c r="D1481" t="s">
         <v>1483</v>
@@ -27468,7 +28620,7 @@
         <v>41</v>
       </c>
       <c r="C1482">
-        <v>4190</v>
+        <v>3990</v>
       </c>
       <c r="D1482" t="s">
         <v>1484</v>
@@ -27482,7 +28634,7 @@
         <v>42</v>
       </c>
       <c r="C1483">
-        <v>4110</v>
+        <v>3910</v>
       </c>
       <c r="D1483" t="s">
         <v>1485</v>
@@ -27496,7 +28648,7 @@
         <v>43</v>
       </c>
       <c r="C1484">
-        <v>4040</v>
+        <v>3840</v>
       </c>
       <c r="D1484" t="s">
         <v>1486</v>
@@ -27510,7 +28662,7 @@
         <v>44</v>
       </c>
       <c r="C1485">
-        <v>3980</v>
+        <v>3770</v>
       </c>
       <c r="D1485" t="s">
         <v>1487</v>
@@ -27524,7 +28676,7 @@
         <v>45</v>
       </c>
       <c r="C1486">
-        <v>3930</v>
+        <v>3700</v>
       </c>
       <c r="D1486" t="s">
         <v>1488</v>
@@ -27538,7 +28690,7 @@
         <v>46</v>
       </c>
       <c r="C1487">
-        <v>3890</v>
+        <v>3660</v>
       </c>
       <c r="D1487" t="s">
         <v>1489</v>
@@ -27552,7 +28704,7 @@
         <v>47</v>
       </c>
       <c r="C1488">
-        <v>3860</v>
+        <v>3630</v>
       </c>
       <c r="D1488" t="s">
         <v>1490</v>
@@ -27566,7 +28718,7 @@
         <v>48</v>
       </c>
       <c r="C1489">
-        <v>3830</v>
+        <v>3620</v>
       </c>
       <c r="D1489" t="s">
         <v>1491</v>
@@ -27580,7 +28732,7 @@
         <v>49</v>
       </c>
       <c r="C1490">
-        <v>3810</v>
+        <v>3600</v>
       </c>
       <c r="D1490" t="s">
         <v>1492</v>
@@ -27594,7 +28746,7 @@
         <v>50</v>
       </c>
       <c r="C1491">
-        <v>3790</v>
+        <v>3600</v>
       </c>
       <c r="D1491" t="s">
         <v>1493</v>
@@ -27608,7 +28760,7 @@
         <v>51</v>
       </c>
       <c r="C1492">
-        <v>3770</v>
+        <v>3600</v>
       </c>
       <c r="D1492" t="s">
         <v>1494</v>
@@ -27622,7 +28774,7 @@
         <v>52</v>
       </c>
       <c r="C1493">
-        <v>3760</v>
+        <v>3600</v>
       </c>
       <c r="D1493" t="s">
         <v>1495</v>
@@ -27636,7 +28788,7 @@
         <v>53</v>
       </c>
       <c r="C1494">
-        <v>3750</v>
+        <v>3610</v>
       </c>
       <c r="D1494" t="s">
         <v>1496</v>
@@ -27650,7 +28802,7 @@
         <v>54</v>
       </c>
       <c r="C1495">
-        <v>3740</v>
+        <v>3630</v>
       </c>
       <c r="D1495" t="s">
         <v>1497</v>
@@ -27664,7 +28816,7 @@
         <v>55</v>
       </c>
       <c r="C1496">
-        <v>3740</v>
+        <v>3650</v>
       </c>
       <c r="D1496" t="s">
         <v>1498</v>
@@ -27678,7 +28830,7 @@
         <v>56</v>
       </c>
       <c r="C1497">
-        <v>3750</v>
+        <v>3680</v>
       </c>
       <c r="D1497" t="s">
         <v>1499</v>
@@ -27692,7 +28844,7 @@
         <v>57</v>
       </c>
       <c r="C1498">
-        <v>3780</v>
+        <v>3730</v>
       </c>
       <c r="D1498" t="s">
         <v>1500</v>
@@ -27706,7 +28858,7 @@
         <v>58</v>
       </c>
       <c r="C1499">
-        <v>3810</v>
+        <v>3780</v>
       </c>
       <c r="D1499" t="s">
         <v>1501</v>
@@ -27720,7 +28872,7 @@
         <v>59</v>
       </c>
       <c r="C1500">
-        <v>3850</v>
+        <v>3820</v>
       </c>
       <c r="D1500" t="s">
         <v>1502</v>
@@ -27734,7 +28886,7 @@
         <v>60</v>
       </c>
       <c r="C1501">
-        <v>3900</v>
+        <v>3880</v>
       </c>
       <c r="D1501" t="s">
         <v>1503</v>
@@ -27748,7 +28900,7 @@
         <v>61</v>
       </c>
       <c r="C1502">
-        <v>3960</v>
+        <v>3940</v>
       </c>
       <c r="D1502" t="s">
         <v>1504</v>
@@ -27762,7 +28914,7 @@
         <v>62</v>
       </c>
       <c r="C1503">
-        <v>4020</v>
+        <v>4010</v>
       </c>
       <c r="D1503" t="s">
         <v>1505</v>
@@ -27776,7 +28928,7 @@
         <v>63</v>
       </c>
       <c r="C1504">
-        <v>4090</v>
+        <v>4080</v>
       </c>
       <c r="D1504" t="s">
         <v>1506</v>
@@ -27804,7 +28956,7 @@
         <v>65</v>
       </c>
       <c r="C1506">
-        <v>4270</v>
+        <v>4300</v>
       </c>
       <c r="D1506" t="s">
         <v>1508</v>
@@ -27818,7 +28970,7 @@
         <v>66</v>
       </c>
       <c r="C1507">
-        <v>4380</v>
+        <v>4420</v>
       </c>
       <c r="D1507" t="s">
         <v>1509</v>
@@ -27832,7 +28984,7 @@
         <v>67</v>
       </c>
       <c r="C1508">
-        <v>4490</v>
+        <v>4560</v>
       </c>
       <c r="D1508" t="s">
         <v>1510</v>
@@ -27846,7 +28998,7 @@
         <v>68</v>
       </c>
       <c r="C1509">
-        <v>4620</v>
+        <v>4700</v>
       </c>
       <c r="D1509" t="s">
         <v>1511</v>
@@ -27860,7 +29012,7 @@
         <v>69</v>
       </c>
       <c r="C1510">
-        <v>4760</v>
+        <v>4840</v>
       </c>
       <c r="D1510" t="s">
         <v>1512</v>
@@ -27874,7 +29026,7 @@
         <v>70</v>
       </c>
       <c r="C1511">
-        <v>4900</v>
+        <v>4980</v>
       </c>
       <c r="D1511" t="s">
         <v>1513</v>
@@ -27888,7 +29040,7 @@
         <v>71</v>
       </c>
       <c r="C1512">
-        <v>5040</v>
+        <v>5120</v>
       </c>
       <c r="D1512" t="s">
         <v>1514</v>
@@ -27902,7 +29054,7 @@
         <v>72</v>
       </c>
       <c r="C1513">
-        <v>5170</v>
+        <v>5260</v>
       </c>
       <c r="D1513" t="s">
         <v>1515</v>
@@ -27916,7 +29068,7 @@
         <v>73</v>
       </c>
       <c r="C1514">
-        <v>5300</v>
+        <v>5420</v>
       </c>
       <c r="D1514" t="s">
         <v>1516</v>
@@ -27930,7 +29082,7 @@
         <v>74</v>
       </c>
       <c r="C1515">
-        <v>5420</v>
+        <v>5540</v>
       </c>
       <c r="D1515" t="s">
         <v>1517</v>
@@ -27944,7 +29096,7 @@
         <v>75</v>
       </c>
       <c r="C1516">
-        <v>5540</v>
+        <v>5660</v>
       </c>
       <c r="D1516" t="s">
         <v>1518</v>
@@ -27958,7 +29110,7 @@
         <v>76</v>
       </c>
       <c r="C1517">
-        <v>5670</v>
+        <v>5770</v>
       </c>
       <c r="D1517" t="s">
         <v>1519</v>
@@ -27972,7 +29124,7 @@
         <v>77</v>
       </c>
       <c r="C1518">
-        <v>5790</v>
+        <v>5870</v>
       </c>
       <c r="D1518" t="s">
         <v>1520</v>
@@ -27986,7 +29138,7 @@
         <v>78</v>
       </c>
       <c r="C1519">
-        <v>5920</v>
+        <v>5970</v>
       </c>
       <c r="D1519" t="s">
         <v>1521</v>
@@ -28000,7 +29152,7 @@
         <v>79</v>
       </c>
       <c r="C1520">
-        <v>6030</v>
+        <v>6050</v>
       </c>
       <c r="D1520" t="s">
         <v>1522</v>
@@ -28028,7 +29180,7 @@
         <v>81</v>
       </c>
       <c r="C1522">
-        <v>6230</v>
+        <v>6210</v>
       </c>
       <c r="D1522" t="s">
         <v>1524</v>
@@ -28042,7 +29194,7 @@
         <v>82</v>
       </c>
       <c r="C1523">
-        <v>6330</v>
+        <v>6280</v>
       </c>
       <c r="D1523" t="s">
         <v>1525</v>
@@ -28056,7 +29208,7 @@
         <v>83</v>
       </c>
       <c r="C1524">
-        <v>6390</v>
+        <v>6340</v>
       </c>
       <c r="D1524" t="s">
         <v>1526</v>
@@ -28084,7 +29236,7 @@
         <v>85</v>
       </c>
       <c r="C1526">
-        <v>6400</v>
+        <v>6430</v>
       </c>
       <c r="D1526" t="s">
         <v>1528</v>
@@ -28098,7 +29250,7 @@
         <v>86</v>
       </c>
       <c r="C1527">
-        <v>6400</v>
+        <v>6410</v>
       </c>
       <c r="D1527" t="s">
         <v>1529</v>
@@ -28112,7 +29264,7 @@
         <v>87</v>
       </c>
       <c r="C1528">
-        <v>6380</v>
+        <v>6370</v>
       </c>
       <c r="D1528" t="s">
         <v>1530</v>
@@ -28126,7 +29278,7 @@
         <v>88</v>
       </c>
       <c r="C1529">
-        <v>6320</v>
+        <v>6300</v>
       </c>
       <c r="D1529" t="s">
         <v>1531</v>
@@ -28140,7 +29292,7 @@
         <v>89</v>
       </c>
       <c r="C1530">
-        <v>6200</v>
+        <v>6160</v>
       </c>
       <c r="D1530" t="s">
         <v>1532</v>
@@ -28154,7 +29306,7 @@
         <v>90</v>
       </c>
       <c r="C1531">
-        <v>6100</v>
+        <v>6020</v>
       </c>
       <c r="D1531" t="s">
         <v>1533</v>
@@ -28168,7 +29320,7 @@
         <v>91</v>
       </c>
       <c r="C1532">
-        <v>5950</v>
+        <v>5880</v>
       </c>
       <c r="D1532" t="s">
         <v>1534</v>
@@ -28182,7 +29334,7 @@
         <v>92</v>
       </c>
       <c r="C1533">
-        <v>5830</v>
+        <v>5760</v>
       </c>
       <c r="D1533" t="s">
         <v>1535</v>
@@ -28196,7 +29348,7 @@
         <v>93</v>
       </c>
       <c r="C1534">
-        <v>5690</v>
+        <v>5660</v>
       </c>
       <c r="D1534" t="s">
         <v>1536</v>
@@ -28210,7 +29362,7 @@
         <v>94</v>
       </c>
       <c r="C1535">
-        <v>5540</v>
+        <v>5550</v>
       </c>
       <c r="D1535" t="s">
         <v>1537</v>
@@ -28224,7 +29376,7 @@
         <v>95</v>
       </c>
       <c r="C1536">
-        <v>5450</v>
+        <v>5440</v>
       </c>
       <c r="D1536" t="s">
         <v>1538</v>
@@ -28238,7 +29390,7 @@
         <v>96</v>
       </c>
       <c r="C1537">
-        <v>5340</v>
+        <v>5330</v>
       </c>
       <c r="D1537" t="s">
         <v>1539</v>
@@ -28252,7 +29404,7 @@
         <v>1</v>
       </c>
       <c r="C1538">
-        <v>5210</v>
+        <v>5140</v>
       </c>
       <c r="D1538" t="s">
         <v>1540</v>
@@ -28266,7 +29418,7 @@
         <v>2</v>
       </c>
       <c r="C1539">
-        <v>5140</v>
+        <v>5070</v>
       </c>
       <c r="D1539" t="s">
         <v>1541</v>
@@ -28280,7 +29432,7 @@
         <v>3</v>
       </c>
       <c r="C1540">
-        <v>5110</v>
+        <v>5020</v>
       </c>
       <c r="D1540" t="s">
         <v>1542</v>
@@ -28294,7 +29446,7 @@
         <v>4</v>
       </c>
       <c r="C1541">
-        <v>5040</v>
+        <v>4970</v>
       </c>
       <c r="D1541" t="s">
         <v>1543</v>
@@ -28308,7 +29460,7 @@
         <v>5</v>
       </c>
       <c r="C1542">
-        <v>4960</v>
+        <v>4900</v>
       </c>
       <c r="D1542" t="s">
         <v>1544</v>
@@ -28322,7 +29474,7 @@
         <v>6</v>
       </c>
       <c r="C1543">
-        <v>4900</v>
+        <v>4840</v>
       </c>
       <c r="D1543" t="s">
         <v>1545</v>
@@ -28336,7 +29488,7 @@
         <v>7</v>
       </c>
       <c r="C1544">
-        <v>4850</v>
+        <v>4790</v>
       </c>
       <c r="D1544" t="s">
         <v>1546</v>
@@ -28350,7 +29502,7 @@
         <v>8</v>
       </c>
       <c r="C1545">
-        <v>4810</v>
+        <v>4750</v>
       </c>
       <c r="D1545" t="s">
         <v>1547</v>
@@ -28364,7 +29516,7 @@
         <v>9</v>
       </c>
       <c r="C1546">
-        <v>4790</v>
+        <v>4720</v>
       </c>
       <c r="D1546" t="s">
         <v>1548</v>
@@ -28378,7 +29530,7 @@
         <v>10</v>
       </c>
       <c r="C1547">
-        <v>4770</v>
+        <v>4700</v>
       </c>
       <c r="D1547" t="s">
         <v>1549</v>
@@ -28392,7 +29544,7 @@
         <v>11</v>
       </c>
       <c r="C1548">
-        <v>4760</v>
+        <v>4690</v>
       </c>
       <c r="D1548" t="s">
         <v>1550</v>
@@ -28406,7 +29558,7 @@
         <v>12</v>
       </c>
       <c r="C1549">
-        <v>4740</v>
+        <v>4680</v>
       </c>
       <c r="D1549" t="s">
         <v>1551</v>
@@ -28420,7 +29572,7 @@
         <v>13</v>
       </c>
       <c r="C1550">
-        <v>4730</v>
+        <v>4650</v>
       </c>
       <c r="D1550" t="s">
         <v>1552</v>
@@ -28434,7 +29586,7 @@
         <v>14</v>
       </c>
       <c r="C1551">
-        <v>4710</v>
+        <v>4650</v>
       </c>
       <c r="D1551" t="s">
         <v>1553</v>
@@ -28448,7 +29600,7 @@
         <v>15</v>
       </c>
       <c r="C1552">
-        <v>4690</v>
+        <v>4650</v>
       </c>
       <c r="D1552" t="s">
         <v>1554</v>
@@ -28462,7 +29614,7 @@
         <v>16</v>
       </c>
       <c r="C1553">
-        <v>4680</v>
+        <v>4650</v>
       </c>
       <c r="D1553" t="s">
         <v>1555</v>
@@ -28476,7 +29628,7 @@
         <v>17</v>
       </c>
       <c r="C1554">
-        <v>4670</v>
+        <v>4650</v>
       </c>
       <c r="D1554" t="s">
         <v>1556</v>
@@ -28490,7 +29642,7 @@
         <v>18</v>
       </c>
       <c r="C1555">
-        <v>4660</v>
+        <v>4650</v>
       </c>
       <c r="D1555" t="s">
         <v>1557</v>
@@ -28518,7 +29670,7 @@
         <v>20</v>
       </c>
       <c r="C1557">
-        <v>4650</v>
+        <v>4640</v>
       </c>
       <c r="D1557" t="s">
         <v>1559</v>
@@ -28532,7 +29684,7 @@
         <v>21</v>
       </c>
       <c r="C1558">
-        <v>4640</v>
+        <v>4610</v>
       </c>
       <c r="D1558" t="s">
         <v>1560</v>
@@ -28546,7 +29698,7 @@
         <v>22</v>
       </c>
       <c r="C1559">
-        <v>4640</v>
+        <v>4600</v>
       </c>
       <c r="D1559" t="s">
         <v>1561</v>
@@ -28560,7 +29712,7 @@
         <v>23</v>
       </c>
       <c r="C1560">
-        <v>4630</v>
+        <v>4600</v>
       </c>
       <c r="D1560" t="s">
         <v>1562</v>
@@ -28574,7 +29726,7 @@
         <v>24</v>
       </c>
       <c r="C1561">
-        <v>4620</v>
+        <v>4590</v>
       </c>
       <c r="D1561" t="s">
         <v>1563</v>
@@ -28588,7 +29740,7 @@
         <v>25</v>
       </c>
       <c r="C1562">
-        <v>4610</v>
+        <v>4570</v>
       </c>
       <c r="D1562" t="s">
         <v>1564</v>
@@ -28602,7 +29754,7 @@
         <v>26</v>
       </c>
       <c r="C1563">
-        <v>4610</v>
+        <v>4570</v>
       </c>
       <c r="D1563" t="s">
         <v>1565</v>
@@ -28616,7 +29768,7 @@
         <v>27</v>
       </c>
       <c r="C1564">
-        <v>4610</v>
+        <v>4570</v>
       </c>
       <c r="D1564" t="s">
         <v>1566</v>
@@ -28630,7 +29782,7 @@
         <v>28</v>
       </c>
       <c r="C1565">
-        <v>4620</v>
+        <v>4570</v>
       </c>
       <c r="D1565" t="s">
         <v>1567</v>
@@ -28644,7 +29796,7 @@
         <v>29</v>
       </c>
       <c r="C1566">
-        <v>4630</v>
+        <v>4580</v>
       </c>
       <c r="D1566" t="s">
         <v>1568</v>
@@ -28658,7 +29810,7 @@
         <v>30</v>
       </c>
       <c r="C1567">
-        <v>4660</v>
+        <v>4600</v>
       </c>
       <c r="D1567" t="s">
         <v>1569</v>
@@ -28672,7 +29824,7 @@
         <v>31</v>
       </c>
       <c r="C1568">
-        <v>4690</v>
+        <v>4630</v>
       </c>
       <c r="D1568" t="s">
         <v>1570</v>
@@ -28686,7 +29838,7 @@
         <v>32</v>
       </c>
       <c r="C1569">
-        <v>4730</v>
+        <v>4670</v>
       </c>
       <c r="D1569" t="s">
         <v>1571</v>
@@ -28700,7 +29852,7 @@
         <v>33</v>
       </c>
       <c r="C1570">
-        <v>4760</v>
+        <v>4750</v>
       </c>
       <c r="D1570" t="s">
         <v>1572</v>
@@ -28714,7 +29866,7 @@
         <v>34</v>
       </c>
       <c r="C1571">
-        <v>4820</v>
+        <v>4800</v>
       </c>
       <c r="D1571" t="s">
         <v>1573</v>
@@ -28728,7 +29880,7 @@
         <v>35</v>
       </c>
       <c r="C1572">
-        <v>4850</v>
+        <v>4820</v>
       </c>
       <c r="D1572" t="s">
         <v>1574</v>
@@ -28742,7 +29894,7 @@
         <v>36</v>
       </c>
       <c r="C1573">
-        <v>4840</v>
+        <v>4830</v>
       </c>
       <c r="D1573" t="s">
         <v>1575</v>
@@ -28756,7 +29908,7 @@
         <v>37</v>
       </c>
       <c r="C1574">
-        <v>4830</v>
+        <v>4820</v>
       </c>
       <c r="D1574" t="s">
         <v>1576</v>
@@ -28770,7 +29922,7 @@
         <v>38</v>
       </c>
       <c r="C1575">
-        <v>4820</v>
+        <v>4810</v>
       </c>
       <c r="D1575" t="s">
         <v>1577</v>
@@ -28784,7 +29936,7 @@
         <v>39</v>
       </c>
       <c r="C1576">
-        <v>4790</v>
+        <v>4800</v>
       </c>
       <c r="D1576" t="s">
         <v>1578</v>
@@ -28798,7 +29950,7 @@
         <v>40</v>
       </c>
       <c r="C1577">
-        <v>4750</v>
+        <v>4770</v>
       </c>
       <c r="D1577" t="s">
         <v>1579</v>
@@ -28812,7 +29964,7 @@
         <v>41</v>
       </c>
       <c r="C1578">
-        <v>4700</v>
+        <v>4730</v>
       </c>
       <c r="D1578" t="s">
         <v>1580</v>
@@ -28826,7 +29978,7 @@
         <v>42</v>
       </c>
       <c r="C1579">
-        <v>4660</v>
+        <v>4680</v>
       </c>
       <c r="D1579" t="s">
         <v>1581</v>
@@ -28840,7 +29992,7 @@
         <v>43</v>
       </c>
       <c r="C1580">
-        <v>4610</v>
+        <v>4620</v>
       </c>
       <c r="D1580" t="s">
         <v>1582</v>
@@ -28854,7 +30006,7 @@
         <v>44</v>
       </c>
       <c r="C1581">
-        <v>4570</v>
+        <v>4550</v>
       </c>
       <c r="D1581" t="s">
         <v>1583</v>
@@ -28868,7 +30020,7 @@
         <v>45</v>
       </c>
       <c r="C1582">
-        <v>4530</v>
+        <v>4460</v>
       </c>
       <c r="D1582" t="s">
         <v>1584</v>
@@ -28882,7 +30034,7 @@
         <v>46</v>
       </c>
       <c r="C1583">
-        <v>4500</v>
+        <v>4390</v>
       </c>
       <c r="D1583" t="s">
         <v>1585</v>
@@ -28896,7 +30048,7 @@
         <v>47</v>
       </c>
       <c r="C1584">
-        <v>4480</v>
+        <v>4340</v>
       </c>
       <c r="D1584" t="s">
         <v>1586</v>
@@ -28910,7 +30062,7 @@
         <v>48</v>
       </c>
       <c r="C1585">
-        <v>4460</v>
+        <v>4290</v>
       </c>
       <c r="D1585" t="s">
         <v>1587</v>
@@ -28924,7 +30076,7 @@
         <v>49</v>
       </c>
       <c r="C1586">
-        <v>4450</v>
+        <v>4220</v>
       </c>
       <c r="D1586" t="s">
         <v>1588</v>
@@ -28938,7 +30090,7 @@
         <v>50</v>
       </c>
       <c r="C1587">
-        <v>4440</v>
+        <v>4170</v>
       </c>
       <c r="D1587" t="s">
         <v>1589</v>
@@ -28952,7 +30104,7 @@
         <v>51</v>
       </c>
       <c r="C1588">
-        <v>4430</v>
+        <v>4130</v>
       </c>
       <c r="D1588" t="s">
         <v>1590</v>
@@ -28966,7 +30118,7 @@
         <v>52</v>
       </c>
       <c r="C1589">
-        <v>4420</v>
+        <v>4100</v>
       </c>
       <c r="D1589" t="s">
         <v>1591</v>
@@ -28980,7 +30132,7 @@
         <v>53</v>
       </c>
       <c r="C1590">
-        <v>4410</v>
+        <v>4070</v>
       </c>
       <c r="D1590" t="s">
         <v>1592</v>
@@ -28994,7 +30146,7 @@
         <v>54</v>
       </c>
       <c r="C1591">
-        <v>4400</v>
+        <v>4040</v>
       </c>
       <c r="D1591" t="s">
         <v>1593</v>
@@ -29008,7 +30160,7 @@
         <v>55</v>
       </c>
       <c r="C1592">
-        <v>4390</v>
+        <v>4020</v>
       </c>
       <c r="D1592" t="s">
         <v>1594</v>
@@ -29022,7 +30174,7 @@
         <v>56</v>
       </c>
       <c r="C1593">
-        <v>4390</v>
+        <v>3990</v>
       </c>
       <c r="D1593" t="s">
         <v>1595</v>
@@ -29036,7 +30188,7 @@
         <v>57</v>
       </c>
       <c r="C1594">
-        <v>4380</v>
+        <v>3930</v>
       </c>
       <c r="D1594" t="s">
         <v>1596</v>
@@ -29050,7 +30202,7 @@
         <v>58</v>
       </c>
       <c r="C1595">
-        <v>4370</v>
+        <v>3920</v>
       </c>
       <c r="D1595" t="s">
         <v>1597</v>
@@ -29064,7 +30216,7 @@
         <v>59</v>
       </c>
       <c r="C1596">
-        <v>4360</v>
+        <v>3920</v>
       </c>
       <c r="D1596" t="s">
         <v>1598</v>
@@ -29078,7 +30230,7 @@
         <v>60</v>
       </c>
       <c r="C1597">
-        <v>4360</v>
+        <v>3930</v>
       </c>
       <c r="D1597" t="s">
         <v>1599</v>
@@ -29092,7 +30244,7 @@
         <v>61</v>
       </c>
       <c r="C1598">
-        <v>4360</v>
+        <v>3940</v>
       </c>
       <c r="D1598" t="s">
         <v>1600</v>
@@ -29106,7 +30258,7 @@
         <v>62</v>
       </c>
       <c r="C1599">
-        <v>4360</v>
+        <v>3960</v>
       </c>
       <c r="D1599" t="s">
         <v>1601</v>
@@ -29120,7 +30272,7 @@
         <v>63</v>
       </c>
       <c r="C1600">
-        <v>4380</v>
+        <v>3980</v>
       </c>
       <c r="D1600" t="s">
         <v>1602</v>
@@ -29134,7 +30286,7 @@
         <v>64</v>
       </c>
       <c r="C1601">
-        <v>4420</v>
+        <v>4040</v>
       </c>
       <c r="D1601" t="s">
         <v>1603</v>
@@ -29148,7 +30300,7 @@
         <v>65</v>
       </c>
       <c r="C1602">
-        <v>4470</v>
+        <v>4110</v>
       </c>
       <c r="D1602" t="s">
         <v>1604</v>
@@ -29162,7 +30314,7 @@
         <v>66</v>
       </c>
       <c r="C1603">
-        <v>4550</v>
+        <v>4180</v>
       </c>
       <c r="D1603" t="s">
         <v>1605</v>
@@ -29176,7 +30328,7 @@
         <v>67</v>
       </c>
       <c r="C1604">
-        <v>4650</v>
+        <v>4260</v>
       </c>
       <c r="D1604" t="s">
         <v>1606</v>
@@ -29190,7 +30342,7 @@
         <v>68</v>
       </c>
       <c r="C1605">
-        <v>4760</v>
+        <v>4350</v>
       </c>
       <c r="D1605" t="s">
         <v>1607</v>
@@ -29204,7 +30356,7 @@
         <v>69</v>
       </c>
       <c r="C1606">
-        <v>4870</v>
+        <v>4440</v>
       </c>
       <c r="D1606" t="s">
         <v>1608</v>
@@ -29218,7 +30370,7 @@
         <v>70</v>
       </c>
       <c r="C1607">
-        <v>4970</v>
+        <v>4540</v>
       </c>
       <c r="D1607" t="s">
         <v>1609</v>
@@ -29232,7 +30384,7 @@
         <v>71</v>
       </c>
       <c r="C1608">
-        <v>5060</v>
+        <v>4630</v>
       </c>
       <c r="D1608" t="s">
         <v>1610</v>
@@ -29246,7 +30398,7 @@
         <v>72</v>
       </c>
       <c r="C1609">
-        <v>5130</v>
+        <v>4730</v>
       </c>
       <c r="D1609" t="s">
         <v>1611</v>
@@ -29260,7 +30412,7 @@
         <v>73</v>
       </c>
       <c r="C1610">
-        <v>5190</v>
+        <v>4850</v>
       </c>
       <c r="D1610" t="s">
         <v>1612</v>
@@ -29274,7 +30426,7 @@
         <v>74</v>
       </c>
       <c r="C1611">
-        <v>5260</v>
+        <v>4970</v>
       </c>
       <c r="D1611" t="s">
         <v>1613</v>
@@ -29288,7 +30440,7 @@
         <v>75</v>
       </c>
       <c r="C1612">
-        <v>5330</v>
+        <v>5090</v>
       </c>
       <c r="D1612" t="s">
         <v>1614</v>
@@ -29302,7 +30454,7 @@
         <v>76</v>
       </c>
       <c r="C1613">
-        <v>5420</v>
+        <v>5200</v>
       </c>
       <c r="D1613" t="s">
         <v>1615</v>
@@ -29316,7 +30468,7 @@
         <v>77</v>
       </c>
       <c r="C1614">
-        <v>5530</v>
+        <v>5330</v>
       </c>
       <c r="D1614" t="s">
         <v>1616</v>
@@ -29330,7 +30482,7 @@
         <v>78</v>
       </c>
       <c r="C1615">
-        <v>5640</v>
+        <v>5460</v>
       </c>
       <c r="D1615" t="s">
         <v>1617</v>
@@ -29344,7 +30496,7 @@
         <v>79</v>
       </c>
       <c r="C1616">
-        <v>5740</v>
+        <v>5570</v>
       </c>
       <c r="D1616" t="s">
         <v>1618</v>
@@ -29358,7 +30510,7 @@
         <v>80</v>
       </c>
       <c r="C1617">
-        <v>5810</v>
+        <v>5660</v>
       </c>
       <c r="D1617" t="s">
         <v>1619</v>
@@ -29372,7 +30524,7 @@
         <v>81</v>
       </c>
       <c r="C1618">
-        <v>5870</v>
+        <v>5770</v>
       </c>
       <c r="D1618" t="s">
         <v>1620</v>
@@ -29386,7 +30538,7 @@
         <v>82</v>
       </c>
       <c r="C1619">
-        <v>5940</v>
+        <v>5860</v>
       </c>
       <c r="D1619" t="s">
         <v>1621</v>
@@ -29400,7 +30552,7 @@
         <v>83</v>
       </c>
       <c r="C1620">
-        <v>5970</v>
+        <v>5920</v>
       </c>
       <c r="D1620" t="s">
         <v>1622</v>
@@ -29414,7 +30566,7 @@
         <v>84</v>
       </c>
       <c r="C1621">
-        <v>6000</v>
+        <v>5970</v>
       </c>
       <c r="D1621" t="s">
         <v>1623</v>
@@ -29428,7 +30580,7 @@
         <v>85</v>
       </c>
       <c r="C1622">
-        <v>6000</v>
+        <v>5990</v>
       </c>
       <c r="D1622" t="s">
         <v>1624</v>
@@ -29442,7 +30594,7 @@
         <v>86</v>
       </c>
       <c r="C1623">
-        <v>5990</v>
+        <v>5970</v>
       </c>
       <c r="D1623" t="s">
         <v>1625</v>
@@ -29456,7 +30608,7 @@
         <v>87</v>
       </c>
       <c r="C1624">
-        <v>5980</v>
+        <v>5940</v>
       </c>
       <c r="D1624" t="s">
         <v>1626</v>
@@ -29470,7 +30622,7 @@
         <v>88</v>
       </c>
       <c r="C1625">
-        <v>5930</v>
+        <v>5880</v>
       </c>
       <c r="D1625" t="s">
         <v>1627</v>
@@ -29484,7 +30636,7 @@
         <v>89</v>
       </c>
       <c r="C1626">
-        <v>5810</v>
+        <v>5770</v>
       </c>
       <c r="D1626" t="s">
         <v>1628</v>
@@ -29498,7 +30650,7 @@
         <v>90</v>
       </c>
       <c r="C1627">
-        <v>5730</v>
+        <v>5660</v>
       </c>
       <c r="D1627" t="s">
         <v>1629</v>
@@ -29512,7 +30664,7 @@
         <v>91</v>
       </c>
       <c r="C1628">
-        <v>5600</v>
+        <v>5520</v>
       </c>
       <c r="D1628" t="s">
         <v>1630</v>
@@ -29526,7 +30678,7 @@
         <v>92</v>
       </c>
       <c r="C1629">
-        <v>5480</v>
+        <v>5390</v>
       </c>
       <c r="D1629" t="s">
         <v>1631</v>
@@ -29540,7 +30692,7 @@
         <v>93</v>
       </c>
       <c r="C1630">
-        <v>5330</v>
+        <v>5290</v>
       </c>
       <c r="D1630" t="s">
         <v>1632</v>
@@ -29554,7 +30706,7 @@
         <v>94</v>
       </c>
       <c r="C1631">
-        <v>5230</v>
+        <v>5180</v>
       </c>
       <c r="D1631" t="s">
         <v>1633</v>
@@ -29568,7 +30720,7 @@
         <v>95</v>
       </c>
       <c r="C1632">
-        <v>5110</v>
+        <v>5060</v>
       </c>
       <c r="D1632" t="s">
         <v>1634</v>
@@ -29582,7 +30734,7 @@
         <v>96</v>
       </c>
       <c r="C1633">
-        <v>5010</v>
+        <v>4950</v>
       </c>
       <c r="D1633" t="s">
         <v>1635</v>
@@ -29596,7 +30748,7 @@
         <v>1</v>
       </c>
       <c r="C1634">
-        <v>4990</v>
+        <v>4840</v>
       </c>
       <c r="D1634" t="s">
         <v>1636</v>
@@ -29610,7 +30762,7 @@
         <v>2</v>
       </c>
       <c r="C1635">
-        <v>4950</v>
+        <v>4780</v>
       </c>
       <c r="D1635" t="s">
         <v>1637</v>
@@ -29624,7 +30776,7 @@
         <v>3</v>
       </c>
       <c r="C1636">
-        <v>4890</v>
+        <v>4720</v>
       </c>
       <c r="D1636" t="s">
         <v>1638</v>
@@ -29638,7 +30790,7 @@
         <v>4</v>
       </c>
       <c r="C1637">
-        <v>4820</v>
+        <v>4670</v>
       </c>
       <c r="D1637" t="s">
         <v>1639</v>
@@ -29652,7 +30804,7 @@
         <v>5</v>
       </c>
       <c r="C1638">
-        <v>4770</v>
+        <v>4600</v>
       </c>
       <c r="D1638" t="s">
         <v>1640</v>
@@ -29666,7 +30818,7 @@
         <v>6</v>
       </c>
       <c r="C1639">
-        <v>4730</v>
+        <v>4560</v>
       </c>
       <c r="D1639" t="s">
         <v>1641</v>
@@ -29680,7 +30832,7 @@
         <v>7</v>
       </c>
       <c r="C1640">
-        <v>4690</v>
+        <v>4540</v>
       </c>
       <c r="D1640" t="s">
         <v>1642</v>
@@ -29694,7 +30846,7 @@
         <v>8</v>
       </c>
       <c r="C1641">
-        <v>4660</v>
+        <v>4520</v>
       </c>
       <c r="D1641" t="s">
         <v>1643</v>
@@ -29708,7 +30860,7 @@
         <v>9</v>
       </c>
       <c r="C1642">
-        <v>4630</v>
+        <v>4500</v>
       </c>
       <c r="D1642" t="s">
         <v>1644</v>
@@ -29722,7 +30874,7 @@
         <v>10</v>
       </c>
       <c r="C1643">
-        <v>4620</v>
+        <v>4480</v>
       </c>
       <c r="D1643" t="s">
         <v>1645</v>
@@ -29736,7 +30888,7 @@
         <v>11</v>
       </c>
       <c r="C1644">
-        <v>4600</v>
+        <v>4470</v>
       </c>
       <c r="D1644" t="s">
         <v>1646</v>
@@ -29750,7 +30902,7 @@
         <v>12</v>
       </c>
       <c r="C1645">
-        <v>4600</v>
+        <v>4470</v>
       </c>
       <c r="D1645" t="s">
         <v>1647</v>
@@ -29764,7 +30916,7 @@
         <v>13</v>
       </c>
       <c r="C1646">
-        <v>4600</v>
+        <v>4470</v>
       </c>
       <c r="D1646" t="s">
         <v>1648</v>
@@ -29778,7 +30930,7 @@
         <v>14</v>
       </c>
       <c r="C1647">
-        <v>4610</v>
+        <v>4470</v>
       </c>
       <c r="D1647" t="s">
         <v>1649</v>
@@ -29792,7 +30944,7 @@
         <v>15</v>
       </c>
       <c r="C1648">
-        <v>4620</v>
+        <v>4470</v>
       </c>
       <c r="D1648" t="s">
         <v>1650</v>
@@ -29806,7 +30958,7 @@
         <v>16</v>
       </c>
       <c r="C1649">
-        <v>4630</v>
+        <v>4480</v>
       </c>
       <c r="D1649" t="s">
         <v>1651</v>
@@ -29820,7 +30972,7 @@
         <v>17</v>
       </c>
       <c r="C1650">
-        <v>4630</v>
+        <v>4510</v>
       </c>
       <c r="D1650" t="s">
         <v>1652</v>
@@ -29834,7 +30986,7 @@
         <v>18</v>
       </c>
       <c r="C1651">
-        <v>4640</v>
+        <v>4520</v>
       </c>
       <c r="D1651" t="s">
         <v>1653</v>
@@ -29848,7 +31000,7 @@
         <v>19</v>
       </c>
       <c r="C1652">
-        <v>4650</v>
+        <v>4520</v>
       </c>
       <c r="D1652" t="s">
         <v>1654</v>
@@ -29862,7 +31014,7 @@
         <v>20</v>
       </c>
       <c r="C1653">
-        <v>4670</v>
+        <v>4530</v>
       </c>
       <c r="D1653" t="s">
         <v>1655</v>
@@ -29876,7 +31028,7 @@
         <v>21</v>
       </c>
       <c r="C1654">
-        <v>4710</v>
+        <v>4570</v>
       </c>
       <c r="D1654" t="s">
         <v>1656</v>
@@ -29890,7 +31042,7 @@
         <v>22</v>
       </c>
       <c r="C1655">
-        <v>4780</v>
+        <v>4630</v>
       </c>
       <c r="D1655" t="s">
         <v>1657</v>
@@ -29904,7 +31056,7 @@
         <v>23</v>
       </c>
       <c r="C1656">
-        <v>4860</v>
+        <v>4710</v>
       </c>
       <c r="D1656" t="s">
         <v>1658</v>
@@ -29918,7 +31070,7 @@
         <v>24</v>
       </c>
       <c r="C1657">
-        <v>4960</v>
+        <v>4810</v>
       </c>
       <c r="D1657" t="s">
         <v>1659</v>
@@ -29932,7 +31084,7 @@
         <v>25</v>
       </c>
       <c r="C1658">
-        <v>5070</v>
+        <v>4900</v>
       </c>
       <c r="D1658" t="s">
         <v>1660</v>
@@ -29946,7 +31098,7 @@
         <v>26</v>
       </c>
       <c r="C1659">
-        <v>5200</v>
+        <v>5030</v>
       </c>
       <c r="D1659" t="s">
         <v>1661</v>
@@ -29960,7 +31112,7 @@
         <v>27</v>
       </c>
       <c r="C1660">
-        <v>5340</v>
+        <v>5150</v>
       </c>
       <c r="D1660" t="s">
         <v>1662</v>
@@ -29974,7 +31126,7 @@
         <v>28</v>
       </c>
       <c r="C1661">
-        <v>5470</v>
+        <v>5270</v>
       </c>
       <c r="D1661" t="s">
         <v>1663</v>
@@ -29988,7 +31140,7 @@
         <v>29</v>
       </c>
       <c r="C1662">
-        <v>5600</v>
+        <v>5440</v>
       </c>
       <c r="D1662" t="s">
         <v>1664</v>
@@ -30002,7 +31154,7 @@
         <v>30</v>
       </c>
       <c r="C1663">
-        <v>5720</v>
+        <v>5540</v>
       </c>
       <c r="D1663" t="s">
         <v>1665</v>
@@ -30016,7 +31168,7 @@
         <v>31</v>
       </c>
       <c r="C1664">
-        <v>5830</v>
+        <v>5600</v>
       </c>
       <c r="D1664" t="s">
         <v>1666</v>
@@ -30030,7 +31182,7 @@
         <v>32</v>
       </c>
       <c r="C1665">
-        <v>5920</v>
+        <v>5610</v>
       </c>
       <c r="D1665" t="s">
         <v>1667</v>
@@ -30044,7 +31196,7 @@
         <v>33</v>
       </c>
       <c r="C1666">
-        <v>5990</v>
+        <v>5600</v>
       </c>
       <c r="D1666" t="s">
         <v>1668</v>
@@ -30058,7 +31210,7 @@
         <v>34</v>
       </c>
       <c r="C1667">
-        <v>6030</v>
+        <v>5580</v>
       </c>
       <c r="D1667" t="s">
         <v>1669</v>
@@ -30072,7 +31224,7 @@
         <v>35</v>
       </c>
       <c r="C1668">
-        <v>6050</v>
+        <v>5540</v>
       </c>
       <c r="D1668" t="s">
         <v>1670</v>
@@ -30086,7 +31238,7 @@
         <v>36</v>
       </c>
       <c r="C1669">
-        <v>6050</v>
+        <v>5480</v>
       </c>
       <c r="D1669" t="s">
         <v>1671</v>
@@ -30100,7 +31252,7 @@
         <v>37</v>
       </c>
       <c r="C1670">
-        <v>6050</v>
+        <v>5380</v>
       </c>
       <c r="D1670" t="s">
         <v>1672</v>
@@ -30114,7 +31266,7 @@
         <v>38</v>
       </c>
       <c r="C1671">
-        <v>6020</v>
+        <v>5290</v>
       </c>
       <c r="D1671" t="s">
         <v>1673</v>
@@ -30128,7 +31280,7 @@
         <v>39</v>
       </c>
       <c r="C1672">
-        <v>5970</v>
+        <v>5180</v>
       </c>
       <c r="D1672" t="s">
         <v>1674</v>
@@ -30142,7 +31294,7 @@
         <v>40</v>
       </c>
       <c r="C1673">
-        <v>5910</v>
+        <v>5080</v>
       </c>
       <c r="D1673" t="s">
         <v>1675</v>
@@ -30156,7 +31308,7 @@
         <v>41</v>
       </c>
       <c r="C1674">
-        <v>5830</v>
+        <v>4990</v>
       </c>
       <c r="D1674" t="s">
         <v>1676</v>
@@ -30170,7 +31322,7 @@
         <v>42</v>
       </c>
       <c r="C1675">
-        <v>5750</v>
+        <v>4900</v>
       </c>
       <c r="D1675" t="s">
         <v>1677</v>
@@ -30184,7 +31336,7 @@
         <v>43</v>
       </c>
       <c r="C1676">
-        <v>5660</v>
+        <v>4800</v>
       </c>
       <c r="D1676" t="s">
         <v>1678</v>
@@ -30198,7 +31350,7 @@
         <v>44</v>
       </c>
       <c r="C1677">
-        <v>5560</v>
+        <v>4700</v>
       </c>
       <c r="D1677" t="s">
         <v>1679</v>
@@ -30212,7 +31364,7 @@
         <v>45</v>
       </c>
       <c r="C1678">
-        <v>5470</v>
+        <v>4590</v>
       </c>
       <c r="D1678" t="s">
         <v>1680</v>
@@ -30226,7 +31378,7 @@
         <v>46</v>
       </c>
       <c r="C1679">
-        <v>5390</v>
+        <v>4520</v>
       </c>
       <c r="D1679" t="s">
         <v>1681</v>
@@ -30240,7 +31392,7 @@
         <v>47</v>
       </c>
       <c r="C1680">
-        <v>5310</v>
+        <v>4470</v>
       </c>
       <c r="D1680" t="s">
         <v>1682</v>
@@ -30254,7 +31406,7 @@
         <v>48</v>
       </c>
       <c r="C1681">
-        <v>5230</v>
+        <v>4420</v>
       </c>
       <c r="D1681" t="s">
         <v>1683</v>
@@ -30268,7 +31420,7 @@
         <v>49</v>
       </c>
       <c r="C1682">
-        <v>5170</v>
+        <v>4390</v>
       </c>
       <c r="D1682" t="s">
         <v>1684</v>
@@ -30282,7 +31434,7 @@
         <v>50</v>
       </c>
       <c r="C1683">
-        <v>5110</v>
+        <v>4360</v>
       </c>
       <c r="D1683" t="s">
         <v>1685</v>
@@ -30296,7 +31448,7 @@
         <v>51</v>
       </c>
       <c r="C1684">
-        <v>5070</v>
+        <v>4340</v>
       </c>
       <c r="D1684" t="s">
         <v>1686</v>
@@ -30310,7 +31462,7 @@
         <v>52</v>
       </c>
       <c r="C1685">
-        <v>5040</v>
+        <v>4330</v>
       </c>
       <c r="D1685" t="s">
         <v>1687</v>
@@ -30324,7 +31476,7 @@
         <v>53</v>
       </c>
       <c r="C1686">
-        <v>5010</v>
+        <v>4330</v>
       </c>
       <c r="D1686" t="s">
         <v>1688</v>
@@ -30338,7 +31490,7 @@
         <v>54</v>
       </c>
       <c r="C1687">
-        <v>5000</v>
+        <v>4340</v>
       </c>
       <c r="D1687" t="s">
         <v>1689</v>
@@ -30352,7 +31504,7 @@
         <v>55</v>
       </c>
       <c r="C1688">
-        <v>5000</v>
+        <v>4350</v>
       </c>
       <c r="D1688" t="s">
         <v>1690</v>
@@ -30366,7 +31518,7 @@
         <v>56</v>
       </c>
       <c r="C1689">
-        <v>5000</v>
+        <v>4360</v>
       </c>
       <c r="D1689" t="s">
         <v>1691</v>
@@ -30380,7 +31532,7 @@
         <v>57</v>
       </c>
       <c r="C1690">
-        <v>5010</v>
+        <v>4370</v>
       </c>
       <c r="D1690" t="s">
         <v>1692</v>
@@ -30394,7 +31546,7 @@
         <v>58</v>
       </c>
       <c r="C1691">
-        <v>5020</v>
+        <v>4390</v>
       </c>
       <c r="D1691" t="s">
         <v>1693</v>
@@ -30408,7 +31560,7 @@
         <v>59</v>
       </c>
       <c r="C1692">
-        <v>5020</v>
+        <v>4410</v>
       </c>
       <c r="D1692" t="s">
         <v>1694</v>
@@ -30422,7 +31574,7 @@
         <v>60</v>
       </c>
       <c r="C1693">
-        <v>5030</v>
+        <v>4450</v>
       </c>
       <c r="D1693" t="s">
         <v>1695</v>
@@ -30436,7 +31588,7 @@
         <v>61</v>
       </c>
       <c r="C1694">
-        <v>5040</v>
+        <v>4490</v>
       </c>
       <c r="D1694" t="s">
         <v>1696</v>
@@ -30450,7 +31602,7 @@
         <v>62</v>
       </c>
       <c r="C1695">
-        <v>5060</v>
+        <v>4530</v>
       </c>
       <c r="D1695" t="s">
         <v>1697</v>
@@ -30464,7 +31616,7 @@
         <v>63</v>
       </c>
       <c r="C1696">
-        <v>5080</v>
+        <v>4570</v>
       </c>
       <c r="D1696" t="s">
         <v>1698</v>
@@ -30478,7 +31630,7 @@
         <v>64</v>
       </c>
       <c r="C1697">
-        <v>5120</v>
+        <v>4620</v>
       </c>
       <c r="D1697" t="s">
         <v>1699</v>
@@ -30492,7 +31644,7 @@
         <v>65</v>
       </c>
       <c r="C1698">
-        <v>5180</v>
+        <v>4680</v>
       </c>
       <c r="D1698" t="s">
         <v>1700</v>
@@ -30506,7 +31658,7 @@
         <v>66</v>
       </c>
       <c r="C1699">
-        <v>5250</v>
+        <v>4750</v>
       </c>
       <c r="D1699" t="s">
         <v>1701</v>
@@ -30520,7 +31672,7 @@
         <v>67</v>
       </c>
       <c r="C1700">
-        <v>5330</v>
+        <v>4840</v>
       </c>
       <c r="D1700" t="s">
         <v>1702</v>
@@ -30534,7 +31686,7 @@
         <v>68</v>
       </c>
       <c r="C1701">
-        <v>5420</v>
+        <v>4930</v>
       </c>
       <c r="D1701" t="s">
         <v>1703</v>
@@ -30548,7 +31700,7 @@
         <v>69</v>
       </c>
       <c r="C1702">
-        <v>5520</v>
+        <v>5030</v>
       </c>
       <c r="D1702" t="s">
         <v>1704</v>
@@ -30562,7 +31714,7 @@
         <v>70</v>
       </c>
       <c r="C1703">
-        <v>5610</v>
+        <v>5150</v>
       </c>
       <c r="D1703" t="s">
         <v>1705</v>
@@ -30576,7 +31728,7 @@
         <v>71</v>
       </c>
       <c r="C1704">
-        <v>5700</v>
+        <v>5260</v>
       </c>
       <c r="D1704" t="s">
         <v>1706</v>
@@ -30590,7 +31742,7 @@
         <v>72</v>
       </c>
       <c r="C1705">
-        <v>5790</v>
+        <v>5380</v>
       </c>
       <c r="D1705" t="s">
         <v>1707</v>
@@ -30604,7 +31756,7 @@
         <v>73</v>
       </c>
       <c r="C1706">
-        <v>5870</v>
+        <v>5540</v>
       </c>
       <c r="D1706" t="s">
         <v>1708</v>
@@ -30618,7 +31770,7 @@
         <v>74</v>
       </c>
       <c r="C1707">
-        <v>5970</v>
+        <v>5670</v>
       </c>
       <c r="D1707" t="s">
         <v>1709</v>
@@ -30632,7 +31784,7 @@
         <v>75</v>
       </c>
       <c r="C1708">
-        <v>6080</v>
+        <v>5810</v>
       </c>
       <c r="D1708" t="s">
         <v>1710</v>
@@ -30646,7 +31798,7 @@
         <v>76</v>
       </c>
       <c r="C1709">
-        <v>6200</v>
+        <v>5970</v>
       </c>
       <c r="D1709" t="s">
         <v>1711</v>
@@ -30660,7 +31812,7 @@
         <v>77</v>
       </c>
       <c r="C1710">
-        <v>6320</v>
+        <v>6120</v>
       </c>
       <c r="D1710" t="s">
         <v>1712</v>
@@ -30674,7 +31826,7 @@
         <v>78</v>
       </c>
       <c r="C1711">
-        <v>6440</v>
+        <v>6270</v>
       </c>
       <c r="D1711" t="s">
         <v>1713</v>
@@ -30688,7 +31840,7 @@
         <v>79</v>
       </c>
       <c r="C1712">
-        <v>6540</v>
+        <v>6380</v>
       </c>
       <c r="D1712" t="s">
         <v>1714</v>
@@ -30702,7 +31854,7 @@
         <v>80</v>
       </c>
       <c r="C1713">
-        <v>6600</v>
+        <v>6460</v>
       </c>
       <c r="D1713" t="s">
         <v>1715</v>
@@ -30716,7 +31868,7 @@
         <v>81</v>
       </c>
       <c r="C1714">
-        <v>6670</v>
+        <v>6520</v>
       </c>
       <c r="D1714" t="s">
         <v>1716</v>
@@ -30730,7 +31882,7 @@
         <v>82</v>
       </c>
       <c r="C1715">
-        <v>6750</v>
+        <v>6590</v>
       </c>
       <c r="D1715" t="s">
         <v>1717</v>
@@ -30744,7 +31896,7 @@
         <v>83</v>
       </c>
       <c r="C1716">
-        <v>6820</v>
+        <v>6660</v>
       </c>
       <c r="D1716" t="s">
         <v>1718</v>
@@ -30758,7 +31910,7 @@
         <v>84</v>
       </c>
       <c r="C1717">
-        <v>6900</v>
+        <v>6760</v>
       </c>
       <c r="D1717" t="s">
         <v>1719</v>
@@ -30772,7 +31924,7 @@
         <v>85</v>
       </c>
       <c r="C1718">
-        <v>6900</v>
+        <v>6830</v>
       </c>
       <c r="D1718" t="s">
         <v>1720</v>
@@ -30786,7 +31938,7 @@
         <v>86</v>
       </c>
       <c r="C1719">
-        <v>6900</v>
+        <v>6840</v>
       </c>
       <c r="D1719" t="s">
         <v>1721</v>
@@ -30800,7 +31952,7 @@
         <v>87</v>
       </c>
       <c r="C1720">
-        <v>6880</v>
+        <v>6820</v>
       </c>
       <c r="D1720" t="s">
         <v>1722</v>
@@ -30814,7 +31966,7 @@
         <v>88</v>
       </c>
       <c r="C1721">
-        <v>6770</v>
+        <v>6710</v>
       </c>
       <c r="D1721" t="s">
         <v>1723</v>
@@ -30828,7 +31980,7 @@
         <v>89</v>
       </c>
       <c r="C1722">
-        <v>6600</v>
+        <v>6510</v>
       </c>
       <c r="D1722" t="s">
         <v>1724</v>
@@ -30842,7 +31994,7 @@
         <v>90</v>
       </c>
       <c r="C1723">
-        <v>6480</v>
+        <v>6350</v>
       </c>
       <c r="D1723" t="s">
         <v>1725</v>
@@ -30856,7 +32008,7 @@
         <v>91</v>
       </c>
       <c r="C1724">
-        <v>6330</v>
+        <v>6210</v>
       </c>
       <c r="D1724" t="s">
         <v>1726</v>
@@ -30870,7 +32022,7 @@
         <v>92</v>
       </c>
       <c r="C1725">
-        <v>6170</v>
+        <v>6050</v>
       </c>
       <c r="D1725" t="s">
         <v>1727</v>
@@ -30884,7 +32036,7 @@
         <v>93</v>
       </c>
       <c r="C1726">
-        <v>5940</v>
+        <v>5880</v>
       </c>
       <c r="D1726" t="s">
         <v>1728</v>
@@ -30898,7 +32050,7 @@
         <v>94</v>
       </c>
       <c r="C1727">
-        <v>5760</v>
+        <v>5740</v>
       </c>
       <c r="D1727" t="s">
         <v>1729</v>
@@ -30912,7 +32064,7 @@
         <v>95</v>
       </c>
       <c r="C1728">
-        <v>5680</v>
+        <v>5630</v>
       </c>
       <c r="D1728" t="s">
         <v>1730</v>
@@ -30926,7 +32078,7 @@
         <v>96</v>
       </c>
       <c r="C1729">
-        <v>5570</v>
+        <v>5520</v>
       </c>
       <c r="D1729" t="s">
         <v>1731</v>
@@ -30940,7 +32092,7 @@
         <v>1</v>
       </c>
       <c r="C1730">
-        <v>5450</v>
+        <v>5390</v>
       </c>
       <c r="D1730" t="s">
         <v>1732</v>
@@ -30954,7 +32106,7 @@
         <v>2</v>
       </c>
       <c r="C1731">
-        <v>5410</v>
+        <v>5300</v>
       </c>
       <c r="D1731" t="s">
         <v>1733</v>
@@ -30968,7 +32120,7 @@
         <v>3</v>
       </c>
       <c r="C1732">
-        <v>5350</v>
+        <v>5230</v>
       </c>
       <c r="D1732" t="s">
         <v>1734</v>
@@ -30982,7 +32134,7 @@
         <v>4</v>
       </c>
       <c r="C1733">
-        <v>5280</v>
+        <v>5160</v>
       </c>
       <c r="D1733" t="s">
         <v>1735</v>
@@ -30996,7 +32148,7 @@
         <v>5</v>
       </c>
       <c r="C1734">
-        <v>5230</v>
+        <v>5110</v>
       </c>
       <c r="D1734" t="s">
         <v>1736</v>
@@ -31010,7 +32162,7 @@
         <v>6</v>
       </c>
       <c r="C1735">
-        <v>5190</v>
+        <v>5060</v>
       </c>
       <c r="D1735" t="s">
         <v>1737</v>
@@ -31024,7 +32176,7 @@
         <v>7</v>
       </c>
       <c r="C1736">
-        <v>5150</v>
+        <v>5020</v>
       </c>
       <c r="D1736" t="s">
         <v>1738</v>
@@ -31038,7 +32190,7 @@
         <v>8</v>
       </c>
       <c r="C1737">
-        <v>5110</v>
+        <v>4990</v>
       </c>
       <c r="D1737" t="s">
         <v>1739</v>
@@ -31052,7 +32204,7 @@
         <v>9</v>
       </c>
       <c r="C1738">
-        <v>5080</v>
+        <v>4960</v>
       </c>
       <c r="D1738" t="s">
         <v>1740</v>
@@ -31066,7 +32218,7 @@
         <v>10</v>
       </c>
       <c r="C1739">
-        <v>5060</v>
+        <v>4940</v>
       </c>
       <c r="D1739" t="s">
         <v>1741</v>
@@ -31080,7 +32232,7 @@
         <v>11</v>
       </c>
       <c r="C1740">
-        <v>5050</v>
+        <v>4920</v>
       </c>
       <c r="D1740" t="s">
         <v>1742</v>
@@ -31094,7 +32246,7 @@
         <v>12</v>
       </c>
       <c r="C1741">
-        <v>5050</v>
+        <v>4910</v>
       </c>
       <c r="D1741" t="s">
         <v>1743</v>
@@ -31108,7 +32260,7 @@
         <v>13</v>
       </c>
       <c r="C1742">
-        <v>5050</v>
+        <v>4910</v>
       </c>
       <c r="D1742" t="s">
         <v>1744</v>
@@ -31122,7 +32274,7 @@
         <v>14</v>
       </c>
       <c r="C1743">
-        <v>5060</v>
+        <v>4910</v>
       </c>
       <c r="D1743" t="s">
         <v>1745</v>
@@ -31136,7 +32288,7 @@
         <v>15</v>
       </c>
       <c r="C1744">
-        <v>5070</v>
+        <v>4910</v>
       </c>
       <c r="D1744" t="s">
         <v>1746</v>
@@ -31150,7 +32302,7 @@
         <v>16</v>
       </c>
       <c r="C1745">
-        <v>5070</v>
+        <v>4920</v>
       </c>
       <c r="D1745" t="s">
         <v>1747</v>
@@ -31164,7 +32316,7 @@
         <v>17</v>
       </c>
       <c r="C1746">
-        <v>5070</v>
+        <v>4930</v>
       </c>
       <c r="D1746" t="s">
         <v>1748</v>
@@ -31178,7 +32330,7 @@
         <v>18</v>
       </c>
       <c r="C1747">
-        <v>5070</v>
+        <v>4940</v>
       </c>
       <c r="D1747" t="s">
         <v>1749</v>
@@ -31192,7 +32344,7 @@
         <v>19</v>
       </c>
       <c r="C1748">
-        <v>5070</v>
+        <v>4960</v>
       </c>
       <c r="D1748" t="s">
         <v>1750</v>
@@ -31206,7 +32358,7 @@
         <v>20</v>
       </c>
       <c r="C1749">
-        <v>5080</v>
+        <v>4980</v>
       </c>
       <c r="D1749" t="s">
         <v>1751</v>
@@ -31220,7 +32372,7 @@
         <v>21</v>
       </c>
       <c r="C1750">
-        <v>5100</v>
+        <v>5010</v>
       </c>
       <c r="D1750" t="s">
         <v>1752</v>
@@ -31234,7 +32386,7 @@
         <v>22</v>
       </c>
       <c r="C1751">
-        <v>5140</v>
+        <v>5050</v>
       </c>
       <c r="D1751" t="s">
         <v>1753</v>
@@ -31248,7 +32400,7 @@
         <v>23</v>
       </c>
       <c r="C1752">
-        <v>5190</v>
+        <v>5090</v>
       </c>
       <c r="D1752" t="s">
         <v>1754</v>
@@ -31262,7 +32414,7 @@
         <v>24</v>
       </c>
       <c r="C1753">
-        <v>5260</v>
+        <v>5140</v>
       </c>
       <c r="D1753" t="s">
         <v>1755</v>
@@ -31276,7 +32428,7 @@
         <v>25</v>
       </c>
       <c r="C1754">
-        <v>5340</v>
+        <v>5200</v>
       </c>
       <c r="D1754" t="s">
         <v>1756</v>
@@ -31290,7 +32442,7 @@
         <v>26</v>
       </c>
       <c r="C1755">
-        <v>5440</v>
+        <v>5270</v>
       </c>
       <c r="D1755" t="s">
         <v>1757</v>
@@ -31304,7 +32456,7 @@
         <v>27</v>
       </c>
       <c r="C1756">
-        <v>5550</v>
+        <v>5370</v>
       </c>
       <c r="D1756" t="s">
         <v>1758</v>
@@ -31318,7 +32470,7 @@
         <v>28</v>
       </c>
       <c r="C1757">
-        <v>5650</v>
+        <v>5480</v>
       </c>
       <c r="D1757" t="s">
         <v>1759</v>
@@ -31332,7 +32484,7 @@
         <v>29</v>
       </c>
       <c r="C1758">
-        <v>5760</v>
+        <v>5600</v>
       </c>
       <c r="D1758" t="s">
         <v>1760</v>
@@ -31346,7 +32498,7 @@
         <v>30</v>
       </c>
       <c r="C1759">
-        <v>5860</v>
+        <v>5700</v>
       </c>
       <c r="D1759" t="s">
         <v>1761</v>
@@ -31360,7 +32512,7 @@
         <v>31</v>
       </c>
       <c r="C1760">
-        <v>5950</v>
+        <v>5740</v>
       </c>
       <c r="D1760" t="s">
         <v>1762</v>
@@ -31374,7 +32526,7 @@
         <v>32</v>
       </c>
       <c r="C1761">
-        <v>6020</v>
+        <v>5750</v>
       </c>
       <c r="D1761" t="s">
         <v>1763</v>
@@ -31388,7 +32540,7 @@
         <v>33</v>
       </c>
       <c r="C1762">
-        <v>6070</v>
+        <v>5720</v>
       </c>
       <c r="D1762" t="s">
         <v>1764</v>
@@ -31402,7 +32554,7 @@
         <v>34</v>
       </c>
       <c r="C1763">
-        <v>6100</v>
+        <v>5680</v>
       </c>
       <c r="D1763" t="s">
         <v>1765</v>
@@ -31416,7 +32568,7 @@
         <v>35</v>
       </c>
       <c r="C1764">
-        <v>6100</v>
+        <v>5630</v>
       </c>
       <c r="D1764" t="s">
         <v>1766</v>
@@ -31430,7 +32582,7 @@
         <v>36</v>
       </c>
       <c r="C1765">
-        <v>6080</v>
+        <v>5590</v>
       </c>
       <c r="D1765" t="s">
         <v>1767</v>
@@ -31444,7 +32596,7 @@
         <v>37</v>
       </c>
       <c r="C1766">
-        <v>6040</v>
+        <v>5540</v>
       </c>
       <c r="D1766" t="s">
         <v>1768</v>
@@ -31458,7 +32610,7 @@
         <v>38</v>
       </c>
       <c r="C1767">
-        <v>5980</v>
+        <v>5490</v>
       </c>
       <c r="D1767" t="s">
         <v>1769</v>
@@ -31472,7 +32624,7 @@
         <v>39</v>
       </c>
       <c r="C1768">
-        <v>5900</v>
+        <v>5420</v>
       </c>
       <c r="D1768" t="s">
         <v>1770</v>
@@ -31486,7 +32638,7 @@
         <v>40</v>
       </c>
       <c r="C1769">
-        <v>5810</v>
+        <v>5340</v>
       </c>
       <c r="D1769" t="s">
         <v>1771</v>
@@ -31500,7 +32652,7 @@
         <v>41</v>
       </c>
       <c r="C1770">
-        <v>5720</v>
+        <v>5250</v>
       </c>
       <c r="D1770" t="s">
         <v>1772</v>
@@ -31514,7 +32666,7 @@
         <v>42</v>
       </c>
       <c r="C1771">
-        <v>5620</v>
+        <v>5140</v>
       </c>
       <c r="D1771" t="s">
         <v>1773</v>
@@ -31528,7 +32680,7 @@
         <v>43</v>
       </c>
       <c r="C1772">
-        <v>5530</v>
+        <v>5020</v>
       </c>
       <c r="D1772" t="s">
         <v>1774</v>
@@ -31542,7 +32694,7 @@
         <v>44</v>
       </c>
       <c r="C1773">
-        <v>5450</v>
+        <v>4890</v>
       </c>
       <c r="D1773" t="s">
         <v>1775</v>
@@ -31556,7 +32708,7 @@
         <v>45</v>
       </c>
       <c r="C1774">
-        <v>5370</v>
+        <v>4740</v>
       </c>
       <c r="D1774" t="s">
         <v>1776</v>
@@ -31570,7 +32722,7 @@
         <v>46</v>
       </c>
       <c r="C1775">
-        <v>5300</v>
+        <v>4610</v>
       </c>
       <c r="D1775" t="s">
         <v>1777</v>
@@ -31584,7 +32736,7 @@
         <v>47</v>
       </c>
       <c r="C1776">
-        <v>5250</v>
+        <v>4500</v>
       </c>
       <c r="D1776" t="s">
         <v>1778</v>
@@ -31598,7 +32750,7 @@
         <v>48</v>
       </c>
       <c r="C1777">
-        <v>5200</v>
+        <v>4420</v>
       </c>
       <c r="D1777" t="s">
         <v>1779</v>
@@ -31612,7 +32764,7 @@
         <v>49</v>
       </c>
       <c r="C1778">
-        <v>5170</v>
+        <v>4350</v>
       </c>
       <c r="D1778" t="s">
         <v>1780</v>
@@ -31626,7 +32778,7 @@
         <v>50</v>
       </c>
       <c r="C1779">
-        <v>5140</v>
+        <v>4310</v>
       </c>
       <c r="D1779" t="s">
         <v>1781</v>
@@ -31640,7 +32792,7 @@
         <v>51</v>
       </c>
       <c r="C1780">
-        <v>5110</v>
+        <v>4280</v>
       </c>
       <c r="D1780" t="s">
         <v>1782</v>
@@ -31654,7 +32806,7 @@
         <v>52</v>
       </c>
       <c r="C1781">
-        <v>5100</v>
+        <v>4280</v>
       </c>
       <c r="D1781" t="s">
         <v>1783</v>
@@ -31668,7 +32820,7 @@
         <v>53</v>
       </c>
       <c r="C1782">
-        <v>5080</v>
+        <v>4290</v>
       </c>
       <c r="D1782" t="s">
         <v>1784</v>
@@ -31682,7 +32834,7 @@
         <v>54</v>
       </c>
       <c r="C1783">
-        <v>5080</v>
+        <v>4300</v>
       </c>
       <c r="D1783" t="s">
         <v>1785</v>
@@ -31696,7 +32848,7 @@
         <v>55</v>
       </c>
       <c r="C1784">
-        <v>5070</v>
+        <v>4310</v>
       </c>
       <c r="D1784" t="s">
         <v>1786</v>
@@ -31710,7 +32862,7 @@
         <v>56</v>
       </c>
       <c r="C1785">
-        <v>5070</v>
+        <v>4310</v>
       </c>
       <c r="D1785" t="s">
         <v>1787</v>
@@ -31724,7 +32876,7 @@
         <v>57</v>
       </c>
       <c r="C1786">
-        <v>5070</v>
+        <v>4320</v>
       </c>
       <c r="D1786" t="s">
         <v>1788</v>
@@ -31738,7 +32890,7 @@
         <v>58</v>
       </c>
       <c r="C1787">
-        <v>5080</v>
+        <v>4330</v>
       </c>
       <c r="D1787" t="s">
         <v>1789</v>
@@ -31752,7 +32904,7 @@
         <v>59</v>
       </c>
       <c r="C1788">
-        <v>5090</v>
+        <v>4350</v>
       </c>
       <c r="D1788" t="s">
         <v>1790</v>
@@ -31766,7 +32918,7 @@
         <v>60</v>
       </c>
       <c r="C1789">
-        <v>5100</v>
+        <v>4380</v>
       </c>
       <c r="D1789" t="s">
         <v>1791</v>
@@ -31780,7 +32932,7 @@
         <v>61</v>
       </c>
       <c r="C1790">
-        <v>5120</v>
+        <v>4430</v>
       </c>
       <c r="D1790" t="s">
         <v>1792</v>
@@ -31794,7 +32946,7 @@
         <v>62</v>
       </c>
       <c r="C1791">
-        <v>5140</v>
+        <v>4480</v>
       </c>
       <c r="D1791" t="s">
         <v>1793</v>
@@ -31808,7 +32960,7 @@
         <v>63</v>
       </c>
       <c r="C1792">
-        <v>5170</v>
+        <v>4540</v>
       </c>
       <c r="D1792" t="s">
         <v>1794</v>
@@ -31822,7 +32974,7 @@
         <v>64</v>
       </c>
       <c r="C1793">
-        <v>5220</v>
+        <v>4620</v>
       </c>
       <c r="D1793" t="s">
         <v>1795</v>
@@ -31836,7 +32988,7 @@
         <v>65</v>
       </c>
       <c r="C1794">
-        <v>5280</v>
+        <v>4700</v>
       </c>
       <c r="D1794" t="s">
         <v>1796</v>
@@ -31850,7 +33002,7 @@
         <v>66</v>
       </c>
       <c r="C1795">
-        <v>5360</v>
+        <v>4790</v>
       </c>
       <c r="D1795" t="s">
         <v>1797</v>
@@ -31864,7 +33016,7 @@
         <v>67</v>
       </c>
       <c r="C1796">
-        <v>5440</v>
+        <v>4880</v>
       </c>
       <c r="D1796" t="s">
         <v>1798</v>
@@ -31878,7 +33030,7 @@
         <v>68</v>
       </c>
       <c r="C1797">
-        <v>5530</v>
+        <v>4990</v>
       </c>
       <c r="D1797" t="s">
         <v>1799</v>
@@ -31892,7 +33044,7 @@
         <v>69</v>
       </c>
       <c r="C1798">
-        <v>5630</v>
+        <v>5090</v>
       </c>
       <c r="D1798" t="s">
         <v>1800</v>
@@ -31906,7 +33058,7 @@
         <v>70</v>
       </c>
       <c r="C1799">
-        <v>5720</v>
+        <v>5210</v>
       </c>
       <c r="D1799" t="s">
         <v>1801</v>
@@ -31920,7 +33072,7 @@
         <v>71</v>
       </c>
       <c r="C1800">
-        <v>5800</v>
+        <v>5320</v>
       </c>
       <c r="D1800" t="s">
         <v>1802</v>
@@ -31934,7 +33086,7 @@
         <v>72</v>
       </c>
       <c r="C1801">
-        <v>5880</v>
+        <v>5450</v>
       </c>
       <c r="D1801" t="s">
         <v>1803</v>
@@ -31948,7 +33100,7 @@
         <v>73</v>
       </c>
       <c r="C1802">
-        <v>5960</v>
+        <v>5570</v>
       </c>
       <c r="D1802" t="s">
         <v>1804</v>
@@ -31962,7 +33114,7 @@
         <v>74</v>
       </c>
       <c r="C1803">
-        <v>6050</v>
+        <v>5700</v>
       </c>
       <c r="D1803" t="s">
         <v>1805</v>
@@ -31976,7 +33128,7 @@
         <v>75</v>
       </c>
       <c r="C1804">
-        <v>6150</v>
+        <v>5840</v>
       </c>
       <c r="D1804" t="s">
         <v>1806</v>
@@ -31990,7 +33142,7 @@
         <v>76</v>
       </c>
       <c r="C1805">
-        <v>6260</v>
+        <v>5970</v>
       </c>
       <c r="D1805" t="s">
         <v>1807</v>
@@ -32004,7 +33156,7 @@
         <v>77</v>
       </c>
       <c r="C1806">
-        <v>6380</v>
+        <v>6110</v>
       </c>
       <c r="D1806" t="s">
         <v>1808</v>
@@ -32018,7 +33170,7 @@
         <v>78</v>
       </c>
       <c r="C1807">
-        <v>6490</v>
+        <v>6230</v>
       </c>
       <c r="D1807" t="s">
         <v>1809</v>
@@ -32032,7 +33184,7 @@
         <v>79</v>
       </c>
       <c r="C1808">
-        <v>6580</v>
+        <v>6320</v>
       </c>
       <c r="D1808" t="s">
         <v>1810</v>
@@ -32046,7 +33198,7 @@
         <v>80</v>
       </c>
       <c r="C1809">
-        <v>6630</v>
+        <v>6390</v>
       </c>
       <c r="D1809" t="s">
         <v>1811</v>
@@ -32060,7 +33212,7 @@
         <v>81</v>
       </c>
       <c r="C1810">
-        <v>6690</v>
+        <v>6450</v>
       </c>
       <c r="D1810" t="s">
         <v>1812</v>
@@ -32074,7 +33226,7 @@
         <v>82</v>
       </c>
       <c r="C1811">
-        <v>6760</v>
+        <v>6510</v>
       </c>
       <c r="D1811" t="s">
         <v>1813</v>
@@ -32088,7 +33240,7 @@
         <v>83</v>
       </c>
       <c r="C1812">
-        <v>6820</v>
+        <v>6580</v>
       </c>
       <c r="D1812" t="s">
         <v>1814</v>
@@ -32102,7 +33254,7 @@
         <v>84</v>
       </c>
       <c r="C1813">
-        <v>6900</v>
+        <v>6660</v>
       </c>
       <c r="D1813" t="s">
         <v>1815</v>
@@ -32116,7 +33268,7 @@
         <v>85</v>
       </c>
       <c r="C1814">
-        <v>6900</v>
+        <v>6750</v>
       </c>
       <c r="D1814" t="s">
         <v>1816</v>
@@ -32130,7 +33282,7 @@
         <v>86</v>
       </c>
       <c r="C1815">
-        <v>6900</v>
+        <v>6780</v>
       </c>
       <c r="D1815" t="s">
         <v>1817</v>
@@ -32144,7 +33296,7 @@
         <v>87</v>
       </c>
       <c r="C1816">
-        <v>6880</v>
+        <v>6750</v>
       </c>
       <c r="D1816" t="s">
         <v>1818</v>
@@ -32158,7 +33310,7 @@
         <v>88</v>
       </c>
       <c r="C1817">
-        <v>6780</v>
+        <v>6660</v>
       </c>
       <c r="D1817" t="s">
         <v>1819</v>
@@ -32172,7 +33324,7 @@
         <v>89</v>
       </c>
       <c r="C1818">
-        <v>6610</v>
+        <v>6510</v>
       </c>
       <c r="D1818" t="s">
         <v>1820</v>
@@ -32186,7 +33338,7 @@
         <v>90</v>
       </c>
       <c r="C1819">
-        <v>6490</v>
+        <v>6360</v>
       </c>
       <c r="D1819" t="s">
         <v>1821</v>
@@ -32200,7 +33352,7 @@
         <v>91</v>
       </c>
       <c r="C1820">
-        <v>6350</v>
+        <v>6200</v>
       </c>
       <c r="D1820" t="s">
         <v>1822</v>
@@ -32214,7 +33366,7 @@
         <v>92</v>
       </c>
       <c r="C1821">
-        <v>6190</v>
+        <v>6050</v>
       </c>
       <c r="D1821" t="s">
         <v>1823</v>
@@ -32228,7 +33380,7 @@
         <v>93</v>
       </c>
       <c r="C1822">
-        <v>5970</v>
+        <v>5890</v>
       </c>
       <c r="D1822" t="s">
         <v>1824</v>
@@ -32242,7 +33394,7 @@
         <v>94</v>
       </c>
       <c r="C1823">
-        <v>5790</v>
+        <v>5750</v>
       </c>
       <c r="D1823" t="s">
         <v>1825</v>
@@ -32256,7 +33408,7 @@
         <v>95</v>
       </c>
       <c r="C1824">
-        <v>5710</v>
+        <v>5620</v>
       </c>
       <c r="D1824" t="s">
         <v>1826</v>
@@ -32270,7 +33422,7 @@
         <v>96</v>
       </c>
       <c r="C1825">
-        <v>5600</v>
+        <v>5500</v>
       </c>
       <c r="D1825" t="s">
         <v>1827</v>
@@ -36306,6 +37458,5382 @@
       </c>
       <c r="D2113" t="s">
         <v>2115</v>
+      </c>
+    </row>
+    <row r="2114" spans="1:4">
+      <c r="A2114" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2114">
+        <v>1</v>
+      </c>
+      <c r="C2114">
+        <v>5450</v>
+      </c>
+      <c r="D2114" t="s">
+        <v>2116</v>
+      </c>
+    </row>
+    <row r="2115" spans="1:4">
+      <c r="A2115" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2115">
+        <v>2</v>
+      </c>
+      <c r="C2115">
+        <v>5360</v>
+      </c>
+      <c r="D2115" t="s">
+        <v>2117</v>
+      </c>
+    </row>
+    <row r="2116" spans="1:4">
+      <c r="A2116" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2116">
+        <v>3</v>
+      </c>
+      <c r="C2116">
+        <v>5280</v>
+      </c>
+      <c r="D2116" t="s">
+        <v>2118</v>
+      </c>
+    </row>
+    <row r="2117" spans="1:4">
+      <c r="A2117" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2117">
+        <v>4</v>
+      </c>
+      <c r="C2117">
+        <v>5210</v>
+      </c>
+      <c r="D2117" t="s">
+        <v>2119</v>
+      </c>
+    </row>
+    <row r="2118" spans="1:4">
+      <c r="A2118" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2118">
+        <v>5</v>
+      </c>
+      <c r="C2118">
+        <v>5150</v>
+      </c>
+      <c r="D2118" t="s">
+        <v>2120</v>
+      </c>
+    </row>
+    <row r="2119" spans="1:4">
+      <c r="A2119" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2119">
+        <v>6</v>
+      </c>
+      <c r="C2119">
+        <v>5100</v>
+      </c>
+      <c r="D2119" t="s">
+        <v>2121</v>
+      </c>
+    </row>
+    <row r="2120" spans="1:4">
+      <c r="A2120" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2120">
+        <v>7</v>
+      </c>
+      <c r="C2120">
+        <v>5060</v>
+      </c>
+      <c r="D2120" t="s">
+        <v>2122</v>
+      </c>
+    </row>
+    <row r="2121" spans="1:4">
+      <c r="A2121" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2121">
+        <v>8</v>
+      </c>
+      <c r="C2121">
+        <v>5030</v>
+      </c>
+      <c r="D2121" t="s">
+        <v>2123</v>
+      </c>
+    </row>
+    <row r="2122" spans="1:4">
+      <c r="A2122" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2122">
+        <v>9</v>
+      </c>
+      <c r="C2122">
+        <v>5010</v>
+      </c>
+      <c r="D2122" t="s">
+        <v>2124</v>
+      </c>
+    </row>
+    <row r="2123" spans="1:4">
+      <c r="A2123" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2123">
+        <v>10</v>
+      </c>
+      <c r="C2123">
+        <v>4980</v>
+      </c>
+      <c r="D2123" t="s">
+        <v>2125</v>
+      </c>
+    </row>
+    <row r="2124" spans="1:4">
+      <c r="A2124" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2124">
+        <v>11</v>
+      </c>
+      <c r="C2124">
+        <v>4960</v>
+      </c>
+      <c r="D2124" t="s">
+        <v>2126</v>
+      </c>
+    </row>
+    <row r="2125" spans="1:4">
+      <c r="A2125" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2125">
+        <v>12</v>
+      </c>
+      <c r="C2125">
+        <v>4930</v>
+      </c>
+      <c r="D2125" t="s">
+        <v>2127</v>
+      </c>
+    </row>
+    <row r="2126" spans="1:4">
+      <c r="A2126" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2126">
+        <v>13</v>
+      </c>
+      <c r="C2126">
+        <v>4900</v>
+      </c>
+      <c r="D2126" t="s">
+        <v>2128</v>
+      </c>
+    </row>
+    <row r="2127" spans="1:4">
+      <c r="A2127" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2127">
+        <v>14</v>
+      </c>
+      <c r="C2127">
+        <v>4880</v>
+      </c>
+      <c r="D2127" t="s">
+        <v>2129</v>
+      </c>
+    </row>
+    <row r="2128" spans="1:4">
+      <c r="A2128" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2128">
+        <v>15</v>
+      </c>
+      <c r="C2128">
+        <v>4880</v>
+      </c>
+      <c r="D2128" t="s">
+        <v>2130</v>
+      </c>
+    </row>
+    <row r="2129" spans="1:4">
+      <c r="A2129" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2129">
+        <v>16</v>
+      </c>
+      <c r="C2129">
+        <v>4880</v>
+      </c>
+      <c r="D2129" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="2130" spans="1:4">
+      <c r="A2130" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2130">
+        <v>17</v>
+      </c>
+      <c r="C2130">
+        <v>4880</v>
+      </c>
+      <c r="D2130" t="s">
+        <v>2132</v>
+      </c>
+    </row>
+    <row r="2131" spans="1:4">
+      <c r="A2131" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2131">
+        <v>18</v>
+      </c>
+      <c r="C2131">
+        <v>4880</v>
+      </c>
+      <c r="D2131" t="s">
+        <v>2133</v>
+      </c>
+    </row>
+    <row r="2132" spans="1:4">
+      <c r="A2132" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2132">
+        <v>19</v>
+      </c>
+      <c r="C2132">
+        <v>4880</v>
+      </c>
+      <c r="D2132" t="s">
+        <v>2134</v>
+      </c>
+    </row>
+    <row r="2133" spans="1:4">
+      <c r="A2133" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2133">
+        <v>20</v>
+      </c>
+      <c r="C2133">
+        <v>4870</v>
+      </c>
+      <c r="D2133" t="s">
+        <v>2135</v>
+      </c>
+    </row>
+    <row r="2134" spans="1:4">
+      <c r="A2134" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2134">
+        <v>21</v>
+      </c>
+      <c r="C2134">
+        <v>4850</v>
+      </c>
+      <c r="D2134" t="s">
+        <v>2136</v>
+      </c>
+    </row>
+    <row r="2135" spans="1:4">
+      <c r="A2135" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2135">
+        <v>22</v>
+      </c>
+      <c r="C2135">
+        <v>4840</v>
+      </c>
+      <c r="D2135" t="s">
+        <v>2137</v>
+      </c>
+    </row>
+    <row r="2136" spans="1:4">
+      <c r="A2136" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2136">
+        <v>23</v>
+      </c>
+      <c r="C2136">
+        <v>4830</v>
+      </c>
+      <c r="D2136" t="s">
+        <v>2138</v>
+      </c>
+    </row>
+    <row r="2137" spans="1:4">
+      <c r="A2137" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2137">
+        <v>24</v>
+      </c>
+      <c r="C2137">
+        <v>4830</v>
+      </c>
+      <c r="D2137" t="s">
+        <v>2139</v>
+      </c>
+    </row>
+    <row r="2138" spans="1:4">
+      <c r="A2138" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2138">
+        <v>25</v>
+      </c>
+      <c r="C2138">
+        <v>4830</v>
+      </c>
+      <c r="D2138" t="s">
+        <v>2140</v>
+      </c>
+    </row>
+    <row r="2139" spans="1:4">
+      <c r="A2139" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2139">
+        <v>26</v>
+      </c>
+      <c r="C2139">
+        <v>4840</v>
+      </c>
+      <c r="D2139" t="s">
+        <v>2141</v>
+      </c>
+    </row>
+    <row r="2140" spans="1:4">
+      <c r="A2140" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2140">
+        <v>27</v>
+      </c>
+      <c r="C2140">
+        <v>4860</v>
+      </c>
+      <c r="D2140" t="s">
+        <v>2142</v>
+      </c>
+    </row>
+    <row r="2141" spans="1:4">
+      <c r="A2141" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2141">
+        <v>28</v>
+      </c>
+      <c r="C2141">
+        <v>4890</v>
+      </c>
+      <c r="D2141" t="s">
+        <v>2143</v>
+      </c>
+    </row>
+    <row r="2142" spans="1:4">
+      <c r="A2142" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2142">
+        <v>29</v>
+      </c>
+      <c r="C2142">
+        <v>4920</v>
+      </c>
+      <c r="D2142" t="s">
+        <v>2144</v>
+      </c>
+    </row>
+    <row r="2143" spans="1:4">
+      <c r="A2143" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2143">
+        <v>30</v>
+      </c>
+      <c r="C2143">
+        <v>4960</v>
+      </c>
+      <c r="D2143" t="s">
+        <v>2145</v>
+      </c>
+    </row>
+    <row r="2144" spans="1:4">
+      <c r="A2144" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2144">
+        <v>31</v>
+      </c>
+      <c r="C2144">
+        <v>4990</v>
+      </c>
+      <c r="D2144" t="s">
+        <v>2146</v>
+      </c>
+    </row>
+    <row r="2145" spans="1:4">
+      <c r="A2145" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2145">
+        <v>32</v>
+      </c>
+      <c r="C2145">
+        <v>5030</v>
+      </c>
+      <c r="D2145" t="s">
+        <v>2147</v>
+      </c>
+    </row>
+    <row r="2146" spans="1:4">
+      <c r="A2146" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2146">
+        <v>33</v>
+      </c>
+      <c r="C2146">
+        <v>5070</v>
+      </c>
+      <c r="D2146" t="s">
+        <v>2148</v>
+      </c>
+    </row>
+    <row r="2147" spans="1:4">
+      <c r="A2147" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2147">
+        <v>34</v>
+      </c>
+      <c r="C2147">
+        <v>5080</v>
+      </c>
+      <c r="D2147" t="s">
+        <v>2149</v>
+      </c>
+    </row>
+    <row r="2148" spans="1:4">
+      <c r="A2148" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2148">
+        <v>35</v>
+      </c>
+      <c r="C2148">
+        <v>5050</v>
+      </c>
+      <c r="D2148" t="s">
+        <v>2150</v>
+      </c>
+    </row>
+    <row r="2149" spans="1:4">
+      <c r="A2149" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2149">
+        <v>36</v>
+      </c>
+      <c r="C2149">
+        <v>4990</v>
+      </c>
+      <c r="D2149" t="s">
+        <v>2151</v>
+      </c>
+    </row>
+    <row r="2150" spans="1:4">
+      <c r="A2150" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2150">
+        <v>37</v>
+      </c>
+      <c r="C2150">
+        <v>4900</v>
+      </c>
+      <c r="D2150" t="s">
+        <v>2152</v>
+      </c>
+    </row>
+    <row r="2151" spans="1:4">
+      <c r="A2151" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2151">
+        <v>38</v>
+      </c>
+      <c r="C2151">
+        <v>4830</v>
+      </c>
+      <c r="D2151" t="s">
+        <v>2153</v>
+      </c>
+    </row>
+    <row r="2152" spans="1:4">
+      <c r="A2152" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2152">
+        <v>39</v>
+      </c>
+      <c r="C2152">
+        <v>4770</v>
+      </c>
+      <c r="D2152" t="s">
+        <v>2154</v>
+      </c>
+    </row>
+    <row r="2153" spans="1:4">
+      <c r="A2153" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2153">
+        <v>40</v>
+      </c>
+      <c r="C2153">
+        <v>4720</v>
+      </c>
+      <c r="D2153" t="s">
+        <v>2155</v>
+      </c>
+    </row>
+    <row r="2154" spans="1:4">
+      <c r="A2154" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2154">
+        <v>41</v>
+      </c>
+      <c r="C2154">
+        <v>4690</v>
+      </c>
+      <c r="D2154" t="s">
+        <v>2156</v>
+      </c>
+    </row>
+    <row r="2155" spans="1:4">
+      <c r="A2155" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2155">
+        <v>42</v>
+      </c>
+      <c r="C2155">
+        <v>4650</v>
+      </c>
+      <c r="D2155" t="s">
+        <v>2157</v>
+      </c>
+    </row>
+    <row r="2156" spans="1:4">
+      <c r="A2156" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2156">
+        <v>43</v>
+      </c>
+      <c r="C2156">
+        <v>4590</v>
+      </c>
+      <c r="D2156" t="s">
+        <v>2158</v>
+      </c>
+    </row>
+    <row r="2157" spans="1:4">
+      <c r="A2157" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2157">
+        <v>44</v>
+      </c>
+      <c r="C2157">
+        <v>4520</v>
+      </c>
+      <c r="D2157" t="s">
+        <v>2159</v>
+      </c>
+    </row>
+    <row r="2158" spans="1:4">
+      <c r="A2158" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2158">
+        <v>45</v>
+      </c>
+      <c r="C2158">
+        <v>4440</v>
+      </c>
+      <c r="D2158" t="s">
+        <v>2160</v>
+      </c>
+    </row>
+    <row r="2159" spans="1:4">
+      <c r="A2159" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2159">
+        <v>46</v>
+      </c>
+      <c r="C2159">
+        <v>4370</v>
+      </c>
+      <c r="D2159" t="s">
+        <v>2161</v>
+      </c>
+    </row>
+    <row r="2160" spans="1:4">
+      <c r="A2160" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2160">
+        <v>47</v>
+      </c>
+      <c r="C2160">
+        <v>4320</v>
+      </c>
+      <c r="D2160" t="s">
+        <v>2162</v>
+      </c>
+    </row>
+    <row r="2161" spans="1:4">
+      <c r="A2161" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2161">
+        <v>48</v>
+      </c>
+      <c r="C2161">
+        <v>4280</v>
+      </c>
+      <c r="D2161" t="s">
+        <v>2163</v>
+      </c>
+    </row>
+    <row r="2162" spans="1:4">
+      <c r="A2162" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2162">
+        <v>49</v>
+      </c>
+      <c r="C2162">
+        <v>4260</v>
+      </c>
+      <c r="D2162" t="s">
+        <v>2164</v>
+      </c>
+    </row>
+    <row r="2163" spans="1:4">
+      <c r="A2163" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2163">
+        <v>50</v>
+      </c>
+      <c r="C2163">
+        <v>4250</v>
+      </c>
+      <c r="D2163" t="s">
+        <v>2165</v>
+      </c>
+    </row>
+    <row r="2164" spans="1:4">
+      <c r="A2164" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2164">
+        <v>51</v>
+      </c>
+      <c r="C2164">
+        <v>4230</v>
+      </c>
+      <c r="D2164" t="s">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="2165" spans="1:4">
+      <c r="A2165" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2165">
+        <v>52</v>
+      </c>
+      <c r="C2165">
+        <v>4210</v>
+      </c>
+      <c r="D2165" t="s">
+        <v>2167</v>
+      </c>
+    </row>
+    <row r="2166" spans="1:4">
+      <c r="A2166" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2166">
+        <v>53</v>
+      </c>
+      <c r="C2166">
+        <v>4190</v>
+      </c>
+      <c r="D2166" t="s">
+        <v>2168</v>
+      </c>
+    </row>
+    <row r="2167" spans="1:4">
+      <c r="A2167" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2167">
+        <v>54</v>
+      </c>
+      <c r="C2167">
+        <v>4180</v>
+      </c>
+      <c r="D2167" t="s">
+        <v>2169</v>
+      </c>
+    </row>
+    <row r="2168" spans="1:4">
+      <c r="A2168" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2168">
+        <v>55</v>
+      </c>
+      <c r="C2168">
+        <v>4160</v>
+      </c>
+      <c r="D2168" t="s">
+        <v>2170</v>
+      </c>
+    </row>
+    <row r="2169" spans="1:4">
+      <c r="A2169" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2169">
+        <v>56</v>
+      </c>
+      <c r="C2169">
+        <v>4150</v>
+      </c>
+      <c r="D2169" t="s">
+        <v>2171</v>
+      </c>
+    </row>
+    <row r="2170" spans="1:4">
+      <c r="A2170" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2170">
+        <v>57</v>
+      </c>
+      <c r="C2170">
+        <v>4150</v>
+      </c>
+      <c r="D2170" t="s">
+        <v>2172</v>
+      </c>
+    </row>
+    <row r="2171" spans="1:4">
+      <c r="A2171" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2171">
+        <v>58</v>
+      </c>
+      <c r="C2171">
+        <v>4150</v>
+      </c>
+      <c r="D2171" t="s">
+        <v>2173</v>
+      </c>
+    </row>
+    <row r="2172" spans="1:4">
+      <c r="A2172" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2172">
+        <v>59</v>
+      </c>
+      <c r="C2172">
+        <v>4160</v>
+      </c>
+      <c r="D2172" t="s">
+        <v>2174</v>
+      </c>
+    </row>
+    <row r="2173" spans="1:4">
+      <c r="A2173" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2173">
+        <v>60</v>
+      </c>
+      <c r="C2173">
+        <v>4180</v>
+      </c>
+      <c r="D2173" t="s">
+        <v>2175</v>
+      </c>
+    </row>
+    <row r="2174" spans="1:4">
+      <c r="A2174" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2174">
+        <v>61</v>
+      </c>
+      <c r="C2174">
+        <v>4200</v>
+      </c>
+      <c r="D2174" t="s">
+        <v>2176</v>
+      </c>
+    </row>
+    <row r="2175" spans="1:4">
+      <c r="A2175" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2175">
+        <v>62</v>
+      </c>
+      <c r="C2175">
+        <v>4240</v>
+      </c>
+      <c r="D2175" t="s">
+        <v>2177</v>
+      </c>
+    </row>
+    <row r="2176" spans="1:4">
+      <c r="A2176" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2176">
+        <v>63</v>
+      </c>
+      <c r="C2176">
+        <v>4280</v>
+      </c>
+      <c r="D2176" t="s">
+        <v>2178</v>
+      </c>
+    </row>
+    <row r="2177" spans="1:4">
+      <c r="A2177" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2177">
+        <v>64</v>
+      </c>
+      <c r="C2177">
+        <v>4330</v>
+      </c>
+      <c r="D2177" t="s">
+        <v>2179</v>
+      </c>
+    </row>
+    <row r="2178" spans="1:4">
+      <c r="A2178" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2178">
+        <v>65</v>
+      </c>
+      <c r="C2178">
+        <v>4390</v>
+      </c>
+      <c r="D2178" t="s">
+        <v>2180</v>
+      </c>
+    </row>
+    <row r="2179" spans="1:4">
+      <c r="A2179" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2179">
+        <v>66</v>
+      </c>
+      <c r="C2179">
+        <v>4470</v>
+      </c>
+      <c r="D2179" t="s">
+        <v>2181</v>
+      </c>
+    </row>
+    <row r="2180" spans="1:4">
+      <c r="A2180" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2180">
+        <v>67</v>
+      </c>
+      <c r="C2180">
+        <v>4550</v>
+      </c>
+      <c r="D2180" t="s">
+        <v>2182</v>
+      </c>
+    </row>
+    <row r="2181" spans="1:4">
+      <c r="A2181" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2181">
+        <v>68</v>
+      </c>
+      <c r="C2181">
+        <v>4650</v>
+      </c>
+      <c r="D2181" t="s">
+        <v>2183</v>
+      </c>
+    </row>
+    <row r="2182" spans="1:4">
+      <c r="A2182" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2182">
+        <v>69</v>
+      </c>
+      <c r="C2182">
+        <v>4770</v>
+      </c>
+      <c r="D2182" t="s">
+        <v>2184</v>
+      </c>
+    </row>
+    <row r="2183" spans="1:4">
+      <c r="A2183" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2183">
+        <v>70</v>
+      </c>
+      <c r="C2183">
+        <v>4880</v>
+      </c>
+      <c r="D2183" t="s">
+        <v>2185</v>
+      </c>
+    </row>
+    <row r="2184" spans="1:4">
+      <c r="A2184" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2184">
+        <v>71</v>
+      </c>
+      <c r="C2184">
+        <v>4990</v>
+      </c>
+      <c r="D2184" t="s">
+        <v>2186</v>
+      </c>
+    </row>
+    <row r="2185" spans="1:4">
+      <c r="A2185" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2185">
+        <v>72</v>
+      </c>
+      <c r="C2185">
+        <v>5090</v>
+      </c>
+      <c r="D2185" t="s">
+        <v>2187</v>
+      </c>
+    </row>
+    <row r="2186" spans="1:4">
+      <c r="A2186" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2186">
+        <v>73</v>
+      </c>
+      <c r="C2186">
+        <v>5200</v>
+      </c>
+      <c r="D2186" t="s">
+        <v>2188</v>
+      </c>
+    </row>
+    <row r="2187" spans="1:4">
+      <c r="A2187" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2187">
+        <v>74</v>
+      </c>
+      <c r="C2187">
+        <v>5310</v>
+      </c>
+      <c r="D2187" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="2188" spans="1:4">
+      <c r="A2188" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2188">
+        <v>75</v>
+      </c>
+      <c r="C2188">
+        <v>5410</v>
+      </c>
+      <c r="D2188" t="s">
+        <v>2190</v>
+      </c>
+    </row>
+    <row r="2189" spans="1:4">
+      <c r="A2189" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2189">
+        <v>76</v>
+      </c>
+      <c r="C2189">
+        <v>5530</v>
+      </c>
+      <c r="D2189" t="s">
+        <v>2191</v>
+      </c>
+    </row>
+    <row r="2190" spans="1:4">
+      <c r="A2190" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2190">
+        <v>77</v>
+      </c>
+      <c r="C2190">
+        <v>5640</v>
+      </c>
+      <c r="D2190" t="s">
+        <v>2192</v>
+      </c>
+    </row>
+    <row r="2191" spans="1:4">
+      <c r="A2191" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2191">
+        <v>78</v>
+      </c>
+      <c r="C2191">
+        <v>5730</v>
+      </c>
+      <c r="D2191" t="s">
+        <v>2193</v>
+      </c>
+    </row>
+    <row r="2192" spans="1:4">
+      <c r="A2192" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2192">
+        <v>79</v>
+      </c>
+      <c r="C2192">
+        <v>5810</v>
+      </c>
+      <c r="D2192" t="s">
+        <v>2194</v>
+      </c>
+    </row>
+    <row r="2193" spans="1:4">
+      <c r="A2193" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2193">
+        <v>80</v>
+      </c>
+      <c r="C2193">
+        <v>5870</v>
+      </c>
+      <c r="D2193" t="s">
+        <v>2195</v>
+      </c>
+    </row>
+    <row r="2194" spans="1:4">
+      <c r="A2194" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2194">
+        <v>81</v>
+      </c>
+      <c r="C2194">
+        <v>5920</v>
+      </c>
+      <c r="D2194" t="s">
+        <v>2196</v>
+      </c>
+    </row>
+    <row r="2195" spans="1:4">
+      <c r="A2195" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2195">
+        <v>82</v>
+      </c>
+      <c r="C2195">
+        <v>5980</v>
+      </c>
+      <c r="D2195" t="s">
+        <v>2197</v>
+      </c>
+    </row>
+    <row r="2196" spans="1:4">
+      <c r="A2196" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2196">
+        <v>83</v>
+      </c>
+      <c r="C2196">
+        <v>6050</v>
+      </c>
+      <c r="D2196" t="s">
+        <v>2198</v>
+      </c>
+    </row>
+    <row r="2197" spans="1:4">
+      <c r="A2197" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2197">
+        <v>84</v>
+      </c>
+      <c r="C2197">
+        <v>6130</v>
+      </c>
+      <c r="D2197" t="s">
+        <v>2199</v>
+      </c>
+    </row>
+    <row r="2198" spans="1:4">
+      <c r="A2198" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2198">
+        <v>85</v>
+      </c>
+      <c r="C2198">
+        <v>6210</v>
+      </c>
+      <c r="D2198" t="s">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="2199" spans="1:4">
+      <c r="A2199" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2199">
+        <v>86</v>
+      </c>
+      <c r="C2199">
+        <v>6260</v>
+      </c>
+      <c r="D2199" t="s">
+        <v>2201</v>
+      </c>
+    </row>
+    <row r="2200" spans="1:4">
+      <c r="A2200" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2200">
+        <v>87</v>
+      </c>
+      <c r="C2200">
+        <v>6250</v>
+      </c>
+      <c r="D2200" t="s">
+        <v>2202</v>
+      </c>
+    </row>
+    <row r="2201" spans="1:4">
+      <c r="A2201" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2201">
+        <v>88</v>
+      </c>
+      <c r="C2201">
+        <v>6180</v>
+      </c>
+      <c r="D2201" t="s">
+        <v>2203</v>
+      </c>
+    </row>
+    <row r="2202" spans="1:4">
+      <c r="A2202" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2202">
+        <v>89</v>
+      </c>
+      <c r="C2202">
+        <v>6070</v>
+      </c>
+      <c r="D2202" t="s">
+        <v>2204</v>
+      </c>
+    </row>
+    <row r="2203" spans="1:4">
+      <c r="A2203" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2203">
+        <v>90</v>
+      </c>
+      <c r="C2203">
+        <v>5950</v>
+      </c>
+      <c r="D2203" t="s">
+        <v>2205</v>
+      </c>
+    </row>
+    <row r="2204" spans="1:4">
+      <c r="A2204" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2204">
+        <v>91</v>
+      </c>
+      <c r="C2204">
+        <v>5830</v>
+      </c>
+      <c r="D2204" t="s">
+        <v>2206</v>
+      </c>
+    </row>
+    <row r="2205" spans="1:4">
+      <c r="A2205" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2205">
+        <v>92</v>
+      </c>
+      <c r="C2205">
+        <v>5710</v>
+      </c>
+      <c r="D2205" t="s">
+        <v>2207</v>
+      </c>
+    </row>
+    <row r="2206" spans="1:4">
+      <c r="A2206" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2206">
+        <v>93</v>
+      </c>
+      <c r="C2206">
+        <v>5590</v>
+      </c>
+      <c r="D2206" t="s">
+        <v>2208</v>
+      </c>
+    </row>
+    <row r="2207" spans="1:4">
+      <c r="A2207" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2207">
+        <v>94</v>
+      </c>
+      <c r="C2207">
+        <v>5470</v>
+      </c>
+      <c r="D2207" t="s">
+        <v>2209</v>
+      </c>
+    </row>
+    <row r="2208" spans="1:4">
+      <c r="A2208" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2208">
+        <v>95</v>
+      </c>
+      <c r="C2208">
+        <v>5360</v>
+      </c>
+      <c r="D2208" t="s">
+        <v>2210</v>
+      </c>
+    </row>
+    <row r="2209" spans="1:4">
+      <c r="A2209" s="2">
+        <v>46165</v>
+      </c>
+      <c r="B2209">
+        <v>96</v>
+      </c>
+      <c r="C2209">
+        <v>5250</v>
+      </c>
+      <c r="D2209" t="s">
+        <v>2211</v>
+      </c>
+    </row>
+    <row r="2210" spans="1:4">
+      <c r="A2210" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2210">
+        <v>1</v>
+      </c>
+      <c r="C2210">
+        <v>5140</v>
+      </c>
+      <c r="D2210" t="s">
+        <v>2212</v>
+      </c>
+    </row>
+    <row r="2211" spans="1:4">
+      <c r="A2211" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2211">
+        <v>2</v>
+      </c>
+      <c r="C2211">
+        <v>5050</v>
+      </c>
+      <c r="D2211" t="s">
+        <v>2213</v>
+      </c>
+    </row>
+    <row r="2212" spans="1:4">
+      <c r="A2212" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2212">
+        <v>3</v>
+      </c>
+      <c r="C2212">
+        <v>4970</v>
+      </c>
+      <c r="D2212" t="s">
+        <v>2214</v>
+      </c>
+    </row>
+    <row r="2213" spans="1:4">
+      <c r="A2213" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2213">
+        <v>4</v>
+      </c>
+      <c r="C2213">
+        <v>4900</v>
+      </c>
+      <c r="D2213" t="s">
+        <v>2215</v>
+      </c>
+    </row>
+    <row r="2214" spans="1:4">
+      <c r="A2214" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2214">
+        <v>5</v>
+      </c>
+      <c r="C2214">
+        <v>4830</v>
+      </c>
+      <c r="D2214" t="s">
+        <v>2216</v>
+      </c>
+    </row>
+    <row r="2215" spans="1:4">
+      <c r="A2215" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2215">
+        <v>6</v>
+      </c>
+      <c r="C2215">
+        <v>4780</v>
+      </c>
+      <c r="D2215" t="s">
+        <v>2217</v>
+      </c>
+    </row>
+    <row r="2216" spans="1:4">
+      <c r="A2216" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2216">
+        <v>7</v>
+      </c>
+      <c r="C2216">
+        <v>4740</v>
+      </c>
+      <c r="D2216" t="s">
+        <v>2218</v>
+      </c>
+    </row>
+    <row r="2217" spans="1:4">
+      <c r="A2217" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2217">
+        <v>8</v>
+      </c>
+      <c r="C2217">
+        <v>4700</v>
+      </c>
+      <c r="D2217" t="s">
+        <v>2219</v>
+      </c>
+    </row>
+    <row r="2218" spans="1:4">
+      <c r="A2218" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2218">
+        <v>9</v>
+      </c>
+      <c r="C2218">
+        <v>4670</v>
+      </c>
+      <c r="D2218" t="s">
+        <v>2220</v>
+      </c>
+    </row>
+    <row r="2219" spans="1:4">
+      <c r="A2219" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2219">
+        <v>10</v>
+      </c>
+      <c r="C2219">
+        <v>4640</v>
+      </c>
+      <c r="D2219" t="s">
+        <v>2221</v>
+      </c>
+    </row>
+    <row r="2220" spans="1:4">
+      <c r="A2220" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2220">
+        <v>11</v>
+      </c>
+      <c r="C2220">
+        <v>4620</v>
+      </c>
+      <c r="D2220" t="s">
+        <v>2222</v>
+      </c>
+    </row>
+    <row r="2221" spans="1:4">
+      <c r="A2221" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2221">
+        <v>12</v>
+      </c>
+      <c r="C2221">
+        <v>4600</v>
+      </c>
+      <c r="D2221" t="s">
+        <v>2223</v>
+      </c>
+    </row>
+    <row r="2222" spans="1:4">
+      <c r="A2222" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2222">
+        <v>13</v>
+      </c>
+      <c r="C2222">
+        <v>4580</v>
+      </c>
+      <c r="D2222" t="s">
+        <v>2224</v>
+      </c>
+    </row>
+    <row r="2223" spans="1:4">
+      <c r="A2223" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2223">
+        <v>14</v>
+      </c>
+      <c r="C2223">
+        <v>4570</v>
+      </c>
+      <c r="D2223" t="s">
+        <v>2225</v>
+      </c>
+    </row>
+    <row r="2224" spans="1:4">
+      <c r="A2224" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2224">
+        <v>15</v>
+      </c>
+      <c r="C2224">
+        <v>4560</v>
+      </c>
+      <c r="D2224" t="s">
+        <v>2226</v>
+      </c>
+    </row>
+    <row r="2225" spans="1:4">
+      <c r="A2225" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2225">
+        <v>16</v>
+      </c>
+      <c r="C2225">
+        <v>4560</v>
+      </c>
+      <c r="D2225" t="s">
+        <v>2227</v>
+      </c>
+    </row>
+    <row r="2226" spans="1:4">
+      <c r="A2226" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2226">
+        <v>17</v>
+      </c>
+      <c r="C2226">
+        <v>4570</v>
+      </c>
+      <c r="D2226" t="s">
+        <v>2228</v>
+      </c>
+    </row>
+    <row r="2227" spans="1:4">
+      <c r="A2227" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2227">
+        <v>18</v>
+      </c>
+      <c r="C2227">
+        <v>4560</v>
+      </c>
+      <c r="D2227" t="s">
+        <v>2229</v>
+      </c>
+    </row>
+    <row r="2228" spans="1:4">
+      <c r="A2228" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2228">
+        <v>19</v>
+      </c>
+      <c r="C2228">
+        <v>4540</v>
+      </c>
+      <c r="D2228" t="s">
+        <v>2230</v>
+      </c>
+    </row>
+    <row r="2229" spans="1:4">
+      <c r="A2229" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2229">
+        <v>20</v>
+      </c>
+      <c r="C2229">
+        <v>4500</v>
+      </c>
+      <c r="D2229" t="s">
+        <v>2231</v>
+      </c>
+    </row>
+    <row r="2230" spans="1:4">
+      <c r="A2230" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2230">
+        <v>21</v>
+      </c>
+      <c r="C2230">
+        <v>4460</v>
+      </c>
+      <c r="D2230" t="s">
+        <v>2232</v>
+      </c>
+    </row>
+    <row r="2231" spans="1:4">
+      <c r="A2231" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2231">
+        <v>22</v>
+      </c>
+      <c r="C2231">
+        <v>4430</v>
+      </c>
+      <c r="D2231" t="s">
+        <v>2233</v>
+      </c>
+    </row>
+    <row r="2232" spans="1:4">
+      <c r="A2232" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2232">
+        <v>23</v>
+      </c>
+      <c r="C2232">
+        <v>4410</v>
+      </c>
+      <c r="D2232" t="s">
+        <v>2234</v>
+      </c>
+    </row>
+    <row r="2233" spans="1:4">
+      <c r="A2233" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2233">
+        <v>24</v>
+      </c>
+      <c r="C2233">
+        <v>4410</v>
+      </c>
+      <c r="D2233" t="s">
+        <v>2235</v>
+      </c>
+    </row>
+    <row r="2234" spans="1:4">
+      <c r="A2234" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2234">
+        <v>25</v>
+      </c>
+      <c r="C2234">
+        <v>4420</v>
+      </c>
+      <c r="D2234" t="s">
+        <v>2236</v>
+      </c>
+    </row>
+    <row r="2235" spans="1:4">
+      <c r="A2235" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2235">
+        <v>26</v>
+      </c>
+      <c r="C2235">
+        <v>4420</v>
+      </c>
+      <c r="D2235" t="s">
+        <v>2237</v>
+      </c>
+    </row>
+    <row r="2236" spans="1:4">
+      <c r="A2236" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2236">
+        <v>27</v>
+      </c>
+      <c r="C2236">
+        <v>4410</v>
+      </c>
+      <c r="D2236" t="s">
+        <v>2238</v>
+      </c>
+    </row>
+    <row r="2237" spans="1:4">
+      <c r="A2237" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2237">
+        <v>28</v>
+      </c>
+      <c r="C2237">
+        <v>4380</v>
+      </c>
+      <c r="D2237" t="s">
+        <v>2239</v>
+      </c>
+    </row>
+    <row r="2238" spans="1:4">
+      <c r="A2238" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2238">
+        <v>29</v>
+      </c>
+      <c r="C2238">
+        <v>4350</v>
+      </c>
+      <c r="D2238" t="s">
+        <v>2240</v>
+      </c>
+    </row>
+    <row r="2239" spans="1:4">
+      <c r="A2239" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2239">
+        <v>30</v>
+      </c>
+      <c r="C2239">
+        <v>4330</v>
+      </c>
+      <c r="D2239" t="s">
+        <v>2241</v>
+      </c>
+    </row>
+    <row r="2240" spans="1:4">
+      <c r="A2240" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2240">
+        <v>31</v>
+      </c>
+      <c r="C2240">
+        <v>4310</v>
+      </c>
+      <c r="D2240" t="s">
+        <v>2242</v>
+      </c>
+    </row>
+    <row r="2241" spans="1:4">
+      <c r="A2241" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2241">
+        <v>32</v>
+      </c>
+      <c r="C2241">
+        <v>4310</v>
+      </c>
+      <c r="D2241" t="s">
+        <v>2243</v>
+      </c>
+    </row>
+    <row r="2242" spans="1:4">
+      <c r="A2242" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2242">
+        <v>33</v>
+      </c>
+      <c r="C2242">
+        <v>4310</v>
+      </c>
+      <c r="D2242" t="s">
+        <v>2244</v>
+      </c>
+    </row>
+    <row r="2243" spans="1:4">
+      <c r="A2243" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2243">
+        <v>34</v>
+      </c>
+      <c r="C2243">
+        <v>4290</v>
+      </c>
+      <c r="D2243" t="s">
+        <v>2245</v>
+      </c>
+    </row>
+    <row r="2244" spans="1:4">
+      <c r="A2244" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2244">
+        <v>35</v>
+      </c>
+      <c r="C2244">
+        <v>4240</v>
+      </c>
+      <c r="D2244" t="s">
+        <v>2246</v>
+      </c>
+    </row>
+    <row r="2245" spans="1:4">
+      <c r="A2245" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2245">
+        <v>36</v>
+      </c>
+      <c r="C2245">
+        <v>4160</v>
+      </c>
+      <c r="D2245" t="s">
+        <v>2247</v>
+      </c>
+    </row>
+    <row r="2246" spans="1:4">
+      <c r="A2246" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2246">
+        <v>37</v>
+      </c>
+      <c r="C2246">
+        <v>4060</v>
+      </c>
+      <c r="D2246" t="s">
+        <v>2248</v>
+      </c>
+    </row>
+    <row r="2247" spans="1:4">
+      <c r="A2247" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2247">
+        <v>38</v>
+      </c>
+      <c r="C2247">
+        <v>3970</v>
+      </c>
+      <c r="D2247" t="s">
+        <v>2249</v>
+      </c>
+    </row>
+    <row r="2248" spans="1:4">
+      <c r="A2248" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2248">
+        <v>39</v>
+      </c>
+      <c r="C2248">
+        <v>3890</v>
+      </c>
+      <c r="D2248" t="s">
+        <v>2250</v>
+      </c>
+    </row>
+    <row r="2249" spans="1:4">
+      <c r="A2249" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2249">
+        <v>40</v>
+      </c>
+      <c r="C2249">
+        <v>3840</v>
+      </c>
+      <c r="D2249" t="s">
+        <v>2251</v>
+      </c>
+    </row>
+    <row r="2250" spans="1:4">
+      <c r="A2250" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2250">
+        <v>41</v>
+      </c>
+      <c r="C2250">
+        <v>3790</v>
+      </c>
+      <c r="D2250" t="s">
+        <v>2252</v>
+      </c>
+    </row>
+    <row r="2251" spans="1:4">
+      <c r="A2251" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2251">
+        <v>42</v>
+      </c>
+      <c r="C2251">
+        <v>3740</v>
+      </c>
+      <c r="D2251" t="s">
+        <v>2253</v>
+      </c>
+    </row>
+    <row r="2252" spans="1:4">
+      <c r="A2252" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2252">
+        <v>43</v>
+      </c>
+      <c r="C2252">
+        <v>3690</v>
+      </c>
+      <c r="D2252" t="s">
+        <v>2254</v>
+      </c>
+    </row>
+    <row r="2253" spans="1:4">
+      <c r="A2253" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2253">
+        <v>44</v>
+      </c>
+      <c r="C2253">
+        <v>3620</v>
+      </c>
+      <c r="D2253" t="s">
+        <v>2255</v>
+      </c>
+    </row>
+    <row r="2254" spans="1:4">
+      <c r="A2254" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2254">
+        <v>45</v>
+      </c>
+      <c r="C2254">
+        <v>3550</v>
+      </c>
+      <c r="D2254" t="s">
+        <v>2256</v>
+      </c>
+    </row>
+    <row r="2255" spans="1:4">
+      <c r="A2255" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2255">
+        <v>46</v>
+      </c>
+      <c r="C2255">
+        <v>3490</v>
+      </c>
+      <c r="D2255" t="s">
+        <v>2257</v>
+      </c>
+    </row>
+    <row r="2256" spans="1:4">
+      <c r="A2256" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2256">
+        <v>47</v>
+      </c>
+      <c r="C2256">
+        <v>3450</v>
+      </c>
+      <c r="D2256" t="s">
+        <v>2258</v>
+      </c>
+    </row>
+    <row r="2257" spans="1:4">
+      <c r="A2257" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2257">
+        <v>48</v>
+      </c>
+      <c r="C2257">
+        <v>3420</v>
+      </c>
+      <c r="D2257" t="s">
+        <v>2259</v>
+      </c>
+    </row>
+    <row r="2258" spans="1:4">
+      <c r="A2258" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2258">
+        <v>49</v>
+      </c>
+      <c r="C2258">
+        <v>3400</v>
+      </c>
+      <c r="D2258" t="s">
+        <v>2260</v>
+      </c>
+    </row>
+    <row r="2259" spans="1:4">
+      <c r="A2259" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2259">
+        <v>50</v>
+      </c>
+      <c r="C2259">
+        <v>3390</v>
+      </c>
+      <c r="D2259" t="s">
+        <v>2261</v>
+      </c>
+    </row>
+    <row r="2260" spans="1:4">
+      <c r="A2260" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2260">
+        <v>51</v>
+      </c>
+      <c r="C2260">
+        <v>3390</v>
+      </c>
+      <c r="D2260" t="s">
+        <v>2262</v>
+      </c>
+    </row>
+    <row r="2261" spans="1:4">
+      <c r="A2261" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2261">
+        <v>52</v>
+      </c>
+      <c r="C2261">
+        <v>3390</v>
+      </c>
+      <c r="D2261" t="s">
+        <v>2263</v>
+      </c>
+    </row>
+    <row r="2262" spans="1:4">
+      <c r="A2262" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2262">
+        <v>53</v>
+      </c>
+      <c r="C2262">
+        <v>3390</v>
+      </c>
+      <c r="D2262" t="s">
+        <v>2264</v>
+      </c>
+    </row>
+    <row r="2263" spans="1:4">
+      <c r="A2263" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2263">
+        <v>54</v>
+      </c>
+      <c r="C2263">
+        <v>3390</v>
+      </c>
+      <c r="D2263" t="s">
+        <v>2265</v>
+      </c>
+    </row>
+    <row r="2264" spans="1:4">
+      <c r="A2264" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2264">
+        <v>55</v>
+      </c>
+      <c r="C2264">
+        <v>3390</v>
+      </c>
+      <c r="D2264" t="s">
+        <v>2266</v>
+      </c>
+    </row>
+    <row r="2265" spans="1:4">
+      <c r="A2265" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2265">
+        <v>56</v>
+      </c>
+      <c r="C2265">
+        <v>3380</v>
+      </c>
+      <c r="D2265" t="s">
+        <v>2267</v>
+      </c>
+    </row>
+    <row r="2266" spans="1:4">
+      <c r="A2266" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2266">
+        <v>57</v>
+      </c>
+      <c r="C2266">
+        <v>3370</v>
+      </c>
+      <c r="D2266" t="s">
+        <v>2268</v>
+      </c>
+    </row>
+    <row r="2267" spans="1:4">
+      <c r="A2267" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2267">
+        <v>58</v>
+      </c>
+      <c r="C2267">
+        <v>3370</v>
+      </c>
+      <c r="D2267" t="s">
+        <v>2269</v>
+      </c>
+    </row>
+    <row r="2268" spans="1:4">
+      <c r="A2268" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2268">
+        <v>59</v>
+      </c>
+      <c r="C2268">
+        <v>3380</v>
+      </c>
+      <c r="D2268" t="s">
+        <v>2270</v>
+      </c>
+    </row>
+    <row r="2269" spans="1:4">
+      <c r="A2269" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2269">
+        <v>60</v>
+      </c>
+      <c r="C2269">
+        <v>3410</v>
+      </c>
+      <c r="D2269" t="s">
+        <v>2271</v>
+      </c>
+    </row>
+    <row r="2270" spans="1:4">
+      <c r="A2270" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2270">
+        <v>61</v>
+      </c>
+      <c r="C2270">
+        <v>3450</v>
+      </c>
+      <c r="D2270" t="s">
+        <v>2272</v>
+      </c>
+    </row>
+    <row r="2271" spans="1:4">
+      <c r="A2271" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2271">
+        <v>62</v>
+      </c>
+      <c r="C2271">
+        <v>3500</v>
+      </c>
+      <c r="D2271" t="s">
+        <v>2273</v>
+      </c>
+    </row>
+    <row r="2272" spans="1:4">
+      <c r="A2272" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2272">
+        <v>63</v>
+      </c>
+      <c r="C2272">
+        <v>3570</v>
+      </c>
+      <c r="D2272" t="s">
+        <v>2274</v>
+      </c>
+    </row>
+    <row r="2273" spans="1:4">
+      <c r="A2273" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2273">
+        <v>64</v>
+      </c>
+      <c r="C2273">
+        <v>3640</v>
+      </c>
+      <c r="D2273" t="s">
+        <v>2275</v>
+      </c>
+    </row>
+    <row r="2274" spans="1:4">
+      <c r="A2274" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2274">
+        <v>65</v>
+      </c>
+      <c r="C2274">
+        <v>3720</v>
+      </c>
+      <c r="D2274" t="s">
+        <v>2276</v>
+      </c>
+    </row>
+    <row r="2275" spans="1:4">
+      <c r="A2275" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2275">
+        <v>66</v>
+      </c>
+      <c r="C2275">
+        <v>3820</v>
+      </c>
+      <c r="D2275" t="s">
+        <v>2277</v>
+      </c>
+    </row>
+    <row r="2276" spans="1:4">
+      <c r="A2276" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2276">
+        <v>67</v>
+      </c>
+      <c r="C2276">
+        <v>3910</v>
+      </c>
+      <c r="D2276" t="s">
+        <v>2278</v>
+      </c>
+    </row>
+    <row r="2277" spans="1:4">
+      <c r="A2277" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2277">
+        <v>68</v>
+      </c>
+      <c r="C2277">
+        <v>4020</v>
+      </c>
+      <c r="D2277" t="s">
+        <v>2279</v>
+      </c>
+    </row>
+    <row r="2278" spans="1:4">
+      <c r="A2278" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2278">
+        <v>69</v>
+      </c>
+      <c r="C2278">
+        <v>4130</v>
+      </c>
+      <c r="D2278" t="s">
+        <v>2280</v>
+      </c>
+    </row>
+    <row r="2279" spans="1:4">
+      <c r="A2279" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2279">
+        <v>70</v>
+      </c>
+      <c r="C2279">
+        <v>4250</v>
+      </c>
+      <c r="D2279" t="s">
+        <v>2281</v>
+      </c>
+    </row>
+    <row r="2280" spans="1:4">
+      <c r="A2280" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2280">
+        <v>71</v>
+      </c>
+      <c r="C2280">
+        <v>4360</v>
+      </c>
+      <c r="D2280" t="s">
+        <v>2282</v>
+      </c>
+    </row>
+    <row r="2281" spans="1:4">
+      <c r="A2281" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2281">
+        <v>72</v>
+      </c>
+      <c r="C2281">
+        <v>4480</v>
+      </c>
+      <c r="D2281" t="s">
+        <v>2283</v>
+      </c>
+    </row>
+    <row r="2282" spans="1:4">
+      <c r="A2282" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2282">
+        <v>73</v>
+      </c>
+      <c r="C2282">
+        <v>4610</v>
+      </c>
+      <c r="D2282" t="s">
+        <v>2284</v>
+      </c>
+    </row>
+    <row r="2283" spans="1:4">
+      <c r="A2283" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2283">
+        <v>74</v>
+      </c>
+      <c r="C2283">
+        <v>4730</v>
+      </c>
+      <c r="D2283" t="s">
+        <v>2285</v>
+      </c>
+    </row>
+    <row r="2284" spans="1:4">
+      <c r="A2284" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2284">
+        <v>75</v>
+      </c>
+      <c r="C2284">
+        <v>4860</v>
+      </c>
+      <c r="D2284" t="s">
+        <v>2286</v>
+      </c>
+    </row>
+    <row r="2285" spans="1:4">
+      <c r="A2285" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2285">
+        <v>76</v>
+      </c>
+      <c r="C2285">
+        <v>4990</v>
+      </c>
+      <c r="D2285" t="s">
+        <v>2287</v>
+      </c>
+    </row>
+    <row r="2286" spans="1:4">
+      <c r="A2286" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2286">
+        <v>77</v>
+      </c>
+      <c r="C2286">
+        <v>5120</v>
+      </c>
+      <c r="D2286" t="s">
+        <v>2288</v>
+      </c>
+    </row>
+    <row r="2287" spans="1:4">
+      <c r="A2287" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2287">
+        <v>78</v>
+      </c>
+      <c r="C2287">
+        <v>5220</v>
+      </c>
+      <c r="D2287" t="s">
+        <v>2289</v>
+      </c>
+    </row>
+    <row r="2288" spans="1:4">
+      <c r="A2288" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2288">
+        <v>79</v>
+      </c>
+      <c r="C2288">
+        <v>5310</v>
+      </c>
+      <c r="D2288" t="s">
+        <v>2290</v>
+      </c>
+    </row>
+    <row r="2289" spans="1:4">
+      <c r="A2289" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2289">
+        <v>80</v>
+      </c>
+      <c r="C2289">
+        <v>5370</v>
+      </c>
+      <c r="D2289" t="s">
+        <v>2291</v>
+      </c>
+    </row>
+    <row r="2290" spans="1:4">
+      <c r="A2290" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2290">
+        <v>81</v>
+      </c>
+      <c r="C2290">
+        <v>5420</v>
+      </c>
+      <c r="D2290" t="s">
+        <v>2292</v>
+      </c>
+    </row>
+    <row r="2291" spans="1:4">
+      <c r="A2291" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2291">
+        <v>82</v>
+      </c>
+      <c r="C2291">
+        <v>5480</v>
+      </c>
+      <c r="D2291" t="s">
+        <v>2293</v>
+      </c>
+    </row>
+    <row r="2292" spans="1:4">
+      <c r="A2292" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2292">
+        <v>83</v>
+      </c>
+      <c r="C2292">
+        <v>5560</v>
+      </c>
+      <c r="D2292" t="s">
+        <v>2294</v>
+      </c>
+    </row>
+    <row r="2293" spans="1:4">
+      <c r="A2293" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2293">
+        <v>84</v>
+      </c>
+      <c r="C2293">
+        <v>5680</v>
+      </c>
+      <c r="D2293" t="s">
+        <v>2295</v>
+      </c>
+    </row>
+    <row r="2294" spans="1:4">
+      <c r="A2294" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2294">
+        <v>85</v>
+      </c>
+      <c r="C2294">
+        <v>5800</v>
+      </c>
+      <c r="D2294" t="s">
+        <v>2296</v>
+      </c>
+    </row>
+    <row r="2295" spans="1:4">
+      <c r="A2295" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2295">
+        <v>86</v>
+      </c>
+      <c r="C2295">
+        <v>5870</v>
+      </c>
+      <c r="D2295" t="s">
+        <v>2297</v>
+      </c>
+    </row>
+    <row r="2296" spans="1:4">
+      <c r="A2296" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2296">
+        <v>87</v>
+      </c>
+      <c r="C2296">
+        <v>5890</v>
+      </c>
+      <c r="D2296" t="s">
+        <v>2298</v>
+      </c>
+    </row>
+    <row r="2297" spans="1:4">
+      <c r="A2297" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2297">
+        <v>88</v>
+      </c>
+      <c r="C2297">
+        <v>5840</v>
+      </c>
+      <c r="D2297" t="s">
+        <v>2299</v>
+      </c>
+    </row>
+    <row r="2298" spans="1:4">
+      <c r="A2298" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2298">
+        <v>89</v>
+      </c>
+      <c r="C2298">
+        <v>5740</v>
+      </c>
+      <c r="D2298" t="s">
+        <v>2300</v>
+      </c>
+    </row>
+    <row r="2299" spans="1:4">
+      <c r="A2299" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2299">
+        <v>90</v>
+      </c>
+      <c r="C2299">
+        <v>5620</v>
+      </c>
+      <c r="D2299" t="s">
+        <v>2301</v>
+      </c>
+    </row>
+    <row r="2300" spans="1:4">
+      <c r="A2300" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2300">
+        <v>91</v>
+      </c>
+      <c r="C2300">
+        <v>5510</v>
+      </c>
+      <c r="D2300" t="s">
+        <v>2302</v>
+      </c>
+    </row>
+    <row r="2301" spans="1:4">
+      <c r="A2301" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2301">
+        <v>92</v>
+      </c>
+      <c r="C2301">
+        <v>5390</v>
+      </c>
+      <c r="D2301" t="s">
+        <v>2303</v>
+      </c>
+    </row>
+    <row r="2302" spans="1:4">
+      <c r="A2302" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2302">
+        <v>93</v>
+      </c>
+      <c r="C2302">
+        <v>5270</v>
+      </c>
+      <c r="D2302" t="s">
+        <v>2304</v>
+      </c>
+    </row>
+    <row r="2303" spans="1:4">
+      <c r="A2303" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2303">
+        <v>94</v>
+      </c>
+      <c r="C2303">
+        <v>5160</v>
+      </c>
+      <c r="D2303" t="s">
+        <v>2305</v>
+      </c>
+    </row>
+    <row r="2304" spans="1:4">
+      <c r="A2304" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2304">
+        <v>95</v>
+      </c>
+      <c r="C2304">
+        <v>5060</v>
+      </c>
+      <c r="D2304" t="s">
+        <v>2306</v>
+      </c>
+    </row>
+    <row r="2305" spans="1:4">
+      <c r="A2305" s="2">
+        <v>46166</v>
+      </c>
+      <c r="B2305">
+        <v>96</v>
+      </c>
+      <c r="C2305">
+        <v>4970</v>
+      </c>
+      <c r="D2305" t="s">
+        <v>2307</v>
+      </c>
+    </row>
+    <row r="2306" spans="1:4">
+      <c r="A2306" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2306">
+        <v>1</v>
+      </c>
+      <c r="C2306">
+        <v>4860</v>
+      </c>
+      <c r="D2306" t="s">
+        <v>2308</v>
+      </c>
+    </row>
+    <row r="2307" spans="1:4">
+      <c r="A2307" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2307">
+        <v>2</v>
+      </c>
+      <c r="C2307">
+        <v>4790</v>
+      </c>
+      <c r="D2307" t="s">
+        <v>2309</v>
+      </c>
+    </row>
+    <row r="2308" spans="1:4">
+      <c r="A2308" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2308">
+        <v>3</v>
+      </c>
+      <c r="C2308">
+        <v>4720</v>
+      </c>
+      <c r="D2308" t="s">
+        <v>2310</v>
+      </c>
+    </row>
+    <row r="2309" spans="1:4">
+      <c r="A2309" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2309">
+        <v>4</v>
+      </c>
+      <c r="C2309">
+        <v>4660</v>
+      </c>
+      <c r="D2309" t="s">
+        <v>2311</v>
+      </c>
+    </row>
+    <row r="2310" spans="1:4">
+      <c r="A2310" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2310">
+        <v>5</v>
+      </c>
+      <c r="C2310">
+        <v>4600</v>
+      </c>
+      <c r="D2310" t="s">
+        <v>2312</v>
+      </c>
+    </row>
+    <row r="2311" spans="1:4">
+      <c r="A2311" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2311">
+        <v>6</v>
+      </c>
+      <c r="C2311">
+        <v>4560</v>
+      </c>
+      <c r="D2311" t="s">
+        <v>2313</v>
+      </c>
+    </row>
+    <row r="2312" spans="1:4">
+      <c r="A2312" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2312">
+        <v>7</v>
+      </c>
+      <c r="C2312">
+        <v>4520</v>
+      </c>
+      <c r="D2312" t="s">
+        <v>2314</v>
+      </c>
+    </row>
+    <row r="2313" spans="1:4">
+      <c r="A2313" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2313">
+        <v>8</v>
+      </c>
+      <c r="C2313">
+        <v>4490</v>
+      </c>
+      <c r="D2313" t="s">
+        <v>2315</v>
+      </c>
+    </row>
+    <row r="2314" spans="1:4">
+      <c r="A2314" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2314">
+        <v>9</v>
+      </c>
+      <c r="C2314">
+        <v>4480</v>
+      </c>
+      <c r="D2314" t="s">
+        <v>2316</v>
+      </c>
+    </row>
+    <row r="2315" spans="1:4">
+      <c r="A2315" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2315">
+        <v>10</v>
+      </c>
+      <c r="C2315">
+        <v>4470</v>
+      </c>
+      <c r="D2315" t="s">
+        <v>2317</v>
+      </c>
+    </row>
+    <row r="2316" spans="1:4">
+      <c r="A2316" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2316">
+        <v>11</v>
+      </c>
+      <c r="C2316">
+        <v>4460</v>
+      </c>
+      <c r="D2316" t="s">
+        <v>2318</v>
+      </c>
+    </row>
+    <row r="2317" spans="1:4">
+      <c r="A2317" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2317">
+        <v>12</v>
+      </c>
+      <c r="C2317">
+        <v>4450</v>
+      </c>
+      <c r="D2317" t="s">
+        <v>2319</v>
+      </c>
+    </row>
+    <row r="2318" spans="1:4">
+      <c r="A2318" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2318">
+        <v>13</v>
+      </c>
+      <c r="C2318">
+        <v>4450</v>
+      </c>
+      <c r="D2318" t="s">
+        <v>2320</v>
+      </c>
+    </row>
+    <row r="2319" spans="1:4">
+      <c r="A2319" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2319">
+        <v>14</v>
+      </c>
+      <c r="C2319">
+        <v>4450</v>
+      </c>
+      <c r="D2319" t="s">
+        <v>2321</v>
+      </c>
+    </row>
+    <row r="2320" spans="1:4">
+      <c r="A2320" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2320">
+        <v>15</v>
+      </c>
+      <c r="C2320">
+        <v>4460</v>
+      </c>
+      <c r="D2320" t="s">
+        <v>2322</v>
+      </c>
+    </row>
+    <row r="2321" spans="1:4">
+      <c r="A2321" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2321">
+        <v>16</v>
+      </c>
+      <c r="C2321">
+        <v>4470</v>
+      </c>
+      <c r="D2321" t="s">
+        <v>2323</v>
+      </c>
+    </row>
+    <row r="2322" spans="1:4">
+      <c r="A2322" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2322">
+        <v>17</v>
+      </c>
+      <c r="C2322">
+        <v>4480</v>
+      </c>
+      <c r="D2322" t="s">
+        <v>2324</v>
+      </c>
+    </row>
+    <row r="2323" spans="1:4">
+      <c r="A2323" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2323">
+        <v>18</v>
+      </c>
+      <c r="C2323">
+        <v>4490</v>
+      </c>
+      <c r="D2323" t="s">
+        <v>2325</v>
+      </c>
+    </row>
+    <row r="2324" spans="1:4">
+      <c r="A2324" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2324">
+        <v>19</v>
+      </c>
+      <c r="C2324">
+        <v>4500</v>
+      </c>
+      <c r="D2324" t="s">
+        <v>2326</v>
+      </c>
+    </row>
+    <row r="2325" spans="1:4">
+      <c r="A2325" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2325">
+        <v>20</v>
+      </c>
+      <c r="C2325">
+        <v>4510</v>
+      </c>
+      <c r="D2325" t="s">
+        <v>2327</v>
+      </c>
+    </row>
+    <row r="2326" spans="1:4">
+      <c r="A2326" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2326">
+        <v>21</v>
+      </c>
+      <c r="C2326">
+        <v>4520</v>
+      </c>
+      <c r="D2326" t="s">
+        <v>2328</v>
+      </c>
+    </row>
+    <row r="2327" spans="1:4">
+      <c r="A2327" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2327">
+        <v>22</v>
+      </c>
+      <c r="C2327">
+        <v>4560</v>
+      </c>
+      <c r="D2327" t="s">
+        <v>2329</v>
+      </c>
+    </row>
+    <row r="2328" spans="1:4">
+      <c r="A2328" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2328">
+        <v>23</v>
+      </c>
+      <c r="C2328">
+        <v>4630</v>
+      </c>
+      <c r="D2328" t="s">
+        <v>2330</v>
+      </c>
+    </row>
+    <row r="2329" spans="1:4">
+      <c r="A2329" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2329">
+        <v>24</v>
+      </c>
+      <c r="C2329">
+        <v>4730</v>
+      </c>
+      <c r="D2329" t="s">
+        <v>2331</v>
+      </c>
+    </row>
+    <row r="2330" spans="1:4">
+      <c r="A2330" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2330">
+        <v>25</v>
+      </c>
+      <c r="C2330">
+        <v>4850</v>
+      </c>
+      <c r="D2330" t="s">
+        <v>2332</v>
+      </c>
+    </row>
+    <row r="2331" spans="1:4">
+      <c r="A2331" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2331">
+        <v>26</v>
+      </c>
+      <c r="C2331">
+        <v>4980</v>
+      </c>
+      <c r="D2331" t="s">
+        <v>2333</v>
+      </c>
+    </row>
+    <row r="2332" spans="1:4">
+      <c r="A2332" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2332">
+        <v>27</v>
+      </c>
+      <c r="C2332">
+        <v>5120</v>
+      </c>
+      <c r="D2332" t="s">
+        <v>2334</v>
+      </c>
+    </row>
+    <row r="2333" spans="1:4">
+      <c r="A2333" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2333">
+        <v>28</v>
+      </c>
+      <c r="C2333">
+        <v>5250</v>
+      </c>
+      <c r="D2333" t="s">
+        <v>2335</v>
+      </c>
+    </row>
+    <row r="2334" spans="1:4">
+      <c r="A2334" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2334">
+        <v>29</v>
+      </c>
+      <c r="C2334">
+        <v>5380</v>
+      </c>
+      <c r="D2334" t="s">
+        <v>2336</v>
+      </c>
+    </row>
+    <row r="2335" spans="1:4">
+      <c r="A2335" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2335">
+        <v>30</v>
+      </c>
+      <c r="C2335">
+        <v>5500</v>
+      </c>
+      <c r="D2335" t="s">
+        <v>2337</v>
+      </c>
+    </row>
+    <row r="2336" spans="1:4">
+      <c r="A2336" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2336">
+        <v>31</v>
+      </c>
+      <c r="C2336">
+        <v>5580</v>
+      </c>
+      <c r="D2336" t="s">
+        <v>2338</v>
+      </c>
+    </row>
+    <row r="2337" spans="1:4">
+      <c r="A2337" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2337">
+        <v>32</v>
+      </c>
+      <c r="C2337">
+        <v>5640</v>
+      </c>
+      <c r="D2337" t="s">
+        <v>2339</v>
+      </c>
+    </row>
+    <row r="2338" spans="1:4">
+      <c r="A2338" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2338">
+        <v>33</v>
+      </c>
+      <c r="C2338">
+        <v>5680</v>
+      </c>
+      <c r="D2338" t="s">
+        <v>2340</v>
+      </c>
+    </row>
+    <row r="2339" spans="1:4">
+      <c r="A2339" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2339">
+        <v>34</v>
+      </c>
+      <c r="C2339">
+        <v>5680</v>
+      </c>
+      <c r="D2339" t="s">
+        <v>2341</v>
+      </c>
+    </row>
+    <row r="2340" spans="1:4">
+      <c r="A2340" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2340">
+        <v>35</v>
+      </c>
+      <c r="C2340">
+        <v>5660</v>
+      </c>
+      <c r="D2340" t="s">
+        <v>2342</v>
+      </c>
+    </row>
+    <row r="2341" spans="1:4">
+      <c r="A2341" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2341">
+        <v>36</v>
+      </c>
+      <c r="C2341">
+        <v>5590</v>
+      </c>
+      <c r="D2341" t="s">
+        <v>2343</v>
+      </c>
+    </row>
+    <row r="2342" spans="1:4">
+      <c r="A2342" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2342">
+        <v>37</v>
+      </c>
+      <c r="C2342">
+        <v>5510</v>
+      </c>
+      <c r="D2342" t="s">
+        <v>2344</v>
+      </c>
+    </row>
+    <row r="2343" spans="1:4">
+      <c r="A2343" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2343">
+        <v>38</v>
+      </c>
+      <c r="C2343">
+        <v>5420</v>
+      </c>
+      <c r="D2343" t="s">
+        <v>2345</v>
+      </c>
+    </row>
+    <row r="2344" spans="1:4">
+      <c r="A2344" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2344">
+        <v>39</v>
+      </c>
+      <c r="C2344">
+        <v>5330</v>
+      </c>
+      <c r="D2344" t="s">
+        <v>2346</v>
+      </c>
+    </row>
+    <row r="2345" spans="1:4">
+      <c r="A2345" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2345">
+        <v>40</v>
+      </c>
+      <c r="C2345">
+        <v>5250</v>
+      </c>
+      <c r="D2345" t="s">
+        <v>2347</v>
+      </c>
+    </row>
+    <row r="2346" spans="1:4">
+      <c r="A2346" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2346">
+        <v>41</v>
+      </c>
+      <c r="C2346">
+        <v>5180</v>
+      </c>
+      <c r="D2346" t="s">
+        <v>2348</v>
+      </c>
+    </row>
+    <row r="2347" spans="1:4">
+      <c r="A2347" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2347">
+        <v>42</v>
+      </c>
+      <c r="C2347">
+        <v>5090</v>
+      </c>
+      <c r="D2347" t="s">
+        <v>2349</v>
+      </c>
+    </row>
+    <row r="2348" spans="1:4">
+      <c r="A2348" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2348">
+        <v>43</v>
+      </c>
+      <c r="C2348">
+        <v>4990</v>
+      </c>
+      <c r="D2348" t="s">
+        <v>2350</v>
+      </c>
+    </row>
+    <row r="2349" spans="1:4">
+      <c r="A2349" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2349">
+        <v>44</v>
+      </c>
+      <c r="C2349">
+        <v>4890</v>
+      </c>
+      <c r="D2349" t="s">
+        <v>2351</v>
+      </c>
+    </row>
+    <row r="2350" spans="1:4">
+      <c r="A2350" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2350">
+        <v>45</v>
+      </c>
+      <c r="C2350">
+        <v>4770</v>
+      </c>
+      <c r="D2350" t="s">
+        <v>2352</v>
+      </c>
+    </row>
+    <row r="2351" spans="1:4">
+      <c r="A2351" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2351">
+        <v>46</v>
+      </c>
+      <c r="C2351">
+        <v>4680</v>
+      </c>
+      <c r="D2351" t="s">
+        <v>2353</v>
+      </c>
+    </row>
+    <row r="2352" spans="1:4">
+      <c r="A2352" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2352">
+        <v>47</v>
+      </c>
+      <c r="C2352">
+        <v>4610</v>
+      </c>
+      <c r="D2352" t="s">
+        <v>2354</v>
+      </c>
+    </row>
+    <row r="2353" spans="1:4">
+      <c r="A2353" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2353">
+        <v>48</v>
+      </c>
+      <c r="C2353">
+        <v>4570</v>
+      </c>
+      <c r="D2353" t="s">
+        <v>2355</v>
+      </c>
+    </row>
+    <row r="2354" spans="1:4">
+      <c r="A2354" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2354">
+        <v>49</v>
+      </c>
+      <c r="C2354">
+        <v>4560</v>
+      </c>
+      <c r="D2354" t="s">
+        <v>2356</v>
+      </c>
+    </row>
+    <row r="2355" spans="1:4">
+      <c r="A2355" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2355">
+        <v>50</v>
+      </c>
+      <c r="C2355">
+        <v>4550</v>
+      </c>
+      <c r="D2355" t="s">
+        <v>2357</v>
+      </c>
+    </row>
+    <row r="2356" spans="1:4">
+      <c r="A2356" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2356">
+        <v>51</v>
+      </c>
+      <c r="C2356">
+        <v>4560</v>
+      </c>
+      <c r="D2356" t="s">
+        <v>2358</v>
+      </c>
+    </row>
+    <row r="2357" spans="1:4">
+      <c r="A2357" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2357">
+        <v>52</v>
+      </c>
+      <c r="C2357">
+        <v>4560</v>
+      </c>
+      <c r="D2357" t="s">
+        <v>2359</v>
+      </c>
+    </row>
+    <row r="2358" spans="1:4">
+      <c r="A2358" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2358">
+        <v>53</v>
+      </c>
+      <c r="C2358">
+        <v>4580</v>
+      </c>
+      <c r="D2358" t="s">
+        <v>2360</v>
+      </c>
+    </row>
+    <row r="2359" spans="1:4">
+      <c r="A2359" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2359">
+        <v>54</v>
+      </c>
+      <c r="C2359">
+        <v>4580</v>
+      </c>
+      <c r="D2359" t="s">
+        <v>2361</v>
+      </c>
+    </row>
+    <row r="2360" spans="1:4">
+      <c r="A2360" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2360">
+        <v>55</v>
+      </c>
+      <c r="C2360">
+        <v>4580</v>
+      </c>
+      <c r="D2360" t="s">
+        <v>2362</v>
+      </c>
+    </row>
+    <row r="2361" spans="1:4">
+      <c r="A2361" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2361">
+        <v>56</v>
+      </c>
+      <c r="C2361">
+        <v>4570</v>
+      </c>
+      <c r="D2361" t="s">
+        <v>2363</v>
+      </c>
+    </row>
+    <row r="2362" spans="1:4">
+      <c r="A2362" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2362">
+        <v>57</v>
+      </c>
+      <c r="C2362">
+        <v>4550</v>
+      </c>
+      <c r="D2362" t="s">
+        <v>2364</v>
+      </c>
+    </row>
+    <row r="2363" spans="1:4">
+      <c r="A2363" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2363">
+        <v>58</v>
+      </c>
+      <c r="C2363">
+        <v>4550</v>
+      </c>
+      <c r="D2363" t="s">
+        <v>2365</v>
+      </c>
+    </row>
+    <row r="2364" spans="1:4">
+      <c r="A2364" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2364">
+        <v>59</v>
+      </c>
+      <c r="C2364">
+        <v>4580</v>
+      </c>
+      <c r="D2364" t="s">
+        <v>2366</v>
+      </c>
+    </row>
+    <row r="2365" spans="1:4">
+      <c r="A2365" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2365">
+        <v>60</v>
+      </c>
+      <c r="C2365">
+        <v>4620</v>
+      </c>
+      <c r="D2365" t="s">
+        <v>2367</v>
+      </c>
+    </row>
+    <row r="2366" spans="1:4">
+      <c r="A2366" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2366">
+        <v>61</v>
+      </c>
+      <c r="C2366">
+        <v>4680</v>
+      </c>
+      <c r="D2366" t="s">
+        <v>2368</v>
+      </c>
+    </row>
+    <row r="2367" spans="1:4">
+      <c r="A2367" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2367">
+        <v>62</v>
+      </c>
+      <c r="C2367">
+        <v>4750</v>
+      </c>
+      <c r="D2367" t="s">
+        <v>2369</v>
+      </c>
+    </row>
+    <row r="2368" spans="1:4">
+      <c r="A2368" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2368">
+        <v>63</v>
+      </c>
+      <c r="C2368">
+        <v>4810</v>
+      </c>
+      <c r="D2368" t="s">
+        <v>2370</v>
+      </c>
+    </row>
+    <row r="2369" spans="1:4">
+      <c r="A2369" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2369">
+        <v>64</v>
+      </c>
+      <c r="C2369">
+        <v>4870</v>
+      </c>
+      <c r="D2369" t="s">
+        <v>2371</v>
+      </c>
+    </row>
+    <row r="2370" spans="1:4">
+      <c r="A2370" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2370">
+        <v>65</v>
+      </c>
+      <c r="C2370">
+        <v>4930</v>
+      </c>
+      <c r="D2370" t="s">
+        <v>2372</v>
+      </c>
+    </row>
+    <row r="2371" spans="1:4">
+      <c r="A2371" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2371">
+        <v>66</v>
+      </c>
+      <c r="C2371">
+        <v>4990</v>
+      </c>
+      <c r="D2371" t="s">
+        <v>2373</v>
+      </c>
+    </row>
+    <row r="2372" spans="1:4">
+      <c r="A2372" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2372">
+        <v>67</v>
+      </c>
+      <c r="C2372">
+        <v>5070</v>
+      </c>
+      <c r="D2372" t="s">
+        <v>2374</v>
+      </c>
+    </row>
+    <row r="2373" spans="1:4">
+      <c r="A2373" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2373">
+        <v>68</v>
+      </c>
+      <c r="C2373">
+        <v>5150</v>
+      </c>
+      <c r="D2373" t="s">
+        <v>2375</v>
+      </c>
+    </row>
+    <row r="2374" spans="1:4">
+      <c r="A2374" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2374">
+        <v>69</v>
+      </c>
+      <c r="C2374">
+        <v>5230</v>
+      </c>
+      <c r="D2374" t="s">
+        <v>2376</v>
+      </c>
+    </row>
+    <row r="2375" spans="1:4">
+      <c r="A2375" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2375">
+        <v>70</v>
+      </c>
+      <c r="C2375">
+        <v>5330</v>
+      </c>
+      <c r="D2375" t="s">
+        <v>2377</v>
+      </c>
+    </row>
+    <row r="2376" spans="1:4">
+      <c r="A2376" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2376">
+        <v>71</v>
+      </c>
+      <c r="C2376">
+        <v>5430</v>
+      </c>
+      <c r="D2376" t="s">
+        <v>2378</v>
+      </c>
+    </row>
+    <row r="2377" spans="1:4">
+      <c r="A2377" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2377">
+        <v>72</v>
+      </c>
+      <c r="C2377">
+        <v>5540</v>
+      </c>
+      <c r="D2377" t="s">
+        <v>2379</v>
+      </c>
+    </row>
+    <row r="2378" spans="1:4">
+      <c r="A2378" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2378">
+        <v>73</v>
+      </c>
+      <c r="C2378">
+        <v>5650</v>
+      </c>
+      <c r="D2378" t="s">
+        <v>2380</v>
+      </c>
+    </row>
+    <row r="2379" spans="1:4">
+      <c r="A2379" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2379">
+        <v>74</v>
+      </c>
+      <c r="C2379">
+        <v>5760</v>
+      </c>
+      <c r="D2379" t="s">
+        <v>2381</v>
+      </c>
+    </row>
+    <row r="2380" spans="1:4">
+      <c r="A2380" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2380">
+        <v>75</v>
+      </c>
+      <c r="C2380">
+        <v>5880</v>
+      </c>
+      <c r="D2380" t="s">
+        <v>2382</v>
+      </c>
+    </row>
+    <row r="2381" spans="1:4">
+      <c r="A2381" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2381">
+        <v>76</v>
+      </c>
+      <c r="C2381">
+        <v>5990</v>
+      </c>
+      <c r="D2381" t="s">
+        <v>2383</v>
+      </c>
+    </row>
+    <row r="2382" spans="1:4">
+      <c r="A2382" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2382">
+        <v>77</v>
+      </c>
+      <c r="C2382">
+        <v>6100</v>
+      </c>
+      <c r="D2382" t="s">
+        <v>2384</v>
+      </c>
+    </row>
+    <row r="2383" spans="1:4">
+      <c r="A2383" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2383">
+        <v>78</v>
+      </c>
+      <c r="C2383">
+        <v>6190</v>
+      </c>
+      <c r="D2383" t="s">
+        <v>2385</v>
+      </c>
+    </row>
+    <row r="2384" spans="1:4">
+      <c r="A2384" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2384">
+        <v>79</v>
+      </c>
+      <c r="C2384">
+        <v>6280</v>
+      </c>
+      <c r="D2384" t="s">
+        <v>2386</v>
+      </c>
+    </row>
+    <row r="2385" spans="1:4">
+      <c r="A2385" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2385">
+        <v>80</v>
+      </c>
+      <c r="C2385">
+        <v>6340</v>
+      </c>
+      <c r="D2385" t="s">
+        <v>2387</v>
+      </c>
+    </row>
+    <row r="2386" spans="1:4">
+      <c r="A2386" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2386">
+        <v>81</v>
+      </c>
+      <c r="C2386">
+        <v>6390</v>
+      </c>
+      <c r="D2386" t="s">
+        <v>2388</v>
+      </c>
+    </row>
+    <row r="2387" spans="1:4">
+      <c r="A2387" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2387">
+        <v>82</v>
+      </c>
+      <c r="C2387">
+        <v>6460</v>
+      </c>
+      <c r="D2387" t="s">
+        <v>2389</v>
+      </c>
+    </row>
+    <row r="2388" spans="1:4">
+      <c r="A2388" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2388">
+        <v>83</v>
+      </c>
+      <c r="C2388">
+        <v>6530</v>
+      </c>
+      <c r="D2388" t="s">
+        <v>2390</v>
+      </c>
+    </row>
+    <row r="2389" spans="1:4">
+      <c r="A2389" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2389">
+        <v>84</v>
+      </c>
+      <c r="C2389">
+        <v>6610</v>
+      </c>
+      <c r="D2389" t="s">
+        <v>2391</v>
+      </c>
+    </row>
+    <row r="2390" spans="1:4">
+      <c r="A2390" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2390">
+        <v>85</v>
+      </c>
+      <c r="C2390">
+        <v>6690</v>
+      </c>
+      <c r="D2390" t="s">
+        <v>2392</v>
+      </c>
+    </row>
+    <row r="2391" spans="1:4">
+      <c r="A2391" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2391">
+        <v>86</v>
+      </c>
+      <c r="C2391">
+        <v>6730</v>
+      </c>
+      <c r="D2391" t="s">
+        <v>2393</v>
+      </c>
+    </row>
+    <row r="2392" spans="1:4">
+      <c r="A2392" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2392">
+        <v>87</v>
+      </c>
+      <c r="C2392">
+        <v>6710</v>
+      </c>
+      <c r="D2392" t="s">
+        <v>2394</v>
+      </c>
+    </row>
+    <row r="2393" spans="1:4">
+      <c r="A2393" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2393">
+        <v>88</v>
+      </c>
+      <c r="C2393">
+        <v>6620</v>
+      </c>
+      <c r="D2393" t="s">
+        <v>2395</v>
+      </c>
+    </row>
+    <row r="2394" spans="1:4">
+      <c r="A2394" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2394">
+        <v>89</v>
+      </c>
+      <c r="C2394">
+        <v>6490</v>
+      </c>
+      <c r="D2394" t="s">
+        <v>2396</v>
+      </c>
+    </row>
+    <row r="2395" spans="1:4">
+      <c r="A2395" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2395">
+        <v>90</v>
+      </c>
+      <c r="C2395">
+        <v>6340</v>
+      </c>
+      <c r="D2395" t="s">
+        <v>2397</v>
+      </c>
+    </row>
+    <row r="2396" spans="1:4">
+      <c r="A2396" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2396">
+        <v>91</v>
+      </c>
+      <c r="C2396">
+        <v>6190</v>
+      </c>
+      <c r="D2396" t="s">
+        <v>2398</v>
+      </c>
+    </row>
+    <row r="2397" spans="1:4">
+      <c r="A2397" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2397">
+        <v>92</v>
+      </c>
+      <c r="C2397">
+        <v>6030</v>
+      </c>
+      <c r="D2397" t="s">
+        <v>2399</v>
+      </c>
+    </row>
+    <row r="2398" spans="1:4">
+      <c r="A2398" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2398">
+        <v>93</v>
+      </c>
+      <c r="C2398">
+        <v>5870</v>
+      </c>
+      <c r="D2398" t="s">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="2399" spans="1:4">
+      <c r="A2399" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2399">
+        <v>94</v>
+      </c>
+      <c r="C2399">
+        <v>5730</v>
+      </c>
+      <c r="D2399" t="s">
+        <v>2401</v>
+      </c>
+    </row>
+    <row r="2400" spans="1:4">
+      <c r="A2400" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2400">
+        <v>95</v>
+      </c>
+      <c r="C2400">
+        <v>5600</v>
+      </c>
+      <c r="D2400" t="s">
+        <v>2402</v>
+      </c>
+    </row>
+    <row r="2401" spans="1:4">
+      <c r="A2401" s="2">
+        <v>46167</v>
+      </c>
+      <c r="B2401">
+        <v>96</v>
+      </c>
+      <c r="C2401">
+        <v>5490</v>
+      </c>
+      <c r="D2401" t="s">
+        <v>2403</v>
+      </c>
+    </row>
+    <row r="2402" spans="1:4">
+      <c r="A2402" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2402">
+        <v>1</v>
+      </c>
+      <c r="C2402">
+        <v>5390</v>
+      </c>
+      <c r="D2402" t="s">
+        <v>2404</v>
+      </c>
+    </row>
+    <row r="2403" spans="1:4">
+      <c r="A2403" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2403">
+        <v>2</v>
+      </c>
+      <c r="C2403">
+        <v>5310</v>
+      </c>
+      <c r="D2403" t="s">
+        <v>2405</v>
+      </c>
+    </row>
+    <row r="2404" spans="1:4">
+      <c r="A2404" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2404">
+        <v>3</v>
+      </c>
+      <c r="C2404">
+        <v>5230</v>
+      </c>
+      <c r="D2404" t="s">
+        <v>2406</v>
+      </c>
+    </row>
+    <row r="2405" spans="1:4">
+      <c r="A2405" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2405">
+        <v>4</v>
+      </c>
+      <c r="C2405">
+        <v>5170</v>
+      </c>
+      <c r="D2405" t="s">
+        <v>2407</v>
+      </c>
+    </row>
+    <row r="2406" spans="1:4">
+      <c r="A2406" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2406">
+        <v>5</v>
+      </c>
+      <c r="C2406">
+        <v>5110</v>
+      </c>
+      <c r="D2406" t="s">
+        <v>2408</v>
+      </c>
+    </row>
+    <row r="2407" spans="1:4">
+      <c r="A2407" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2407">
+        <v>6</v>
+      </c>
+      <c r="C2407">
+        <v>5070</v>
+      </c>
+      <c r="D2407" t="s">
+        <v>2409</v>
+      </c>
+    </row>
+    <row r="2408" spans="1:4">
+      <c r="A2408" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2408">
+        <v>7</v>
+      </c>
+      <c r="C2408">
+        <v>5030</v>
+      </c>
+      <c r="D2408" t="s">
+        <v>2410</v>
+      </c>
+    </row>
+    <row r="2409" spans="1:4">
+      <c r="A2409" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2409">
+        <v>8</v>
+      </c>
+      <c r="C2409">
+        <v>5000</v>
+      </c>
+      <c r="D2409" t="s">
+        <v>2411</v>
+      </c>
+    </row>
+    <row r="2410" spans="1:4">
+      <c r="A2410" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2410">
+        <v>9</v>
+      </c>
+      <c r="C2410">
+        <v>4970</v>
+      </c>
+      <c r="D2410" t="s">
+        <v>2412</v>
+      </c>
+    </row>
+    <row r="2411" spans="1:4">
+      <c r="A2411" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2411">
+        <v>10</v>
+      </c>
+      <c r="C2411">
+        <v>4950</v>
+      </c>
+      <c r="D2411" t="s">
+        <v>2413</v>
+      </c>
+    </row>
+    <row r="2412" spans="1:4">
+      <c r="A2412" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2412">
+        <v>11</v>
+      </c>
+      <c r="C2412">
+        <v>4940</v>
+      </c>
+      <c r="D2412" t="s">
+        <v>2414</v>
+      </c>
+    </row>
+    <row r="2413" spans="1:4">
+      <c r="A2413" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2413">
+        <v>12</v>
+      </c>
+      <c r="C2413">
+        <v>4920</v>
+      </c>
+      <c r="D2413" t="s">
+        <v>2415</v>
+      </c>
+    </row>
+    <row r="2414" spans="1:4">
+      <c r="A2414" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2414">
+        <v>13</v>
+      </c>
+      <c r="C2414">
+        <v>4920</v>
+      </c>
+      <c r="D2414" t="s">
+        <v>2416</v>
+      </c>
+    </row>
+    <row r="2415" spans="1:4">
+      <c r="A2415" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2415">
+        <v>14</v>
+      </c>
+      <c r="C2415">
+        <v>4910</v>
+      </c>
+      <c r="D2415" t="s">
+        <v>2417</v>
+      </c>
+    </row>
+    <row r="2416" spans="1:4">
+      <c r="A2416" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2416">
+        <v>15</v>
+      </c>
+      <c r="C2416">
+        <v>4920</v>
+      </c>
+      <c r="D2416" t="s">
+        <v>2418</v>
+      </c>
+    </row>
+    <row r="2417" spans="1:4">
+      <c r="A2417" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2417">
+        <v>16</v>
+      </c>
+      <c r="C2417">
+        <v>4920</v>
+      </c>
+      <c r="D2417" t="s">
+        <v>2419</v>
+      </c>
+    </row>
+    <row r="2418" spans="1:4">
+      <c r="A2418" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2418">
+        <v>17</v>
+      </c>
+      <c r="C2418">
+        <v>4930</v>
+      </c>
+      <c r="D2418" t="s">
+        <v>2420</v>
+      </c>
+    </row>
+    <row r="2419" spans="1:4">
+      <c r="A2419" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2419">
+        <v>18</v>
+      </c>
+      <c r="C2419">
+        <v>4930</v>
+      </c>
+      <c r="D2419" t="s">
+        <v>2421</v>
+      </c>
+    </row>
+    <row r="2420" spans="1:4">
+      <c r="A2420" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2420">
+        <v>19</v>
+      </c>
+      <c r="C2420">
+        <v>4940</v>
+      </c>
+      <c r="D2420" t="s">
+        <v>2422</v>
+      </c>
+    </row>
+    <row r="2421" spans="1:4">
+      <c r="A2421" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2421">
+        <v>20</v>
+      </c>
+      <c r="C2421">
+        <v>4940</v>
+      </c>
+      <c r="D2421" t="s">
+        <v>2423</v>
+      </c>
+    </row>
+    <row r="2422" spans="1:4">
+      <c r="A2422" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2422">
+        <v>21</v>
+      </c>
+      <c r="C2422">
+        <v>4950</v>
+      </c>
+      <c r="D2422" t="s">
+        <v>2424</v>
+      </c>
+    </row>
+    <row r="2423" spans="1:4">
+      <c r="A2423" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2423">
+        <v>22</v>
+      </c>
+      <c r="C2423">
+        <v>4970</v>
+      </c>
+      <c r="D2423" t="s">
+        <v>2425</v>
+      </c>
+    </row>
+    <row r="2424" spans="1:4">
+      <c r="A2424" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2424">
+        <v>23</v>
+      </c>
+      <c r="C2424">
+        <v>5010</v>
+      </c>
+      <c r="D2424" t="s">
+        <v>2426</v>
+      </c>
+    </row>
+    <row r="2425" spans="1:4">
+      <c r="A2425" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2425">
+        <v>24</v>
+      </c>
+      <c r="C2425">
+        <v>5070</v>
+      </c>
+      <c r="D2425" t="s">
+        <v>2427</v>
+      </c>
+    </row>
+    <row r="2426" spans="1:4">
+      <c r="A2426" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2426">
+        <v>25</v>
+      </c>
+      <c r="C2426">
+        <v>5150</v>
+      </c>
+      <c r="D2426" t="s">
+        <v>2428</v>
+      </c>
+    </row>
+    <row r="2427" spans="1:4">
+      <c r="A2427" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2427">
+        <v>26</v>
+      </c>
+      <c r="C2427">
+        <v>5250</v>
+      </c>
+      <c r="D2427" t="s">
+        <v>2429</v>
+      </c>
+    </row>
+    <row r="2428" spans="1:4">
+      <c r="A2428" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2428">
+        <v>27</v>
+      </c>
+      <c r="C2428">
+        <v>5360</v>
+      </c>
+      <c r="D2428" t="s">
+        <v>2430</v>
+      </c>
+    </row>
+    <row r="2429" spans="1:4">
+      <c r="A2429" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2429">
+        <v>28</v>
+      </c>
+      <c r="C2429">
+        <v>5480</v>
+      </c>
+      <c r="D2429" t="s">
+        <v>2431</v>
+      </c>
+    </row>
+    <row r="2430" spans="1:4">
+      <c r="A2430" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2430">
+        <v>29</v>
+      </c>
+      <c r="C2430">
+        <v>5600</v>
+      </c>
+      <c r="D2430" t="s">
+        <v>2432</v>
+      </c>
+    </row>
+    <row r="2431" spans="1:4">
+      <c r="A2431" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2431">
+        <v>30</v>
+      </c>
+      <c r="C2431">
+        <v>5700</v>
+      </c>
+      <c r="D2431" t="s">
+        <v>2433</v>
+      </c>
+    </row>
+    <row r="2432" spans="1:4">
+      <c r="A2432" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2432">
+        <v>31</v>
+      </c>
+      <c r="C2432">
+        <v>5780</v>
+      </c>
+      <c r="D2432" t="s">
+        <v>2434</v>
+      </c>
+    </row>
+    <row r="2433" spans="1:4">
+      <c r="A2433" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2433">
+        <v>32</v>
+      </c>
+      <c r="C2433">
+        <v>5820</v>
+      </c>
+      <c r="D2433" t="s">
+        <v>2435</v>
+      </c>
+    </row>
+    <row r="2434" spans="1:4">
+      <c r="A2434" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2434">
+        <v>33</v>
+      </c>
+      <c r="C2434">
+        <v>5830</v>
+      </c>
+      <c r="D2434" t="s">
+        <v>2436</v>
+      </c>
+    </row>
+    <row r="2435" spans="1:4">
+      <c r="A2435" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2435">
+        <v>34</v>
+      </c>
+      <c r="C2435">
+        <v>5820</v>
+      </c>
+      <c r="D2435" t="s">
+        <v>2437</v>
+      </c>
+    </row>
+    <row r="2436" spans="1:4">
+      <c r="A2436" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2436">
+        <v>35</v>
+      </c>
+      <c r="C2436">
+        <v>5780</v>
+      </c>
+      <c r="D2436" t="s">
+        <v>2438</v>
+      </c>
+    </row>
+    <row r="2437" spans="1:4">
+      <c r="A2437" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2437">
+        <v>36</v>
+      </c>
+      <c r="C2437">
+        <v>5720</v>
+      </c>
+      <c r="D2437" t="s">
+        <v>2439</v>
+      </c>
+    </row>
+    <row r="2438" spans="1:4">
+      <c r="A2438" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2438">
+        <v>37</v>
+      </c>
+      <c r="C2438">
+        <v>5640</v>
+      </c>
+      <c r="D2438" t="s">
+        <v>2440</v>
+      </c>
+    </row>
+    <row r="2439" spans="1:4">
+      <c r="A2439" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2439">
+        <v>38</v>
+      </c>
+      <c r="C2439">
+        <v>5560</v>
+      </c>
+      <c r="D2439" t="s">
+        <v>2441</v>
+      </c>
+    </row>
+    <row r="2440" spans="1:4">
+      <c r="A2440" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2440">
+        <v>39</v>
+      </c>
+      <c r="C2440">
+        <v>5480</v>
+      </c>
+      <c r="D2440" t="s">
+        <v>2442</v>
+      </c>
+    </row>
+    <row r="2441" spans="1:4">
+      <c r="A2441" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2441">
+        <v>40</v>
+      </c>
+      <c r="C2441">
+        <v>5410</v>
+      </c>
+      <c r="D2441" t="s">
+        <v>2443</v>
+      </c>
+    </row>
+    <row r="2442" spans="1:4">
+      <c r="A2442" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2442">
+        <v>41</v>
+      </c>
+      <c r="C2442">
+        <v>5330</v>
+      </c>
+      <c r="D2442" t="s">
+        <v>2444</v>
+      </c>
+    </row>
+    <row r="2443" spans="1:4">
+      <c r="A2443" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2443">
+        <v>42</v>
+      </c>
+      <c r="C2443">
+        <v>5250</v>
+      </c>
+      <c r="D2443" t="s">
+        <v>2445</v>
+      </c>
+    </row>
+    <row r="2444" spans="1:4">
+      <c r="A2444" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2444">
+        <v>43</v>
+      </c>
+      <c r="C2444">
+        <v>5150</v>
+      </c>
+      <c r="D2444" t="s">
+        <v>2446</v>
+      </c>
+    </row>
+    <row r="2445" spans="1:4">
+      <c r="A2445" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2445">
+        <v>44</v>
+      </c>
+      <c r="C2445">
+        <v>5040</v>
+      </c>
+      <c r="D2445" t="s">
+        <v>2447</v>
+      </c>
+    </row>
+    <row r="2446" spans="1:4">
+      <c r="A2446" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2446">
+        <v>45</v>
+      </c>
+      <c r="C2446">
+        <v>4920</v>
+      </c>
+      <c r="D2446" t="s">
+        <v>2448</v>
+      </c>
+    </row>
+    <row r="2447" spans="1:4">
+      <c r="A2447" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2447">
+        <v>46</v>
+      </c>
+      <c r="C2447">
+        <v>4820</v>
+      </c>
+      <c r="D2447" t="s">
+        <v>2449</v>
+      </c>
+    </row>
+    <row r="2448" spans="1:4">
+      <c r="A2448" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2448">
+        <v>47</v>
+      </c>
+      <c r="C2448">
+        <v>4760</v>
+      </c>
+      <c r="D2448" t="s">
+        <v>2450</v>
+      </c>
+    </row>
+    <row r="2449" spans="1:4">
+      <c r="A2449" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2449">
+        <v>48</v>
+      </c>
+      <c r="C2449">
+        <v>4720</v>
+      </c>
+      <c r="D2449" t="s">
+        <v>2451</v>
+      </c>
+    </row>
+    <row r="2450" spans="1:4">
+      <c r="A2450" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2450">
+        <v>49</v>
+      </c>
+      <c r="C2450">
+        <v>4710</v>
+      </c>
+      <c r="D2450" t="s">
+        <v>2452</v>
+      </c>
+    </row>
+    <row r="2451" spans="1:4">
+      <c r="A2451" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2451">
+        <v>50</v>
+      </c>
+      <c r="C2451">
+        <v>4700</v>
+      </c>
+      <c r="D2451" t="s">
+        <v>2453</v>
+      </c>
+    </row>
+    <row r="2452" spans="1:4">
+      <c r="A2452" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2452">
+        <v>51</v>
+      </c>
+      <c r="C2452">
+        <v>4700</v>
+      </c>
+      <c r="D2452" t="s">
+        <v>2454</v>
+      </c>
+    </row>
+    <row r="2453" spans="1:4">
+      <c r="A2453" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2453">
+        <v>52</v>
+      </c>
+      <c r="C2453">
+        <v>4700</v>
+      </c>
+      <c r="D2453" t="s">
+        <v>2455</v>
+      </c>
+    </row>
+    <row r="2454" spans="1:4">
+      <c r="A2454" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2454">
+        <v>53</v>
+      </c>
+      <c r="C2454">
+        <v>4710</v>
+      </c>
+      <c r="D2454" t="s">
+        <v>2456</v>
+      </c>
+    </row>
+    <row r="2455" spans="1:4">
+      <c r="A2455" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2455">
+        <v>54</v>
+      </c>
+      <c r="C2455">
+        <v>4710</v>
+      </c>
+      <c r="D2455" t="s">
+        <v>2457</v>
+      </c>
+    </row>
+    <row r="2456" spans="1:4">
+      <c r="A2456" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2456">
+        <v>55</v>
+      </c>
+      <c r="C2456">
+        <v>4710</v>
+      </c>
+      <c r="D2456" t="s">
+        <v>2458</v>
+      </c>
+    </row>
+    <row r="2457" spans="1:4">
+      <c r="A2457" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2457">
+        <v>56</v>
+      </c>
+      <c r="C2457">
+        <v>4700</v>
+      </c>
+      <c r="D2457" t="s">
+        <v>2459</v>
+      </c>
+    </row>
+    <row r="2458" spans="1:4">
+      <c r="A2458" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2458">
+        <v>57</v>
+      </c>
+      <c r="C2458">
+        <v>4700</v>
+      </c>
+      <c r="D2458" t="s">
+        <v>2460</v>
+      </c>
+    </row>
+    <row r="2459" spans="1:4">
+      <c r="A2459" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2459">
+        <v>58</v>
+      </c>
+      <c r="C2459">
+        <v>4700</v>
+      </c>
+      <c r="D2459" t="s">
+        <v>2461</v>
+      </c>
+    </row>
+    <row r="2460" spans="1:4">
+      <c r="A2460" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2460">
+        <v>59</v>
+      </c>
+      <c r="C2460">
+        <v>4710</v>
+      </c>
+      <c r="D2460" t="s">
+        <v>2462</v>
+      </c>
+    </row>
+    <row r="2461" spans="1:4">
+      <c r="A2461" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2461">
+        <v>60</v>
+      </c>
+      <c r="C2461">
+        <v>4730</v>
+      </c>
+      <c r="D2461" t="s">
+        <v>2463</v>
+      </c>
+    </row>
+    <row r="2462" spans="1:4">
+      <c r="A2462" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2462">
+        <v>61</v>
+      </c>
+      <c r="C2462">
+        <v>4760</v>
+      </c>
+      <c r="D2462" t="s">
+        <v>2464</v>
+      </c>
+    </row>
+    <row r="2463" spans="1:4">
+      <c r="A2463" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2463">
+        <v>62</v>
+      </c>
+      <c r="C2463">
+        <v>4800</v>
+      </c>
+      <c r="D2463" t="s">
+        <v>2465</v>
+      </c>
+    </row>
+    <row r="2464" spans="1:4">
+      <c r="A2464" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2464">
+        <v>63</v>
+      </c>
+      <c r="C2464">
+        <v>4850</v>
+      </c>
+      <c r="D2464" t="s">
+        <v>2466</v>
+      </c>
+    </row>
+    <row r="2465" spans="1:4">
+      <c r="A2465" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2465">
+        <v>64</v>
+      </c>
+      <c r="C2465">
+        <v>4910</v>
+      </c>
+      <c r="D2465" t="s">
+        <v>2467</v>
+      </c>
+    </row>
+    <row r="2466" spans="1:4">
+      <c r="A2466" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2466">
+        <v>65</v>
+      </c>
+      <c r="C2466">
+        <v>4970</v>
+      </c>
+      <c r="D2466" t="s">
+        <v>2468</v>
+      </c>
+    </row>
+    <row r="2467" spans="1:4">
+      <c r="A2467" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2467">
+        <v>66</v>
+      </c>
+      <c r="C2467">
+        <v>5040</v>
+      </c>
+      <c r="D2467" t="s">
+        <v>2469</v>
+      </c>
+    </row>
+    <row r="2468" spans="1:4">
+      <c r="A2468" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2468">
+        <v>67</v>
+      </c>
+      <c r="C2468">
+        <v>5120</v>
+      </c>
+      <c r="D2468" t="s">
+        <v>2470</v>
+      </c>
+    </row>
+    <row r="2469" spans="1:4">
+      <c r="A2469" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2469">
+        <v>68</v>
+      </c>
+      <c r="C2469">
+        <v>5190</v>
+      </c>
+      <c r="D2469" t="s">
+        <v>2471</v>
+      </c>
+    </row>
+    <row r="2470" spans="1:4">
+      <c r="A2470" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2470">
+        <v>69</v>
+      </c>
+      <c r="C2470">
+        <v>5280</v>
+      </c>
+      <c r="D2470" t="s">
+        <v>2472</v>
+      </c>
+    </row>
+    <row r="2471" spans="1:4">
+      <c r="A2471" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2471">
+        <v>70</v>
+      </c>
+      <c r="C2471">
+        <v>5370</v>
+      </c>
+      <c r="D2471" t="s">
+        <v>2473</v>
+      </c>
+    </row>
+    <row r="2472" spans="1:4">
+      <c r="A2472" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2472">
+        <v>71</v>
+      </c>
+      <c r="C2472">
+        <v>5470</v>
+      </c>
+      <c r="D2472" t="s">
+        <v>2474</v>
+      </c>
+    </row>
+    <row r="2473" spans="1:4">
+      <c r="A2473" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2473">
+        <v>72</v>
+      </c>
+      <c r="C2473">
+        <v>5570</v>
+      </c>
+      <c r="D2473" t="s">
+        <v>2475</v>
+      </c>
+    </row>
+    <row r="2474" spans="1:4">
+      <c r="A2474" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2474">
+        <v>73</v>
+      </c>
+      <c r="C2474">
+        <v>5690</v>
+      </c>
+      <c r="D2474" t="s">
+        <v>2476</v>
+      </c>
+    </row>
+    <row r="2475" spans="1:4">
+      <c r="A2475" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2475">
+        <v>74</v>
+      </c>
+      <c r="C2475">
+        <v>5800</v>
+      </c>
+      <c r="D2475" t="s">
+        <v>2477</v>
+      </c>
+    </row>
+    <row r="2476" spans="1:4">
+      <c r="A2476" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2476">
+        <v>75</v>
+      </c>
+      <c r="C2476">
+        <v>5920</v>
+      </c>
+      <c r="D2476" t="s">
+        <v>2478</v>
+      </c>
+    </row>
+    <row r="2477" spans="1:4">
+      <c r="A2477" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2477">
+        <v>76</v>
+      </c>
+      <c r="C2477">
+        <v>6030</v>
+      </c>
+      <c r="D2477" t="s">
+        <v>2479</v>
+      </c>
+    </row>
+    <row r="2478" spans="1:4">
+      <c r="A2478" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2478">
+        <v>77</v>
+      </c>
+      <c r="C2478">
+        <v>6140</v>
+      </c>
+      <c r="D2478" t="s">
+        <v>2480</v>
+      </c>
+    </row>
+    <row r="2479" spans="1:4">
+      <c r="A2479" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2479">
+        <v>78</v>
+      </c>
+      <c r="C2479">
+        <v>6240</v>
+      </c>
+      <c r="D2479" t="s">
+        <v>2481</v>
+      </c>
+    </row>
+    <row r="2480" spans="1:4">
+      <c r="A2480" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2480">
+        <v>79</v>
+      </c>
+      <c r="C2480">
+        <v>6320</v>
+      </c>
+      <c r="D2480" t="s">
+        <v>2482</v>
+      </c>
+    </row>
+    <row r="2481" spans="1:4">
+      <c r="A2481" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2481">
+        <v>80</v>
+      </c>
+      <c r="C2481">
+        <v>6380</v>
+      </c>
+      <c r="D2481" t="s">
+        <v>2483</v>
+      </c>
+    </row>
+    <row r="2482" spans="1:4">
+      <c r="A2482" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2482">
+        <v>81</v>
+      </c>
+      <c r="C2482">
+        <v>6430</v>
+      </c>
+      <c r="D2482" t="s">
+        <v>2484</v>
+      </c>
+    </row>
+    <row r="2483" spans="1:4">
+      <c r="A2483" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2483">
+        <v>82</v>
+      </c>
+      <c r="C2483">
+        <v>6490</v>
+      </c>
+      <c r="D2483" t="s">
+        <v>2485</v>
+      </c>
+    </row>
+    <row r="2484" spans="1:4">
+      <c r="A2484" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2484">
+        <v>83</v>
+      </c>
+      <c r="C2484">
+        <v>6560</v>
+      </c>
+      <c r="D2484" t="s">
+        <v>2486</v>
+      </c>
+    </row>
+    <row r="2485" spans="1:4">
+      <c r="A2485" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2485">
+        <v>84</v>
+      </c>
+      <c r="C2485">
+        <v>6640</v>
+      </c>
+      <c r="D2485" t="s">
+        <v>2487</v>
+      </c>
+    </row>
+    <row r="2486" spans="1:4">
+      <c r="A2486" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2486">
+        <v>85</v>
+      </c>
+      <c r="C2486">
+        <v>6720</v>
+      </c>
+      <c r="D2486" t="s">
+        <v>2488</v>
+      </c>
+    </row>
+    <row r="2487" spans="1:4">
+      <c r="A2487" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2487">
+        <v>86</v>
+      </c>
+      <c r="C2487">
+        <v>6750</v>
+      </c>
+      <c r="D2487" t="s">
+        <v>2489</v>
+      </c>
+    </row>
+    <row r="2488" spans="1:4">
+      <c r="A2488" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2488">
+        <v>87</v>
+      </c>
+      <c r="C2488">
+        <v>6730</v>
+      </c>
+      <c r="D2488" t="s">
+        <v>2490</v>
+      </c>
+    </row>
+    <row r="2489" spans="1:4">
+      <c r="A2489" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2489">
+        <v>88</v>
+      </c>
+      <c r="C2489">
+        <v>6650</v>
+      </c>
+      <c r="D2489" t="s">
+        <v>2491</v>
+      </c>
+    </row>
+    <row r="2490" spans="1:4">
+      <c r="A2490" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2490">
+        <v>89</v>
+      </c>
+      <c r="C2490">
+        <v>6520</v>
+      </c>
+      <c r="D2490" t="s">
+        <v>2492</v>
+      </c>
+    </row>
+    <row r="2491" spans="1:4">
+      <c r="A2491" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2491">
+        <v>90</v>
+      </c>
+      <c r="C2491">
+        <v>6370</v>
+      </c>
+      <c r="D2491" t="s">
+        <v>2493</v>
+      </c>
+    </row>
+    <row r="2492" spans="1:4">
+      <c r="A2492" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2492">
+        <v>91</v>
+      </c>
+      <c r="C2492">
+        <v>6220</v>
+      </c>
+      <c r="D2492" t="s">
+        <v>2494</v>
+      </c>
+    </row>
+    <row r="2493" spans="1:4">
+      <c r="A2493" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2493">
+        <v>92</v>
+      </c>
+      <c r="C2493">
+        <v>6070</v>
+      </c>
+      <c r="D2493" t="s">
+        <v>2495</v>
+      </c>
+    </row>
+    <row r="2494" spans="1:4">
+      <c r="A2494" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2494">
+        <v>93</v>
+      </c>
+      <c r="C2494">
+        <v>5910</v>
+      </c>
+      <c r="D2494" t="s">
+        <v>2496</v>
+      </c>
+    </row>
+    <row r="2495" spans="1:4">
+      <c r="A2495" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2495">
+        <v>94</v>
+      </c>
+      <c r="C2495">
+        <v>5760</v>
+      </c>
+      <c r="D2495" t="s">
+        <v>2497</v>
+      </c>
+    </row>
+    <row r="2496" spans="1:4">
+      <c r="A2496" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2496">
+        <v>95</v>
+      </c>
+      <c r="C2496">
+        <v>5640</v>
+      </c>
+      <c r="D2496" t="s">
+        <v>2498</v>
+      </c>
+    </row>
+    <row r="2497" spans="1:4">
+      <c r="A2497" s="2">
+        <v>46168</v>
+      </c>
+      <c r="B2497">
+        <v>96</v>
+      </c>
+      <c r="C2497">
+        <v>5520</v>
+      </c>
+      <c r="D2497" t="s">
+        <v>2499</v>
       </c>
     </row>
   </sheetData>

--- a/Market Fundamentals/Transelectrica_data/Cons_Prod_final/Weekly_Consumption_2026.xlsx
+++ b/Market Fundamentals/Transelectrica_data/Cons_Prod_final/Weekly_Consumption_2026.xlsx
@@ -42940,7 +42940,7 @@
         <v>1</v>
       </c>
       <c r="C2402">
-        <v>5280</v>
+        <v>5220</v>
       </c>
       <c r="D2402" t="s">
         <v>2404</v>
@@ -42954,7 +42954,7 @@
         <v>2</v>
       </c>
       <c r="C2403">
-        <v>5220</v>
+        <v>5160</v>
       </c>
       <c r="D2403" t="s">
         <v>2405</v>
@@ -42968,7 +42968,7 @@
         <v>3</v>
       </c>
       <c r="C2404">
-        <v>5150</v>
+        <v>5100</v>
       </c>
       <c r="D2404" t="s">
         <v>2406</v>
@@ -42982,7 +42982,7 @@
         <v>4</v>
       </c>
       <c r="C2405">
-        <v>5120</v>
+        <v>5040</v>
       </c>
       <c r="D2405" t="s">
         <v>2407</v>
@@ -42996,7 +42996,7 @@
         <v>5</v>
       </c>
       <c r="C2406">
-        <v>5100</v>
+        <v>4970</v>
       </c>
       <c r="D2406" t="s">
         <v>2408</v>
@@ -43010,7 +43010,7 @@
         <v>6</v>
       </c>
       <c r="C2407">
-        <v>5060</v>
+        <v>4930</v>
       </c>
       <c r="D2407" t="s">
         <v>2409</v>
@@ -43024,7 +43024,7 @@
         <v>7</v>
       </c>
       <c r="C2408">
-        <v>5030</v>
+        <v>4910</v>
       </c>
       <c r="D2408" t="s">
         <v>2410</v>
@@ -43038,7 +43038,7 @@
         <v>8</v>
       </c>
       <c r="C2409">
-        <v>5000</v>
+        <v>4890</v>
       </c>
       <c r="D2409" t="s">
         <v>2411</v>
@@ -43052,7 +43052,7 @@
         <v>9</v>
       </c>
       <c r="C2410">
-        <v>4970</v>
+        <v>4870</v>
       </c>
       <c r="D2410" t="s">
         <v>2412</v>
@@ -43066,7 +43066,7 @@
         <v>10</v>
       </c>
       <c r="C2411">
-        <v>4950</v>
+        <v>4860</v>
       </c>
       <c r="D2411" t="s">
         <v>2413</v>
@@ -43080,7 +43080,7 @@
         <v>11</v>
       </c>
       <c r="C2412">
-        <v>4950</v>
+        <v>4860</v>
       </c>
       <c r="D2412" t="s">
         <v>2414</v>
@@ -43094,7 +43094,7 @@
         <v>12</v>
       </c>
       <c r="C2413">
-        <v>4950</v>
+        <v>4850</v>
       </c>
       <c r="D2413" t="s">
         <v>2415</v>
@@ -43108,7 +43108,7 @@
         <v>13</v>
       </c>
       <c r="C2414">
-        <v>4960</v>
+        <v>4830</v>
       </c>
       <c r="D2414" t="s">
         <v>2416</v>
@@ -43122,7 +43122,7 @@
         <v>14</v>
       </c>
       <c r="C2415">
-        <v>4970</v>
+        <v>4820</v>
       </c>
       <c r="D2415" t="s">
         <v>2417</v>
@@ -43136,7 +43136,7 @@
         <v>15</v>
       </c>
       <c r="C2416">
-        <v>4980</v>
+        <v>4820</v>
       </c>
       <c r="D2416" t="s">
         <v>2418</v>
@@ -43150,7 +43150,7 @@
         <v>16</v>
       </c>
       <c r="C2417">
-        <v>4990</v>
+        <v>4820</v>
       </c>
       <c r="D2417" t="s">
         <v>2419</v>
@@ -43164,7 +43164,7 @@
         <v>17</v>
       </c>
       <c r="C2418">
-        <v>4990</v>
+        <v>4830</v>
       </c>
       <c r="D2418" t="s">
         <v>2420</v>
@@ -43178,7 +43178,7 @@
         <v>18</v>
       </c>
       <c r="C2419">
-        <v>4990</v>
+        <v>4830</v>
       </c>
       <c r="D2419" t="s">
         <v>2421</v>
@@ -43192,7 +43192,7 @@
         <v>19</v>
       </c>
       <c r="C2420">
-        <v>5000</v>
+        <v>4830</v>
       </c>
       <c r="D2420" t="s">
         <v>2422</v>
@@ -43206,7 +43206,7 @@
         <v>20</v>
       </c>
       <c r="C2421">
-        <v>5010</v>
+        <v>4830</v>
       </c>
       <c r="D2421" t="s">
         <v>2423</v>
@@ -43220,7 +43220,7 @@
         <v>21</v>
       </c>
       <c r="C2422">
-        <v>5040</v>
+        <v>4830</v>
       </c>
       <c r="D2422" t="s">
         <v>2424</v>
@@ -43234,7 +43234,7 @@
         <v>22</v>
       </c>
       <c r="C2423">
-        <v>5080</v>
+        <v>4850</v>
       </c>
       <c r="D2423" t="s">
         <v>2425</v>
@@ -43248,7 +43248,7 @@
         <v>23</v>
       </c>
       <c r="C2424">
-        <v>5130</v>
+        <v>4890</v>
       </c>
       <c r="D2424" t="s">
         <v>2426</v>
@@ -43262,7 +43262,7 @@
         <v>24</v>
       </c>
       <c r="C2425">
-        <v>5190</v>
+        <v>4950</v>
       </c>
       <c r="D2425" t="s">
         <v>2427</v>
@@ -43276,7 +43276,7 @@
         <v>25</v>
       </c>
       <c r="C2426">
-        <v>5260</v>
+        <v>5000</v>
       </c>
       <c r="D2426" t="s">
         <v>2428</v>
@@ -43290,7 +43290,7 @@
         <v>26</v>
       </c>
       <c r="C2427">
-        <v>5340</v>
+        <v>5070</v>
       </c>
       <c r="D2427" t="s">
         <v>2429</v>
@@ -43304,7 +43304,7 @@
         <v>27</v>
       </c>
       <c r="C2428">
-        <v>5400</v>
+        <v>5120</v>
       </c>
       <c r="D2428" t="s">
         <v>2430</v>
@@ -43318,7 +43318,7 @@
         <v>28</v>
       </c>
       <c r="C2429">
-        <v>5460</v>
+        <v>5210</v>
       </c>
       <c r="D2429" t="s">
         <v>2431</v>
@@ -43332,7 +43332,7 @@
         <v>29</v>
       </c>
       <c r="C2430">
-        <v>5510</v>
+        <v>5340</v>
       </c>
       <c r="D2430" t="s">
         <v>2432</v>
@@ -43346,7 +43346,7 @@
         <v>30</v>
       </c>
       <c r="C2431">
-        <v>5540</v>
+        <v>5380</v>
       </c>
       <c r="D2431" t="s">
         <v>2433</v>
@@ -43360,7 +43360,7 @@
         <v>31</v>
       </c>
       <c r="C2432">
-        <v>5550</v>
+        <v>5400</v>
       </c>
       <c r="D2432" t="s">
         <v>2434</v>
@@ -43374,7 +43374,7 @@
         <v>32</v>
       </c>
       <c r="C2433">
-        <v>5570</v>
+        <v>5400</v>
       </c>
       <c r="D2433" t="s">
         <v>2435</v>
@@ -43388,7 +43388,7 @@
         <v>33</v>
       </c>
       <c r="C2434">
-        <v>5600</v>
+        <v>5350</v>
       </c>
       <c r="D2434" t="s">
         <v>2436</v>
@@ -43402,7 +43402,7 @@
         <v>34</v>
       </c>
       <c r="C2435">
-        <v>5470</v>
+        <v>5280</v>
       </c>
       <c r="D2435" t="s">
         <v>2437</v>
@@ -43416,7 +43416,7 @@
         <v>35</v>
       </c>
       <c r="C2436">
-        <v>5410</v>
+        <v>5210</v>
       </c>
       <c r="D2436" t="s">
         <v>2438</v>
@@ -43430,7 +43430,7 @@
         <v>36</v>
       </c>
       <c r="C2437">
-        <v>5330</v>
+        <v>5130</v>
       </c>
       <c r="D2437" t="s">
         <v>2439</v>
@@ -43444,7 +43444,7 @@
         <v>37</v>
       </c>
       <c r="C2438">
-        <v>5230</v>
+        <v>5010</v>
       </c>
       <c r="D2438" t="s">
         <v>2440</v>
@@ -43458,7 +43458,7 @@
         <v>38</v>
       </c>
       <c r="C2439">
-        <v>5120</v>
+        <v>4900</v>
       </c>
       <c r="D2439" t="s">
         <v>2441</v>
@@ -43472,7 +43472,7 @@
         <v>39</v>
       </c>
       <c r="C2440">
-        <v>5000</v>
+        <v>4780</v>
       </c>
       <c r="D2440" t="s">
         <v>2442</v>
@@ -43486,7 +43486,7 @@
         <v>40</v>
       </c>
       <c r="C2441">
-        <v>4880</v>
+        <v>4680</v>
       </c>
       <c r="D2441" t="s">
         <v>2443</v>
@@ -43500,7 +43500,7 @@
         <v>41</v>
       </c>
       <c r="C2442">
-        <v>4760</v>
+        <v>4590</v>
       </c>
       <c r="D2442" t="s">
         <v>2444</v>
@@ -43514,7 +43514,7 @@
         <v>42</v>
       </c>
       <c r="C2443">
-        <v>4640</v>
+        <v>4490</v>
       </c>
       <c r="D2443" t="s">
         <v>2445</v>
@@ -43528,7 +43528,7 @@
         <v>43</v>
       </c>
       <c r="C2444">
-        <v>4520</v>
+        <v>4410</v>
       </c>
       <c r="D2444" t="s">
         <v>2446</v>
@@ -43542,7 +43542,7 @@
         <v>44</v>
       </c>
       <c r="C2445">
-        <v>4420</v>
+        <v>4330</v>
       </c>
       <c r="D2445" t="s">
         <v>2447</v>
@@ -43556,7 +43556,7 @@
         <v>45</v>
       </c>
       <c r="C2446">
-        <v>4340</v>
+        <v>4240</v>
       </c>
       <c r="D2446" t="s">
         <v>2448</v>
@@ -43570,7 +43570,7 @@
         <v>46</v>
       </c>
       <c r="C2447">
-        <v>4270</v>
+        <v>4190</v>
       </c>
       <c r="D2447" t="s">
         <v>2449</v>
@@ -43584,7 +43584,7 @@
         <v>47</v>
       </c>
       <c r="C2448">
-        <v>4220</v>
+        <v>4190</v>
       </c>
       <c r="D2448" t="s">
         <v>2450</v>
@@ -43598,7 +43598,7 @@
         <v>48</v>
       </c>
       <c r="C2449">
-        <v>4180</v>
+        <v>4200</v>
       </c>
       <c r="D2449" t="s">
         <v>2451</v>
@@ -43612,7 +43612,7 @@
         <v>49</v>
       </c>
       <c r="C2450">
-        <v>4160</v>
+        <v>4200</v>
       </c>
       <c r="D2450" t="s">
         <v>2452</v>
@@ -43626,7 +43626,7 @@
         <v>50</v>
       </c>
       <c r="C2451">
-        <v>4140</v>
+        <v>4200</v>
       </c>
       <c r="D2451" t="s">
         <v>2453</v>
@@ -43640,7 +43640,7 @@
         <v>51</v>
       </c>
       <c r="C2452">
-        <v>4130</v>
+        <v>4200</v>
       </c>
       <c r="D2452" t="s">
         <v>2454</v>
@@ -43654,7 +43654,7 @@
         <v>52</v>
       </c>
       <c r="C2453">
-        <v>4130</v>
+        <v>4210</v>
       </c>
       <c r="D2453" t="s">
         <v>2455</v>
@@ -43668,7 +43668,7 @@
         <v>53</v>
       </c>
       <c r="C2454">
-        <v>4120</v>
+        <v>4250</v>
       </c>
       <c r="D2454" t="s">
         <v>2456</v>
@@ -43682,7 +43682,7 @@
         <v>54</v>
       </c>
       <c r="C2455">
-        <v>4130</v>
+        <v>4260</v>
       </c>
       <c r="D2455" t="s">
         <v>2457</v>
@@ -43696,7 +43696,7 @@
         <v>55</v>
       </c>
       <c r="C2456">
-        <v>4130</v>
+        <v>4270</v>
       </c>
       <c r="D2456" t="s">
         <v>2458</v>
@@ -43710,7 +43710,7 @@
         <v>56</v>
       </c>
       <c r="C2457">
-        <v>4150</v>
+        <v>4270</v>
       </c>
       <c r="D2457" t="s">
         <v>2459</v>
@@ -43724,7 +43724,7 @@
         <v>57</v>
       </c>
       <c r="C2458">
-        <v>4170</v>
+        <v>4270</v>
       </c>
       <c r="D2458" t="s">
         <v>2460</v>
@@ -43738,7 +43738,7 @@
         <v>58</v>
       </c>
       <c r="C2459">
-        <v>4190</v>
+        <v>4270</v>
       </c>
       <c r="D2459" t="s">
         <v>2461</v>
@@ -43752,7 +43752,7 @@
         <v>59</v>
       </c>
       <c r="C2460">
-        <v>4220</v>
+        <v>4280</v>
       </c>
       <c r="D2460" t="s">
         <v>2462</v>
@@ -43766,7 +43766,7 @@
         <v>60</v>
       </c>
       <c r="C2461">
-        <v>4260</v>
+        <v>4300</v>
       </c>
       <c r="D2461" t="s">
         <v>2463</v>
@@ -43780,7 +43780,7 @@
         <v>61</v>
       </c>
       <c r="C2462">
-        <v>4300</v>
+        <v>4350</v>
       </c>
       <c r="D2462" t="s">
         <v>2464</v>
@@ -43794,7 +43794,7 @@
         <v>62</v>
       </c>
       <c r="C2463">
-        <v>4350</v>
+        <v>4400</v>
       </c>
       <c r="D2463" t="s">
         <v>2465</v>
@@ -43808,7 +43808,7 @@
         <v>63</v>
       </c>
       <c r="C2464">
-        <v>4410</v>
+        <v>4430</v>
       </c>
       <c r="D2464" t="s">
         <v>2466</v>
@@ -43836,7 +43836,7 @@
         <v>65</v>
       </c>
       <c r="C2466">
-        <v>4530</v>
+        <v>4520</v>
       </c>
       <c r="D2466" t="s">
         <v>2468</v>
@@ -43850,7 +43850,7 @@
         <v>66</v>
       </c>
       <c r="C2467">
-        <v>4610</v>
+        <v>4600</v>
       </c>
       <c r="D2467" t="s">
         <v>2469</v>
@@ -43864,7 +43864,7 @@
         <v>67</v>
       </c>
       <c r="C2468">
-        <v>4690</v>
+        <v>4680</v>
       </c>
       <c r="D2468" t="s">
         <v>2470</v>
@@ -43906,7 +43906,7 @@
         <v>70</v>
       </c>
       <c r="C2471">
-        <v>4980</v>
+        <v>5000</v>
       </c>
       <c r="D2471" t="s">
         <v>2473</v>
@@ -43920,7 +43920,7 @@
         <v>71</v>
       </c>
       <c r="C2472">
-        <v>5090</v>
+        <v>5120</v>
       </c>
       <c r="D2472" t="s">
         <v>2474</v>
@@ -43934,7 +43934,7 @@
         <v>72</v>
       </c>
       <c r="C2473">
-        <v>5200</v>
+        <v>5250</v>
       </c>
       <c r="D2473" t="s">
         <v>2475</v>
@@ -43948,7 +43948,7 @@
         <v>73</v>
       </c>
       <c r="C2474">
-        <v>5320</v>
+        <v>5430</v>
       </c>
       <c r="D2474" t="s">
         <v>2476</v>
@@ -43962,7 +43962,7 @@
         <v>74</v>
       </c>
       <c r="C2475">
-        <v>5460</v>
+        <v>5570</v>
       </c>
       <c r="D2475" t="s">
         <v>2477</v>
@@ -43976,7 +43976,7 @@
         <v>75</v>
       </c>
       <c r="C2476">
-        <v>5610</v>
+        <v>5720</v>
       </c>
       <c r="D2476" t="s">
         <v>2478</v>
@@ -43990,7 +43990,7 @@
         <v>76</v>
       </c>
       <c r="C2477">
-        <v>5770</v>
+        <v>5880</v>
       </c>
       <c r="D2477" t="s">
         <v>2479</v>
@@ -44004,7 +44004,7 @@
         <v>77</v>
       </c>
       <c r="C2478">
-        <v>5940</v>
+        <v>6010</v>
       </c>
       <c r="D2478" t="s">
         <v>2480</v>
@@ -44018,7 +44018,7 @@
         <v>78</v>
       </c>
       <c r="C2479">
-        <v>6090</v>
+        <v>6140</v>
       </c>
       <c r="D2479" t="s">
         <v>2481</v>
@@ -44046,7 +44046,7 @@
         <v>80</v>
       </c>
       <c r="C2481">
-        <v>6340</v>
+        <v>6300</v>
       </c>
       <c r="D2481" t="s">
         <v>2483</v>
@@ -44060,7 +44060,7 @@
         <v>81</v>
       </c>
       <c r="C2482">
-        <v>6440</v>
+        <v>6350</v>
       </c>
       <c r="D2482" t="s">
         <v>2484</v>
@@ -44074,7 +44074,7 @@
         <v>82</v>
       </c>
       <c r="C2483">
-        <v>6550</v>
+        <v>6430</v>
       </c>
       <c r="D2483" t="s">
         <v>2485</v>
@@ -44088,7 +44088,7 @@
         <v>83</v>
       </c>
       <c r="C2484">
-        <v>6650</v>
+        <v>6500</v>
       </c>
       <c r="D2484" t="s">
         <v>2486</v>
@@ -44102,7 +44102,7 @@
         <v>84</v>
       </c>
       <c r="C2485">
-        <v>6760</v>
+        <v>6600</v>
       </c>
       <c r="D2485" t="s">
         <v>2487</v>
@@ -44116,7 +44116,7 @@
         <v>85</v>
       </c>
       <c r="C2486">
-        <v>6800</v>
+        <v>6700</v>
       </c>
       <c r="D2486" t="s">
         <v>2488</v>
@@ -44130,7 +44130,7 @@
         <v>86</v>
       </c>
       <c r="C2487">
-        <v>6800</v>
+        <v>6700</v>
       </c>
       <c r="D2487" t="s">
         <v>2489</v>
@@ -44144,7 +44144,7 @@
         <v>87</v>
       </c>
       <c r="C2488">
-        <v>6780</v>
+        <v>6700</v>
       </c>
       <c r="D2488" t="s">
         <v>2490</v>
@@ -44158,7 +44158,7 @@
         <v>88</v>
       </c>
       <c r="C2489">
-        <v>6690</v>
+        <v>6620</v>
       </c>
       <c r="D2489" t="s">
         <v>2491</v>
@@ -44172,7 +44172,7 @@
         <v>89</v>
       </c>
       <c r="C2490">
-        <v>6530</v>
+        <v>6460</v>
       </c>
       <c r="D2490" t="s">
         <v>2492</v>
@@ -44186,7 +44186,7 @@
         <v>90</v>
       </c>
       <c r="C2491">
-        <v>6410</v>
+        <v>6330</v>
       </c>
       <c r="D2491" t="s">
         <v>2493</v>
@@ -44200,7 +44200,7 @@
         <v>91</v>
       </c>
       <c r="C2492">
-        <v>6270</v>
+        <v>6190</v>
       </c>
       <c r="D2492" t="s">
         <v>2494</v>
@@ -44214,7 +44214,7 @@
         <v>92</v>
       </c>
       <c r="C2493">
-        <v>6110</v>
+        <v>6020</v>
       </c>
       <c r="D2493" t="s">
         <v>2495</v>
@@ -44228,7 +44228,7 @@
         <v>93</v>
       </c>
       <c r="C2494">
-        <v>5890</v>
+        <v>5840</v>
       </c>
       <c r="D2494" t="s">
         <v>2496</v>
@@ -44242,7 +44242,7 @@
         <v>94</v>
       </c>
       <c r="C2495">
-        <v>5710</v>
+        <v>5700</v>
       </c>
       <c r="D2495" t="s">
         <v>2497</v>
@@ -44256,7 +44256,7 @@
         <v>95</v>
       </c>
       <c r="C2496">
-        <v>5630</v>
+        <v>5590</v>
       </c>
       <c r="D2496" t="s">
         <v>2498</v>
@@ -44270,7 +44270,7 @@
         <v>96</v>
       </c>
       <c r="C2497">
-        <v>5520</v>
+        <v>5480</v>
       </c>
       <c r="D2497" t="s">
         <v>2499</v>
@@ -44284,7 +44284,7 @@
         <v>1</v>
       </c>
       <c r="C2498">
-        <v>5260</v>
+        <v>5310</v>
       </c>
       <c r="D2498" t="s">
         <v>2500</v>
@@ -44298,7 +44298,7 @@
         <v>2</v>
       </c>
       <c r="C2499">
-        <v>5230</v>
+        <v>5280</v>
       </c>
       <c r="D2499" t="s">
         <v>2501</v>
@@ -44312,7 +44312,7 @@
         <v>3</v>
       </c>
       <c r="C2500">
-        <v>5150</v>
+        <v>5200</v>
       </c>
       <c r="D2500" t="s">
         <v>2502</v>
@@ -44326,7 +44326,7 @@
         <v>4</v>
       </c>
       <c r="C2501">
-        <v>5070</v>
+        <v>5120</v>
       </c>
       <c r="D2501" t="s">
         <v>2503</v>
@@ -44340,7 +44340,7 @@
         <v>5</v>
       </c>
       <c r="C2502">
-        <v>5020</v>
+        <v>5070</v>
       </c>
       <c r="D2502" t="s">
         <v>2504</v>
@@ -44354,7 +44354,7 @@
         <v>6</v>
       </c>
       <c r="C2503">
-        <v>4980</v>
+        <v>5020</v>
       </c>
       <c r="D2503" t="s">
         <v>2505</v>
@@ -44368,7 +44368,7 @@
         <v>7</v>
       </c>
       <c r="C2504">
-        <v>4950</v>
+        <v>4960</v>
       </c>
       <c r="D2504" t="s">
         <v>2506</v>
@@ -44382,7 +44382,7 @@
         <v>8</v>
       </c>
       <c r="C2505">
-        <v>4920</v>
+        <v>4910</v>
       </c>
       <c r="D2505" t="s">
         <v>2507</v>
@@ -44396,7 +44396,7 @@
         <v>9</v>
       </c>
       <c r="C2506">
-        <v>4890</v>
+        <v>4870</v>
       </c>
       <c r="D2506" t="s">
         <v>2508</v>
@@ -44410,7 +44410,7 @@
         <v>10</v>
       </c>
       <c r="C2507">
-        <v>4870</v>
+        <v>4840</v>
       </c>
       <c r="D2507" t="s">
         <v>2509</v>
@@ -44424,7 +44424,7 @@
         <v>11</v>
       </c>
       <c r="C2508">
-        <v>4870</v>
+        <v>4820</v>
       </c>
       <c r="D2508" t="s">
         <v>2510</v>
@@ -44438,7 +44438,7 @@
         <v>12</v>
       </c>
       <c r="C2509">
-        <v>4870</v>
+        <v>4820</v>
       </c>
       <c r="D2509" t="s">
         <v>2511</v>
@@ -44452,7 +44452,7 @@
         <v>13</v>
       </c>
       <c r="C2510">
-        <v>4880</v>
+        <v>4820</v>
       </c>
       <c r="D2510" t="s">
         <v>2512</v>
@@ -44466,7 +44466,7 @@
         <v>14</v>
       </c>
       <c r="C2511">
-        <v>4890</v>
+        <v>4820</v>
       </c>
       <c r="D2511" t="s">
         <v>2513</v>
@@ -44480,7 +44480,7 @@
         <v>15</v>
       </c>
       <c r="C2512">
-        <v>4900</v>
+        <v>4820</v>
       </c>
       <c r="D2512" t="s">
         <v>2514</v>
@@ -44494,7 +44494,7 @@
         <v>16</v>
       </c>
       <c r="C2513">
-        <v>4910</v>
+        <v>4810</v>
       </c>
       <c r="D2513" t="s">
         <v>2515</v>
@@ -44508,7 +44508,7 @@
         <v>17</v>
       </c>
       <c r="C2514">
-        <v>4910</v>
+        <v>4810</v>
       </c>
       <c r="D2514" t="s">
         <v>2516</v>
@@ -44522,7 +44522,7 @@
         <v>18</v>
       </c>
       <c r="C2515">
-        <v>4910</v>
+        <v>4800</v>
       </c>
       <c r="D2515" t="s">
         <v>2517</v>
@@ -44536,7 +44536,7 @@
         <v>19</v>
       </c>
       <c r="C2516">
-        <v>4920</v>
+        <v>4800</v>
       </c>
       <c r="D2516" t="s">
         <v>2518</v>
@@ -44550,7 +44550,7 @@
         <v>20</v>
       </c>
       <c r="C2517">
-        <v>4930</v>
+        <v>4810</v>
       </c>
       <c r="D2517" t="s">
         <v>2519</v>
@@ -44564,7 +44564,7 @@
         <v>21</v>
       </c>
       <c r="C2518">
-        <v>4960</v>
+        <v>4840</v>
       </c>
       <c r="D2518" t="s">
         <v>2520</v>
@@ -44578,7 +44578,7 @@
         <v>22</v>
       </c>
       <c r="C2519">
-        <v>5000</v>
+        <v>4890</v>
       </c>
       <c r="D2519" t="s">
         <v>2521</v>
@@ -44592,7 +44592,7 @@
         <v>23</v>
       </c>
       <c r="C2520">
-        <v>5050</v>
+        <v>4950</v>
       </c>
       <c r="D2520" t="s">
         <v>2522</v>
@@ -44606,7 +44606,7 @@
         <v>24</v>
       </c>
       <c r="C2521">
-        <v>5110</v>
+        <v>5020</v>
       </c>
       <c r="D2521" t="s">
         <v>2523</v>
@@ -44620,7 +44620,7 @@
         <v>25</v>
       </c>
       <c r="C2522">
-        <v>5180</v>
+        <v>5100</v>
       </c>
       <c r="D2522" t="s">
         <v>2524</v>
@@ -44634,7 +44634,7 @@
         <v>26</v>
       </c>
       <c r="C2523">
-        <v>5260</v>
+        <v>5180</v>
       </c>
       <c r="D2523" t="s">
         <v>2525</v>
@@ -44648,7 +44648,7 @@
         <v>27</v>
       </c>
       <c r="C2524">
-        <v>5320</v>
+        <v>5250</v>
       </c>
       <c r="D2524" t="s">
         <v>2526</v>
@@ -44662,7 +44662,7 @@
         <v>28</v>
       </c>
       <c r="C2525">
-        <v>5380</v>
+        <v>5310</v>
       </c>
       <c r="D2525" t="s">
         <v>2527</v>
@@ -44676,7 +44676,7 @@
         <v>29</v>
       </c>
       <c r="C2526">
-        <v>5430</v>
+        <v>5350</v>
       </c>
       <c r="D2526" t="s">
         <v>2528</v>
@@ -44690,7 +44690,7 @@
         <v>30</v>
       </c>
       <c r="C2527">
-        <v>5460</v>
+        <v>5370</v>
       </c>
       <c r="D2527" t="s">
         <v>2529</v>
@@ -44704,7 +44704,7 @@
         <v>31</v>
       </c>
       <c r="C2528">
-        <v>5470</v>
+        <v>5400</v>
       </c>
       <c r="D2528" t="s">
         <v>2530</v>
@@ -44718,7 +44718,7 @@
         <v>32</v>
       </c>
       <c r="C2529">
-        <v>5490</v>
+        <v>5400</v>
       </c>
       <c r="D2529" t="s">
         <v>2531</v>
@@ -44732,7 +44732,7 @@
         <v>33</v>
       </c>
       <c r="C2530">
-        <v>5520</v>
+        <v>5350</v>
       </c>
       <c r="D2530" t="s">
         <v>2532</v>
@@ -44746,7 +44746,7 @@
         <v>34</v>
       </c>
       <c r="C2531">
-        <v>5390</v>
+        <v>5270</v>
       </c>
       <c r="D2531" t="s">
         <v>2533</v>
@@ -44760,7 +44760,7 @@
         <v>35</v>
       </c>
       <c r="C2532">
-        <v>5330</v>
+        <v>5210</v>
       </c>
       <c r="D2532" t="s">
         <v>2534</v>
@@ -44774,7 +44774,7 @@
         <v>36</v>
       </c>
       <c r="C2533">
-        <v>5250</v>
+        <v>5130</v>
       </c>
       <c r="D2533" t="s">
         <v>2535</v>
@@ -44788,7 +44788,7 @@
         <v>37</v>
       </c>
       <c r="C2534">
-        <v>5150</v>
+        <v>5030</v>
       </c>
       <c r="D2534" t="s">
         <v>2536</v>
@@ -44802,7 +44802,7 @@
         <v>38</v>
       </c>
       <c r="C2535">
-        <v>5040</v>
+        <v>4930</v>
       </c>
       <c r="D2535" t="s">
         <v>2537</v>
@@ -44816,7 +44816,7 @@
         <v>39</v>
       </c>
       <c r="C2536">
-        <v>4920</v>
+        <v>4830</v>
       </c>
       <c r="D2536" t="s">
         <v>2538</v>
@@ -44830,7 +44830,7 @@
         <v>40</v>
       </c>
       <c r="C2537">
-        <v>4800</v>
+        <v>4720</v>
       </c>
       <c r="D2537" t="s">
         <v>2539</v>
@@ -44844,7 +44844,7 @@
         <v>41</v>
       </c>
       <c r="C2538">
-        <v>4680</v>
+        <v>4620</v>
       </c>
       <c r="D2538" t="s">
         <v>2540</v>
@@ -44858,7 +44858,7 @@
         <v>42</v>
       </c>
       <c r="C2539">
-        <v>4560</v>
+        <v>4520</v>
       </c>
       <c r="D2539" t="s">
         <v>2541</v>
@@ -44872,7 +44872,7 @@
         <v>43</v>
       </c>
       <c r="C2540">
-        <v>4440</v>
+        <v>4430</v>
       </c>
       <c r="D2540" t="s">
         <v>2542</v>
@@ -44886,7 +44886,7 @@
         <v>44</v>
       </c>
       <c r="C2541">
-        <v>4340</v>
+        <v>4360</v>
       </c>
       <c r="D2541" t="s">
         <v>2543</v>
@@ -44900,7 +44900,7 @@
         <v>45</v>
       </c>
       <c r="C2542">
-        <v>4260</v>
+        <v>4300</v>
       </c>
       <c r="D2542" t="s">
         <v>2544</v>
@@ -44914,7 +44914,7 @@
         <v>46</v>
       </c>
       <c r="C2543">
-        <v>4190</v>
+        <v>4260</v>
       </c>
       <c r="D2543" t="s">
         <v>2545</v>
@@ -44928,7 +44928,7 @@
         <v>47</v>
       </c>
       <c r="C2544">
-        <v>4140</v>
+        <v>4230</v>
       </c>
       <c r="D2544" t="s">
         <v>2546</v>
@@ -44942,7 +44942,7 @@
         <v>48</v>
       </c>
       <c r="C2545">
-        <v>4100</v>
+        <v>4210</v>
       </c>
       <c r="D2545" t="s">
         <v>2547</v>
@@ -44956,7 +44956,7 @@
         <v>49</v>
       </c>
       <c r="C2546">
-        <v>4080</v>
+        <v>4200</v>
       </c>
       <c r="D2546" t="s">
         <v>2548</v>
@@ -44970,7 +44970,7 @@
         <v>50</v>
       </c>
       <c r="C2547">
-        <v>4060</v>
+        <v>4200</v>
       </c>
       <c r="D2547" t="s">
         <v>2549</v>
@@ -44984,7 +44984,7 @@
         <v>51</v>
       </c>
       <c r="C2548">
-        <v>4050</v>
+        <v>4210</v>
       </c>
       <c r="D2548" t="s">
         <v>2550</v>
@@ -44998,7 +44998,7 @@
         <v>52</v>
       </c>
       <c r="C2549">
-        <v>4050</v>
+        <v>4210</v>
       </c>
       <c r="D2549" t="s">
         <v>2551</v>
@@ -45012,7 +45012,7 @@
         <v>53</v>
       </c>
       <c r="C2550">
-        <v>4040</v>
+        <v>4220</v>
       </c>
       <c r="D2550" t="s">
         <v>2552</v>
@@ -45026,7 +45026,7 @@
         <v>54</v>
       </c>
       <c r="C2551">
-        <v>4050</v>
+        <v>4240</v>
       </c>
       <c r="D2551" t="s">
         <v>2553</v>
@@ -45040,7 +45040,7 @@
         <v>55</v>
       </c>
       <c r="C2552">
-        <v>4050</v>
+        <v>4250</v>
       </c>
       <c r="D2552" t="s">
         <v>2554</v>
@@ -45054,7 +45054,7 @@
         <v>56</v>
       </c>
       <c r="C2553">
-        <v>4070</v>
+        <v>4280</v>
       </c>
       <c r="D2553" t="s">
         <v>2555</v>
@@ -45068,7 +45068,7 @@
         <v>57</v>
       </c>
       <c r="C2554">
-        <v>4090</v>
+        <v>4300</v>
       </c>
       <c r="D2554" t="s">
         <v>2556</v>
@@ -45082,7 +45082,7 @@
         <v>58</v>
       </c>
       <c r="C2555">
-        <v>4110</v>
+        <v>4330</v>
       </c>
       <c r="D2555" t="s">
         <v>2557</v>
@@ -45096,7 +45096,7 @@
         <v>59</v>
       </c>
       <c r="C2556">
-        <v>4140</v>
+        <v>4370</v>
       </c>
       <c r="D2556" t="s">
         <v>2558</v>
@@ -45110,7 +45110,7 @@
         <v>60</v>
       </c>
       <c r="C2557">
-        <v>4180</v>
+        <v>4400</v>
       </c>
       <c r="D2557" t="s">
         <v>2559</v>
@@ -45124,7 +45124,7 @@
         <v>61</v>
       </c>
       <c r="C2558">
-        <v>4220</v>
+        <v>4440</v>
       </c>
       <c r="D2558" t="s">
         <v>2560</v>
@@ -45138,7 +45138,7 @@
         <v>62</v>
       </c>
       <c r="C2559">
-        <v>4270</v>
+        <v>4490</v>
       </c>
       <c r="D2559" t="s">
         <v>2561</v>
@@ -45152,7 +45152,7 @@
         <v>63</v>
       </c>
       <c r="C2560">
-        <v>4330</v>
+        <v>4530</v>
       </c>
       <c r="D2560" t="s">
         <v>2562</v>
@@ -45166,7 +45166,7 @@
         <v>64</v>
       </c>
       <c r="C2561">
-        <v>4390</v>
+        <v>4590</v>
       </c>
       <c r="D2561" t="s">
         <v>2563</v>
@@ -45180,7 +45180,7 @@
         <v>65</v>
       </c>
       <c r="C2562">
-        <v>4450</v>
+        <v>4650</v>
       </c>
       <c r="D2562" t="s">
         <v>2564</v>
@@ -45194,7 +45194,7 @@
         <v>66</v>
       </c>
       <c r="C2563">
-        <v>4530</v>
+        <v>4730</v>
       </c>
       <c r="D2563" t="s">
         <v>2565</v>
@@ -45208,7 +45208,7 @@
         <v>67</v>
       </c>
       <c r="C2564">
-        <v>4610</v>
+        <v>4820</v>
       </c>
       <c r="D2564" t="s">
         <v>2566</v>
@@ -45222,7 +45222,7 @@
         <v>68</v>
       </c>
       <c r="C2565">
-        <v>4700</v>
+        <v>4920</v>
       </c>
       <c r="D2565" t="s">
         <v>2567</v>
@@ -45236,7 +45236,7 @@
         <v>69</v>
       </c>
       <c r="C2566">
-        <v>4800</v>
+        <v>5040</v>
       </c>
       <c r="D2566" t="s">
         <v>2568</v>
@@ -45250,7 +45250,7 @@
         <v>70</v>
       </c>
       <c r="C2567">
-        <v>4900</v>
+        <v>5170</v>
       </c>
       <c r="D2567" t="s">
         <v>2569</v>
@@ -45264,7 +45264,7 @@
         <v>71</v>
       </c>
       <c r="C2568">
-        <v>5010</v>
+        <v>5300</v>
       </c>
       <c r="D2568" t="s">
         <v>2570</v>
@@ -45278,7 +45278,7 @@
         <v>72</v>
       </c>
       <c r="C2569">
-        <v>5120</v>
+        <v>5430</v>
       </c>
       <c r="D2569" t="s">
         <v>2571</v>
@@ -45292,7 +45292,7 @@
         <v>73</v>
       </c>
       <c r="C2570">
-        <v>5240</v>
+        <v>5560</v>
       </c>
       <c r="D2570" t="s">
         <v>2572</v>
@@ -45306,7 +45306,7 @@
         <v>74</v>
       </c>
       <c r="C2571">
-        <v>5380</v>
+        <v>5710</v>
       </c>
       <c r="D2571" t="s">
         <v>2573</v>
@@ -45320,7 +45320,7 @@
         <v>75</v>
       </c>
       <c r="C2572">
-        <v>5530</v>
+        <v>5850</v>
       </c>
       <c r="D2572" t="s">
         <v>2574</v>
@@ -45334,7 +45334,7 @@
         <v>76</v>
       </c>
       <c r="C2573">
-        <v>5690</v>
+        <v>6000</v>
       </c>
       <c r="D2573" t="s">
         <v>2575</v>
@@ -45348,7 +45348,7 @@
         <v>77</v>
       </c>
       <c r="C2574">
-        <v>5860</v>
+        <v>6150</v>
       </c>
       <c r="D2574" t="s">
         <v>2576</v>
@@ -45362,7 +45362,7 @@
         <v>78</v>
       </c>
       <c r="C2575">
-        <v>6010</v>
+        <v>6290</v>
       </c>
       <c r="D2575" t="s">
         <v>2577</v>
@@ -45376,7 +45376,7 @@
         <v>79</v>
       </c>
       <c r="C2576">
-        <v>6150</v>
+        <v>6400</v>
       </c>
       <c r="D2576" t="s">
         <v>2578</v>
@@ -45390,7 +45390,7 @@
         <v>80</v>
       </c>
       <c r="C2577">
-        <v>6260</v>
+        <v>6480</v>
       </c>
       <c r="D2577" t="s">
         <v>2579</v>
@@ -45404,7 +45404,7 @@
         <v>81</v>
       </c>
       <c r="C2578">
-        <v>6360</v>
+        <v>6550</v>
       </c>
       <c r="D2578" t="s">
         <v>2580</v>
@@ -45418,7 +45418,7 @@
         <v>82</v>
       </c>
       <c r="C2579">
-        <v>6470</v>
+        <v>6630</v>
       </c>
       <c r="D2579" t="s">
         <v>2581</v>
@@ -45432,7 +45432,7 @@
         <v>83</v>
       </c>
       <c r="C2580">
-        <v>6570</v>
+        <v>6690</v>
       </c>
       <c r="D2580" t="s">
         <v>2582</v>
@@ -45446,7 +45446,7 @@
         <v>84</v>
       </c>
       <c r="C2581">
-        <v>6680</v>
+        <v>6780</v>
       </c>
       <c r="D2581" t="s">
         <v>2583</v>
@@ -45460,7 +45460,7 @@
         <v>85</v>
       </c>
       <c r="C2582">
-        <v>6720</v>
+        <v>6800</v>
       </c>
       <c r="D2582" t="s">
         <v>2584</v>
@@ -45474,7 +45474,7 @@
         <v>86</v>
       </c>
       <c r="C2583">
-        <v>6720</v>
+        <v>6800</v>
       </c>
       <c r="D2583" t="s">
         <v>2585</v>
@@ -45488,7 +45488,7 @@
         <v>87</v>
       </c>
       <c r="C2584">
-        <v>6700</v>
+        <v>6790</v>
       </c>
       <c r="D2584" t="s">
         <v>2586</v>
@@ -45502,7 +45502,7 @@
         <v>88</v>
       </c>
       <c r="C2585">
-        <v>6610</v>
+        <v>6730</v>
       </c>
       <c r="D2585" t="s">
         <v>2587</v>
@@ -45516,7 +45516,7 @@
         <v>89</v>
       </c>
       <c r="C2586">
-        <v>6450</v>
+        <v>6610</v>
       </c>
       <c r="D2586" t="s">
         <v>2588</v>
@@ -45530,7 +45530,7 @@
         <v>90</v>
       </c>
       <c r="C2587">
-        <v>6330</v>
+        <v>6540</v>
       </c>
       <c r="D2587" t="s">
         <v>2589</v>
@@ -45544,7 +45544,7 @@
         <v>91</v>
       </c>
       <c r="C2588">
-        <v>6190</v>
+        <v>6410</v>
       </c>
       <c r="D2588" t="s">
         <v>2590</v>
@@ -45558,7 +45558,7 @@
         <v>92</v>
       </c>
       <c r="C2589">
-        <v>6030</v>
+        <v>6240</v>
       </c>
       <c r="D2589" t="s">
         <v>2591</v>
@@ -45572,7 +45572,7 @@
         <v>93</v>
       </c>
       <c r="C2590">
-        <v>5810</v>
+        <v>6000</v>
       </c>
       <c r="D2590" t="s">
         <v>2592</v>
@@ -45586,7 +45586,7 @@
         <v>94</v>
       </c>
       <c r="C2591">
-        <v>5630</v>
+        <v>5840</v>
       </c>
       <c r="D2591" t="s">
         <v>2593</v>
@@ -45600,7 +45600,7 @@
         <v>95</v>
       </c>
       <c r="C2592">
-        <v>5550</v>
+        <v>5750</v>
       </c>
       <c r="D2592" t="s">
         <v>2594</v>
@@ -45614,7 +45614,7 @@
         <v>96</v>
       </c>
       <c r="C2593">
-        <v>5440</v>
+        <v>5640</v>
       </c>
       <c r="D2593" t="s">
         <v>2595</v>
@@ -45628,7 +45628,7 @@
         <v>1</v>
       </c>
       <c r="C2594">
-        <v>5320</v>
+        <v>5470</v>
       </c>
       <c r="D2594" t="s">
         <v>2596</v>
@@ -45642,7 +45642,7 @@
         <v>2</v>
       </c>
       <c r="C2595">
-        <v>5290</v>
+        <v>5420</v>
       </c>
       <c r="D2595" t="s">
         <v>2597</v>
@@ -45656,7 +45656,7 @@
         <v>3</v>
       </c>
       <c r="C2596">
-        <v>5210</v>
+        <v>5370</v>
       </c>
       <c r="D2596" t="s">
         <v>2598</v>
@@ -45670,7 +45670,7 @@
         <v>4</v>
       </c>
       <c r="C2597">
-        <v>5130</v>
+        <v>5300</v>
       </c>
       <c r="D2597" t="s">
         <v>2599</v>
@@ -45684,7 +45684,7 @@
         <v>5</v>
       </c>
       <c r="C2598">
-        <v>5080</v>
+        <v>5240</v>
       </c>
       <c r="D2598" t="s">
         <v>2600</v>
@@ -45698,7 +45698,7 @@
         <v>6</v>
       </c>
       <c r="C2599">
-        <v>5040</v>
+        <v>5180</v>
       </c>
       <c r="D2599" t="s">
         <v>2601</v>
@@ -45712,7 +45712,7 @@
         <v>7</v>
       </c>
       <c r="C2600">
-        <v>5010</v>
+        <v>5120</v>
       </c>
       <c r="D2600" t="s">
         <v>2602</v>
@@ -45726,7 +45726,7 @@
         <v>8</v>
       </c>
       <c r="C2601">
-        <v>4980</v>
+        <v>5070</v>
       </c>
       <c r="D2601" t="s">
         <v>2603</v>
@@ -45740,7 +45740,7 @@
         <v>9</v>
       </c>
       <c r="C2602">
-        <v>4950</v>
+        <v>5030</v>
       </c>
       <c r="D2602" t="s">
         <v>2604</v>
@@ -45754,7 +45754,7 @@
         <v>10</v>
       </c>
       <c r="C2603">
-        <v>4930</v>
+        <v>4990</v>
       </c>
       <c r="D2603" t="s">
         <v>2605</v>
@@ -45768,7 +45768,7 @@
         <v>11</v>
       </c>
       <c r="C2604">
-        <v>4930</v>
+        <v>4960</v>
       </c>
       <c r="D2604" t="s">
         <v>2606</v>
@@ -45782,7 +45782,7 @@
         <v>12</v>
       </c>
       <c r="C2605">
-        <v>4930</v>
+        <v>4940</v>
       </c>
       <c r="D2605" t="s">
         <v>2607</v>
@@ -45796,7 +45796,7 @@
         <v>13</v>
       </c>
       <c r="C2606">
-        <v>4940</v>
+        <v>4930</v>
       </c>
       <c r="D2606" t="s">
         <v>2608</v>
@@ -45810,7 +45810,7 @@
         <v>14</v>
       </c>
       <c r="C2607">
-        <v>4950</v>
+        <v>4920</v>
       </c>
       <c r="D2607" t="s">
         <v>2609</v>
@@ -45824,7 +45824,7 @@
         <v>15</v>
       </c>
       <c r="C2608">
-        <v>4960</v>
+        <v>4910</v>
       </c>
       <c r="D2608" t="s">
         <v>2610</v>
@@ -45838,7 +45838,7 @@
         <v>16</v>
       </c>
       <c r="C2609">
-        <v>4970</v>
+        <v>4910</v>
       </c>
       <c r="D2609" t="s">
         <v>2611</v>
@@ -45852,7 +45852,7 @@
         <v>17</v>
       </c>
       <c r="C2610">
-        <v>4970</v>
+        <v>4910</v>
       </c>
       <c r="D2610" t="s">
         <v>2612</v>
@@ -45866,7 +45866,7 @@
         <v>18</v>
       </c>
       <c r="C2611">
-        <v>4970</v>
+        <v>4910</v>
       </c>
       <c r="D2611" t="s">
         <v>2613</v>
@@ -45880,7 +45880,7 @@
         <v>19</v>
       </c>
       <c r="C2612">
-        <v>4980</v>
+        <v>4930</v>
       </c>
       <c r="D2612" t="s">
         <v>2614</v>
@@ -45894,7 +45894,7 @@
         <v>20</v>
       </c>
       <c r="C2613">
-        <v>4990</v>
+        <v>4950</v>
       </c>
       <c r="D2613" t="s">
         <v>2615</v>
@@ -45908,7 +45908,7 @@
         <v>21</v>
       </c>
       <c r="C2614">
-        <v>5020</v>
+        <v>4980</v>
       </c>
       <c r="D2614" t="s">
         <v>2616</v>
@@ -45922,7 +45922,7 @@
         <v>22</v>
       </c>
       <c r="C2615">
-        <v>5060</v>
+        <v>5020</v>
       </c>
       <c r="D2615" t="s">
         <v>2617</v>
@@ -45936,7 +45936,7 @@
         <v>23</v>
       </c>
       <c r="C2616">
-        <v>5110</v>
+        <v>5080</v>
       </c>
       <c r="D2616" t="s">
         <v>2618</v>
@@ -45950,7 +45950,7 @@
         <v>24</v>
       </c>
       <c r="C2617">
-        <v>5170</v>
+        <v>5130</v>
       </c>
       <c r="D2617" t="s">
         <v>2619</v>
@@ -45964,7 +45964,7 @@
         <v>25</v>
       </c>
       <c r="C2618">
-        <v>5240</v>
+        <v>5200</v>
       </c>
       <c r="D2618" t="s">
         <v>2620</v>
@@ -45978,7 +45978,7 @@
         <v>26</v>
       </c>
       <c r="C2619">
-        <v>5360</v>
+        <v>5260</v>
       </c>
       <c r="D2619" t="s">
         <v>2621</v>
@@ -45992,7 +45992,7 @@
         <v>27</v>
       </c>
       <c r="C2620">
-        <v>5420</v>
+        <v>5330</v>
       </c>
       <c r="D2620" t="s">
         <v>2622</v>
@@ -46006,7 +46006,7 @@
         <v>28</v>
       </c>
       <c r="C2621">
-        <v>5480</v>
+        <v>5390</v>
       </c>
       <c r="D2621" t="s">
         <v>2623</v>
@@ -46020,7 +46020,7 @@
         <v>29</v>
       </c>
       <c r="C2622">
-        <v>5530</v>
+        <v>5450</v>
       </c>
       <c r="D2622" t="s">
         <v>2624</v>
@@ -46034,7 +46034,7 @@
         <v>30</v>
       </c>
       <c r="C2623">
-        <v>5560</v>
+        <v>5490</v>
       </c>
       <c r="D2623" t="s">
         <v>2625</v>
@@ -46048,7 +46048,7 @@
         <v>31</v>
       </c>
       <c r="C2624">
-        <v>5570</v>
+        <v>5520</v>
       </c>
       <c r="D2624" t="s">
         <v>2626</v>
@@ -46062,7 +46062,7 @@
         <v>32</v>
       </c>
       <c r="C2625">
-        <v>5590</v>
+        <v>5530</v>
       </c>
       <c r="D2625" t="s">
         <v>2627</v>
@@ -46076,7 +46076,7 @@
         <v>33</v>
       </c>
       <c r="C2626">
-        <v>5620</v>
+        <v>5520</v>
       </c>
       <c r="D2626" t="s">
         <v>2628</v>
@@ -46104,7 +46104,7 @@
         <v>35</v>
       </c>
       <c r="C2628">
-        <v>5430</v>
+        <v>5440</v>
       </c>
       <c r="D2628" t="s">
         <v>2630</v>
@@ -46118,7 +46118,7 @@
         <v>36</v>
       </c>
       <c r="C2629">
-        <v>5350</v>
+        <v>5360</v>
       </c>
       <c r="D2629" t="s">
         <v>2631</v>
@@ -46132,7 +46132,7 @@
         <v>37</v>
       </c>
       <c r="C2630">
-        <v>5250</v>
+        <v>5270</v>
       </c>
       <c r="D2630" t="s">
         <v>2632</v>
@@ -46146,7 +46146,7 @@
         <v>38</v>
       </c>
       <c r="C2631">
-        <v>5140</v>
+        <v>5150</v>
       </c>
       <c r="D2631" t="s">
         <v>2633</v>
@@ -46160,7 +46160,7 @@
         <v>39</v>
       </c>
       <c r="C2632">
-        <v>5020</v>
+        <v>5030</v>
       </c>
       <c r="D2632" t="s">
         <v>2634</v>
@@ -46188,7 +46188,7 @@
         <v>41</v>
       </c>
       <c r="C2634">
-        <v>4780</v>
+        <v>4770</v>
       </c>
       <c r="D2634" t="s">
         <v>2636</v>
@@ -46216,7 +46216,7 @@
         <v>43</v>
       </c>
       <c r="C2636">
-        <v>4540</v>
+        <v>4550</v>
       </c>
       <c r="D2636" t="s">
         <v>2638</v>
@@ -46230,7 +46230,7 @@
         <v>44</v>
       </c>
       <c r="C2637">
-        <v>4440</v>
+        <v>4470</v>
       </c>
       <c r="D2637" t="s">
         <v>2639</v>
@@ -46244,7 +46244,7 @@
         <v>45</v>
       </c>
       <c r="C2638">
-        <v>4320</v>
+        <v>4400</v>
       </c>
       <c r="D2638" t="s">
         <v>2640</v>
@@ -46258,7 +46258,7 @@
         <v>46</v>
       </c>
       <c r="C2639">
-        <v>4250</v>
+        <v>4360</v>
       </c>
       <c r="D2639" t="s">
         <v>2641</v>
@@ -46272,7 +46272,7 @@
         <v>47</v>
       </c>
       <c r="C2640">
-        <v>4200</v>
+        <v>4320</v>
       </c>
       <c r="D2640" t="s">
         <v>2642</v>
@@ -46286,7 +46286,7 @@
         <v>48</v>
       </c>
       <c r="C2641">
-        <v>4160</v>
+        <v>4300</v>
       </c>
       <c r="D2641" t="s">
         <v>2643</v>
@@ -46300,7 +46300,7 @@
         <v>49</v>
       </c>
       <c r="C2642">
-        <v>4140</v>
+        <v>4290</v>
       </c>
       <c r="D2642" t="s">
         <v>2644</v>
@@ -46314,7 +46314,7 @@
         <v>50</v>
       </c>
       <c r="C2643">
-        <v>4120</v>
+        <v>4280</v>
       </c>
       <c r="D2643" t="s">
         <v>2645</v>
@@ -46328,7 +46328,7 @@
         <v>51</v>
       </c>
       <c r="C2644">
-        <v>4110</v>
+        <v>4270</v>
       </c>
       <c r="D2644" t="s">
         <v>2646</v>
@@ -46342,7 +46342,7 @@
         <v>52</v>
       </c>
       <c r="C2645">
-        <v>4110</v>
+        <v>4260</v>
       </c>
       <c r="D2645" t="s">
         <v>2647</v>
@@ -46356,7 +46356,7 @@
         <v>53</v>
       </c>
       <c r="C2646">
-        <v>4100</v>
+        <v>4260</v>
       </c>
       <c r="D2646" t="s">
         <v>2648</v>
@@ -46370,7 +46370,7 @@
         <v>54</v>
       </c>
       <c r="C2647">
-        <v>4110</v>
+        <v>4260</v>
       </c>
       <c r="D2647" t="s">
         <v>2649</v>
@@ -46384,7 +46384,7 @@
         <v>55</v>
       </c>
       <c r="C2648">
-        <v>4110</v>
+        <v>4260</v>
       </c>
       <c r="D2648" t="s">
         <v>2650</v>
@@ -46398,7 +46398,7 @@
         <v>56</v>
       </c>
       <c r="C2649">
-        <v>4130</v>
+        <v>4270</v>
       </c>
       <c r="D2649" t="s">
         <v>2651</v>
@@ -46412,7 +46412,7 @@
         <v>57</v>
       </c>
       <c r="C2650">
-        <v>4150</v>
+        <v>4290</v>
       </c>
       <c r="D2650" t="s">
         <v>2652</v>
@@ -46426,7 +46426,7 @@
         <v>58</v>
       </c>
       <c r="C2651">
-        <v>4170</v>
+        <v>4320</v>
       </c>
       <c r="D2651" t="s">
         <v>2653</v>
@@ -46440,7 +46440,7 @@
         <v>59</v>
       </c>
       <c r="C2652">
-        <v>4200</v>
+        <v>4350</v>
       </c>
       <c r="D2652" t="s">
         <v>2654</v>
@@ -46454,7 +46454,7 @@
         <v>60</v>
       </c>
       <c r="C2653">
-        <v>4240</v>
+        <v>4380</v>
       </c>
       <c r="D2653" t="s">
         <v>2655</v>
@@ -46468,7 +46468,7 @@
         <v>61</v>
       </c>
       <c r="C2654">
-        <v>4280</v>
+        <v>4420</v>
       </c>
       <c r="D2654" t="s">
         <v>2656</v>
@@ -46482,7 +46482,7 @@
         <v>62</v>
       </c>
       <c r="C2655">
-        <v>4330</v>
+        <v>4450</v>
       </c>
       <c r="D2655" t="s">
         <v>2657</v>
@@ -46496,7 +46496,7 @@
         <v>63</v>
       </c>
       <c r="C2656">
-        <v>4390</v>
+        <v>4490</v>
       </c>
       <c r="D2656" t="s">
         <v>2658</v>
@@ -46510,7 +46510,7 @@
         <v>64</v>
       </c>
       <c r="C2657">
-        <v>4450</v>
+        <v>4530</v>
       </c>
       <c r="D2657" t="s">
         <v>2659</v>
@@ -46524,7 +46524,7 @@
         <v>65</v>
       </c>
       <c r="C2658">
-        <v>4510</v>
+        <v>4590</v>
       </c>
       <c r="D2658" t="s">
         <v>2660</v>
@@ -46538,7 +46538,7 @@
         <v>66</v>
       </c>
       <c r="C2659">
-        <v>4590</v>
+        <v>4660</v>
       </c>
       <c r="D2659" t="s">
         <v>2661</v>
@@ -46552,7 +46552,7 @@
         <v>67</v>
       </c>
       <c r="C2660">
-        <v>4670</v>
+        <v>4750</v>
       </c>
       <c r="D2660" t="s">
         <v>2662</v>
@@ -46566,7 +46566,7 @@
         <v>68</v>
       </c>
       <c r="C2661">
-        <v>4760</v>
+        <v>4850</v>
       </c>
       <c r="D2661" t="s">
         <v>2663</v>
@@ -46580,7 +46580,7 @@
         <v>69</v>
       </c>
       <c r="C2662">
-        <v>4860</v>
+        <v>4960</v>
       </c>
       <c r="D2662" t="s">
         <v>2664</v>
@@ -46594,7 +46594,7 @@
         <v>70</v>
       </c>
       <c r="C2663">
-        <v>4960</v>
+        <v>5080</v>
       </c>
       <c r="D2663" t="s">
         <v>2665</v>
@@ -46608,7 +46608,7 @@
         <v>71</v>
       </c>
       <c r="C2664">
-        <v>5070</v>
+        <v>5190</v>
       </c>
       <c r="D2664" t="s">
         <v>2666</v>
@@ -46622,7 +46622,7 @@
         <v>72</v>
       </c>
       <c r="C2665">
-        <v>5180</v>
+        <v>5310</v>
       </c>
       <c r="D2665" t="s">
         <v>2667</v>
@@ -46636,7 +46636,7 @@
         <v>73</v>
       </c>
       <c r="C2666">
-        <v>5300</v>
+        <v>5420</v>
       </c>
       <c r="D2666" t="s">
         <v>2668</v>
@@ -46650,7 +46650,7 @@
         <v>74</v>
       </c>
       <c r="C2667">
-        <v>5440</v>
+        <v>5530</v>
       </c>
       <c r="D2667" t="s">
         <v>2669</v>
@@ -46664,7 +46664,7 @@
         <v>75</v>
       </c>
       <c r="C2668">
-        <v>5590</v>
+        <v>5660</v>
       </c>
       <c r="D2668" t="s">
         <v>2670</v>
@@ -46678,7 +46678,7 @@
         <v>76</v>
       </c>
       <c r="C2669">
-        <v>5750</v>
+        <v>5790</v>
       </c>
       <c r="D2669" t="s">
         <v>2671</v>
@@ -46692,7 +46692,7 @@
         <v>77</v>
       </c>
       <c r="C2670">
-        <v>5920</v>
+        <v>5940</v>
       </c>
       <c r="D2670" t="s">
         <v>2672</v>
@@ -46720,7 +46720,7 @@
         <v>79</v>
       </c>
       <c r="C2672">
-        <v>6210</v>
+        <v>6190</v>
       </c>
       <c r="D2672" t="s">
         <v>2674</v>
@@ -46734,7 +46734,7 @@
         <v>80</v>
       </c>
       <c r="C2673">
-        <v>6320</v>
+        <v>6280</v>
       </c>
       <c r="D2673" t="s">
         <v>2675</v>
@@ -46748,7 +46748,7 @@
         <v>81</v>
       </c>
       <c r="C2674">
-        <v>6420</v>
+        <v>6370</v>
       </c>
       <c r="D2674" t="s">
         <v>2676</v>
@@ -46762,7 +46762,7 @@
         <v>82</v>
       </c>
       <c r="C2675">
-        <v>6530</v>
+        <v>6470</v>
       </c>
       <c r="D2675" t="s">
         <v>2677</v>
@@ -46776,7 +46776,7 @@
         <v>83</v>
       </c>
       <c r="C2676">
-        <v>6630</v>
+        <v>6550</v>
       </c>
       <c r="D2676" t="s">
         <v>2678</v>
@@ -46790,7 +46790,7 @@
         <v>84</v>
       </c>
       <c r="C2677">
-        <v>6740</v>
+        <v>6650</v>
       </c>
       <c r="D2677" t="s">
         <v>2679</v>
@@ -46804,7 +46804,7 @@
         <v>85</v>
       </c>
       <c r="C2678">
-        <v>6780</v>
+        <v>6700</v>
       </c>
       <c r="D2678" t="s">
         <v>2680</v>
@@ -46818,7 +46818,7 @@
         <v>86</v>
       </c>
       <c r="C2679">
-        <v>6780</v>
+        <v>6700</v>
       </c>
       <c r="D2679" t="s">
         <v>2681</v>
@@ -46832,7 +46832,7 @@
         <v>87</v>
       </c>
       <c r="C2680">
-        <v>6760</v>
+        <v>6700</v>
       </c>
       <c r="D2680" t="s">
         <v>2682</v>
@@ -46846,7 +46846,7 @@
         <v>88</v>
       </c>
       <c r="C2681">
-        <v>6670</v>
+        <v>6630</v>
       </c>
       <c r="D2681" t="s">
         <v>2683</v>
@@ -46860,7 +46860,7 @@
         <v>89</v>
       </c>
       <c r="C2682">
-        <v>6510</v>
+        <v>6500</v>
       </c>
       <c r="D2682" t="s">
         <v>2684</v>
@@ -46874,7 +46874,7 @@
         <v>90</v>
       </c>
       <c r="C2683">
-        <v>6390</v>
+        <v>6420</v>
       </c>
       <c r="D2683" t="s">
         <v>2685</v>
@@ -46888,7 +46888,7 @@
         <v>91</v>
       </c>
       <c r="C2684">
-        <v>6250</v>
+        <v>6290</v>
       </c>
       <c r="D2684" t="s">
         <v>2686</v>
@@ -46902,7 +46902,7 @@
         <v>92</v>
       </c>
       <c r="C2685">
-        <v>6090</v>
+        <v>6130</v>
       </c>
       <c r="D2685" t="s">
         <v>2687</v>
@@ -46916,7 +46916,7 @@
         <v>93</v>
       </c>
       <c r="C2686">
-        <v>5870</v>
+        <v>5900</v>
       </c>
       <c r="D2686" t="s">
         <v>2688</v>
@@ -46930,7 +46930,7 @@
         <v>94</v>
       </c>
       <c r="C2687">
-        <v>5690</v>
+        <v>5750</v>
       </c>
       <c r="D2687" t="s">
         <v>2689</v>
@@ -46944,7 +46944,7 @@
         <v>95</v>
       </c>
       <c r="C2688">
-        <v>5610</v>
+        <v>5660</v>
       </c>
       <c r="D2688" t="s">
         <v>2690</v>
@@ -46958,7 +46958,7 @@
         <v>96</v>
       </c>
       <c r="C2689">
-        <v>5500</v>
+        <v>5550</v>
       </c>
       <c r="D2689" t="s">
         <v>2691</v>

--- a/Market Fundamentals/Transelectrica_data/Cons_Prod_final/Weekly_Consumption_2026.xlsx
+++ b/Market Fundamentals/Transelectrica_data/Cons_Prod_final/Weekly_Consumption_2026.xlsx
@@ -44284,7 +44284,7 @@
         <v>1</v>
       </c>
       <c r="C2498">
-        <v>5310</v>
+        <v>5390</v>
       </c>
       <c r="D2498" t="s">
         <v>2500</v>
@@ -44298,7 +44298,7 @@
         <v>2</v>
       </c>
       <c r="C2499">
-        <v>5280</v>
+        <v>5330</v>
       </c>
       <c r="D2499" t="s">
         <v>2501</v>
@@ -44312,7 +44312,7 @@
         <v>3</v>
       </c>
       <c r="C2500">
-        <v>5200</v>
+        <v>5270</v>
       </c>
       <c r="D2500" t="s">
         <v>2502</v>
@@ -44326,7 +44326,7 @@
         <v>4</v>
       </c>
       <c r="C2501">
-        <v>5120</v>
+        <v>5210</v>
       </c>
       <c r="D2501" t="s">
         <v>2503</v>
@@ -44340,7 +44340,7 @@
         <v>5</v>
       </c>
       <c r="C2502">
-        <v>5070</v>
+        <v>5100</v>
       </c>
       <c r="D2502" t="s">
         <v>2504</v>
@@ -44354,7 +44354,7 @@
         <v>6</v>
       </c>
       <c r="C2503">
-        <v>5020</v>
+        <v>5050</v>
       </c>
       <c r="D2503" t="s">
         <v>2505</v>
@@ -44368,7 +44368,7 @@
         <v>7</v>
       </c>
       <c r="C2504">
-        <v>4960</v>
+        <v>5040</v>
       </c>
       <c r="D2504" t="s">
         <v>2506</v>
@@ -44382,7 +44382,7 @@
         <v>8</v>
       </c>
       <c r="C2505">
-        <v>4910</v>
+        <v>5020</v>
       </c>
       <c r="D2505" t="s">
         <v>2507</v>
@@ -44396,7 +44396,7 @@
         <v>9</v>
       </c>
       <c r="C2506">
-        <v>4870</v>
+        <v>4990</v>
       </c>
       <c r="D2506" t="s">
         <v>2508</v>
@@ -44410,7 +44410,7 @@
         <v>10</v>
       </c>
       <c r="C2507">
-        <v>4840</v>
+        <v>4980</v>
       </c>
       <c r="D2507" t="s">
         <v>2509</v>
@@ -44424,7 +44424,7 @@
         <v>11</v>
       </c>
       <c r="C2508">
-        <v>4820</v>
+        <v>4980</v>
       </c>
       <c r="D2508" t="s">
         <v>2510</v>
@@ -44438,7 +44438,7 @@
         <v>12</v>
       </c>
       <c r="C2509">
-        <v>4820</v>
+        <v>4980</v>
       </c>
       <c r="D2509" t="s">
         <v>2511</v>
@@ -44452,7 +44452,7 @@
         <v>13</v>
       </c>
       <c r="C2510">
-        <v>4820</v>
+        <v>5000</v>
       </c>
       <c r="D2510" t="s">
         <v>2512</v>
@@ -44466,7 +44466,7 @@
         <v>14</v>
       </c>
       <c r="C2511">
-        <v>4820</v>
+        <v>5000</v>
       </c>
       <c r="D2511" t="s">
         <v>2513</v>
@@ -44480,7 +44480,7 @@
         <v>15</v>
       </c>
       <c r="C2512">
-        <v>4820</v>
+        <v>5000</v>
       </c>
       <c r="D2512" t="s">
         <v>2514</v>
@@ -44494,7 +44494,7 @@
         <v>16</v>
       </c>
       <c r="C2513">
-        <v>4810</v>
+        <v>5000</v>
       </c>
       <c r="D2513" t="s">
         <v>2515</v>
@@ -44508,7 +44508,7 @@
         <v>17</v>
       </c>
       <c r="C2514">
-        <v>4810</v>
+        <v>5000</v>
       </c>
       <c r="D2514" t="s">
         <v>2516</v>
@@ -44522,7 +44522,7 @@
         <v>18</v>
       </c>
       <c r="C2515">
-        <v>4800</v>
+        <v>5000</v>
       </c>
       <c r="D2515" t="s">
         <v>2517</v>
@@ -44536,7 +44536,7 @@
         <v>19</v>
       </c>
       <c r="C2516">
-        <v>4800</v>
+        <v>5000</v>
       </c>
       <c r="D2516" t="s">
         <v>2518</v>
@@ -44550,7 +44550,7 @@
         <v>20</v>
       </c>
       <c r="C2517">
-        <v>4810</v>
+        <v>4980</v>
       </c>
       <c r="D2517" t="s">
         <v>2519</v>
@@ -44564,7 +44564,7 @@
         <v>21</v>
       </c>
       <c r="C2518">
-        <v>4840</v>
+        <v>4950</v>
       </c>
       <c r="D2518" t="s">
         <v>2520</v>
@@ -44578,7 +44578,7 @@
         <v>22</v>
       </c>
       <c r="C2519">
-        <v>4890</v>
+        <v>4950</v>
       </c>
       <c r="D2519" t="s">
         <v>2521</v>
@@ -44606,7 +44606,7 @@
         <v>24</v>
       </c>
       <c r="C2521">
-        <v>5020</v>
+        <v>4950</v>
       </c>
       <c r="D2521" t="s">
         <v>2523</v>
@@ -44620,7 +44620,7 @@
         <v>25</v>
       </c>
       <c r="C2522">
-        <v>5100</v>
+        <v>5050</v>
       </c>
       <c r="D2522" t="s">
         <v>2524</v>
@@ -44634,7 +44634,7 @@
         <v>26</v>
       </c>
       <c r="C2523">
-        <v>5180</v>
+        <v>5140</v>
       </c>
       <c r="D2523" t="s">
         <v>2525</v>
@@ -44648,7 +44648,7 @@
         <v>27</v>
       </c>
       <c r="C2524">
-        <v>5250</v>
+        <v>5230</v>
       </c>
       <c r="D2524" t="s">
         <v>2526</v>
@@ -44662,7 +44662,7 @@
         <v>28</v>
       </c>
       <c r="C2525">
-        <v>5310</v>
+        <v>5330</v>
       </c>
       <c r="D2525" t="s">
         <v>2527</v>
@@ -44676,7 +44676,7 @@
         <v>29</v>
       </c>
       <c r="C2526">
-        <v>5350</v>
+        <v>5440</v>
       </c>
       <c r="D2526" t="s">
         <v>2528</v>
@@ -44690,7 +44690,7 @@
         <v>30</v>
       </c>
       <c r="C2527">
-        <v>5370</v>
+        <v>5490</v>
       </c>
       <c r="D2527" t="s">
         <v>2529</v>
@@ -44704,7 +44704,7 @@
         <v>31</v>
       </c>
       <c r="C2528">
-        <v>5400</v>
+        <v>5500</v>
       </c>
       <c r="D2528" t="s">
         <v>2530</v>
@@ -44718,7 +44718,7 @@
         <v>32</v>
       </c>
       <c r="C2529">
-        <v>5400</v>
+        <v>5490</v>
       </c>
       <c r="D2529" t="s">
         <v>2531</v>
@@ -44732,7 +44732,7 @@
         <v>33</v>
       </c>
       <c r="C2530">
-        <v>5350</v>
+        <v>5410</v>
       </c>
       <c r="D2530" t="s">
         <v>2532</v>
@@ -44746,7 +44746,7 @@
         <v>34</v>
       </c>
       <c r="C2531">
-        <v>5270</v>
+        <v>5320</v>
       </c>
       <c r="D2531" t="s">
         <v>2533</v>
@@ -44760,7 +44760,7 @@
         <v>35</v>
       </c>
       <c r="C2532">
-        <v>5210</v>
+        <v>5220</v>
       </c>
       <c r="D2532" t="s">
         <v>2534</v>
@@ -44774,7 +44774,7 @@
         <v>36</v>
       </c>
       <c r="C2533">
-        <v>5130</v>
+        <v>5120</v>
       </c>
       <c r="D2533" t="s">
         <v>2535</v>
@@ -44788,7 +44788,7 @@
         <v>37</v>
       </c>
       <c r="C2534">
-        <v>5030</v>
+        <v>5000</v>
       </c>
       <c r="D2534" t="s">
         <v>2536</v>
@@ -44802,7 +44802,7 @@
         <v>38</v>
       </c>
       <c r="C2535">
-        <v>4930</v>
+        <v>4880</v>
       </c>
       <c r="D2535" t="s">
         <v>2537</v>
@@ -44816,7 +44816,7 @@
         <v>39</v>
       </c>
       <c r="C2536">
-        <v>4830</v>
+        <v>4780</v>
       </c>
       <c r="D2536" t="s">
         <v>2538</v>
@@ -44830,7 +44830,7 @@
         <v>40</v>
       </c>
       <c r="C2537">
-        <v>4720</v>
+        <v>4660</v>
       </c>
       <c r="D2537" t="s">
         <v>2539</v>
@@ -44844,7 +44844,7 @@
         <v>41</v>
       </c>
       <c r="C2538">
-        <v>4620</v>
+        <v>4550</v>
       </c>
       <c r="D2538" t="s">
         <v>2540</v>
@@ -44858,7 +44858,7 @@
         <v>42</v>
       </c>
       <c r="C2539">
-        <v>4520</v>
+        <v>4450</v>
       </c>
       <c r="D2539" t="s">
         <v>2541</v>
@@ -44872,7 +44872,7 @@
         <v>43</v>
       </c>
       <c r="C2540">
-        <v>4430</v>
+        <v>4380</v>
       </c>
       <c r="D2540" t="s">
         <v>2542</v>
@@ -44886,7 +44886,7 @@
         <v>44</v>
       </c>
       <c r="C2541">
-        <v>4360</v>
+        <v>4300</v>
       </c>
       <c r="D2541" t="s">
         <v>2543</v>
@@ -44900,7 +44900,7 @@
         <v>45</v>
       </c>
       <c r="C2542">
-        <v>4300</v>
+        <v>4190</v>
       </c>
       <c r="D2542" t="s">
         <v>2544</v>
@@ -44914,7 +44914,7 @@
         <v>46</v>
       </c>
       <c r="C2543">
-        <v>4260</v>
+        <v>4140</v>
       </c>
       <c r="D2543" t="s">
         <v>2545</v>
@@ -44928,7 +44928,7 @@
         <v>47</v>
       </c>
       <c r="C2544">
-        <v>4230</v>
+        <v>4140</v>
       </c>
       <c r="D2544" t="s">
         <v>2546</v>
@@ -44942,7 +44942,7 @@
         <v>48</v>
       </c>
       <c r="C2545">
-        <v>4210</v>
+        <v>4140</v>
       </c>
       <c r="D2545" t="s">
         <v>2547</v>
@@ -44956,7 +44956,7 @@
         <v>49</v>
       </c>
       <c r="C2546">
-        <v>4200</v>
+        <v>4180</v>
       </c>
       <c r="D2546" t="s">
         <v>2548</v>
@@ -44970,7 +44970,7 @@
         <v>50</v>
       </c>
       <c r="C2547">
-        <v>4200</v>
+        <v>4190</v>
       </c>
       <c r="D2547" t="s">
         <v>2549</v>
@@ -44984,7 +44984,7 @@
         <v>51</v>
       </c>
       <c r="C2548">
-        <v>4210</v>
+        <v>4200</v>
       </c>
       <c r="D2548" t="s">
         <v>2550</v>
@@ -45012,7 +45012,7 @@
         <v>53</v>
       </c>
       <c r="C2550">
-        <v>4220</v>
+        <v>4230</v>
       </c>
       <c r="D2550" t="s">
         <v>2552</v>
@@ -45026,7 +45026,7 @@
         <v>54</v>
       </c>
       <c r="C2551">
-        <v>4240</v>
+        <v>4250</v>
       </c>
       <c r="D2551" t="s">
         <v>2553</v>
@@ -45040,7 +45040,7 @@
         <v>55</v>
       </c>
       <c r="C2552">
-        <v>4250</v>
+        <v>4260</v>
       </c>
       <c r="D2552" t="s">
         <v>2554</v>
@@ -45054,7 +45054,7 @@
         <v>56</v>
       </c>
       <c r="C2553">
-        <v>4280</v>
+        <v>4290</v>
       </c>
       <c r="D2553" t="s">
         <v>2555</v>
@@ -45068,7 +45068,7 @@
         <v>57</v>
       </c>
       <c r="C2554">
-        <v>4300</v>
+        <v>4320</v>
       </c>
       <c r="D2554" t="s">
         <v>2556</v>
@@ -45082,7 +45082,7 @@
         <v>58</v>
       </c>
       <c r="C2555">
-        <v>4330</v>
+        <v>4350</v>
       </c>
       <c r="D2555" t="s">
         <v>2557</v>
@@ -45096,7 +45096,7 @@
         <v>59</v>
       </c>
       <c r="C2556">
-        <v>4370</v>
+        <v>4380</v>
       </c>
       <c r="D2556" t="s">
         <v>2558</v>
@@ -45110,7 +45110,7 @@
         <v>60</v>
       </c>
       <c r="C2557">
-        <v>4400</v>
+        <v>4430</v>
       </c>
       <c r="D2557" t="s">
         <v>2559</v>
@@ -45124,7 +45124,7 @@
         <v>61</v>
       </c>
       <c r="C2558">
-        <v>4440</v>
+        <v>4480</v>
       </c>
       <c r="D2558" t="s">
         <v>2560</v>
@@ -45138,7 +45138,7 @@
         <v>62</v>
       </c>
       <c r="C2559">
-        <v>4490</v>
+        <v>4520</v>
       </c>
       <c r="D2559" t="s">
         <v>2561</v>
@@ -45152,7 +45152,7 @@
         <v>63</v>
       </c>
       <c r="C2560">
-        <v>4530</v>
+        <v>4570</v>
       </c>
       <c r="D2560" t="s">
         <v>2562</v>
@@ -45166,7 +45166,7 @@
         <v>64</v>
       </c>
       <c r="C2561">
-        <v>4590</v>
+        <v>4640</v>
       </c>
       <c r="D2561" t="s">
         <v>2563</v>
@@ -45180,7 +45180,7 @@
         <v>65</v>
       </c>
       <c r="C2562">
-        <v>4650</v>
+        <v>4720</v>
       </c>
       <c r="D2562" t="s">
         <v>2564</v>
@@ -45194,7 +45194,7 @@
         <v>66</v>
       </c>
       <c r="C2563">
-        <v>4730</v>
+        <v>4810</v>
       </c>
       <c r="D2563" t="s">
         <v>2565</v>
@@ -45208,7 +45208,7 @@
         <v>67</v>
       </c>
       <c r="C2564">
-        <v>4820</v>
+        <v>4910</v>
       </c>
       <c r="D2564" t="s">
         <v>2566</v>
@@ -45222,7 +45222,7 @@
         <v>68</v>
       </c>
       <c r="C2565">
-        <v>4920</v>
+        <v>5030</v>
       </c>
       <c r="D2565" t="s">
         <v>2567</v>
@@ -45236,7 +45236,7 @@
         <v>69</v>
       </c>
       <c r="C2566">
-        <v>5040</v>
+        <v>5160</v>
       </c>
       <c r="D2566" t="s">
         <v>2568</v>
@@ -45250,7 +45250,7 @@
         <v>70</v>
       </c>
       <c r="C2567">
-        <v>5170</v>
+        <v>5270</v>
       </c>
       <c r="D2567" t="s">
         <v>2569</v>
@@ -45264,7 +45264,7 @@
         <v>71</v>
       </c>
       <c r="C2568">
-        <v>5300</v>
+        <v>5400</v>
       </c>
       <c r="D2568" t="s">
         <v>2570</v>
@@ -45278,7 +45278,7 @@
         <v>72</v>
       </c>
       <c r="C2569">
-        <v>5430</v>
+        <v>5500</v>
       </c>
       <c r="D2569" t="s">
         <v>2571</v>
@@ -45292,7 +45292,7 @@
         <v>73</v>
       </c>
       <c r="C2570">
-        <v>5560</v>
+        <v>5640</v>
       </c>
       <c r="D2570" t="s">
         <v>2572</v>
@@ -45306,7 +45306,7 @@
         <v>74</v>
       </c>
       <c r="C2571">
-        <v>5710</v>
+        <v>5750</v>
       </c>
       <c r="D2571" t="s">
         <v>2573</v>
@@ -45320,7 +45320,7 @@
         <v>75</v>
       </c>
       <c r="C2572">
-        <v>5850</v>
+        <v>5880</v>
       </c>
       <c r="D2572" t="s">
         <v>2574</v>
@@ -45334,7 +45334,7 @@
         <v>76</v>
       </c>
       <c r="C2573">
-        <v>6000</v>
+        <v>6020</v>
       </c>
       <c r="D2573" t="s">
         <v>2575</v>
@@ -45362,7 +45362,7 @@
         <v>78</v>
       </c>
       <c r="C2575">
-        <v>6290</v>
+        <v>6280</v>
       </c>
       <c r="D2575" t="s">
         <v>2577</v>
@@ -45376,7 +45376,7 @@
         <v>79</v>
       </c>
       <c r="C2576">
-        <v>6400</v>
+        <v>6380</v>
       </c>
       <c r="D2576" t="s">
         <v>2578</v>
@@ -45390,7 +45390,7 @@
         <v>80</v>
       </c>
       <c r="C2577">
-        <v>6480</v>
+        <v>6460</v>
       </c>
       <c r="D2577" t="s">
         <v>2579</v>
@@ -45404,7 +45404,7 @@
         <v>81</v>
       </c>
       <c r="C2578">
-        <v>6550</v>
+        <v>6510</v>
       </c>
       <c r="D2578" t="s">
         <v>2580</v>
@@ -45418,7 +45418,7 @@
         <v>82</v>
       </c>
       <c r="C2579">
-        <v>6630</v>
+        <v>6570</v>
       </c>
       <c r="D2579" t="s">
         <v>2581</v>
@@ -45432,7 +45432,7 @@
         <v>83</v>
       </c>
       <c r="C2580">
-        <v>6690</v>
+        <v>6620</v>
       </c>
       <c r="D2580" t="s">
         <v>2582</v>
@@ -45446,7 +45446,7 @@
         <v>84</v>
       </c>
       <c r="C2581">
-        <v>6780</v>
+        <v>6700</v>
       </c>
       <c r="D2581" t="s">
         <v>2583</v>
@@ -45460,7 +45460,7 @@
         <v>85</v>
       </c>
       <c r="C2582">
-        <v>6800</v>
+        <v>6760</v>
       </c>
       <c r="D2582" t="s">
         <v>2584</v>
@@ -45474,7 +45474,7 @@
         <v>86</v>
       </c>
       <c r="C2583">
-        <v>6800</v>
+        <v>6780</v>
       </c>
       <c r="D2583" t="s">
         <v>2585</v>
@@ -45488,7 +45488,7 @@
         <v>87</v>
       </c>
       <c r="C2584">
-        <v>6790</v>
+        <v>6760</v>
       </c>
       <c r="D2584" t="s">
         <v>2586</v>
@@ -45502,7 +45502,7 @@
         <v>88</v>
       </c>
       <c r="C2585">
-        <v>6730</v>
+        <v>6690</v>
       </c>
       <c r="D2585" t="s">
         <v>2587</v>
@@ -45516,7 +45516,7 @@
         <v>89</v>
       </c>
       <c r="C2586">
-        <v>6610</v>
+        <v>6550</v>
       </c>
       <c r="D2586" t="s">
         <v>2588</v>
@@ -45530,7 +45530,7 @@
         <v>90</v>
       </c>
       <c r="C2587">
-        <v>6540</v>
+        <v>6420</v>
       </c>
       <c r="D2587" t="s">
         <v>2589</v>
@@ -45544,7 +45544,7 @@
         <v>91</v>
       </c>
       <c r="C2588">
-        <v>6410</v>
+        <v>6290</v>
       </c>
       <c r="D2588" t="s">
         <v>2590</v>
@@ -45558,7 +45558,7 @@
         <v>92</v>
       </c>
       <c r="C2589">
-        <v>6240</v>
+        <v>6150</v>
       </c>
       <c r="D2589" t="s">
         <v>2591</v>
@@ -45572,7 +45572,7 @@
         <v>93</v>
       </c>
       <c r="C2590">
-        <v>6000</v>
+        <v>5990</v>
       </c>
       <c r="D2590" t="s">
         <v>2592</v>
@@ -45586,7 +45586,7 @@
         <v>94</v>
       </c>
       <c r="C2591">
-        <v>5840</v>
+        <v>5870</v>
       </c>
       <c r="D2591" t="s">
         <v>2593</v>
@@ -45600,7 +45600,7 @@
         <v>95</v>
       </c>
       <c r="C2592">
-        <v>5750</v>
+        <v>5760</v>
       </c>
       <c r="D2592" t="s">
         <v>2594</v>
@@ -45642,7 +45642,7 @@
         <v>2</v>
       </c>
       <c r="C2595">
-        <v>5420</v>
+        <v>5440</v>
       </c>
       <c r="D2595" t="s">
         <v>2597</v>
@@ -45656,7 +45656,7 @@
         <v>3</v>
       </c>
       <c r="C2596">
-        <v>5370</v>
+        <v>5360</v>
       </c>
       <c r="D2596" t="s">
         <v>2598</v>
@@ -45670,7 +45670,7 @@
         <v>4</v>
       </c>
       <c r="C2597">
-        <v>5300</v>
+        <v>5290</v>
       </c>
       <c r="D2597" t="s">
         <v>2599</v>
@@ -45684,7 +45684,7 @@
         <v>5</v>
       </c>
       <c r="C2598">
-        <v>5240</v>
+        <v>5230</v>
       </c>
       <c r="D2598" t="s">
         <v>2600</v>
@@ -45712,7 +45712,7 @@
         <v>7</v>
       </c>
       <c r="C2600">
-        <v>5120</v>
+        <v>5130</v>
       </c>
       <c r="D2600" t="s">
         <v>2602</v>
@@ -45726,7 +45726,7 @@
         <v>8</v>
       </c>
       <c r="C2601">
-        <v>5070</v>
+        <v>5080</v>
       </c>
       <c r="D2601" t="s">
         <v>2603</v>
@@ -45754,7 +45754,7 @@
         <v>10</v>
       </c>
       <c r="C2603">
-        <v>4990</v>
+        <v>4980</v>
       </c>
       <c r="D2603" t="s">
         <v>2605</v>
@@ -45768,7 +45768,7 @@
         <v>11</v>
       </c>
       <c r="C2604">
-        <v>4960</v>
+        <v>4950</v>
       </c>
       <c r="D2604" t="s">
         <v>2606</v>
@@ -45782,7 +45782,7 @@
         <v>12</v>
       </c>
       <c r="C2605">
-        <v>4940</v>
+        <v>4930</v>
       </c>
       <c r="D2605" t="s">
         <v>2607</v>
@@ -45796,7 +45796,7 @@
         <v>13</v>
       </c>
       <c r="C2606">
-        <v>4930</v>
+        <v>4900</v>
       </c>
       <c r="D2606" t="s">
         <v>2608</v>
@@ -45810,7 +45810,7 @@
         <v>14</v>
       </c>
       <c r="C2607">
-        <v>4920</v>
+        <v>4900</v>
       </c>
       <c r="D2607" t="s">
         <v>2609</v>
@@ -45824,7 +45824,7 @@
         <v>15</v>
       </c>
       <c r="C2608">
-        <v>4910</v>
+        <v>4900</v>
       </c>
       <c r="D2608" t="s">
         <v>2610</v>
@@ -45838,7 +45838,7 @@
         <v>16</v>
       </c>
       <c r="C2609">
-        <v>4910</v>
+        <v>4900</v>
       </c>
       <c r="D2609" t="s">
         <v>2611</v>
@@ -45866,7 +45866,7 @@
         <v>18</v>
       </c>
       <c r="C2611">
-        <v>4910</v>
+        <v>4920</v>
       </c>
       <c r="D2611" t="s">
         <v>2613</v>
@@ -45894,7 +45894,7 @@
         <v>20</v>
       </c>
       <c r="C2613">
-        <v>4950</v>
+        <v>4940</v>
       </c>
       <c r="D2613" t="s">
         <v>2615</v>
@@ -45908,7 +45908,7 @@
         <v>21</v>
       </c>
       <c r="C2614">
-        <v>4980</v>
+        <v>4970</v>
       </c>
       <c r="D2614" t="s">
         <v>2616</v>
@@ -45922,7 +45922,7 @@
         <v>22</v>
       </c>
       <c r="C2615">
-        <v>5020</v>
+        <v>5000</v>
       </c>
       <c r="D2615" t="s">
         <v>2617</v>
@@ -45936,7 +45936,7 @@
         <v>23</v>
       </c>
       <c r="C2616">
-        <v>5080</v>
+        <v>5060</v>
       </c>
       <c r="D2616" t="s">
         <v>2618</v>
@@ -45964,7 +45964,7 @@
         <v>25</v>
       </c>
       <c r="C2618">
-        <v>5200</v>
+        <v>5210</v>
       </c>
       <c r="D2618" t="s">
         <v>2620</v>
@@ -45978,7 +45978,7 @@
         <v>26</v>
       </c>
       <c r="C2619">
-        <v>5260</v>
+        <v>5290</v>
       </c>
       <c r="D2619" t="s">
         <v>2621</v>
@@ -45992,7 +45992,7 @@
         <v>27</v>
       </c>
       <c r="C2620">
-        <v>5330</v>
+        <v>5380</v>
       </c>
       <c r="D2620" t="s">
         <v>2622</v>
@@ -46006,7 +46006,7 @@
         <v>28</v>
       </c>
       <c r="C2621">
-        <v>5390</v>
+        <v>5460</v>
       </c>
       <c r="D2621" t="s">
         <v>2623</v>
@@ -46020,7 +46020,7 @@
         <v>29</v>
       </c>
       <c r="C2622">
-        <v>5450</v>
+        <v>5530</v>
       </c>
       <c r="D2622" t="s">
         <v>2624</v>
@@ -46034,7 +46034,7 @@
         <v>30</v>
       </c>
       <c r="C2623">
-        <v>5490</v>
+        <v>5590</v>
       </c>
       <c r="D2623" t="s">
         <v>2625</v>
@@ -46048,7 +46048,7 @@
         <v>31</v>
       </c>
       <c r="C2624">
-        <v>5520</v>
+        <v>5630</v>
       </c>
       <c r="D2624" t="s">
         <v>2626</v>
@@ -46062,7 +46062,7 @@
         <v>32</v>
       </c>
       <c r="C2625">
-        <v>5530</v>
+        <v>5650</v>
       </c>
       <c r="D2625" t="s">
         <v>2627</v>
@@ -46076,7 +46076,7 @@
         <v>33</v>
       </c>
       <c r="C2626">
-        <v>5520</v>
+        <v>5640</v>
       </c>
       <c r="D2626" t="s">
         <v>2628</v>
@@ -46090,7 +46090,7 @@
         <v>34</v>
       </c>
       <c r="C2627">
-        <v>5490</v>
+        <v>5610</v>
       </c>
       <c r="D2627" t="s">
         <v>2629</v>
@@ -46104,7 +46104,7 @@
         <v>35</v>
       </c>
       <c r="C2628">
-        <v>5440</v>
+        <v>5560</v>
       </c>
       <c r="D2628" t="s">
         <v>2630</v>
@@ -46118,7 +46118,7 @@
         <v>36</v>
       </c>
       <c r="C2629">
-        <v>5360</v>
+        <v>5480</v>
       </c>
       <c r="D2629" t="s">
         <v>2631</v>
@@ -46132,7 +46132,7 @@
         <v>37</v>
       </c>
       <c r="C2630">
-        <v>5270</v>
+        <v>5380</v>
       </c>
       <c r="D2630" t="s">
         <v>2632</v>
@@ -46146,7 +46146,7 @@
         <v>38</v>
       </c>
       <c r="C2631">
-        <v>5150</v>
+        <v>5270</v>
       </c>
       <c r="D2631" t="s">
         <v>2633</v>
@@ -46160,7 +46160,7 @@
         <v>39</v>
       </c>
       <c r="C2632">
-        <v>5030</v>
+        <v>5150</v>
       </c>
       <c r="D2632" t="s">
         <v>2634</v>
@@ -46174,7 +46174,7 @@
         <v>40</v>
       </c>
       <c r="C2633">
-        <v>4900</v>
+        <v>5020</v>
       </c>
       <c r="D2633" t="s">
         <v>2635</v>
@@ -46188,7 +46188,7 @@
         <v>41</v>
       </c>
       <c r="C2634">
-        <v>4770</v>
+        <v>4890</v>
       </c>
       <c r="D2634" t="s">
         <v>2636</v>
@@ -46202,7 +46202,7 @@
         <v>42</v>
       </c>
       <c r="C2635">
-        <v>4660</v>
+        <v>4770</v>
       </c>
       <c r="D2635" t="s">
         <v>2637</v>
@@ -46216,7 +46216,7 @@
         <v>43</v>
       </c>
       <c r="C2636">
-        <v>4550</v>
+        <v>4660</v>
       </c>
       <c r="D2636" t="s">
         <v>2638</v>
@@ -46230,7 +46230,7 @@
         <v>44</v>
       </c>
       <c r="C2637">
-        <v>4470</v>
+        <v>4570</v>
       </c>
       <c r="D2637" t="s">
         <v>2639</v>
@@ -46244,7 +46244,7 @@
         <v>45</v>
       </c>
       <c r="C2638">
-        <v>4400</v>
+        <v>4480</v>
       </c>
       <c r="D2638" t="s">
         <v>2640</v>
@@ -46258,7 +46258,7 @@
         <v>46</v>
       </c>
       <c r="C2639">
-        <v>4360</v>
+        <v>4420</v>
       </c>
       <c r="D2639" t="s">
         <v>2641</v>
@@ -46272,7 +46272,7 @@
         <v>47</v>
       </c>
       <c r="C2640">
-        <v>4320</v>
+        <v>4370</v>
       </c>
       <c r="D2640" t="s">
         <v>2642</v>
@@ -46286,7 +46286,7 @@
         <v>48</v>
       </c>
       <c r="C2641">
-        <v>4300</v>
+        <v>4330</v>
       </c>
       <c r="D2641" t="s">
         <v>2643</v>
@@ -46300,7 +46300,7 @@
         <v>49</v>
       </c>
       <c r="C2642">
-        <v>4290</v>
+        <v>4310</v>
       </c>
       <c r="D2642" t="s">
         <v>2644</v>
@@ -46314,7 +46314,7 @@
         <v>50</v>
       </c>
       <c r="C2643">
-        <v>4280</v>
+        <v>4290</v>
       </c>
       <c r="D2643" t="s">
         <v>2645</v>
@@ -46328,7 +46328,7 @@
         <v>51</v>
       </c>
       <c r="C2644">
-        <v>4270</v>
+        <v>4280</v>
       </c>
       <c r="D2644" t="s">
         <v>2646</v>
@@ -46342,7 +46342,7 @@
         <v>52</v>
       </c>
       <c r="C2645">
-        <v>4260</v>
+        <v>4280</v>
       </c>
       <c r="D2645" t="s">
         <v>2647</v>
@@ -46356,7 +46356,7 @@
         <v>53</v>
       </c>
       <c r="C2646">
-        <v>4260</v>
+        <v>4280</v>
       </c>
       <c r="D2646" t="s">
         <v>2648</v>
@@ -46370,7 +46370,7 @@
         <v>54</v>
       </c>
       <c r="C2647">
-        <v>4260</v>
+        <v>4290</v>
       </c>
       <c r="D2647" t="s">
         <v>2649</v>
@@ -46384,7 +46384,7 @@
         <v>55</v>
       </c>
       <c r="C2648">
-        <v>4260</v>
+        <v>4310</v>
       </c>
       <c r="D2648" t="s">
         <v>2650</v>
@@ -46398,7 +46398,7 @@
         <v>56</v>
       </c>
       <c r="C2649">
-        <v>4270</v>
+        <v>4330</v>
       </c>
       <c r="D2649" t="s">
         <v>2651</v>
@@ -46412,7 +46412,7 @@
         <v>57</v>
       </c>
       <c r="C2650">
-        <v>4290</v>
+        <v>4350</v>
       </c>
       <c r="D2650" t="s">
         <v>2652</v>
@@ -46426,7 +46426,7 @@
         <v>58</v>
       </c>
       <c r="C2651">
-        <v>4320</v>
+        <v>4370</v>
       </c>
       <c r="D2651" t="s">
         <v>2653</v>
@@ -46440,7 +46440,7 @@
         <v>59</v>
       </c>
       <c r="C2652">
-        <v>4350</v>
+        <v>4400</v>
       </c>
       <c r="D2652" t="s">
         <v>2654</v>
@@ -46454,7 +46454,7 @@
         <v>60</v>
       </c>
       <c r="C2653">
-        <v>4380</v>
+        <v>4420</v>
       </c>
       <c r="D2653" t="s">
         <v>2655</v>
@@ -46468,7 +46468,7 @@
         <v>61</v>
       </c>
       <c r="C2654">
-        <v>4420</v>
+        <v>4450</v>
       </c>
       <c r="D2654" t="s">
         <v>2656</v>
@@ -46482,7 +46482,7 @@
         <v>62</v>
       </c>
       <c r="C2655">
-        <v>4450</v>
+        <v>4480</v>
       </c>
       <c r="D2655" t="s">
         <v>2657</v>
@@ -46496,7 +46496,7 @@
         <v>63</v>
       </c>
       <c r="C2656">
-        <v>4490</v>
+        <v>4510</v>
       </c>
       <c r="D2656" t="s">
         <v>2658</v>
@@ -46510,7 +46510,7 @@
         <v>64</v>
       </c>
       <c r="C2657">
-        <v>4530</v>
+        <v>4560</v>
       </c>
       <c r="D2657" t="s">
         <v>2659</v>
@@ -46524,7 +46524,7 @@
         <v>65</v>
       </c>
       <c r="C2658">
-        <v>4590</v>
+        <v>4610</v>
       </c>
       <c r="D2658" t="s">
         <v>2660</v>
@@ -46538,7 +46538,7 @@
         <v>66</v>
       </c>
       <c r="C2659">
-        <v>4660</v>
+        <v>4680</v>
       </c>
       <c r="D2659" t="s">
         <v>2661</v>
@@ -46552,7 +46552,7 @@
         <v>67</v>
       </c>
       <c r="C2660">
-        <v>4750</v>
+        <v>4760</v>
       </c>
       <c r="D2660" t="s">
         <v>2662</v>
@@ -46566,7 +46566,7 @@
         <v>68</v>
       </c>
       <c r="C2661">
-        <v>4850</v>
+        <v>4860</v>
       </c>
       <c r="D2661" t="s">
         <v>2663</v>
@@ -46594,7 +46594,7 @@
         <v>70</v>
       </c>
       <c r="C2663">
-        <v>5080</v>
+        <v>5070</v>
       </c>
       <c r="D2663" t="s">
         <v>2665</v>
@@ -46608,7 +46608,7 @@
         <v>71</v>
       </c>
       <c r="C2664">
-        <v>5190</v>
+        <v>5180</v>
       </c>
       <c r="D2664" t="s">
         <v>2666</v>
@@ -46622,7 +46622,7 @@
         <v>72</v>
       </c>
       <c r="C2665">
-        <v>5310</v>
+        <v>5290</v>
       </c>
       <c r="D2665" t="s">
         <v>2667</v>
@@ -46636,7 +46636,7 @@
         <v>73</v>
       </c>
       <c r="C2666">
-        <v>5420</v>
+        <v>5410</v>
       </c>
       <c r="D2666" t="s">
         <v>2668</v>
@@ -46650,7 +46650,7 @@
         <v>74</v>
       </c>
       <c r="C2667">
-        <v>5530</v>
+        <v>5540</v>
       </c>
       <c r="D2667" t="s">
         <v>2669</v>
@@ -46664,7 +46664,7 @@
         <v>75</v>
       </c>
       <c r="C2668">
-        <v>5660</v>
+        <v>5670</v>
       </c>
       <c r="D2668" t="s">
         <v>2670</v>
@@ -46678,7 +46678,7 @@
         <v>76</v>
       </c>
       <c r="C2669">
-        <v>5790</v>
+        <v>5820</v>
       </c>
       <c r="D2669" t="s">
         <v>2671</v>
@@ -46692,7 +46692,7 @@
         <v>77</v>
       </c>
       <c r="C2670">
-        <v>5940</v>
+        <v>5970</v>
       </c>
       <c r="D2670" t="s">
         <v>2672</v>
@@ -46706,7 +46706,7 @@
         <v>78</v>
       </c>
       <c r="C2671">
-        <v>6070</v>
+        <v>6110</v>
       </c>
       <c r="D2671" t="s">
         <v>2673</v>
@@ -46720,7 +46720,7 @@
         <v>79</v>
       </c>
       <c r="C2672">
-        <v>6190</v>
+        <v>6240</v>
       </c>
       <c r="D2672" t="s">
         <v>2674</v>
@@ -46734,7 +46734,7 @@
         <v>80</v>
       </c>
       <c r="C2673">
-        <v>6280</v>
+        <v>6330</v>
       </c>
       <c r="D2673" t="s">
         <v>2675</v>
@@ -46748,7 +46748,7 @@
         <v>81</v>
       </c>
       <c r="C2674">
-        <v>6370</v>
+        <v>6420</v>
       </c>
       <c r="D2674" t="s">
         <v>2676</v>
@@ -46762,7 +46762,7 @@
         <v>82</v>
       </c>
       <c r="C2675">
-        <v>6470</v>
+        <v>6520</v>
       </c>
       <c r="D2675" t="s">
         <v>2677</v>
@@ -46776,7 +46776,7 @@
         <v>83</v>
       </c>
       <c r="C2676">
-        <v>6550</v>
+        <v>6600</v>
       </c>
       <c r="D2676" t="s">
         <v>2678</v>
@@ -46790,7 +46790,7 @@
         <v>84</v>
       </c>
       <c r="C2677">
-        <v>6650</v>
+        <v>6690</v>
       </c>
       <c r="D2677" t="s">
         <v>2679</v>
@@ -46846,7 +46846,7 @@
         <v>88</v>
       </c>
       <c r="C2681">
-        <v>6630</v>
+        <v>6640</v>
       </c>
       <c r="D2681" t="s">
         <v>2683</v>
@@ -46860,7 +46860,7 @@
         <v>89</v>
       </c>
       <c r="C2682">
-        <v>6500</v>
+        <v>6510</v>
       </c>
       <c r="D2682" t="s">
         <v>2684</v>
@@ -46888,7 +46888,7 @@
         <v>91</v>
       </c>
       <c r="C2684">
-        <v>6290</v>
+        <v>6280</v>
       </c>
       <c r="D2684" t="s">
         <v>2686</v>
@@ -46916,7 +46916,7 @@
         <v>93</v>
       </c>
       <c r="C2686">
-        <v>5900</v>
+        <v>5910</v>
       </c>
       <c r="D2686" t="s">
         <v>2688</v>
@@ -46972,7 +46972,7 @@
         <v>1</v>
       </c>
       <c r="C2690">
-        <v>5200</v>
+        <v>5420</v>
       </c>
       <c r="D2690" t="s">
         <v>2692</v>
@@ -46986,7 +46986,7 @@
         <v>2</v>
       </c>
       <c r="C2691">
-        <v>5170</v>
+        <v>5340</v>
       </c>
       <c r="D2691" t="s">
         <v>2693</v>
@@ -47000,7 +47000,7 @@
         <v>3</v>
       </c>
       <c r="C2692">
-        <v>5090</v>
+        <v>5270</v>
       </c>
       <c r="D2692" t="s">
         <v>2694</v>
@@ -47014,7 +47014,7 @@
         <v>4</v>
       </c>
       <c r="C2693">
-        <v>5010</v>
+        <v>5210</v>
       </c>
       <c r="D2693" t="s">
         <v>2695</v>
@@ -47028,7 +47028,7 @@
         <v>5</v>
       </c>
       <c r="C2694">
-        <v>4960</v>
+        <v>5150</v>
       </c>
       <c r="D2694" t="s">
         <v>2696</v>
@@ -47042,7 +47042,7 @@
         <v>6</v>
       </c>
       <c r="C2695">
-        <v>4920</v>
+        <v>5110</v>
       </c>
       <c r="D2695" t="s">
         <v>2697</v>
@@ -47056,7 +47056,7 @@
         <v>7</v>
       </c>
       <c r="C2696">
-        <v>4890</v>
+        <v>5070</v>
       </c>
       <c r="D2696" t="s">
         <v>2698</v>
@@ -47070,7 +47070,7 @@
         <v>8</v>
       </c>
       <c r="C2697">
-        <v>4860</v>
+        <v>5030</v>
       </c>
       <c r="D2697" t="s">
         <v>2699</v>
@@ -47084,7 +47084,7 @@
         <v>9</v>
       </c>
       <c r="C2698">
-        <v>4830</v>
+        <v>5000</v>
       </c>
       <c r="D2698" t="s">
         <v>2700</v>
@@ -47098,7 +47098,7 @@
         <v>10</v>
       </c>
       <c r="C2699">
-        <v>4810</v>
+        <v>4980</v>
       </c>
       <c r="D2699" t="s">
         <v>2701</v>
@@ -47112,7 +47112,7 @@
         <v>11</v>
       </c>
       <c r="C2700">
-        <v>4810</v>
+        <v>4960</v>
       </c>
       <c r="D2700" t="s">
         <v>2702</v>
@@ -47126,7 +47126,7 @@
         <v>12</v>
       </c>
       <c r="C2701">
-        <v>4810</v>
+        <v>4940</v>
       </c>
       <c r="D2701" t="s">
         <v>2703</v>
@@ -47140,7 +47140,7 @@
         <v>13</v>
       </c>
       <c r="C2702">
-        <v>4820</v>
+        <v>4930</v>
       </c>
       <c r="D2702" t="s">
         <v>2704</v>
@@ -47154,7 +47154,7 @@
         <v>14</v>
       </c>
       <c r="C2703">
-        <v>4830</v>
+        <v>4920</v>
       </c>
       <c r="D2703" t="s">
         <v>2705</v>
@@ -47168,7 +47168,7 @@
         <v>15</v>
       </c>
       <c r="C2704">
-        <v>4840</v>
+        <v>4920</v>
       </c>
       <c r="D2704" t="s">
         <v>2706</v>
@@ -47182,7 +47182,7 @@
         <v>16</v>
       </c>
       <c r="C2705">
-        <v>4850</v>
+        <v>4920</v>
       </c>
       <c r="D2705" t="s">
         <v>2707</v>
@@ -47196,7 +47196,7 @@
         <v>17</v>
       </c>
       <c r="C2706">
-        <v>4850</v>
+        <v>4920</v>
       </c>
       <c r="D2706" t="s">
         <v>2708</v>
@@ -47210,7 +47210,7 @@
         <v>18</v>
       </c>
       <c r="C2707">
-        <v>4850</v>
+        <v>4930</v>
       </c>
       <c r="D2707" t="s">
         <v>2709</v>
@@ -47224,7 +47224,7 @@
         <v>19</v>
       </c>
       <c r="C2708">
-        <v>4860</v>
+        <v>4940</v>
       </c>
       <c r="D2708" t="s">
         <v>2710</v>
@@ -47238,7 +47238,7 @@
         <v>20</v>
       </c>
       <c r="C2709">
-        <v>4870</v>
+        <v>4960</v>
       </c>
       <c r="D2709" t="s">
         <v>2711</v>
@@ -47252,7 +47252,7 @@
         <v>21</v>
       </c>
       <c r="C2710">
-        <v>4900</v>
+        <v>4980</v>
       </c>
       <c r="D2710" t="s">
         <v>2712</v>
@@ -47266,7 +47266,7 @@
         <v>22</v>
       </c>
       <c r="C2711">
-        <v>4940</v>
+        <v>5000</v>
       </c>
       <c r="D2711" t="s">
         <v>2713</v>
@@ -47280,7 +47280,7 @@
         <v>23</v>
       </c>
       <c r="C2712">
-        <v>4990</v>
+        <v>5040</v>
       </c>
       <c r="D2712" t="s">
         <v>2714</v>
@@ -47294,7 +47294,7 @@
         <v>24</v>
       </c>
       <c r="C2713">
-        <v>5050</v>
+        <v>5080</v>
       </c>
       <c r="D2713" t="s">
         <v>2715</v>
@@ -47322,7 +47322,7 @@
         <v>26</v>
       </c>
       <c r="C2715">
-        <v>5240</v>
+        <v>5170</v>
       </c>
       <c r="D2715" t="s">
         <v>2717</v>
@@ -47336,7 +47336,7 @@
         <v>27</v>
       </c>
       <c r="C2716">
-        <v>5300</v>
+        <v>5220</v>
       </c>
       <c r="D2716" t="s">
         <v>2718</v>
@@ -47350,7 +47350,7 @@
         <v>28</v>
       </c>
       <c r="C2717">
-        <v>5360</v>
+        <v>5270</v>
       </c>
       <c r="D2717" t="s">
         <v>2719</v>
@@ -47364,7 +47364,7 @@
         <v>29</v>
       </c>
       <c r="C2718">
-        <v>5410</v>
+        <v>5310</v>
       </c>
       <c r="D2718" t="s">
         <v>2720</v>
@@ -47378,7 +47378,7 @@
         <v>30</v>
       </c>
       <c r="C2719">
-        <v>5440</v>
+        <v>5350</v>
       </c>
       <c r="D2719" t="s">
         <v>2721</v>
@@ -47392,7 +47392,7 @@
         <v>31</v>
       </c>
       <c r="C2720">
-        <v>5450</v>
+        <v>5350</v>
       </c>
       <c r="D2720" t="s">
         <v>2722</v>
@@ -47406,7 +47406,7 @@
         <v>32</v>
       </c>
       <c r="C2721">
-        <v>5470</v>
+        <v>5340</v>
       </c>
       <c r="D2721" t="s">
         <v>2723</v>
@@ -47420,7 +47420,7 @@
         <v>33</v>
       </c>
       <c r="C2722">
-        <v>5500</v>
+        <v>5310</v>
       </c>
       <c r="D2722" t="s">
         <v>2724</v>
@@ -47434,7 +47434,7 @@
         <v>34</v>
       </c>
       <c r="C2723">
-        <v>5370</v>
+        <v>5250</v>
       </c>
       <c r="D2723" t="s">
         <v>2725</v>
@@ -47448,7 +47448,7 @@
         <v>35</v>
       </c>
       <c r="C2724">
-        <v>5310</v>
+        <v>5160</v>
       </c>
       <c r="D2724" t="s">
         <v>2726</v>
@@ -47462,7 +47462,7 @@
         <v>36</v>
       </c>
       <c r="C2725">
-        <v>5230</v>
+        <v>5040</v>
       </c>
       <c r="D2725" t="s">
         <v>2727</v>
@@ -47476,7 +47476,7 @@
         <v>37</v>
       </c>
       <c r="C2726">
-        <v>5130</v>
+        <v>4900</v>
       </c>
       <c r="D2726" t="s">
         <v>2728</v>
@@ -47490,7 +47490,7 @@
         <v>38</v>
       </c>
       <c r="C2727">
-        <v>5020</v>
+        <v>4770</v>
       </c>
       <c r="D2727" t="s">
         <v>2729</v>
@@ -47504,7 +47504,7 @@
         <v>39</v>
       </c>
       <c r="C2728">
-        <v>4900</v>
+        <v>4660</v>
       </c>
       <c r="D2728" t="s">
         <v>2730</v>
@@ -47518,7 +47518,7 @@
         <v>40</v>
       </c>
       <c r="C2729">
-        <v>4780</v>
+        <v>4570</v>
       </c>
       <c r="D2729" t="s">
         <v>2731</v>
@@ -47532,7 +47532,7 @@
         <v>41</v>
       </c>
       <c r="C2730">
-        <v>4660</v>
+        <v>4490</v>
       </c>
       <c r="D2730" t="s">
         <v>2732</v>
@@ -47546,7 +47546,7 @@
         <v>42</v>
       </c>
       <c r="C2731">
-        <v>4540</v>
+        <v>4400</v>
       </c>
       <c r="D2731" t="s">
         <v>2733</v>
@@ -47560,7 +47560,7 @@
         <v>43</v>
       </c>
       <c r="C2732">
-        <v>4420</v>
+        <v>4300</v>
       </c>
       <c r="D2732" t="s">
         <v>2734</v>
@@ -47574,7 +47574,7 @@
         <v>44</v>
       </c>
       <c r="C2733">
-        <v>4320</v>
+        <v>4200</v>
       </c>
       <c r="D2733" t="s">
         <v>2735</v>
@@ -47588,7 +47588,7 @@
         <v>45</v>
       </c>
       <c r="C2734">
-        <v>4200</v>
+        <v>4080</v>
       </c>
       <c r="D2734" t="s">
         <v>2736</v>
@@ -47602,7 +47602,7 @@
         <v>46</v>
       </c>
       <c r="C2735">
-        <v>4130</v>
+        <v>4000</v>
       </c>
       <c r="D2735" t="s">
         <v>2737</v>
@@ -47616,7 +47616,7 @@
         <v>47</v>
       </c>
       <c r="C2736">
-        <v>4080</v>
+        <v>3950</v>
       </c>
       <c r="D2736" t="s">
         <v>2738</v>
@@ -47630,7 +47630,7 @@
         <v>48</v>
       </c>
       <c r="C2737">
-        <v>4040</v>
+        <v>3940</v>
       </c>
       <c r="D2737" t="s">
         <v>2739</v>
@@ -47644,7 +47644,7 @@
         <v>49</v>
       </c>
       <c r="C2738">
-        <v>4020</v>
+        <v>3960</v>
       </c>
       <c r="D2738" t="s">
         <v>2740</v>
@@ -47658,7 +47658,7 @@
         <v>50</v>
       </c>
       <c r="C2739">
-        <v>4000</v>
+        <v>3970</v>
       </c>
       <c r="D2739" t="s">
         <v>2741</v>
@@ -47700,7 +47700,7 @@
         <v>53</v>
       </c>
       <c r="C2742">
-        <v>3980</v>
+        <v>4000</v>
       </c>
       <c r="D2742" t="s">
         <v>2744</v>
@@ -47714,7 +47714,7 @@
         <v>54</v>
       </c>
       <c r="C2743">
-        <v>3990</v>
+        <v>4000</v>
       </c>
       <c r="D2743" t="s">
         <v>2745</v>
@@ -47742,7 +47742,7 @@
         <v>56</v>
       </c>
       <c r="C2745">
-        <v>4010</v>
+        <v>3990</v>
       </c>
       <c r="D2745" t="s">
         <v>2747</v>
@@ -47756,7 +47756,7 @@
         <v>57</v>
       </c>
       <c r="C2746">
-        <v>4030</v>
+        <v>3980</v>
       </c>
       <c r="D2746" t="s">
         <v>2748</v>
@@ -47770,7 +47770,7 @@
         <v>58</v>
       </c>
       <c r="C2747">
-        <v>4050</v>
+        <v>3980</v>
       </c>
       <c r="D2747" t="s">
         <v>2749</v>
@@ -47784,7 +47784,7 @@
         <v>59</v>
       </c>
       <c r="C2748">
-        <v>4080</v>
+        <v>4000</v>
       </c>
       <c r="D2748" t="s">
         <v>2750</v>
@@ -47798,7 +47798,7 @@
         <v>60</v>
       </c>
       <c r="C2749">
-        <v>4120</v>
+        <v>4030</v>
       </c>
       <c r="D2749" t="s">
         <v>2751</v>
@@ -47812,7 +47812,7 @@
         <v>61</v>
       </c>
       <c r="C2750">
-        <v>4160</v>
+        <v>4070</v>
       </c>
       <c r="D2750" t="s">
         <v>2752</v>
@@ -47826,7 +47826,7 @@
         <v>62</v>
       </c>
       <c r="C2751">
-        <v>4210</v>
+        <v>4120</v>
       </c>
       <c r="D2751" t="s">
         <v>2753</v>
@@ -47840,7 +47840,7 @@
         <v>63</v>
       </c>
       <c r="C2752">
-        <v>4270</v>
+        <v>4170</v>
       </c>
       <c r="D2752" t="s">
         <v>2754</v>
@@ -47854,7 +47854,7 @@
         <v>64</v>
       </c>
       <c r="C2753">
-        <v>4330</v>
+        <v>4220</v>
       </c>
       <c r="D2753" t="s">
         <v>2755</v>
@@ -47868,7 +47868,7 @@
         <v>65</v>
       </c>
       <c r="C2754">
-        <v>4390</v>
+        <v>4280</v>
       </c>
       <c r="D2754" t="s">
         <v>2756</v>
@@ -47882,7 +47882,7 @@
         <v>66</v>
       </c>
       <c r="C2755">
-        <v>4470</v>
+        <v>4350</v>
       </c>
       <c r="D2755" t="s">
         <v>2757</v>
@@ -47896,7 +47896,7 @@
         <v>67</v>
       </c>
       <c r="C2756">
-        <v>4550</v>
+        <v>4430</v>
       </c>
       <c r="D2756" t="s">
         <v>2758</v>
@@ -47910,7 +47910,7 @@
         <v>68</v>
       </c>
       <c r="C2757">
-        <v>4640</v>
+        <v>4530</v>
       </c>
       <c r="D2757" t="s">
         <v>2759</v>
@@ -47924,7 +47924,7 @@
         <v>69</v>
       </c>
       <c r="C2758">
-        <v>4740</v>
+        <v>4640</v>
       </c>
       <c r="D2758" t="s">
         <v>2760</v>
@@ -47938,7 +47938,7 @@
         <v>70</v>
       </c>
       <c r="C2759">
-        <v>4840</v>
+        <v>4770</v>
       </c>
       <c r="D2759" t="s">
         <v>2761</v>
@@ -47952,7 +47952,7 @@
         <v>71</v>
       </c>
       <c r="C2760">
-        <v>4950</v>
+        <v>4890</v>
       </c>
       <c r="D2760" t="s">
         <v>2762</v>
@@ -47966,7 +47966,7 @@
         <v>72</v>
       </c>
       <c r="C2761">
-        <v>5060</v>
+        <v>5030</v>
       </c>
       <c r="D2761" t="s">
         <v>2763</v>
@@ -47980,7 +47980,7 @@
         <v>73</v>
       </c>
       <c r="C2762">
-        <v>5180</v>
+        <v>5170</v>
       </c>
       <c r="D2762" t="s">
         <v>2764</v>
@@ -47994,7 +47994,7 @@
         <v>74</v>
       </c>
       <c r="C2763">
-        <v>5320</v>
+        <v>5310</v>
       </c>
       <c r="D2763" t="s">
         <v>2765</v>
@@ -48008,7 +48008,7 @@
         <v>75</v>
       </c>
       <c r="C2764">
-        <v>5470</v>
+        <v>5460</v>
       </c>
       <c r="D2764" t="s">
         <v>2766</v>
@@ -48022,7 +48022,7 @@
         <v>76</v>
       </c>
       <c r="C2765">
-        <v>5630</v>
+        <v>5620</v>
       </c>
       <c r="D2765" t="s">
         <v>2767</v>
@@ -48036,7 +48036,7 @@
         <v>77</v>
       </c>
       <c r="C2766">
-        <v>5800</v>
+        <v>5780</v>
       </c>
       <c r="D2766" t="s">
         <v>2768</v>
@@ -48050,7 +48050,7 @@
         <v>78</v>
       </c>
       <c r="C2767">
-        <v>5950</v>
+        <v>5920</v>
       </c>
       <c r="D2767" t="s">
         <v>2769</v>
@@ -48064,7 +48064,7 @@
         <v>79</v>
       </c>
       <c r="C2768">
-        <v>6090</v>
+        <v>6030</v>
       </c>
       <c r="D2768" t="s">
         <v>2770</v>
@@ -48078,7 +48078,7 @@
         <v>80</v>
       </c>
       <c r="C2769">
-        <v>6200</v>
+        <v>6130</v>
       </c>
       <c r="D2769" t="s">
         <v>2771</v>
@@ -48092,7 +48092,7 @@
         <v>81</v>
       </c>
       <c r="C2770">
-        <v>6300</v>
+        <v>6200</v>
       </c>
       <c r="D2770" t="s">
         <v>2772</v>
@@ -48106,7 +48106,7 @@
         <v>82</v>
       </c>
       <c r="C2771">
-        <v>6410</v>
+        <v>6270</v>
       </c>
       <c r="D2771" t="s">
         <v>2773</v>
@@ -48120,7 +48120,7 @@
         <v>83</v>
       </c>
       <c r="C2772">
-        <v>6510</v>
+        <v>6350</v>
       </c>
       <c r="D2772" t="s">
         <v>2774</v>
@@ -48134,7 +48134,7 @@
         <v>84</v>
       </c>
       <c r="C2773">
-        <v>6620</v>
+        <v>6430</v>
       </c>
       <c r="D2773" t="s">
         <v>2775</v>
@@ -48148,7 +48148,7 @@
         <v>85</v>
       </c>
       <c r="C2774">
-        <v>6660</v>
+        <v>6510</v>
       </c>
       <c r="D2774" t="s">
         <v>2776</v>
@@ -48162,7 +48162,7 @@
         <v>86</v>
       </c>
       <c r="C2775">
-        <v>6660</v>
+        <v>6550</v>
       </c>
       <c r="D2775" t="s">
         <v>2777</v>
@@ -48176,7 +48176,7 @@
         <v>87</v>
       </c>
       <c r="C2776">
-        <v>6640</v>
+        <v>6540</v>
       </c>
       <c r="D2776" t="s">
         <v>2778</v>
@@ -48190,7 +48190,7 @@
         <v>88</v>
       </c>
       <c r="C2777">
-        <v>6550</v>
+        <v>6490</v>
       </c>
       <c r="D2777" t="s">
         <v>2779</v>
@@ -48232,7 +48232,7 @@
         <v>91</v>
       </c>
       <c r="C2780">
-        <v>6130</v>
+        <v>6140</v>
       </c>
       <c r="D2780" t="s">
         <v>2782</v>
@@ -48246,7 +48246,7 @@
         <v>92</v>
       </c>
       <c r="C2781">
-        <v>5970</v>
+        <v>5980</v>
       </c>
       <c r="D2781" t="s">
         <v>2783</v>
@@ -48260,7 +48260,7 @@
         <v>93</v>
       </c>
       <c r="C2782">
-        <v>5750</v>
+        <v>5830</v>
       </c>
       <c r="D2782" t="s">
         <v>2784</v>
@@ -48274,7 +48274,7 @@
         <v>94</v>
       </c>
       <c r="C2783">
-        <v>5570</v>
+        <v>5680</v>
       </c>
       <c r="D2783" t="s">
         <v>2785</v>
@@ -48288,7 +48288,7 @@
         <v>95</v>
       </c>
       <c r="C2784">
-        <v>5490</v>
+        <v>5560</v>
       </c>
       <c r="D2784" t="s">
         <v>2786</v>
@@ -48302,7 +48302,7 @@
         <v>96</v>
       </c>
       <c r="C2785">
-        <v>5380</v>
+        <v>5450</v>
       </c>
       <c r="D2785" t="s">
         <v>2787</v>

--- a/Market Fundamentals/Transelectrica_data/Cons_Prod_final/Weekly_Consumption_2026.xlsx
+++ b/Market Fundamentals/Transelectrica_data/Cons_Prod_final/Weekly_Consumption_2026.xlsx
@@ -45628,7 +45628,7 @@
         <v>1</v>
       </c>
       <c r="C2594">
-        <v>5470</v>
+        <v>5500</v>
       </c>
       <c r="D2594" t="s">
         <v>2596</v>
@@ -45642,7 +45642,7 @@
         <v>2</v>
       </c>
       <c r="C2595">
-        <v>5440</v>
+        <v>5430</v>
       </c>
       <c r="D2595" t="s">
         <v>2597</v>
@@ -45670,7 +45670,7 @@
         <v>4</v>
       </c>
       <c r="C2597">
-        <v>5290</v>
+        <v>5300</v>
       </c>
       <c r="D2597" t="s">
         <v>2599</v>
@@ -45684,7 +45684,7 @@
         <v>5</v>
       </c>
       <c r="C2598">
-        <v>5230</v>
+        <v>5250</v>
       </c>
       <c r="D2598" t="s">
         <v>2600</v>
@@ -45712,7 +45712,7 @@
         <v>7</v>
       </c>
       <c r="C2600">
-        <v>5130</v>
+        <v>5120</v>
       </c>
       <c r="D2600" t="s">
         <v>2602</v>
@@ -45726,7 +45726,7 @@
         <v>8</v>
       </c>
       <c r="C2601">
-        <v>5080</v>
+        <v>5060</v>
       </c>
       <c r="D2601" t="s">
         <v>2603</v>
@@ -45754,7 +45754,7 @@
         <v>10</v>
       </c>
       <c r="C2603">
-        <v>4980</v>
+        <v>4990</v>
       </c>
       <c r="D2603" t="s">
         <v>2605</v>
@@ -45768,7 +45768,7 @@
         <v>11</v>
       </c>
       <c r="C2604">
-        <v>4950</v>
+        <v>4960</v>
       </c>
       <c r="D2604" t="s">
         <v>2606</v>
@@ -45782,7 +45782,7 @@
         <v>12</v>
       </c>
       <c r="C2605">
-        <v>4930</v>
+        <v>4940</v>
       </c>
       <c r="D2605" t="s">
         <v>2607</v>
@@ -45796,7 +45796,7 @@
         <v>13</v>
       </c>
       <c r="C2606">
-        <v>4900</v>
+        <v>4930</v>
       </c>
       <c r="D2606" t="s">
         <v>2608</v>
@@ -45810,7 +45810,7 @@
         <v>14</v>
       </c>
       <c r="C2607">
-        <v>4900</v>
+        <v>4920</v>
       </c>
       <c r="D2607" t="s">
         <v>2609</v>
@@ -45824,7 +45824,7 @@
         <v>15</v>
       </c>
       <c r="C2608">
-        <v>4900</v>
+        <v>4920</v>
       </c>
       <c r="D2608" t="s">
         <v>2610</v>
@@ -45838,7 +45838,7 @@
         <v>16</v>
       </c>
       <c r="C2609">
-        <v>4900</v>
+        <v>4930</v>
       </c>
       <c r="D2609" t="s">
         <v>2611</v>
@@ -45852,7 +45852,7 @@
         <v>17</v>
       </c>
       <c r="C2610">
-        <v>4910</v>
+        <v>4940</v>
       </c>
       <c r="D2610" t="s">
         <v>2612</v>
@@ -45866,7 +45866,7 @@
         <v>18</v>
       </c>
       <c r="C2611">
-        <v>4920</v>
+        <v>4950</v>
       </c>
       <c r="D2611" t="s">
         <v>2613</v>
@@ -45880,7 +45880,7 @@
         <v>19</v>
       </c>
       <c r="C2612">
-        <v>4930</v>
+        <v>4950</v>
       </c>
       <c r="D2612" t="s">
         <v>2614</v>
@@ -45894,7 +45894,7 @@
         <v>20</v>
       </c>
       <c r="C2613">
-        <v>4940</v>
+        <v>4970</v>
       </c>
       <c r="D2613" t="s">
         <v>2615</v>
@@ -45908,7 +45908,7 @@
         <v>21</v>
       </c>
       <c r="C2614">
-        <v>4970</v>
+        <v>4990</v>
       </c>
       <c r="D2614" t="s">
         <v>2616</v>
@@ -45922,7 +45922,7 @@
         <v>22</v>
       </c>
       <c r="C2615">
-        <v>5000</v>
+        <v>5030</v>
       </c>
       <c r="D2615" t="s">
         <v>2617</v>
@@ -45936,7 +45936,7 @@
         <v>23</v>
       </c>
       <c r="C2616">
-        <v>5060</v>
+        <v>5080</v>
       </c>
       <c r="D2616" t="s">
         <v>2618</v>
@@ -45950,7 +45950,7 @@
         <v>24</v>
       </c>
       <c r="C2617">
-        <v>5130</v>
+        <v>5120</v>
       </c>
       <c r="D2617" t="s">
         <v>2619</v>
@@ -45964,7 +45964,7 @@
         <v>25</v>
       </c>
       <c r="C2618">
-        <v>5210</v>
+        <v>5190</v>
       </c>
       <c r="D2618" t="s">
         <v>2620</v>
@@ -45978,7 +45978,7 @@
         <v>26</v>
       </c>
       <c r="C2619">
-        <v>5290</v>
+        <v>5250</v>
       </c>
       <c r="D2619" t="s">
         <v>2621</v>
@@ -45992,7 +45992,7 @@
         <v>27</v>
       </c>
       <c r="C2620">
-        <v>5380</v>
+        <v>5320</v>
       </c>
       <c r="D2620" t="s">
         <v>2622</v>
@@ -46006,7 +46006,7 @@
         <v>28</v>
       </c>
       <c r="C2621">
-        <v>5460</v>
+        <v>5380</v>
       </c>
       <c r="D2621" t="s">
         <v>2623</v>
@@ -46020,7 +46020,7 @@
         <v>29</v>
       </c>
       <c r="C2622">
-        <v>5530</v>
+        <v>5440</v>
       </c>
       <c r="D2622" t="s">
         <v>2624</v>
@@ -46034,7 +46034,7 @@
         <v>30</v>
       </c>
       <c r="C2623">
-        <v>5590</v>
+        <v>5480</v>
       </c>
       <c r="D2623" t="s">
         <v>2625</v>
@@ -46048,7 +46048,7 @@
         <v>31</v>
       </c>
       <c r="C2624">
-        <v>5630</v>
+        <v>5500</v>
       </c>
       <c r="D2624" t="s">
         <v>2626</v>
@@ -46062,7 +46062,7 @@
         <v>32</v>
       </c>
       <c r="C2625">
-        <v>5650</v>
+        <v>5510</v>
       </c>
       <c r="D2625" t="s">
         <v>2627</v>
@@ -46076,7 +46076,7 @@
         <v>33</v>
       </c>
       <c r="C2626">
-        <v>5640</v>
+        <v>5510</v>
       </c>
       <c r="D2626" t="s">
         <v>2628</v>
@@ -46090,7 +46090,7 @@
         <v>34</v>
       </c>
       <c r="C2627">
-        <v>5610</v>
+        <v>5480</v>
       </c>
       <c r="D2627" t="s">
         <v>2629</v>
@@ -46104,7 +46104,7 @@
         <v>35</v>
       </c>
       <c r="C2628">
-        <v>5560</v>
+        <v>5420</v>
       </c>
       <c r="D2628" t="s">
         <v>2630</v>
@@ -46118,7 +46118,7 @@
         <v>36</v>
       </c>
       <c r="C2629">
-        <v>5480</v>
+        <v>5350</v>
       </c>
       <c r="D2629" t="s">
         <v>2631</v>
@@ -46132,7 +46132,7 @@
         <v>37</v>
       </c>
       <c r="C2630">
-        <v>5380</v>
+        <v>5260</v>
       </c>
       <c r="D2630" t="s">
         <v>2632</v>
@@ -46146,7 +46146,7 @@
         <v>38</v>
       </c>
       <c r="C2631">
-        <v>5270</v>
+        <v>5160</v>
       </c>
       <c r="D2631" t="s">
         <v>2633</v>
@@ -46160,7 +46160,7 @@
         <v>39</v>
       </c>
       <c r="C2632">
-        <v>5150</v>
+        <v>5040</v>
       </c>
       <c r="D2632" t="s">
         <v>2634</v>
@@ -46174,7 +46174,7 @@
         <v>40</v>
       </c>
       <c r="C2633">
-        <v>5020</v>
+        <v>4910</v>
       </c>
       <c r="D2633" t="s">
         <v>2635</v>
@@ -46188,7 +46188,7 @@
         <v>41</v>
       </c>
       <c r="C2634">
-        <v>4890</v>
+        <v>4780</v>
       </c>
       <c r="D2634" t="s">
         <v>2636</v>
@@ -46202,7 +46202,7 @@
         <v>42</v>
       </c>
       <c r="C2635">
-        <v>4770</v>
+        <v>4660</v>
       </c>
       <c r="D2635" t="s">
         <v>2637</v>
@@ -46216,7 +46216,7 @@
         <v>43</v>
       </c>
       <c r="C2636">
-        <v>4660</v>
+        <v>4540</v>
       </c>
       <c r="D2636" t="s">
         <v>2638</v>
@@ -46230,7 +46230,7 @@
         <v>44</v>
       </c>
       <c r="C2637">
-        <v>4570</v>
+        <v>4440</v>
       </c>
       <c r="D2637" t="s">
         <v>2639</v>
@@ -46244,7 +46244,7 @@
         <v>45</v>
       </c>
       <c r="C2638">
-        <v>4480</v>
+        <v>4350</v>
       </c>
       <c r="D2638" t="s">
         <v>2640</v>
@@ -46258,7 +46258,7 @@
         <v>46</v>
       </c>
       <c r="C2639">
-        <v>4420</v>
+        <v>4270</v>
       </c>
       <c r="D2639" t="s">
         <v>2641</v>
@@ -46272,7 +46272,7 @@
         <v>47</v>
       </c>
       <c r="C2640">
-        <v>4370</v>
+        <v>4220</v>
       </c>
       <c r="D2640" t="s">
         <v>2642</v>
@@ -46286,7 +46286,7 @@
         <v>48</v>
       </c>
       <c r="C2641">
-        <v>4330</v>
+        <v>4170</v>
       </c>
       <c r="D2641" t="s">
         <v>2643</v>
@@ -46300,7 +46300,7 @@
         <v>49</v>
       </c>
       <c r="C2642">
-        <v>4310</v>
+        <v>4150</v>
       </c>
       <c r="D2642" t="s">
         <v>2644</v>
@@ -46314,7 +46314,7 @@
         <v>50</v>
       </c>
       <c r="C2643">
-        <v>4290</v>
+        <v>4130</v>
       </c>
       <c r="D2643" t="s">
         <v>2645</v>
@@ -46328,7 +46328,7 @@
         <v>51</v>
       </c>
       <c r="C2644">
-        <v>4280</v>
+        <v>4120</v>
       </c>
       <c r="D2644" t="s">
         <v>2646</v>
@@ -46342,7 +46342,7 @@
         <v>52</v>
       </c>
       <c r="C2645">
-        <v>4280</v>
+        <v>4120</v>
       </c>
       <c r="D2645" t="s">
         <v>2647</v>
@@ -46356,7 +46356,7 @@
         <v>53</v>
       </c>
       <c r="C2646">
-        <v>4280</v>
+        <v>4120</v>
       </c>
       <c r="D2646" t="s">
         <v>2648</v>
@@ -46370,7 +46370,7 @@
         <v>54</v>
       </c>
       <c r="C2647">
-        <v>4290</v>
+        <v>4140</v>
       </c>
       <c r="D2647" t="s">
         <v>2649</v>
@@ -46384,7 +46384,7 @@
         <v>55</v>
       </c>
       <c r="C2648">
-        <v>4310</v>
+        <v>4170</v>
       </c>
       <c r="D2648" t="s">
         <v>2650</v>
@@ -46398,7 +46398,7 @@
         <v>56</v>
       </c>
       <c r="C2649">
-        <v>4330</v>
+        <v>4200</v>
       </c>
       <c r="D2649" t="s">
         <v>2651</v>
@@ -46412,7 +46412,7 @@
         <v>57</v>
       </c>
       <c r="C2650">
-        <v>4350</v>
+        <v>4230</v>
       </c>
       <c r="D2650" t="s">
         <v>2652</v>
@@ -46426,7 +46426,7 @@
         <v>58</v>
       </c>
       <c r="C2651">
-        <v>4370</v>
+        <v>4270</v>
       </c>
       <c r="D2651" t="s">
         <v>2653</v>
@@ -46440,7 +46440,7 @@
         <v>59</v>
       </c>
       <c r="C2652">
-        <v>4400</v>
+        <v>4310</v>
       </c>
       <c r="D2652" t="s">
         <v>2654</v>
@@ -46454,7 +46454,7 @@
         <v>60</v>
       </c>
       <c r="C2653">
-        <v>4420</v>
+        <v>4350</v>
       </c>
       <c r="D2653" t="s">
         <v>2655</v>
@@ -46468,7 +46468,7 @@
         <v>61</v>
       </c>
       <c r="C2654">
-        <v>4450</v>
+        <v>4380</v>
       </c>
       <c r="D2654" t="s">
         <v>2656</v>
@@ -46482,7 +46482,7 @@
         <v>62</v>
       </c>
       <c r="C2655">
-        <v>4480</v>
+        <v>4430</v>
       </c>
       <c r="D2655" t="s">
         <v>2657</v>
@@ -46496,7 +46496,7 @@
         <v>63</v>
       </c>
       <c r="C2656">
-        <v>4510</v>
+        <v>4470</v>
       </c>
       <c r="D2656" t="s">
         <v>2658</v>
@@ -46510,7 +46510,7 @@
         <v>64</v>
       </c>
       <c r="C2657">
-        <v>4560</v>
+        <v>4520</v>
       </c>
       <c r="D2657" t="s">
         <v>2659</v>
@@ -46524,7 +46524,7 @@
         <v>65</v>
       </c>
       <c r="C2658">
-        <v>4610</v>
+        <v>4590</v>
       </c>
       <c r="D2658" t="s">
         <v>2660</v>
@@ -46552,7 +46552,7 @@
         <v>67</v>
       </c>
       <c r="C2660">
-        <v>4760</v>
+        <v>4780</v>
       </c>
       <c r="D2660" t="s">
         <v>2662</v>
@@ -46566,7 +46566,7 @@
         <v>68</v>
       </c>
       <c r="C2661">
-        <v>4860</v>
+        <v>4900</v>
       </c>
       <c r="D2661" t="s">
         <v>2663</v>
@@ -46580,7 +46580,7 @@
         <v>69</v>
       </c>
       <c r="C2662">
-        <v>4960</v>
+        <v>5000</v>
       </c>
       <c r="D2662" t="s">
         <v>2664</v>
@@ -46594,7 +46594,7 @@
         <v>70</v>
       </c>
       <c r="C2663">
-        <v>5070</v>
+        <v>5130</v>
       </c>
       <c r="D2663" t="s">
         <v>2665</v>
@@ -46608,7 +46608,7 @@
         <v>71</v>
       </c>
       <c r="C2664">
-        <v>5180</v>
+        <v>5250</v>
       </c>
       <c r="D2664" t="s">
         <v>2666</v>
@@ -46622,7 +46622,7 @@
         <v>72</v>
       </c>
       <c r="C2665">
-        <v>5290</v>
+        <v>5370</v>
       </c>
       <c r="D2665" t="s">
         <v>2667</v>
@@ -46636,7 +46636,7 @@
         <v>73</v>
       </c>
       <c r="C2666">
-        <v>5410</v>
+        <v>5500</v>
       </c>
       <c r="D2666" t="s">
         <v>2668</v>
@@ -46650,7 +46650,7 @@
         <v>74</v>
       </c>
       <c r="C2667">
-        <v>5540</v>
+        <v>5620</v>
       </c>
       <c r="D2667" t="s">
         <v>2669</v>
@@ -46664,7 +46664,7 @@
         <v>75</v>
       </c>
       <c r="C2668">
-        <v>5670</v>
+        <v>5750</v>
       </c>
       <c r="D2668" t="s">
         <v>2670</v>
@@ -46678,7 +46678,7 @@
         <v>76</v>
       </c>
       <c r="C2669">
-        <v>5820</v>
+        <v>5880</v>
       </c>
       <c r="D2669" t="s">
         <v>2671</v>
@@ -46692,7 +46692,7 @@
         <v>77</v>
       </c>
       <c r="C2670">
-        <v>5970</v>
+        <v>6020</v>
       </c>
       <c r="D2670" t="s">
         <v>2672</v>
@@ -46706,7 +46706,7 @@
         <v>78</v>
       </c>
       <c r="C2671">
-        <v>6110</v>
+        <v>6150</v>
       </c>
       <c r="D2671" t="s">
         <v>2673</v>
@@ -46720,7 +46720,7 @@
         <v>79</v>
       </c>
       <c r="C2672">
-        <v>6240</v>
+        <v>6270</v>
       </c>
       <c r="D2672" t="s">
         <v>2674</v>
@@ -46734,7 +46734,7 @@
         <v>80</v>
       </c>
       <c r="C2673">
-        <v>6330</v>
+        <v>6390</v>
       </c>
       <c r="D2673" t="s">
         <v>2675</v>
@@ -46748,7 +46748,7 @@
         <v>81</v>
       </c>
       <c r="C2674">
-        <v>6420</v>
+        <v>6480</v>
       </c>
       <c r="D2674" t="s">
         <v>2676</v>
@@ -46762,7 +46762,7 @@
         <v>82</v>
       </c>
       <c r="C2675">
-        <v>6520</v>
+        <v>6570</v>
       </c>
       <c r="D2675" t="s">
         <v>2677</v>
@@ -46776,7 +46776,7 @@
         <v>83</v>
       </c>
       <c r="C2676">
-        <v>6600</v>
+        <v>6640</v>
       </c>
       <c r="D2676" t="s">
         <v>2678</v>
@@ -46790,7 +46790,7 @@
         <v>84</v>
       </c>
       <c r="C2677">
-        <v>6690</v>
+        <v>6720</v>
       </c>
       <c r="D2677" t="s">
         <v>2679</v>
@@ -46804,7 +46804,7 @@
         <v>85</v>
       </c>
       <c r="C2678">
-        <v>6700</v>
+        <v>6740</v>
       </c>
       <c r="D2678" t="s">
         <v>2680</v>
@@ -46818,7 +46818,7 @@
         <v>86</v>
       </c>
       <c r="C2679">
-        <v>6700</v>
+        <v>6730</v>
       </c>
       <c r="D2679" t="s">
         <v>2681</v>
@@ -46846,7 +46846,7 @@
         <v>88</v>
       </c>
       <c r="C2681">
-        <v>6640</v>
+        <v>6650</v>
       </c>
       <c r="D2681" t="s">
         <v>2683</v>
@@ -46860,7 +46860,7 @@
         <v>89</v>
       </c>
       <c r="C2682">
-        <v>6510</v>
+        <v>6550</v>
       </c>
       <c r="D2682" t="s">
         <v>2684</v>
@@ -46874,7 +46874,7 @@
         <v>90</v>
       </c>
       <c r="C2683">
-        <v>6420</v>
+        <v>6450</v>
       </c>
       <c r="D2683" t="s">
         <v>2685</v>
@@ -46888,7 +46888,7 @@
         <v>91</v>
       </c>
       <c r="C2684">
-        <v>6280</v>
+        <v>6300</v>
       </c>
       <c r="D2684" t="s">
         <v>2686</v>
@@ -46902,7 +46902,7 @@
         <v>92</v>
       </c>
       <c r="C2685">
-        <v>6130</v>
+        <v>6120</v>
       </c>
       <c r="D2685" t="s">
         <v>2687</v>
@@ -46916,7 +46916,7 @@
         <v>93</v>
       </c>
       <c r="C2686">
-        <v>5910</v>
+        <v>5980</v>
       </c>
       <c r="D2686" t="s">
         <v>2688</v>
@@ -46930,7 +46930,7 @@
         <v>94</v>
       </c>
       <c r="C2687">
-        <v>5750</v>
+        <v>5820</v>
       </c>
       <c r="D2687" t="s">
         <v>2689</v>
@@ -46944,7 +46944,7 @@
         <v>95</v>
       </c>
       <c r="C2688">
-        <v>5660</v>
+        <v>5680</v>
       </c>
       <c r="D2688" t="s">
         <v>2690</v>
@@ -46958,7 +46958,7 @@
         <v>96</v>
       </c>
       <c r="C2689">
-        <v>5550</v>
+        <v>5520</v>
       </c>
       <c r="D2689" t="s">
         <v>2691</v>
@@ -46972,7 +46972,7 @@
         <v>1</v>
       </c>
       <c r="C2690">
-        <v>5420</v>
+        <v>5400</v>
       </c>
       <c r="D2690" t="s">
         <v>2692</v>
@@ -46986,7 +46986,7 @@
         <v>2</v>
       </c>
       <c r="C2691">
-        <v>5340</v>
+        <v>5360</v>
       </c>
       <c r="D2691" t="s">
         <v>2693</v>
@@ -47000,7 +47000,7 @@
         <v>3</v>
       </c>
       <c r="C2692">
-        <v>5270</v>
+        <v>5290</v>
       </c>
       <c r="D2692" t="s">
         <v>2694</v>
@@ -47014,7 +47014,7 @@
         <v>4</v>
       </c>
       <c r="C2693">
-        <v>5210</v>
+        <v>5230</v>
       </c>
       <c r="D2693" t="s">
         <v>2695</v>
@@ -47028,7 +47028,7 @@
         <v>5</v>
       </c>
       <c r="C2694">
-        <v>5150</v>
+        <v>5180</v>
       </c>
       <c r="D2694" t="s">
         <v>2696</v>
@@ -47042,7 +47042,7 @@
         <v>6</v>
       </c>
       <c r="C2695">
-        <v>5110</v>
+        <v>5130</v>
       </c>
       <c r="D2695" t="s">
         <v>2697</v>
@@ -47056,7 +47056,7 @@
         <v>7</v>
       </c>
       <c r="C2696">
-        <v>5070</v>
+        <v>5080</v>
       </c>
       <c r="D2696" t="s">
         <v>2698</v>
@@ -47084,7 +47084,7 @@
         <v>9</v>
       </c>
       <c r="C2698">
-        <v>5000</v>
+        <v>4980</v>
       </c>
       <c r="D2698" t="s">
         <v>2700</v>
@@ -47098,7 +47098,7 @@
         <v>10</v>
       </c>
       <c r="C2699">
-        <v>4980</v>
+        <v>4940</v>
       </c>
       <c r="D2699" t="s">
         <v>2701</v>
@@ -47112,7 +47112,7 @@
         <v>11</v>
       </c>
       <c r="C2700">
-        <v>4960</v>
+        <v>4920</v>
       </c>
       <c r="D2700" t="s">
         <v>2702</v>
@@ -47126,7 +47126,7 @@
         <v>12</v>
       </c>
       <c r="C2701">
-        <v>4940</v>
+        <v>4900</v>
       </c>
       <c r="D2701" t="s">
         <v>2703</v>
@@ -47140,7 +47140,7 @@
         <v>13</v>
       </c>
       <c r="C2702">
-        <v>4930</v>
+        <v>4900</v>
       </c>
       <c r="D2702" t="s">
         <v>2704</v>
@@ -47154,7 +47154,7 @@
         <v>14</v>
       </c>
       <c r="C2703">
-        <v>4920</v>
+        <v>4900</v>
       </c>
       <c r="D2703" t="s">
         <v>2705</v>
@@ -47168,7 +47168,7 @@
         <v>15</v>
       </c>
       <c r="C2704">
-        <v>4920</v>
+        <v>4900</v>
       </c>
       <c r="D2704" t="s">
         <v>2706</v>
@@ -47182,7 +47182,7 @@
         <v>16</v>
       </c>
       <c r="C2705">
-        <v>4920</v>
+        <v>4900</v>
       </c>
       <c r="D2705" t="s">
         <v>2707</v>
@@ -47196,7 +47196,7 @@
         <v>17</v>
       </c>
       <c r="C2706">
-        <v>4920</v>
+        <v>4900</v>
       </c>
       <c r="D2706" t="s">
         <v>2708</v>
@@ -47210,7 +47210,7 @@
         <v>18</v>
       </c>
       <c r="C2707">
-        <v>4930</v>
+        <v>4900</v>
       </c>
       <c r="D2707" t="s">
         <v>2709</v>
@@ -47224,7 +47224,7 @@
         <v>19</v>
       </c>
       <c r="C2708">
-        <v>4940</v>
+        <v>4910</v>
       </c>
       <c r="D2708" t="s">
         <v>2710</v>
@@ -47238,7 +47238,7 @@
         <v>20</v>
       </c>
       <c r="C2709">
-        <v>4960</v>
+        <v>4920</v>
       </c>
       <c r="D2709" t="s">
         <v>2711</v>
@@ -47252,7 +47252,7 @@
         <v>21</v>
       </c>
       <c r="C2710">
-        <v>4980</v>
+        <v>4940</v>
       </c>
       <c r="D2710" t="s">
         <v>2712</v>
@@ -47266,7 +47266,7 @@
         <v>22</v>
       </c>
       <c r="C2711">
-        <v>5000</v>
+        <v>4970</v>
       </c>
       <c r="D2711" t="s">
         <v>2713</v>
@@ -47280,7 +47280,7 @@
         <v>23</v>
       </c>
       <c r="C2712">
-        <v>5040</v>
+        <v>5020</v>
       </c>
       <c r="D2712" t="s">
         <v>2714</v>
@@ -47294,7 +47294,7 @@
         <v>24</v>
       </c>
       <c r="C2713">
-        <v>5080</v>
+        <v>5070</v>
       </c>
       <c r="D2713" t="s">
         <v>2715</v>
@@ -47308,7 +47308,7 @@
         <v>25</v>
       </c>
       <c r="C2714">
-        <v>5120</v>
+        <v>5140</v>
       </c>
       <c r="D2714" t="s">
         <v>2716</v>
@@ -47322,7 +47322,7 @@
         <v>26</v>
       </c>
       <c r="C2715">
-        <v>5170</v>
+        <v>5200</v>
       </c>
       <c r="D2715" t="s">
         <v>2717</v>
@@ -47336,7 +47336,7 @@
         <v>27</v>
       </c>
       <c r="C2716">
-        <v>5220</v>
+        <v>5260</v>
       </c>
       <c r="D2716" t="s">
         <v>2718</v>
@@ -47350,7 +47350,7 @@
         <v>28</v>
       </c>
       <c r="C2717">
-        <v>5270</v>
+        <v>5310</v>
       </c>
       <c r="D2717" t="s">
         <v>2719</v>
@@ -47364,7 +47364,7 @@
         <v>29</v>
       </c>
       <c r="C2718">
-        <v>5310</v>
+        <v>5350</v>
       </c>
       <c r="D2718" t="s">
         <v>2720</v>
@@ -47378,7 +47378,7 @@
         <v>30</v>
       </c>
       <c r="C2719">
-        <v>5350</v>
+        <v>5400</v>
       </c>
       <c r="D2719" t="s">
         <v>2721</v>
@@ -47392,7 +47392,7 @@
         <v>31</v>
       </c>
       <c r="C2720">
-        <v>5350</v>
+        <v>5400</v>
       </c>
       <c r="D2720" t="s">
         <v>2722</v>
@@ -47406,7 +47406,7 @@
         <v>32</v>
       </c>
       <c r="C2721">
-        <v>5340</v>
+        <v>5370</v>
       </c>
       <c r="D2721" t="s">
         <v>2723</v>
@@ -47420,7 +47420,7 @@
         <v>33</v>
       </c>
       <c r="C2722">
-        <v>5310</v>
+        <v>5300</v>
       </c>
       <c r="D2722" t="s">
         <v>2724</v>
@@ -47434,7 +47434,7 @@
         <v>34</v>
       </c>
       <c r="C2723">
-        <v>5250</v>
+        <v>5240</v>
       </c>
       <c r="D2723" t="s">
         <v>2725</v>
@@ -47462,7 +47462,7 @@
         <v>36</v>
       </c>
       <c r="C2725">
-        <v>5040</v>
+        <v>5060</v>
       </c>
       <c r="D2725" t="s">
         <v>2727</v>
@@ -47476,7 +47476,7 @@
         <v>37</v>
       </c>
       <c r="C2726">
-        <v>4900</v>
+        <v>4950</v>
       </c>
       <c r="D2726" t="s">
         <v>2728</v>
@@ -47490,7 +47490,7 @@
         <v>38</v>
       </c>
       <c r="C2727">
-        <v>4770</v>
+        <v>4830</v>
       </c>
       <c r="D2727" t="s">
         <v>2729</v>
@@ -47504,7 +47504,7 @@
         <v>39</v>
       </c>
       <c r="C2728">
-        <v>4660</v>
+        <v>4710</v>
       </c>
       <c r="D2728" t="s">
         <v>2730</v>
@@ -47518,7 +47518,7 @@
         <v>40</v>
       </c>
       <c r="C2729">
-        <v>4570</v>
+        <v>4580</v>
       </c>
       <c r="D2729" t="s">
         <v>2731</v>
@@ -47532,7 +47532,7 @@
         <v>41</v>
       </c>
       <c r="C2730">
-        <v>4490</v>
+        <v>4470</v>
       </c>
       <c r="D2730" t="s">
         <v>2732</v>
@@ -47546,7 +47546,7 @@
         <v>42</v>
       </c>
       <c r="C2731">
-        <v>4400</v>
+        <v>4360</v>
       </c>
       <c r="D2731" t="s">
         <v>2733</v>
@@ -47560,7 +47560,7 @@
         <v>43</v>
       </c>
       <c r="C2732">
-        <v>4300</v>
+        <v>4270</v>
       </c>
       <c r="D2732" t="s">
         <v>2734</v>
@@ -47574,7 +47574,7 @@
         <v>44</v>
       </c>
       <c r="C2733">
-        <v>4200</v>
+        <v>4180</v>
       </c>
       <c r="D2733" t="s">
         <v>2735</v>
@@ -47588,7 +47588,7 @@
         <v>45</v>
       </c>
       <c r="C2734">
-        <v>4080</v>
+        <v>4120</v>
       </c>
       <c r="D2734" t="s">
         <v>2736</v>
@@ -47602,7 +47602,7 @@
         <v>46</v>
       </c>
       <c r="C2735">
-        <v>4000</v>
+        <v>4060</v>
       </c>
       <c r="D2735" t="s">
         <v>2737</v>
@@ -47616,7 +47616,7 @@
         <v>47</v>
       </c>
       <c r="C2736">
-        <v>3950</v>
+        <v>4030</v>
       </c>
       <c r="D2736" t="s">
         <v>2738</v>
@@ -47630,7 +47630,7 @@
         <v>48</v>
       </c>
       <c r="C2737">
-        <v>3940</v>
+        <v>4000</v>
       </c>
       <c r="D2737" t="s">
         <v>2739</v>
@@ -47644,7 +47644,7 @@
         <v>49</v>
       </c>
       <c r="C2738">
-        <v>3960</v>
+        <v>3980</v>
       </c>
       <c r="D2738" t="s">
         <v>2740</v>
@@ -47672,7 +47672,7 @@
         <v>51</v>
       </c>
       <c r="C2740">
-        <v>3990</v>
+        <v>3960</v>
       </c>
       <c r="D2740" t="s">
         <v>2742</v>
@@ -47686,7 +47686,7 @@
         <v>52</v>
       </c>
       <c r="C2741">
-        <v>3990</v>
+        <v>3950</v>
       </c>
       <c r="D2741" t="s">
         <v>2743</v>
@@ -47700,7 +47700,7 @@
         <v>53</v>
       </c>
       <c r="C2742">
-        <v>4000</v>
+        <v>3950</v>
       </c>
       <c r="D2742" t="s">
         <v>2744</v>
@@ -47714,7 +47714,7 @@
         <v>54</v>
       </c>
       <c r="C2743">
-        <v>4000</v>
+        <v>3960</v>
       </c>
       <c r="D2743" t="s">
         <v>2745</v>
@@ -47728,7 +47728,7 @@
         <v>55</v>
       </c>
       <c r="C2744">
-        <v>3990</v>
+        <v>3960</v>
       </c>
       <c r="D2744" t="s">
         <v>2746</v>
@@ -47742,7 +47742,7 @@
         <v>56</v>
       </c>
       <c r="C2745">
-        <v>3990</v>
+        <v>3970</v>
       </c>
       <c r="D2745" t="s">
         <v>2747</v>
@@ -47756,7 +47756,7 @@
         <v>57</v>
       </c>
       <c r="C2746">
-        <v>3980</v>
+        <v>3990</v>
       </c>
       <c r="D2746" t="s">
         <v>2748</v>
@@ -47770,7 +47770,7 @@
         <v>58</v>
       </c>
       <c r="C2747">
-        <v>3980</v>
+        <v>4000</v>
       </c>
       <c r="D2747" t="s">
         <v>2749</v>
@@ -47784,7 +47784,7 @@
         <v>59</v>
       </c>
       <c r="C2748">
-        <v>4000</v>
+        <v>4020</v>
       </c>
       <c r="D2748" t="s">
         <v>2750</v>
@@ -47798,7 +47798,7 @@
         <v>60</v>
       </c>
       <c r="C2749">
-        <v>4030</v>
+        <v>4040</v>
       </c>
       <c r="D2749" t="s">
         <v>2751</v>
@@ -47826,7 +47826,7 @@
         <v>62</v>
       </c>
       <c r="C2751">
-        <v>4120</v>
+        <v>4100</v>
       </c>
       <c r="D2751" t="s">
         <v>2753</v>
@@ -47840,7 +47840,7 @@
         <v>63</v>
       </c>
       <c r="C2752">
-        <v>4170</v>
+        <v>4140</v>
       </c>
       <c r="D2752" t="s">
         <v>2754</v>
@@ -47854,7 +47854,7 @@
         <v>64</v>
       </c>
       <c r="C2753">
-        <v>4220</v>
+        <v>4190</v>
       </c>
       <c r="D2753" t="s">
         <v>2755</v>
@@ -47868,7 +47868,7 @@
         <v>65</v>
       </c>
       <c r="C2754">
-        <v>4280</v>
+        <v>4260</v>
       </c>
       <c r="D2754" t="s">
         <v>2756</v>
@@ -47882,7 +47882,7 @@
         <v>66</v>
       </c>
       <c r="C2755">
-        <v>4350</v>
+        <v>4340</v>
       </c>
       <c r="D2755" t="s">
         <v>2757</v>
@@ -47938,7 +47938,7 @@
         <v>70</v>
       </c>
       <c r="C2759">
-        <v>4770</v>
+        <v>4750</v>
       </c>
       <c r="D2759" t="s">
         <v>2761</v>
@@ -47952,7 +47952,7 @@
         <v>71</v>
       </c>
       <c r="C2760">
-        <v>4890</v>
+        <v>4870</v>
       </c>
       <c r="D2760" t="s">
         <v>2762</v>
@@ -47966,7 +47966,7 @@
         <v>72</v>
       </c>
       <c r="C2761">
-        <v>5030</v>
+        <v>4980</v>
       </c>
       <c r="D2761" t="s">
         <v>2763</v>
@@ -47980,7 +47980,7 @@
         <v>73</v>
       </c>
       <c r="C2762">
-        <v>5170</v>
+        <v>5110</v>
       </c>
       <c r="D2762" t="s">
         <v>2764</v>
@@ -47994,7 +47994,7 @@
         <v>74</v>
       </c>
       <c r="C2763">
-        <v>5310</v>
+        <v>5260</v>
       </c>
       <c r="D2763" t="s">
         <v>2765</v>
@@ -48008,7 +48008,7 @@
         <v>75</v>
       </c>
       <c r="C2764">
-        <v>5460</v>
+        <v>5420</v>
       </c>
       <c r="D2764" t="s">
         <v>2766</v>
@@ -48022,7 +48022,7 @@
         <v>76</v>
       </c>
       <c r="C2765">
-        <v>5620</v>
+        <v>5600</v>
       </c>
       <c r="D2765" t="s">
         <v>2767</v>
@@ -48050,7 +48050,7 @@
         <v>78</v>
       </c>
       <c r="C2767">
-        <v>5920</v>
+        <v>5950</v>
       </c>
       <c r="D2767" t="s">
         <v>2769</v>
@@ -48064,7 +48064,7 @@
         <v>79</v>
       </c>
       <c r="C2768">
-        <v>6030</v>
+        <v>6090</v>
       </c>
       <c r="D2768" t="s">
         <v>2770</v>
@@ -48078,7 +48078,7 @@
         <v>80</v>
       </c>
       <c r="C2769">
-        <v>6130</v>
+        <v>6190</v>
       </c>
       <c r="D2769" t="s">
         <v>2771</v>
@@ -48092,7 +48092,7 @@
         <v>81</v>
       </c>
       <c r="C2770">
-        <v>6200</v>
+        <v>6280</v>
       </c>
       <c r="D2770" t="s">
         <v>2772</v>
@@ -48106,7 +48106,7 @@
         <v>82</v>
       </c>
       <c r="C2771">
-        <v>6270</v>
+        <v>6370</v>
       </c>
       <c r="D2771" t="s">
         <v>2773</v>
@@ -48120,7 +48120,7 @@
         <v>83</v>
       </c>
       <c r="C2772">
-        <v>6350</v>
+        <v>6450</v>
       </c>
       <c r="D2772" t="s">
         <v>2774</v>
@@ -48134,7 +48134,7 @@
         <v>84</v>
       </c>
       <c r="C2773">
-        <v>6430</v>
+        <v>6550</v>
       </c>
       <c r="D2773" t="s">
         <v>2775</v>
@@ -48148,7 +48148,7 @@
         <v>85</v>
       </c>
       <c r="C2774">
-        <v>6510</v>
+        <v>6600</v>
       </c>
       <c r="D2774" t="s">
         <v>2776</v>
@@ -48162,7 +48162,7 @@
         <v>86</v>
       </c>
       <c r="C2775">
-        <v>6550</v>
+        <v>6600</v>
       </c>
       <c r="D2775" t="s">
         <v>2777</v>
@@ -48176,7 +48176,7 @@
         <v>87</v>
       </c>
       <c r="C2776">
-        <v>6540</v>
+        <v>6600</v>
       </c>
       <c r="D2776" t="s">
         <v>2778</v>
@@ -48190,7 +48190,7 @@
         <v>88</v>
       </c>
       <c r="C2777">
-        <v>6490</v>
+        <v>6520</v>
       </c>
       <c r="D2777" t="s">
         <v>2779</v>
@@ -48218,7 +48218,7 @@
         <v>90</v>
       </c>
       <c r="C2779">
-        <v>6270</v>
+        <v>6310</v>
       </c>
       <c r="D2779" t="s">
         <v>2781</v>
@@ -48232,7 +48232,7 @@
         <v>91</v>
       </c>
       <c r="C2780">
-        <v>6140</v>
+        <v>6180</v>
       </c>
       <c r="D2780" t="s">
         <v>2782</v>
@@ -48246,7 +48246,7 @@
         <v>92</v>
       </c>
       <c r="C2781">
-        <v>5980</v>
+        <v>6020</v>
       </c>
       <c r="D2781" t="s">
         <v>2783</v>
@@ -48260,7 +48260,7 @@
         <v>93</v>
       </c>
       <c r="C2782">
-        <v>5830</v>
+        <v>5800</v>
       </c>
       <c r="D2782" t="s">
         <v>2784</v>
@@ -48274,7 +48274,7 @@
         <v>94</v>
       </c>
       <c r="C2783">
-        <v>5680</v>
+        <v>5650</v>
       </c>
       <c r="D2783" t="s">
         <v>2785</v>
@@ -48316,7 +48316,7 @@
         <v>1</v>
       </c>
       <c r="C2786">
-        <v>5200</v>
+        <v>5360</v>
       </c>
       <c r="D2786" t="s">
         <v>2788</v>
@@ -48330,7 +48330,7 @@
         <v>2</v>
       </c>
       <c r="C2787">
-        <v>5160</v>
+        <v>5270</v>
       </c>
       <c r="D2787" t="s">
         <v>2789</v>
@@ -48344,7 +48344,7 @@
         <v>3</v>
       </c>
       <c r="C2788">
-        <v>5100</v>
+        <v>5190</v>
       </c>
       <c r="D2788" t="s">
         <v>2790</v>
@@ -48358,7 +48358,7 @@
         <v>4</v>
       </c>
       <c r="C2789">
-        <v>5030</v>
+        <v>5110</v>
       </c>
       <c r="D2789" t="s">
         <v>2791</v>
@@ -48372,7 +48372,7 @@
         <v>5</v>
       </c>
       <c r="C2790">
-        <v>4970</v>
+        <v>5050</v>
       </c>
       <c r="D2790" t="s">
         <v>2792</v>
@@ -48386,7 +48386,7 @@
         <v>6</v>
       </c>
       <c r="C2791">
-        <v>4920</v>
+        <v>4990</v>
       </c>
       <c r="D2791" t="s">
         <v>2793</v>
@@ -48400,7 +48400,7 @@
         <v>7</v>
       </c>
       <c r="C2792">
-        <v>4870</v>
+        <v>4940</v>
       </c>
       <c r="D2792" t="s">
         <v>2794</v>
@@ -48414,7 +48414,7 @@
         <v>8</v>
       </c>
       <c r="C2793">
-        <v>4830</v>
+        <v>4900</v>
       </c>
       <c r="D2793" t="s">
         <v>2795</v>
@@ -48428,7 +48428,7 @@
         <v>9</v>
       </c>
       <c r="C2794">
-        <v>4800</v>
+        <v>4860</v>
       </c>
       <c r="D2794" t="s">
         <v>2796</v>
@@ -48442,7 +48442,7 @@
         <v>10</v>
       </c>
       <c r="C2795">
-        <v>4770</v>
+        <v>4830</v>
       </c>
       <c r="D2795" t="s">
         <v>2797</v>
@@ -48456,7 +48456,7 @@
         <v>11</v>
       </c>
       <c r="C2796">
-        <v>4750</v>
+        <v>4810</v>
       </c>
       <c r="D2796" t="s">
         <v>2798</v>
@@ -48470,7 +48470,7 @@
         <v>12</v>
       </c>
       <c r="C2797">
-        <v>4740</v>
+        <v>4790</v>
       </c>
       <c r="D2797" t="s">
         <v>2799</v>
@@ -48484,7 +48484,7 @@
         <v>13</v>
       </c>
       <c r="C2798">
-        <v>4730</v>
+        <v>4770</v>
       </c>
       <c r="D2798" t="s">
         <v>2800</v>
@@ -48498,7 +48498,7 @@
         <v>14</v>
       </c>
       <c r="C2799">
-        <v>4730</v>
+        <v>4760</v>
       </c>
       <c r="D2799" t="s">
         <v>2801</v>
@@ -48512,7 +48512,7 @@
         <v>15</v>
       </c>
       <c r="C2800">
-        <v>4720</v>
+        <v>4750</v>
       </c>
       <c r="D2800" t="s">
         <v>2802</v>
@@ -48526,7 +48526,7 @@
         <v>16</v>
       </c>
       <c r="C2801">
-        <v>4720</v>
+        <v>4740</v>
       </c>
       <c r="D2801" t="s">
         <v>2803</v>
@@ -48540,7 +48540,7 @@
         <v>17</v>
       </c>
       <c r="C2802">
-        <v>4710</v>
+        <v>4740</v>
       </c>
       <c r="D2802" t="s">
         <v>2804</v>
@@ -48554,7 +48554,7 @@
         <v>18</v>
       </c>
       <c r="C2803">
-        <v>4710</v>
+        <v>4730</v>
       </c>
       <c r="D2803" t="s">
         <v>2805</v>
@@ -48568,7 +48568,7 @@
         <v>19</v>
       </c>
       <c r="C2804">
-        <v>4710</v>
+        <v>4720</v>
       </c>
       <c r="D2804" t="s">
         <v>2806</v>
@@ -48596,7 +48596,7 @@
         <v>21</v>
       </c>
       <c r="C2806">
-        <v>4710</v>
+        <v>4700</v>
       </c>
       <c r="D2806" t="s">
         <v>2808</v>
@@ -48610,7 +48610,7 @@
         <v>22</v>
       </c>
       <c r="C2807">
-        <v>4670</v>
+        <v>4690</v>
       </c>
       <c r="D2807" t="s">
         <v>2809</v>
@@ -48638,7 +48638,7 @@
         <v>24</v>
       </c>
       <c r="C2809">
-        <v>4690</v>
+        <v>4660</v>
       </c>
       <c r="D2809" t="s">
         <v>2811</v>
@@ -48652,7 +48652,7 @@
         <v>25</v>
       </c>
       <c r="C2810">
-        <v>4700</v>
+        <v>4650</v>
       </c>
       <c r="D2810" t="s">
         <v>2812</v>
@@ -48666,7 +48666,7 @@
         <v>26</v>
       </c>
       <c r="C2811">
-        <v>4720</v>
+        <v>4640</v>
       </c>
       <c r="D2811" t="s">
         <v>2813</v>
@@ -48680,7 +48680,7 @@
         <v>27</v>
       </c>
       <c r="C2812">
-        <v>4750</v>
+        <v>4620</v>
       </c>
       <c r="D2812" t="s">
         <v>2814</v>
@@ -48694,7 +48694,7 @@
         <v>28</v>
       </c>
       <c r="C2813">
-        <v>4770</v>
+        <v>4590</v>
       </c>
       <c r="D2813" t="s">
         <v>2815</v>
@@ -48708,7 +48708,7 @@
         <v>29</v>
       </c>
       <c r="C2814">
-        <v>4800</v>
+        <v>4560</v>
       </c>
       <c r="D2814" t="s">
         <v>2816</v>
@@ -48722,7 +48722,7 @@
         <v>30</v>
       </c>
       <c r="C2815">
-        <v>4830</v>
+        <v>4530</v>
       </c>
       <c r="D2815" t="s">
         <v>2817</v>
@@ -48736,7 +48736,7 @@
         <v>31</v>
       </c>
       <c r="C2816">
-        <v>4860</v>
+        <v>4510</v>
       </c>
       <c r="D2816" t="s">
         <v>2818</v>
@@ -48750,7 +48750,7 @@
         <v>32</v>
       </c>
       <c r="C2817">
-        <v>4860</v>
+        <v>4490</v>
       </c>
       <c r="D2817" t="s">
         <v>2819</v>
@@ -48764,7 +48764,7 @@
         <v>33</v>
       </c>
       <c r="C2818">
-        <v>4860</v>
+        <v>4470</v>
       </c>
       <c r="D2818" t="s">
         <v>2820</v>
@@ -48778,7 +48778,7 @@
         <v>34</v>
       </c>
       <c r="C2819">
-        <v>4860</v>
+        <v>4430</v>
       </c>
       <c r="D2819" t="s">
         <v>2821</v>
@@ -48792,7 +48792,7 @@
         <v>35</v>
       </c>
       <c r="C2820">
-        <v>4820</v>
+        <v>4370</v>
       </c>
       <c r="D2820" t="s">
         <v>2822</v>
@@ -48806,7 +48806,7 @@
         <v>36</v>
       </c>
       <c r="C2821">
-        <v>4780</v>
+        <v>4270</v>
       </c>
       <c r="D2821" t="s">
         <v>2823</v>
@@ -48820,7 +48820,7 @@
         <v>37</v>
       </c>
       <c r="C2822">
-        <v>4730</v>
+        <v>4160</v>
       </c>
       <c r="D2822" t="s">
         <v>2824</v>
@@ -48834,7 +48834,7 @@
         <v>38</v>
       </c>
       <c r="C2823">
-        <v>4670</v>
+        <v>4060</v>
       </c>
       <c r="D2823" t="s">
         <v>2825</v>
@@ -48848,7 +48848,7 @@
         <v>39</v>
       </c>
       <c r="C2824">
-        <v>4600</v>
+        <v>3980</v>
       </c>
       <c r="D2824" t="s">
         <v>2826</v>
@@ -48862,7 +48862,7 @@
         <v>40</v>
       </c>
       <c r="C2825">
-        <v>4530</v>
+        <v>3930</v>
       </c>
       <c r="D2825" t="s">
         <v>2827</v>
@@ -48876,7 +48876,7 @@
         <v>41</v>
       </c>
       <c r="C2826">
-        <v>4440</v>
+        <v>3890</v>
       </c>
       <c r="D2826" t="s">
         <v>2828</v>
@@ -48890,7 +48890,7 @@
         <v>42</v>
       </c>
       <c r="C2827">
-        <v>4360</v>
+        <v>3840</v>
       </c>
       <c r="D2827" t="s">
         <v>2829</v>
@@ -48904,7 +48904,7 @@
         <v>43</v>
       </c>
       <c r="C2828">
-        <v>4280</v>
+        <v>3770</v>
       </c>
       <c r="D2828" t="s">
         <v>2830</v>
@@ -48918,7 +48918,7 @@
         <v>44</v>
       </c>
       <c r="C2829">
-        <v>4210</v>
+        <v>3680</v>
       </c>
       <c r="D2829" t="s">
         <v>2831</v>
@@ -48932,7 +48932,7 @@
         <v>45</v>
       </c>
       <c r="C2830">
-        <v>4140</v>
+        <v>3590</v>
       </c>
       <c r="D2830" t="s">
         <v>2832</v>
@@ -48946,7 +48946,7 @@
         <v>46</v>
       </c>
       <c r="C2831">
-        <v>4070</v>
+        <v>3520</v>
       </c>
       <c r="D2831" t="s">
         <v>2833</v>
@@ -48960,7 +48960,7 @@
         <v>47</v>
       </c>
       <c r="C2832">
-        <v>4010</v>
+        <v>3480</v>
       </c>
       <c r="D2832" t="s">
         <v>2834</v>
@@ -48974,7 +48974,7 @@
         <v>48</v>
       </c>
       <c r="C2833">
-        <v>3960</v>
+        <v>3480</v>
       </c>
       <c r="D2833" t="s">
         <v>2835</v>
@@ -48988,7 +48988,7 @@
         <v>49</v>
       </c>
       <c r="C2834">
-        <v>3910</v>
+        <v>3500</v>
       </c>
       <c r="D2834" t="s">
         <v>2836</v>
@@ -49002,7 +49002,7 @@
         <v>50</v>
       </c>
       <c r="C2835">
-        <v>3870</v>
+        <v>3520</v>
       </c>
       <c r="D2835" t="s">
         <v>2837</v>
@@ -49016,7 +49016,7 @@
         <v>51</v>
       </c>
       <c r="C2836">
-        <v>3830</v>
+        <v>3530</v>
       </c>
       <c r="D2836" t="s">
         <v>2838</v>
@@ -49030,7 +49030,7 @@
         <v>52</v>
       </c>
       <c r="C2837">
-        <v>3800</v>
+        <v>3530</v>
       </c>
       <c r="D2837" t="s">
         <v>2839</v>
@@ -49044,7 +49044,7 @@
         <v>53</v>
       </c>
       <c r="C2838">
-        <v>3790</v>
+        <v>3510</v>
       </c>
       <c r="D2838" t="s">
         <v>2840</v>
@@ -49058,7 +49058,7 @@
         <v>54</v>
       </c>
       <c r="C2839">
-        <v>3780</v>
+        <v>3500</v>
       </c>
       <c r="D2839" t="s">
         <v>2841</v>
@@ -49072,7 +49072,7 @@
         <v>55</v>
       </c>
       <c r="C2840">
-        <v>3780</v>
+        <v>3480</v>
       </c>
       <c r="D2840" t="s">
         <v>2842</v>
@@ -49086,7 +49086,7 @@
         <v>56</v>
       </c>
       <c r="C2841">
-        <v>3800</v>
+        <v>3460</v>
       </c>
       <c r="D2841" t="s">
         <v>2843</v>
@@ -49100,7 +49100,7 @@
         <v>57</v>
       </c>
       <c r="C2842">
-        <v>3820</v>
+        <v>3450</v>
       </c>
       <c r="D2842" t="s">
         <v>2844</v>
@@ -49114,7 +49114,7 @@
         <v>58</v>
       </c>
       <c r="C2843">
-        <v>3850</v>
+        <v>3460</v>
       </c>
       <c r="D2843" t="s">
         <v>2845</v>
@@ -49128,7 +49128,7 @@
         <v>59</v>
       </c>
       <c r="C2844">
-        <v>3890</v>
+        <v>3510</v>
       </c>
       <c r="D2844" t="s">
         <v>2846</v>
@@ -49142,7 +49142,7 @@
         <v>60</v>
       </c>
       <c r="C2845">
-        <v>3920</v>
+        <v>3590</v>
       </c>
       <c r="D2845" t="s">
         <v>2847</v>
@@ -49156,7 +49156,7 @@
         <v>61</v>
       </c>
       <c r="C2846">
-        <v>3950</v>
+        <v>3700</v>
       </c>
       <c r="D2846" t="s">
         <v>2848</v>
@@ -49170,7 +49170,7 @@
         <v>62</v>
       </c>
       <c r="C2847">
-        <v>3990</v>
+        <v>3810</v>
       </c>
       <c r="D2847" t="s">
         <v>2849</v>
@@ -49184,7 +49184,7 @@
         <v>63</v>
       </c>
       <c r="C2848">
-        <v>4030</v>
+        <v>3910</v>
       </c>
       <c r="D2848" t="s">
         <v>2850</v>
@@ -49198,7 +49198,7 @@
         <v>64</v>
       </c>
       <c r="C2849">
-        <v>4080</v>
+        <v>3990</v>
       </c>
       <c r="D2849" t="s">
         <v>2851</v>
@@ -49212,7 +49212,7 @@
         <v>65</v>
       </c>
       <c r="C2850">
-        <v>4130</v>
+        <v>4070</v>
       </c>
       <c r="D2850" t="s">
         <v>2852</v>
@@ -49226,7 +49226,7 @@
         <v>66</v>
       </c>
       <c r="C2851">
-        <v>4210</v>
+        <v>4140</v>
       </c>
       <c r="D2851" t="s">
         <v>2853</v>
@@ -49240,7 +49240,7 @@
         <v>67</v>
       </c>
       <c r="C2852">
-        <v>4300</v>
+        <v>4220</v>
       </c>
       <c r="D2852" t="s">
         <v>2854</v>
@@ -49254,7 +49254,7 @@
         <v>68</v>
       </c>
       <c r="C2853">
-        <v>4410</v>
+        <v>4310</v>
       </c>
       <c r="D2853" t="s">
         <v>2855</v>
@@ -49268,7 +49268,7 @@
         <v>69</v>
       </c>
       <c r="C2854">
-        <v>4520</v>
+        <v>4410</v>
       </c>
       <c r="D2854" t="s">
         <v>2856</v>
@@ -49282,7 +49282,7 @@
         <v>70</v>
       </c>
       <c r="C2855">
-        <v>4640</v>
+        <v>4520</v>
       </c>
       <c r="D2855" t="s">
         <v>2857</v>
@@ -49296,7 +49296,7 @@
         <v>71</v>
       </c>
       <c r="C2856">
-        <v>4760</v>
+        <v>4660</v>
       </c>
       <c r="D2856" t="s">
         <v>2858</v>
@@ -49310,7 +49310,7 @@
         <v>72</v>
       </c>
       <c r="C2857">
-        <v>4880</v>
+        <v>4820</v>
       </c>
       <c r="D2857" t="s">
         <v>2859</v>
@@ -49324,7 +49324,7 @@
         <v>73</v>
       </c>
       <c r="C2858">
-        <v>5000</v>
+        <v>4990</v>
       </c>
       <c r="D2858" t="s">
         <v>2860</v>
@@ -49338,7 +49338,7 @@
         <v>74</v>
       </c>
       <c r="C2859">
-        <v>5110</v>
+        <v>5150</v>
       </c>
       <c r="D2859" t="s">
         <v>2861</v>
@@ -49352,7 +49352,7 @@
         <v>75</v>
       </c>
       <c r="C2860">
-        <v>5230</v>
+        <v>5290</v>
       </c>
       <c r="D2860" t="s">
         <v>2862</v>
@@ -49366,7 +49366,7 @@
         <v>76</v>
       </c>
       <c r="C2861">
-        <v>5350</v>
+        <v>5410</v>
       </c>
       <c r="D2861" t="s">
         <v>2863</v>
@@ -49380,7 +49380,7 @@
         <v>77</v>
       </c>
       <c r="C2862">
-        <v>5460</v>
+        <v>5520</v>
       </c>
       <c r="D2862" t="s">
         <v>2864</v>
@@ -49394,7 +49394,7 @@
         <v>78</v>
       </c>
       <c r="C2863">
-        <v>5560</v>
+        <v>5600</v>
       </c>
       <c r="D2863" t="s">
         <v>2865</v>
@@ -49408,7 +49408,7 @@
         <v>79</v>
       </c>
       <c r="C2864">
-        <v>5630</v>
+        <v>5670</v>
       </c>
       <c r="D2864" t="s">
         <v>2866</v>
@@ -49422,7 +49422,7 @@
         <v>80</v>
       </c>
       <c r="C2865">
-        <v>5680</v>
+        <v>5720</v>
       </c>
       <c r="D2865" t="s">
         <v>2867</v>
@@ -49436,7 +49436,7 @@
         <v>81</v>
       </c>
       <c r="C2866">
-        <v>5780</v>
+        <v>5770</v>
       </c>
       <c r="D2866" t="s">
         <v>2868</v>
@@ -49450,7 +49450,7 @@
         <v>82</v>
       </c>
       <c r="C2867">
-        <v>5850</v>
+        <v>5820</v>
       </c>
       <c r="D2867" t="s">
         <v>2869</v>
@@ -49464,7 +49464,7 @@
         <v>83</v>
       </c>
       <c r="C2868">
-        <v>5980</v>
+        <v>5900</v>
       </c>
       <c r="D2868" t="s">
         <v>2870</v>
@@ -49478,7 +49478,7 @@
         <v>84</v>
       </c>
       <c r="C2869">
-        <v>6060</v>
+        <v>5990</v>
       </c>
       <c r="D2869" t="s">
         <v>2871</v>
@@ -49492,7 +49492,7 @@
         <v>85</v>
       </c>
       <c r="C2870">
-        <v>6110</v>
+        <v>6090</v>
       </c>
       <c r="D2870" t="s">
         <v>2872</v>
@@ -49506,7 +49506,7 @@
         <v>86</v>
       </c>
       <c r="C2871">
-        <v>6130</v>
+        <v>6140</v>
       </c>
       <c r="D2871" t="s">
         <v>2873</v>
@@ -49520,7 +49520,7 @@
         <v>87</v>
       </c>
       <c r="C2872">
-        <v>6080</v>
+        <v>6130</v>
       </c>
       <c r="D2872" t="s">
         <v>2874</v>
@@ -49534,7 +49534,7 @@
         <v>88</v>
       </c>
       <c r="C2873">
-        <v>5990</v>
+        <v>6050</v>
       </c>
       <c r="D2873" t="s">
         <v>2875</v>
@@ -49548,7 +49548,7 @@
         <v>89</v>
       </c>
       <c r="C2874">
-        <v>5880</v>
+        <v>5930</v>
       </c>
       <c r="D2874" t="s">
         <v>2876</v>
@@ -49562,7 +49562,7 @@
         <v>90</v>
       </c>
       <c r="C2875">
-        <v>5800</v>
+        <v>5810</v>
       </c>
       <c r="D2875" t="s">
         <v>2877</v>
@@ -49576,7 +49576,7 @@
         <v>91</v>
       </c>
       <c r="C2876">
-        <v>5680</v>
+        <v>5690</v>
       </c>
       <c r="D2876" t="s">
         <v>2878</v>
@@ -49590,7 +49590,7 @@
         <v>92</v>
       </c>
       <c r="C2877">
-        <v>5540</v>
+        <v>5580</v>
       </c>
       <c r="D2877" t="s">
         <v>2879</v>
@@ -49604,7 +49604,7 @@
         <v>93</v>
       </c>
       <c r="C2878">
-        <v>5370</v>
+        <v>5470</v>
       </c>
       <c r="D2878" t="s">
         <v>2880</v>
@@ -49618,7 +49618,7 @@
         <v>94</v>
       </c>
       <c r="C2879">
-        <v>5240</v>
+        <v>5340</v>
       </c>
       <c r="D2879" t="s">
         <v>2881</v>
@@ -49632,7 +49632,7 @@
         <v>95</v>
       </c>
       <c r="C2880">
-        <v>5140</v>
+        <v>5210</v>
       </c>
       <c r="D2880" t="s">
         <v>2882</v>
@@ -49646,7 +49646,7 @@
         <v>96</v>
       </c>
       <c r="C2881">
-        <v>5030</v>
+        <v>5060</v>
       </c>
       <c r="D2881" t="s">
         <v>2883</v>

--- a/Market Fundamentals/Transelectrica_data/Cons_Prod_final/Weekly_Consumption_2026.xlsx
+++ b/Market Fundamentals/Transelectrica_data/Cons_Prod_final/Weekly_Consumption_2026.xlsx
@@ -46972,7 +46972,7 @@
         <v>1</v>
       </c>
       <c r="C2690">
-        <v>5400</v>
+        <v>5390</v>
       </c>
       <c r="D2690" t="s">
         <v>2692</v>
@@ -46986,7 +46986,7 @@
         <v>2</v>
       </c>
       <c r="C2691">
-        <v>5360</v>
+        <v>5330</v>
       </c>
       <c r="D2691" t="s">
         <v>2693</v>
@@ -47000,7 +47000,7 @@
         <v>3</v>
       </c>
       <c r="C2692">
-        <v>5290</v>
+        <v>5270</v>
       </c>
       <c r="D2692" t="s">
         <v>2694</v>
@@ -47014,7 +47014,7 @@
         <v>4</v>
       </c>
       <c r="C2693">
-        <v>5230</v>
+        <v>5220</v>
       </c>
       <c r="D2693" t="s">
         <v>2695</v>
@@ -47028,7 +47028,7 @@
         <v>5</v>
       </c>
       <c r="C2694">
-        <v>5180</v>
+        <v>5150</v>
       </c>
       <c r="D2694" t="s">
         <v>2696</v>
@@ -47042,7 +47042,7 @@
         <v>6</v>
       </c>
       <c r="C2695">
-        <v>5130</v>
+        <v>5100</v>
       </c>
       <c r="D2695" t="s">
         <v>2697</v>
@@ -47056,7 +47056,7 @@
         <v>7</v>
       </c>
       <c r="C2696">
-        <v>5080</v>
+        <v>5060</v>
       </c>
       <c r="D2696" t="s">
         <v>2698</v>
@@ -47070,7 +47070,7 @@
         <v>8</v>
       </c>
       <c r="C2697">
-        <v>5030</v>
+        <v>5020</v>
       </c>
       <c r="D2697" t="s">
         <v>2699</v>
@@ -47084,7 +47084,7 @@
         <v>9</v>
       </c>
       <c r="C2698">
-        <v>4980</v>
+        <v>4970</v>
       </c>
       <c r="D2698" t="s">
         <v>2700</v>
@@ -47098,7 +47098,7 @@
         <v>10</v>
       </c>
       <c r="C2699">
-        <v>4940</v>
+        <v>4950</v>
       </c>
       <c r="D2699" t="s">
         <v>2701</v>
@@ -47112,7 +47112,7 @@
         <v>11</v>
       </c>
       <c r="C2700">
-        <v>4920</v>
+        <v>4940</v>
       </c>
       <c r="D2700" t="s">
         <v>2702</v>
@@ -47126,7 +47126,7 @@
         <v>12</v>
       </c>
       <c r="C2701">
-        <v>4900</v>
+        <v>4940</v>
       </c>
       <c r="D2701" t="s">
         <v>2703</v>
@@ -47140,7 +47140,7 @@
         <v>13</v>
       </c>
       <c r="C2702">
-        <v>4900</v>
+        <v>4930</v>
       </c>
       <c r="D2702" t="s">
         <v>2704</v>
@@ -47154,7 +47154,7 @@
         <v>14</v>
       </c>
       <c r="C2703">
-        <v>4900</v>
+        <v>4930</v>
       </c>
       <c r="D2703" t="s">
         <v>2705</v>
@@ -47168,7 +47168,7 @@
         <v>15</v>
       </c>
       <c r="C2704">
-        <v>4900</v>
+        <v>4930</v>
       </c>
       <c r="D2704" t="s">
         <v>2706</v>
@@ -47182,7 +47182,7 @@
         <v>16</v>
       </c>
       <c r="C2705">
-        <v>4900</v>
+        <v>4940</v>
       </c>
       <c r="D2705" t="s">
         <v>2707</v>
@@ -47196,7 +47196,7 @@
         <v>17</v>
       </c>
       <c r="C2706">
-        <v>4900</v>
+        <v>4960</v>
       </c>
       <c r="D2706" t="s">
         <v>2708</v>
@@ -47210,7 +47210,7 @@
         <v>18</v>
       </c>
       <c r="C2707">
-        <v>4900</v>
+        <v>4960</v>
       </c>
       <c r="D2707" t="s">
         <v>2709</v>
@@ -47224,7 +47224,7 @@
         <v>19</v>
       </c>
       <c r="C2708">
-        <v>4910</v>
+        <v>4960</v>
       </c>
       <c r="D2708" t="s">
         <v>2710</v>
@@ -47238,7 +47238,7 @@
         <v>20</v>
       </c>
       <c r="C2709">
-        <v>4920</v>
+        <v>4960</v>
       </c>
       <c r="D2709" t="s">
         <v>2711</v>
@@ -47252,7 +47252,7 @@
         <v>21</v>
       </c>
       <c r="C2710">
-        <v>4940</v>
+        <v>4980</v>
       </c>
       <c r="D2710" t="s">
         <v>2712</v>
@@ -47266,7 +47266,7 @@
         <v>22</v>
       </c>
       <c r="C2711">
-        <v>4970</v>
+        <v>5010</v>
       </c>
       <c r="D2711" t="s">
         <v>2713</v>
@@ -47280,7 +47280,7 @@
         <v>23</v>
       </c>
       <c r="C2712">
-        <v>5020</v>
+        <v>5040</v>
       </c>
       <c r="D2712" t="s">
         <v>2714</v>
@@ -47294,7 +47294,7 @@
         <v>24</v>
       </c>
       <c r="C2713">
-        <v>5070</v>
+        <v>5090</v>
       </c>
       <c r="D2713" t="s">
         <v>2715</v>
@@ -47336,7 +47336,7 @@
         <v>27</v>
       </c>
       <c r="C2716">
-        <v>5260</v>
+        <v>5250</v>
       </c>
       <c r="D2716" t="s">
         <v>2718</v>
@@ -47350,7 +47350,7 @@
         <v>28</v>
       </c>
       <c r="C2717">
-        <v>5310</v>
+        <v>5320</v>
       </c>
       <c r="D2717" t="s">
         <v>2719</v>
@@ -47364,7 +47364,7 @@
         <v>29</v>
       </c>
       <c r="C2718">
-        <v>5350</v>
+        <v>5430</v>
       </c>
       <c r="D2718" t="s">
         <v>2720</v>
@@ -47378,7 +47378,7 @@
         <v>30</v>
       </c>
       <c r="C2719">
-        <v>5400</v>
+        <v>5480</v>
       </c>
       <c r="D2719" t="s">
         <v>2721</v>
@@ -47392,7 +47392,7 @@
         <v>31</v>
       </c>
       <c r="C2720">
-        <v>5400</v>
+        <v>5480</v>
       </c>
       <c r="D2720" t="s">
         <v>2722</v>
@@ -47406,7 +47406,7 @@
         <v>32</v>
       </c>
       <c r="C2721">
-        <v>5370</v>
+        <v>5480</v>
       </c>
       <c r="D2721" t="s">
         <v>2723</v>
@@ -47420,7 +47420,7 @@
         <v>33</v>
       </c>
       <c r="C2722">
-        <v>5300</v>
+        <v>5450</v>
       </c>
       <c r="D2722" t="s">
         <v>2724</v>
@@ -47434,7 +47434,7 @@
         <v>34</v>
       </c>
       <c r="C2723">
-        <v>5240</v>
+        <v>5400</v>
       </c>
       <c r="D2723" t="s">
         <v>2725</v>
@@ -47448,7 +47448,7 @@
         <v>35</v>
       </c>
       <c r="C2724">
-        <v>5160</v>
+        <v>5320</v>
       </c>
       <c r="D2724" t="s">
         <v>2726</v>
@@ -47462,7 +47462,7 @@
         <v>36</v>
       </c>
       <c r="C2725">
-        <v>5060</v>
+        <v>5220</v>
       </c>
       <c r="D2725" t="s">
         <v>2727</v>
@@ -47476,7 +47476,7 @@
         <v>37</v>
       </c>
       <c r="C2726">
-        <v>4950</v>
+        <v>5080</v>
       </c>
       <c r="D2726" t="s">
         <v>2728</v>
@@ -47490,7 +47490,7 @@
         <v>38</v>
       </c>
       <c r="C2727">
-        <v>4830</v>
+        <v>4950</v>
       </c>
       <c r="D2727" t="s">
         <v>2729</v>
@@ -47504,7 +47504,7 @@
         <v>39</v>
       </c>
       <c r="C2728">
-        <v>4710</v>
+        <v>4810</v>
       </c>
       <c r="D2728" t="s">
         <v>2730</v>
@@ -47518,7 +47518,7 @@
         <v>40</v>
       </c>
       <c r="C2729">
-        <v>4580</v>
+        <v>4680</v>
       </c>
       <c r="D2729" t="s">
         <v>2731</v>
@@ -47532,7 +47532,7 @@
         <v>41</v>
       </c>
       <c r="C2730">
-        <v>4470</v>
+        <v>4560</v>
       </c>
       <c r="D2730" t="s">
         <v>2732</v>
@@ -47546,7 +47546,7 @@
         <v>42</v>
       </c>
       <c r="C2731">
-        <v>4360</v>
+        <v>4450</v>
       </c>
       <c r="D2731" t="s">
         <v>2733</v>
@@ -47560,7 +47560,7 @@
         <v>43</v>
       </c>
       <c r="C2732">
-        <v>4270</v>
+        <v>4340</v>
       </c>
       <c r="D2732" t="s">
         <v>2734</v>
@@ -47574,7 +47574,7 @@
         <v>44</v>
       </c>
       <c r="C2733">
-        <v>4180</v>
+        <v>4250</v>
       </c>
       <c r="D2733" t="s">
         <v>2735</v>
@@ -47588,7 +47588,7 @@
         <v>45</v>
       </c>
       <c r="C2734">
-        <v>4120</v>
+        <v>4160</v>
       </c>
       <c r="D2734" t="s">
         <v>2736</v>
@@ -47602,7 +47602,7 @@
         <v>46</v>
       </c>
       <c r="C2735">
-        <v>4060</v>
+        <v>4090</v>
       </c>
       <c r="D2735" t="s">
         <v>2737</v>
@@ -47658,7 +47658,7 @@
         <v>50</v>
       </c>
       <c r="C2739">
-        <v>3970</v>
+        <v>3960</v>
       </c>
       <c r="D2739" t="s">
         <v>2741</v>
@@ -47686,7 +47686,7 @@
         <v>52</v>
       </c>
       <c r="C2741">
-        <v>3950</v>
+        <v>3960</v>
       </c>
       <c r="D2741" t="s">
         <v>2743</v>
@@ -47700,7 +47700,7 @@
         <v>53</v>
       </c>
       <c r="C2742">
-        <v>3950</v>
+        <v>3970</v>
       </c>
       <c r="D2742" t="s">
         <v>2744</v>
@@ -47714,7 +47714,7 @@
         <v>54</v>
       </c>
       <c r="C2743">
-        <v>3960</v>
+        <v>3980</v>
       </c>
       <c r="D2743" t="s">
         <v>2745</v>
@@ -47728,7 +47728,7 @@
         <v>55</v>
       </c>
       <c r="C2744">
-        <v>3960</v>
+        <v>3980</v>
       </c>
       <c r="D2744" t="s">
         <v>2746</v>
@@ -47742,7 +47742,7 @@
         <v>56</v>
       </c>
       <c r="C2745">
-        <v>3970</v>
+        <v>3990</v>
       </c>
       <c r="D2745" t="s">
         <v>2747</v>
@@ -47756,7 +47756,7 @@
         <v>57</v>
       </c>
       <c r="C2746">
-        <v>3990</v>
+        <v>4000</v>
       </c>
       <c r="D2746" t="s">
         <v>2748</v>
@@ -47770,7 +47770,7 @@
         <v>58</v>
       </c>
       <c r="C2747">
-        <v>4000</v>
+        <v>4030</v>
       </c>
       <c r="D2747" t="s">
         <v>2749</v>
@@ -47784,7 +47784,7 @@
         <v>59</v>
       </c>
       <c r="C2748">
-        <v>4020</v>
+        <v>4050</v>
       </c>
       <c r="D2748" t="s">
         <v>2750</v>
@@ -47798,7 +47798,7 @@
         <v>60</v>
       </c>
       <c r="C2749">
-        <v>4040</v>
+        <v>4090</v>
       </c>
       <c r="D2749" t="s">
         <v>2751</v>
@@ -47812,7 +47812,7 @@
         <v>61</v>
       </c>
       <c r="C2750">
-        <v>4070</v>
+        <v>4140</v>
       </c>
       <c r="D2750" t="s">
         <v>2752</v>
@@ -47826,7 +47826,7 @@
         <v>62</v>
       </c>
       <c r="C2751">
-        <v>4100</v>
+        <v>4190</v>
       </c>
       <c r="D2751" t="s">
         <v>2753</v>
@@ -47840,7 +47840,7 @@
         <v>63</v>
       </c>
       <c r="C2752">
-        <v>4140</v>
+        <v>4240</v>
       </c>
       <c r="D2752" t="s">
         <v>2754</v>
@@ -47854,7 +47854,7 @@
         <v>64</v>
       </c>
       <c r="C2753">
-        <v>4190</v>
+        <v>4300</v>
       </c>
       <c r="D2753" t="s">
         <v>2755</v>
@@ -47868,7 +47868,7 @@
         <v>65</v>
       </c>
       <c r="C2754">
-        <v>4260</v>
+        <v>4380</v>
       </c>
       <c r="D2754" t="s">
         <v>2756</v>
@@ -47882,7 +47882,7 @@
         <v>66</v>
       </c>
       <c r="C2755">
-        <v>4340</v>
+        <v>4470</v>
       </c>
       <c r="D2755" t="s">
         <v>2757</v>
@@ -47896,7 +47896,7 @@
         <v>67</v>
       </c>
       <c r="C2756">
-        <v>4430</v>
+        <v>4570</v>
       </c>
       <c r="D2756" t="s">
         <v>2758</v>
@@ -47910,7 +47910,7 @@
         <v>68</v>
       </c>
       <c r="C2757">
-        <v>4530</v>
+        <v>4680</v>
       </c>
       <c r="D2757" t="s">
         <v>2759</v>
@@ -47924,7 +47924,7 @@
         <v>69</v>
       </c>
       <c r="C2758">
-        <v>4640</v>
+        <v>4780</v>
       </c>
       <c r="D2758" t="s">
         <v>2760</v>
@@ -47938,7 +47938,7 @@
         <v>70</v>
       </c>
       <c r="C2759">
-        <v>4750</v>
+        <v>4910</v>
       </c>
       <c r="D2759" t="s">
         <v>2761</v>
@@ -47952,7 +47952,7 @@
         <v>71</v>
       </c>
       <c r="C2760">
-        <v>4870</v>
+        <v>5020</v>
       </c>
       <c r="D2760" t="s">
         <v>2762</v>
@@ -47966,7 +47966,7 @@
         <v>72</v>
       </c>
       <c r="C2761">
-        <v>4980</v>
+        <v>5150</v>
       </c>
       <c r="D2761" t="s">
         <v>2763</v>
@@ -47980,7 +47980,7 @@
         <v>73</v>
       </c>
       <c r="C2762">
-        <v>5110</v>
+        <v>5310</v>
       </c>
       <c r="D2762" t="s">
         <v>2764</v>
@@ -47994,7 +47994,7 @@
         <v>74</v>
       </c>
       <c r="C2763">
-        <v>5260</v>
+        <v>5450</v>
       </c>
       <c r="D2763" t="s">
         <v>2765</v>
@@ -48008,7 +48008,7 @@
         <v>75</v>
       </c>
       <c r="C2764">
-        <v>5420</v>
+        <v>5600</v>
       </c>
       <c r="D2764" t="s">
         <v>2766</v>
@@ -48022,7 +48022,7 @@
         <v>76</v>
       </c>
       <c r="C2765">
-        <v>5600</v>
+        <v>5760</v>
       </c>
       <c r="D2765" t="s">
         <v>2767</v>
@@ -48036,7 +48036,7 @@
         <v>77</v>
       </c>
       <c r="C2766">
-        <v>5780</v>
+        <v>5910</v>
       </c>
       <c r="D2766" t="s">
         <v>2768</v>
@@ -48050,7 +48050,7 @@
         <v>78</v>
       </c>
       <c r="C2767">
-        <v>5950</v>
+        <v>6060</v>
       </c>
       <c r="D2767" t="s">
         <v>2769</v>
@@ -48064,7 +48064,7 @@
         <v>79</v>
       </c>
       <c r="C2768">
-        <v>6090</v>
+        <v>6170</v>
       </c>
       <c r="D2768" t="s">
         <v>2770</v>
@@ -48078,7 +48078,7 @@
         <v>80</v>
       </c>
       <c r="C2769">
-        <v>6190</v>
+        <v>6260</v>
       </c>
       <c r="D2769" t="s">
         <v>2771</v>
@@ -48092,7 +48092,7 @@
         <v>81</v>
       </c>
       <c r="C2770">
-        <v>6280</v>
+        <v>6340</v>
       </c>
       <c r="D2770" t="s">
         <v>2772</v>
@@ -48106,7 +48106,7 @@
         <v>82</v>
       </c>
       <c r="C2771">
-        <v>6370</v>
+        <v>6420</v>
       </c>
       <c r="D2771" t="s">
         <v>2773</v>
@@ -48120,7 +48120,7 @@
         <v>83</v>
       </c>
       <c r="C2772">
-        <v>6450</v>
+        <v>6490</v>
       </c>
       <c r="D2772" t="s">
         <v>2774</v>
@@ -48134,7 +48134,7 @@
         <v>84</v>
       </c>
       <c r="C2773">
-        <v>6550</v>
+        <v>6590</v>
       </c>
       <c r="D2773" t="s">
         <v>2775</v>
@@ -48148,7 +48148,7 @@
         <v>85</v>
       </c>
       <c r="C2774">
-        <v>6600</v>
+        <v>6660</v>
       </c>
       <c r="D2774" t="s">
         <v>2776</v>
@@ -48162,7 +48162,7 @@
         <v>86</v>
       </c>
       <c r="C2775">
-        <v>6600</v>
+        <v>6660</v>
       </c>
       <c r="D2775" t="s">
         <v>2777</v>
@@ -48176,7 +48176,7 @@
         <v>87</v>
       </c>
       <c r="C2776">
-        <v>6600</v>
+        <v>6640</v>
       </c>
       <c r="D2776" t="s">
         <v>2778</v>
@@ -48190,7 +48190,7 @@
         <v>88</v>
       </c>
       <c r="C2777">
-        <v>6520</v>
+        <v>6560</v>
       </c>
       <c r="D2777" t="s">
         <v>2779</v>
@@ -48204,7 +48204,7 @@
         <v>89</v>
       </c>
       <c r="C2778">
-        <v>6390</v>
+        <v>6420</v>
       </c>
       <c r="D2778" t="s">
         <v>2780</v>
@@ -48218,7 +48218,7 @@
         <v>90</v>
       </c>
       <c r="C2779">
-        <v>6310</v>
+        <v>6290</v>
       </c>
       <c r="D2779" t="s">
         <v>2781</v>
@@ -48232,7 +48232,7 @@
         <v>91</v>
       </c>
       <c r="C2780">
-        <v>6180</v>
+        <v>6160</v>
       </c>
       <c r="D2780" t="s">
         <v>2782</v>
@@ -48246,7 +48246,7 @@
         <v>92</v>
       </c>
       <c r="C2781">
-        <v>6020</v>
+        <v>6010</v>
       </c>
       <c r="D2781" t="s">
         <v>2783</v>
@@ -48260,7 +48260,7 @@
         <v>93</v>
       </c>
       <c r="C2782">
-        <v>5800</v>
+        <v>5850</v>
       </c>
       <c r="D2782" t="s">
         <v>2784</v>
@@ -48274,7 +48274,7 @@
         <v>94</v>
       </c>
       <c r="C2783">
-        <v>5650</v>
+        <v>5720</v>
       </c>
       <c r="D2783" t="s">
         <v>2785</v>
@@ -48288,7 +48288,7 @@
         <v>95</v>
       </c>
       <c r="C2784">
-        <v>5560</v>
+        <v>5610</v>
       </c>
       <c r="D2784" t="s">
         <v>2786</v>
@@ -48302,7 +48302,7 @@
         <v>96</v>
       </c>
       <c r="C2785">
-        <v>5450</v>
+        <v>5500</v>
       </c>
       <c r="D2785" t="s">
         <v>2787</v>
@@ -48316,7 +48316,7 @@
         <v>1</v>
       </c>
       <c r="C2786">
-        <v>5360</v>
+        <v>5320</v>
       </c>
       <c r="D2786" t="s">
         <v>2788</v>
@@ -48330,7 +48330,7 @@
         <v>2</v>
       </c>
       <c r="C2787">
-        <v>5270</v>
+        <v>5280</v>
       </c>
       <c r="D2787" t="s">
         <v>2789</v>
@@ -48344,7 +48344,7 @@
         <v>3</v>
       </c>
       <c r="C2788">
-        <v>5190</v>
+        <v>5220</v>
       </c>
       <c r="D2788" t="s">
         <v>2790</v>
@@ -48358,7 +48358,7 @@
         <v>4</v>
       </c>
       <c r="C2789">
-        <v>5110</v>
+        <v>5140</v>
       </c>
       <c r="D2789" t="s">
         <v>2791</v>
@@ -48372,7 +48372,7 @@
         <v>5</v>
       </c>
       <c r="C2790">
-        <v>5050</v>
+        <v>5070</v>
       </c>
       <c r="D2790" t="s">
         <v>2792</v>
@@ -48386,7 +48386,7 @@
         <v>6</v>
       </c>
       <c r="C2791">
-        <v>4990</v>
+        <v>5010</v>
       </c>
       <c r="D2791" t="s">
         <v>2793</v>
@@ -48400,7 +48400,7 @@
         <v>7</v>
       </c>
       <c r="C2792">
-        <v>4940</v>
+        <v>4960</v>
       </c>
       <c r="D2792" t="s">
         <v>2794</v>
@@ -48414,7 +48414,7 @@
         <v>8</v>
       </c>
       <c r="C2793">
-        <v>4900</v>
+        <v>4910</v>
       </c>
       <c r="D2793" t="s">
         <v>2795</v>
@@ -48428,7 +48428,7 @@
         <v>9</v>
       </c>
       <c r="C2794">
-        <v>4860</v>
+        <v>4870</v>
       </c>
       <c r="D2794" t="s">
         <v>2796</v>
@@ -48484,7 +48484,7 @@
         <v>13</v>
       </c>
       <c r="C2798">
-        <v>4770</v>
+        <v>4780</v>
       </c>
       <c r="D2798" t="s">
         <v>2800</v>
@@ -48498,7 +48498,7 @@
         <v>14</v>
       </c>
       <c r="C2799">
-        <v>4760</v>
+        <v>4770</v>
       </c>
       <c r="D2799" t="s">
         <v>2801</v>
@@ -48512,7 +48512,7 @@
         <v>15</v>
       </c>
       <c r="C2800">
-        <v>4750</v>
+        <v>4770</v>
       </c>
       <c r="D2800" t="s">
         <v>2802</v>
@@ -48526,7 +48526,7 @@
         <v>16</v>
       </c>
       <c r="C2801">
-        <v>4740</v>
+        <v>4760</v>
       </c>
       <c r="D2801" t="s">
         <v>2803</v>
@@ -48540,7 +48540,7 @@
         <v>17</v>
       </c>
       <c r="C2802">
-        <v>4740</v>
+        <v>4760</v>
       </c>
       <c r="D2802" t="s">
         <v>2804</v>
@@ -48554,7 +48554,7 @@
         <v>18</v>
       </c>
       <c r="C2803">
-        <v>4730</v>
+        <v>4750</v>
       </c>
       <c r="D2803" t="s">
         <v>2805</v>
@@ -48568,7 +48568,7 @@
         <v>19</v>
       </c>
       <c r="C2804">
-        <v>4720</v>
+        <v>4740</v>
       </c>
       <c r="D2804" t="s">
         <v>2806</v>
@@ -48582,7 +48582,7 @@
         <v>20</v>
       </c>
       <c r="C2805">
-        <v>4710</v>
+        <v>4730</v>
       </c>
       <c r="D2805" t="s">
         <v>2807</v>
@@ -48596,7 +48596,7 @@
         <v>21</v>
       </c>
       <c r="C2806">
-        <v>4700</v>
+        <v>4720</v>
       </c>
       <c r="D2806" t="s">
         <v>2808</v>
@@ -48610,7 +48610,7 @@
         <v>22</v>
       </c>
       <c r="C2807">
-        <v>4690</v>
+        <v>4710</v>
       </c>
       <c r="D2807" t="s">
         <v>2809</v>
@@ -48624,7 +48624,7 @@
         <v>23</v>
       </c>
       <c r="C2808">
-        <v>4680</v>
+        <v>4700</v>
       </c>
       <c r="D2808" t="s">
         <v>2810</v>
@@ -48638,7 +48638,7 @@
         <v>24</v>
       </c>
       <c r="C2809">
-        <v>4660</v>
+        <v>4690</v>
       </c>
       <c r="D2809" t="s">
         <v>2811</v>
@@ -48652,7 +48652,7 @@
         <v>25</v>
       </c>
       <c r="C2810">
-        <v>4650</v>
+        <v>4680</v>
       </c>
       <c r="D2810" t="s">
         <v>2812</v>
@@ -48666,7 +48666,7 @@
         <v>26</v>
       </c>
       <c r="C2811">
-        <v>4640</v>
+        <v>4670</v>
       </c>
       <c r="D2811" t="s">
         <v>2813</v>
@@ -48680,7 +48680,7 @@
         <v>27</v>
       </c>
       <c r="C2812">
-        <v>4620</v>
+        <v>4660</v>
       </c>
       <c r="D2812" t="s">
         <v>2814</v>
@@ -48694,7 +48694,7 @@
         <v>28</v>
       </c>
       <c r="C2813">
-        <v>4590</v>
+        <v>4650</v>
       </c>
       <c r="D2813" t="s">
         <v>2815</v>
@@ -48708,7 +48708,7 @@
         <v>29</v>
       </c>
       <c r="C2814">
-        <v>4560</v>
+        <v>4640</v>
       </c>
       <c r="D2814" t="s">
         <v>2816</v>
@@ -48722,7 +48722,7 @@
         <v>30</v>
       </c>
       <c r="C2815">
-        <v>4530</v>
+        <v>4630</v>
       </c>
       <c r="D2815" t="s">
         <v>2817</v>
@@ -48736,7 +48736,7 @@
         <v>31</v>
       </c>
       <c r="C2816">
-        <v>4510</v>
+        <v>4610</v>
       </c>
       <c r="D2816" t="s">
         <v>2818</v>
@@ -48750,7 +48750,7 @@
         <v>32</v>
       </c>
       <c r="C2817">
-        <v>4490</v>
+        <v>4580</v>
       </c>
       <c r="D2817" t="s">
         <v>2819</v>
@@ -48764,7 +48764,7 @@
         <v>33</v>
       </c>
       <c r="C2818">
-        <v>4470</v>
+        <v>4550</v>
       </c>
       <c r="D2818" t="s">
         <v>2820</v>
@@ -48778,7 +48778,7 @@
         <v>34</v>
       </c>
       <c r="C2819">
-        <v>4430</v>
+        <v>4500</v>
       </c>
       <c r="D2819" t="s">
         <v>2821</v>
@@ -48792,7 +48792,7 @@
         <v>35</v>
       </c>
       <c r="C2820">
-        <v>4370</v>
+        <v>4450</v>
       </c>
       <c r="D2820" t="s">
         <v>2822</v>
@@ -48806,7 +48806,7 @@
         <v>36</v>
       </c>
       <c r="C2821">
-        <v>4270</v>
+        <v>4380</v>
       </c>
       <c r="D2821" t="s">
         <v>2823</v>
@@ -48820,7 +48820,7 @@
         <v>37</v>
       </c>
       <c r="C2822">
-        <v>4160</v>
+        <v>4300</v>
       </c>
       <c r="D2822" t="s">
         <v>2824</v>
@@ -48834,7 +48834,7 @@
         <v>38</v>
       </c>
       <c r="C2823">
-        <v>4060</v>
+        <v>4220</v>
       </c>
       <c r="D2823" t="s">
         <v>2825</v>
@@ -48848,7 +48848,7 @@
         <v>39</v>
       </c>
       <c r="C2824">
-        <v>3980</v>
+        <v>4120</v>
       </c>
       <c r="D2824" t="s">
         <v>2826</v>
@@ -48862,7 +48862,7 @@
         <v>40</v>
       </c>
       <c r="C2825">
-        <v>3930</v>
+        <v>4030</v>
       </c>
       <c r="D2825" t="s">
         <v>2827</v>
@@ -48876,7 +48876,7 @@
         <v>41</v>
       </c>
       <c r="C2826">
-        <v>3890</v>
+        <v>3940</v>
       </c>
       <c r="D2826" t="s">
         <v>2828</v>
@@ -48890,7 +48890,7 @@
         <v>42</v>
       </c>
       <c r="C2827">
-        <v>3840</v>
+        <v>3850</v>
       </c>
       <c r="D2827" t="s">
         <v>2829</v>
@@ -48918,7 +48918,7 @@
         <v>44</v>
       </c>
       <c r="C2829">
-        <v>3680</v>
+        <v>3700</v>
       </c>
       <c r="D2829" t="s">
         <v>2831</v>
@@ -48932,7 +48932,7 @@
         <v>45</v>
       </c>
       <c r="C2830">
-        <v>3590</v>
+        <v>3650</v>
       </c>
       <c r="D2830" t="s">
         <v>2832</v>
@@ -48946,7 +48946,7 @@
         <v>46</v>
       </c>
       <c r="C2831">
-        <v>3520</v>
+        <v>3610</v>
       </c>
       <c r="D2831" t="s">
         <v>2833</v>
@@ -48960,7 +48960,7 @@
         <v>47</v>
       </c>
       <c r="C2832">
-        <v>3480</v>
+        <v>3590</v>
       </c>
       <c r="D2832" t="s">
         <v>2834</v>
@@ -48974,7 +48974,7 @@
         <v>48</v>
       </c>
       <c r="C2833">
-        <v>3480</v>
+        <v>3570</v>
       </c>
       <c r="D2833" t="s">
         <v>2835</v>
@@ -48988,7 +48988,7 @@
         <v>49</v>
       </c>
       <c r="C2834">
-        <v>3500</v>
+        <v>3560</v>
       </c>
       <c r="D2834" t="s">
         <v>2836</v>
@@ -49002,7 +49002,7 @@
         <v>50</v>
       </c>
       <c r="C2835">
-        <v>3520</v>
+        <v>3550</v>
       </c>
       <c r="D2835" t="s">
         <v>2837</v>
@@ -49016,7 +49016,7 @@
         <v>51</v>
       </c>
       <c r="C2836">
-        <v>3530</v>
+        <v>3550</v>
       </c>
       <c r="D2836" t="s">
         <v>2838</v>
@@ -49030,7 +49030,7 @@
         <v>52</v>
       </c>
       <c r="C2837">
-        <v>3530</v>
+        <v>3540</v>
       </c>
       <c r="D2837" t="s">
         <v>2839</v>
@@ -49044,7 +49044,7 @@
         <v>53</v>
       </c>
       <c r="C2838">
-        <v>3510</v>
+        <v>3540</v>
       </c>
       <c r="D2838" t="s">
         <v>2840</v>
@@ -49058,7 +49058,7 @@
         <v>54</v>
       </c>
       <c r="C2839">
-        <v>3500</v>
+        <v>3540</v>
       </c>
       <c r="D2839" t="s">
         <v>2841</v>
@@ -49072,7 +49072,7 @@
         <v>55</v>
       </c>
       <c r="C2840">
-        <v>3480</v>
+        <v>3550</v>
       </c>
       <c r="D2840" t="s">
         <v>2842</v>
@@ -49086,7 +49086,7 @@
         <v>56</v>
       </c>
       <c r="C2841">
-        <v>3460</v>
+        <v>3560</v>
       </c>
       <c r="D2841" t="s">
         <v>2843</v>
@@ -49100,7 +49100,7 @@
         <v>57</v>
       </c>
       <c r="C2842">
-        <v>3450</v>
+        <v>3580</v>
       </c>
       <c r="D2842" t="s">
         <v>2844</v>
@@ -49114,7 +49114,7 @@
         <v>58</v>
       </c>
       <c r="C2843">
-        <v>3460</v>
+        <v>3610</v>
       </c>
       <c r="D2843" t="s">
         <v>2845</v>
@@ -49128,7 +49128,7 @@
         <v>59</v>
       </c>
       <c r="C2844">
-        <v>3510</v>
+        <v>3650</v>
       </c>
       <c r="D2844" t="s">
         <v>2846</v>
@@ -49142,7 +49142,7 @@
         <v>60</v>
       </c>
       <c r="C2845">
-        <v>3590</v>
+        <v>3700</v>
       </c>
       <c r="D2845" t="s">
         <v>2847</v>
@@ -49156,7 +49156,7 @@
         <v>61</v>
       </c>
       <c r="C2846">
-        <v>3700</v>
+        <v>3760</v>
       </c>
       <c r="D2846" t="s">
         <v>2848</v>
@@ -49170,7 +49170,7 @@
         <v>62</v>
       </c>
       <c r="C2847">
-        <v>3810</v>
+        <v>3820</v>
       </c>
       <c r="D2847" t="s">
         <v>2849</v>
@@ -49184,7 +49184,7 @@
         <v>63</v>
       </c>
       <c r="C2848">
-        <v>3910</v>
+        <v>3900</v>
       </c>
       <c r="D2848" t="s">
         <v>2850</v>
@@ -49198,7 +49198,7 @@
         <v>64</v>
       </c>
       <c r="C2849">
-        <v>3990</v>
+        <v>3980</v>
       </c>
       <c r="D2849" t="s">
         <v>2851</v>
@@ -49226,7 +49226,7 @@
         <v>66</v>
       </c>
       <c r="C2851">
-        <v>4140</v>
+        <v>4160</v>
       </c>
       <c r="D2851" t="s">
         <v>2853</v>
@@ -49240,7 +49240,7 @@
         <v>67</v>
       </c>
       <c r="C2852">
-        <v>4220</v>
+        <v>4270</v>
       </c>
       <c r="D2852" t="s">
         <v>2854</v>
@@ -49254,7 +49254,7 @@
         <v>68</v>
       </c>
       <c r="C2853">
-        <v>4310</v>
+        <v>4390</v>
       </c>
       <c r="D2853" t="s">
         <v>2855</v>
@@ -49268,7 +49268,7 @@
         <v>69</v>
       </c>
       <c r="C2854">
-        <v>4410</v>
+        <v>4510</v>
       </c>
       <c r="D2854" t="s">
         <v>2856</v>
@@ -49282,7 +49282,7 @@
         <v>70</v>
       </c>
       <c r="C2855">
-        <v>4520</v>
+        <v>4640</v>
       </c>
       <c r="D2855" t="s">
         <v>2857</v>
@@ -49296,7 +49296,7 @@
         <v>71</v>
       </c>
       <c r="C2856">
-        <v>4660</v>
+        <v>4770</v>
       </c>
       <c r="D2856" t="s">
         <v>2858</v>
@@ -49310,7 +49310,7 @@
         <v>72</v>
       </c>
       <c r="C2857">
-        <v>4820</v>
+        <v>4900</v>
       </c>
       <c r="D2857" t="s">
         <v>2859</v>
@@ -49324,7 +49324,7 @@
         <v>73</v>
       </c>
       <c r="C2858">
-        <v>4990</v>
+        <v>5030</v>
       </c>
       <c r="D2858" t="s">
         <v>2860</v>
@@ -49338,7 +49338,7 @@
         <v>74</v>
       </c>
       <c r="C2859">
-        <v>5150</v>
+        <v>5160</v>
       </c>
       <c r="D2859" t="s">
         <v>2861</v>
@@ -49380,7 +49380,7 @@
         <v>77</v>
       </c>
       <c r="C2862">
-        <v>5520</v>
+        <v>5530</v>
       </c>
       <c r="D2862" t="s">
         <v>2864</v>
@@ -49394,7 +49394,7 @@
         <v>78</v>
       </c>
       <c r="C2863">
-        <v>5600</v>
+        <v>5630</v>
       </c>
       <c r="D2863" t="s">
         <v>2865</v>
@@ -49408,7 +49408,7 @@
         <v>79</v>
       </c>
       <c r="C2864">
-        <v>5670</v>
+        <v>5720</v>
       </c>
       <c r="D2864" t="s">
         <v>2866</v>
@@ -49422,7 +49422,7 @@
         <v>80</v>
       </c>
       <c r="C2865">
-        <v>5720</v>
+        <v>5780</v>
       </c>
       <c r="D2865" t="s">
         <v>2867</v>
@@ -49436,7 +49436,7 @@
         <v>81</v>
       </c>
       <c r="C2866">
-        <v>5770</v>
+        <v>5850</v>
       </c>
       <c r="D2866" t="s">
         <v>2868</v>
@@ -49450,7 +49450,7 @@
         <v>82</v>
       </c>
       <c r="C2867">
-        <v>5820</v>
+        <v>5930</v>
       </c>
       <c r="D2867" t="s">
         <v>2869</v>
@@ -49464,7 +49464,7 @@
         <v>83</v>
       </c>
       <c r="C2868">
-        <v>5900</v>
+        <v>6000</v>
       </c>
       <c r="D2868" t="s">
         <v>2870</v>
@@ -49478,7 +49478,7 @@
         <v>84</v>
       </c>
       <c r="C2869">
-        <v>5990</v>
+        <v>6090</v>
       </c>
       <c r="D2869" t="s">
         <v>2871</v>
@@ -49492,7 +49492,7 @@
         <v>85</v>
       </c>
       <c r="C2870">
-        <v>6090</v>
+        <v>6100</v>
       </c>
       <c r="D2870" t="s">
         <v>2872</v>
@@ -49506,7 +49506,7 @@
         <v>86</v>
       </c>
       <c r="C2871">
-        <v>6140</v>
+        <v>6090</v>
       </c>
       <c r="D2871" t="s">
         <v>2873</v>
@@ -49520,7 +49520,7 @@
         <v>87</v>
       </c>
       <c r="C2872">
-        <v>6130</v>
+        <v>6090</v>
       </c>
       <c r="D2872" t="s">
         <v>2874</v>
@@ -49534,7 +49534,7 @@
         <v>88</v>
       </c>
       <c r="C2873">
-        <v>6050</v>
+        <v>6040</v>
       </c>
       <c r="D2873" t="s">
         <v>2875</v>
@@ -49548,7 +49548,7 @@
         <v>89</v>
       </c>
       <c r="C2874">
-        <v>5930</v>
+        <v>5940</v>
       </c>
       <c r="D2874" t="s">
         <v>2876</v>
@@ -49562,7 +49562,7 @@
         <v>90</v>
       </c>
       <c r="C2875">
-        <v>5810</v>
+        <v>5870</v>
       </c>
       <c r="D2875" t="s">
         <v>2877</v>
@@ -49576,7 +49576,7 @@
         <v>91</v>
       </c>
       <c r="C2876">
-        <v>5690</v>
+        <v>5730</v>
       </c>
       <c r="D2876" t="s">
         <v>2878</v>
@@ -49590,7 +49590,7 @@
         <v>92</v>
       </c>
       <c r="C2877">
-        <v>5580</v>
+        <v>5600</v>
       </c>
       <c r="D2877" t="s">
         <v>2879</v>
@@ -49604,7 +49604,7 @@
         <v>93</v>
       </c>
       <c r="C2878">
-        <v>5470</v>
+        <v>5440</v>
       </c>
       <c r="D2878" t="s">
         <v>2880</v>
@@ -49618,7 +49618,7 @@
         <v>94</v>
       </c>
       <c r="C2879">
-        <v>5340</v>
+        <v>5310</v>
       </c>
       <c r="D2879" t="s">
         <v>2881</v>
@@ -49646,7 +49646,7 @@
         <v>96</v>
       </c>
       <c r="C2881">
-        <v>5060</v>
+        <v>5100</v>
       </c>
       <c r="D2881" t="s">
         <v>2883</v>
@@ -49660,7 +49660,7 @@
         <v>1</v>
       </c>
       <c r="C2882">
-        <v>4930</v>
+        <v>4840</v>
       </c>
       <c r="D2882" t="s">
         <v>2884</v>
@@ -49674,7 +49674,7 @@
         <v>2</v>
       </c>
       <c r="C2883">
-        <v>4880</v>
+        <v>4780</v>
       </c>
       <c r="D2883" t="s">
         <v>2885</v>
@@ -49688,7 +49688,7 @@
         <v>3</v>
       </c>
       <c r="C2884">
-        <v>4830</v>
+        <v>4720</v>
       </c>
       <c r="D2884" t="s">
         <v>2886</v>
@@ -49702,7 +49702,7 @@
         <v>4</v>
       </c>
       <c r="C2885">
-        <v>4760</v>
+        <v>4660</v>
       </c>
       <c r="D2885" t="s">
         <v>2887</v>
@@ -49716,7 +49716,7 @@
         <v>5</v>
       </c>
       <c r="C2886">
-        <v>4700</v>
+        <v>4590</v>
       </c>
       <c r="D2886" t="s">
         <v>2888</v>
@@ -49730,7 +49730,7 @@
         <v>6</v>
       </c>
       <c r="C2887">
-        <v>4640</v>
+        <v>4530</v>
       </c>
       <c r="D2887" t="s">
         <v>2889</v>
@@ -49744,7 +49744,7 @@
         <v>7</v>
       </c>
       <c r="C2888">
-        <v>4600</v>
+        <v>4490</v>
       </c>
       <c r="D2888" t="s">
         <v>2890</v>
@@ -49758,7 +49758,7 @@
         <v>8</v>
       </c>
       <c r="C2889">
-        <v>4560</v>
+        <v>4450</v>
       </c>
       <c r="D2889" t="s">
         <v>2891</v>
@@ -49772,7 +49772,7 @@
         <v>9</v>
       </c>
       <c r="C2890">
-        <v>4530</v>
+        <v>4420</v>
       </c>
       <c r="D2890" t="s">
         <v>2892</v>
@@ -49786,7 +49786,7 @@
         <v>10</v>
       </c>
       <c r="C2891">
-        <v>4500</v>
+        <v>4410</v>
       </c>
       <c r="D2891" t="s">
         <v>2893</v>
@@ -49800,7 +49800,7 @@
         <v>11</v>
       </c>
       <c r="C2892">
-        <v>4490</v>
+        <v>4400</v>
       </c>
       <c r="D2892" t="s">
         <v>2894</v>
@@ -49814,7 +49814,7 @@
         <v>12</v>
       </c>
       <c r="C2893">
-        <v>4470</v>
+        <v>4390</v>
       </c>
       <c r="D2893" t="s">
         <v>2895</v>
@@ -49828,7 +49828,7 @@
         <v>13</v>
       </c>
       <c r="C2894">
-        <v>4470</v>
+        <v>4380</v>
       </c>
       <c r="D2894" t="s">
         <v>2896</v>
@@ -49842,7 +49842,7 @@
         <v>14</v>
       </c>
       <c r="C2895">
-        <v>4450</v>
+        <v>4370</v>
       </c>
       <c r="D2895" t="s">
         <v>2897</v>
@@ -49856,7 +49856,7 @@
         <v>15</v>
       </c>
       <c r="C2896">
-        <v>4440</v>
+        <v>4350</v>
       </c>
       <c r="D2896" t="s">
         <v>2898</v>
@@ -49870,7 +49870,7 @@
         <v>16</v>
       </c>
       <c r="C2897">
-        <v>4430</v>
+        <v>4350</v>
       </c>
       <c r="D2897" t="s">
         <v>2899</v>
@@ -49884,7 +49884,7 @@
         <v>17</v>
       </c>
       <c r="C2898">
-        <v>4420</v>
+        <v>4320</v>
       </c>
       <c r="D2898" t="s">
         <v>2900</v>
@@ -49898,7 +49898,7 @@
         <v>18</v>
       </c>
       <c r="C2899">
-        <v>4420</v>
+        <v>4310</v>
       </c>
       <c r="D2899" t="s">
         <v>2901</v>
@@ -49912,7 +49912,7 @@
         <v>19</v>
       </c>
       <c r="C2900">
-        <v>4420</v>
+        <v>4290</v>
       </c>
       <c r="D2900" t="s">
         <v>2902</v>
@@ -49926,7 +49926,7 @@
         <v>20</v>
       </c>
       <c r="C2901">
-        <v>4380</v>
+        <v>4270</v>
       </c>
       <c r="D2901" t="s">
         <v>2903</v>
@@ -49940,7 +49940,7 @@
         <v>21</v>
       </c>
       <c r="C2902">
-        <v>4340</v>
+        <v>4240</v>
       </c>
       <c r="D2902" t="s">
         <v>2904</v>
@@ -49954,7 +49954,7 @@
         <v>22</v>
       </c>
       <c r="C2903">
-        <v>4310</v>
+        <v>4220</v>
       </c>
       <c r="D2903" t="s">
         <v>2905</v>
@@ -49968,7 +49968,7 @@
         <v>23</v>
       </c>
       <c r="C2904">
-        <v>4300</v>
+        <v>4190</v>
       </c>
       <c r="D2904" t="s">
         <v>2906</v>
@@ -49982,7 +49982,7 @@
         <v>24</v>
       </c>
       <c r="C2905">
-        <v>4300</v>
+        <v>4160</v>
       </c>
       <c r="D2905" t="s">
         <v>2907</v>
@@ -49996,7 +49996,7 @@
         <v>25</v>
       </c>
       <c r="C2906">
-        <v>4290</v>
+        <v>4130</v>
       </c>
       <c r="D2906" t="s">
         <v>2908</v>
@@ -50010,7 +50010,7 @@
         <v>26</v>
       </c>
       <c r="C2907">
-        <v>4270</v>
+        <v>4090</v>
       </c>
       <c r="D2907" t="s">
         <v>2909</v>
@@ -50024,7 +50024,7 @@
         <v>27</v>
       </c>
       <c r="C2908">
-        <v>4250</v>
+        <v>4060</v>
       </c>
       <c r="D2908" t="s">
         <v>2910</v>
@@ -50038,7 +50038,7 @@
         <v>28</v>
       </c>
       <c r="C2909">
-        <v>4220</v>
+        <v>4020</v>
       </c>
       <c r="D2909" t="s">
         <v>2911</v>
@@ -50052,7 +50052,7 @@
         <v>29</v>
       </c>
       <c r="C2910">
-        <v>4190</v>
+        <v>3970</v>
       </c>
       <c r="D2910" t="s">
         <v>2912</v>
@@ -50066,7 +50066,7 @@
         <v>30</v>
       </c>
       <c r="C2911">
-        <v>4150</v>
+        <v>3930</v>
       </c>
       <c r="D2911" t="s">
         <v>2913</v>
@@ -50080,7 +50080,7 @@
         <v>31</v>
       </c>
       <c r="C2912">
-        <v>4100</v>
+        <v>3900</v>
       </c>
       <c r="D2912" t="s">
         <v>2914</v>
@@ -50094,7 +50094,7 @@
         <v>32</v>
       </c>
       <c r="C2913">
-        <v>4050</v>
+        <v>3840</v>
       </c>
       <c r="D2913" t="s">
         <v>2915</v>
@@ -50108,7 +50108,7 @@
         <v>33</v>
       </c>
       <c r="C2914">
-        <v>4000</v>
+        <v>3790</v>
       </c>
       <c r="D2914" t="s">
         <v>2916</v>
@@ -50122,7 +50122,7 @@
         <v>34</v>
       </c>
       <c r="C2915">
-        <v>3920</v>
+        <v>3730</v>
       </c>
       <c r="D2915" t="s">
         <v>2917</v>
@@ -50136,7 +50136,7 @@
         <v>35</v>
       </c>
       <c r="C2916">
-        <v>3880</v>
+        <v>3680</v>
       </c>
       <c r="D2916" t="s">
         <v>2918</v>
@@ -50150,7 +50150,7 @@
         <v>36</v>
       </c>
       <c r="C2917">
-        <v>3810</v>
+        <v>3610</v>
       </c>
       <c r="D2917" t="s">
         <v>2919</v>
@@ -50164,7 +50164,7 @@
         <v>37</v>
       </c>
       <c r="C2918">
-        <v>3730</v>
+        <v>3540</v>
       </c>
       <c r="D2918" t="s">
         <v>2920</v>
@@ -50178,7 +50178,7 @@
         <v>38</v>
       </c>
       <c r="C2919">
-        <v>3640</v>
+        <v>3470</v>
       </c>
       <c r="D2919" t="s">
         <v>2921</v>
@@ -50192,7 +50192,7 @@
         <v>39</v>
       </c>
       <c r="C2920">
-        <v>3550</v>
+        <v>3390</v>
       </c>
       <c r="D2920" t="s">
         <v>2922</v>
@@ -50206,7 +50206,7 @@
         <v>40</v>
       </c>
       <c r="C2921">
-        <v>3450</v>
+        <v>3320</v>
       </c>
       <c r="D2921" t="s">
         <v>2923</v>
@@ -50220,7 +50220,7 @@
         <v>41</v>
       </c>
       <c r="C2922">
-        <v>3360</v>
+        <v>3240</v>
       </c>
       <c r="D2922" t="s">
         <v>2924</v>
@@ -50234,7 +50234,7 @@
         <v>42</v>
       </c>
       <c r="C2923">
-        <v>3270</v>
+        <v>3170</v>
       </c>
       <c r="D2923" t="s">
         <v>2925</v>
@@ -50248,7 +50248,7 @@
         <v>43</v>
       </c>
       <c r="C2924">
-        <v>3190</v>
+        <v>3100</v>
       </c>
       <c r="D2924" t="s">
         <v>2926</v>
@@ -50262,7 +50262,7 @@
         <v>44</v>
       </c>
       <c r="C2925">
-        <v>3130</v>
+        <v>3040</v>
       </c>
       <c r="D2925" t="s">
         <v>2927</v>
@@ -50276,7 +50276,7 @@
         <v>45</v>
       </c>
       <c r="C2926">
-        <v>3070</v>
+        <v>2990</v>
       </c>
       <c r="D2926" t="s">
         <v>2928</v>
@@ -50290,7 +50290,7 @@
         <v>46</v>
       </c>
       <c r="C2927">
-        <v>3030</v>
+        <v>2940</v>
       </c>
       <c r="D2927" t="s">
         <v>2929</v>
@@ -50304,7 +50304,7 @@
         <v>47</v>
       </c>
       <c r="C2928">
-        <v>3000</v>
+        <v>2900</v>
       </c>
       <c r="D2928" t="s">
         <v>2930</v>
@@ -50318,7 +50318,7 @@
         <v>48</v>
       </c>
       <c r="C2929">
-        <v>2980</v>
+        <v>2870</v>
       </c>
       <c r="D2929" t="s">
         <v>2931</v>
@@ -50332,7 +50332,7 @@
         <v>49</v>
       </c>
       <c r="C2930">
-        <v>2970</v>
+        <v>2840</v>
       </c>
       <c r="D2930" t="s">
         <v>2932</v>
@@ -50346,7 +50346,7 @@
         <v>50</v>
       </c>
       <c r="C2931">
-        <v>2960</v>
+        <v>2820</v>
       </c>
       <c r="D2931" t="s">
         <v>2933</v>
@@ -50360,7 +50360,7 @@
         <v>51</v>
       </c>
       <c r="C2932">
-        <v>2950</v>
+        <v>2800</v>
       </c>
       <c r="D2932" t="s">
         <v>2934</v>
@@ -50374,7 +50374,7 @@
         <v>52</v>
       </c>
       <c r="C2933">
-        <v>2940</v>
+        <v>2790</v>
       </c>
       <c r="D2933" t="s">
         <v>2935</v>
@@ -50388,7 +50388,7 @@
         <v>53</v>
       </c>
       <c r="C2934">
-        <v>2940</v>
+        <v>2790</v>
       </c>
       <c r="D2934" t="s">
         <v>2936</v>
@@ -50402,7 +50402,7 @@
         <v>54</v>
       </c>
       <c r="C2935">
-        <v>2930</v>
+        <v>2800</v>
       </c>
       <c r="D2935" t="s">
         <v>2937</v>
@@ -50416,7 +50416,7 @@
         <v>55</v>
       </c>
       <c r="C2936">
-        <v>2930</v>
+        <v>2810</v>
       </c>
       <c r="D2936" t="s">
         <v>2938</v>
@@ -50430,7 +50430,7 @@
         <v>56</v>
       </c>
       <c r="C2937">
-        <v>2940</v>
+        <v>2830</v>
       </c>
       <c r="D2937" t="s">
         <v>2939</v>
@@ -50444,7 +50444,7 @@
         <v>57</v>
       </c>
       <c r="C2938">
-        <v>2950</v>
+        <v>2860</v>
       </c>
       <c r="D2938" t="s">
         <v>2940</v>
@@ -50458,7 +50458,7 @@
         <v>58</v>
       </c>
       <c r="C2939">
-        <v>2980</v>
+        <v>2890</v>
       </c>
       <c r="D2939" t="s">
         <v>2941</v>
@@ -50472,7 +50472,7 @@
         <v>59</v>
       </c>
       <c r="C2940">
-        <v>3010</v>
+        <v>2930</v>
       </c>
       <c r="D2940" t="s">
         <v>2942</v>
@@ -50486,7 +50486,7 @@
         <v>60</v>
       </c>
       <c r="C2941">
-        <v>3050</v>
+        <v>2960</v>
       </c>
       <c r="D2941" t="s">
         <v>2943</v>
@@ -50500,7 +50500,7 @@
         <v>61</v>
       </c>
       <c r="C2942">
-        <v>3100</v>
+        <v>3000</v>
       </c>
       <c r="D2942" t="s">
         <v>2944</v>
@@ -50514,7 +50514,7 @@
         <v>62</v>
       </c>
       <c r="C2943">
-        <v>3150</v>
+        <v>3050</v>
       </c>
       <c r="D2943" t="s">
         <v>2945</v>
@@ -50528,7 +50528,7 @@
         <v>63</v>
       </c>
       <c r="C2944">
-        <v>3210</v>
+        <v>3090</v>
       </c>
       <c r="D2944" t="s">
         <v>2946</v>
@@ -50542,7 +50542,7 @@
         <v>64</v>
       </c>
       <c r="C2945">
-        <v>3280</v>
+        <v>3150</v>
       </c>
       <c r="D2945" t="s">
         <v>2947</v>
@@ -50556,7 +50556,7 @@
         <v>65</v>
       </c>
       <c r="C2946">
-        <v>3360</v>
+        <v>3220</v>
       </c>
       <c r="D2946" t="s">
         <v>2948</v>
@@ -50570,7 +50570,7 @@
         <v>66</v>
       </c>
       <c r="C2947">
-        <v>3460</v>
+        <v>3300</v>
       </c>
       <c r="D2947" t="s">
         <v>2949</v>
@@ -50584,7 +50584,7 @@
         <v>67</v>
       </c>
       <c r="C2948">
-        <v>3560</v>
+        <v>3390</v>
       </c>
       <c r="D2948" t="s">
         <v>2950</v>
@@ -50598,7 +50598,7 @@
         <v>68</v>
       </c>
       <c r="C2949">
-        <v>3670</v>
+        <v>3500</v>
       </c>
       <c r="D2949" t="s">
         <v>2951</v>
@@ -50612,7 +50612,7 @@
         <v>69</v>
       </c>
       <c r="C2950">
-        <v>3790</v>
+        <v>3610</v>
       </c>
       <c r="D2950" t="s">
         <v>2952</v>
@@ -50626,7 +50626,7 @@
         <v>70</v>
       </c>
       <c r="C2951">
-        <v>3900</v>
+        <v>3730</v>
       </c>
       <c r="D2951" t="s">
         <v>2953</v>
@@ -50640,7 +50640,7 @@
         <v>71</v>
       </c>
       <c r="C2952">
-        <v>4010</v>
+        <v>3840</v>
       </c>
       <c r="D2952" t="s">
         <v>2954</v>
@@ -50654,7 +50654,7 @@
         <v>72</v>
       </c>
       <c r="C2953">
-        <v>4120</v>
+        <v>3960</v>
       </c>
       <c r="D2953" t="s">
         <v>2955</v>
@@ -50668,7 +50668,7 @@
         <v>73</v>
       </c>
       <c r="C2954">
-        <v>4220</v>
+        <v>4080</v>
       </c>
       <c r="D2954" t="s">
         <v>2956</v>
@@ -50682,7 +50682,7 @@
         <v>74</v>
       </c>
       <c r="C2955">
-        <v>4340</v>
+        <v>4210</v>
       </c>
       <c r="D2955" t="s">
         <v>2957</v>
@@ -50696,7 +50696,7 @@
         <v>75</v>
       </c>
       <c r="C2956">
-        <v>4460</v>
+        <v>4340</v>
       </c>
       <c r="D2956" t="s">
         <v>2958</v>
@@ -50710,7 +50710,7 @@
         <v>76</v>
       </c>
       <c r="C2957">
-        <v>4600</v>
+        <v>4480</v>
       </c>
       <c r="D2957" t="s">
         <v>2959</v>
@@ -50724,7 +50724,7 @@
         <v>77</v>
       </c>
       <c r="C2958">
-        <v>4740</v>
+        <v>4610</v>
       </c>
       <c r="D2958" t="s">
         <v>2960</v>
@@ -50738,7 +50738,7 @@
         <v>78</v>
       </c>
       <c r="C2959">
-        <v>4890</v>
+        <v>4730</v>
       </c>
       <c r="D2959" t="s">
         <v>2961</v>
@@ -50752,7 +50752,7 @@
         <v>79</v>
       </c>
       <c r="C2960">
-        <v>5030</v>
+        <v>4830</v>
       </c>
       <c r="D2960" t="s">
         <v>2962</v>
@@ -50766,7 +50766,7 @@
         <v>80</v>
       </c>
       <c r="C2961">
-        <v>5150</v>
+        <v>4900</v>
       </c>
       <c r="D2961" t="s">
         <v>2963</v>
@@ -50780,7 +50780,7 @@
         <v>81</v>
       </c>
       <c r="C2962">
-        <v>5270</v>
+        <v>4970</v>
       </c>
       <c r="D2962" t="s">
         <v>2964</v>
@@ -50794,7 +50794,7 @@
         <v>82</v>
       </c>
       <c r="C2963">
-        <v>5410</v>
+        <v>5070</v>
       </c>
       <c r="D2963" t="s">
         <v>2965</v>
@@ -50808,7 +50808,7 @@
         <v>83</v>
       </c>
       <c r="C2964">
-        <v>5540</v>
+        <v>5170</v>
       </c>
       <c r="D2964" t="s">
         <v>2966</v>
@@ -50822,7 +50822,7 @@
         <v>84</v>
       </c>
       <c r="C2965">
-        <v>5690</v>
+        <v>5300</v>
       </c>
       <c r="D2965" t="s">
         <v>2967</v>
@@ -50836,7 +50836,7 @@
         <v>85</v>
       </c>
       <c r="C2966">
-        <v>5770</v>
+        <v>5380</v>
       </c>
       <c r="D2966" t="s">
         <v>2968</v>
@@ -50850,7 +50850,7 @@
         <v>86</v>
       </c>
       <c r="C2967">
-        <v>5800</v>
+        <v>5420</v>
       </c>
       <c r="D2967" t="s">
         <v>2969</v>
@@ -50864,7 +50864,7 @@
         <v>87</v>
       </c>
       <c r="C2968">
-        <v>5820</v>
+        <v>5450</v>
       </c>
       <c r="D2968" t="s">
         <v>2970</v>
@@ -50878,7 +50878,7 @@
         <v>88</v>
       </c>
       <c r="C2969">
-        <v>5760</v>
+        <v>5440</v>
       </c>
       <c r="D2969" t="s">
         <v>2971</v>
@@ -50892,7 +50892,7 @@
         <v>89</v>
       </c>
       <c r="C2970">
-        <v>5620</v>
+        <v>5360</v>
       </c>
       <c r="D2970" t="s">
         <v>2972</v>
@@ -50906,7 +50906,7 @@
         <v>90</v>
       </c>
       <c r="C2971">
-        <v>5520</v>
+        <v>5300</v>
       </c>
       <c r="D2971" t="s">
         <v>2973</v>
@@ -50920,7 +50920,7 @@
         <v>91</v>
       </c>
       <c r="C2972">
-        <v>5390</v>
+        <v>5190</v>
       </c>
       <c r="D2972" t="s">
         <v>2974</v>
@@ -50934,7 +50934,7 @@
         <v>92</v>
       </c>
       <c r="C2973">
-        <v>5270</v>
+        <v>5070</v>
       </c>
       <c r="D2973" t="s">
         <v>2975</v>
@@ -50948,7 +50948,7 @@
         <v>93</v>
       </c>
       <c r="C2974">
-        <v>5110</v>
+        <v>4930</v>
       </c>
       <c r="D2974" t="s">
         <v>2976</v>
@@ -50962,7 +50962,7 @@
         <v>94</v>
       </c>
       <c r="C2975">
-        <v>4990</v>
+        <v>4840</v>
       </c>
       <c r="D2975" t="s">
         <v>2977</v>
@@ -50976,7 +50976,7 @@
         <v>95</v>
       </c>
       <c r="C2976">
-        <v>4890</v>
+        <v>4720</v>
       </c>
       <c r="D2976" t="s">
         <v>2978</v>
@@ -50990,7 +50990,7 @@
         <v>96</v>
       </c>
       <c r="C2977">
-        <v>4780</v>
+        <v>4620</v>
       </c>
       <c r="D2977" t="s">
         <v>2979</v>

--- a/Market Fundamentals/Transelectrica_data/Cons_Prod_final/Weekly_Consumption_2026.xlsx
+++ b/Market Fundamentals/Transelectrica_data/Cons_Prod_final/Weekly_Consumption_2026.xlsx
@@ -7324,7 +7324,7 @@
         <v>1</v>
       </c>
       <c r="C290">
-        <v>5280</v>
+        <v>5450</v>
       </c>
       <c r="D290" t="s">
         <v>292</v>
@@ -7338,7 +7338,7 @@
         <v>2</v>
       </c>
       <c r="C291">
-        <v>5250</v>
+        <v>5380</v>
       </c>
       <c r="D291" t="s">
         <v>293</v>
@@ -7352,7 +7352,7 @@
         <v>3</v>
       </c>
       <c r="C292">
-        <v>5190</v>
+        <v>5310</v>
       </c>
       <c r="D292" t="s">
         <v>294</v>
@@ -7366,7 +7366,7 @@
         <v>4</v>
       </c>
       <c r="C293">
-        <v>5120</v>
+        <v>5240</v>
       </c>
       <c r="D293" t="s">
         <v>295</v>
@@ -7380,7 +7380,7 @@
         <v>5</v>
       </c>
       <c r="C294">
-        <v>5080</v>
+        <v>5170</v>
       </c>
       <c r="D294" t="s">
         <v>296</v>
@@ -7394,7 +7394,7 @@
         <v>6</v>
       </c>
       <c r="C295">
-        <v>5040</v>
+        <v>5100</v>
       </c>
       <c r="D295" t="s">
         <v>297</v>
@@ -7408,7 +7408,7 @@
         <v>7</v>
       </c>
       <c r="C296">
-        <v>5000</v>
+        <v>5040</v>
       </c>
       <c r="D296" t="s">
         <v>298</v>
@@ -7422,7 +7422,7 @@
         <v>8</v>
       </c>
       <c r="C297">
-        <v>4960</v>
+        <v>4990</v>
       </c>
       <c r="D297" t="s">
         <v>299</v>
@@ -7436,7 +7436,7 @@
         <v>9</v>
       </c>
       <c r="C298">
-        <v>4920</v>
+        <v>4970</v>
       </c>
       <c r="D298" t="s">
         <v>300</v>
@@ -7450,7 +7450,7 @@
         <v>10</v>
       </c>
       <c r="C299">
-        <v>4890</v>
+        <v>4940</v>
       </c>
       <c r="D299" t="s">
         <v>301</v>
@@ -7464,7 +7464,7 @@
         <v>11</v>
       </c>
       <c r="C300">
-        <v>4870</v>
+        <v>4930</v>
       </c>
       <c r="D300" t="s">
         <v>302</v>
@@ -7478,7 +7478,7 @@
         <v>12</v>
       </c>
       <c r="C301">
-        <v>4860</v>
+        <v>4920</v>
       </c>
       <c r="D301" t="s">
         <v>303</v>
@@ -7492,7 +7492,7 @@
         <v>13</v>
       </c>
       <c r="C302">
-        <v>4860</v>
+        <v>4920</v>
       </c>
       <c r="D302" t="s">
         <v>304</v>
@@ -7506,7 +7506,7 @@
         <v>14</v>
       </c>
       <c r="C303">
-        <v>4870</v>
+        <v>4920</v>
       </c>
       <c r="D303" t="s">
         <v>305</v>
@@ -7520,7 +7520,7 @@
         <v>15</v>
       </c>
       <c r="C304">
-        <v>4880</v>
+        <v>4920</v>
       </c>
       <c r="D304" t="s">
         <v>306</v>
@@ -7534,7 +7534,7 @@
         <v>16</v>
       </c>
       <c r="C305">
-        <v>4890</v>
+        <v>4930</v>
       </c>
       <c r="D305" t="s">
         <v>307</v>
@@ -7548,7 +7548,7 @@
         <v>17</v>
       </c>
       <c r="C306">
-        <v>4900</v>
+        <v>4940</v>
       </c>
       <c r="D306" t="s">
         <v>308</v>
@@ -7562,7 +7562,7 @@
         <v>18</v>
       </c>
       <c r="C307">
-        <v>4910</v>
+        <v>4950</v>
       </c>
       <c r="D307" t="s">
         <v>309</v>
@@ -7576,7 +7576,7 @@
         <v>19</v>
       </c>
       <c r="C308">
-        <v>4930</v>
+        <v>4960</v>
       </c>
       <c r="D308" t="s">
         <v>310</v>
@@ -7590,7 +7590,7 @@
         <v>20</v>
       </c>
       <c r="C309">
-        <v>4960</v>
+        <v>4970</v>
       </c>
       <c r="D309" t="s">
         <v>311</v>
@@ -7604,7 +7604,7 @@
         <v>21</v>
       </c>
       <c r="C310">
-        <v>5010</v>
+        <v>4990</v>
       </c>
       <c r="D310" t="s">
         <v>312</v>
@@ -7618,7 +7618,7 @@
         <v>22</v>
       </c>
       <c r="C311">
-        <v>5070</v>
+        <v>5030</v>
       </c>
       <c r="D311" t="s">
         <v>313</v>
@@ -7632,7 +7632,7 @@
         <v>23</v>
       </c>
       <c r="C312">
-        <v>5150</v>
+        <v>5060</v>
       </c>
       <c r="D312" t="s">
         <v>314</v>
@@ -7646,7 +7646,7 @@
         <v>24</v>
       </c>
       <c r="C313">
-        <v>5240</v>
+        <v>5100</v>
       </c>
       <c r="D313" t="s">
         <v>315</v>
@@ -7660,7 +7660,7 @@
         <v>25</v>
       </c>
       <c r="C314">
-        <v>5350</v>
+        <v>5150</v>
       </c>
       <c r="D314" t="s">
         <v>316</v>
@@ -7674,7 +7674,7 @@
         <v>26</v>
       </c>
       <c r="C315">
-        <v>5470</v>
+        <v>5210</v>
       </c>
       <c r="D315" t="s">
         <v>317</v>
@@ -7688,7 +7688,7 @@
         <v>27</v>
       </c>
       <c r="C316">
-        <v>5600</v>
+        <v>5280</v>
       </c>
       <c r="D316" t="s">
         <v>318</v>
@@ -7702,7 +7702,7 @@
         <v>28</v>
       </c>
       <c r="C317">
-        <v>5730</v>
+        <v>5390</v>
       </c>
       <c r="D317" t="s">
         <v>319</v>
@@ -7716,7 +7716,7 @@
         <v>29</v>
       </c>
       <c r="C318">
-        <v>5860</v>
+        <v>5530</v>
       </c>
       <c r="D318" t="s">
         <v>320</v>
@@ -7730,7 +7730,7 @@
         <v>30</v>
       </c>
       <c r="C319">
-        <v>5970</v>
+        <v>5630</v>
       </c>
       <c r="D319" t="s">
         <v>321</v>
@@ -7744,7 +7744,7 @@
         <v>31</v>
       </c>
       <c r="C320">
-        <v>6060</v>
+        <v>5700</v>
       </c>
       <c r="D320" t="s">
         <v>322</v>
@@ -7758,7 +7758,7 @@
         <v>32</v>
       </c>
       <c r="C321">
-        <v>6140</v>
+        <v>5740</v>
       </c>
       <c r="D321" t="s">
         <v>323</v>
@@ -7772,7 +7772,7 @@
         <v>33</v>
       </c>
       <c r="C322">
-        <v>6180</v>
+        <v>5760</v>
       </c>
       <c r="D322" t="s">
         <v>324</v>
@@ -7786,7 +7786,7 @@
         <v>34</v>
       </c>
       <c r="C323">
-        <v>6200</v>
+        <v>5760</v>
       </c>
       <c r="D323" t="s">
         <v>325</v>
@@ -7800,7 +7800,7 @@
         <v>35</v>
       </c>
       <c r="C324">
-        <v>6200</v>
+        <v>5750</v>
       </c>
       <c r="D324" t="s">
         <v>326</v>
@@ -7814,7 +7814,7 @@
         <v>36</v>
       </c>
       <c r="C325">
-        <v>6170</v>
+        <v>5700</v>
       </c>
       <c r="D325" t="s">
         <v>327</v>
@@ -7828,7 +7828,7 @@
         <v>37</v>
       </c>
       <c r="C326">
-        <v>6120</v>
+        <v>5610</v>
       </c>
       <c r="D326" t="s">
         <v>328</v>
@@ -7842,7 +7842,7 @@
         <v>38</v>
       </c>
       <c r="C327">
-        <v>6050</v>
+        <v>5510</v>
       </c>
       <c r="D327" t="s">
         <v>329</v>
@@ -7856,7 +7856,7 @@
         <v>39</v>
       </c>
       <c r="C328">
-        <v>5970</v>
+        <v>5410</v>
       </c>
       <c r="D328" t="s">
         <v>330</v>
@@ -7870,7 +7870,7 @@
         <v>40</v>
       </c>
       <c r="C329">
-        <v>5880</v>
+        <v>5290</v>
       </c>
       <c r="D329" t="s">
         <v>331</v>
@@ -7884,7 +7884,7 @@
         <v>41</v>
       </c>
       <c r="C330">
-        <v>5800</v>
+        <v>5180</v>
       </c>
       <c r="D330" t="s">
         <v>332</v>
@@ -7898,7 +7898,7 @@
         <v>42</v>
       </c>
       <c r="C331">
-        <v>5730</v>
+        <v>5080</v>
       </c>
       <c r="D331" t="s">
         <v>333</v>
@@ -7912,7 +7912,7 @@
         <v>43</v>
       </c>
       <c r="C332">
-        <v>5660</v>
+        <v>4980</v>
       </c>
       <c r="D332" t="s">
         <v>334</v>
@@ -7926,7 +7926,7 @@
         <v>44</v>
       </c>
       <c r="C333">
-        <v>5610</v>
+        <v>4900</v>
       </c>
       <c r="D333" t="s">
         <v>335</v>
@@ -7940,7 +7940,7 @@
         <v>45</v>
       </c>
       <c r="C334">
-        <v>5560</v>
+        <v>4820</v>
       </c>
       <c r="D334" t="s">
         <v>336</v>
@@ -7954,7 +7954,7 @@
         <v>46</v>
       </c>
       <c r="C335">
-        <v>5530</v>
+        <v>4760</v>
       </c>
       <c r="D335" t="s">
         <v>337</v>
@@ -7968,7 +7968,7 @@
         <v>47</v>
       </c>
       <c r="C336">
-        <v>5510</v>
+        <v>4730</v>
       </c>
       <c r="D336" t="s">
         <v>338</v>
@@ -7982,7 +7982,7 @@
         <v>48</v>
       </c>
       <c r="C337">
-        <v>5490</v>
+        <v>4700</v>
       </c>
       <c r="D337" t="s">
         <v>339</v>
@@ -7996,7 +7996,7 @@
         <v>49</v>
       </c>
       <c r="C338">
-        <v>5480</v>
+        <v>4680</v>
       </c>
       <c r="D338" t="s">
         <v>340</v>
@@ -8010,7 +8010,7 @@
         <v>50</v>
       </c>
       <c r="C339">
-        <v>5470</v>
+        <v>4660</v>
       </c>
       <c r="D339" t="s">
         <v>341</v>
@@ -8024,7 +8024,7 @@
         <v>51</v>
       </c>
       <c r="C340">
-        <v>5460</v>
+        <v>4650</v>
       </c>
       <c r="D340" t="s">
         <v>342</v>
@@ -8038,7 +8038,7 @@
         <v>52</v>
       </c>
       <c r="C341">
-        <v>5450</v>
+        <v>4650</v>
       </c>
       <c r="D341" t="s">
         <v>343</v>
@@ -8052,7 +8052,7 @@
         <v>53</v>
       </c>
       <c r="C342">
-        <v>5440</v>
+        <v>4660</v>
       </c>
       <c r="D342" t="s">
         <v>344</v>
@@ -8066,7 +8066,7 @@
         <v>54</v>
       </c>
       <c r="C343">
-        <v>5440</v>
+        <v>4700</v>
       </c>
       <c r="D343" t="s">
         <v>345</v>
@@ -8080,7 +8080,7 @@
         <v>55</v>
       </c>
       <c r="C344">
-        <v>5440</v>
+        <v>4740</v>
       </c>
       <c r="D344" t="s">
         <v>346</v>
@@ -8094,7 +8094,7 @@
         <v>56</v>
       </c>
       <c r="C345">
-        <v>5450</v>
+        <v>4780</v>
       </c>
       <c r="D345" t="s">
         <v>347</v>
@@ -8108,7 +8108,7 @@
         <v>57</v>
       </c>
       <c r="C346">
-        <v>5450</v>
+        <v>4810</v>
       </c>
       <c r="D346" t="s">
         <v>348</v>
@@ -8122,7 +8122,7 @@
         <v>58</v>
       </c>
       <c r="C347">
-        <v>5470</v>
+        <v>4830</v>
       </c>
       <c r="D347" t="s">
         <v>349</v>
@@ -8136,7 +8136,7 @@
         <v>59</v>
       </c>
       <c r="C348">
-        <v>5480</v>
+        <v>4860</v>
       </c>
       <c r="D348" t="s">
         <v>350</v>
@@ -8150,7 +8150,7 @@
         <v>60</v>
       </c>
       <c r="C349">
-        <v>5490</v>
+        <v>4910</v>
       </c>
       <c r="D349" t="s">
         <v>351</v>
@@ -8164,7 +8164,7 @@
         <v>61</v>
       </c>
       <c r="C350">
-        <v>5490</v>
+        <v>4970</v>
       </c>
       <c r="D350" t="s">
         <v>352</v>
@@ -8178,7 +8178,7 @@
         <v>62</v>
       </c>
       <c r="C351">
-        <v>5500</v>
+        <v>5020</v>
       </c>
       <c r="D351" t="s">
         <v>353</v>
@@ -8192,7 +8192,7 @@
         <v>63</v>
       </c>
       <c r="C352">
-        <v>5510</v>
+        <v>5070</v>
       </c>
       <c r="D352" t="s">
         <v>354</v>
@@ -8206,7 +8206,7 @@
         <v>64</v>
       </c>
       <c r="C353">
-        <v>5520</v>
+        <v>5130</v>
       </c>
       <c r="D353" t="s">
         <v>355</v>
@@ -8220,7 +8220,7 @@
         <v>65</v>
       </c>
       <c r="C354">
-        <v>5540</v>
+        <v>5190</v>
       </c>
       <c r="D354" t="s">
         <v>356</v>
@@ -8234,7 +8234,7 @@
         <v>66</v>
       </c>
       <c r="C355">
-        <v>5580</v>
+        <v>5270</v>
       </c>
       <c r="D355" t="s">
         <v>357</v>
@@ -8248,7 +8248,7 @@
         <v>67</v>
       </c>
       <c r="C356">
-        <v>5630</v>
+        <v>5360</v>
       </c>
       <c r="D356" t="s">
         <v>358</v>
@@ -8262,7 +8262,7 @@
         <v>68</v>
       </c>
       <c r="C357">
-        <v>5700</v>
+        <v>5450</v>
       </c>
       <c r="D357" t="s">
         <v>359</v>
@@ -8276,7 +8276,7 @@
         <v>69</v>
       </c>
       <c r="C358">
-        <v>5770</v>
+        <v>5550</v>
       </c>
       <c r="D358" t="s">
         <v>360</v>
@@ -8290,7 +8290,7 @@
         <v>70</v>
       </c>
       <c r="C359">
-        <v>5840</v>
+        <v>5630</v>
       </c>
       <c r="D359" t="s">
         <v>361</v>
@@ -8304,7 +8304,7 @@
         <v>71</v>
       </c>
       <c r="C360">
-        <v>5900</v>
+        <v>5710</v>
       </c>
       <c r="D360" t="s">
         <v>362</v>
@@ -8318,7 +8318,7 @@
         <v>72</v>
       </c>
       <c r="C361">
-        <v>5970</v>
+        <v>5800</v>
       </c>
       <c r="D361" t="s">
         <v>363</v>
@@ -8332,7 +8332,7 @@
         <v>73</v>
       </c>
       <c r="C362">
-        <v>6030</v>
+        <v>5900</v>
       </c>
       <c r="D362" t="s">
         <v>364</v>
@@ -8346,7 +8346,7 @@
         <v>74</v>
       </c>
       <c r="C363">
-        <v>6100</v>
+        <v>5980</v>
       </c>
       <c r="D363" t="s">
         <v>365</v>
@@ -8360,7 +8360,7 @@
         <v>75</v>
       </c>
       <c r="C364">
-        <v>6180</v>
+        <v>6070</v>
       </c>
       <c r="D364" t="s">
         <v>366</v>
@@ -8374,7 +8374,7 @@
         <v>76</v>
       </c>
       <c r="C365">
-        <v>6280</v>
+        <v>6160</v>
       </c>
       <c r="D365" t="s">
         <v>367</v>
@@ -8388,7 +8388,7 @@
         <v>77</v>
       </c>
       <c r="C366">
-        <v>6380</v>
+        <v>6240</v>
       </c>
       <c r="D366" t="s">
         <v>368</v>
@@ -8402,7 +8402,7 @@
         <v>78</v>
       </c>
       <c r="C367">
-        <v>6480</v>
+        <v>6320</v>
       </c>
       <c r="D367" t="s">
         <v>369</v>
@@ -8416,7 +8416,7 @@
         <v>79</v>
       </c>
       <c r="C368">
-        <v>6560</v>
+        <v>6390</v>
       </c>
       <c r="D368" t="s">
         <v>370</v>
@@ -8430,7 +8430,7 @@
         <v>80</v>
       </c>
       <c r="C369">
-        <v>6610</v>
+        <v>6450</v>
       </c>
       <c r="D369" t="s">
         <v>371</v>
@@ -8444,7 +8444,7 @@
         <v>81</v>
       </c>
       <c r="C370">
-        <v>6660</v>
+        <v>6500</v>
       </c>
       <c r="D370" t="s">
         <v>372</v>
@@ -8458,7 +8458,7 @@
         <v>82</v>
       </c>
       <c r="C371">
-        <v>6700</v>
+        <v>6550</v>
       </c>
       <c r="D371" t="s">
         <v>373</v>
@@ -8472,7 +8472,7 @@
         <v>83</v>
       </c>
       <c r="C372">
-        <v>6720</v>
+        <v>6600</v>
       </c>
       <c r="D372" t="s">
         <v>374</v>
@@ -8486,7 +8486,7 @@
         <v>84</v>
       </c>
       <c r="C373">
-        <v>6770</v>
+        <v>6660</v>
       </c>
       <c r="D373" t="s">
         <v>375</v>
@@ -8500,7 +8500,7 @@
         <v>85</v>
       </c>
       <c r="C374">
-        <v>6760</v>
+        <v>6700</v>
       </c>
       <c r="D374" t="s">
         <v>376</v>
@@ -8528,7 +8528,7 @@
         <v>87</v>
       </c>
       <c r="C376">
-        <v>6690</v>
+        <v>6700</v>
       </c>
       <c r="D376" t="s">
         <v>378</v>
@@ -8542,7 +8542,7 @@
         <v>88</v>
       </c>
       <c r="C377">
-        <v>6600</v>
+        <v>6640</v>
       </c>
       <c r="D377" t="s">
         <v>379</v>
@@ -8556,7 +8556,7 @@
         <v>89</v>
       </c>
       <c r="C378">
-        <v>6460</v>
+        <v>6520</v>
       </c>
       <c r="D378" t="s">
         <v>380</v>
@@ -8570,7 +8570,7 @@
         <v>90</v>
       </c>
       <c r="C379">
-        <v>6370</v>
+        <v>6380</v>
       </c>
       <c r="D379" t="s">
         <v>381</v>
@@ -8584,7 +8584,7 @@
         <v>91</v>
       </c>
       <c r="C380">
-        <v>6230</v>
+        <v>6220</v>
       </c>
       <c r="D380" t="s">
         <v>382</v>
@@ -8598,7 +8598,7 @@
         <v>92</v>
       </c>
       <c r="C381">
-        <v>6080</v>
+        <v>6040</v>
       </c>
       <c r="D381" t="s">
         <v>383</v>
@@ -8612,7 +8612,7 @@
         <v>93</v>
       </c>
       <c r="C382">
-        <v>5870</v>
+        <v>5900</v>
       </c>
       <c r="D382" t="s">
         <v>384</v>
@@ -8626,7 +8626,7 @@
         <v>94</v>
       </c>
       <c r="C383">
-        <v>5720</v>
+        <v>5750</v>
       </c>
       <c r="D383" t="s">
         <v>385</v>
@@ -8640,7 +8640,7 @@
         <v>95</v>
       </c>
       <c r="C384">
-        <v>5630</v>
+        <v>5640</v>
       </c>
       <c r="D384" t="s">
         <v>386</v>
@@ -8668,7 +8668,7 @@
         <v>1</v>
       </c>
       <c r="C386">
-        <v>5540</v>
+        <v>5400</v>
       </c>
       <c r="D386" t="s">
         <v>388</v>
@@ -8682,7 +8682,7 @@
         <v>2</v>
       </c>
       <c r="C387">
-        <v>5460</v>
+        <v>5330</v>
       </c>
       <c r="D387" t="s">
         <v>389</v>
@@ -8696,7 +8696,7 @@
         <v>3</v>
       </c>
       <c r="C388">
-        <v>5380</v>
+        <v>5250</v>
       </c>
       <c r="D388" t="s">
         <v>390</v>
@@ -8710,7 +8710,7 @@
         <v>4</v>
       </c>
       <c r="C389">
-        <v>5320</v>
+        <v>5200</v>
       </c>
       <c r="D389" t="s">
         <v>391</v>
@@ -8724,7 +8724,7 @@
         <v>5</v>
       </c>
       <c r="C390">
-        <v>5260</v>
+        <v>5140</v>
       </c>
       <c r="D390" t="s">
         <v>392</v>
@@ -8738,7 +8738,7 @@
         <v>6</v>
       </c>
       <c r="C391">
-        <v>5210</v>
+        <v>5100</v>
       </c>
       <c r="D391" t="s">
         <v>393</v>
@@ -8752,7 +8752,7 @@
         <v>7</v>
       </c>
       <c r="C392">
-        <v>5170</v>
+        <v>5060</v>
       </c>
       <c r="D392" t="s">
         <v>394</v>
@@ -8766,7 +8766,7 @@
         <v>8</v>
       </c>
       <c r="C393">
-        <v>5130</v>
+        <v>5020</v>
       </c>
       <c r="D393" t="s">
         <v>395</v>
@@ -8780,7 +8780,7 @@
         <v>9</v>
       </c>
       <c r="C394">
-        <v>5090</v>
+        <v>4970</v>
       </c>
       <c r="D394" t="s">
         <v>396</v>
@@ -8794,7 +8794,7 @@
         <v>10</v>
       </c>
       <c r="C395">
-        <v>5070</v>
+        <v>4940</v>
       </c>
       <c r="D395" t="s">
         <v>397</v>
@@ -8808,7 +8808,7 @@
         <v>11</v>
       </c>
       <c r="C396">
-        <v>5050</v>
+        <v>4920</v>
       </c>
       <c r="D396" t="s">
         <v>398</v>
@@ -8822,7 +8822,7 @@
         <v>12</v>
       </c>
       <c r="C397">
-        <v>5040</v>
+        <v>4910</v>
       </c>
       <c r="D397" t="s">
         <v>399</v>
@@ -8836,7 +8836,7 @@
         <v>13</v>
       </c>
       <c r="C398">
-        <v>5030</v>
+        <v>4900</v>
       </c>
       <c r="D398" t="s">
         <v>400</v>
@@ -8850,7 +8850,7 @@
         <v>14</v>
       </c>
       <c r="C399">
-        <v>5030</v>
+        <v>4900</v>
       </c>
       <c r="D399" t="s">
         <v>401</v>
@@ -8864,7 +8864,7 @@
         <v>15</v>
       </c>
       <c r="C400">
-        <v>5030</v>
+        <v>4900</v>
       </c>
       <c r="D400" t="s">
         <v>402</v>
@@ -8878,7 +8878,7 @@
         <v>16</v>
       </c>
       <c r="C401">
-        <v>5030</v>
+        <v>4910</v>
       </c>
       <c r="D401" t="s">
         <v>403</v>
@@ -8892,7 +8892,7 @@
         <v>17</v>
       </c>
       <c r="C402">
-        <v>5040</v>
+        <v>4920</v>
       </c>
       <c r="D402" t="s">
         <v>404</v>
@@ -8906,7 +8906,7 @@
         <v>18</v>
       </c>
       <c r="C403">
-        <v>5040</v>
+        <v>4930</v>
       </c>
       <c r="D403" t="s">
         <v>405</v>
@@ -8920,7 +8920,7 @@
         <v>19</v>
       </c>
       <c r="C404">
-        <v>5060</v>
+        <v>4950</v>
       </c>
       <c r="D404" t="s">
         <v>406</v>
@@ -8934,7 +8934,7 @@
         <v>20</v>
       </c>
       <c r="C405">
-        <v>5080</v>
+        <v>4960</v>
       </c>
       <c r="D405" t="s">
         <v>407</v>
@@ -8948,7 +8948,7 @@
         <v>21</v>
       </c>
       <c r="C406">
-        <v>5110</v>
+        <v>4990</v>
       </c>
       <c r="D406" t="s">
         <v>408</v>
@@ -8962,7 +8962,7 @@
         <v>22</v>
       </c>
       <c r="C407">
-        <v>5140</v>
+        <v>5040</v>
       </c>
       <c r="D407" t="s">
         <v>409</v>
@@ -8976,7 +8976,7 @@
         <v>23</v>
       </c>
       <c r="C408">
-        <v>5170</v>
+        <v>5100</v>
       </c>
       <c r="D408" t="s">
         <v>410</v>
@@ -8990,7 +8990,7 @@
         <v>24</v>
       </c>
       <c r="C409">
-        <v>5220</v>
+        <v>5180</v>
       </c>
       <c r="D409" t="s">
         <v>411</v>
@@ -9004,7 +9004,7 @@
         <v>25</v>
       </c>
       <c r="C410">
-        <v>5270</v>
+        <v>5280</v>
       </c>
       <c r="D410" t="s">
         <v>412</v>
@@ -9018,7 +9018,7 @@
         <v>26</v>
       </c>
       <c r="C411">
-        <v>5330</v>
+        <v>5380</v>
       </c>
       <c r="D411" t="s">
         <v>413</v>
@@ -9032,7 +9032,7 @@
         <v>27</v>
       </c>
       <c r="C412">
-        <v>5410</v>
+        <v>5480</v>
       </c>
       <c r="D412" t="s">
         <v>414</v>
@@ -9046,7 +9046,7 @@
         <v>28</v>
       </c>
       <c r="C413">
-        <v>5500</v>
+        <v>5550</v>
       </c>
       <c r="D413" t="s">
         <v>415</v>
@@ -9060,7 +9060,7 @@
         <v>29</v>
       </c>
       <c r="C414">
-        <v>5610</v>
+        <v>5630</v>
       </c>
       <c r="D414" t="s">
         <v>416</v>
@@ -9088,7 +9088,7 @@
         <v>31</v>
       </c>
       <c r="C416">
-        <v>5760</v>
+        <v>5740</v>
       </c>
       <c r="D416" t="s">
         <v>418</v>
@@ -9102,7 +9102,7 @@
         <v>32</v>
       </c>
       <c r="C417">
-        <v>5810</v>
+        <v>5750</v>
       </c>
       <c r="D417" t="s">
         <v>419</v>
@@ -9116,7 +9116,7 @@
         <v>33</v>
       </c>
       <c r="C418">
-        <v>5830</v>
+        <v>5750</v>
       </c>
       <c r="D418" t="s">
         <v>420</v>
@@ -9130,7 +9130,7 @@
         <v>34</v>
       </c>
       <c r="C419">
-        <v>5820</v>
+        <v>5740</v>
       </c>
       <c r="D419" t="s">
         <v>421</v>
@@ -9144,7 +9144,7 @@
         <v>35</v>
       </c>
       <c r="C420">
-        <v>5780</v>
+        <v>5720</v>
       </c>
       <c r="D420" t="s">
         <v>422</v>
@@ -9158,7 +9158,7 @@
         <v>36</v>
       </c>
       <c r="C421">
-        <v>5700</v>
+        <v>5670</v>
       </c>
       <c r="D421" t="s">
         <v>423</v>
@@ -9186,7 +9186,7 @@
         <v>38</v>
       </c>
       <c r="C423">
-        <v>5510</v>
+        <v>5520</v>
       </c>
       <c r="D423" t="s">
         <v>425</v>
@@ -9200,7 +9200,7 @@
         <v>39</v>
       </c>
       <c r="C424">
-        <v>5420</v>
+        <v>5440</v>
       </c>
       <c r="D424" t="s">
         <v>426</v>
@@ -9214,7 +9214,7 @@
         <v>40</v>
       </c>
       <c r="C425">
-        <v>5350</v>
+        <v>5340</v>
       </c>
       <c r="D425" t="s">
         <v>427</v>
@@ -9228,7 +9228,7 @@
         <v>41</v>
       </c>
       <c r="C426">
-        <v>5290</v>
+        <v>5230</v>
       </c>
       <c r="D426" t="s">
         <v>428</v>
@@ -9242,7 +9242,7 @@
         <v>42</v>
       </c>
       <c r="C427">
-        <v>5220</v>
+        <v>5130</v>
       </c>
       <c r="D427" t="s">
         <v>429</v>
@@ -9256,7 +9256,7 @@
         <v>43</v>
       </c>
       <c r="C428">
-        <v>5130</v>
+        <v>5030</v>
       </c>
       <c r="D428" t="s">
         <v>430</v>
@@ -9270,7 +9270,7 @@
         <v>44</v>
       </c>
       <c r="C429">
-        <v>5020</v>
+        <v>4930</v>
       </c>
       <c r="D429" t="s">
         <v>431</v>
@@ -9284,7 +9284,7 @@
         <v>45</v>
       </c>
       <c r="C430">
-        <v>4910</v>
+        <v>4850</v>
       </c>
       <c r="D430" t="s">
         <v>432</v>
@@ -9298,7 +9298,7 @@
         <v>46</v>
       </c>
       <c r="C431">
-        <v>4810</v>
+        <v>4770</v>
       </c>
       <c r="D431" t="s">
         <v>433</v>
@@ -9312,7 +9312,7 @@
         <v>47</v>
       </c>
       <c r="C432">
-        <v>4750</v>
+        <v>4710</v>
       </c>
       <c r="D432" t="s">
         <v>434</v>
@@ -9326,7 +9326,7 @@
         <v>48</v>
       </c>
       <c r="C433">
-        <v>4710</v>
+        <v>4660</v>
       </c>
       <c r="D433" t="s">
         <v>435</v>
@@ -9340,7 +9340,7 @@
         <v>49</v>
       </c>
       <c r="C434">
-        <v>4690</v>
+        <v>4620</v>
       </c>
       <c r="D434" t="s">
         <v>436</v>
@@ -9354,7 +9354,7 @@
         <v>50</v>
       </c>
       <c r="C435">
-        <v>4690</v>
+        <v>4580</v>
       </c>
       <c r="D435" t="s">
         <v>437</v>
@@ -9368,7 +9368,7 @@
         <v>51</v>
       </c>
       <c r="C436">
-        <v>4690</v>
+        <v>4560</v>
       </c>
       <c r="D436" t="s">
         <v>438</v>
@@ -9382,7 +9382,7 @@
         <v>52</v>
       </c>
       <c r="C437">
-        <v>4700</v>
+        <v>4550</v>
       </c>
       <c r="D437" t="s">
         <v>439</v>
@@ -9396,7 +9396,7 @@
         <v>53</v>
       </c>
       <c r="C438">
-        <v>4720</v>
+        <v>4540</v>
       </c>
       <c r="D438" t="s">
         <v>440</v>
@@ -9410,7 +9410,7 @@
         <v>54</v>
       </c>
       <c r="C439">
-        <v>4730</v>
+        <v>4530</v>
       </c>
       <c r="D439" t="s">
         <v>441</v>
@@ -9424,7 +9424,7 @@
         <v>55</v>
       </c>
       <c r="C440">
-        <v>4740</v>
+        <v>4540</v>
       </c>
       <c r="D440" t="s">
         <v>442</v>
@@ -9438,7 +9438,7 @@
         <v>56</v>
       </c>
       <c r="C441">
-        <v>4740</v>
+        <v>4540</v>
       </c>
       <c r="D441" t="s">
         <v>443</v>
@@ -9452,7 +9452,7 @@
         <v>57</v>
       </c>
       <c r="C442">
-        <v>4730</v>
+        <v>4560</v>
       </c>
       <c r="D442" t="s">
         <v>444</v>
@@ -9466,7 +9466,7 @@
         <v>58</v>
       </c>
       <c r="C443">
-        <v>4750</v>
+        <v>4580</v>
       </c>
       <c r="D443" t="s">
         <v>445</v>
@@ -9480,7 +9480,7 @@
         <v>59</v>
       </c>
       <c r="C444">
-        <v>4780</v>
+        <v>4600</v>
       </c>
       <c r="D444" t="s">
         <v>446</v>
@@ -9494,7 +9494,7 @@
         <v>60</v>
       </c>
       <c r="C445">
-        <v>4820</v>
+        <v>4630</v>
       </c>
       <c r="D445" t="s">
         <v>447</v>
@@ -9508,7 +9508,7 @@
         <v>61</v>
       </c>
       <c r="C446">
-        <v>4890</v>
+        <v>4670</v>
       </c>
       <c r="D446" t="s">
         <v>448</v>
@@ -9522,7 +9522,7 @@
         <v>62</v>
       </c>
       <c r="C447">
-        <v>4960</v>
+        <v>4710</v>
       </c>
       <c r="D447" t="s">
         <v>449</v>
@@ -9536,7 +9536,7 @@
         <v>63</v>
       </c>
       <c r="C448">
-        <v>5020</v>
+        <v>4760</v>
       </c>
       <c r="D448" t="s">
         <v>450</v>
@@ -9550,7 +9550,7 @@
         <v>64</v>
       </c>
       <c r="C449">
-        <v>5090</v>
+        <v>4820</v>
       </c>
       <c r="D449" t="s">
         <v>451</v>
@@ -9564,7 +9564,7 @@
         <v>65</v>
       </c>
       <c r="C450">
-        <v>5160</v>
+        <v>4890</v>
       </c>
       <c r="D450" t="s">
         <v>452</v>
@@ -9578,7 +9578,7 @@
         <v>66</v>
       </c>
       <c r="C451">
-        <v>5240</v>
+        <v>4970</v>
       </c>
       <c r="D451" t="s">
         <v>453</v>
@@ -9592,7 +9592,7 @@
         <v>67</v>
       </c>
       <c r="C452">
-        <v>5320</v>
+        <v>5060</v>
       </c>
       <c r="D452" t="s">
         <v>454</v>
@@ -9606,7 +9606,7 @@
         <v>68</v>
       </c>
       <c r="C453">
-        <v>5410</v>
+        <v>5160</v>
       </c>
       <c r="D453" t="s">
         <v>455</v>
@@ -9620,7 +9620,7 @@
         <v>69</v>
       </c>
       <c r="C454">
-        <v>5510</v>
+        <v>5260</v>
       </c>
       <c r="D454" t="s">
         <v>456</v>
@@ -9634,7 +9634,7 @@
         <v>70</v>
       </c>
       <c r="C455">
-        <v>5610</v>
+        <v>5360</v>
       </c>
       <c r="D455" t="s">
         <v>457</v>
@@ -9648,7 +9648,7 @@
         <v>71</v>
       </c>
       <c r="C456">
-        <v>5710</v>
+        <v>5460</v>
       </c>
       <c r="D456" t="s">
         <v>458</v>
@@ -9662,7 +9662,7 @@
         <v>72</v>
       </c>
       <c r="C457">
-        <v>5810</v>
+        <v>5550</v>
       </c>
       <c r="D457" t="s">
         <v>459</v>
@@ -9676,7 +9676,7 @@
         <v>73</v>
       </c>
       <c r="C458">
-        <v>5910</v>
+        <v>5640</v>
       </c>
       <c r="D458" t="s">
         <v>460</v>
@@ -9690,7 +9690,7 @@
         <v>74</v>
       </c>
       <c r="C459">
-        <v>6010</v>
+        <v>5740</v>
       </c>
       <c r="D459" t="s">
         <v>461</v>
@@ -9704,7 +9704,7 @@
         <v>75</v>
       </c>
       <c r="C460">
-        <v>6110</v>
+        <v>5840</v>
       </c>
       <c r="D460" t="s">
         <v>462</v>
@@ -9718,7 +9718,7 @@
         <v>76</v>
       </c>
       <c r="C461">
-        <v>6220</v>
+        <v>5960</v>
       </c>
       <c r="D461" t="s">
         <v>463</v>
@@ -9732,7 +9732,7 @@
         <v>77</v>
       </c>
       <c r="C462">
-        <v>6330</v>
+        <v>6070</v>
       </c>
       <c r="D462" t="s">
         <v>464</v>
@@ -9746,7 +9746,7 @@
         <v>78</v>
       </c>
       <c r="C463">
-        <v>6420</v>
+        <v>6180</v>
       </c>
       <c r="D463" t="s">
         <v>465</v>
@@ -9760,7 +9760,7 @@
         <v>79</v>
       </c>
       <c r="C464">
-        <v>6490</v>
+        <v>6260</v>
       </c>
       <c r="D464" t="s">
         <v>466</v>
@@ -9774,7 +9774,7 @@
         <v>80</v>
       </c>
       <c r="C465">
-        <v>6540</v>
+        <v>6350</v>
       </c>
       <c r="D465" t="s">
         <v>467</v>
@@ -9788,7 +9788,7 @@
         <v>81</v>
       </c>
       <c r="C466">
-        <v>6560</v>
+        <v>6420</v>
       </c>
       <c r="D466" t="s">
         <v>468</v>
@@ -9802,7 +9802,7 @@
         <v>82</v>
       </c>
       <c r="C467">
-        <v>6600</v>
+        <v>6500</v>
       </c>
       <c r="D467" t="s">
         <v>469</v>
@@ -9816,7 +9816,7 @@
         <v>83</v>
       </c>
       <c r="C468">
-        <v>6660</v>
+        <v>6530</v>
       </c>
       <c r="D468" t="s">
         <v>470</v>
@@ -9830,7 +9830,7 @@
         <v>84</v>
       </c>
       <c r="C469">
-        <v>6720</v>
+        <v>6550</v>
       </c>
       <c r="D469" t="s">
         <v>471</v>
@@ -9844,7 +9844,7 @@
         <v>85</v>
       </c>
       <c r="C470">
-        <v>6800</v>
+        <v>6550</v>
       </c>
       <c r="D470" t="s">
         <v>472</v>
@@ -9858,7 +9858,7 @@
         <v>86</v>
       </c>
       <c r="C471">
-        <v>6830</v>
+        <v>6550</v>
       </c>
       <c r="D471" t="s">
         <v>473</v>
@@ -9872,7 +9872,7 @@
         <v>87</v>
       </c>
       <c r="C472">
-        <v>6810</v>
+        <v>6540</v>
       </c>
       <c r="D472" t="s">
         <v>474</v>
@@ -9886,7 +9886,7 @@
         <v>88</v>
       </c>
       <c r="C473">
-        <v>6740</v>
+        <v>6500</v>
       </c>
       <c r="D473" t="s">
         <v>475</v>
@@ -9900,7 +9900,7 @@
         <v>89</v>
       </c>
       <c r="C474">
-        <v>6620</v>
+        <v>6420</v>
       </c>
       <c r="D474" t="s">
         <v>476</v>
@@ -9914,7 +9914,7 @@
         <v>90</v>
       </c>
       <c r="C475">
-        <v>6490</v>
+        <v>6330</v>
       </c>
       <c r="D475" t="s">
         <v>477</v>
@@ -9928,7 +9928,7 @@
         <v>91</v>
       </c>
       <c r="C476">
-        <v>6350</v>
+        <v>6200</v>
       </c>
       <c r="D476" t="s">
         <v>478</v>
@@ -9942,7 +9942,7 @@
         <v>92</v>
       </c>
       <c r="C477">
-        <v>6210</v>
+        <v>6060</v>
       </c>
       <c r="D477" t="s">
         <v>479</v>
@@ -9956,7 +9956,7 @@
         <v>93</v>
       </c>
       <c r="C478">
-        <v>6060</v>
+        <v>5880</v>
       </c>
       <c r="D478" t="s">
         <v>480</v>
@@ -9970,7 +9970,7 @@
         <v>94</v>
       </c>
       <c r="C479">
-        <v>5920</v>
+        <v>5750</v>
       </c>
       <c r="D479" t="s">
         <v>481</v>
@@ -9984,7 +9984,7 @@
         <v>95</v>
       </c>
       <c r="C480">
-        <v>5790</v>
+        <v>5630</v>
       </c>
       <c r="D480" t="s">
         <v>482</v>
@@ -9998,7 +9998,7 @@
         <v>96</v>
       </c>
       <c r="C481">
-        <v>5670</v>
+        <v>5520</v>
       </c>
       <c r="D481" t="s">
         <v>483</v>

--- a/Market Fundamentals/Transelectrica_data/Cons_Prod_final/Weekly_Consumption_2026.xlsx
+++ b/Market Fundamentals/Transelectrica_data/Cons_Prod_final/Weekly_Consumption_2026.xlsx
@@ -30460,7 +30460,7 @@
         <v>1</v>
       </c>
       <c r="C1634">
-        <v>5450</v>
+        <v>5400</v>
       </c>
       <c r="D1634" t="s">
         <v>1636</v>
@@ -30474,7 +30474,7 @@
         <v>2</v>
       </c>
       <c r="C1635">
-        <v>5380</v>
+        <v>5320</v>
       </c>
       <c r="D1635" t="s">
         <v>1637</v>
@@ -30488,7 +30488,7 @@
         <v>3</v>
       </c>
       <c r="C1636">
-        <v>5330</v>
+        <v>5250</v>
       </c>
       <c r="D1636" t="s">
         <v>1638</v>
@@ -30502,7 +30502,7 @@
         <v>4</v>
       </c>
       <c r="C1637">
-        <v>5270</v>
+        <v>5190</v>
       </c>
       <c r="D1637" t="s">
         <v>1639</v>
@@ -30516,7 +30516,7 @@
         <v>5</v>
       </c>
       <c r="C1638">
-        <v>5210</v>
+        <v>5140</v>
       </c>
       <c r="D1638" t="s">
         <v>1640</v>
@@ -30530,7 +30530,7 @@
         <v>6</v>
       </c>
       <c r="C1639">
-        <v>5170</v>
+        <v>5080</v>
       </c>
       <c r="D1639" t="s">
         <v>1641</v>
@@ -30544,7 +30544,7 @@
         <v>7</v>
       </c>
       <c r="C1640">
-        <v>5130</v>
+        <v>5040</v>
       </c>
       <c r="D1640" t="s">
         <v>1642</v>
@@ -30558,7 +30558,7 @@
         <v>8</v>
       </c>
       <c r="C1641">
-        <v>5080</v>
+        <v>5010</v>
       </c>
       <c r="D1641" t="s">
         <v>1643</v>
@@ -30572,7 +30572,7 @@
         <v>9</v>
       </c>
       <c r="C1642">
-        <v>5050</v>
+        <v>4980</v>
       </c>
       <c r="D1642" t="s">
         <v>1644</v>
@@ -30586,7 +30586,7 @@
         <v>10</v>
       </c>
       <c r="C1643">
-        <v>5020</v>
+        <v>4960</v>
       </c>
       <c r="D1643" t="s">
         <v>1645</v>
@@ -30600,7 +30600,7 @@
         <v>11</v>
       </c>
       <c r="C1644">
-        <v>5000</v>
+        <v>4930</v>
       </c>
       <c r="D1644" t="s">
         <v>1646</v>
@@ -30614,7 +30614,7 @@
         <v>12</v>
       </c>
       <c r="C1645">
-        <v>4990</v>
+        <v>4930</v>
       </c>
       <c r="D1645" t="s">
         <v>1647</v>
@@ -30628,7 +30628,7 @@
         <v>13</v>
       </c>
       <c r="C1646">
-        <v>4990</v>
+        <v>4930</v>
       </c>
       <c r="D1646" t="s">
         <v>1648</v>
@@ -30642,7 +30642,7 @@
         <v>14</v>
       </c>
       <c r="C1647">
-        <v>4990</v>
+        <v>4930</v>
       </c>
       <c r="D1647" t="s">
         <v>1649</v>
@@ -30656,7 +30656,7 @@
         <v>15</v>
       </c>
       <c r="C1648">
-        <v>5000</v>
+        <v>4940</v>
       </c>
       <c r="D1648" t="s">
         <v>1650</v>
@@ -30670,7 +30670,7 @@
         <v>16</v>
       </c>
       <c r="C1649">
-        <v>5000</v>
+        <v>4950</v>
       </c>
       <c r="D1649" t="s">
         <v>1651</v>
@@ -30684,7 +30684,7 @@
         <v>17</v>
       </c>
       <c r="C1650">
-        <v>5000</v>
+        <v>4980</v>
       </c>
       <c r="D1650" t="s">
         <v>1652</v>
@@ -30698,7 +30698,7 @@
         <v>18</v>
       </c>
       <c r="C1651">
-        <v>5000</v>
+        <v>4990</v>
       </c>
       <c r="D1651" t="s">
         <v>1653</v>
@@ -30712,7 +30712,7 @@
         <v>19</v>
       </c>
       <c r="C1652">
-        <v>5010</v>
+        <v>4990</v>
       </c>
       <c r="D1652" t="s">
         <v>1654</v>
@@ -30726,7 +30726,7 @@
         <v>20</v>
       </c>
       <c r="C1653">
-        <v>5010</v>
+        <v>5000</v>
       </c>
       <c r="D1653" t="s">
         <v>1655</v>
@@ -30740,7 +30740,7 @@
         <v>21</v>
       </c>
       <c r="C1654">
-        <v>5030</v>
+        <v>5020</v>
       </c>
       <c r="D1654" t="s">
         <v>1656</v>
@@ -30754,7 +30754,7 @@
         <v>22</v>
       </c>
       <c r="C1655">
-        <v>5060</v>
+        <v>5040</v>
       </c>
       <c r="D1655" t="s">
         <v>1657</v>
@@ -30768,7 +30768,7 @@
         <v>23</v>
       </c>
       <c r="C1656">
-        <v>5100</v>
+        <v>5080</v>
       </c>
       <c r="D1656" t="s">
         <v>1658</v>
@@ -30782,7 +30782,7 @@
         <v>24</v>
       </c>
       <c r="C1657">
-        <v>5160</v>
+        <v>5130</v>
       </c>
       <c r="D1657" t="s">
         <v>1659</v>
@@ -30796,7 +30796,7 @@
         <v>25</v>
       </c>
       <c r="C1658">
-        <v>5230</v>
+        <v>5200</v>
       </c>
       <c r="D1658" t="s">
         <v>1660</v>
@@ -30810,7 +30810,7 @@
         <v>26</v>
       </c>
       <c r="C1659">
-        <v>5320</v>
+        <v>5270</v>
       </c>
       <c r="D1659" t="s">
         <v>1661</v>
@@ -30824,7 +30824,7 @@
         <v>27</v>
       </c>
       <c r="C1660">
-        <v>5420</v>
+        <v>5350</v>
       </c>
       <c r="D1660" t="s">
         <v>1662</v>
@@ -30838,7 +30838,7 @@
         <v>28</v>
       </c>
       <c r="C1661">
-        <v>5520</v>
+        <v>5440</v>
       </c>
       <c r="D1661" t="s">
         <v>1663</v>
@@ -30852,7 +30852,7 @@
         <v>29</v>
       </c>
       <c r="C1662">
-        <v>5620</v>
+        <v>5530</v>
       </c>
       <c r="D1662" t="s">
         <v>1664</v>
@@ -30866,7 +30866,7 @@
         <v>30</v>
       </c>
       <c r="C1663">
-        <v>5710</v>
+        <v>5610</v>
       </c>
       <c r="D1663" t="s">
         <v>1665</v>
@@ -30880,7 +30880,7 @@
         <v>31</v>
       </c>
       <c r="C1664">
-        <v>5800</v>
+        <v>5680</v>
       </c>
       <c r="D1664" t="s">
         <v>1666</v>
@@ -30894,7 +30894,7 @@
         <v>32</v>
       </c>
       <c r="C1665">
-        <v>5860</v>
+        <v>5740</v>
       </c>
       <c r="D1665" t="s">
         <v>1667</v>
@@ -30908,7 +30908,7 @@
         <v>33</v>
       </c>
       <c r="C1666">
-        <v>5910</v>
+        <v>5770</v>
       </c>
       <c r="D1666" t="s">
         <v>1668</v>
@@ -30922,7 +30922,7 @@
         <v>34</v>
       </c>
       <c r="C1667">
-        <v>5930</v>
+        <v>5790</v>
       </c>
       <c r="D1667" t="s">
         <v>1669</v>
@@ -30936,7 +30936,7 @@
         <v>35</v>
       </c>
       <c r="C1668">
-        <v>5920</v>
+        <v>5780</v>
       </c>
       <c r="D1668" t="s">
         <v>1670</v>
@@ -30950,7 +30950,7 @@
         <v>36</v>
       </c>
       <c r="C1669">
-        <v>5890</v>
+        <v>5750</v>
       </c>
       <c r="D1669" t="s">
         <v>1671</v>
@@ -30964,7 +30964,7 @@
         <v>37</v>
       </c>
       <c r="C1670">
-        <v>5840</v>
+        <v>5700</v>
       </c>
       <c r="D1670" t="s">
         <v>1672</v>
@@ -30978,7 +30978,7 @@
         <v>38</v>
       </c>
       <c r="C1671">
-        <v>5780</v>
+        <v>5630</v>
       </c>
       <c r="D1671" t="s">
         <v>1673</v>
@@ -30992,7 +30992,7 @@
         <v>39</v>
       </c>
       <c r="C1672">
-        <v>5690</v>
+        <v>5550</v>
       </c>
       <c r="D1672" t="s">
         <v>1674</v>
@@ -31006,7 +31006,7 @@
         <v>40</v>
       </c>
       <c r="C1673">
-        <v>5610</v>
+        <v>5460</v>
       </c>
       <c r="D1673" t="s">
         <v>1675</v>
@@ -31020,7 +31020,7 @@
         <v>41</v>
       </c>
       <c r="C1674">
-        <v>5520</v>
+        <v>5370</v>
       </c>
       <c r="D1674" t="s">
         <v>1676</v>
@@ -31034,7 +31034,7 @@
         <v>42</v>
       </c>
       <c r="C1675">
-        <v>5430</v>
+        <v>5280</v>
       </c>
       <c r="D1675" t="s">
         <v>1677</v>
@@ -31048,7 +31048,7 @@
         <v>43</v>
       </c>
       <c r="C1676">
-        <v>5360</v>
+        <v>5200</v>
       </c>
       <c r="D1676" t="s">
         <v>1678</v>
@@ -31062,7 +31062,7 @@
         <v>44</v>
       </c>
       <c r="C1677">
-        <v>5300</v>
+        <v>5130</v>
       </c>
       <c r="D1677" t="s">
         <v>1679</v>
@@ -31076,7 +31076,7 @@
         <v>45</v>
       </c>
       <c r="C1678">
-        <v>5250</v>
+        <v>5070</v>
       </c>
       <c r="D1678" t="s">
         <v>1680</v>
@@ -31090,7 +31090,7 @@
         <v>46</v>
       </c>
       <c r="C1679">
-        <v>5210</v>
+        <v>5020</v>
       </c>
       <c r="D1679" t="s">
         <v>1681</v>
@@ -31104,7 +31104,7 @@
         <v>47</v>
       </c>
       <c r="C1680">
-        <v>5190</v>
+        <v>4980</v>
       </c>
       <c r="D1680" t="s">
         <v>1682</v>
@@ -31118,7 +31118,7 @@
         <v>48</v>
       </c>
       <c r="C1681">
-        <v>5170</v>
+        <v>4950</v>
       </c>
       <c r="D1681" t="s">
         <v>1683</v>
@@ -31132,7 +31132,7 @@
         <v>49</v>
       </c>
       <c r="C1682">
-        <v>5160</v>
+        <v>4930</v>
       </c>
       <c r="D1682" t="s">
         <v>1684</v>
@@ -31146,7 +31146,7 @@
         <v>50</v>
       </c>
       <c r="C1683">
-        <v>5150</v>
+        <v>4920</v>
       </c>
       <c r="D1683" t="s">
         <v>1685</v>
@@ -31160,7 +31160,7 @@
         <v>51</v>
       </c>
       <c r="C1684">
-        <v>5150</v>
+        <v>4910</v>
       </c>
       <c r="D1684" t="s">
         <v>1686</v>
@@ -31174,7 +31174,7 @@
         <v>52</v>
       </c>
       <c r="C1685">
-        <v>5150</v>
+        <v>4920</v>
       </c>
       <c r="D1685" t="s">
         <v>1687</v>
@@ -31188,7 +31188,7 @@
         <v>53</v>
       </c>
       <c r="C1686">
-        <v>5150</v>
+        <v>4940</v>
       </c>
       <c r="D1686" t="s">
         <v>1688</v>
@@ -31202,7 +31202,7 @@
         <v>54</v>
       </c>
       <c r="C1687">
-        <v>5160</v>
+        <v>4960</v>
       </c>
       <c r="D1687" t="s">
         <v>1689</v>
@@ -31216,7 +31216,7 @@
         <v>55</v>
       </c>
       <c r="C1688">
-        <v>5180</v>
+        <v>4990</v>
       </c>
       <c r="D1688" t="s">
         <v>1690</v>
@@ -31230,7 +31230,7 @@
         <v>56</v>
       </c>
       <c r="C1689">
-        <v>5200</v>
+        <v>5030</v>
       </c>
       <c r="D1689" t="s">
         <v>1691</v>
@@ -31244,7 +31244,7 @@
         <v>57</v>
       </c>
       <c r="C1690">
-        <v>5230</v>
+        <v>5070</v>
       </c>
       <c r="D1690" t="s">
         <v>1692</v>
@@ -31258,7 +31258,7 @@
         <v>58</v>
       </c>
       <c r="C1691">
-        <v>5260</v>
+        <v>5110</v>
       </c>
       <c r="D1691" t="s">
         <v>1693</v>
@@ -31272,7 +31272,7 @@
         <v>59</v>
       </c>
       <c r="C1692">
-        <v>5300</v>
+        <v>5150</v>
       </c>
       <c r="D1692" t="s">
         <v>1694</v>
@@ -31286,7 +31286,7 @@
         <v>60</v>
       </c>
       <c r="C1693">
-        <v>5330</v>
+        <v>5190</v>
       </c>
       <c r="D1693" t="s">
         <v>1695</v>
@@ -31300,7 +31300,7 @@
         <v>61</v>
       </c>
       <c r="C1694">
-        <v>5370</v>
+        <v>5220</v>
       </c>
       <c r="D1694" t="s">
         <v>1696</v>
@@ -31314,7 +31314,7 @@
         <v>62</v>
       </c>
       <c r="C1695">
-        <v>5410</v>
+        <v>5250</v>
       </c>
       <c r="D1695" t="s">
         <v>1697</v>
@@ -31328,7 +31328,7 @@
         <v>63</v>
       </c>
       <c r="C1696">
-        <v>5450</v>
+        <v>5280</v>
       </c>
       <c r="D1696" t="s">
         <v>1698</v>
@@ -31342,7 +31342,7 @@
         <v>64</v>
       </c>
       <c r="C1697">
-        <v>5490</v>
+        <v>5320</v>
       </c>
       <c r="D1697" t="s">
         <v>1699</v>
@@ -31356,7 +31356,7 @@
         <v>65</v>
       </c>
       <c r="C1698">
-        <v>5550</v>
+        <v>5380</v>
       </c>
       <c r="D1698" t="s">
         <v>1700</v>
@@ -31370,7 +31370,7 @@
         <v>66</v>
       </c>
       <c r="C1699">
-        <v>5610</v>
+        <v>5450</v>
       </c>
       <c r="D1699" t="s">
         <v>1701</v>
@@ -31384,7 +31384,7 @@
         <v>67</v>
       </c>
       <c r="C1700">
-        <v>5690</v>
+        <v>5520</v>
       </c>
       <c r="D1700" t="s">
         <v>1702</v>
@@ -31398,7 +31398,7 @@
         <v>68</v>
       </c>
       <c r="C1701">
-        <v>5780</v>
+        <v>5600</v>
       </c>
       <c r="D1701" t="s">
         <v>1703</v>
@@ -31412,7 +31412,7 @@
         <v>69</v>
       </c>
       <c r="C1702">
-        <v>5880</v>
+        <v>5700</v>
       </c>
       <c r="D1702" t="s">
         <v>1704</v>
@@ -31426,7 +31426,7 @@
         <v>70</v>
       </c>
       <c r="C1703">
-        <v>5980</v>
+        <v>5800</v>
       </c>
       <c r="D1703" t="s">
         <v>1705</v>
@@ -31440,7 +31440,7 @@
         <v>71</v>
       </c>
       <c r="C1704">
-        <v>6080</v>
+        <v>5900</v>
       </c>
       <c r="D1704" t="s">
         <v>1706</v>
@@ -31454,7 +31454,7 @@
         <v>72</v>
       </c>
       <c r="C1705">
-        <v>6170</v>
+        <v>6000</v>
       </c>
       <c r="D1705" t="s">
         <v>1707</v>
@@ -31468,7 +31468,7 @@
         <v>73</v>
       </c>
       <c r="C1706">
-        <v>6250</v>
+        <v>6100</v>
       </c>
       <c r="D1706" t="s">
         <v>1708</v>
@@ -31482,7 +31482,7 @@
         <v>74</v>
       </c>
       <c r="C1707">
-        <v>6330</v>
+        <v>6200</v>
       </c>
       <c r="D1707" t="s">
         <v>1709</v>
@@ -31496,7 +31496,7 @@
         <v>75</v>
       </c>
       <c r="C1708">
-        <v>6400</v>
+        <v>6300</v>
       </c>
       <c r="D1708" t="s">
         <v>1710</v>
@@ -31510,7 +31510,7 @@
         <v>76</v>
       </c>
       <c r="C1709">
-        <v>6480</v>
+        <v>6410</v>
       </c>
       <c r="D1709" t="s">
         <v>1711</v>
@@ -31524,7 +31524,7 @@
         <v>77</v>
       </c>
       <c r="C1710">
-        <v>6550</v>
+        <v>6480</v>
       </c>
       <c r="D1710" t="s">
         <v>1712</v>
@@ -31538,7 +31538,7 @@
         <v>78</v>
       </c>
       <c r="C1711">
-        <v>6610</v>
+        <v>6580</v>
       </c>
       <c r="D1711" t="s">
         <v>1713</v>
@@ -31552,7 +31552,7 @@
         <v>79</v>
       </c>
       <c r="C1712">
-        <v>6670</v>
+        <v>6660</v>
       </c>
       <c r="D1712" t="s">
         <v>1714</v>
@@ -31566,7 +31566,7 @@
         <v>80</v>
       </c>
       <c r="C1713">
-        <v>6710</v>
+        <v>6720</v>
       </c>
       <c r="D1713" t="s">
         <v>1715</v>
@@ -31580,7 +31580,7 @@
         <v>81</v>
       </c>
       <c r="C1714">
-        <v>6760</v>
+        <v>6790</v>
       </c>
       <c r="D1714" t="s">
         <v>1716</v>
@@ -31594,7 +31594,7 @@
         <v>82</v>
       </c>
       <c r="C1715">
-        <v>6830</v>
+        <v>6850</v>
       </c>
       <c r="D1715" t="s">
         <v>1717</v>
@@ -31622,7 +31622,7 @@
         <v>84</v>
       </c>
       <c r="C1717">
-        <v>6920</v>
+        <v>6930</v>
       </c>
       <c r="D1717" t="s">
         <v>1719</v>
@@ -31636,7 +31636,7 @@
         <v>85</v>
       </c>
       <c r="C1718">
-        <v>6920</v>
+        <v>6940</v>
       </c>
       <c r="D1718" t="s">
         <v>1720</v>
@@ -31650,7 +31650,7 @@
         <v>86</v>
       </c>
       <c r="C1719">
-        <v>6910</v>
+        <v>6920</v>
       </c>
       <c r="D1719" t="s">
         <v>1721</v>
@@ -31664,7 +31664,7 @@
         <v>87</v>
       </c>
       <c r="C1720">
-        <v>6880</v>
+        <v>6870</v>
       </c>
       <c r="D1720" t="s">
         <v>1722</v>
@@ -31678,7 +31678,7 @@
         <v>88</v>
       </c>
       <c r="C1721">
-        <v>6750</v>
+        <v>6740</v>
       </c>
       <c r="D1721" t="s">
         <v>1723</v>
@@ -31692,7 +31692,7 @@
         <v>89</v>
       </c>
       <c r="C1722">
-        <v>6510</v>
+        <v>6590</v>
       </c>
       <c r="D1722" t="s">
         <v>1724</v>
@@ -31706,7 +31706,7 @@
         <v>90</v>
       </c>
       <c r="C1723">
-        <v>6300</v>
+        <v>6450</v>
       </c>
       <c r="D1723" t="s">
         <v>1725</v>
@@ -31720,7 +31720,7 @@
         <v>91</v>
       </c>
       <c r="C1724">
-        <v>6130</v>
+        <v>6300</v>
       </c>
       <c r="D1724" t="s">
         <v>1726</v>
@@ -31734,7 +31734,7 @@
         <v>92</v>
       </c>
       <c r="C1725">
-        <v>6000</v>
+        <v>6150</v>
       </c>
       <c r="D1725" t="s">
         <v>1727</v>
@@ -31748,7 +31748,7 @@
         <v>93</v>
       </c>
       <c r="C1726">
-        <v>5860</v>
+        <v>6000</v>
       </c>
       <c r="D1726" t="s">
         <v>1728</v>
@@ -31762,7 +31762,7 @@
         <v>94</v>
       </c>
       <c r="C1727">
-        <v>5730</v>
+        <v>5850</v>
       </c>
       <c r="D1727" t="s">
         <v>1729</v>
@@ -31776,7 +31776,7 @@
         <v>95</v>
       </c>
       <c r="C1728">
-        <v>5600</v>
+        <v>5730</v>
       </c>
       <c r="D1728" t="s">
         <v>1730</v>
@@ -31790,7 +31790,7 @@
         <v>96</v>
       </c>
       <c r="C1729">
-        <v>5480</v>
+        <v>5600</v>
       </c>
       <c r="D1729" t="s">
         <v>1731</v>
@@ -31804,7 +31804,7 @@
         <v>1</v>
       </c>
       <c r="C1730">
-        <v>5520</v>
+        <v>5500</v>
       </c>
       <c r="D1730" t="s">
         <v>1732</v>
@@ -31818,7 +31818,7 @@
         <v>2</v>
       </c>
       <c r="C1731">
-        <v>5480</v>
+        <v>5450</v>
       </c>
       <c r="D1731" t="s">
         <v>1733</v>
@@ -31832,7 +31832,7 @@
         <v>3</v>
       </c>
       <c r="C1732">
-        <v>5410</v>
+        <v>5390</v>
       </c>
       <c r="D1732" t="s">
         <v>1734</v>
@@ -31846,7 +31846,7 @@
         <v>4</v>
       </c>
       <c r="C1733">
-        <v>5340</v>
+        <v>5310</v>
       </c>
       <c r="D1733" t="s">
         <v>1735</v>
@@ -31860,7 +31860,7 @@
         <v>5</v>
       </c>
       <c r="C1734">
-        <v>5290</v>
+        <v>5250</v>
       </c>
       <c r="D1734" t="s">
         <v>1736</v>
@@ -31874,7 +31874,7 @@
         <v>6</v>
       </c>
       <c r="C1735">
-        <v>5250</v>
+        <v>5190</v>
       </c>
       <c r="D1735" t="s">
         <v>1737</v>
@@ -31888,7 +31888,7 @@
         <v>7</v>
       </c>
       <c r="C1736">
-        <v>5210</v>
+        <v>5140</v>
       </c>
       <c r="D1736" t="s">
         <v>1738</v>
@@ -31902,7 +31902,7 @@
         <v>8</v>
       </c>
       <c r="C1737">
-        <v>5160</v>
+        <v>5090</v>
       </c>
       <c r="D1737" t="s">
         <v>1739</v>
@@ -31916,7 +31916,7 @@
         <v>9</v>
       </c>
       <c r="C1738">
-        <v>5120</v>
+        <v>5060</v>
       </c>
       <c r="D1738" t="s">
         <v>1740</v>
@@ -31930,7 +31930,7 @@
         <v>10</v>
       </c>
       <c r="C1739">
-        <v>5090</v>
+        <v>5030</v>
       </c>
       <c r="D1739" t="s">
         <v>1741</v>
@@ -31944,7 +31944,7 @@
         <v>11</v>
       </c>
       <c r="C1740">
-        <v>5070</v>
+        <v>5020</v>
       </c>
       <c r="D1740" t="s">
         <v>1742</v>
@@ -31958,7 +31958,7 @@
         <v>12</v>
       </c>
       <c r="C1741">
-        <v>5060</v>
+        <v>5010</v>
       </c>
       <c r="D1741" t="s">
         <v>1743</v>
@@ -31972,7 +31972,7 @@
         <v>13</v>
       </c>
       <c r="C1742">
-        <v>5060</v>
+        <v>5010</v>
       </c>
       <c r="D1742" t="s">
         <v>1744</v>
@@ -31986,7 +31986,7 @@
         <v>14</v>
       </c>
       <c r="C1743">
-        <v>5070</v>
+        <v>5010</v>
       </c>
       <c r="D1743" t="s">
         <v>1745</v>
@@ -32000,7 +32000,7 @@
         <v>15</v>
       </c>
       <c r="C1744">
-        <v>5070</v>
+        <v>5000</v>
       </c>
       <c r="D1744" t="s">
         <v>1746</v>
@@ -32014,7 +32014,7 @@
         <v>16</v>
       </c>
       <c r="C1745">
-        <v>5080</v>
+        <v>5020</v>
       </c>
       <c r="D1745" t="s">
         <v>1747</v>
@@ -32028,7 +32028,7 @@
         <v>17</v>
       </c>
       <c r="C1746">
-        <v>5080</v>
+        <v>5020</v>
       </c>
       <c r="D1746" t="s">
         <v>1748</v>
@@ -32042,7 +32042,7 @@
         <v>18</v>
       </c>
       <c r="C1747">
-        <v>5080</v>
+        <v>5020</v>
       </c>
       <c r="D1747" t="s">
         <v>1749</v>
@@ -32056,7 +32056,7 @@
         <v>19</v>
       </c>
       <c r="C1748">
-        <v>5080</v>
+        <v>5030</v>
       </c>
       <c r="D1748" t="s">
         <v>1750</v>
@@ -32070,7 +32070,7 @@
         <v>20</v>
       </c>
       <c r="C1749">
-        <v>5090</v>
+        <v>5050</v>
       </c>
       <c r="D1749" t="s">
         <v>1751</v>
@@ -32084,7 +32084,7 @@
         <v>21</v>
       </c>
       <c r="C1750">
-        <v>5110</v>
+        <v>5080</v>
       </c>
       <c r="D1750" t="s">
         <v>1752</v>
@@ -32098,7 +32098,7 @@
         <v>22</v>
       </c>
       <c r="C1751">
-        <v>5140</v>
+        <v>5120</v>
       </c>
       <c r="D1751" t="s">
         <v>1753</v>
@@ -32112,7 +32112,7 @@
         <v>23</v>
       </c>
       <c r="C1752">
-        <v>5190</v>
+        <v>5180</v>
       </c>
       <c r="D1752" t="s">
         <v>1754</v>
@@ -32126,7 +32126,7 @@
         <v>24</v>
       </c>
       <c r="C1753">
-        <v>5250</v>
+        <v>5240</v>
       </c>
       <c r="D1753" t="s">
         <v>1755</v>
@@ -32140,7 +32140,7 @@
         <v>25</v>
       </c>
       <c r="C1754">
-        <v>5320</v>
+        <v>5310</v>
       </c>
       <c r="D1754" t="s">
         <v>1756</v>
@@ -32154,7 +32154,7 @@
         <v>26</v>
       </c>
       <c r="C1755">
-        <v>5410</v>
+        <v>5390</v>
       </c>
       <c r="D1755" t="s">
         <v>1757</v>
@@ -32168,7 +32168,7 @@
         <v>27</v>
       </c>
       <c r="C1756">
-        <v>5510</v>
+        <v>5470</v>
       </c>
       <c r="D1756" t="s">
         <v>1758</v>
@@ -32182,7 +32182,7 @@
         <v>28</v>
       </c>
       <c r="C1757">
-        <v>5610</v>
+        <v>5550</v>
       </c>
       <c r="D1757" t="s">
         <v>1759</v>
@@ -32196,7 +32196,7 @@
         <v>29</v>
       </c>
       <c r="C1758">
-        <v>5710</v>
+        <v>5620</v>
       </c>
       <c r="D1758" t="s">
         <v>1760</v>
@@ -32210,7 +32210,7 @@
         <v>30</v>
       </c>
       <c r="C1759">
-        <v>5800</v>
+        <v>5690</v>
       </c>
       <c r="D1759" t="s">
         <v>1761</v>
@@ -32224,7 +32224,7 @@
         <v>31</v>
       </c>
       <c r="C1760">
-        <v>5880</v>
+        <v>5740</v>
       </c>
       <c r="D1760" t="s">
         <v>1762</v>
@@ -32238,7 +32238,7 @@
         <v>32</v>
       </c>
       <c r="C1761">
-        <v>5940</v>
+        <v>5780</v>
       </c>
       <c r="D1761" t="s">
         <v>1763</v>
@@ -32252,7 +32252,7 @@
         <v>33</v>
       </c>
       <c r="C1762">
-        <v>5980</v>
+        <v>5800</v>
       </c>
       <c r="D1762" t="s">
         <v>1764</v>
@@ -32266,7 +32266,7 @@
         <v>34</v>
       </c>
       <c r="C1763">
-        <v>5990</v>
+        <v>5800</v>
       </c>
       <c r="D1763" t="s">
         <v>1765</v>
@@ -32280,7 +32280,7 @@
         <v>35</v>
       </c>
       <c r="C1764">
-        <v>5980</v>
+        <v>5790</v>
       </c>
       <c r="D1764" t="s">
         <v>1766</v>
@@ -32294,7 +32294,7 @@
         <v>36</v>
       </c>
       <c r="C1765">
-        <v>5950</v>
+        <v>5760</v>
       </c>
       <c r="D1765" t="s">
         <v>1767</v>
@@ -32308,7 +32308,7 @@
         <v>37</v>
       </c>
       <c r="C1766">
-        <v>5890</v>
+        <v>5710</v>
       </c>
       <c r="D1766" t="s">
         <v>1768</v>
@@ -32322,7 +32322,7 @@
         <v>38</v>
       </c>
       <c r="C1767">
-        <v>5810</v>
+        <v>5650</v>
       </c>
       <c r="D1767" t="s">
         <v>1769</v>
@@ -32336,7 +32336,7 @@
         <v>39</v>
       </c>
       <c r="C1768">
-        <v>5720</v>
+        <v>5570</v>
       </c>
       <c r="D1768" t="s">
         <v>1770</v>
@@ -32350,7 +32350,7 @@
         <v>40</v>
       </c>
       <c r="C1769">
-        <v>5620</v>
+        <v>5490</v>
       </c>
       <c r="D1769" t="s">
         <v>1771</v>
@@ -32364,7 +32364,7 @@
         <v>41</v>
       </c>
       <c r="C1770">
-        <v>5530</v>
+        <v>5410</v>
       </c>
       <c r="D1770" t="s">
         <v>1772</v>
@@ -32378,7 +32378,7 @@
         <v>42</v>
       </c>
       <c r="C1771">
-        <v>5440</v>
+        <v>5330</v>
       </c>
       <c r="D1771" t="s">
         <v>1773</v>
@@ -32392,7 +32392,7 @@
         <v>43</v>
       </c>
       <c r="C1772">
-        <v>5360</v>
+        <v>5260</v>
       </c>
       <c r="D1772" t="s">
         <v>1774</v>
@@ -32406,7 +32406,7 @@
         <v>44</v>
       </c>
       <c r="C1773">
-        <v>5290</v>
+        <v>5200</v>
       </c>
       <c r="D1773" t="s">
         <v>1775</v>
@@ -32420,7 +32420,7 @@
         <v>45</v>
       </c>
       <c r="C1774">
-        <v>5240</v>
+        <v>5160</v>
       </c>
       <c r="D1774" t="s">
         <v>1776</v>
@@ -32434,7 +32434,7 @@
         <v>46</v>
       </c>
       <c r="C1775">
-        <v>5200</v>
+        <v>5130</v>
       </c>
       <c r="D1775" t="s">
         <v>1777</v>
@@ -32448,7 +32448,7 @@
         <v>47</v>
       </c>
       <c r="C1776">
-        <v>5180</v>
+        <v>5110</v>
       </c>
       <c r="D1776" t="s">
         <v>1778</v>
@@ -32462,7 +32462,7 @@
         <v>48</v>
       </c>
       <c r="C1777">
-        <v>5160</v>
+        <v>5110</v>
       </c>
       <c r="D1777" t="s">
         <v>1779</v>
@@ -32476,7 +32476,7 @@
         <v>49</v>
       </c>
       <c r="C1778">
-        <v>5150</v>
+        <v>5110</v>
       </c>
       <c r="D1778" t="s">
         <v>1780</v>
@@ -32490,7 +32490,7 @@
         <v>50</v>
       </c>
       <c r="C1779">
-        <v>5150</v>
+        <v>5110</v>
       </c>
       <c r="D1779" t="s">
         <v>1781</v>
@@ -32504,7 +32504,7 @@
         <v>51</v>
       </c>
       <c r="C1780">
-        <v>5150</v>
+        <v>5120</v>
       </c>
       <c r="D1780" t="s">
         <v>1782</v>
@@ -32518,7 +32518,7 @@
         <v>52</v>
       </c>
       <c r="C1781">
-        <v>5160</v>
+        <v>5130</v>
       </c>
       <c r="D1781" t="s">
         <v>1783</v>
@@ -32532,7 +32532,7 @@
         <v>53</v>
       </c>
       <c r="C1782">
-        <v>5180</v>
+        <v>5140</v>
       </c>
       <c r="D1782" t="s">
         <v>1784</v>
@@ -32546,7 +32546,7 @@
         <v>54</v>
       </c>
       <c r="C1783">
-        <v>5200</v>
+        <v>5160</v>
       </c>
       <c r="D1783" t="s">
         <v>1785</v>
@@ -32560,7 +32560,7 @@
         <v>55</v>
       </c>
       <c r="C1784">
-        <v>5240</v>
+        <v>5180</v>
       </c>
       <c r="D1784" t="s">
         <v>1786</v>
@@ -32574,7 +32574,7 @@
         <v>56</v>
       </c>
       <c r="C1785">
-        <v>5280</v>
+        <v>5210</v>
       </c>
       <c r="D1785" t="s">
         <v>1787</v>
@@ -32588,7 +32588,7 @@
         <v>57</v>
       </c>
       <c r="C1786">
-        <v>5320</v>
+        <v>5250</v>
       </c>
       <c r="D1786" t="s">
         <v>1788</v>
@@ -32602,7 +32602,7 @@
         <v>58</v>
       </c>
       <c r="C1787">
-        <v>5370</v>
+        <v>5300</v>
       </c>
       <c r="D1787" t="s">
         <v>1789</v>
@@ -32616,7 +32616,7 @@
         <v>59</v>
       </c>
       <c r="C1788">
-        <v>5420</v>
+        <v>5350</v>
       </c>
       <c r="D1788" t="s">
         <v>1790</v>
@@ -32630,7 +32630,7 @@
         <v>60</v>
       </c>
       <c r="C1789">
-        <v>5470</v>
+        <v>5400</v>
       </c>
       <c r="D1789" t="s">
         <v>1791</v>
@@ -32644,7 +32644,7 @@
         <v>61</v>
       </c>
       <c r="C1790">
-        <v>5520</v>
+        <v>5460</v>
       </c>
       <c r="D1790" t="s">
         <v>1792</v>
@@ -32658,7 +32658,7 @@
         <v>62</v>
       </c>
       <c r="C1791">
-        <v>5560</v>
+        <v>5530</v>
       </c>
       <c r="D1791" t="s">
         <v>1793</v>
@@ -32672,7 +32672,7 @@
         <v>63</v>
       </c>
       <c r="C1792">
-        <v>5610</v>
+        <v>5590</v>
       </c>
       <c r="D1792" t="s">
         <v>1794</v>
@@ -32714,7 +32714,7 @@
         <v>66</v>
       </c>
       <c r="C1795">
-        <v>5810</v>
+        <v>5800</v>
       </c>
       <c r="D1795" t="s">
         <v>1797</v>
@@ -32728,7 +32728,7 @@
         <v>67</v>
       </c>
       <c r="C1796">
-        <v>5910</v>
+        <v>5880</v>
       </c>
       <c r="D1796" t="s">
         <v>1798</v>
@@ -32742,7 +32742,7 @@
         <v>68</v>
       </c>
       <c r="C1797">
-        <v>6030</v>
+        <v>5970</v>
       </c>
       <c r="D1797" t="s">
         <v>1799</v>
@@ -32756,7 +32756,7 @@
         <v>69</v>
       </c>
       <c r="C1798">
-        <v>6150</v>
+        <v>6050</v>
       </c>
       <c r="D1798" t="s">
         <v>1800</v>
@@ -32770,7 +32770,7 @@
         <v>70</v>
       </c>
       <c r="C1799">
-        <v>6260</v>
+        <v>6140</v>
       </c>
       <c r="D1799" t="s">
         <v>1801</v>
@@ -32784,7 +32784,7 @@
         <v>71</v>
       </c>
       <c r="C1800">
-        <v>6370</v>
+        <v>6220</v>
       </c>
       <c r="D1800" t="s">
         <v>1802</v>
@@ -32798,7 +32798,7 @@
         <v>72</v>
       </c>
       <c r="C1801">
-        <v>6470</v>
+        <v>6300</v>
       </c>
       <c r="D1801" t="s">
         <v>1803</v>
@@ -32812,7 +32812,7 @@
         <v>73</v>
       </c>
       <c r="C1802">
-        <v>6550</v>
+        <v>6390</v>
       </c>
       <c r="D1802" t="s">
         <v>1804</v>
@@ -32826,7 +32826,7 @@
         <v>74</v>
       </c>
       <c r="C1803">
-        <v>6630</v>
+        <v>6480</v>
       </c>
       <c r="D1803" t="s">
         <v>1805</v>
@@ -32840,7 +32840,7 @@
         <v>75</v>
       </c>
       <c r="C1804">
-        <v>6720</v>
+        <v>6580</v>
       </c>
       <c r="D1804" t="s">
         <v>1806</v>
@@ -32854,7 +32854,7 @@
         <v>76</v>
       </c>
       <c r="C1805">
-        <v>6810</v>
+        <v>6690</v>
       </c>
       <c r="D1805" t="s">
         <v>1807</v>
@@ -32868,7 +32868,7 @@
         <v>77</v>
       </c>
       <c r="C1806">
-        <v>6910</v>
+        <v>6800</v>
       </c>
       <c r="D1806" t="s">
         <v>1808</v>
@@ -32882,7 +32882,7 @@
         <v>78</v>
       </c>
       <c r="C1807">
-        <v>7000</v>
+        <v>6890</v>
       </c>
       <c r="D1807" t="s">
         <v>1809</v>
@@ -32896,7 +32896,7 @@
         <v>79</v>
       </c>
       <c r="C1808">
-        <v>7070</v>
+        <v>6950</v>
       </c>
       <c r="D1808" t="s">
         <v>1810</v>
@@ -32910,7 +32910,7 @@
         <v>80</v>
       </c>
       <c r="C1809">
-        <v>7110</v>
+        <v>6980</v>
       </c>
       <c r="D1809" t="s">
         <v>1811</v>
@@ -32924,7 +32924,7 @@
         <v>81</v>
       </c>
       <c r="C1810">
-        <v>7140</v>
+        <v>7000</v>
       </c>
       <c r="D1810" t="s">
         <v>1812</v>
@@ -32938,7 +32938,7 @@
         <v>82</v>
       </c>
       <c r="C1811">
-        <v>7190</v>
+        <v>7000</v>
       </c>
       <c r="D1811" t="s">
         <v>1813</v>
@@ -32952,7 +32952,7 @@
         <v>83</v>
       </c>
       <c r="C1812">
-        <v>7220</v>
+        <v>7000</v>
       </c>
       <c r="D1812" t="s">
         <v>1814</v>
@@ -32966,7 +32966,7 @@
         <v>84</v>
       </c>
       <c r="C1813">
-        <v>7250</v>
+        <v>7000</v>
       </c>
       <c r="D1813" t="s">
         <v>1815</v>
@@ -32980,7 +32980,7 @@
         <v>85</v>
       </c>
       <c r="C1814">
-        <v>7250</v>
+        <v>7000</v>
       </c>
       <c r="D1814" t="s">
         <v>1816</v>
@@ -32994,7 +32994,7 @@
         <v>86</v>
       </c>
       <c r="C1815">
-        <v>7250</v>
+        <v>6920</v>
       </c>
       <c r="D1815" t="s">
         <v>1817</v>
@@ -33008,7 +33008,7 @@
         <v>87</v>
       </c>
       <c r="C1816">
-        <v>7210</v>
+        <v>6880</v>
       </c>
       <c r="D1816" t="s">
         <v>1818</v>
@@ -33022,7 +33022,7 @@
         <v>88</v>
       </c>
       <c r="C1817">
-        <v>7040</v>
+        <v>6780</v>
       </c>
       <c r="D1817" t="s">
         <v>1819</v>
@@ -33036,7 +33036,7 @@
         <v>89</v>
       </c>
       <c r="C1818">
-        <v>6810</v>
+        <v>6630</v>
       </c>
       <c r="D1818" t="s">
         <v>1820</v>
@@ -33050,7 +33050,7 @@
         <v>90</v>
       </c>
       <c r="C1819">
-        <v>6650</v>
+        <v>6520</v>
       </c>
       <c r="D1819" t="s">
         <v>1821</v>
@@ -33064,7 +33064,7 @@
         <v>91</v>
       </c>
       <c r="C1820">
-        <v>6490</v>
+        <v>6370</v>
       </c>
       <c r="D1820" t="s">
         <v>1822</v>
@@ -33078,7 +33078,7 @@
         <v>92</v>
       </c>
       <c r="C1821">
-        <v>6330</v>
+        <v>6240</v>
       </c>
       <c r="D1821" t="s">
         <v>1823</v>
@@ -33092,7 +33092,7 @@
         <v>93</v>
       </c>
       <c r="C1822">
-        <v>6100</v>
+        <v>6070</v>
       </c>
       <c r="D1822" t="s">
         <v>1824</v>
@@ -33106,7 +33106,7 @@
         <v>94</v>
       </c>
       <c r="C1823">
-        <v>5910</v>
+        <v>5920</v>
       </c>
       <c r="D1823" t="s">
         <v>1825</v>

--- a/Market Fundamentals/Transelectrica_data/Cons_Prod_final/Weekly_Consumption_2026.xlsx
+++ b/Market Fundamentals/Transelectrica_data/Cons_Prod_final/Weekly_Consumption_2026.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2404" uniqueCount="2404">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2500" uniqueCount="2500">
   <si>
     <t>Date</t>
   </si>
@@ -7226,6 +7226,294 @@
   </si>
   <si>
     <t>25.08.202696.0</t>
+  </si>
+  <si>
+    <t>26.08.20261.0</t>
+  </si>
+  <si>
+    <t>26.08.20262.0</t>
+  </si>
+  <si>
+    <t>26.08.20263.0</t>
+  </si>
+  <si>
+    <t>26.08.20264.0</t>
+  </si>
+  <si>
+    <t>26.08.20265.0</t>
+  </si>
+  <si>
+    <t>26.08.20266.0</t>
+  </si>
+  <si>
+    <t>26.08.20267.0</t>
+  </si>
+  <si>
+    <t>26.08.20268.0</t>
+  </si>
+  <si>
+    <t>26.08.20269.0</t>
+  </si>
+  <si>
+    <t>26.08.202610.0</t>
+  </si>
+  <si>
+    <t>26.08.202611.0</t>
+  </si>
+  <si>
+    <t>26.08.202612.0</t>
+  </si>
+  <si>
+    <t>26.08.202613.0</t>
+  </si>
+  <si>
+    <t>26.08.202614.0</t>
+  </si>
+  <si>
+    <t>26.08.202615.0</t>
+  </si>
+  <si>
+    <t>26.08.202616.0</t>
+  </si>
+  <si>
+    <t>26.08.202617.0</t>
+  </si>
+  <si>
+    <t>26.08.202618.0</t>
+  </si>
+  <si>
+    <t>26.08.202619.0</t>
+  </si>
+  <si>
+    <t>26.08.202620.0</t>
+  </si>
+  <si>
+    <t>26.08.202621.0</t>
+  </si>
+  <si>
+    <t>26.08.202622.0</t>
+  </si>
+  <si>
+    <t>26.08.202623.0</t>
+  </si>
+  <si>
+    <t>26.08.202624.0</t>
+  </si>
+  <si>
+    <t>26.08.202625.0</t>
+  </si>
+  <si>
+    <t>26.08.202626.0</t>
+  </si>
+  <si>
+    <t>26.08.202627.0</t>
+  </si>
+  <si>
+    <t>26.08.202628.0</t>
+  </si>
+  <si>
+    <t>26.08.202629.0</t>
+  </si>
+  <si>
+    <t>26.08.202630.0</t>
+  </si>
+  <si>
+    <t>26.08.202631.0</t>
+  </si>
+  <si>
+    <t>26.08.202632.0</t>
+  </si>
+  <si>
+    <t>26.08.202633.0</t>
+  </si>
+  <si>
+    <t>26.08.202634.0</t>
+  </si>
+  <si>
+    <t>26.08.202635.0</t>
+  </si>
+  <si>
+    <t>26.08.202636.0</t>
+  </si>
+  <si>
+    <t>26.08.202637.0</t>
+  </si>
+  <si>
+    <t>26.08.202638.0</t>
+  </si>
+  <si>
+    <t>26.08.202639.0</t>
+  </si>
+  <si>
+    <t>26.08.202640.0</t>
+  </si>
+  <si>
+    <t>26.08.202641.0</t>
+  </si>
+  <si>
+    <t>26.08.202642.0</t>
+  </si>
+  <si>
+    <t>26.08.202643.0</t>
+  </si>
+  <si>
+    <t>26.08.202644.0</t>
+  </si>
+  <si>
+    <t>26.08.202645.0</t>
+  </si>
+  <si>
+    <t>26.08.202646.0</t>
+  </si>
+  <si>
+    <t>26.08.202647.0</t>
+  </si>
+  <si>
+    <t>26.08.202648.0</t>
+  </si>
+  <si>
+    <t>26.08.202649.0</t>
+  </si>
+  <si>
+    <t>26.08.202650.0</t>
+  </si>
+  <si>
+    <t>26.08.202651.0</t>
+  </si>
+  <si>
+    <t>26.08.202652.0</t>
+  </si>
+  <si>
+    <t>26.08.202653.0</t>
+  </si>
+  <si>
+    <t>26.08.202654.0</t>
+  </si>
+  <si>
+    <t>26.08.202655.0</t>
+  </si>
+  <si>
+    <t>26.08.202656.0</t>
+  </si>
+  <si>
+    <t>26.08.202657.0</t>
+  </si>
+  <si>
+    <t>26.08.202658.0</t>
+  </si>
+  <si>
+    <t>26.08.202659.0</t>
+  </si>
+  <si>
+    <t>26.08.202660.0</t>
+  </si>
+  <si>
+    <t>26.08.202661.0</t>
+  </si>
+  <si>
+    <t>26.08.202662.0</t>
+  </si>
+  <si>
+    <t>26.08.202663.0</t>
+  </si>
+  <si>
+    <t>26.08.202664.0</t>
+  </si>
+  <si>
+    <t>26.08.202665.0</t>
+  </si>
+  <si>
+    <t>26.08.202666.0</t>
+  </si>
+  <si>
+    <t>26.08.202667.0</t>
+  </si>
+  <si>
+    <t>26.08.202668.0</t>
+  </si>
+  <si>
+    <t>26.08.202669.0</t>
+  </si>
+  <si>
+    <t>26.08.202670.0</t>
+  </si>
+  <si>
+    <t>26.08.202671.0</t>
+  </si>
+  <si>
+    <t>26.08.202672.0</t>
+  </si>
+  <si>
+    <t>26.08.202673.0</t>
+  </si>
+  <si>
+    <t>26.08.202674.0</t>
+  </si>
+  <si>
+    <t>26.08.202675.0</t>
+  </si>
+  <si>
+    <t>26.08.202676.0</t>
+  </si>
+  <si>
+    <t>26.08.202677.0</t>
+  </si>
+  <si>
+    <t>26.08.202678.0</t>
+  </si>
+  <si>
+    <t>26.08.202679.0</t>
+  </si>
+  <si>
+    <t>26.08.202680.0</t>
+  </si>
+  <si>
+    <t>26.08.202681.0</t>
+  </si>
+  <si>
+    <t>26.08.202682.0</t>
+  </si>
+  <si>
+    <t>26.08.202683.0</t>
+  </si>
+  <si>
+    <t>26.08.202684.0</t>
+  </si>
+  <si>
+    <t>26.08.202685.0</t>
+  </si>
+  <si>
+    <t>26.08.202686.0</t>
+  </si>
+  <si>
+    <t>26.08.202687.0</t>
+  </si>
+  <si>
+    <t>26.08.202688.0</t>
+  </si>
+  <si>
+    <t>26.08.202689.0</t>
+  </si>
+  <si>
+    <t>26.08.202690.0</t>
+  </si>
+  <si>
+    <t>26.08.202691.0</t>
+  </si>
+  <si>
+    <t>26.08.202692.0</t>
+  </si>
+  <si>
+    <t>26.08.202693.0</t>
+  </si>
+  <si>
+    <t>26.08.202694.0</t>
+  </si>
+  <si>
+    <t>26.08.202695.0</t>
+  </si>
+  <si>
+    <t>26.08.202696.0</t>
   </si>
 </sst>
 </file>
@@ -7587,7 +7875,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D2401"/>
+  <dimension ref="A1:D2497"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -31804,7 +32092,7 @@
         <v>1</v>
       </c>
       <c r="C1730">
-        <v>5500</v>
+        <v>5550</v>
       </c>
       <c r="D1730" t="s">
         <v>1732</v>
@@ -31818,7 +32106,7 @@
         <v>2</v>
       </c>
       <c r="C1731">
-        <v>5450</v>
+        <v>5480</v>
       </c>
       <c r="D1731" t="s">
         <v>1733</v>
@@ -31832,7 +32120,7 @@
         <v>3</v>
       </c>
       <c r="C1732">
-        <v>5390</v>
+        <v>5410</v>
       </c>
       <c r="D1732" t="s">
         <v>1734</v>
@@ -31846,7 +32134,7 @@
         <v>4</v>
       </c>
       <c r="C1733">
-        <v>5310</v>
+        <v>5350</v>
       </c>
       <c r="D1733" t="s">
         <v>1735</v>
@@ -31860,7 +32148,7 @@
         <v>5</v>
       </c>
       <c r="C1734">
-        <v>5250</v>
+        <v>5280</v>
       </c>
       <c r="D1734" t="s">
         <v>1736</v>
@@ -31874,7 +32162,7 @@
         <v>6</v>
       </c>
       <c r="C1735">
-        <v>5190</v>
+        <v>5230</v>
       </c>
       <c r="D1735" t="s">
         <v>1737</v>
@@ -31888,7 +32176,7 @@
         <v>7</v>
       </c>
       <c r="C1736">
-        <v>5140</v>
+        <v>5170</v>
       </c>
       <c r="D1736" t="s">
         <v>1738</v>
@@ -31902,7 +32190,7 @@
         <v>8</v>
       </c>
       <c r="C1737">
-        <v>5090</v>
+        <v>5140</v>
       </c>
       <c r="D1737" t="s">
         <v>1739</v>
@@ -31916,7 +32204,7 @@
         <v>9</v>
       </c>
       <c r="C1738">
-        <v>5060</v>
+        <v>5100</v>
       </c>
       <c r="D1738" t="s">
         <v>1740</v>
@@ -31930,7 +32218,7 @@
         <v>10</v>
       </c>
       <c r="C1739">
-        <v>5030</v>
+        <v>5080</v>
       </c>
       <c r="D1739" t="s">
         <v>1741</v>
@@ -31944,7 +32232,7 @@
         <v>11</v>
       </c>
       <c r="C1740">
-        <v>5020</v>
+        <v>5070</v>
       </c>
       <c r="D1740" t="s">
         <v>1742</v>
@@ -31958,7 +32246,7 @@
         <v>12</v>
       </c>
       <c r="C1741">
-        <v>5010</v>
+        <v>5060</v>
       </c>
       <c r="D1741" t="s">
         <v>1743</v>
@@ -31972,7 +32260,7 @@
         <v>13</v>
       </c>
       <c r="C1742">
-        <v>5010</v>
+        <v>5060</v>
       </c>
       <c r="D1742" t="s">
         <v>1744</v>
@@ -31986,7 +32274,7 @@
         <v>14</v>
       </c>
       <c r="C1743">
-        <v>5010</v>
+        <v>5080</v>
       </c>
       <c r="D1743" t="s">
         <v>1745</v>
@@ -32000,7 +32288,7 @@
         <v>15</v>
       </c>
       <c r="C1744">
-        <v>5000</v>
+        <v>5090</v>
       </c>
       <c r="D1744" t="s">
         <v>1746</v>
@@ -32014,7 +32302,7 @@
         <v>16</v>
       </c>
       <c r="C1745">
-        <v>5020</v>
+        <v>5120</v>
       </c>
       <c r="D1745" t="s">
         <v>1747</v>
@@ -32028,7 +32316,7 @@
         <v>17</v>
       </c>
       <c r="C1746">
-        <v>5020</v>
+        <v>5130</v>
       </c>
       <c r="D1746" t="s">
         <v>1748</v>
@@ -32042,7 +32330,7 @@
         <v>18</v>
       </c>
       <c r="C1747">
-        <v>5020</v>
+        <v>5150</v>
       </c>
       <c r="D1747" t="s">
         <v>1749</v>
@@ -32056,7 +32344,7 @@
         <v>19</v>
       </c>
       <c r="C1748">
-        <v>5030</v>
+        <v>5170</v>
       </c>
       <c r="D1748" t="s">
         <v>1750</v>
@@ -32070,7 +32358,7 @@
         <v>20</v>
       </c>
       <c r="C1749">
-        <v>5050</v>
+        <v>5200</v>
       </c>
       <c r="D1749" t="s">
         <v>1751</v>
@@ -32084,7 +32372,7 @@
         <v>21</v>
       </c>
       <c r="C1750">
-        <v>5080</v>
+        <v>5220</v>
       </c>
       <c r="D1750" t="s">
         <v>1752</v>
@@ -32098,7 +32386,7 @@
         <v>22</v>
       </c>
       <c r="C1751">
-        <v>5120</v>
+        <v>5240</v>
       </c>
       <c r="D1751" t="s">
         <v>1753</v>
@@ -32112,7 +32400,7 @@
         <v>23</v>
       </c>
       <c r="C1752">
-        <v>5180</v>
+        <v>5270</v>
       </c>
       <c r="D1752" t="s">
         <v>1754</v>
@@ -32126,7 +32414,7 @@
         <v>24</v>
       </c>
       <c r="C1753">
-        <v>5240</v>
+        <v>5290</v>
       </c>
       <c r="D1753" t="s">
         <v>1755</v>
@@ -32140,7 +32428,7 @@
         <v>25</v>
       </c>
       <c r="C1754">
-        <v>5310</v>
+        <v>5330</v>
       </c>
       <c r="D1754" t="s">
         <v>1756</v>
@@ -32154,7 +32442,7 @@
         <v>26</v>
       </c>
       <c r="C1755">
-        <v>5390</v>
+        <v>5400</v>
       </c>
       <c r="D1755" t="s">
         <v>1757</v>
@@ -32168,7 +32456,7 @@
         <v>27</v>
       </c>
       <c r="C1756">
-        <v>5470</v>
+        <v>5480</v>
       </c>
       <c r="D1756" t="s">
         <v>1758</v>
@@ -32182,7 +32470,7 @@
         <v>28</v>
       </c>
       <c r="C1757">
-        <v>5550</v>
+        <v>5570</v>
       </c>
       <c r="D1757" t="s">
         <v>1759</v>
@@ -32196,7 +32484,7 @@
         <v>29</v>
       </c>
       <c r="C1758">
-        <v>5620</v>
+        <v>5660</v>
       </c>
       <c r="D1758" t="s">
         <v>1760</v>
@@ -32210,7 +32498,7 @@
         <v>30</v>
       </c>
       <c r="C1759">
-        <v>5690</v>
+        <v>5770</v>
       </c>
       <c r="D1759" t="s">
         <v>1761</v>
@@ -32224,7 +32512,7 @@
         <v>31</v>
       </c>
       <c r="C1760">
-        <v>5740</v>
+        <v>5870</v>
       </c>
       <c r="D1760" t="s">
         <v>1762</v>
@@ -32238,7 +32526,7 @@
         <v>32</v>
       </c>
       <c r="C1761">
-        <v>5780</v>
+        <v>5960</v>
       </c>
       <c r="D1761" t="s">
         <v>1763</v>
@@ -32252,7 +32540,7 @@
         <v>33</v>
       </c>
       <c r="C1762">
-        <v>5800</v>
+        <v>6030</v>
       </c>
       <c r="D1762" t="s">
         <v>1764</v>
@@ -32266,7 +32554,7 @@
         <v>34</v>
       </c>
       <c r="C1763">
-        <v>5800</v>
+        <v>6090</v>
       </c>
       <c r="D1763" t="s">
         <v>1765</v>
@@ -32280,7 +32568,7 @@
         <v>35</v>
       </c>
       <c r="C1764">
-        <v>5790</v>
+        <v>6120</v>
       </c>
       <c r="D1764" t="s">
         <v>1766</v>
@@ -32294,7 +32582,7 @@
         <v>36</v>
       </c>
       <c r="C1765">
-        <v>5760</v>
+        <v>6130</v>
       </c>
       <c r="D1765" t="s">
         <v>1767</v>
@@ -32308,7 +32596,7 @@
         <v>37</v>
       </c>
       <c r="C1766">
-        <v>5710</v>
+        <v>6110</v>
       </c>
       <c r="D1766" t="s">
         <v>1768</v>
@@ -32322,7 +32610,7 @@
         <v>38</v>
       </c>
       <c r="C1767">
-        <v>5650</v>
+        <v>6070</v>
       </c>
       <c r="D1767" t="s">
         <v>1769</v>
@@ -32336,7 +32624,7 @@
         <v>39</v>
       </c>
       <c r="C1768">
-        <v>5570</v>
+        <v>6010</v>
       </c>
       <c r="D1768" t="s">
         <v>1770</v>
@@ -32350,7 +32638,7 @@
         <v>40</v>
       </c>
       <c r="C1769">
-        <v>5490</v>
+        <v>5940</v>
       </c>
       <c r="D1769" t="s">
         <v>1771</v>
@@ -32364,7 +32652,7 @@
         <v>41</v>
       </c>
       <c r="C1770">
-        <v>5410</v>
+        <v>5850</v>
       </c>
       <c r="D1770" t="s">
         <v>1772</v>
@@ -32378,7 +32666,7 @@
         <v>42</v>
       </c>
       <c r="C1771">
-        <v>5330</v>
+        <v>5770</v>
       </c>
       <c r="D1771" t="s">
         <v>1773</v>
@@ -32392,7 +32680,7 @@
         <v>43</v>
       </c>
       <c r="C1772">
-        <v>5260</v>
+        <v>5680</v>
       </c>
       <c r="D1772" t="s">
         <v>1774</v>
@@ -32406,7 +32694,7 @@
         <v>44</v>
       </c>
       <c r="C1773">
-        <v>5200</v>
+        <v>5600</v>
       </c>
       <c r="D1773" t="s">
         <v>1775</v>
@@ -32420,7 +32708,7 @@
         <v>45</v>
       </c>
       <c r="C1774">
-        <v>5160</v>
+        <v>5520</v>
       </c>
       <c r="D1774" t="s">
         <v>1776</v>
@@ -32434,7 +32722,7 @@
         <v>46</v>
       </c>
       <c r="C1775">
-        <v>5130</v>
+        <v>5450</v>
       </c>
       <c r="D1775" t="s">
         <v>1777</v>
@@ -32448,7 +32736,7 @@
         <v>47</v>
       </c>
       <c r="C1776">
-        <v>5110</v>
+        <v>5390</v>
       </c>
       <c r="D1776" t="s">
         <v>1778</v>
@@ -32462,7 +32750,7 @@
         <v>48</v>
       </c>
       <c r="C1777">
-        <v>5110</v>
+        <v>5340</v>
       </c>
       <c r="D1777" t="s">
         <v>1779</v>
@@ -32476,7 +32764,7 @@
         <v>49</v>
       </c>
       <c r="C1778">
-        <v>5110</v>
+        <v>5290</v>
       </c>
       <c r="D1778" t="s">
         <v>1780</v>
@@ -32490,7 +32778,7 @@
         <v>50</v>
       </c>
       <c r="C1779">
-        <v>5110</v>
+        <v>5250</v>
       </c>
       <c r="D1779" t="s">
         <v>1781</v>
@@ -32504,7 +32792,7 @@
         <v>51</v>
       </c>
       <c r="C1780">
-        <v>5120</v>
+        <v>5220</v>
       </c>
       <c r="D1780" t="s">
         <v>1782</v>
@@ -32518,7 +32806,7 @@
         <v>52</v>
       </c>
       <c r="C1781">
-        <v>5130</v>
+        <v>5210</v>
       </c>
       <c r="D1781" t="s">
         <v>1783</v>
@@ -32532,7 +32820,7 @@
         <v>53</v>
       </c>
       <c r="C1782">
-        <v>5140</v>
+        <v>5200</v>
       </c>
       <c r="D1782" t="s">
         <v>1784</v>
@@ -32546,7 +32834,7 @@
         <v>54</v>
       </c>
       <c r="C1783">
-        <v>5160</v>
+        <v>5210</v>
       </c>
       <c r="D1783" t="s">
         <v>1785</v>
@@ -32560,7 +32848,7 @@
         <v>55</v>
       </c>
       <c r="C1784">
-        <v>5180</v>
+        <v>5220</v>
       </c>
       <c r="D1784" t="s">
         <v>1786</v>
@@ -32574,7 +32862,7 @@
         <v>56</v>
       </c>
       <c r="C1785">
-        <v>5210</v>
+        <v>5240</v>
       </c>
       <c r="D1785" t="s">
         <v>1787</v>
@@ -32588,7 +32876,7 @@
         <v>57</v>
       </c>
       <c r="C1786">
-        <v>5250</v>
+        <v>5270</v>
       </c>
       <c r="D1786" t="s">
         <v>1788</v>
@@ -32616,7 +32904,7 @@
         <v>59</v>
       </c>
       <c r="C1788">
-        <v>5350</v>
+        <v>5330</v>
       </c>
       <c r="D1788" t="s">
         <v>1790</v>
@@ -32630,7 +32918,7 @@
         <v>60</v>
       </c>
       <c r="C1789">
-        <v>5400</v>
+        <v>5360</v>
       </c>
       <c r="D1789" t="s">
         <v>1791</v>
@@ -32644,7 +32932,7 @@
         <v>61</v>
       </c>
       <c r="C1790">
-        <v>5460</v>
+        <v>5380</v>
       </c>
       <c r="D1790" t="s">
         <v>1792</v>
@@ -32658,7 +32946,7 @@
         <v>62</v>
       </c>
       <c r="C1791">
-        <v>5530</v>
+        <v>5400</v>
       </c>
       <c r="D1791" t="s">
         <v>1793</v>
@@ -32672,7 +32960,7 @@
         <v>63</v>
       </c>
       <c r="C1792">
-        <v>5590</v>
+        <v>5420</v>
       </c>
       <c r="D1792" t="s">
         <v>1794</v>
@@ -32686,7 +32974,7 @@
         <v>64</v>
       </c>
       <c r="C1793">
-        <v>5660</v>
+        <v>5450</v>
       </c>
       <c r="D1793" t="s">
         <v>1795</v>
@@ -32700,7 +32988,7 @@
         <v>65</v>
       </c>
       <c r="C1794">
-        <v>5730</v>
+        <v>5500</v>
       </c>
       <c r="D1794" t="s">
         <v>1796</v>
@@ -32714,7 +33002,7 @@
         <v>66</v>
       </c>
       <c r="C1795">
-        <v>5800</v>
+        <v>5560</v>
       </c>
       <c r="D1795" t="s">
         <v>1797</v>
@@ -32728,7 +33016,7 @@
         <v>67</v>
       </c>
       <c r="C1796">
-        <v>5880</v>
+        <v>5640</v>
       </c>
       <c r="D1796" t="s">
         <v>1798</v>
@@ -32742,7 +33030,7 @@
         <v>68</v>
       </c>
       <c r="C1797">
-        <v>5970</v>
+        <v>5730</v>
       </c>
       <c r="D1797" t="s">
         <v>1799</v>
@@ -32756,7 +33044,7 @@
         <v>69</v>
       </c>
       <c r="C1798">
-        <v>6050</v>
+        <v>5830</v>
       </c>
       <c r="D1798" t="s">
         <v>1800</v>
@@ -32770,7 +33058,7 @@
         <v>70</v>
       </c>
       <c r="C1799">
-        <v>6140</v>
+        <v>5930</v>
       </c>
       <c r="D1799" t="s">
         <v>1801</v>
@@ -32784,7 +33072,7 @@
         <v>71</v>
       </c>
       <c r="C1800">
-        <v>6220</v>
+        <v>6030</v>
       </c>
       <c r="D1800" t="s">
         <v>1802</v>
@@ -32798,7 +33086,7 @@
         <v>72</v>
       </c>
       <c r="C1801">
-        <v>6300</v>
+        <v>6130</v>
       </c>
       <c r="D1801" t="s">
         <v>1803</v>
@@ -32812,7 +33100,7 @@
         <v>73</v>
       </c>
       <c r="C1802">
-        <v>6390</v>
+        <v>6220</v>
       </c>
       <c r="D1802" t="s">
         <v>1804</v>
@@ -32826,7 +33114,7 @@
         <v>74</v>
       </c>
       <c r="C1803">
-        <v>6480</v>
+        <v>6320</v>
       </c>
       <c r="D1803" t="s">
         <v>1805</v>
@@ -32840,7 +33128,7 @@
         <v>75</v>
       </c>
       <c r="C1804">
-        <v>6580</v>
+        <v>6430</v>
       </c>
       <c r="D1804" t="s">
         <v>1806</v>
@@ -32854,7 +33142,7 @@
         <v>76</v>
       </c>
       <c r="C1805">
-        <v>6690</v>
+        <v>6520</v>
       </c>
       <c r="D1805" t="s">
         <v>1807</v>
@@ -32868,7 +33156,7 @@
         <v>77</v>
       </c>
       <c r="C1806">
-        <v>6800</v>
+        <v>6620</v>
       </c>
       <c r="D1806" t="s">
         <v>1808</v>
@@ -32882,7 +33170,7 @@
         <v>78</v>
       </c>
       <c r="C1807">
-        <v>6890</v>
+        <v>6720</v>
       </c>
       <c r="D1807" t="s">
         <v>1809</v>
@@ -32896,7 +33184,7 @@
         <v>79</v>
       </c>
       <c r="C1808">
-        <v>6950</v>
+        <v>6800</v>
       </c>
       <c r="D1808" t="s">
         <v>1810</v>
@@ -32910,7 +33198,7 @@
         <v>80</v>
       </c>
       <c r="C1809">
-        <v>6980</v>
+        <v>6890</v>
       </c>
       <c r="D1809" t="s">
         <v>1811</v>
@@ -32924,7 +33212,7 @@
         <v>81</v>
       </c>
       <c r="C1810">
-        <v>7000</v>
+        <v>6940</v>
       </c>
       <c r="D1810" t="s">
         <v>1812</v>
@@ -32938,7 +33226,7 @@
         <v>82</v>
       </c>
       <c r="C1811">
-        <v>7000</v>
+        <v>6990</v>
       </c>
       <c r="D1811" t="s">
         <v>1813</v>
@@ -32952,7 +33240,7 @@
         <v>83</v>
       </c>
       <c r="C1812">
-        <v>7000</v>
+        <v>7030</v>
       </c>
       <c r="D1812" t="s">
         <v>1814</v>
@@ -32966,7 +33254,7 @@
         <v>84</v>
       </c>
       <c r="C1813">
-        <v>7000</v>
+        <v>7060</v>
       </c>
       <c r="D1813" t="s">
         <v>1815</v>
@@ -32980,7 +33268,7 @@
         <v>85</v>
       </c>
       <c r="C1814">
-        <v>7000</v>
+        <v>7050</v>
       </c>
       <c r="D1814" t="s">
         <v>1816</v>
@@ -32994,7 +33282,7 @@
         <v>86</v>
       </c>
       <c r="C1815">
-        <v>6920</v>
+        <v>7020</v>
       </c>
       <c r="D1815" t="s">
         <v>1817</v>
@@ -33008,7 +33296,7 @@
         <v>87</v>
       </c>
       <c r="C1816">
-        <v>6880</v>
+        <v>6960</v>
       </c>
       <c r="D1816" t="s">
         <v>1818</v>
@@ -33022,7 +33310,7 @@
         <v>88</v>
       </c>
       <c r="C1817">
-        <v>6780</v>
+        <v>6860</v>
       </c>
       <c r="D1817" t="s">
         <v>1819</v>
@@ -33036,7 +33324,7 @@
         <v>89</v>
       </c>
       <c r="C1818">
-        <v>6630</v>
+        <v>6740</v>
       </c>
       <c r="D1818" t="s">
         <v>1820</v>
@@ -33050,7 +33338,7 @@
         <v>90</v>
       </c>
       <c r="C1819">
-        <v>6520</v>
+        <v>6610</v>
       </c>
       <c r="D1819" t="s">
         <v>1821</v>
@@ -33064,7 +33352,7 @@
         <v>91</v>
       </c>
       <c r="C1820">
-        <v>6370</v>
+        <v>6460</v>
       </c>
       <c r="D1820" t="s">
         <v>1822</v>
@@ -33078,7 +33366,7 @@
         <v>92</v>
       </c>
       <c r="C1821">
-        <v>6240</v>
+        <v>6300</v>
       </c>
       <c r="D1821" t="s">
         <v>1823</v>
@@ -33092,7 +33380,7 @@
         <v>93</v>
       </c>
       <c r="C1822">
-        <v>6070</v>
+        <v>6130</v>
       </c>
       <c r="D1822" t="s">
         <v>1824</v>
@@ -33106,7 +33394,7 @@
         <v>94</v>
       </c>
       <c r="C1823">
-        <v>5920</v>
+        <v>6000</v>
       </c>
       <c r="D1823" t="s">
         <v>1825</v>
@@ -33120,7 +33408,7 @@
         <v>95</v>
       </c>
       <c r="C1824">
-        <v>5830</v>
+        <v>5880</v>
       </c>
       <c r="D1824" t="s">
         <v>1826</v>
@@ -33134,7 +33422,7 @@
         <v>96</v>
       </c>
       <c r="C1825">
-        <v>5720</v>
+        <v>5750</v>
       </c>
       <c r="D1825" t="s">
         <v>1827</v>
@@ -33148,7 +33436,7 @@
         <v>1</v>
       </c>
       <c r="C1826">
-        <v>5620</v>
+        <v>5400</v>
       </c>
       <c r="D1826" t="s">
         <v>1828</v>
@@ -33162,7 +33450,7 @@
         <v>2</v>
       </c>
       <c r="C1827">
-        <v>5580</v>
+        <v>5340</v>
       </c>
       <c r="D1827" t="s">
         <v>1829</v>
@@ -33176,7 +33464,7 @@
         <v>3</v>
       </c>
       <c r="C1828">
-        <v>5520</v>
+        <v>5300</v>
       </c>
       <c r="D1828" t="s">
         <v>1830</v>
@@ -33190,7 +33478,7 @@
         <v>4</v>
       </c>
       <c r="C1829">
-        <v>5440</v>
+        <v>5260</v>
       </c>
       <c r="D1829" t="s">
         <v>1831</v>
@@ -33204,7 +33492,7 @@
         <v>5</v>
       </c>
       <c r="C1830">
-        <v>5390</v>
+        <v>5230</v>
       </c>
       <c r="D1830" t="s">
         <v>1832</v>
@@ -33218,7 +33506,7 @@
         <v>6</v>
       </c>
       <c r="C1831">
-        <v>5340</v>
+        <v>5200</v>
       </c>
       <c r="D1831" t="s">
         <v>1833</v>
@@ -33232,7 +33520,7 @@
         <v>7</v>
       </c>
       <c r="C1832">
-        <v>5290</v>
+        <v>5170</v>
       </c>
       <c r="D1832" t="s">
         <v>1834</v>
@@ -33246,7 +33534,7 @@
         <v>8</v>
       </c>
       <c r="C1833">
-        <v>5250</v>
+        <v>5130</v>
       </c>
       <c r="D1833" t="s">
         <v>1835</v>
@@ -33260,7 +33548,7 @@
         <v>9</v>
       </c>
       <c r="C1834">
-        <v>5210</v>
+        <v>5090</v>
       </c>
       <c r="D1834" t="s">
         <v>1836</v>
@@ -33274,7 +33562,7 @@
         <v>10</v>
       </c>
       <c r="C1835">
-        <v>5180</v>
+        <v>5060</v>
       </c>
       <c r="D1835" t="s">
         <v>1837</v>
@@ -33288,7 +33576,7 @@
         <v>11</v>
       </c>
       <c r="C1836">
-        <v>5160</v>
+        <v>5040</v>
       </c>
       <c r="D1836" t="s">
         <v>1838</v>
@@ -33302,7 +33590,7 @@
         <v>12</v>
       </c>
       <c r="C1837">
-        <v>5150</v>
+        <v>5030</v>
       </c>
       <c r="D1837" t="s">
         <v>1839</v>
@@ -33316,7 +33604,7 @@
         <v>13</v>
       </c>
       <c r="C1838">
-        <v>5140</v>
+        <v>5030</v>
       </c>
       <c r="D1838" t="s">
         <v>1840</v>
@@ -33330,7 +33618,7 @@
         <v>14</v>
       </c>
       <c r="C1839">
-        <v>5150</v>
+        <v>5040</v>
       </c>
       <c r="D1839" t="s">
         <v>1841</v>
@@ -33344,7 +33632,7 @@
         <v>15</v>
       </c>
       <c r="C1840">
-        <v>5150</v>
+        <v>5050</v>
       </c>
       <c r="D1840" t="s">
         <v>1842</v>
@@ -33358,7 +33646,7 @@
         <v>16</v>
       </c>
       <c r="C1841">
-        <v>5150</v>
+        <v>5070</v>
       </c>
       <c r="D1841" t="s">
         <v>1843</v>
@@ -33372,7 +33660,7 @@
         <v>17</v>
       </c>
       <c r="C1842">
-        <v>5150</v>
+        <v>5090</v>
       </c>
       <c r="D1842" t="s">
         <v>1844</v>
@@ -33386,7 +33674,7 @@
         <v>18</v>
       </c>
       <c r="C1843">
-        <v>5160</v>
+        <v>5110</v>
       </c>
       <c r="D1843" t="s">
         <v>1845</v>
@@ -33400,7 +33688,7 @@
         <v>19</v>
       </c>
       <c r="C1844">
-        <v>5160</v>
+        <v>5130</v>
       </c>
       <c r="D1844" t="s">
         <v>1846</v>
@@ -33414,7 +33702,7 @@
         <v>20</v>
       </c>
       <c r="C1845">
-        <v>5170</v>
+        <v>5150</v>
       </c>
       <c r="D1845" t="s">
         <v>1847</v>
@@ -33428,7 +33716,7 @@
         <v>21</v>
       </c>
       <c r="C1846">
-        <v>5190</v>
+        <v>5200</v>
       </c>
       <c r="D1846" t="s">
         <v>1848</v>
@@ -33442,7 +33730,7 @@
         <v>22</v>
       </c>
       <c r="C1847">
-        <v>5210</v>
+        <v>5230</v>
       </c>
       <c r="D1847" t="s">
         <v>1849</v>
@@ -33456,7 +33744,7 @@
         <v>23</v>
       </c>
       <c r="C1848">
-        <v>5260</v>
+        <v>5250</v>
       </c>
       <c r="D1848" t="s">
         <v>1850</v>
@@ -33470,7 +33758,7 @@
         <v>24</v>
       </c>
       <c r="C1849">
-        <v>5320</v>
+        <v>5270</v>
       </c>
       <c r="D1849" t="s">
         <v>1851</v>
@@ -33484,7 +33772,7 @@
         <v>25</v>
       </c>
       <c r="C1850">
-        <v>5390</v>
+        <v>5310</v>
       </c>
       <c r="D1850" t="s">
         <v>1852</v>
@@ -33498,7 +33786,7 @@
         <v>26</v>
       </c>
       <c r="C1851">
-        <v>5480</v>
+        <v>5350</v>
       </c>
       <c r="D1851" t="s">
         <v>1853</v>
@@ -33512,7 +33800,7 @@
         <v>27</v>
       </c>
       <c r="C1852">
-        <v>5570</v>
+        <v>5400</v>
       </c>
       <c r="D1852" t="s">
         <v>1854</v>
@@ -33526,7 +33814,7 @@
         <v>28</v>
       </c>
       <c r="C1853">
-        <v>5670</v>
+        <v>5500</v>
       </c>
       <c r="D1853" t="s">
         <v>1855</v>
@@ -33540,7 +33828,7 @@
         <v>29</v>
       </c>
       <c r="C1854">
-        <v>5770</v>
+        <v>5620</v>
       </c>
       <c r="D1854" t="s">
         <v>1856</v>
@@ -33554,7 +33842,7 @@
         <v>30</v>
       </c>
       <c r="C1855">
-        <v>5860</v>
+        <v>5700</v>
       </c>
       <c r="D1855" t="s">
         <v>1857</v>
@@ -33568,7 +33856,7 @@
         <v>31</v>
       </c>
       <c r="C1856">
-        <v>5930</v>
+        <v>5750</v>
       </c>
       <c r="D1856" t="s">
         <v>1858</v>
@@ -33582,7 +33870,7 @@
         <v>32</v>
       </c>
       <c r="C1857">
-        <v>5990</v>
+        <v>5780</v>
       </c>
       <c r="D1857" t="s">
         <v>1859</v>
@@ -33596,7 +33884,7 @@
         <v>33</v>
       </c>
       <c r="C1858">
-        <v>6030</v>
+        <v>5790</v>
       </c>
       <c r="D1858" t="s">
         <v>1860</v>
@@ -33610,7 +33898,7 @@
         <v>34</v>
       </c>
       <c r="C1859">
-        <v>6040</v>
+        <v>5800</v>
       </c>
       <c r="D1859" t="s">
         <v>1861</v>
@@ -33624,7 +33912,7 @@
         <v>35</v>
       </c>
       <c r="C1860">
-        <v>6020</v>
+        <v>5780</v>
       </c>
       <c r="D1860" t="s">
         <v>1862</v>
@@ -33638,7 +33926,7 @@
         <v>36</v>
       </c>
       <c r="C1861">
-        <v>5990</v>
+        <v>5740</v>
       </c>
       <c r="D1861" t="s">
         <v>1863</v>
@@ -33652,7 +33940,7 @@
         <v>37</v>
       </c>
       <c r="C1862">
-        <v>5920</v>
+        <v>5650</v>
       </c>
       <c r="D1862" t="s">
         <v>1864</v>
@@ -33666,7 +33954,7 @@
         <v>38</v>
       </c>
       <c r="C1863">
-        <v>5850</v>
+        <v>5560</v>
       </c>
       <c r="D1863" t="s">
         <v>1865</v>
@@ -33680,7 +33968,7 @@
         <v>39</v>
       </c>
       <c r="C1864">
-        <v>5760</v>
+        <v>5460</v>
       </c>
       <c r="D1864" t="s">
         <v>1866</v>
@@ -33694,7 +33982,7 @@
         <v>40</v>
       </c>
       <c r="C1865">
-        <v>5660</v>
+        <v>5360</v>
       </c>
       <c r="D1865" t="s">
         <v>1867</v>
@@ -33708,7 +33996,7 @@
         <v>41</v>
       </c>
       <c r="C1866">
-        <v>5560</v>
+        <v>5250</v>
       </c>
       <c r="D1866" t="s">
         <v>1868</v>
@@ -33722,7 +34010,7 @@
         <v>42</v>
       </c>
       <c r="C1867">
-        <v>5470</v>
+        <v>5140</v>
       </c>
       <c r="D1867" t="s">
         <v>1869</v>
@@ -33736,7 +34024,7 @@
         <v>43</v>
       </c>
       <c r="C1868">
-        <v>5390</v>
+        <v>5050</v>
       </c>
       <c r="D1868" t="s">
         <v>1870</v>
@@ -33750,7 +34038,7 @@
         <v>44</v>
       </c>
       <c r="C1869">
-        <v>5320</v>
+        <v>4970</v>
       </c>
       <c r="D1869" t="s">
         <v>1871</v>
@@ -33764,7 +34052,7 @@
         <v>45</v>
       </c>
       <c r="C1870">
-        <v>5260</v>
+        <v>4900</v>
       </c>
       <c r="D1870" t="s">
         <v>1872</v>
@@ -33778,7 +34066,7 @@
         <v>46</v>
       </c>
       <c r="C1871">
-        <v>5220</v>
+        <v>4850</v>
       </c>
       <c r="D1871" t="s">
         <v>1873</v>
@@ -33792,7 +34080,7 @@
         <v>47</v>
       </c>
       <c r="C1872">
-        <v>5190</v>
+        <v>4830</v>
       </c>
       <c r="D1872" t="s">
         <v>1874</v>
@@ -33806,7 +34094,7 @@
         <v>48</v>
       </c>
       <c r="C1873">
-        <v>5170</v>
+        <v>4820</v>
       </c>
       <c r="D1873" t="s">
         <v>1875</v>
@@ -33820,7 +34108,7 @@
         <v>49</v>
       </c>
       <c r="C1874">
-        <v>5160</v>
+        <v>4820</v>
       </c>
       <c r="D1874" t="s">
         <v>1876</v>
@@ -33834,7 +34122,7 @@
         <v>50</v>
       </c>
       <c r="C1875">
-        <v>5160</v>
+        <v>4820</v>
       </c>
       <c r="D1875" t="s">
         <v>1877</v>
@@ -33848,7 +34136,7 @@
         <v>51</v>
       </c>
       <c r="C1876">
-        <v>5170</v>
+        <v>4830</v>
       </c>
       <c r="D1876" t="s">
         <v>1878</v>
@@ -33862,7 +34150,7 @@
         <v>52</v>
       </c>
       <c r="C1877">
-        <v>5180</v>
+        <v>4850</v>
       </c>
       <c r="D1877" t="s">
         <v>1879</v>
@@ -33876,7 +34164,7 @@
         <v>53</v>
       </c>
       <c r="C1878">
-        <v>5200</v>
+        <v>4900</v>
       </c>
       <c r="D1878" t="s">
         <v>1880</v>
@@ -33890,7 +34178,7 @@
         <v>54</v>
       </c>
       <c r="C1879">
-        <v>5220</v>
+        <v>4950</v>
       </c>
       <c r="D1879" t="s">
         <v>1881</v>
@@ -33904,7 +34192,7 @@
         <v>55</v>
       </c>
       <c r="C1880">
-        <v>5250</v>
+        <v>4990</v>
       </c>
       <c r="D1880" t="s">
         <v>1882</v>
@@ -33918,7 +34206,7 @@
         <v>56</v>
       </c>
       <c r="C1881">
-        <v>5290</v>
+        <v>5020</v>
       </c>
       <c r="D1881" t="s">
         <v>1883</v>
@@ -33932,7 +34220,7 @@
         <v>57</v>
       </c>
       <c r="C1882">
-        <v>5340</v>
+        <v>5070</v>
       </c>
       <c r="D1882" t="s">
         <v>1884</v>
@@ -33946,7 +34234,7 @@
         <v>58</v>
       </c>
       <c r="C1883">
-        <v>5380</v>
+        <v>5110</v>
       </c>
       <c r="D1883" t="s">
         <v>1885</v>
@@ -33960,7 +34248,7 @@
         <v>59</v>
       </c>
       <c r="C1884">
-        <v>5440</v>
+        <v>5140</v>
       </c>
       <c r="D1884" t="s">
         <v>1886</v>
@@ -33974,7 +34262,7 @@
         <v>60</v>
       </c>
       <c r="C1885">
-        <v>5490</v>
+        <v>5190</v>
       </c>
       <c r="D1885" t="s">
         <v>1887</v>
@@ -33988,7 +34276,7 @@
         <v>61</v>
       </c>
       <c r="C1886">
-        <v>5550</v>
+        <v>5270</v>
       </c>
       <c r="D1886" t="s">
         <v>1888</v>
@@ -34002,7 +34290,7 @@
         <v>62</v>
       </c>
       <c r="C1887">
-        <v>5620</v>
+        <v>5320</v>
       </c>
       <c r="D1887" t="s">
         <v>1889</v>
@@ -34016,7 +34304,7 @@
         <v>63</v>
       </c>
       <c r="C1888">
-        <v>5680</v>
+        <v>5370</v>
       </c>
       <c r="D1888" t="s">
         <v>1890</v>
@@ -34030,7 +34318,7 @@
         <v>64</v>
       </c>
       <c r="C1889">
-        <v>5760</v>
+        <v>5430</v>
       </c>
       <c r="D1889" t="s">
         <v>1891</v>
@@ -34044,7 +34332,7 @@
         <v>65</v>
       </c>
       <c r="C1890">
-        <v>5850</v>
+        <v>5510</v>
       </c>
       <c r="D1890" t="s">
         <v>1892</v>
@@ -34058,7 +34346,7 @@
         <v>66</v>
       </c>
       <c r="C1891">
-        <v>5940</v>
+        <v>5580</v>
       </c>
       <c r="D1891" t="s">
         <v>1893</v>
@@ -34072,7 +34360,7 @@
         <v>67</v>
       </c>
       <c r="C1892">
-        <v>6050</v>
+        <v>5680</v>
       </c>
       <c r="D1892" t="s">
         <v>1894</v>
@@ -34086,7 +34374,7 @@
         <v>68</v>
       </c>
       <c r="C1893">
-        <v>6160</v>
+        <v>5790</v>
       </c>
       <c r="D1893" t="s">
         <v>1895</v>
@@ -34100,7 +34388,7 @@
         <v>69</v>
       </c>
       <c r="C1894">
-        <v>6270</v>
+        <v>5900</v>
       </c>
       <c r="D1894" t="s">
         <v>1896</v>
@@ -34114,7 +34402,7 @@
         <v>70</v>
       </c>
       <c r="C1895">
-        <v>6380</v>
+        <v>6010</v>
       </c>
       <c r="D1895" t="s">
         <v>1897</v>
@@ -34128,7 +34416,7 @@
         <v>71</v>
       </c>
       <c r="C1896">
-        <v>6480</v>
+        <v>6110</v>
       </c>
       <c r="D1896" t="s">
         <v>1898</v>
@@ -34142,7 +34430,7 @@
         <v>72</v>
       </c>
       <c r="C1897">
-        <v>6570</v>
+        <v>6220</v>
       </c>
       <c r="D1897" t="s">
         <v>1899</v>
@@ -34156,7 +34444,7 @@
         <v>73</v>
       </c>
       <c r="C1898">
-        <v>6660</v>
+        <v>6330</v>
       </c>
       <c r="D1898" t="s">
         <v>1900</v>
@@ -34170,7 +34458,7 @@
         <v>74</v>
       </c>
       <c r="C1899">
-        <v>6740</v>
+        <v>6440</v>
       </c>
       <c r="D1899" t="s">
         <v>1901</v>
@@ -34184,7 +34472,7 @@
         <v>75</v>
       </c>
       <c r="C1900">
-        <v>6830</v>
+        <v>6540</v>
       </c>
       <c r="D1900" t="s">
         <v>1902</v>
@@ -34198,7 +34486,7 @@
         <v>76</v>
       </c>
       <c r="C1901">
-        <v>6920</v>
+        <v>6660</v>
       </c>
       <c r="D1901" t="s">
         <v>1903</v>
@@ -34212,7 +34500,7 @@
         <v>77</v>
       </c>
       <c r="C1902">
-        <v>7010</v>
+        <v>6790</v>
       </c>
       <c r="D1902" t="s">
         <v>1904</v>
@@ -34226,7 +34514,7 @@
         <v>78</v>
       </c>
       <c r="C1903">
-        <v>7090</v>
+        <v>6870</v>
       </c>
       <c r="D1903" t="s">
         <v>1905</v>
@@ -34240,7 +34528,7 @@
         <v>79</v>
       </c>
       <c r="C1904">
-        <v>7140</v>
+        <v>6940</v>
       </c>
       <c r="D1904" t="s">
         <v>1906</v>
@@ -34254,7 +34542,7 @@
         <v>80</v>
       </c>
       <c r="C1905">
-        <v>7170</v>
+        <v>7000</v>
       </c>
       <c r="D1905" t="s">
         <v>1907</v>
@@ -34268,7 +34556,7 @@
         <v>81</v>
       </c>
       <c r="C1906">
-        <v>7200</v>
+        <v>7050</v>
       </c>
       <c r="D1906" t="s">
         <v>1908</v>
@@ -34282,7 +34570,7 @@
         <v>82</v>
       </c>
       <c r="C1907">
-        <v>7240</v>
+        <v>7080</v>
       </c>
       <c r="D1907" t="s">
         <v>1909</v>
@@ -34296,7 +34584,7 @@
         <v>83</v>
       </c>
       <c r="C1908">
-        <v>7250</v>
+        <v>7090</v>
       </c>
       <c r="D1908" t="s">
         <v>1910</v>
@@ -34310,7 +34598,7 @@
         <v>84</v>
       </c>
       <c r="C1909">
-        <v>7250</v>
+        <v>7090</v>
       </c>
       <c r="D1909" t="s">
         <v>1911</v>
@@ -34324,7 +34612,7 @@
         <v>85</v>
       </c>
       <c r="C1910">
-        <v>7250</v>
+        <v>7080</v>
       </c>
       <c r="D1910" t="s">
         <v>1912</v>
@@ -34338,7 +34626,7 @@
         <v>86</v>
       </c>
       <c r="C1911">
-        <v>7250</v>
+        <v>7070</v>
       </c>
       <c r="D1911" t="s">
         <v>1913</v>
@@ -34352,7 +34640,7 @@
         <v>87</v>
       </c>
       <c r="C1912">
-        <v>7250</v>
+        <v>7020</v>
       </c>
       <c r="D1912" t="s">
         <v>1914</v>
@@ -34366,7 +34654,7 @@
         <v>88</v>
       </c>
       <c r="C1913">
-        <v>7120</v>
+        <v>6940</v>
       </c>
       <c r="D1913" t="s">
         <v>1915</v>
@@ -34380,7 +34668,7 @@
         <v>89</v>
       </c>
       <c r="C1914">
-        <v>6920</v>
+        <v>6780</v>
       </c>
       <c r="D1914" t="s">
         <v>1916</v>
@@ -34394,7 +34682,7 @@
         <v>90</v>
       </c>
       <c r="C1915">
-        <v>6780</v>
+        <v>6610</v>
       </c>
       <c r="D1915" t="s">
         <v>1917</v>
@@ -34408,7 +34696,7 @@
         <v>91</v>
       </c>
       <c r="C1916">
-        <v>6620</v>
+        <v>6440</v>
       </c>
       <c r="D1916" t="s">
         <v>1918</v>
@@ -34422,7 +34710,7 @@
         <v>92</v>
       </c>
       <c r="C1917">
-        <v>6460</v>
+        <v>6280</v>
       </c>
       <c r="D1917" t="s">
         <v>1919</v>
@@ -34436,7 +34724,7 @@
         <v>93</v>
       </c>
       <c r="C1918">
-        <v>6250</v>
+        <v>6140</v>
       </c>
       <c r="D1918" t="s">
         <v>1920</v>
@@ -34450,7 +34738,7 @@
         <v>94</v>
       </c>
       <c r="C1919">
-        <v>6060</v>
+        <v>6010</v>
       </c>
       <c r="D1919" t="s">
         <v>1921</v>
@@ -34464,7 +34752,7 @@
         <v>95</v>
       </c>
       <c r="C1920">
-        <v>5980</v>
+        <v>5920</v>
       </c>
       <c r="D1920" t="s">
         <v>1922</v>
@@ -34478,7 +34766,7 @@
         <v>96</v>
       </c>
       <c r="C1921">
-        <v>5870</v>
+        <v>5820</v>
       </c>
       <c r="D1921" t="s">
         <v>1923</v>
@@ -34492,7 +34780,7 @@
         <v>1</v>
       </c>
       <c r="C1922">
-        <v>5680</v>
+        <v>5640</v>
       </c>
       <c r="D1922" t="s">
         <v>1924</v>
@@ -34506,7 +34794,7 @@
         <v>2</v>
       </c>
       <c r="C1923">
-        <v>5640</v>
+        <v>5590</v>
       </c>
       <c r="D1923" t="s">
         <v>1925</v>
@@ -34520,7 +34808,7 @@
         <v>3</v>
       </c>
       <c r="C1924">
-        <v>5580</v>
+        <v>5540</v>
       </c>
       <c r="D1924" t="s">
         <v>1926</v>
@@ -34534,7 +34822,7 @@
         <v>4</v>
       </c>
       <c r="C1925">
-        <v>5500</v>
+        <v>5470</v>
       </c>
       <c r="D1925" t="s">
         <v>1927</v>
@@ -34548,7 +34836,7 @@
         <v>5</v>
       </c>
       <c r="C1926">
-        <v>5450</v>
+        <v>5400</v>
       </c>
       <c r="D1926" t="s">
         <v>1928</v>
@@ -34562,7 +34850,7 @@
         <v>6</v>
       </c>
       <c r="C1927">
-        <v>5400</v>
+        <v>5340</v>
       </c>
       <c r="D1927" t="s">
         <v>1929</v>
@@ -34576,7 +34864,7 @@
         <v>7</v>
       </c>
       <c r="C1928">
-        <v>5350</v>
+        <v>5280</v>
       </c>
       <c r="D1928" t="s">
         <v>1930</v>
@@ -34590,7 +34878,7 @@
         <v>8</v>
       </c>
       <c r="C1929">
-        <v>5310</v>
+        <v>5240</v>
       </c>
       <c r="D1929" t="s">
         <v>1931</v>
@@ -34604,7 +34892,7 @@
         <v>9</v>
       </c>
       <c r="C1930">
-        <v>5260</v>
+        <v>5200</v>
       </c>
       <c r="D1930" t="s">
         <v>1932</v>
@@ -34618,7 +34906,7 @@
         <v>10</v>
       </c>
       <c r="C1931">
-        <v>5230</v>
+        <v>5170</v>
       </c>
       <c r="D1931" t="s">
         <v>1933</v>
@@ -34632,7 +34920,7 @@
         <v>11</v>
       </c>
       <c r="C1932">
-        <v>5210</v>
+        <v>5140</v>
       </c>
       <c r="D1932" t="s">
         <v>1934</v>
@@ -34646,7 +34934,7 @@
         <v>12</v>
       </c>
       <c r="C1933">
-        <v>5190</v>
+        <v>5130</v>
       </c>
       <c r="D1933" t="s">
         <v>1935</v>
@@ -34660,7 +34948,7 @@
         <v>13</v>
       </c>
       <c r="C1934">
-        <v>5190</v>
+        <v>5120</v>
       </c>
       <c r="D1934" t="s">
         <v>1936</v>
@@ -34674,7 +34962,7 @@
         <v>14</v>
       </c>
       <c r="C1935">
-        <v>5190</v>
+        <v>5110</v>
       </c>
       <c r="D1935" t="s">
         <v>1937</v>
@@ -34688,7 +34976,7 @@
         <v>15</v>
       </c>
       <c r="C1936">
-        <v>5190</v>
+        <v>5100</v>
       </c>
       <c r="D1936" t="s">
         <v>1938</v>
@@ -34702,7 +34990,7 @@
         <v>16</v>
       </c>
       <c r="C1937">
-        <v>5190</v>
+        <v>5100</v>
       </c>
       <c r="D1937" t="s">
         <v>1939</v>
@@ -34716,7 +35004,7 @@
         <v>17</v>
       </c>
       <c r="C1938">
-        <v>5190</v>
+        <v>5110</v>
       </c>
       <c r="D1938" t="s">
         <v>1940</v>
@@ -34730,7 +35018,7 @@
         <v>18</v>
       </c>
       <c r="C1939">
-        <v>5190</v>
+        <v>5120</v>
       </c>
       <c r="D1939" t="s">
         <v>1941</v>
@@ -34744,7 +35032,7 @@
         <v>19</v>
       </c>
       <c r="C1940">
-        <v>5190</v>
+        <v>5130</v>
       </c>
       <c r="D1940" t="s">
         <v>1942</v>
@@ -34758,7 +35046,7 @@
         <v>20</v>
       </c>
       <c r="C1941">
-        <v>5200</v>
+        <v>5150</v>
       </c>
       <c r="D1941" t="s">
         <v>1943</v>
@@ -34772,7 +35060,7 @@
         <v>21</v>
       </c>
       <c r="C1942">
-        <v>5220</v>
+        <v>5180</v>
       </c>
       <c r="D1942" t="s">
         <v>1944</v>
@@ -34786,7 +35074,7 @@
         <v>22</v>
       </c>
       <c r="C1943">
-        <v>5250</v>
+        <v>5210</v>
       </c>
       <c r="D1943" t="s">
         <v>1945</v>
@@ -34800,7 +35088,7 @@
         <v>23</v>
       </c>
       <c r="C1944">
-        <v>5300</v>
+        <v>5240</v>
       </c>
       <c r="D1944" t="s">
         <v>1946</v>
@@ -34814,7 +35102,7 @@
         <v>24</v>
       </c>
       <c r="C1945">
-        <v>5360</v>
+        <v>5290</v>
       </c>
       <c r="D1945" t="s">
         <v>1947</v>
@@ -34828,7 +35116,7 @@
         <v>25</v>
       </c>
       <c r="C1946">
-        <v>5430</v>
+        <v>5360</v>
       </c>
       <c r="D1946" t="s">
         <v>1948</v>
@@ -34842,7 +35130,7 @@
         <v>26</v>
       </c>
       <c r="C1947">
-        <v>5520</v>
+        <v>5430</v>
       </c>
       <c r="D1947" t="s">
         <v>1949</v>
@@ -34856,7 +35144,7 @@
         <v>27</v>
       </c>
       <c r="C1948">
-        <v>5610</v>
+        <v>5510</v>
       </c>
       <c r="D1948" t="s">
         <v>1950</v>
@@ -34870,7 +35158,7 @@
         <v>28</v>
       </c>
       <c r="C1949">
-        <v>5700</v>
+        <v>5590</v>
       </c>
       <c r="D1949" t="s">
         <v>1951</v>
@@ -34884,7 +35172,7 @@
         <v>29</v>
       </c>
       <c r="C1950">
-        <v>5790</v>
+        <v>5670</v>
       </c>
       <c r="D1950" t="s">
         <v>1952</v>
@@ -34898,7 +35186,7 @@
         <v>30</v>
       </c>
       <c r="C1951">
-        <v>5870</v>
+        <v>5750</v>
       </c>
       <c r="D1951" t="s">
         <v>1953</v>
@@ -34912,7 +35200,7 @@
         <v>31</v>
       </c>
       <c r="C1952">
-        <v>5940</v>
+        <v>5810</v>
       </c>
       <c r="D1952" t="s">
         <v>1954</v>
@@ -34926,7 +35214,7 @@
         <v>32</v>
       </c>
       <c r="C1953">
-        <v>6000</v>
+        <v>5840</v>
       </c>
       <c r="D1953" t="s">
         <v>1955</v>
@@ -34940,7 +35228,7 @@
         <v>33</v>
       </c>
       <c r="C1954">
-        <v>6030</v>
+        <v>5850</v>
       </c>
       <c r="D1954" t="s">
         <v>1956</v>
@@ -34954,7 +35242,7 @@
         <v>34</v>
       </c>
       <c r="C1955">
-        <v>6030</v>
+        <v>5850</v>
       </c>
       <c r="D1955" t="s">
         <v>1957</v>
@@ -34968,7 +35256,7 @@
         <v>35</v>
       </c>
       <c r="C1956">
-        <v>6020</v>
+        <v>5820</v>
       </c>
       <c r="D1956" t="s">
         <v>1958</v>
@@ -34982,7 +35270,7 @@
         <v>36</v>
       </c>
       <c r="C1957">
-        <v>5970</v>
+        <v>5740</v>
       </c>
       <c r="D1957" t="s">
         <v>1959</v>
@@ -34996,7 +35284,7 @@
         <v>37</v>
       </c>
       <c r="C1958">
-        <v>5910</v>
+        <v>5640</v>
       </c>
       <c r="D1958" t="s">
         <v>1960</v>
@@ -35010,7 +35298,7 @@
         <v>38</v>
       </c>
       <c r="C1959">
-        <v>5820</v>
+        <v>5530</v>
       </c>
       <c r="D1959" t="s">
         <v>1961</v>
@@ -35024,7 +35312,7 @@
         <v>39</v>
       </c>
       <c r="C1960">
-        <v>5720</v>
+        <v>5430</v>
       </c>
       <c r="D1960" t="s">
         <v>1962</v>
@@ -35038,7 +35326,7 @@
         <v>40</v>
       </c>
       <c r="C1961">
-        <v>5620</v>
+        <v>5310</v>
       </c>
       <c r="D1961" t="s">
         <v>1963</v>
@@ -35052,7 +35340,7 @@
         <v>41</v>
       </c>
       <c r="C1962">
-        <v>5510</v>
+        <v>5200</v>
       </c>
       <c r="D1962" t="s">
         <v>1964</v>
@@ -35066,7 +35354,7 @@
         <v>42</v>
       </c>
       <c r="C1963">
-        <v>5410</v>
+        <v>5100</v>
       </c>
       <c r="D1963" t="s">
         <v>1965</v>
@@ -35080,7 +35368,7 @@
         <v>43</v>
       </c>
       <c r="C1964">
-        <v>5320</v>
+        <v>5010</v>
       </c>
       <c r="D1964" t="s">
         <v>1966</v>
@@ -35094,7 +35382,7 @@
         <v>44</v>
       </c>
       <c r="C1965">
-        <v>5240</v>
+        <v>4940</v>
       </c>
       <c r="D1965" t="s">
         <v>1967</v>
@@ -35108,7 +35396,7 @@
         <v>45</v>
       </c>
       <c r="C1966">
-        <v>5180</v>
+        <v>4890</v>
       </c>
       <c r="D1966" t="s">
         <v>1968</v>
@@ -35122,7 +35410,7 @@
         <v>46</v>
       </c>
       <c r="C1967">
-        <v>5140</v>
+        <v>4860</v>
       </c>
       <c r="D1967" t="s">
         <v>1969</v>
@@ -35136,7 +35424,7 @@
         <v>47</v>
       </c>
       <c r="C1968">
-        <v>5120</v>
+        <v>4830</v>
       </c>
       <c r="D1968" t="s">
         <v>1970</v>
@@ -35150,7 +35438,7 @@
         <v>48</v>
       </c>
       <c r="C1969">
-        <v>5110</v>
+        <v>4820</v>
       </c>
       <c r="D1969" t="s">
         <v>1971</v>
@@ -35164,7 +35452,7 @@
         <v>49</v>
       </c>
       <c r="C1970">
-        <v>5100</v>
+        <v>4810</v>
       </c>
       <c r="D1970" t="s">
         <v>1972</v>
@@ -35178,7 +35466,7 @@
         <v>50</v>
       </c>
       <c r="C1971">
-        <v>5110</v>
+        <v>4810</v>
       </c>
       <c r="D1971" t="s">
         <v>1973</v>
@@ -35192,7 +35480,7 @@
         <v>51</v>
       </c>
       <c r="C1972">
-        <v>5120</v>
+        <v>4820</v>
       </c>
       <c r="D1972" t="s">
         <v>1974</v>
@@ -35206,7 +35494,7 @@
         <v>52</v>
       </c>
       <c r="C1973">
-        <v>5140</v>
+        <v>4830</v>
       </c>
       <c r="D1973" t="s">
         <v>1975</v>
@@ -35220,7 +35508,7 @@
         <v>53</v>
       </c>
       <c r="C1974">
-        <v>5160</v>
+        <v>4850</v>
       </c>
       <c r="D1974" t="s">
         <v>1976</v>
@@ -35234,7 +35522,7 @@
         <v>54</v>
       </c>
       <c r="C1975">
-        <v>5180</v>
+        <v>4880</v>
       </c>
       <c r="D1975" t="s">
         <v>1977</v>
@@ -35248,7 +35536,7 @@
         <v>55</v>
       </c>
       <c r="C1976">
-        <v>5210</v>
+        <v>4920</v>
       </c>
       <c r="D1976" t="s">
         <v>1978</v>
@@ -35262,7 +35550,7 @@
         <v>56</v>
       </c>
       <c r="C1977">
-        <v>5250</v>
+        <v>4970</v>
       </c>
       <c r="D1977" t="s">
         <v>1979</v>
@@ -35276,7 +35564,7 @@
         <v>57</v>
       </c>
       <c r="C1978">
-        <v>5290</v>
+        <v>5020</v>
       </c>
       <c r="D1978" t="s">
         <v>1980</v>
@@ -35290,7 +35578,7 @@
         <v>58</v>
       </c>
       <c r="C1979">
-        <v>5340</v>
+        <v>5080</v>
       </c>
       <c r="D1979" t="s">
         <v>1981</v>
@@ -35304,7 +35592,7 @@
         <v>59</v>
       </c>
       <c r="C1980">
-        <v>5390</v>
+        <v>5140</v>
       </c>
       <c r="D1980" t="s">
         <v>1982</v>
@@ -35318,7 +35606,7 @@
         <v>60</v>
       </c>
       <c r="C1981">
-        <v>5440</v>
+        <v>5200</v>
       </c>
       <c r="D1981" t="s">
         <v>1983</v>
@@ -35332,7 +35620,7 @@
         <v>61</v>
       </c>
       <c r="C1982">
-        <v>5490</v>
+        <v>5250</v>
       </c>
       <c r="D1982" t="s">
         <v>1984</v>
@@ -35346,7 +35634,7 @@
         <v>62</v>
       </c>
       <c r="C1983">
-        <v>5550</v>
+        <v>5290</v>
       </c>
       <c r="D1983" t="s">
         <v>1985</v>
@@ -35360,7 +35648,7 @@
         <v>63</v>
       </c>
       <c r="C1984">
-        <v>5610</v>
+        <v>5330</v>
       </c>
       <c r="D1984" t="s">
         <v>1986</v>
@@ -35374,7 +35662,7 @@
         <v>64</v>
       </c>
       <c r="C1985">
-        <v>5680</v>
+        <v>5380</v>
       </c>
       <c r="D1985" t="s">
         <v>1987</v>
@@ -35388,7 +35676,7 @@
         <v>65</v>
       </c>
       <c r="C1986">
-        <v>5750</v>
+        <v>5440</v>
       </c>
       <c r="D1986" t="s">
         <v>1988</v>
@@ -35402,7 +35690,7 @@
         <v>66</v>
       </c>
       <c r="C1987">
-        <v>5840</v>
+        <v>5510</v>
       </c>
       <c r="D1987" t="s">
         <v>1989</v>
@@ -35416,7 +35704,7 @@
         <v>67</v>
       </c>
       <c r="C1988">
-        <v>5940</v>
+        <v>5590</v>
       </c>
       <c r="D1988" t="s">
         <v>1990</v>
@@ -35430,7 +35718,7 @@
         <v>68</v>
       </c>
       <c r="C1989">
-        <v>6050</v>
+        <v>5690</v>
       </c>
       <c r="D1989" t="s">
         <v>1991</v>
@@ -35444,7 +35732,7 @@
         <v>69</v>
       </c>
       <c r="C1990">
-        <v>6160</v>
+        <v>5810</v>
       </c>
       <c r="D1990" t="s">
         <v>1992</v>
@@ -35458,7 +35746,7 @@
         <v>70</v>
       </c>
       <c r="C1991">
-        <v>6270</v>
+        <v>5920</v>
       </c>
       <c r="D1991" t="s">
         <v>1993</v>
@@ -35472,7 +35760,7 @@
         <v>71</v>
       </c>
       <c r="C1992">
-        <v>6380</v>
+        <v>6030</v>
       </c>
       <c r="D1992" t="s">
         <v>1994</v>
@@ -35486,7 +35774,7 @@
         <v>72</v>
       </c>
       <c r="C1993">
-        <v>6480</v>
+        <v>6140</v>
       </c>
       <c r="D1993" t="s">
         <v>1995</v>
@@ -35500,7 +35788,7 @@
         <v>73</v>
       </c>
       <c r="C1994">
-        <v>6580</v>
+        <v>6250</v>
       </c>
       <c r="D1994" t="s">
         <v>1996</v>
@@ -35514,7 +35802,7 @@
         <v>74</v>
       </c>
       <c r="C1995">
-        <v>6670</v>
+        <v>6360</v>
       </c>
       <c r="D1995" t="s">
         <v>1997</v>
@@ -35528,7 +35816,7 @@
         <v>75</v>
       </c>
       <c r="C1996">
-        <v>6760</v>
+        <v>6480</v>
       </c>
       <c r="D1996" t="s">
         <v>1998</v>
@@ -35542,7 +35830,7 @@
         <v>76</v>
       </c>
       <c r="C1997">
-        <v>6850</v>
+        <v>6610</v>
       </c>
       <c r="D1997" t="s">
         <v>1999</v>
@@ -35556,7 +35844,7 @@
         <v>77</v>
       </c>
       <c r="C1998">
-        <v>6940</v>
+        <v>6740</v>
       </c>
       <c r="D1998" t="s">
         <v>2000</v>
@@ -35570,7 +35858,7 @@
         <v>78</v>
       </c>
       <c r="C1999">
-        <v>7010</v>
+        <v>6860</v>
       </c>
       <c r="D1999" t="s">
         <v>2001</v>
@@ -35584,7 +35872,7 @@
         <v>79</v>
       </c>
       <c r="C2000">
-        <v>7060</v>
+        <v>6950</v>
       </c>
       <c r="D2000" t="s">
         <v>2002</v>
@@ -35598,7 +35886,7 @@
         <v>80</v>
       </c>
       <c r="C2001">
-        <v>7080</v>
+        <v>7040</v>
       </c>
       <c r="D2001" t="s">
         <v>2003</v>
@@ -35612,7 +35900,7 @@
         <v>81</v>
       </c>
       <c r="C2002">
-        <v>7110</v>
+        <v>7120</v>
       </c>
       <c r="D2002" t="s">
         <v>2004</v>
@@ -35626,7 +35914,7 @@
         <v>82</v>
       </c>
       <c r="C2003">
-        <v>7140</v>
+        <v>7190</v>
       </c>
       <c r="D2003" t="s">
         <v>2005</v>
@@ -35640,7 +35928,7 @@
         <v>83</v>
       </c>
       <c r="C2004">
-        <v>7170</v>
+        <v>7200</v>
       </c>
       <c r="D2004" t="s">
         <v>2006</v>
@@ -35696,7 +35984,7 @@
         <v>87</v>
       </c>
       <c r="C2008">
-        <v>7150</v>
+        <v>7170</v>
       </c>
       <c r="D2008" t="s">
         <v>2010</v>
@@ -35710,7 +35998,7 @@
         <v>88</v>
       </c>
       <c r="C2009">
-        <v>7000</v>
+        <v>7100</v>
       </c>
       <c r="D2009" t="s">
         <v>2011</v>
@@ -35724,7 +36012,7 @@
         <v>89</v>
       </c>
       <c r="C2010">
-        <v>6810</v>
+        <v>6950</v>
       </c>
       <c r="D2010" t="s">
         <v>2012</v>
@@ -35738,7 +36026,7 @@
         <v>90</v>
       </c>
       <c r="C2011">
-        <v>6680</v>
+        <v>6820</v>
       </c>
       <c r="D2011" t="s">
         <v>2013</v>
@@ -35752,7 +36040,7 @@
         <v>91</v>
       </c>
       <c r="C2012">
-        <v>6520</v>
+        <v>6670</v>
       </c>
       <c r="D2012" t="s">
         <v>2014</v>
@@ -35766,7 +36054,7 @@
         <v>92</v>
       </c>
       <c r="C2013">
-        <v>6370</v>
+        <v>6520</v>
       </c>
       <c r="D2013" t="s">
         <v>2015</v>
@@ -35780,7 +36068,7 @@
         <v>93</v>
       </c>
       <c r="C2014">
-        <v>6150</v>
+        <v>6380</v>
       </c>
       <c r="D2014" t="s">
         <v>2016</v>
@@ -35794,7 +36082,7 @@
         <v>94</v>
       </c>
       <c r="C2015">
-        <v>6000</v>
+        <v>6260</v>
       </c>
       <c r="D2015" t="s">
         <v>2017</v>
@@ -35808,7 +36096,7 @@
         <v>95</v>
       </c>
       <c r="C2016">
-        <v>5880</v>
+        <v>6150</v>
       </c>
       <c r="D2016" t="s">
         <v>2018</v>
@@ -35822,7 +36110,7 @@
         <v>96</v>
       </c>
       <c r="C2017">
-        <v>5770</v>
+        <v>6040</v>
       </c>
       <c r="D2017" t="s">
         <v>2019</v>
@@ -41202,6 +41490,1350 @@
       </c>
       <c r="D2401" t="s">
         <v>2403</v>
+      </c>
+    </row>
+    <row r="2402" spans="1:4">
+      <c r="A2402" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2402">
+        <v>1</v>
+      </c>
+      <c r="C2402">
+        <v>5640</v>
+      </c>
+      <c r="D2402" t="s">
+        <v>2404</v>
+      </c>
+    </row>
+    <row r="2403" spans="1:4">
+      <c r="A2403" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2403">
+        <v>2</v>
+      </c>
+      <c r="C2403">
+        <v>5590</v>
+      </c>
+      <c r="D2403" t="s">
+        <v>2405</v>
+      </c>
+    </row>
+    <row r="2404" spans="1:4">
+      <c r="A2404" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2404">
+        <v>3</v>
+      </c>
+      <c r="C2404">
+        <v>5540</v>
+      </c>
+      <c r="D2404" t="s">
+        <v>2406</v>
+      </c>
+    </row>
+    <row r="2405" spans="1:4">
+      <c r="A2405" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2405">
+        <v>4</v>
+      </c>
+      <c r="C2405">
+        <v>5470</v>
+      </c>
+      <c r="D2405" t="s">
+        <v>2407</v>
+      </c>
+    </row>
+    <row r="2406" spans="1:4">
+      <c r="A2406" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2406">
+        <v>5</v>
+      </c>
+      <c r="C2406">
+        <v>5400</v>
+      </c>
+      <c r="D2406" t="s">
+        <v>2408</v>
+      </c>
+    </row>
+    <row r="2407" spans="1:4">
+      <c r="A2407" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2407">
+        <v>6</v>
+      </c>
+      <c r="C2407">
+        <v>5340</v>
+      </c>
+      <c r="D2407" t="s">
+        <v>2409</v>
+      </c>
+    </row>
+    <row r="2408" spans="1:4">
+      <c r="A2408" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2408">
+        <v>7</v>
+      </c>
+      <c r="C2408">
+        <v>5280</v>
+      </c>
+      <c r="D2408" t="s">
+        <v>2410</v>
+      </c>
+    </row>
+    <row r="2409" spans="1:4">
+      <c r="A2409" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2409">
+        <v>8</v>
+      </c>
+      <c r="C2409">
+        <v>5240</v>
+      </c>
+      <c r="D2409" t="s">
+        <v>2411</v>
+      </c>
+    </row>
+    <row r="2410" spans="1:4">
+      <c r="A2410" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2410">
+        <v>9</v>
+      </c>
+      <c r="C2410">
+        <v>5210</v>
+      </c>
+      <c r="D2410" t="s">
+        <v>2412</v>
+      </c>
+    </row>
+    <row r="2411" spans="1:4">
+      <c r="A2411" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2411">
+        <v>10</v>
+      </c>
+      <c r="C2411">
+        <v>5190</v>
+      </c>
+      <c r="D2411" t="s">
+        <v>2413</v>
+      </c>
+    </row>
+    <row r="2412" spans="1:4">
+      <c r="A2412" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2412">
+        <v>11</v>
+      </c>
+      <c r="C2412">
+        <v>5170</v>
+      </c>
+      <c r="D2412" t="s">
+        <v>2414</v>
+      </c>
+    </row>
+    <row r="2413" spans="1:4">
+      <c r="A2413" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2413">
+        <v>12</v>
+      </c>
+      <c r="C2413">
+        <v>5160</v>
+      </c>
+      <c r="D2413" t="s">
+        <v>2415</v>
+      </c>
+    </row>
+    <row r="2414" spans="1:4">
+      <c r="A2414" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2414">
+        <v>13</v>
+      </c>
+      <c r="C2414">
+        <v>5160</v>
+      </c>
+      <c r="D2414" t="s">
+        <v>2416</v>
+      </c>
+    </row>
+    <row r="2415" spans="1:4">
+      <c r="A2415" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2415">
+        <v>14</v>
+      </c>
+      <c r="C2415">
+        <v>5160</v>
+      </c>
+      <c r="D2415" t="s">
+        <v>2417</v>
+      </c>
+    </row>
+    <row r="2416" spans="1:4">
+      <c r="A2416" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2416">
+        <v>15</v>
+      </c>
+      <c r="C2416">
+        <v>5160</v>
+      </c>
+      <c r="D2416" t="s">
+        <v>2418</v>
+      </c>
+    </row>
+    <row r="2417" spans="1:4">
+      <c r="A2417" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2417">
+        <v>16</v>
+      </c>
+      <c r="C2417">
+        <v>5160</v>
+      </c>
+      <c r="D2417" t="s">
+        <v>2419</v>
+      </c>
+    </row>
+    <row r="2418" spans="1:4">
+      <c r="A2418" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2418">
+        <v>17</v>
+      </c>
+      <c r="C2418">
+        <v>5170</v>
+      </c>
+      <c r="D2418" t="s">
+        <v>2420</v>
+      </c>
+    </row>
+    <row r="2419" spans="1:4">
+      <c r="A2419" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2419">
+        <v>18</v>
+      </c>
+      <c r="C2419">
+        <v>5170</v>
+      </c>
+      <c r="D2419" t="s">
+        <v>2421</v>
+      </c>
+    </row>
+    <row r="2420" spans="1:4">
+      <c r="A2420" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2420">
+        <v>19</v>
+      </c>
+      <c r="C2420">
+        <v>5190</v>
+      </c>
+      <c r="D2420" t="s">
+        <v>2422</v>
+      </c>
+    </row>
+    <row r="2421" spans="1:4">
+      <c r="A2421" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2421">
+        <v>20</v>
+      </c>
+      <c r="C2421">
+        <v>5210</v>
+      </c>
+      <c r="D2421" t="s">
+        <v>2423</v>
+      </c>
+    </row>
+    <row r="2422" spans="1:4">
+      <c r="A2422" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2422">
+        <v>21</v>
+      </c>
+      <c r="C2422">
+        <v>5240</v>
+      </c>
+      <c r="D2422" t="s">
+        <v>2424</v>
+      </c>
+    </row>
+    <row r="2423" spans="1:4">
+      <c r="A2423" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2423">
+        <v>22</v>
+      </c>
+      <c r="C2423">
+        <v>5280</v>
+      </c>
+      <c r="D2423" t="s">
+        <v>2425</v>
+      </c>
+    </row>
+    <row r="2424" spans="1:4">
+      <c r="A2424" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2424">
+        <v>23</v>
+      </c>
+      <c r="C2424">
+        <v>5330</v>
+      </c>
+      <c r="D2424" t="s">
+        <v>2426</v>
+      </c>
+    </row>
+    <row r="2425" spans="1:4">
+      <c r="A2425" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2425">
+        <v>24</v>
+      </c>
+      <c r="C2425">
+        <v>5390</v>
+      </c>
+      <c r="D2425" t="s">
+        <v>2427</v>
+      </c>
+    </row>
+    <row r="2426" spans="1:4">
+      <c r="A2426" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2426">
+        <v>25</v>
+      </c>
+      <c r="C2426">
+        <v>5460</v>
+      </c>
+      <c r="D2426" t="s">
+        <v>2428</v>
+      </c>
+    </row>
+    <row r="2427" spans="1:4">
+      <c r="A2427" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2427">
+        <v>26</v>
+      </c>
+      <c r="C2427">
+        <v>5530</v>
+      </c>
+      <c r="D2427" t="s">
+        <v>2429</v>
+      </c>
+    </row>
+    <row r="2428" spans="1:4">
+      <c r="A2428" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2428">
+        <v>27</v>
+      </c>
+      <c r="C2428">
+        <v>5620</v>
+      </c>
+      <c r="D2428" t="s">
+        <v>2430</v>
+      </c>
+    </row>
+    <row r="2429" spans="1:4">
+      <c r="A2429" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2429">
+        <v>28</v>
+      </c>
+      <c r="C2429">
+        <v>5710</v>
+      </c>
+      <c r="D2429" t="s">
+        <v>2431</v>
+      </c>
+    </row>
+    <row r="2430" spans="1:4">
+      <c r="A2430" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2430">
+        <v>29</v>
+      </c>
+      <c r="C2430">
+        <v>5800</v>
+      </c>
+      <c r="D2430" t="s">
+        <v>2432</v>
+      </c>
+    </row>
+    <row r="2431" spans="1:4">
+      <c r="A2431" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2431">
+        <v>30</v>
+      </c>
+      <c r="C2431">
+        <v>5890</v>
+      </c>
+      <c r="D2431" t="s">
+        <v>2433</v>
+      </c>
+    </row>
+    <row r="2432" spans="1:4">
+      <c r="A2432" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2432">
+        <v>31</v>
+      </c>
+      <c r="C2432">
+        <v>5970</v>
+      </c>
+      <c r="D2432" t="s">
+        <v>2434</v>
+      </c>
+    </row>
+    <row r="2433" spans="1:4">
+      <c r="A2433" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2433">
+        <v>32</v>
+      </c>
+      <c r="C2433">
+        <v>6040</v>
+      </c>
+      <c r="D2433" t="s">
+        <v>2435</v>
+      </c>
+    </row>
+    <row r="2434" spans="1:4">
+      <c r="A2434" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2434">
+        <v>33</v>
+      </c>
+      <c r="C2434">
+        <v>6080</v>
+      </c>
+      <c r="D2434" t="s">
+        <v>2436</v>
+      </c>
+    </row>
+    <row r="2435" spans="1:4">
+      <c r="A2435" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2435">
+        <v>34</v>
+      </c>
+      <c r="C2435">
+        <v>6090</v>
+      </c>
+      <c r="D2435" t="s">
+        <v>2437</v>
+      </c>
+    </row>
+    <row r="2436" spans="1:4">
+      <c r="A2436" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2436">
+        <v>35</v>
+      </c>
+      <c r="C2436">
+        <v>6070</v>
+      </c>
+      <c r="D2436" t="s">
+        <v>2438</v>
+      </c>
+    </row>
+    <row r="2437" spans="1:4">
+      <c r="A2437" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2437">
+        <v>36</v>
+      </c>
+      <c r="C2437">
+        <v>6010</v>
+      </c>
+      <c r="D2437" t="s">
+        <v>2439</v>
+      </c>
+    </row>
+    <row r="2438" spans="1:4">
+      <c r="A2438" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2438">
+        <v>37</v>
+      </c>
+      <c r="C2438">
+        <v>5930</v>
+      </c>
+      <c r="D2438" t="s">
+        <v>2440</v>
+      </c>
+    </row>
+    <row r="2439" spans="1:4">
+      <c r="A2439" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2439">
+        <v>38</v>
+      </c>
+      <c r="C2439">
+        <v>5830</v>
+      </c>
+      <c r="D2439" t="s">
+        <v>2441</v>
+      </c>
+    </row>
+    <row r="2440" spans="1:4">
+      <c r="A2440" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2440">
+        <v>39</v>
+      </c>
+      <c r="C2440">
+        <v>5700</v>
+      </c>
+      <c r="D2440" t="s">
+        <v>2442</v>
+      </c>
+    </row>
+    <row r="2441" spans="1:4">
+      <c r="A2441" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2441">
+        <v>40</v>
+      </c>
+      <c r="C2441">
+        <v>5580</v>
+      </c>
+      <c r="D2441" t="s">
+        <v>2443</v>
+      </c>
+    </row>
+    <row r="2442" spans="1:4">
+      <c r="A2442" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2442">
+        <v>41</v>
+      </c>
+      <c r="C2442">
+        <v>5460</v>
+      </c>
+      <c r="D2442" t="s">
+        <v>2444</v>
+      </c>
+    </row>
+    <row r="2443" spans="1:4">
+      <c r="A2443" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2443">
+        <v>42</v>
+      </c>
+      <c r="C2443">
+        <v>5350</v>
+      </c>
+      <c r="D2443" t="s">
+        <v>2445</v>
+      </c>
+    </row>
+    <row r="2444" spans="1:4">
+      <c r="A2444" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2444">
+        <v>43</v>
+      </c>
+      <c r="C2444">
+        <v>5260</v>
+      </c>
+      <c r="D2444" t="s">
+        <v>2446</v>
+      </c>
+    </row>
+    <row r="2445" spans="1:4">
+      <c r="A2445" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2445">
+        <v>44</v>
+      </c>
+      <c r="C2445">
+        <v>5210</v>
+      </c>
+      <c r="D2445" t="s">
+        <v>2447</v>
+      </c>
+    </row>
+    <row r="2446" spans="1:4">
+      <c r="A2446" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2446">
+        <v>45</v>
+      </c>
+      <c r="C2446">
+        <v>5170</v>
+      </c>
+      <c r="D2446" t="s">
+        <v>2448</v>
+      </c>
+    </row>
+    <row r="2447" spans="1:4">
+      <c r="A2447" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2447">
+        <v>46</v>
+      </c>
+      <c r="C2447">
+        <v>5170</v>
+      </c>
+      <c r="D2447" t="s">
+        <v>2449</v>
+      </c>
+    </row>
+    <row r="2448" spans="1:4">
+      <c r="A2448" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2448">
+        <v>47</v>
+      </c>
+      <c r="C2448">
+        <v>5180</v>
+      </c>
+      <c r="D2448" t="s">
+        <v>2450</v>
+      </c>
+    </row>
+    <row r="2449" spans="1:4">
+      <c r="A2449" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2449">
+        <v>48</v>
+      </c>
+      <c r="C2449">
+        <v>5200</v>
+      </c>
+      <c r="D2449" t="s">
+        <v>2451</v>
+      </c>
+    </row>
+    <row r="2450" spans="1:4">
+      <c r="A2450" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2450">
+        <v>49</v>
+      </c>
+      <c r="C2450">
+        <v>5230</v>
+      </c>
+      <c r="D2450" t="s">
+        <v>2452</v>
+      </c>
+    </row>
+    <row r="2451" spans="1:4">
+      <c r="A2451" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2451">
+        <v>50</v>
+      </c>
+      <c r="C2451">
+        <v>5250</v>
+      </c>
+      <c r="D2451" t="s">
+        <v>2453</v>
+      </c>
+    </row>
+    <row r="2452" spans="1:4">
+      <c r="A2452" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2452">
+        <v>51</v>
+      </c>
+      <c r="C2452">
+        <v>5270</v>
+      </c>
+      <c r="D2452" t="s">
+        <v>2454</v>
+      </c>
+    </row>
+    <row r="2453" spans="1:4">
+      <c r="A2453" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2453">
+        <v>52</v>
+      </c>
+      <c r="C2453">
+        <v>5280</v>
+      </c>
+      <c r="D2453" t="s">
+        <v>2455</v>
+      </c>
+    </row>
+    <row r="2454" spans="1:4">
+      <c r="A2454" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2454">
+        <v>53</v>
+      </c>
+      <c r="C2454">
+        <v>5300</v>
+      </c>
+      <c r="D2454" t="s">
+        <v>2456</v>
+      </c>
+    </row>
+    <row r="2455" spans="1:4">
+      <c r="A2455" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2455">
+        <v>54</v>
+      </c>
+      <c r="C2455">
+        <v>5310</v>
+      </c>
+      <c r="D2455" t="s">
+        <v>2457</v>
+      </c>
+    </row>
+    <row r="2456" spans="1:4">
+      <c r="A2456" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2456">
+        <v>55</v>
+      </c>
+      <c r="C2456">
+        <v>5330</v>
+      </c>
+      <c r="D2456" t="s">
+        <v>2458</v>
+      </c>
+    </row>
+    <row r="2457" spans="1:4">
+      <c r="A2457" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2457">
+        <v>56</v>
+      </c>
+      <c r="C2457">
+        <v>5350</v>
+      </c>
+      <c r="D2457" t="s">
+        <v>2459</v>
+      </c>
+    </row>
+    <row r="2458" spans="1:4">
+      <c r="A2458" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2458">
+        <v>57</v>
+      </c>
+      <c r="C2458">
+        <v>5390</v>
+      </c>
+      <c r="D2458" t="s">
+        <v>2460</v>
+      </c>
+    </row>
+    <row r="2459" spans="1:4">
+      <c r="A2459" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2459">
+        <v>58</v>
+      </c>
+      <c r="C2459">
+        <v>5440</v>
+      </c>
+      <c r="D2459" t="s">
+        <v>2461</v>
+      </c>
+    </row>
+    <row r="2460" spans="1:4">
+      <c r="A2460" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2460">
+        <v>59</v>
+      </c>
+      <c r="C2460">
+        <v>5500</v>
+      </c>
+      <c r="D2460" t="s">
+        <v>2462</v>
+      </c>
+    </row>
+    <row r="2461" spans="1:4">
+      <c r="A2461" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2461">
+        <v>60</v>
+      </c>
+      <c r="C2461">
+        <v>5560</v>
+      </c>
+      <c r="D2461" t="s">
+        <v>2463</v>
+      </c>
+    </row>
+    <row r="2462" spans="1:4">
+      <c r="A2462" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2462">
+        <v>61</v>
+      </c>
+      <c r="C2462">
+        <v>5620</v>
+      </c>
+      <c r="D2462" t="s">
+        <v>2464</v>
+      </c>
+    </row>
+    <row r="2463" spans="1:4">
+      <c r="A2463" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2463">
+        <v>62</v>
+      </c>
+      <c r="C2463">
+        <v>5680</v>
+      </c>
+      <c r="D2463" t="s">
+        <v>2465</v>
+      </c>
+    </row>
+    <row r="2464" spans="1:4">
+      <c r="A2464" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2464">
+        <v>63</v>
+      </c>
+      <c r="C2464">
+        <v>5740</v>
+      </c>
+      <c r="D2464" t="s">
+        <v>2466</v>
+      </c>
+    </row>
+    <row r="2465" spans="1:4">
+      <c r="A2465" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2465">
+        <v>64</v>
+      </c>
+      <c r="C2465">
+        <v>5810</v>
+      </c>
+      <c r="D2465" t="s">
+        <v>2467</v>
+      </c>
+    </row>
+    <row r="2466" spans="1:4">
+      <c r="A2466" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2466">
+        <v>65</v>
+      </c>
+      <c r="C2466">
+        <v>5870</v>
+      </c>
+      <c r="D2466" t="s">
+        <v>2468</v>
+      </c>
+    </row>
+    <row r="2467" spans="1:4">
+      <c r="A2467" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2467">
+        <v>66</v>
+      </c>
+      <c r="C2467">
+        <v>5950</v>
+      </c>
+      <c r="D2467" t="s">
+        <v>2469</v>
+      </c>
+    </row>
+    <row r="2468" spans="1:4">
+      <c r="A2468" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2468">
+        <v>67</v>
+      </c>
+      <c r="C2468">
+        <v>6040</v>
+      </c>
+      <c r="D2468" t="s">
+        <v>2470</v>
+      </c>
+    </row>
+    <row r="2469" spans="1:4">
+      <c r="A2469" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2469">
+        <v>68</v>
+      </c>
+      <c r="C2469">
+        <v>6130</v>
+      </c>
+      <c r="D2469" t="s">
+        <v>2471</v>
+      </c>
+    </row>
+    <row r="2470" spans="1:4">
+      <c r="A2470" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2470">
+        <v>69</v>
+      </c>
+      <c r="C2470">
+        <v>6230</v>
+      </c>
+      <c r="D2470" t="s">
+        <v>2472</v>
+      </c>
+    </row>
+    <row r="2471" spans="1:4">
+      <c r="A2471" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2471">
+        <v>70</v>
+      </c>
+      <c r="C2471">
+        <v>6330</v>
+      </c>
+      <c r="D2471" t="s">
+        <v>2473</v>
+      </c>
+    </row>
+    <row r="2472" spans="1:4">
+      <c r="A2472" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2472">
+        <v>71</v>
+      </c>
+      <c r="C2472">
+        <v>6420</v>
+      </c>
+      <c r="D2472" t="s">
+        <v>2474</v>
+      </c>
+    </row>
+    <row r="2473" spans="1:4">
+      <c r="A2473" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2473">
+        <v>72</v>
+      </c>
+      <c r="C2473">
+        <v>6500</v>
+      </c>
+      <c r="D2473" t="s">
+        <v>2475</v>
+      </c>
+    </row>
+    <row r="2474" spans="1:4">
+      <c r="A2474" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2474">
+        <v>73</v>
+      </c>
+      <c r="C2474">
+        <v>6570</v>
+      </c>
+      <c r="D2474" t="s">
+        <v>2476</v>
+      </c>
+    </row>
+    <row r="2475" spans="1:4">
+      <c r="A2475" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2475">
+        <v>74</v>
+      </c>
+      <c r="C2475">
+        <v>6640</v>
+      </c>
+      <c r="D2475" t="s">
+        <v>2477</v>
+      </c>
+    </row>
+    <row r="2476" spans="1:4">
+      <c r="A2476" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2476">
+        <v>75</v>
+      </c>
+      <c r="C2476">
+        <v>6720</v>
+      </c>
+      <c r="D2476" t="s">
+        <v>2478</v>
+      </c>
+    </row>
+    <row r="2477" spans="1:4">
+      <c r="A2477" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2477">
+        <v>76</v>
+      </c>
+      <c r="C2477">
+        <v>6820</v>
+      </c>
+      <c r="D2477" t="s">
+        <v>2479</v>
+      </c>
+    </row>
+    <row r="2478" spans="1:4">
+      <c r="A2478" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2478">
+        <v>77</v>
+      </c>
+      <c r="C2478">
+        <v>6930</v>
+      </c>
+      <c r="D2478" t="s">
+        <v>2480</v>
+      </c>
+    </row>
+    <row r="2479" spans="1:4">
+      <c r="A2479" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2479">
+        <v>78</v>
+      </c>
+      <c r="C2479">
+        <v>7030</v>
+      </c>
+      <c r="D2479" t="s">
+        <v>2481</v>
+      </c>
+    </row>
+    <row r="2480" spans="1:4">
+      <c r="A2480" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2480">
+        <v>79</v>
+      </c>
+      <c r="C2480">
+        <v>7120</v>
+      </c>
+      <c r="D2480" t="s">
+        <v>2482</v>
+      </c>
+    </row>
+    <row r="2481" spans="1:4">
+      <c r="A2481" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2481">
+        <v>80</v>
+      </c>
+      <c r="C2481">
+        <v>7170</v>
+      </c>
+      <c r="D2481" t="s">
+        <v>2483</v>
+      </c>
+    </row>
+    <row r="2482" spans="1:4">
+      <c r="A2482" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2482">
+        <v>81</v>
+      </c>
+      <c r="C2482">
+        <v>7210</v>
+      </c>
+      <c r="D2482" t="s">
+        <v>2484</v>
+      </c>
+    </row>
+    <row r="2483" spans="1:4">
+      <c r="A2483" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2483">
+        <v>82</v>
+      </c>
+      <c r="C2483">
+        <v>7240</v>
+      </c>
+      <c r="D2483" t="s">
+        <v>2485</v>
+      </c>
+    </row>
+    <row r="2484" spans="1:4">
+      <c r="A2484" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2484">
+        <v>83</v>
+      </c>
+      <c r="C2484">
+        <v>7260</v>
+      </c>
+      <c r="D2484" t="s">
+        <v>2486</v>
+      </c>
+    </row>
+    <row r="2485" spans="1:4">
+      <c r="A2485" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2485">
+        <v>84</v>
+      </c>
+      <c r="C2485">
+        <v>7300</v>
+      </c>
+      <c r="D2485" t="s">
+        <v>2487</v>
+      </c>
+    </row>
+    <row r="2486" spans="1:4">
+      <c r="A2486" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2486">
+        <v>85</v>
+      </c>
+      <c r="C2486">
+        <v>7290</v>
+      </c>
+      <c r="D2486" t="s">
+        <v>2488</v>
+      </c>
+    </row>
+    <row r="2487" spans="1:4">
+      <c r="A2487" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2487">
+        <v>86</v>
+      </c>
+      <c r="C2487">
+        <v>7240</v>
+      </c>
+      <c r="D2487" t="s">
+        <v>2489</v>
+      </c>
+    </row>
+    <row r="2488" spans="1:4">
+      <c r="A2488" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2488">
+        <v>87</v>
+      </c>
+      <c r="C2488">
+        <v>7180</v>
+      </c>
+      <c r="D2488" t="s">
+        <v>2490</v>
+      </c>
+    </row>
+    <row r="2489" spans="1:4">
+      <c r="A2489" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2489">
+        <v>88</v>
+      </c>
+      <c r="C2489">
+        <v>7050</v>
+      </c>
+      <c r="D2489" t="s">
+        <v>2491</v>
+      </c>
+    </row>
+    <row r="2490" spans="1:4">
+      <c r="A2490" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2490">
+        <v>89</v>
+      </c>
+      <c r="C2490">
+        <v>6850</v>
+      </c>
+      <c r="D2490" t="s">
+        <v>2492</v>
+      </c>
+    </row>
+    <row r="2491" spans="1:4">
+      <c r="A2491" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2491">
+        <v>90</v>
+      </c>
+      <c r="C2491">
+        <v>6720</v>
+      </c>
+      <c r="D2491" t="s">
+        <v>2493</v>
+      </c>
+    </row>
+    <row r="2492" spans="1:4">
+      <c r="A2492" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2492">
+        <v>91</v>
+      </c>
+      <c r="C2492">
+        <v>6580</v>
+      </c>
+      <c r="D2492" t="s">
+        <v>2494</v>
+      </c>
+    </row>
+    <row r="2493" spans="1:4">
+      <c r="A2493" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2493">
+        <v>92</v>
+      </c>
+      <c r="C2493">
+        <v>6420</v>
+      </c>
+      <c r="D2493" t="s">
+        <v>2495</v>
+      </c>
+    </row>
+    <row r="2494" spans="1:4">
+      <c r="A2494" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2494">
+        <v>93</v>
+      </c>
+      <c r="C2494">
+        <v>6190</v>
+      </c>
+      <c r="D2494" t="s">
+        <v>2496</v>
+      </c>
+    </row>
+    <row r="2495" spans="1:4">
+      <c r="A2495" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2495">
+        <v>94</v>
+      </c>
+      <c r="C2495">
+        <v>6020</v>
+      </c>
+      <c r="D2495" t="s">
+        <v>2497</v>
+      </c>
+    </row>
+    <row r="2496" spans="1:4">
+      <c r="A2496" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2496">
+        <v>95</v>
+      </c>
+      <c r="C2496">
+        <v>5930</v>
+      </c>
+      <c r="D2496" t="s">
+        <v>2498</v>
+      </c>
+    </row>
+    <row r="2497" spans="1:4">
+      <c r="A2497" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B2497">
+        <v>96</v>
+      </c>
+      <c r="C2497">
+        <v>5820</v>
+      </c>
+      <c r="D2497" t="s">
+        <v>2499</v>
       </c>
     </row>
   </sheetData>

--- a/Market Fundamentals/Transelectrica_data/Cons_Prod_final/Weekly_Consumption_2026.xlsx
+++ b/Market Fundamentals/Transelectrica_data/Cons_Prod_final/Weekly_Consumption_2026.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2500" uniqueCount="2500">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2692" uniqueCount="2692">
   <si>
     <t>Date</t>
   </si>
@@ -7514,6 +7514,582 @@
   </si>
   <si>
     <t>26.08.202696.0</t>
+  </si>
+  <si>
+    <t>27.08.20261.0</t>
+  </si>
+  <si>
+    <t>27.08.20262.0</t>
+  </si>
+  <si>
+    <t>27.08.20263.0</t>
+  </si>
+  <si>
+    <t>27.08.20264.0</t>
+  </si>
+  <si>
+    <t>27.08.20265.0</t>
+  </si>
+  <si>
+    <t>27.08.20266.0</t>
+  </si>
+  <si>
+    <t>27.08.20267.0</t>
+  </si>
+  <si>
+    <t>27.08.20268.0</t>
+  </si>
+  <si>
+    <t>27.08.20269.0</t>
+  </si>
+  <si>
+    <t>27.08.202610.0</t>
+  </si>
+  <si>
+    <t>27.08.202611.0</t>
+  </si>
+  <si>
+    <t>27.08.202612.0</t>
+  </si>
+  <si>
+    <t>27.08.202613.0</t>
+  </si>
+  <si>
+    <t>27.08.202614.0</t>
+  </si>
+  <si>
+    <t>27.08.202615.0</t>
+  </si>
+  <si>
+    <t>27.08.202616.0</t>
+  </si>
+  <si>
+    <t>27.08.202617.0</t>
+  </si>
+  <si>
+    <t>27.08.202618.0</t>
+  </si>
+  <si>
+    <t>27.08.202619.0</t>
+  </si>
+  <si>
+    <t>27.08.202620.0</t>
+  </si>
+  <si>
+    <t>27.08.202621.0</t>
+  </si>
+  <si>
+    <t>27.08.202622.0</t>
+  </si>
+  <si>
+    <t>27.08.202623.0</t>
+  </si>
+  <si>
+    <t>27.08.202624.0</t>
+  </si>
+  <si>
+    <t>27.08.202625.0</t>
+  </si>
+  <si>
+    <t>27.08.202626.0</t>
+  </si>
+  <si>
+    <t>27.08.202627.0</t>
+  </si>
+  <si>
+    <t>27.08.202628.0</t>
+  </si>
+  <si>
+    <t>27.08.202629.0</t>
+  </si>
+  <si>
+    <t>27.08.202630.0</t>
+  </si>
+  <si>
+    <t>27.08.202631.0</t>
+  </si>
+  <si>
+    <t>27.08.202632.0</t>
+  </si>
+  <si>
+    <t>27.08.202633.0</t>
+  </si>
+  <si>
+    <t>27.08.202634.0</t>
+  </si>
+  <si>
+    <t>27.08.202635.0</t>
+  </si>
+  <si>
+    <t>27.08.202636.0</t>
+  </si>
+  <si>
+    <t>27.08.202637.0</t>
+  </si>
+  <si>
+    <t>27.08.202638.0</t>
+  </si>
+  <si>
+    <t>27.08.202639.0</t>
+  </si>
+  <si>
+    <t>27.08.202640.0</t>
+  </si>
+  <si>
+    <t>27.08.202641.0</t>
+  </si>
+  <si>
+    <t>27.08.202642.0</t>
+  </si>
+  <si>
+    <t>27.08.202643.0</t>
+  </si>
+  <si>
+    <t>27.08.202644.0</t>
+  </si>
+  <si>
+    <t>27.08.202645.0</t>
+  </si>
+  <si>
+    <t>27.08.202646.0</t>
+  </si>
+  <si>
+    <t>27.08.202647.0</t>
+  </si>
+  <si>
+    <t>27.08.202648.0</t>
+  </si>
+  <si>
+    <t>27.08.202649.0</t>
+  </si>
+  <si>
+    <t>27.08.202650.0</t>
+  </si>
+  <si>
+    <t>27.08.202651.0</t>
+  </si>
+  <si>
+    <t>27.08.202652.0</t>
+  </si>
+  <si>
+    <t>27.08.202653.0</t>
+  </si>
+  <si>
+    <t>27.08.202654.0</t>
+  </si>
+  <si>
+    <t>27.08.202655.0</t>
+  </si>
+  <si>
+    <t>27.08.202656.0</t>
+  </si>
+  <si>
+    <t>27.08.202657.0</t>
+  </si>
+  <si>
+    <t>27.08.202658.0</t>
+  </si>
+  <si>
+    <t>27.08.202659.0</t>
+  </si>
+  <si>
+    <t>27.08.202660.0</t>
+  </si>
+  <si>
+    <t>27.08.202661.0</t>
+  </si>
+  <si>
+    <t>27.08.202662.0</t>
+  </si>
+  <si>
+    <t>27.08.202663.0</t>
+  </si>
+  <si>
+    <t>27.08.202664.0</t>
+  </si>
+  <si>
+    <t>27.08.202665.0</t>
+  </si>
+  <si>
+    <t>27.08.202666.0</t>
+  </si>
+  <si>
+    <t>27.08.202667.0</t>
+  </si>
+  <si>
+    <t>27.08.202668.0</t>
+  </si>
+  <si>
+    <t>27.08.202669.0</t>
+  </si>
+  <si>
+    <t>27.08.202670.0</t>
+  </si>
+  <si>
+    <t>27.08.202671.0</t>
+  </si>
+  <si>
+    <t>27.08.202672.0</t>
+  </si>
+  <si>
+    <t>27.08.202673.0</t>
+  </si>
+  <si>
+    <t>27.08.202674.0</t>
+  </si>
+  <si>
+    <t>27.08.202675.0</t>
+  </si>
+  <si>
+    <t>27.08.202676.0</t>
+  </si>
+  <si>
+    <t>27.08.202677.0</t>
+  </si>
+  <si>
+    <t>27.08.202678.0</t>
+  </si>
+  <si>
+    <t>27.08.202679.0</t>
+  </si>
+  <si>
+    <t>27.08.202680.0</t>
+  </si>
+  <si>
+    <t>27.08.202681.0</t>
+  </si>
+  <si>
+    <t>27.08.202682.0</t>
+  </si>
+  <si>
+    <t>27.08.202683.0</t>
+  </si>
+  <si>
+    <t>27.08.202684.0</t>
+  </si>
+  <si>
+    <t>27.08.202685.0</t>
+  </si>
+  <si>
+    <t>27.08.202686.0</t>
+  </si>
+  <si>
+    <t>27.08.202687.0</t>
+  </si>
+  <si>
+    <t>27.08.202688.0</t>
+  </si>
+  <si>
+    <t>27.08.202689.0</t>
+  </si>
+  <si>
+    <t>27.08.202690.0</t>
+  </si>
+  <si>
+    <t>27.08.202691.0</t>
+  </si>
+  <si>
+    <t>27.08.202692.0</t>
+  </si>
+  <si>
+    <t>27.08.202693.0</t>
+  </si>
+  <si>
+    <t>27.08.202694.0</t>
+  </si>
+  <si>
+    <t>27.08.202695.0</t>
+  </si>
+  <si>
+    <t>27.08.202696.0</t>
+  </si>
+  <si>
+    <t>28.08.20261.0</t>
+  </si>
+  <si>
+    <t>28.08.20262.0</t>
+  </si>
+  <si>
+    <t>28.08.20263.0</t>
+  </si>
+  <si>
+    <t>28.08.20264.0</t>
+  </si>
+  <si>
+    <t>28.08.20265.0</t>
+  </si>
+  <si>
+    <t>28.08.20266.0</t>
+  </si>
+  <si>
+    <t>28.08.20267.0</t>
+  </si>
+  <si>
+    <t>28.08.20268.0</t>
+  </si>
+  <si>
+    <t>28.08.20269.0</t>
+  </si>
+  <si>
+    <t>28.08.202610.0</t>
+  </si>
+  <si>
+    <t>28.08.202611.0</t>
+  </si>
+  <si>
+    <t>28.08.202612.0</t>
+  </si>
+  <si>
+    <t>28.08.202613.0</t>
+  </si>
+  <si>
+    <t>28.08.202614.0</t>
+  </si>
+  <si>
+    <t>28.08.202615.0</t>
+  </si>
+  <si>
+    <t>28.08.202616.0</t>
+  </si>
+  <si>
+    <t>28.08.202617.0</t>
+  </si>
+  <si>
+    <t>28.08.202618.0</t>
+  </si>
+  <si>
+    <t>28.08.202619.0</t>
+  </si>
+  <si>
+    <t>28.08.202620.0</t>
+  </si>
+  <si>
+    <t>28.08.202621.0</t>
+  </si>
+  <si>
+    <t>28.08.202622.0</t>
+  </si>
+  <si>
+    <t>28.08.202623.0</t>
+  </si>
+  <si>
+    <t>28.08.202624.0</t>
+  </si>
+  <si>
+    <t>28.08.202625.0</t>
+  </si>
+  <si>
+    <t>28.08.202626.0</t>
+  </si>
+  <si>
+    <t>28.08.202627.0</t>
+  </si>
+  <si>
+    <t>28.08.202628.0</t>
+  </si>
+  <si>
+    <t>28.08.202629.0</t>
+  </si>
+  <si>
+    <t>28.08.202630.0</t>
+  </si>
+  <si>
+    <t>28.08.202631.0</t>
+  </si>
+  <si>
+    <t>28.08.202632.0</t>
+  </si>
+  <si>
+    <t>28.08.202633.0</t>
+  </si>
+  <si>
+    <t>28.08.202634.0</t>
+  </si>
+  <si>
+    <t>28.08.202635.0</t>
+  </si>
+  <si>
+    <t>28.08.202636.0</t>
+  </si>
+  <si>
+    <t>28.08.202637.0</t>
+  </si>
+  <si>
+    <t>28.08.202638.0</t>
+  </si>
+  <si>
+    <t>28.08.202639.0</t>
+  </si>
+  <si>
+    <t>28.08.202640.0</t>
+  </si>
+  <si>
+    <t>28.08.202641.0</t>
+  </si>
+  <si>
+    <t>28.08.202642.0</t>
+  </si>
+  <si>
+    <t>28.08.202643.0</t>
+  </si>
+  <si>
+    <t>28.08.202644.0</t>
+  </si>
+  <si>
+    <t>28.08.202645.0</t>
+  </si>
+  <si>
+    <t>28.08.202646.0</t>
+  </si>
+  <si>
+    <t>28.08.202647.0</t>
+  </si>
+  <si>
+    <t>28.08.202648.0</t>
+  </si>
+  <si>
+    <t>28.08.202649.0</t>
+  </si>
+  <si>
+    <t>28.08.202650.0</t>
+  </si>
+  <si>
+    <t>28.08.202651.0</t>
+  </si>
+  <si>
+    <t>28.08.202652.0</t>
+  </si>
+  <si>
+    <t>28.08.202653.0</t>
+  </si>
+  <si>
+    <t>28.08.202654.0</t>
+  </si>
+  <si>
+    <t>28.08.202655.0</t>
+  </si>
+  <si>
+    <t>28.08.202656.0</t>
+  </si>
+  <si>
+    <t>28.08.202657.0</t>
+  </si>
+  <si>
+    <t>28.08.202658.0</t>
+  </si>
+  <si>
+    <t>28.08.202659.0</t>
+  </si>
+  <si>
+    <t>28.08.202660.0</t>
+  </si>
+  <si>
+    <t>28.08.202661.0</t>
+  </si>
+  <si>
+    <t>28.08.202662.0</t>
+  </si>
+  <si>
+    <t>28.08.202663.0</t>
+  </si>
+  <si>
+    <t>28.08.202664.0</t>
+  </si>
+  <si>
+    <t>28.08.202665.0</t>
+  </si>
+  <si>
+    <t>28.08.202666.0</t>
+  </si>
+  <si>
+    <t>28.08.202667.0</t>
+  </si>
+  <si>
+    <t>28.08.202668.0</t>
+  </si>
+  <si>
+    <t>28.08.202669.0</t>
+  </si>
+  <si>
+    <t>28.08.202670.0</t>
+  </si>
+  <si>
+    <t>28.08.202671.0</t>
+  </si>
+  <si>
+    <t>28.08.202672.0</t>
+  </si>
+  <si>
+    <t>28.08.202673.0</t>
+  </si>
+  <si>
+    <t>28.08.202674.0</t>
+  </si>
+  <si>
+    <t>28.08.202675.0</t>
+  </si>
+  <si>
+    <t>28.08.202676.0</t>
+  </si>
+  <si>
+    <t>28.08.202677.0</t>
+  </si>
+  <si>
+    <t>28.08.202678.0</t>
+  </si>
+  <si>
+    <t>28.08.202679.0</t>
+  </si>
+  <si>
+    <t>28.08.202680.0</t>
+  </si>
+  <si>
+    <t>28.08.202681.0</t>
+  </si>
+  <si>
+    <t>28.08.202682.0</t>
+  </si>
+  <si>
+    <t>28.08.202683.0</t>
+  </si>
+  <si>
+    <t>28.08.202684.0</t>
+  </si>
+  <si>
+    <t>28.08.202685.0</t>
+  </si>
+  <si>
+    <t>28.08.202686.0</t>
+  </si>
+  <si>
+    <t>28.08.202687.0</t>
+  </si>
+  <si>
+    <t>28.08.202688.0</t>
+  </si>
+  <si>
+    <t>28.08.202689.0</t>
+  </si>
+  <si>
+    <t>28.08.202690.0</t>
+  </si>
+  <si>
+    <t>28.08.202691.0</t>
+  </si>
+  <si>
+    <t>28.08.202692.0</t>
+  </si>
+  <si>
+    <t>28.08.202693.0</t>
+  </si>
+  <si>
+    <t>28.08.202694.0</t>
+  </si>
+  <si>
+    <t>28.08.202695.0</t>
+  </si>
+  <si>
+    <t>28.08.202696.0</t>
   </si>
 </sst>
 </file>
@@ -7875,7 +8451,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D2497"/>
+  <dimension ref="A1:D2689"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -34808,7 +35384,7 @@
         <v>3</v>
       </c>
       <c r="C1924">
-        <v>5540</v>
+        <v>5520</v>
       </c>
       <c r="D1924" t="s">
         <v>1926</v>
@@ -34822,7 +35398,7 @@
         <v>4</v>
       </c>
       <c r="C1925">
-        <v>5470</v>
+        <v>5450</v>
       </c>
       <c r="D1925" t="s">
         <v>1927</v>
@@ -34836,7 +35412,7 @@
         <v>5</v>
       </c>
       <c r="C1926">
-        <v>5400</v>
+        <v>5380</v>
       </c>
       <c r="D1926" t="s">
         <v>1928</v>
@@ -34850,7 +35426,7 @@
         <v>6</v>
       </c>
       <c r="C1927">
-        <v>5340</v>
+        <v>5310</v>
       </c>
       <c r="D1927" t="s">
         <v>1929</v>
@@ -34864,7 +35440,7 @@
         <v>7</v>
       </c>
       <c r="C1928">
-        <v>5280</v>
+        <v>5240</v>
       </c>
       <c r="D1928" t="s">
         <v>1930</v>
@@ -34878,7 +35454,7 @@
         <v>8</v>
       </c>
       <c r="C1929">
-        <v>5240</v>
+        <v>5190</v>
       </c>
       <c r="D1929" t="s">
         <v>1931</v>
@@ -34892,7 +35468,7 @@
         <v>9</v>
       </c>
       <c r="C1930">
-        <v>5200</v>
+        <v>5130</v>
       </c>
       <c r="D1930" t="s">
         <v>1932</v>
@@ -34906,7 +35482,7 @@
         <v>10</v>
       </c>
       <c r="C1931">
-        <v>5170</v>
+        <v>5100</v>
       </c>
       <c r="D1931" t="s">
         <v>1933</v>
@@ -34920,7 +35496,7 @@
         <v>11</v>
       </c>
       <c r="C1932">
-        <v>5140</v>
+        <v>5080</v>
       </c>
       <c r="D1932" t="s">
         <v>1934</v>
@@ -34934,7 +35510,7 @@
         <v>12</v>
       </c>
       <c r="C1933">
-        <v>5130</v>
+        <v>5090</v>
       </c>
       <c r="D1933" t="s">
         <v>1935</v>
@@ -34962,7 +35538,7 @@
         <v>14</v>
       </c>
       <c r="C1935">
-        <v>5110</v>
+        <v>5130</v>
       </c>
       <c r="D1935" t="s">
         <v>1937</v>
@@ -34976,7 +35552,7 @@
         <v>15</v>
       </c>
       <c r="C1936">
-        <v>5100</v>
+        <v>5160</v>
       </c>
       <c r="D1936" t="s">
         <v>1938</v>
@@ -34990,7 +35566,7 @@
         <v>16</v>
       </c>
       <c r="C1937">
-        <v>5100</v>
+        <v>5190</v>
       </c>
       <c r="D1937" t="s">
         <v>1939</v>
@@ -35004,7 +35580,7 @@
         <v>17</v>
       </c>
       <c r="C1938">
-        <v>5110</v>
+        <v>5210</v>
       </c>
       <c r="D1938" t="s">
         <v>1940</v>
@@ -35018,7 +35594,7 @@
         <v>18</v>
       </c>
       <c r="C1939">
-        <v>5120</v>
+        <v>5220</v>
       </c>
       <c r="D1939" t="s">
         <v>1941</v>
@@ -35032,7 +35608,7 @@
         <v>19</v>
       </c>
       <c r="C1940">
-        <v>5130</v>
+        <v>5220</v>
       </c>
       <c r="D1940" t="s">
         <v>1942</v>
@@ -35046,7 +35622,7 @@
         <v>20</v>
       </c>
       <c r="C1941">
-        <v>5150</v>
+        <v>5230</v>
       </c>
       <c r="D1941" t="s">
         <v>1943</v>
@@ -35060,7 +35636,7 @@
         <v>21</v>
       </c>
       <c r="C1942">
-        <v>5180</v>
+        <v>5280</v>
       </c>
       <c r="D1942" t="s">
         <v>1944</v>
@@ -35074,7 +35650,7 @@
         <v>22</v>
       </c>
       <c r="C1943">
-        <v>5210</v>
+        <v>5320</v>
       </c>
       <c r="D1943" t="s">
         <v>1945</v>
@@ -35088,7 +35664,7 @@
         <v>23</v>
       </c>
       <c r="C1944">
-        <v>5240</v>
+        <v>5330</v>
       </c>
       <c r="D1944" t="s">
         <v>1946</v>
@@ -35102,7 +35678,7 @@
         <v>24</v>
       </c>
       <c r="C1945">
-        <v>5290</v>
+        <v>5350</v>
       </c>
       <c r="D1945" t="s">
         <v>1947</v>
@@ -35116,7 +35692,7 @@
         <v>25</v>
       </c>
       <c r="C1946">
-        <v>5360</v>
+        <v>5370</v>
       </c>
       <c r="D1946" t="s">
         <v>1948</v>
@@ -35130,7 +35706,7 @@
         <v>26</v>
       </c>
       <c r="C1947">
-        <v>5430</v>
+        <v>5420</v>
       </c>
       <c r="D1947" t="s">
         <v>1949</v>
@@ -35144,7 +35720,7 @@
         <v>27</v>
       </c>
       <c r="C1948">
-        <v>5510</v>
+        <v>5460</v>
       </c>
       <c r="D1948" t="s">
         <v>1950</v>
@@ -35158,7 +35734,7 @@
         <v>28</v>
       </c>
       <c r="C1949">
-        <v>5590</v>
+        <v>5550</v>
       </c>
       <c r="D1949" t="s">
         <v>1951</v>
@@ -35172,7 +35748,7 @@
         <v>29</v>
       </c>
       <c r="C1950">
-        <v>5670</v>
+        <v>5730</v>
       </c>
       <c r="D1950" t="s">
         <v>1952</v>
@@ -35186,7 +35762,7 @@
         <v>30</v>
       </c>
       <c r="C1951">
-        <v>5750</v>
+        <v>5820</v>
       </c>
       <c r="D1951" t="s">
         <v>1953</v>
@@ -35200,7 +35776,7 @@
         <v>31</v>
       </c>
       <c r="C1952">
-        <v>5810</v>
+        <v>5860</v>
       </c>
       <c r="D1952" t="s">
         <v>1954</v>
@@ -35214,7 +35790,7 @@
         <v>32</v>
       </c>
       <c r="C1953">
-        <v>5840</v>
+        <v>5870</v>
       </c>
       <c r="D1953" t="s">
         <v>1955</v>
@@ -35228,7 +35804,7 @@
         <v>33</v>
       </c>
       <c r="C1954">
-        <v>5850</v>
+        <v>5880</v>
       </c>
       <c r="D1954" t="s">
         <v>1956</v>
@@ -35242,7 +35818,7 @@
         <v>34</v>
       </c>
       <c r="C1955">
-        <v>5850</v>
+        <v>5870</v>
       </c>
       <c r="D1955" t="s">
         <v>1957</v>
@@ -35256,7 +35832,7 @@
         <v>35</v>
       </c>
       <c r="C1956">
-        <v>5820</v>
+        <v>5850</v>
       </c>
       <c r="D1956" t="s">
         <v>1958</v>
@@ -35270,7 +35846,7 @@
         <v>36</v>
       </c>
       <c r="C1957">
-        <v>5740</v>
+        <v>5800</v>
       </c>
       <c r="D1957" t="s">
         <v>1959</v>
@@ -35284,7 +35860,7 @@
         <v>37</v>
       </c>
       <c r="C1958">
-        <v>5640</v>
+        <v>5690</v>
       </c>
       <c r="D1958" t="s">
         <v>1960</v>
@@ -35298,7 +35874,7 @@
         <v>38</v>
       </c>
       <c r="C1959">
-        <v>5530</v>
+        <v>5590</v>
       </c>
       <c r="D1959" t="s">
         <v>1961</v>
@@ -35312,7 +35888,7 @@
         <v>39</v>
       </c>
       <c r="C1960">
-        <v>5430</v>
+        <v>5510</v>
       </c>
       <c r="D1960" t="s">
         <v>1962</v>
@@ -35326,7 +35902,7 @@
         <v>40</v>
       </c>
       <c r="C1961">
-        <v>5310</v>
+        <v>5410</v>
       </c>
       <c r="D1961" t="s">
         <v>1963</v>
@@ -35340,7 +35916,7 @@
         <v>41</v>
       </c>
       <c r="C1962">
-        <v>5200</v>
+        <v>5350</v>
       </c>
       <c r="D1962" t="s">
         <v>1964</v>
@@ -35354,7 +35930,7 @@
         <v>42</v>
       </c>
       <c r="C1963">
-        <v>5100</v>
+        <v>5260</v>
       </c>
       <c r="D1963" t="s">
         <v>1965</v>
@@ -35368,7 +35944,7 @@
         <v>43</v>
       </c>
       <c r="C1964">
-        <v>5010</v>
+        <v>5190</v>
       </c>
       <c r="D1964" t="s">
         <v>1966</v>
@@ -35382,7 +35958,7 @@
         <v>44</v>
       </c>
       <c r="C1965">
-        <v>4940</v>
+        <v>5120</v>
       </c>
       <c r="D1965" t="s">
         <v>1967</v>
@@ -35396,7 +35972,7 @@
         <v>45</v>
       </c>
       <c r="C1966">
-        <v>4890</v>
+        <v>5020</v>
       </c>
       <c r="D1966" t="s">
         <v>1968</v>
@@ -35410,7 +35986,7 @@
         <v>46</v>
       </c>
       <c r="C1967">
-        <v>4860</v>
+        <v>4930</v>
       </c>
       <c r="D1967" t="s">
         <v>1969</v>
@@ -35424,7 +36000,7 @@
         <v>47</v>
       </c>
       <c r="C1968">
-        <v>4830</v>
+        <v>4920</v>
       </c>
       <c r="D1968" t="s">
         <v>1970</v>
@@ -35438,7 +36014,7 @@
         <v>48</v>
       </c>
       <c r="C1969">
-        <v>4820</v>
+        <v>4930</v>
       </c>
       <c r="D1969" t="s">
         <v>1971</v>
@@ -35452,7 +36028,7 @@
         <v>49</v>
       </c>
       <c r="C1970">
-        <v>4810</v>
+        <v>4970</v>
       </c>
       <c r="D1970" t="s">
         <v>1972</v>
@@ -35466,7 +36042,7 @@
         <v>50</v>
       </c>
       <c r="C1971">
-        <v>4810</v>
+        <v>4990</v>
       </c>
       <c r="D1971" t="s">
         <v>1973</v>
@@ -35480,7 +36056,7 @@
         <v>51</v>
       </c>
       <c r="C1972">
-        <v>4820</v>
+        <v>5010</v>
       </c>
       <c r="D1972" t="s">
         <v>1974</v>
@@ -35494,7 +36070,7 @@
         <v>52</v>
       </c>
       <c r="C1973">
-        <v>4830</v>
+        <v>5030</v>
       </c>
       <c r="D1973" t="s">
         <v>1975</v>
@@ -35508,7 +36084,7 @@
         <v>53</v>
       </c>
       <c r="C1974">
-        <v>4850</v>
+        <v>5060</v>
       </c>
       <c r="D1974" t="s">
         <v>1976</v>
@@ -35522,7 +36098,7 @@
         <v>54</v>
       </c>
       <c r="C1975">
-        <v>4880</v>
+        <v>5090</v>
       </c>
       <c r="D1975" t="s">
         <v>1977</v>
@@ -35536,7 +36112,7 @@
         <v>55</v>
       </c>
       <c r="C1976">
-        <v>4920</v>
+        <v>5110</v>
       </c>
       <c r="D1976" t="s">
         <v>1978</v>
@@ -35550,7 +36126,7 @@
         <v>56</v>
       </c>
       <c r="C1977">
-        <v>4970</v>
+        <v>5140</v>
       </c>
       <c r="D1977" t="s">
         <v>1979</v>
@@ -35564,7 +36140,7 @@
         <v>57</v>
       </c>
       <c r="C1978">
-        <v>5020</v>
+        <v>5160</v>
       </c>
       <c r="D1978" t="s">
         <v>1980</v>
@@ -35578,7 +36154,7 @@
         <v>58</v>
       </c>
       <c r="C1979">
-        <v>5080</v>
+        <v>5180</v>
       </c>
       <c r="D1979" t="s">
         <v>1981</v>
@@ -35592,7 +36168,7 @@
         <v>59</v>
       </c>
       <c r="C1980">
-        <v>5140</v>
+        <v>5210</v>
       </c>
       <c r="D1980" t="s">
         <v>1982</v>
@@ -35606,7 +36182,7 @@
         <v>60</v>
       </c>
       <c r="C1981">
-        <v>5200</v>
+        <v>5250</v>
       </c>
       <c r="D1981" t="s">
         <v>1983</v>
@@ -35620,7 +36196,7 @@
         <v>61</v>
       </c>
       <c r="C1982">
-        <v>5250</v>
+        <v>5300</v>
       </c>
       <c r="D1982" t="s">
         <v>1984</v>
@@ -35634,7 +36210,7 @@
         <v>62</v>
       </c>
       <c r="C1983">
-        <v>5290</v>
+        <v>5350</v>
       </c>
       <c r="D1983" t="s">
         <v>1985</v>
@@ -35648,7 +36224,7 @@
         <v>63</v>
       </c>
       <c r="C1984">
-        <v>5330</v>
+        <v>5390</v>
       </c>
       <c r="D1984" t="s">
         <v>1986</v>
@@ -35662,7 +36238,7 @@
         <v>64</v>
       </c>
       <c r="C1985">
-        <v>5380</v>
+        <v>5440</v>
       </c>
       <c r="D1985" t="s">
         <v>1987</v>
@@ -35676,7 +36252,7 @@
         <v>65</v>
       </c>
       <c r="C1986">
-        <v>5440</v>
+        <v>5500</v>
       </c>
       <c r="D1986" t="s">
         <v>1988</v>
@@ -35690,7 +36266,7 @@
         <v>66</v>
       </c>
       <c r="C1987">
-        <v>5510</v>
+        <v>5560</v>
       </c>
       <c r="D1987" t="s">
         <v>1989</v>
@@ -35704,7 +36280,7 @@
         <v>67</v>
       </c>
       <c r="C1988">
-        <v>5590</v>
+        <v>5650</v>
       </c>
       <c r="D1988" t="s">
         <v>1990</v>
@@ -35718,7 +36294,7 @@
         <v>68</v>
       </c>
       <c r="C1989">
-        <v>5690</v>
+        <v>5770</v>
       </c>
       <c r="D1989" t="s">
         <v>1991</v>
@@ -35732,7 +36308,7 @@
         <v>69</v>
       </c>
       <c r="C1990">
-        <v>5810</v>
+        <v>5870</v>
       </c>
       <c r="D1990" t="s">
         <v>1992</v>
@@ -35746,7 +36322,7 @@
         <v>70</v>
       </c>
       <c r="C1991">
-        <v>5920</v>
+        <v>5990</v>
       </c>
       <c r="D1991" t="s">
         <v>1993</v>
@@ -35760,7 +36336,7 @@
         <v>71</v>
       </c>
       <c r="C1992">
-        <v>6030</v>
+        <v>6110</v>
       </c>
       <c r="D1992" t="s">
         <v>1994</v>
@@ -35774,7 +36350,7 @@
         <v>72</v>
       </c>
       <c r="C1993">
-        <v>6140</v>
+        <v>6230</v>
       </c>
       <c r="D1993" t="s">
         <v>1995</v>
@@ -35788,7 +36364,7 @@
         <v>73</v>
       </c>
       <c r="C1994">
-        <v>6250</v>
+        <v>6380</v>
       </c>
       <c r="D1994" t="s">
         <v>1996</v>
@@ -35802,7 +36378,7 @@
         <v>74</v>
       </c>
       <c r="C1995">
-        <v>6360</v>
+        <v>6490</v>
       </c>
       <c r="D1995" t="s">
         <v>1997</v>
@@ -35816,7 +36392,7 @@
         <v>75</v>
       </c>
       <c r="C1996">
-        <v>6480</v>
+        <v>6610</v>
       </c>
       <c r="D1996" t="s">
         <v>1998</v>
@@ -35830,7 +36406,7 @@
         <v>76</v>
       </c>
       <c r="C1997">
-        <v>6610</v>
+        <v>6720</v>
       </c>
       <c r="D1997" t="s">
         <v>1999</v>
@@ -35844,7 +36420,7 @@
         <v>77</v>
       </c>
       <c r="C1998">
-        <v>6740</v>
+        <v>6810</v>
       </c>
       <c r="D1998" t="s">
         <v>2000</v>
@@ -35858,7 +36434,7 @@
         <v>78</v>
       </c>
       <c r="C1999">
-        <v>6860</v>
+        <v>6900</v>
       </c>
       <c r="D1999" t="s">
         <v>2001</v>
@@ -35872,7 +36448,7 @@
         <v>79</v>
       </c>
       <c r="C2000">
-        <v>6950</v>
+        <v>6980</v>
       </c>
       <c r="D2000" t="s">
         <v>2002</v>
@@ -35886,7 +36462,7 @@
         <v>80</v>
       </c>
       <c r="C2001">
-        <v>7040</v>
+        <v>7030</v>
       </c>
       <c r="D2001" t="s">
         <v>2003</v>
@@ -35900,7 +36476,7 @@
         <v>81</v>
       </c>
       <c r="C2002">
-        <v>7120</v>
+        <v>7070</v>
       </c>
       <c r="D2002" t="s">
         <v>2004</v>
@@ -35914,7 +36490,7 @@
         <v>82</v>
       </c>
       <c r="C2003">
-        <v>7190</v>
+        <v>7110</v>
       </c>
       <c r="D2003" t="s">
         <v>2005</v>
@@ -35928,7 +36504,7 @@
         <v>83</v>
       </c>
       <c r="C2004">
-        <v>7200</v>
+        <v>7130</v>
       </c>
       <c r="D2004" t="s">
         <v>2006</v>
@@ -35942,7 +36518,7 @@
         <v>84</v>
       </c>
       <c r="C2005">
-        <v>7200</v>
+        <v>7170</v>
       </c>
       <c r="D2005" t="s">
         <v>2007</v>
@@ -35956,7 +36532,7 @@
         <v>85</v>
       </c>
       <c r="C2006">
-        <v>7200</v>
+        <v>7170</v>
       </c>
       <c r="D2006" t="s">
         <v>2008</v>
@@ -35970,7 +36546,7 @@
         <v>86</v>
       </c>
       <c r="C2007">
-        <v>7190</v>
+        <v>7140</v>
       </c>
       <c r="D2007" t="s">
         <v>2009</v>
@@ -35984,7 +36560,7 @@
         <v>87</v>
       </c>
       <c r="C2008">
-        <v>7170</v>
+        <v>7090</v>
       </c>
       <c r="D2008" t="s">
         <v>2010</v>
@@ -35998,7 +36574,7 @@
         <v>88</v>
       </c>
       <c r="C2009">
-        <v>7100</v>
+        <v>7000</v>
       </c>
       <c r="D2009" t="s">
         <v>2011</v>
@@ -36012,7 +36588,7 @@
         <v>89</v>
       </c>
       <c r="C2010">
-        <v>6950</v>
+        <v>6800</v>
       </c>
       <c r="D2010" t="s">
         <v>2012</v>
@@ -36026,7 +36602,7 @@
         <v>90</v>
       </c>
       <c r="C2011">
-        <v>6820</v>
+        <v>6660</v>
       </c>
       <c r="D2011" t="s">
         <v>2013</v>
@@ -36040,7 +36616,7 @@
         <v>91</v>
       </c>
       <c r="C2012">
-        <v>6670</v>
+        <v>6530</v>
       </c>
       <c r="D2012" t="s">
         <v>2014</v>
@@ -36054,7 +36630,7 @@
         <v>92</v>
       </c>
       <c r="C2013">
-        <v>6520</v>
+        <v>6410</v>
       </c>
       <c r="D2013" t="s">
         <v>2015</v>
@@ -36068,7 +36644,7 @@
         <v>93</v>
       </c>
       <c r="C2014">
-        <v>6380</v>
+        <v>6290</v>
       </c>
       <c r="D2014" t="s">
         <v>2016</v>
@@ -36082,7 +36658,7 @@
         <v>94</v>
       </c>
       <c r="C2015">
-        <v>6260</v>
+        <v>6160</v>
       </c>
       <c r="D2015" t="s">
         <v>2017</v>
@@ -36096,7 +36672,7 @@
         <v>95</v>
       </c>
       <c r="C2016">
-        <v>6150</v>
+        <v>6030</v>
       </c>
       <c r="D2016" t="s">
         <v>2018</v>
@@ -36110,7 +36686,7 @@
         <v>96</v>
       </c>
       <c r="C2017">
-        <v>6040</v>
+        <v>5920</v>
       </c>
       <c r="D2017" t="s">
         <v>2019</v>
@@ -36124,7 +36700,7 @@
         <v>1</v>
       </c>
       <c r="C2018">
-        <v>5630</v>
+        <v>5590</v>
       </c>
       <c r="D2018" t="s">
         <v>2020</v>
@@ -36138,7 +36714,7 @@
         <v>2</v>
       </c>
       <c r="C2019">
-        <v>5570</v>
+        <v>5550</v>
       </c>
       <c r="D2019" t="s">
         <v>2021</v>
@@ -36152,7 +36728,7 @@
         <v>3</v>
       </c>
       <c r="C2020">
-        <v>5520</v>
+        <v>5490</v>
       </c>
       <c r="D2020" t="s">
         <v>2022</v>
@@ -36166,7 +36742,7 @@
         <v>4</v>
       </c>
       <c r="C2021">
-        <v>5450</v>
+        <v>5410</v>
       </c>
       <c r="D2021" t="s">
         <v>2023</v>
@@ -36180,7 +36756,7 @@
         <v>5</v>
       </c>
       <c r="C2022">
-        <v>5390</v>
+        <v>5340</v>
       </c>
       <c r="D2022" t="s">
         <v>2024</v>
@@ -36194,7 +36770,7 @@
         <v>6</v>
       </c>
       <c r="C2023">
-        <v>5330</v>
+        <v>5290</v>
       </c>
       <c r="D2023" t="s">
         <v>2025</v>
@@ -36208,7 +36784,7 @@
         <v>7</v>
       </c>
       <c r="C2024">
-        <v>5280</v>
+        <v>5240</v>
       </c>
       <c r="D2024" t="s">
         <v>2026</v>
@@ -36222,7 +36798,7 @@
         <v>8</v>
       </c>
       <c r="C2025">
-        <v>5240</v>
+        <v>5190</v>
       </c>
       <c r="D2025" t="s">
         <v>2027</v>
@@ -36236,7 +36812,7 @@
         <v>9</v>
       </c>
       <c r="C2026">
-        <v>5200</v>
+        <v>5150</v>
       </c>
       <c r="D2026" t="s">
         <v>2028</v>
@@ -36250,7 +36826,7 @@
         <v>10</v>
       </c>
       <c r="C2027">
-        <v>5160</v>
+        <v>5110</v>
       </c>
       <c r="D2027" t="s">
         <v>2029</v>
@@ -36264,7 +36840,7 @@
         <v>11</v>
       </c>
       <c r="C2028">
-        <v>5130</v>
+        <v>5080</v>
       </c>
       <c r="D2028" t="s">
         <v>2030</v>
@@ -36278,7 +36854,7 @@
         <v>12</v>
       </c>
       <c r="C2029">
-        <v>5110</v>
+        <v>5060</v>
       </c>
       <c r="D2029" t="s">
         <v>2031</v>
@@ -36292,7 +36868,7 @@
         <v>13</v>
       </c>
       <c r="C2030">
-        <v>5090</v>
+        <v>5040</v>
       </c>
       <c r="D2030" t="s">
         <v>2032</v>
@@ -36306,7 +36882,7 @@
         <v>14</v>
       </c>
       <c r="C2031">
-        <v>5070</v>
+        <v>5020</v>
       </c>
       <c r="D2031" t="s">
         <v>2033</v>
@@ -36320,7 +36896,7 @@
         <v>15</v>
       </c>
       <c r="C2032">
-        <v>5060</v>
+        <v>5010</v>
       </c>
       <c r="D2032" t="s">
         <v>2034</v>
@@ -36334,7 +36910,7 @@
         <v>16</v>
       </c>
       <c r="C2033">
-        <v>5060</v>
+        <v>4990</v>
       </c>
       <c r="D2033" t="s">
         <v>2035</v>
@@ -36348,7 +36924,7 @@
         <v>17</v>
       </c>
       <c r="C2034">
-        <v>5060</v>
+        <v>4970</v>
       </c>
       <c r="D2034" t="s">
         <v>2036</v>
@@ -36362,7 +36938,7 @@
         <v>18</v>
       </c>
       <c r="C2035">
-        <v>5050</v>
+        <v>4960</v>
       </c>
       <c r="D2035" t="s">
         <v>2037</v>
@@ -36376,7 +36952,7 @@
         <v>19</v>
       </c>
       <c r="C2036">
-        <v>5050</v>
+        <v>4950</v>
       </c>
       <c r="D2036" t="s">
         <v>2038</v>
@@ -36390,7 +36966,7 @@
         <v>20</v>
       </c>
       <c r="C2037">
-        <v>5040</v>
+        <v>4950</v>
       </c>
       <c r="D2037" t="s">
         <v>2039</v>
@@ -36404,7 +36980,7 @@
         <v>21</v>
       </c>
       <c r="C2038">
-        <v>5030</v>
+        <v>4950</v>
       </c>
       <c r="D2038" t="s">
         <v>2040</v>
@@ -36418,7 +36994,7 @@
         <v>22</v>
       </c>
       <c r="C2039">
-        <v>5020</v>
+        <v>4950</v>
       </c>
       <c r="D2039" t="s">
         <v>2041</v>
@@ -36432,7 +37008,7 @@
         <v>23</v>
       </c>
       <c r="C2040">
-        <v>5020</v>
+        <v>4960</v>
       </c>
       <c r="D2040" t="s">
         <v>2042</v>
@@ -36446,7 +37022,7 @@
         <v>24</v>
       </c>
       <c r="C2041">
-        <v>5010</v>
+        <v>4970</v>
       </c>
       <c r="D2041" t="s">
         <v>2043</v>
@@ -36460,7 +37036,7 @@
         <v>25</v>
       </c>
       <c r="C2042">
-        <v>5010</v>
+        <v>4980</v>
       </c>
       <c r="D2042" t="s">
         <v>2044</v>
@@ -36474,7 +37050,7 @@
         <v>26</v>
       </c>
       <c r="C2043">
-        <v>5020</v>
+        <v>4980</v>
       </c>
       <c r="D2043" t="s">
         <v>2045</v>
@@ -36488,7 +37064,7 @@
         <v>27</v>
       </c>
       <c r="C2044">
-        <v>5030</v>
+        <v>4940</v>
       </c>
       <c r="D2044" t="s">
         <v>2046</v>
@@ -36502,7 +37078,7 @@
         <v>28</v>
       </c>
       <c r="C2045">
-        <v>5050</v>
+        <v>4900</v>
       </c>
       <c r="D2045" t="s">
         <v>2047</v>
@@ -36516,7 +37092,7 @@
         <v>29</v>
       </c>
       <c r="C2046">
-        <v>5070</v>
+        <v>4900</v>
       </c>
       <c r="D2046" t="s">
         <v>2048</v>
@@ -36530,7 +37106,7 @@
         <v>30</v>
       </c>
       <c r="C2047">
-        <v>5090</v>
+        <v>4890</v>
       </c>
       <c r="D2047" t="s">
         <v>2049</v>
@@ -36544,7 +37120,7 @@
         <v>31</v>
       </c>
       <c r="C2048">
-        <v>5110</v>
+        <v>4850</v>
       </c>
       <c r="D2048" t="s">
         <v>2050</v>
@@ -36558,7 +37134,7 @@
         <v>32</v>
       </c>
       <c r="C2049">
-        <v>5110</v>
+        <v>4790</v>
       </c>
       <c r="D2049" t="s">
         <v>2051</v>
@@ -36572,7 +37148,7 @@
         <v>33</v>
       </c>
       <c r="C2050">
-        <v>5110</v>
+        <v>4720</v>
       </c>
       <c r="D2050" t="s">
         <v>2052</v>
@@ -36586,7 +37162,7 @@
         <v>34</v>
       </c>
       <c r="C2051">
-        <v>5080</v>
+        <v>4650</v>
       </c>
       <c r="D2051" t="s">
         <v>2053</v>
@@ -36600,7 +37176,7 @@
         <v>35</v>
       </c>
       <c r="C2052">
-        <v>5040</v>
+        <v>4580</v>
       </c>
       <c r="D2052" t="s">
         <v>2054</v>
@@ -36614,7 +37190,7 @@
         <v>36</v>
       </c>
       <c r="C2053">
-        <v>4980</v>
+        <v>4500</v>
       </c>
       <c r="D2053" t="s">
         <v>2055</v>
@@ -36628,7 +37204,7 @@
         <v>37</v>
       </c>
       <c r="C2054">
-        <v>4910</v>
+        <v>4420</v>
       </c>
       <c r="D2054" t="s">
         <v>2056</v>
@@ -36642,7 +37218,7 @@
         <v>38</v>
       </c>
       <c r="C2055">
-        <v>4820</v>
+        <v>4350</v>
       </c>
       <c r="D2055" t="s">
         <v>2057</v>
@@ -36656,7 +37232,7 @@
         <v>39</v>
       </c>
       <c r="C2056">
-        <v>4730</v>
+        <v>4290</v>
       </c>
       <c r="D2056" t="s">
         <v>2058</v>
@@ -36670,7 +37246,7 @@
         <v>40</v>
       </c>
       <c r="C2057">
-        <v>4640</v>
+        <v>4230</v>
       </c>
       <c r="D2057" t="s">
         <v>2059</v>
@@ -36684,7 +37260,7 @@
         <v>41</v>
       </c>
       <c r="C2058">
-        <v>4560</v>
+        <v>4180</v>
       </c>
       <c r="D2058" t="s">
         <v>2060</v>
@@ -36698,7 +37274,7 @@
         <v>42</v>
       </c>
       <c r="C2059">
-        <v>4480</v>
+        <v>4140</v>
       </c>
       <c r="D2059" t="s">
         <v>2061</v>
@@ -36712,7 +37288,7 @@
         <v>43</v>
       </c>
       <c r="C2060">
-        <v>4420</v>
+        <v>4100</v>
       </c>
       <c r="D2060" t="s">
         <v>2062</v>
@@ -36726,7 +37302,7 @@
         <v>44</v>
       </c>
       <c r="C2061">
-        <v>4370</v>
+        <v>4080</v>
       </c>
       <c r="D2061" t="s">
         <v>2063</v>
@@ -36740,7 +37316,7 @@
         <v>45</v>
       </c>
       <c r="C2062">
-        <v>4340</v>
+        <v>4060</v>
       </c>
       <c r="D2062" t="s">
         <v>2064</v>
@@ -36754,7 +37330,7 @@
         <v>46</v>
       </c>
       <c r="C2063">
-        <v>4320</v>
+        <v>4060</v>
       </c>
       <c r="D2063" t="s">
         <v>2065</v>
@@ -36768,7 +37344,7 @@
         <v>47</v>
       </c>
       <c r="C2064">
-        <v>4310</v>
+        <v>4060</v>
       </c>
       <c r="D2064" t="s">
         <v>2066</v>
@@ -36782,7 +37358,7 @@
         <v>48</v>
       </c>
       <c r="C2065">
-        <v>4310</v>
+        <v>4060</v>
       </c>
       <c r="D2065" t="s">
         <v>2067</v>
@@ -36796,7 +37372,7 @@
         <v>49</v>
       </c>
       <c r="C2066">
-        <v>4300</v>
+        <v>4060</v>
       </c>
       <c r="D2066" t="s">
         <v>2068</v>
@@ -36810,7 +37386,7 @@
         <v>50</v>
       </c>
       <c r="C2067">
-        <v>4300</v>
+        <v>4070</v>
       </c>
       <c r="D2067" t="s">
         <v>2069</v>
@@ -36824,7 +37400,7 @@
         <v>51</v>
       </c>
       <c r="C2068">
-        <v>4300</v>
+        <v>4090</v>
       </c>
       <c r="D2068" t="s">
         <v>2070</v>
@@ -36838,7 +37414,7 @@
         <v>52</v>
       </c>
       <c r="C2069">
-        <v>4310</v>
+        <v>4100</v>
       </c>
       <c r="D2069" t="s">
         <v>2071</v>
@@ -36852,7 +37428,7 @@
         <v>53</v>
       </c>
       <c r="C2070">
-        <v>4320</v>
+        <v>4120</v>
       </c>
       <c r="D2070" t="s">
         <v>2072</v>
@@ -36866,7 +37442,7 @@
         <v>54</v>
       </c>
       <c r="C2071">
-        <v>4330</v>
+        <v>4140</v>
       </c>
       <c r="D2071" t="s">
         <v>2073</v>
@@ -36880,7 +37456,7 @@
         <v>55</v>
       </c>
       <c r="C2072">
-        <v>4350</v>
+        <v>4170</v>
       </c>
       <c r="D2072" t="s">
         <v>2074</v>
@@ -36894,7 +37470,7 @@
         <v>56</v>
       </c>
       <c r="C2073">
-        <v>4380</v>
+        <v>4210</v>
       </c>
       <c r="D2073" t="s">
         <v>2075</v>
@@ -36908,7 +37484,7 @@
         <v>57</v>
       </c>
       <c r="C2074">
-        <v>4430</v>
+        <v>4250</v>
       </c>
       <c r="D2074" t="s">
         <v>2076</v>
@@ -36922,7 +37498,7 @@
         <v>58</v>
       </c>
       <c r="C2075">
-        <v>4470</v>
+        <v>4300</v>
       </c>
       <c r="D2075" t="s">
         <v>2077</v>
@@ -36936,7 +37512,7 @@
         <v>59</v>
       </c>
       <c r="C2076">
-        <v>4520</v>
+        <v>4360</v>
       </c>
       <c r="D2076" t="s">
         <v>2078</v>
@@ -36950,7 +37526,7 @@
         <v>60</v>
       </c>
       <c r="C2077">
-        <v>4580</v>
+        <v>4420</v>
       </c>
       <c r="D2077" t="s">
         <v>2079</v>
@@ -36964,7 +37540,7 @@
         <v>61</v>
       </c>
       <c r="C2078">
-        <v>4640</v>
+        <v>4480</v>
       </c>
       <c r="D2078" t="s">
         <v>2080</v>
@@ -36978,7 +37554,7 @@
         <v>62</v>
       </c>
       <c r="C2079">
-        <v>4700</v>
+        <v>4550</v>
       </c>
       <c r="D2079" t="s">
         <v>2081</v>
@@ -36992,7 +37568,7 @@
         <v>63</v>
       </c>
       <c r="C2080">
-        <v>4760</v>
+        <v>4630</v>
       </c>
       <c r="D2080" t="s">
         <v>2082</v>
@@ -37006,7 +37582,7 @@
         <v>64</v>
       </c>
       <c r="C2081">
-        <v>4840</v>
+        <v>4710</v>
       </c>
       <c r="D2081" t="s">
         <v>2083</v>
@@ -37020,7 +37596,7 @@
         <v>65</v>
       </c>
       <c r="C2082">
-        <v>4930</v>
+        <v>4800</v>
       </c>
       <c r="D2082" t="s">
         <v>2084</v>
@@ -37034,7 +37610,7 @@
         <v>66</v>
       </c>
       <c r="C2083">
-        <v>5040</v>
+        <v>4890</v>
       </c>
       <c r="D2083" t="s">
         <v>2085</v>
@@ -37048,7 +37624,7 @@
         <v>67</v>
       </c>
       <c r="C2084">
-        <v>5160</v>
+        <v>5000</v>
       </c>
       <c r="D2084" t="s">
         <v>2086</v>
@@ -37062,7 +37638,7 @@
         <v>68</v>
       </c>
       <c r="C2085">
-        <v>5290</v>
+        <v>5100</v>
       </c>
       <c r="D2085" t="s">
         <v>2087</v>
@@ -37076,7 +37652,7 @@
         <v>69</v>
       </c>
       <c r="C2086">
-        <v>5430</v>
+        <v>5220</v>
       </c>
       <c r="D2086" t="s">
         <v>2088</v>
@@ -37090,7 +37666,7 @@
         <v>70</v>
       </c>
       <c r="C2087">
-        <v>5570</v>
+        <v>5330</v>
       </c>
       <c r="D2087" t="s">
         <v>2089</v>
@@ -37104,7 +37680,7 @@
         <v>71</v>
       </c>
       <c r="C2088">
-        <v>5700</v>
+        <v>5430</v>
       </c>
       <c r="D2088" t="s">
         <v>2090</v>
@@ -37118,7 +37694,7 @@
         <v>72</v>
       </c>
       <c r="C2089">
-        <v>5820</v>
+        <v>5540</v>
       </c>
       <c r="D2089" t="s">
         <v>2091</v>
@@ -37132,7 +37708,7 @@
         <v>73</v>
       </c>
       <c r="C2090">
-        <v>5940</v>
+        <v>5650</v>
       </c>
       <c r="D2090" t="s">
         <v>2092</v>
@@ -37146,7 +37722,7 @@
         <v>74</v>
       </c>
       <c r="C2091">
-        <v>6050</v>
+        <v>5770</v>
       </c>
       <c r="D2091" t="s">
         <v>2093</v>
@@ -37160,7 +37736,7 @@
         <v>75</v>
       </c>
       <c r="C2092">
-        <v>6160</v>
+        <v>5890</v>
       </c>
       <c r="D2092" t="s">
         <v>2094</v>
@@ -37174,7 +37750,7 @@
         <v>76</v>
       </c>
       <c r="C2093">
-        <v>6270</v>
+        <v>6020</v>
       </c>
       <c r="D2093" t="s">
         <v>2095</v>
@@ -37188,7 +37764,7 @@
         <v>77</v>
       </c>
       <c r="C2094">
-        <v>6380</v>
+        <v>6150</v>
       </c>
       <c r="D2094" t="s">
         <v>2096</v>
@@ -37202,7 +37778,7 @@
         <v>78</v>
       </c>
       <c r="C2095">
-        <v>6490</v>
+        <v>6270</v>
       </c>
       <c r="D2095" t="s">
         <v>2097</v>
@@ -37216,7 +37792,7 @@
         <v>79</v>
       </c>
       <c r="C2096">
-        <v>6570</v>
+        <v>6380</v>
       </c>
       <c r="D2096" t="s">
         <v>2098</v>
@@ -37230,7 +37806,7 @@
         <v>80</v>
       </c>
       <c r="C2097">
-        <v>6620</v>
+        <v>6460</v>
       </c>
       <c r="D2097" t="s">
         <v>2099</v>
@@ -37244,7 +37820,7 @@
         <v>81</v>
       </c>
       <c r="C2098">
-        <v>6680</v>
+        <v>6550</v>
       </c>
       <c r="D2098" t="s">
         <v>2100</v>
@@ -37258,7 +37834,7 @@
         <v>82</v>
       </c>
       <c r="C2099">
-        <v>6740</v>
+        <v>6630</v>
       </c>
       <c r="D2099" t="s">
         <v>2101</v>
@@ -37272,7 +37848,7 @@
         <v>83</v>
       </c>
       <c r="C2100">
-        <v>6780</v>
+        <v>6640</v>
       </c>
       <c r="D2100" t="s">
         <v>2102</v>
@@ -37286,7 +37862,7 @@
         <v>84</v>
       </c>
       <c r="C2101">
-        <v>6800</v>
+        <v>6650</v>
       </c>
       <c r="D2101" t="s">
         <v>2103</v>
@@ -37300,7 +37876,7 @@
         <v>85</v>
       </c>
       <c r="C2102">
-        <v>6800</v>
+        <v>6650</v>
       </c>
       <c r="D2102" t="s">
         <v>2104</v>
@@ -37314,7 +37890,7 @@
         <v>86</v>
       </c>
       <c r="C2103">
-        <v>6780</v>
+        <v>6620</v>
       </c>
       <c r="D2103" t="s">
         <v>2105</v>
@@ -37328,7 +37904,7 @@
         <v>87</v>
       </c>
       <c r="C2104">
-        <v>6750</v>
+        <v>6600</v>
       </c>
       <c r="D2104" t="s">
         <v>2106</v>
@@ -37342,7 +37918,7 @@
         <v>88</v>
       </c>
       <c r="C2105">
-        <v>6650</v>
+        <v>6560</v>
       </c>
       <c r="D2105" t="s">
         <v>2107</v>
@@ -37356,7 +37932,7 @@
         <v>89</v>
       </c>
       <c r="C2106">
-        <v>6500</v>
+        <v>6460</v>
       </c>
       <c r="D2106" t="s">
         <v>2108</v>
@@ -37370,7 +37946,7 @@
         <v>90</v>
       </c>
       <c r="C2107">
-        <v>6400</v>
+        <v>6390</v>
       </c>
       <c r="D2107" t="s">
         <v>2109</v>
@@ -37384,7 +37960,7 @@
         <v>91</v>
       </c>
       <c r="C2108">
-        <v>6250</v>
+        <v>6240</v>
       </c>
       <c r="D2108" t="s">
         <v>2110</v>
@@ -37398,7 +37974,7 @@
         <v>92</v>
       </c>
       <c r="C2109">
-        <v>6090</v>
+        <v>6060</v>
       </c>
       <c r="D2109" t="s">
         <v>2111</v>
@@ -37412,7 +37988,7 @@
         <v>93</v>
       </c>
       <c r="C2110">
-        <v>5890</v>
+        <v>5840</v>
       </c>
       <c r="D2110" t="s">
         <v>2112</v>
@@ -37426,7 +38002,7 @@
         <v>94</v>
       </c>
       <c r="C2111">
-        <v>5720</v>
+        <v>5660</v>
       </c>
       <c r="D2111" t="s">
         <v>2113</v>
@@ -37440,7 +38016,7 @@
         <v>95</v>
       </c>
       <c r="C2112">
-        <v>5630</v>
+        <v>5580</v>
       </c>
       <c r="D2112" t="s">
         <v>2114</v>
@@ -37454,7 +38030,7 @@
         <v>96</v>
       </c>
       <c r="C2113">
-        <v>5520</v>
+        <v>5470</v>
       </c>
       <c r="D2113" t="s">
         <v>2115</v>
@@ -37468,7 +38044,7 @@
         <v>1</v>
       </c>
       <c r="C2114">
-        <v>5400</v>
+        <v>5380</v>
       </c>
       <c r="D2114" t="s">
         <v>2116</v>
@@ -37510,7 +38086,7 @@
         <v>4</v>
       </c>
       <c r="C2117">
-        <v>5220</v>
+        <v>5200</v>
       </c>
       <c r="D2117" t="s">
         <v>2119</v>
@@ -37524,7 +38100,7 @@
         <v>5</v>
       </c>
       <c r="C2118">
-        <v>5150</v>
+        <v>5120</v>
       </c>
       <c r="D2118" t="s">
         <v>2120</v>
@@ -37538,7 +38114,7 @@
         <v>6</v>
       </c>
       <c r="C2119">
-        <v>5080</v>
+        <v>5040</v>
       </c>
       <c r="D2119" t="s">
         <v>2121</v>
@@ -37552,7 +38128,7 @@
         <v>7</v>
       </c>
       <c r="C2120">
-        <v>5030</v>
+        <v>4970</v>
       </c>
       <c r="D2120" t="s">
         <v>2122</v>
@@ -37566,7 +38142,7 @@
         <v>8</v>
       </c>
       <c r="C2121">
-        <v>4990</v>
+        <v>4920</v>
       </c>
       <c r="D2121" t="s">
         <v>2123</v>
@@ -37580,7 +38156,7 @@
         <v>9</v>
       </c>
       <c r="C2122">
-        <v>4950</v>
+        <v>4870</v>
       </c>
       <c r="D2122" t="s">
         <v>2124</v>
@@ -37594,7 +38170,7 @@
         <v>10</v>
       </c>
       <c r="C2123">
-        <v>4910</v>
+        <v>4830</v>
       </c>
       <c r="D2123" t="s">
         <v>2125</v>
@@ -37608,7 +38184,7 @@
         <v>11</v>
       </c>
       <c r="C2124">
-        <v>4880</v>
+        <v>4790</v>
       </c>
       <c r="D2124" t="s">
         <v>2126</v>
@@ -37622,7 +38198,7 @@
         <v>12</v>
       </c>
       <c r="C2125">
-        <v>4850</v>
+        <v>4750</v>
       </c>
       <c r="D2125" t="s">
         <v>2127</v>
@@ -37636,7 +38212,7 @@
         <v>13</v>
       </c>
       <c r="C2126">
-        <v>4820</v>
+        <v>4710</v>
       </c>
       <c r="D2126" t="s">
         <v>2128</v>
@@ -37650,7 +38226,7 @@
         <v>14</v>
       </c>
       <c r="C2127">
-        <v>4800</v>
+        <v>4680</v>
       </c>
       <c r="D2127" t="s">
         <v>2129</v>
@@ -37664,7 +38240,7 @@
         <v>15</v>
       </c>
       <c r="C2128">
-        <v>4780</v>
+        <v>4660</v>
       </c>
       <c r="D2128" t="s">
         <v>2130</v>
@@ -37678,7 +38254,7 @@
         <v>16</v>
       </c>
       <c r="C2129">
-        <v>4770</v>
+        <v>4650</v>
       </c>
       <c r="D2129" t="s">
         <v>2131</v>
@@ -37692,7 +38268,7 @@
         <v>17</v>
       </c>
       <c r="C2130">
-        <v>4760</v>
+        <v>4650</v>
       </c>
       <c r="D2130" t="s">
         <v>2132</v>
@@ -37706,7 +38282,7 @@
         <v>18</v>
       </c>
       <c r="C2131">
-        <v>4750</v>
+        <v>4650</v>
       </c>
       <c r="D2131" t="s">
         <v>2133</v>
@@ -37720,7 +38296,7 @@
         <v>19</v>
       </c>
       <c r="C2132">
-        <v>4750</v>
+        <v>4600</v>
       </c>
       <c r="D2132" t="s">
         <v>2134</v>
@@ -37734,7 +38310,7 @@
         <v>20</v>
       </c>
       <c r="C2133">
-        <v>4740</v>
+        <v>4570</v>
       </c>
       <c r="D2133" t="s">
         <v>2135</v>
@@ -37748,7 +38324,7 @@
         <v>21</v>
       </c>
       <c r="C2134">
-        <v>4740</v>
+        <v>4550</v>
       </c>
       <c r="D2134" t="s">
         <v>2136</v>
@@ -37762,7 +38338,7 @@
         <v>22</v>
       </c>
       <c r="C2135">
-        <v>4730</v>
+        <v>4520</v>
       </c>
       <c r="D2135" t="s">
         <v>2137</v>
@@ -37776,7 +38352,7 @@
         <v>23</v>
       </c>
       <c r="C2136">
-        <v>4710</v>
+        <v>4500</v>
       </c>
       <c r="D2136" t="s">
         <v>2138</v>
@@ -37790,7 +38366,7 @@
         <v>24</v>
       </c>
       <c r="C2137">
-        <v>4700</v>
+        <v>4500</v>
       </c>
       <c r="D2137" t="s">
         <v>2139</v>
@@ -37804,7 +38380,7 @@
         <v>25</v>
       </c>
       <c r="C2138">
-        <v>4680</v>
+        <v>4450</v>
       </c>
       <c r="D2138" t="s">
         <v>2140</v>
@@ -37818,7 +38394,7 @@
         <v>26</v>
       </c>
       <c r="C2139">
-        <v>4670</v>
+        <v>4400</v>
       </c>
       <c r="D2139" t="s">
         <v>2141</v>
@@ -37832,7 +38408,7 @@
         <v>27</v>
       </c>
       <c r="C2140">
-        <v>4650</v>
+        <v>4400</v>
       </c>
       <c r="D2140" t="s">
         <v>2142</v>
@@ -37846,7 +38422,7 @@
         <v>28</v>
       </c>
       <c r="C2141">
-        <v>4640</v>
+        <v>4380</v>
       </c>
       <c r="D2141" t="s">
         <v>2143</v>
@@ -37860,7 +38436,7 @@
         <v>29</v>
       </c>
       <c r="C2142">
-        <v>4630</v>
+        <v>4350</v>
       </c>
       <c r="D2142" t="s">
         <v>2144</v>
@@ -37874,7 +38450,7 @@
         <v>30</v>
       </c>
       <c r="C2143">
-        <v>4620</v>
+        <v>4300</v>
       </c>
       <c r="D2143" t="s">
         <v>2145</v>
@@ -37888,7 +38464,7 @@
         <v>31</v>
       </c>
       <c r="C2144">
-        <v>4600</v>
+        <v>4270</v>
       </c>
       <c r="D2144" t="s">
         <v>2146</v>
@@ -37902,7 +38478,7 @@
         <v>32</v>
       </c>
       <c r="C2145">
-        <v>4580</v>
+        <v>4260</v>
       </c>
       <c r="D2145" t="s">
         <v>2147</v>
@@ -37916,7 +38492,7 @@
         <v>33</v>
       </c>
       <c r="C2146">
-        <v>4560</v>
+        <v>4240</v>
       </c>
       <c r="D2146" t="s">
         <v>2148</v>
@@ -37930,7 +38506,7 @@
         <v>34</v>
       </c>
       <c r="C2147">
-        <v>4520</v>
+        <v>4200</v>
       </c>
       <c r="D2147" t="s">
         <v>2149</v>
@@ -37944,7 +38520,7 @@
         <v>35</v>
       </c>
       <c r="C2148">
-        <v>4460</v>
+        <v>4150</v>
       </c>
       <c r="D2148" t="s">
         <v>2150</v>
@@ -37958,7 +38534,7 @@
         <v>36</v>
       </c>
       <c r="C2149">
-        <v>4400</v>
+        <v>4090</v>
       </c>
       <c r="D2149" t="s">
         <v>2151</v>
@@ -37972,7 +38548,7 @@
         <v>37</v>
       </c>
       <c r="C2150">
-        <v>4320</v>
+        <v>4030</v>
       </c>
       <c r="D2150" t="s">
         <v>2152</v>
@@ -37986,7 +38562,7 @@
         <v>38</v>
       </c>
       <c r="C2151">
-        <v>4230</v>
+        <v>3960</v>
       </c>
       <c r="D2151" t="s">
         <v>2153</v>
@@ -38000,7 +38576,7 @@
         <v>39</v>
       </c>
       <c r="C2152">
-        <v>4150</v>
+        <v>3900</v>
       </c>
       <c r="D2152" t="s">
         <v>2154</v>
@@ -38014,7 +38590,7 @@
         <v>40</v>
       </c>
       <c r="C2153">
-        <v>4060</v>
+        <v>3830</v>
       </c>
       <c r="D2153" t="s">
         <v>2155</v>
@@ -38028,7 +38604,7 @@
         <v>41</v>
       </c>
       <c r="C2154">
-        <v>3980</v>
+        <v>3770</v>
       </c>
       <c r="D2154" t="s">
         <v>2156</v>
@@ -38042,7 +38618,7 @@
         <v>42</v>
       </c>
       <c r="C2155">
-        <v>3920</v>
+        <v>3720</v>
       </c>
       <c r="D2155" t="s">
         <v>2157</v>
@@ -38056,7 +38632,7 @@
         <v>43</v>
       </c>
       <c r="C2156">
-        <v>3860</v>
+        <v>3680</v>
       </c>
       <c r="D2156" t="s">
         <v>2158</v>
@@ -38070,7 +38646,7 @@
         <v>44</v>
       </c>
       <c r="C2157">
-        <v>3830</v>
+        <v>3660</v>
       </c>
       <c r="D2157" t="s">
         <v>2159</v>
@@ -38084,7 +38660,7 @@
         <v>45</v>
       </c>
       <c r="C2158">
-        <v>3810</v>
+        <v>3650</v>
       </c>
       <c r="D2158" t="s">
         <v>2160</v>
@@ -38098,7 +38674,7 @@
         <v>46</v>
       </c>
       <c r="C2159">
-        <v>3800</v>
+        <v>3650</v>
       </c>
       <c r="D2159" t="s">
         <v>2161</v>
@@ -38112,7 +38688,7 @@
         <v>47</v>
       </c>
       <c r="C2160">
-        <v>3800</v>
+        <v>3660</v>
       </c>
       <c r="D2160" t="s">
         <v>2162</v>
@@ -38126,7 +38702,7 @@
         <v>48</v>
       </c>
       <c r="C2161">
-        <v>3800</v>
+        <v>3680</v>
       </c>
       <c r="D2161" t="s">
         <v>2163</v>
@@ -38140,7 +38716,7 @@
         <v>49</v>
       </c>
       <c r="C2162">
-        <v>3810</v>
+        <v>3690</v>
       </c>
       <c r="D2162" t="s">
         <v>2164</v>
@@ -38154,7 +38730,7 @@
         <v>50</v>
       </c>
       <c r="C2163">
-        <v>3810</v>
+        <v>3710</v>
       </c>
       <c r="D2163" t="s">
         <v>2165</v>
@@ -38168,7 +38744,7 @@
         <v>51</v>
       </c>
       <c r="C2164">
-        <v>3820</v>
+        <v>3720</v>
       </c>
       <c r="D2164" t="s">
         <v>2166</v>
@@ -38182,7 +38758,7 @@
         <v>52</v>
       </c>
       <c r="C2165">
-        <v>3830</v>
+        <v>3740</v>
       </c>
       <c r="D2165" t="s">
         <v>2167</v>
@@ -38196,7 +38772,7 @@
         <v>53</v>
       </c>
       <c r="C2166">
-        <v>3850</v>
+        <v>3760</v>
       </c>
       <c r="D2166" t="s">
         <v>2168</v>
@@ -38210,7 +38786,7 @@
         <v>54</v>
       </c>
       <c r="C2167">
-        <v>3870</v>
+        <v>3780</v>
       </c>
       <c r="D2167" t="s">
         <v>2169</v>
@@ -38224,7 +38800,7 @@
         <v>55</v>
       </c>
       <c r="C2168">
-        <v>3900</v>
+        <v>3820</v>
       </c>
       <c r="D2168" t="s">
         <v>2170</v>
@@ -38238,7 +38814,7 @@
         <v>56</v>
       </c>
       <c r="C2169">
-        <v>3950</v>
+        <v>3860</v>
       </c>
       <c r="D2169" t="s">
         <v>2171</v>
@@ -38252,7 +38828,7 @@
         <v>57</v>
       </c>
       <c r="C2170">
-        <v>4000</v>
+        <v>3910</v>
       </c>
       <c r="D2170" t="s">
         <v>2172</v>
@@ -38266,7 +38842,7 @@
         <v>58</v>
       </c>
       <c r="C2171">
-        <v>4070</v>
+        <v>3980</v>
       </c>
       <c r="D2171" t="s">
         <v>2173</v>
@@ -38280,7 +38856,7 @@
         <v>59</v>
       </c>
       <c r="C2172">
-        <v>4140</v>
+        <v>4050</v>
       </c>
       <c r="D2172" t="s">
         <v>2174</v>
@@ -38294,7 +38870,7 @@
         <v>60</v>
       </c>
       <c r="C2173">
-        <v>4220</v>
+        <v>4130</v>
       </c>
       <c r="D2173" t="s">
         <v>2175</v>
@@ -38308,7 +38884,7 @@
         <v>61</v>
       </c>
       <c r="C2174">
-        <v>4290</v>
+        <v>4210</v>
       </c>
       <c r="D2174" t="s">
         <v>2176</v>
@@ -38322,7 +38898,7 @@
         <v>62</v>
       </c>
       <c r="C2175">
-        <v>4370</v>
+        <v>4300</v>
       </c>
       <c r="D2175" t="s">
         <v>2177</v>
@@ -38336,7 +38912,7 @@
         <v>63</v>
       </c>
       <c r="C2176">
-        <v>4450</v>
+        <v>4380</v>
       </c>
       <c r="D2176" t="s">
         <v>2178</v>
@@ -38350,7 +38926,7 @@
         <v>64</v>
       </c>
       <c r="C2177">
-        <v>4530</v>
+        <v>4460</v>
       </c>
       <c r="D2177" t="s">
         <v>2179</v>
@@ -38364,7 +38940,7 @@
         <v>65</v>
       </c>
       <c r="C2178">
-        <v>4620</v>
+        <v>4550</v>
       </c>
       <c r="D2178" t="s">
         <v>2180</v>
@@ -38378,7 +38954,7 @@
         <v>66</v>
       </c>
       <c r="C2179">
-        <v>4720</v>
+        <v>4650</v>
       </c>
       <c r="D2179" t="s">
         <v>2181</v>
@@ -38392,7 +38968,7 @@
         <v>67</v>
       </c>
       <c r="C2180">
-        <v>4840</v>
+        <v>4750</v>
       </c>
       <c r="D2180" t="s">
         <v>2182</v>
@@ -38406,7 +38982,7 @@
         <v>68</v>
       </c>
       <c r="C2181">
-        <v>4970</v>
+        <v>4860</v>
       </c>
       <c r="D2181" t="s">
         <v>2183</v>
@@ -38420,7 +38996,7 @@
         <v>69</v>
       </c>
       <c r="C2182">
-        <v>5110</v>
+        <v>4960</v>
       </c>
       <c r="D2182" t="s">
         <v>2184</v>
@@ -38434,7 +39010,7 @@
         <v>70</v>
       </c>
       <c r="C2183">
-        <v>5250</v>
+        <v>5070</v>
       </c>
       <c r="D2183" t="s">
         <v>2185</v>
@@ -38448,7 +39024,7 @@
         <v>71</v>
       </c>
       <c r="C2184">
-        <v>5400</v>
+        <v>5160</v>
       </c>
       <c r="D2184" t="s">
         <v>2186</v>
@@ -38462,7 +39038,7 @@
         <v>72</v>
       </c>
       <c r="C2185">
-        <v>5530</v>
+        <v>5260</v>
       </c>
       <c r="D2185" t="s">
         <v>2187</v>
@@ -38476,7 +39052,7 @@
         <v>73</v>
       </c>
       <c r="C2186">
-        <v>5650</v>
+        <v>5350</v>
       </c>
       <c r="D2186" t="s">
         <v>2188</v>
@@ -38490,7 +39066,7 @@
         <v>74</v>
       </c>
       <c r="C2187">
-        <v>5760</v>
+        <v>5440</v>
       </c>
       <c r="D2187" t="s">
         <v>2189</v>
@@ -38504,7 +39080,7 @@
         <v>75</v>
       </c>
       <c r="C2188">
-        <v>5860</v>
+        <v>5540</v>
       </c>
       <c r="D2188" t="s">
         <v>2190</v>
@@ -38518,7 +39094,7 @@
         <v>76</v>
       </c>
       <c r="C2189">
-        <v>5960</v>
+        <v>5660</v>
       </c>
       <c r="D2189" t="s">
         <v>2191</v>
@@ -38532,7 +39108,7 @@
         <v>77</v>
       </c>
       <c r="C2190">
-        <v>6050</v>
+        <v>5770</v>
       </c>
       <c r="D2190" t="s">
         <v>2192</v>
@@ -38546,7 +39122,7 @@
         <v>78</v>
       </c>
       <c r="C2191">
-        <v>6140</v>
+        <v>5870</v>
       </c>
       <c r="D2191" t="s">
         <v>2193</v>
@@ -38560,7 +39136,7 @@
         <v>79</v>
       </c>
       <c r="C2192">
-        <v>6220</v>
+        <v>5940</v>
       </c>
       <c r="D2192" t="s">
         <v>2194</v>
@@ -38574,7 +39150,7 @@
         <v>80</v>
       </c>
       <c r="C2193">
-        <v>6290</v>
+        <v>5980</v>
       </c>
       <c r="D2193" t="s">
         <v>2195</v>
@@ -38588,7 +39164,7 @@
         <v>81</v>
       </c>
       <c r="C2194">
-        <v>6360</v>
+        <v>6000</v>
       </c>
       <c r="D2194" t="s">
         <v>2196</v>
@@ -38602,7 +39178,7 @@
         <v>82</v>
       </c>
       <c r="C2195">
-        <v>6440</v>
+        <v>6000</v>
       </c>
       <c r="D2195" t="s">
         <v>2197</v>
@@ -38616,7 +39192,7 @@
         <v>83</v>
       </c>
       <c r="C2196">
-        <v>6490</v>
+        <v>6000</v>
       </c>
       <c r="D2196" t="s">
         <v>2198</v>
@@ -38630,7 +39206,7 @@
         <v>84</v>
       </c>
       <c r="C2197">
-        <v>6500</v>
+        <v>6000</v>
       </c>
       <c r="D2197" t="s">
         <v>2199</v>
@@ -38644,7 +39220,7 @@
         <v>85</v>
       </c>
       <c r="C2198">
-        <v>6500</v>
+        <v>5980</v>
       </c>
       <c r="D2198" t="s">
         <v>2200</v>
@@ -38658,7 +39234,7 @@
         <v>86</v>
       </c>
       <c r="C2199">
-        <v>6480</v>
+        <v>5950</v>
       </c>
       <c r="D2199" t="s">
         <v>2201</v>
@@ -38672,7 +39248,7 @@
         <v>87</v>
       </c>
       <c r="C2200">
-        <v>6440</v>
+        <v>5980</v>
       </c>
       <c r="D2200" t="s">
         <v>2202</v>
@@ -38686,7 +39262,7 @@
         <v>88</v>
       </c>
       <c r="C2201">
-        <v>6350</v>
+        <v>5930</v>
       </c>
       <c r="D2201" t="s">
         <v>2203</v>
@@ -38700,7 +39276,7 @@
         <v>89</v>
       </c>
       <c r="C2202">
-        <v>6230</v>
+        <v>5820</v>
       </c>
       <c r="D2202" t="s">
         <v>2204</v>
@@ -38714,7 +39290,7 @@
         <v>90</v>
       </c>
       <c r="C2203">
-        <v>6120</v>
+        <v>5760</v>
       </c>
       <c r="D2203" t="s">
         <v>2205</v>
@@ -38728,7 +39304,7 @@
         <v>91</v>
       </c>
       <c r="C2204">
-        <v>5970</v>
+        <v>5640</v>
       </c>
       <c r="D2204" t="s">
         <v>2206</v>
@@ -38742,7 +39318,7 @@
         <v>92</v>
       </c>
       <c r="C2205">
-        <v>5850</v>
+        <v>5520</v>
       </c>
       <c r="D2205" t="s">
         <v>2207</v>
@@ -38756,7 +39332,7 @@
         <v>93</v>
       </c>
       <c r="C2206">
-        <v>5720</v>
+        <v>5380</v>
       </c>
       <c r="D2206" t="s">
         <v>2208</v>
@@ -38770,7 +39346,7 @@
         <v>94</v>
       </c>
       <c r="C2207">
-        <v>5570</v>
+        <v>5290</v>
       </c>
       <c r="D2207" t="s">
         <v>2209</v>
@@ -38784,7 +39360,7 @@
         <v>95</v>
       </c>
       <c r="C2208">
-        <v>5480</v>
+        <v>5170</v>
       </c>
       <c r="D2208" t="s">
         <v>2210</v>
@@ -38798,7 +39374,7 @@
         <v>96</v>
       </c>
       <c r="C2209">
-        <v>5370</v>
+        <v>5070</v>
       </c>
       <c r="D2209" t="s">
         <v>2211</v>
@@ -38812,7 +39388,7 @@
         <v>1</v>
       </c>
       <c r="C2210">
-        <v>5260</v>
+        <v>5140</v>
       </c>
       <c r="D2210" t="s">
         <v>2212</v>
@@ -38826,7 +39402,7 @@
         <v>2</v>
       </c>
       <c r="C2211">
-        <v>5160</v>
+        <v>5100</v>
       </c>
       <c r="D2211" t="s">
         <v>2213</v>
@@ -38840,7 +39416,7 @@
         <v>3</v>
       </c>
       <c r="C2212">
-        <v>5090</v>
+        <v>5040</v>
       </c>
       <c r="D2212" t="s">
         <v>2214</v>
@@ -38854,7 +39430,7 @@
         <v>4</v>
       </c>
       <c r="C2213">
-        <v>5030</v>
+        <v>4960</v>
       </c>
       <c r="D2213" t="s">
         <v>2215</v>
@@ -38868,7 +39444,7 @@
         <v>5</v>
       </c>
       <c r="C2214">
-        <v>4980</v>
+        <v>4890</v>
       </c>
       <c r="D2214" t="s">
         <v>2216</v>
@@ -38882,7 +39458,7 @@
         <v>6</v>
       </c>
       <c r="C2215">
-        <v>4940</v>
+        <v>4840</v>
       </c>
       <c r="D2215" t="s">
         <v>2217</v>
@@ -38896,7 +39472,7 @@
         <v>7</v>
       </c>
       <c r="C2216">
-        <v>4900</v>
+        <v>4790</v>
       </c>
       <c r="D2216" t="s">
         <v>2218</v>
@@ -38910,7 +39486,7 @@
         <v>8</v>
       </c>
       <c r="C2217">
-        <v>4860</v>
+        <v>4740</v>
       </c>
       <c r="D2217" t="s">
         <v>2219</v>
@@ -38924,7 +39500,7 @@
         <v>9</v>
       </c>
       <c r="C2218">
-        <v>4820</v>
+        <v>4710</v>
       </c>
       <c r="D2218" t="s">
         <v>2220</v>
@@ -38938,7 +39514,7 @@
         <v>10</v>
       </c>
       <c r="C2219">
-        <v>4790</v>
+        <v>4670</v>
       </c>
       <c r="D2219" t="s">
         <v>2221</v>
@@ -38952,7 +39528,7 @@
         <v>11</v>
       </c>
       <c r="C2220">
-        <v>4770</v>
+        <v>4650</v>
       </c>
       <c r="D2220" t="s">
         <v>2222</v>
@@ -38966,7 +39542,7 @@
         <v>12</v>
       </c>
       <c r="C2221">
-        <v>4760</v>
+        <v>4600</v>
       </c>
       <c r="D2221" t="s">
         <v>2223</v>
@@ -38980,7 +39556,7 @@
         <v>13</v>
       </c>
       <c r="C2222">
-        <v>4750</v>
+        <v>4610</v>
       </c>
       <c r="D2222" t="s">
         <v>2224</v>
@@ -38994,7 +39570,7 @@
         <v>14</v>
       </c>
       <c r="C2223">
-        <v>4750</v>
+        <v>4620</v>
       </c>
       <c r="D2223" t="s">
         <v>2225</v>
@@ -39008,7 +39584,7 @@
         <v>15</v>
       </c>
       <c r="C2224">
-        <v>4750</v>
+        <v>4620</v>
       </c>
       <c r="D2224" t="s">
         <v>2226</v>
@@ -39022,7 +39598,7 @@
         <v>16</v>
       </c>
       <c r="C2225">
-        <v>4760</v>
+        <v>4620</v>
       </c>
       <c r="D2225" t="s">
         <v>2227</v>
@@ -39036,7 +39612,7 @@
         <v>17</v>
       </c>
       <c r="C2226">
-        <v>4770</v>
+        <v>4630</v>
       </c>
       <c r="D2226" t="s">
         <v>2228</v>
@@ -39050,7 +39626,7 @@
         <v>18</v>
       </c>
       <c r="C2227">
-        <v>4780</v>
+        <v>4640</v>
       </c>
       <c r="D2227" t="s">
         <v>2229</v>
@@ -39064,7 +39640,7 @@
         <v>19</v>
       </c>
       <c r="C2228">
-        <v>4800</v>
+        <v>4660</v>
       </c>
       <c r="D2228" t="s">
         <v>2230</v>
@@ -39078,7 +39654,7 @@
         <v>20</v>
       </c>
       <c r="C2229">
-        <v>4830</v>
+        <v>4700</v>
       </c>
       <c r="D2229" t="s">
         <v>2231</v>
@@ -39092,7 +39668,7 @@
         <v>21</v>
       </c>
       <c r="C2230">
-        <v>4860</v>
+        <v>4760</v>
       </c>
       <c r="D2230" t="s">
         <v>2232</v>
@@ -39106,7 +39682,7 @@
         <v>22</v>
       </c>
       <c r="C2231">
-        <v>4900</v>
+        <v>4830</v>
       </c>
       <c r="D2231" t="s">
         <v>2233</v>
@@ -39120,7 +39696,7 @@
         <v>23</v>
       </c>
       <c r="C2232">
-        <v>4950</v>
+        <v>4920</v>
       </c>
       <c r="D2232" t="s">
         <v>2234</v>
@@ -39134,7 +39710,7 @@
         <v>24</v>
       </c>
       <c r="C2233">
-        <v>5010</v>
+        <v>5030</v>
       </c>
       <c r="D2233" t="s">
         <v>2235</v>
@@ -39148,7 +39724,7 @@
         <v>25</v>
       </c>
       <c r="C2234">
-        <v>5080</v>
+        <v>5160</v>
       </c>
       <c r="D2234" t="s">
         <v>2236</v>
@@ -39162,7 +39738,7 @@
         <v>26</v>
       </c>
       <c r="C2235">
-        <v>5180</v>
+        <v>5290</v>
       </c>
       <c r="D2235" t="s">
         <v>2237</v>
@@ -39176,7 +39752,7 @@
         <v>27</v>
       </c>
       <c r="C2236">
-        <v>5300</v>
+        <v>5420</v>
       </c>
       <c r="D2236" t="s">
         <v>2238</v>
@@ -39190,7 +39766,7 @@
         <v>28</v>
       </c>
       <c r="C2237">
-        <v>5460</v>
+        <v>5550</v>
       </c>
       <c r="D2237" t="s">
         <v>2239</v>
@@ -39204,7 +39780,7 @@
         <v>29</v>
       </c>
       <c r="C2238">
-        <v>5640</v>
+        <v>5660</v>
       </c>
       <c r="D2238" t="s">
         <v>2240</v>
@@ -39218,7 +39794,7 @@
         <v>30</v>
       </c>
       <c r="C2239">
-        <v>5790</v>
+        <v>5750</v>
       </c>
       <c r="D2239" t="s">
         <v>2241</v>
@@ -39232,7 +39808,7 @@
         <v>31</v>
       </c>
       <c r="C2240">
-        <v>5920</v>
+        <v>5800</v>
       </c>
       <c r="D2240" t="s">
         <v>2242</v>
@@ -39246,7 +39822,7 @@
         <v>32</v>
       </c>
       <c r="C2241">
-        <v>6010</v>
+        <v>5800</v>
       </c>
       <c r="D2241" t="s">
         <v>2243</v>
@@ -39260,7 +39836,7 @@
         <v>33</v>
       </c>
       <c r="C2242">
-        <v>6060</v>
+        <v>5800</v>
       </c>
       <c r="D2242" t="s">
         <v>2244</v>
@@ -39274,7 +39850,7 @@
         <v>34</v>
       </c>
       <c r="C2243">
-        <v>6080</v>
+        <v>5800</v>
       </c>
       <c r="D2243" t="s">
         <v>2245</v>
@@ -39288,7 +39864,7 @@
         <v>35</v>
       </c>
       <c r="C2244">
-        <v>6050</v>
+        <v>5750</v>
       </c>
       <c r="D2244" t="s">
         <v>2246</v>
@@ -39302,7 +39878,7 @@
         <v>36</v>
       </c>
       <c r="C2245">
-        <v>5980</v>
+        <v>5680</v>
       </c>
       <c r="D2245" t="s">
         <v>2247</v>
@@ -39316,7 +39892,7 @@
         <v>37</v>
       </c>
       <c r="C2246">
-        <v>5870</v>
+        <v>5590</v>
       </c>
       <c r="D2246" t="s">
         <v>2248</v>
@@ -39330,7 +39906,7 @@
         <v>38</v>
       </c>
       <c r="C2247">
-        <v>5770</v>
+        <v>5490</v>
       </c>
       <c r="D2247" t="s">
         <v>2249</v>
@@ -39344,7 +39920,7 @@
         <v>39</v>
       </c>
       <c r="C2248">
-        <v>5670</v>
+        <v>5390</v>
       </c>
       <c r="D2248" t="s">
         <v>2250</v>
@@ -39358,7 +39934,7 @@
         <v>40</v>
       </c>
       <c r="C2249">
-        <v>5580</v>
+        <v>5300</v>
       </c>
       <c r="D2249" t="s">
         <v>2251</v>
@@ -39372,7 +39948,7 @@
         <v>41</v>
       </c>
       <c r="C2250">
-        <v>5500</v>
+        <v>5210</v>
       </c>
       <c r="D2250" t="s">
         <v>2252</v>
@@ -39386,7 +39962,7 @@
         <v>42</v>
       </c>
       <c r="C2251">
-        <v>5430</v>
+        <v>5140</v>
       </c>
       <c r="D2251" t="s">
         <v>2253</v>
@@ -39400,7 +39976,7 @@
         <v>43</v>
       </c>
       <c r="C2252">
-        <v>5360</v>
+        <v>5080</v>
       </c>
       <c r="D2252" t="s">
         <v>2254</v>
@@ -39414,7 +39990,7 @@
         <v>44</v>
       </c>
       <c r="C2253">
-        <v>5300</v>
+        <v>5040</v>
       </c>
       <c r="D2253" t="s">
         <v>2255</v>
@@ -39428,7 +40004,7 @@
         <v>45</v>
       </c>
       <c r="C2254">
-        <v>5250</v>
+        <v>5010</v>
       </c>
       <c r="D2254" t="s">
         <v>2256</v>
@@ -39442,7 +40018,7 @@
         <v>46</v>
       </c>
       <c r="C2255">
-        <v>5200</v>
+        <v>5000</v>
       </c>
       <c r="D2255" t="s">
         <v>2257</v>
@@ -39456,7 +40032,7 @@
         <v>47</v>
       </c>
       <c r="C2256">
-        <v>5170</v>
+        <v>4990</v>
       </c>
       <c r="D2256" t="s">
         <v>2258</v>
@@ -39470,7 +40046,7 @@
         <v>48</v>
       </c>
       <c r="C2257">
-        <v>5160</v>
+        <v>5000</v>
       </c>
       <c r="D2257" t="s">
         <v>2259</v>
@@ -39484,7 +40060,7 @@
         <v>49</v>
       </c>
       <c r="C2258">
-        <v>5150</v>
+        <v>5010</v>
       </c>
       <c r="D2258" t="s">
         <v>2260</v>
@@ -39498,7 +40074,7 @@
         <v>50</v>
       </c>
       <c r="C2259">
-        <v>5170</v>
+        <v>5030</v>
       </c>
       <c r="D2259" t="s">
         <v>2261</v>
@@ -39512,7 +40088,7 @@
         <v>51</v>
       </c>
       <c r="C2260">
-        <v>5200</v>
+        <v>5050</v>
       </c>
       <c r="D2260" t="s">
         <v>2262</v>
@@ -39526,7 +40102,7 @@
         <v>52</v>
       </c>
       <c r="C2261">
-        <v>5260</v>
+        <v>5080</v>
       </c>
       <c r="D2261" t="s">
         <v>2263</v>
@@ -39540,7 +40116,7 @@
         <v>53</v>
       </c>
       <c r="C2262">
-        <v>5320</v>
+        <v>5110</v>
       </c>
       <c r="D2262" t="s">
         <v>2264</v>
@@ -39554,7 +40130,7 @@
         <v>54</v>
       </c>
       <c r="C2263">
-        <v>5380</v>
+        <v>5130</v>
       </c>
       <c r="D2263" t="s">
         <v>2265</v>
@@ -39568,7 +40144,7 @@
         <v>55</v>
       </c>
       <c r="C2264">
-        <v>5420</v>
+        <v>5160</v>
       </c>
       <c r="D2264" t="s">
         <v>2266</v>
@@ -39582,7 +40158,7 @@
         <v>56</v>
       </c>
       <c r="C2265">
-        <v>5440</v>
+        <v>5190</v>
       </c>
       <c r="D2265" t="s">
         <v>2267</v>
@@ -39596,7 +40172,7 @@
         <v>57</v>
       </c>
       <c r="C2266">
-        <v>5450</v>
+        <v>5210</v>
       </c>
       <c r="D2266" t="s">
         <v>2268</v>
@@ -39610,7 +40186,7 @@
         <v>58</v>
       </c>
       <c r="C2267">
-        <v>5470</v>
+        <v>5240</v>
       </c>
       <c r="D2267" t="s">
         <v>2269</v>
@@ -39624,7 +40200,7 @@
         <v>59</v>
       </c>
       <c r="C2268">
-        <v>5520</v>
+        <v>5260</v>
       </c>
       <c r="D2268" t="s">
         <v>2270</v>
@@ -39638,7 +40214,7 @@
         <v>60</v>
       </c>
       <c r="C2269">
-        <v>5590</v>
+        <v>5300</v>
       </c>
       <c r="D2269" t="s">
         <v>2271</v>
@@ -39652,7 +40228,7 @@
         <v>61</v>
       </c>
       <c r="C2270">
-        <v>5680</v>
+        <v>5330</v>
       </c>
       <c r="D2270" t="s">
         <v>2272</v>
@@ -39666,7 +40242,7 @@
         <v>62</v>
       </c>
       <c r="C2271">
-        <v>5770</v>
+        <v>5380</v>
       </c>
       <c r="D2271" t="s">
         <v>2273</v>
@@ -39680,7 +40256,7 @@
         <v>63</v>
       </c>
       <c r="C2272">
-        <v>5850</v>
+        <v>5440</v>
       </c>
       <c r="D2272" t="s">
         <v>2274</v>
@@ -39694,7 +40270,7 @@
         <v>64</v>
       </c>
       <c r="C2273">
-        <v>5930</v>
+        <v>5510</v>
       </c>
       <c r="D2273" t="s">
         <v>2275</v>
@@ -39708,7 +40284,7 @@
         <v>65</v>
       </c>
       <c r="C2274">
-        <v>5990</v>
+        <v>5600</v>
       </c>
       <c r="D2274" t="s">
         <v>2276</v>
@@ -39722,7 +40298,7 @@
         <v>66</v>
       </c>
       <c r="C2275">
-        <v>6070</v>
+        <v>5700</v>
       </c>
       <c r="D2275" t="s">
         <v>2277</v>
@@ -39736,7 +40312,7 @@
         <v>67</v>
       </c>
       <c r="C2276">
-        <v>6160</v>
+        <v>5800</v>
       </c>
       <c r="D2276" t="s">
         <v>2278</v>
@@ -39750,7 +40326,7 @@
         <v>68</v>
       </c>
       <c r="C2277">
-        <v>6260</v>
+        <v>5910</v>
       </c>
       <c r="D2277" t="s">
         <v>2279</v>
@@ -39764,7 +40340,7 @@
         <v>69</v>
       </c>
       <c r="C2278">
-        <v>6360</v>
+        <v>6020</v>
       </c>
       <c r="D2278" t="s">
         <v>2280</v>
@@ -39778,7 +40354,7 @@
         <v>70</v>
       </c>
       <c r="C2279">
-        <v>6480</v>
+        <v>6120</v>
       </c>
       <c r="D2279" t="s">
         <v>2281</v>
@@ -39792,7 +40368,7 @@
         <v>71</v>
       </c>
       <c r="C2280">
-        <v>6600</v>
+        <v>6230</v>
       </c>
       <c r="D2280" t="s">
         <v>2282</v>
@@ -39806,7 +40382,7 @@
         <v>72</v>
       </c>
       <c r="C2281">
-        <v>6720</v>
+        <v>6330</v>
       </c>
       <c r="D2281" t="s">
         <v>2283</v>
@@ -39820,7 +40396,7 @@
         <v>73</v>
       </c>
       <c r="C2282">
-        <v>6850</v>
+        <v>6430</v>
       </c>
       <c r="D2282" t="s">
         <v>2284</v>
@@ -39834,7 +40410,7 @@
         <v>74</v>
       </c>
       <c r="C2283">
-        <v>6950</v>
+        <v>6530</v>
       </c>
       <c r="D2283" t="s">
         <v>2285</v>
@@ -39848,7 +40424,7 @@
         <v>75</v>
       </c>
       <c r="C2284">
-        <v>7040</v>
+        <v>6620</v>
       </c>
       <c r="D2284" t="s">
         <v>2286</v>
@@ -39862,7 +40438,7 @@
         <v>76</v>
       </c>
       <c r="C2285">
-        <v>7090</v>
+        <v>6680</v>
       </c>
       <c r="D2285" t="s">
         <v>2287</v>
@@ -39876,7 +40452,7 @@
         <v>77</v>
       </c>
       <c r="C2286">
-        <v>7130</v>
+        <v>6750</v>
       </c>
       <c r="D2286" t="s">
         <v>2288</v>
@@ -39890,7 +40466,7 @@
         <v>78</v>
       </c>
       <c r="C2287">
-        <v>7170</v>
+        <v>6800</v>
       </c>
       <c r="D2287" t="s">
         <v>2289</v>
@@ -39904,7 +40480,7 @@
         <v>79</v>
       </c>
       <c r="C2288">
-        <v>7210</v>
+        <v>6830</v>
       </c>
       <c r="D2288" t="s">
         <v>2290</v>
@@ -39918,7 +40494,7 @@
         <v>80</v>
       </c>
       <c r="C2289">
-        <v>7260</v>
+        <v>6860</v>
       </c>
       <c r="D2289" t="s">
         <v>2291</v>
@@ -39932,7 +40508,7 @@
         <v>81</v>
       </c>
       <c r="C2290">
-        <v>7320</v>
+        <v>6880</v>
       </c>
       <c r="D2290" t="s">
         <v>2292</v>
@@ -39946,7 +40522,7 @@
         <v>82</v>
       </c>
       <c r="C2291">
-        <v>7360</v>
+        <v>6900</v>
       </c>
       <c r="D2291" t="s">
         <v>2293</v>
@@ -39960,7 +40536,7 @@
         <v>83</v>
       </c>
       <c r="C2292">
-        <v>7390</v>
+        <v>6900</v>
       </c>
       <c r="D2292" t="s">
         <v>2294</v>
@@ -39974,7 +40550,7 @@
         <v>84</v>
       </c>
       <c r="C2293">
-        <v>7400</v>
+        <v>6900</v>
       </c>
       <c r="D2293" t="s">
         <v>2295</v>
@@ -39988,7 +40564,7 @@
         <v>85</v>
       </c>
       <c r="C2294">
-        <v>7390</v>
+        <v>6850</v>
       </c>
       <c r="D2294" t="s">
         <v>2296</v>
@@ -40002,7 +40578,7 @@
         <v>86</v>
       </c>
       <c r="C2295">
-        <v>7350</v>
+        <v>6800</v>
       </c>
       <c r="D2295" t="s">
         <v>2297</v>
@@ -40016,7 +40592,7 @@
         <v>87</v>
       </c>
       <c r="C2296">
-        <v>7260</v>
+        <v>6700</v>
       </c>
       <c r="D2296" t="s">
         <v>2298</v>
@@ -40030,7 +40606,7 @@
         <v>88</v>
       </c>
       <c r="C2297">
-        <v>7120</v>
+        <v>6620</v>
       </c>
       <c r="D2297" t="s">
         <v>2299</v>
@@ -40044,7 +40620,7 @@
         <v>89</v>
       </c>
       <c r="C2298">
-        <v>6950</v>
+        <v>6540</v>
       </c>
       <c r="D2298" t="s">
         <v>2300</v>
@@ -40058,7 +40634,7 @@
         <v>90</v>
       </c>
       <c r="C2299">
-        <v>6770</v>
+        <v>6460</v>
       </c>
       <c r="D2299" t="s">
         <v>2301</v>
@@ -40072,7 +40648,7 @@
         <v>91</v>
       </c>
       <c r="C2300">
-        <v>6600</v>
+        <v>6300</v>
       </c>
       <c r="D2300" t="s">
         <v>2302</v>
@@ -40086,7 +40662,7 @@
         <v>92</v>
       </c>
       <c r="C2301">
-        <v>6440</v>
+        <v>6170</v>
       </c>
       <c r="D2301" t="s">
         <v>2303</v>
@@ -40100,7 +40676,7 @@
         <v>93</v>
       </c>
       <c r="C2302">
-        <v>6290</v>
+        <v>6070</v>
       </c>
       <c r="D2302" t="s">
         <v>2304</v>
@@ -40114,7 +40690,7 @@
         <v>94</v>
       </c>
       <c r="C2303">
-        <v>6140</v>
+        <v>5920</v>
       </c>
       <c r="D2303" t="s">
         <v>2305</v>
@@ -40128,7 +40704,7 @@
         <v>95</v>
       </c>
       <c r="C2304">
-        <v>6010</v>
+        <v>5830</v>
       </c>
       <c r="D2304" t="s">
         <v>2306</v>
@@ -40142,7 +40718,7 @@
         <v>96</v>
       </c>
       <c r="C2305">
-        <v>5880</v>
+        <v>5720</v>
       </c>
       <c r="D2305" t="s">
         <v>2307</v>
@@ -40156,7 +40732,7 @@
         <v>1</v>
       </c>
       <c r="C2306">
-        <v>5760</v>
+        <v>5600</v>
       </c>
       <c r="D2306" t="s">
         <v>2308</v>
@@ -40170,7 +40746,7 @@
         <v>2</v>
       </c>
       <c r="C2307">
-        <v>5660</v>
+        <v>5550</v>
       </c>
       <c r="D2307" t="s">
         <v>2309</v>
@@ -40184,7 +40760,7 @@
         <v>3</v>
       </c>
       <c r="C2308">
-        <v>5580</v>
+        <v>5490</v>
       </c>
       <c r="D2308" t="s">
         <v>2310</v>
@@ -40198,7 +40774,7 @@
         <v>4</v>
       </c>
       <c r="C2309">
-        <v>5520</v>
+        <v>5390</v>
       </c>
       <c r="D2309" t="s">
         <v>2311</v>
@@ -40212,7 +40788,7 @@
         <v>5</v>
       </c>
       <c r="C2310">
-        <v>5470</v>
+        <v>5310</v>
       </c>
       <c r="D2310" t="s">
         <v>2312</v>
@@ -40226,7 +40802,7 @@
         <v>6</v>
       </c>
       <c r="C2311">
-        <v>5430</v>
+        <v>5240</v>
       </c>
       <c r="D2311" t="s">
         <v>2313</v>
@@ -40240,7 +40816,7 @@
         <v>7</v>
       </c>
       <c r="C2312">
-        <v>5390</v>
+        <v>5190</v>
       </c>
       <c r="D2312" t="s">
         <v>2314</v>
@@ -40254,7 +40830,7 @@
         <v>8</v>
       </c>
       <c r="C2313">
-        <v>5350</v>
+        <v>5150</v>
       </c>
       <c r="D2313" t="s">
         <v>2315</v>
@@ -40268,7 +40844,7 @@
         <v>9</v>
       </c>
       <c r="C2314">
-        <v>5310</v>
+        <v>5120</v>
       </c>
       <c r="D2314" t="s">
         <v>2316</v>
@@ -40282,7 +40858,7 @@
         <v>10</v>
       </c>
       <c r="C2315">
-        <v>5280</v>
+        <v>5110</v>
       </c>
       <c r="D2315" t="s">
         <v>2317</v>
@@ -40296,7 +40872,7 @@
         <v>11</v>
       </c>
       <c r="C2316">
-        <v>5250</v>
+        <v>5100</v>
       </c>
       <c r="D2316" t="s">
         <v>2318</v>
@@ -40310,7 +40886,7 @@
         <v>12</v>
       </c>
       <c r="C2317">
-        <v>5240</v>
+        <v>5090</v>
       </c>
       <c r="D2317" t="s">
         <v>2319</v>
@@ -40324,7 +40900,7 @@
         <v>13</v>
       </c>
       <c r="C2318">
-        <v>5230</v>
+        <v>5080</v>
       </c>
       <c r="D2318" t="s">
         <v>2320</v>
@@ -40338,7 +40914,7 @@
         <v>14</v>
       </c>
       <c r="C2319">
-        <v>5220</v>
+        <v>5070</v>
       </c>
       <c r="D2319" t="s">
         <v>2321</v>
@@ -40352,7 +40928,7 @@
         <v>15</v>
       </c>
       <c r="C2320">
-        <v>5220</v>
+        <v>5070</v>
       </c>
       <c r="D2320" t="s">
         <v>2322</v>
@@ -40366,7 +40942,7 @@
         <v>16</v>
       </c>
       <c r="C2321">
-        <v>5230</v>
+        <v>5050</v>
       </c>
       <c r="D2321" t="s">
         <v>2323</v>
@@ -40380,7 +40956,7 @@
         <v>17</v>
       </c>
       <c r="C2322">
-        <v>5230</v>
+        <v>5070</v>
       </c>
       <c r="D2322" t="s">
         <v>2324</v>
@@ -40394,7 +40970,7 @@
         <v>18</v>
       </c>
       <c r="C2323">
-        <v>5240</v>
+        <v>5070</v>
       </c>
       <c r="D2323" t="s">
         <v>2325</v>
@@ -40408,7 +40984,7 @@
         <v>19</v>
       </c>
       <c r="C2324">
-        <v>5250</v>
+        <v>5090</v>
       </c>
       <c r="D2324" t="s">
         <v>2326</v>
@@ -40422,7 +40998,7 @@
         <v>20</v>
       </c>
       <c r="C2325">
-        <v>5270</v>
+        <v>5110</v>
       </c>
       <c r="D2325" t="s">
         <v>2327</v>
@@ -40436,7 +41012,7 @@
         <v>21</v>
       </c>
       <c r="C2326">
-        <v>5290</v>
+        <v>5150</v>
       </c>
       <c r="D2326" t="s">
         <v>2328</v>
@@ -40450,7 +41026,7 @@
         <v>22</v>
       </c>
       <c r="C2327">
-        <v>5310</v>
+        <v>5180</v>
       </c>
       <c r="D2327" t="s">
         <v>2329</v>
@@ -40464,7 +41040,7 @@
         <v>23</v>
       </c>
       <c r="C2328">
-        <v>5350</v>
+        <v>5230</v>
       </c>
       <c r="D2328" t="s">
         <v>2330</v>
@@ -40478,7 +41054,7 @@
         <v>24</v>
       </c>
       <c r="C2329">
-        <v>5410</v>
+        <v>5280</v>
       </c>
       <c r="D2329" t="s">
         <v>2331</v>
@@ -40492,7 +41068,7 @@
         <v>25</v>
       </c>
       <c r="C2330">
-        <v>5470</v>
+        <v>5330</v>
       </c>
       <c r="D2330" t="s">
         <v>2332</v>
@@ -40506,7 +41082,7 @@
         <v>26</v>
       </c>
       <c r="C2331">
-        <v>5550</v>
+        <v>5400</v>
       </c>
       <c r="D2331" t="s">
         <v>2333</v>
@@ -40520,7 +41096,7 @@
         <v>27</v>
       </c>
       <c r="C2332">
-        <v>5660</v>
+        <v>5460</v>
       </c>
       <c r="D2332" t="s">
         <v>2334</v>
@@ -40534,7 +41110,7 @@
         <v>28</v>
       </c>
       <c r="C2333">
-        <v>5780</v>
+        <v>5540</v>
       </c>
       <c r="D2333" t="s">
         <v>2335</v>
@@ -40548,7 +41124,7 @@
         <v>29</v>
       </c>
       <c r="C2334">
-        <v>5910</v>
+        <v>5610</v>
       </c>
       <c r="D2334" t="s">
         <v>2336</v>
@@ -40562,7 +41138,7 @@
         <v>30</v>
       </c>
       <c r="C2335">
-        <v>6030</v>
+        <v>5690</v>
       </c>
       <c r="D2335" t="s">
         <v>2337</v>
@@ -40576,7 +41152,7 @@
         <v>31</v>
       </c>
       <c r="C2336">
-        <v>6130</v>
+        <v>5760</v>
       </c>
       <c r="D2336" t="s">
         <v>2338</v>
@@ -40590,7 +41166,7 @@
         <v>32</v>
       </c>
       <c r="C2337">
-        <v>6200</v>
+        <v>5820</v>
       </c>
       <c r="D2337" t="s">
         <v>2339</v>
@@ -40604,7 +41180,7 @@
         <v>33</v>
       </c>
       <c r="C2338">
-        <v>6240</v>
+        <v>5870</v>
       </c>
       <c r="D2338" t="s">
         <v>2340</v>
@@ -40618,7 +41194,7 @@
         <v>34</v>
       </c>
       <c r="C2339">
-        <v>6250</v>
+        <v>5900</v>
       </c>
       <c r="D2339" t="s">
         <v>2341</v>
@@ -40632,7 +41208,7 @@
         <v>35</v>
       </c>
       <c r="C2340">
-        <v>6220</v>
+        <v>5900</v>
       </c>
       <c r="D2340" t="s">
         <v>2342</v>
@@ -40646,7 +41222,7 @@
         <v>36</v>
       </c>
       <c r="C2341">
-        <v>6150</v>
+        <v>5890</v>
       </c>
       <c r="D2341" t="s">
         <v>2343</v>
@@ -40660,7 +41236,7 @@
         <v>37</v>
       </c>
       <c r="C2342">
-        <v>6040</v>
+        <v>5850</v>
       </c>
       <c r="D2342" t="s">
         <v>2344</v>
@@ -40674,7 +41250,7 @@
         <v>38</v>
       </c>
       <c r="C2343">
-        <v>5940</v>
+        <v>5780</v>
       </c>
       <c r="D2343" t="s">
         <v>2345</v>
@@ -40688,7 +41264,7 @@
         <v>39</v>
       </c>
       <c r="C2344">
-        <v>5840</v>
+        <v>5700</v>
       </c>
       <c r="D2344" t="s">
         <v>2346</v>
@@ -40702,7 +41278,7 @@
         <v>40</v>
       </c>
       <c r="C2345">
-        <v>5750</v>
+        <v>5610</v>
       </c>
       <c r="D2345" t="s">
         <v>2347</v>
@@ -40716,7 +41292,7 @@
         <v>41</v>
       </c>
       <c r="C2346">
-        <v>5660</v>
+        <v>5520</v>
       </c>
       <c r="D2346" t="s">
         <v>2348</v>
@@ -40730,7 +41306,7 @@
         <v>42</v>
       </c>
       <c r="C2347">
-        <v>5580</v>
+        <v>5440</v>
       </c>
       <c r="D2347" t="s">
         <v>2349</v>
@@ -40744,7 +41320,7 @@
         <v>43</v>
       </c>
       <c r="C2348">
-        <v>5510</v>
+        <v>5370</v>
       </c>
       <c r="D2348" t="s">
         <v>2350</v>
@@ -40758,7 +41334,7 @@
         <v>44</v>
       </c>
       <c r="C2349">
-        <v>5440</v>
+        <v>5320</v>
       </c>
       <c r="D2349" t="s">
         <v>2351</v>
@@ -40772,7 +41348,7 @@
         <v>45</v>
       </c>
       <c r="C2350">
-        <v>5390</v>
+        <v>5290</v>
       </c>
       <c r="D2350" t="s">
         <v>2352</v>
@@ -40786,7 +41362,7 @@
         <v>46</v>
       </c>
       <c r="C2351">
-        <v>5340</v>
+        <v>5280</v>
       </c>
       <c r="D2351" t="s">
         <v>2353</v>
@@ -40800,7 +41376,7 @@
         <v>47</v>
       </c>
       <c r="C2352">
-        <v>5310</v>
+        <v>5280</v>
       </c>
       <c r="D2352" t="s">
         <v>2354</v>
@@ -40814,7 +41390,7 @@
         <v>48</v>
       </c>
       <c r="C2353">
-        <v>5290</v>
+        <v>5300</v>
       </c>
       <c r="D2353" t="s">
         <v>2355</v>
@@ -40828,7 +41404,7 @@
         <v>49</v>
       </c>
       <c r="C2354">
-        <v>5290</v>
+        <v>5320</v>
       </c>
       <c r="D2354" t="s">
         <v>2356</v>
@@ -40842,7 +41418,7 @@
         <v>50</v>
       </c>
       <c r="C2355">
-        <v>5300</v>
+        <v>5330</v>
       </c>
       <c r="D2355" t="s">
         <v>2357</v>
@@ -40856,7 +41432,7 @@
         <v>51</v>
       </c>
       <c r="C2356">
-        <v>5330</v>
+        <v>5340</v>
       </c>
       <c r="D2356" t="s">
         <v>2358</v>
@@ -40870,7 +41446,7 @@
         <v>52</v>
       </c>
       <c r="C2357">
-        <v>5380</v>
+        <v>5350</v>
       </c>
       <c r="D2357" t="s">
         <v>2359</v>
@@ -40884,7 +41460,7 @@
         <v>53</v>
       </c>
       <c r="C2358">
-        <v>5450</v>
+        <v>5360</v>
       </c>
       <c r="D2358" t="s">
         <v>2360</v>
@@ -40898,7 +41474,7 @@
         <v>54</v>
       </c>
       <c r="C2359">
-        <v>5500</v>
+        <v>5360</v>
       </c>
       <c r="D2359" t="s">
         <v>2361</v>
@@ -40912,7 +41488,7 @@
         <v>55</v>
       </c>
       <c r="C2360">
-        <v>5540</v>
+        <v>5380</v>
       </c>
       <c r="D2360" t="s">
         <v>2362</v>
@@ -40926,7 +41502,7 @@
         <v>56</v>
       </c>
       <c r="C2361">
-        <v>5560</v>
+        <v>5400</v>
       </c>
       <c r="D2361" t="s">
         <v>2363</v>
@@ -40940,7 +41516,7 @@
         <v>57</v>
       </c>
       <c r="C2362">
-        <v>5570</v>
+        <v>5430</v>
       </c>
       <c r="D2362" t="s">
         <v>2364</v>
@@ -40954,7 +41530,7 @@
         <v>58</v>
       </c>
       <c r="C2363">
-        <v>5600</v>
+        <v>5470</v>
       </c>
       <c r="D2363" t="s">
         <v>2365</v>
@@ -40968,7 +41544,7 @@
         <v>59</v>
       </c>
       <c r="C2364">
-        <v>5650</v>
+        <v>5520</v>
       </c>
       <c r="D2364" t="s">
         <v>2366</v>
@@ -40982,7 +41558,7 @@
         <v>60</v>
       </c>
       <c r="C2365">
-        <v>5730</v>
+        <v>5580</v>
       </c>
       <c r="D2365" t="s">
         <v>2367</v>
@@ -40996,7 +41572,7 @@
         <v>61</v>
       </c>
       <c r="C2366">
-        <v>5820</v>
+        <v>5640</v>
       </c>
       <c r="D2366" t="s">
         <v>2368</v>
@@ -41010,7 +41586,7 @@
         <v>62</v>
       </c>
       <c r="C2367">
-        <v>5910</v>
+        <v>5690</v>
       </c>
       <c r="D2367" t="s">
         <v>2369</v>
@@ -41024,7 +41600,7 @@
         <v>63</v>
       </c>
       <c r="C2368">
-        <v>6000</v>
+        <v>5750</v>
       </c>
       <c r="D2368" t="s">
         <v>2370</v>
@@ -41038,7 +41614,7 @@
         <v>64</v>
       </c>
       <c r="C2369">
-        <v>6070</v>
+        <v>5800</v>
       </c>
       <c r="D2369" t="s">
         <v>2371</v>
@@ -41052,7 +41628,7 @@
         <v>65</v>
       </c>
       <c r="C2370">
-        <v>6140</v>
+        <v>5850</v>
       </c>
       <c r="D2370" t="s">
         <v>2372</v>
@@ -41066,7 +41642,7 @@
         <v>66</v>
       </c>
       <c r="C2371">
-        <v>6220</v>
+        <v>5910</v>
       </c>
       <c r="D2371" t="s">
         <v>2373</v>
@@ -41080,7 +41656,7 @@
         <v>67</v>
       </c>
       <c r="C2372">
-        <v>6300</v>
+        <v>5970</v>
       </c>
       <c r="D2372" t="s">
         <v>2374</v>
@@ -41094,7 +41670,7 @@
         <v>68</v>
       </c>
       <c r="C2373">
-        <v>6390</v>
+        <v>6040</v>
       </c>
       <c r="D2373" t="s">
         <v>2375</v>
@@ -41108,7 +41684,7 @@
         <v>69</v>
       </c>
       <c r="C2374">
-        <v>6480</v>
+        <v>6120</v>
       </c>
       <c r="D2374" t="s">
         <v>2376</v>
@@ -41122,7 +41698,7 @@
         <v>70</v>
       </c>
       <c r="C2375">
-        <v>6590</v>
+        <v>6190</v>
       </c>
       <c r="D2375" t="s">
         <v>2377</v>
@@ -41136,7 +41712,7 @@
         <v>71</v>
       </c>
       <c r="C2376">
-        <v>6700</v>
+        <v>6260</v>
       </c>
       <c r="D2376" t="s">
         <v>2378</v>
@@ -41150,7 +41726,7 @@
         <v>72</v>
       </c>
       <c r="C2377">
-        <v>6820</v>
+        <v>6330</v>
       </c>
       <c r="D2377" t="s">
         <v>2379</v>
@@ -41164,7 +41740,7 @@
         <v>73</v>
       </c>
       <c r="C2378">
-        <v>6940</v>
+        <v>6390</v>
       </c>
       <c r="D2378" t="s">
         <v>2380</v>
@@ -41178,7 +41754,7 @@
         <v>74</v>
       </c>
       <c r="C2379">
-        <v>7040</v>
+        <v>6450</v>
       </c>
       <c r="D2379" t="s">
         <v>2381</v>
@@ -41192,7 +41768,7 @@
         <v>75</v>
       </c>
       <c r="C2380">
-        <v>7110</v>
+        <v>6520</v>
       </c>
       <c r="D2380" t="s">
         <v>2382</v>
@@ -41206,7 +41782,7 @@
         <v>76</v>
       </c>
       <c r="C2381">
-        <v>7160</v>
+        <v>6600</v>
       </c>
       <c r="D2381" t="s">
         <v>2383</v>
@@ -41220,7 +41796,7 @@
         <v>77</v>
       </c>
       <c r="C2382">
-        <v>7190</v>
+        <v>6700</v>
       </c>
       <c r="D2382" t="s">
         <v>2384</v>
@@ -41234,7 +41810,7 @@
         <v>78</v>
       </c>
       <c r="C2383">
-        <v>7230</v>
+        <v>6790</v>
       </c>
       <c r="D2383" t="s">
         <v>2385</v>
@@ -41248,7 +41824,7 @@
         <v>79</v>
       </c>
       <c r="C2384">
-        <v>7260</v>
+        <v>6860</v>
       </c>
       <c r="D2384" t="s">
         <v>2386</v>
@@ -41262,7 +41838,7 @@
         <v>80</v>
       </c>
       <c r="C2385">
-        <v>7300</v>
+        <v>6910</v>
       </c>
       <c r="D2385" t="s">
         <v>2387</v>
@@ -41276,7 +41852,7 @@
         <v>81</v>
       </c>
       <c r="C2386">
-        <v>7350</v>
+        <v>6960</v>
       </c>
       <c r="D2386" t="s">
         <v>2388</v>
@@ -41290,7 +41866,7 @@
         <v>82</v>
       </c>
       <c r="C2387">
-        <v>7380</v>
+        <v>6980</v>
       </c>
       <c r="D2387" t="s">
         <v>2389</v>
@@ -41304,7 +41880,7 @@
         <v>83</v>
       </c>
       <c r="C2388">
-        <v>7400</v>
+        <v>6980</v>
       </c>
       <c r="D2388" t="s">
         <v>2390</v>
@@ -41318,7 +41894,7 @@
         <v>84</v>
       </c>
       <c r="C2389">
-        <v>7400</v>
+        <v>7000</v>
       </c>
       <c r="D2389" t="s">
         <v>2391</v>
@@ -41332,7 +41908,7 @@
         <v>85</v>
       </c>
       <c r="C2390">
-        <v>7380</v>
+        <v>7000</v>
       </c>
       <c r="D2390" t="s">
         <v>2392</v>
@@ -41346,7 +41922,7 @@
         <v>86</v>
       </c>
       <c r="C2391">
-        <v>7330</v>
+        <v>7000</v>
       </c>
       <c r="D2391" t="s">
         <v>2393</v>
@@ -41360,7 +41936,7 @@
         <v>87</v>
       </c>
       <c r="C2392">
-        <v>7240</v>
+        <v>6970</v>
       </c>
       <c r="D2392" t="s">
         <v>2394</v>
@@ -41374,7 +41950,7 @@
         <v>88</v>
       </c>
       <c r="C2393">
-        <v>7120</v>
+        <v>6910</v>
       </c>
       <c r="D2393" t="s">
         <v>2395</v>
@@ -41388,7 +41964,7 @@
         <v>89</v>
       </c>
       <c r="C2394">
-        <v>6960</v>
+        <v>6790</v>
       </c>
       <c r="D2394" t="s">
         <v>2396</v>
@@ -41402,7 +41978,7 @@
         <v>90</v>
       </c>
       <c r="C2395">
-        <v>6790</v>
+        <v>6720</v>
       </c>
       <c r="D2395" t="s">
         <v>2397</v>
@@ -41416,7 +41992,7 @@
         <v>91</v>
       </c>
       <c r="C2396">
-        <v>6630</v>
+        <v>6600</v>
       </c>
       <c r="D2396" t="s">
         <v>2398</v>
@@ -41430,7 +42006,7 @@
         <v>92</v>
       </c>
       <c r="C2397">
-        <v>6470</v>
+        <v>6420</v>
       </c>
       <c r="D2397" t="s">
         <v>2399</v>
@@ -41444,7 +42020,7 @@
         <v>93</v>
       </c>
       <c r="C2398">
-        <v>6320</v>
+        <v>6180</v>
       </c>
       <c r="D2398" t="s">
         <v>2400</v>
@@ -41458,7 +42034,7 @@
         <v>94</v>
       </c>
       <c r="C2399">
-        <v>6170</v>
+        <v>6020</v>
       </c>
       <c r="D2399" t="s">
         <v>2401</v>
@@ -41472,7 +42048,7 @@
         <v>95</v>
       </c>
       <c r="C2400">
-        <v>6030</v>
+        <v>5930</v>
       </c>
       <c r="D2400" t="s">
         <v>2402</v>
@@ -41486,7 +42062,7 @@
         <v>96</v>
       </c>
       <c r="C2401">
-        <v>5900</v>
+        <v>5820</v>
       </c>
       <c r="D2401" t="s">
         <v>2403</v>
@@ -41500,7 +42076,7 @@
         <v>1</v>
       </c>
       <c r="C2402">
-        <v>5640</v>
+        <v>5540</v>
       </c>
       <c r="D2402" t="s">
         <v>2404</v>
@@ -41514,7 +42090,7 @@
         <v>2</v>
       </c>
       <c r="C2403">
-        <v>5590</v>
+        <v>5490</v>
       </c>
       <c r="D2403" t="s">
         <v>2405</v>
@@ -41528,7 +42104,7 @@
         <v>3</v>
       </c>
       <c r="C2404">
-        <v>5540</v>
+        <v>5440</v>
       </c>
       <c r="D2404" t="s">
         <v>2406</v>
@@ -41542,7 +42118,7 @@
         <v>4</v>
       </c>
       <c r="C2405">
-        <v>5470</v>
+        <v>5370</v>
       </c>
       <c r="D2405" t="s">
         <v>2407</v>
@@ -41556,7 +42132,7 @@
         <v>5</v>
       </c>
       <c r="C2406">
-        <v>5400</v>
+        <v>5300</v>
       </c>
       <c r="D2406" t="s">
         <v>2408</v>
@@ -41570,7 +42146,7 @@
         <v>6</v>
       </c>
       <c r="C2407">
-        <v>5340</v>
+        <v>5240</v>
       </c>
       <c r="D2407" t="s">
         <v>2409</v>
@@ -41584,7 +42160,7 @@
         <v>7</v>
       </c>
       <c r="C2408">
-        <v>5280</v>
+        <v>5180</v>
       </c>
       <c r="D2408" t="s">
         <v>2410</v>
@@ -41598,7 +42174,7 @@
         <v>8</v>
       </c>
       <c r="C2409">
-        <v>5240</v>
+        <v>5140</v>
       </c>
       <c r="D2409" t="s">
         <v>2411</v>
@@ -41612,7 +42188,7 @@
         <v>9</v>
       </c>
       <c r="C2410">
-        <v>5210</v>
+        <v>5110</v>
       </c>
       <c r="D2410" t="s">
         <v>2412</v>
@@ -41626,7 +42202,7 @@
         <v>10</v>
       </c>
       <c r="C2411">
-        <v>5190</v>
+        <v>5090</v>
       </c>
       <c r="D2411" t="s">
         <v>2413</v>
@@ -41640,7 +42216,7 @@
         <v>11</v>
       </c>
       <c r="C2412">
-        <v>5170</v>
+        <v>5070</v>
       </c>
       <c r="D2412" t="s">
         <v>2414</v>
@@ -41654,7 +42230,7 @@
         <v>12</v>
       </c>
       <c r="C2413">
-        <v>5160</v>
+        <v>5060</v>
       </c>
       <c r="D2413" t="s">
         <v>2415</v>
@@ -41668,7 +42244,7 @@
         <v>13</v>
       </c>
       <c r="C2414">
-        <v>5160</v>
+        <v>5060</v>
       </c>
       <c r="D2414" t="s">
         <v>2416</v>
@@ -41682,7 +42258,7 @@
         <v>14</v>
       </c>
       <c r="C2415">
-        <v>5160</v>
+        <v>5060</v>
       </c>
       <c r="D2415" t="s">
         <v>2417</v>
@@ -41696,7 +42272,7 @@
         <v>15</v>
       </c>
       <c r="C2416">
-        <v>5160</v>
+        <v>5060</v>
       </c>
       <c r="D2416" t="s">
         <v>2418</v>
@@ -41710,7 +42286,7 @@
         <v>16</v>
       </c>
       <c r="C2417">
-        <v>5160</v>
+        <v>5060</v>
       </c>
       <c r="D2417" t="s">
         <v>2419</v>
@@ -41724,7 +42300,7 @@
         <v>17</v>
       </c>
       <c r="C2418">
-        <v>5170</v>
+        <v>5070</v>
       </c>
       <c r="D2418" t="s">
         <v>2420</v>
@@ -41738,7 +42314,7 @@
         <v>18</v>
       </c>
       <c r="C2419">
-        <v>5170</v>
+        <v>5070</v>
       </c>
       <c r="D2419" t="s">
         <v>2421</v>
@@ -41752,7 +42328,7 @@
         <v>19</v>
       </c>
       <c r="C2420">
-        <v>5190</v>
+        <v>5090</v>
       </c>
       <c r="D2420" t="s">
         <v>2422</v>
@@ -41766,7 +42342,7 @@
         <v>20</v>
       </c>
       <c r="C2421">
-        <v>5210</v>
+        <v>5110</v>
       </c>
       <c r="D2421" t="s">
         <v>2423</v>
@@ -41780,7 +42356,7 @@
         <v>21</v>
       </c>
       <c r="C2422">
-        <v>5240</v>
+        <v>5140</v>
       </c>
       <c r="D2422" t="s">
         <v>2424</v>
@@ -41794,7 +42370,7 @@
         <v>22</v>
       </c>
       <c r="C2423">
-        <v>5280</v>
+        <v>5180</v>
       </c>
       <c r="D2423" t="s">
         <v>2425</v>
@@ -41808,7 +42384,7 @@
         <v>23</v>
       </c>
       <c r="C2424">
-        <v>5330</v>
+        <v>5230</v>
       </c>
       <c r="D2424" t="s">
         <v>2426</v>
@@ -41822,7 +42398,7 @@
         <v>24</v>
       </c>
       <c r="C2425">
-        <v>5390</v>
+        <v>5290</v>
       </c>
       <c r="D2425" t="s">
         <v>2427</v>
@@ -41836,7 +42412,7 @@
         <v>25</v>
       </c>
       <c r="C2426">
-        <v>5460</v>
+        <v>5360</v>
       </c>
       <c r="D2426" t="s">
         <v>2428</v>
@@ -41850,7 +42426,7 @@
         <v>26</v>
       </c>
       <c r="C2427">
-        <v>5530</v>
+        <v>5430</v>
       </c>
       <c r="D2427" t="s">
         <v>2429</v>
@@ -41864,7 +42440,7 @@
         <v>27</v>
       </c>
       <c r="C2428">
-        <v>5620</v>
+        <v>5520</v>
       </c>
       <c r="D2428" t="s">
         <v>2430</v>
@@ -41878,7 +42454,7 @@
         <v>28</v>
       </c>
       <c r="C2429">
-        <v>5710</v>
+        <v>5610</v>
       </c>
       <c r="D2429" t="s">
         <v>2431</v>
@@ -41892,7 +42468,7 @@
         <v>29</v>
       </c>
       <c r="C2430">
-        <v>5800</v>
+        <v>5700</v>
       </c>
       <c r="D2430" t="s">
         <v>2432</v>
@@ -41906,7 +42482,7 @@
         <v>30</v>
       </c>
       <c r="C2431">
-        <v>5890</v>
+        <v>5790</v>
       </c>
       <c r="D2431" t="s">
         <v>2433</v>
@@ -41920,7 +42496,7 @@
         <v>31</v>
       </c>
       <c r="C2432">
-        <v>5970</v>
+        <v>5870</v>
       </c>
       <c r="D2432" t="s">
         <v>2434</v>
@@ -41934,7 +42510,7 @@
         <v>32</v>
       </c>
       <c r="C2433">
-        <v>6040</v>
+        <v>5940</v>
       </c>
       <c r="D2433" t="s">
         <v>2435</v>
@@ -41948,7 +42524,7 @@
         <v>33</v>
       </c>
       <c r="C2434">
-        <v>6080</v>
+        <v>5980</v>
       </c>
       <c r="D2434" t="s">
         <v>2436</v>
@@ -41962,7 +42538,7 @@
         <v>34</v>
       </c>
       <c r="C2435">
-        <v>6090</v>
+        <v>5990</v>
       </c>
       <c r="D2435" t="s">
         <v>2437</v>
@@ -41976,7 +42552,7 @@
         <v>35</v>
       </c>
       <c r="C2436">
-        <v>6070</v>
+        <v>5970</v>
       </c>
       <c r="D2436" t="s">
         <v>2438</v>
@@ -41990,7 +42566,7 @@
         <v>36</v>
       </c>
       <c r="C2437">
-        <v>6010</v>
+        <v>5910</v>
       </c>
       <c r="D2437" t="s">
         <v>2439</v>
@@ -42004,7 +42580,7 @@
         <v>37</v>
       </c>
       <c r="C2438">
-        <v>5930</v>
+        <v>5830</v>
       </c>
       <c r="D2438" t="s">
         <v>2440</v>
@@ -42018,7 +42594,7 @@
         <v>38</v>
       </c>
       <c r="C2439">
-        <v>5830</v>
+        <v>5730</v>
       </c>
       <c r="D2439" t="s">
         <v>2441</v>
@@ -42032,7 +42608,7 @@
         <v>39</v>
       </c>
       <c r="C2440">
-        <v>5700</v>
+        <v>5600</v>
       </c>
       <c r="D2440" t="s">
         <v>2442</v>
@@ -42046,7 +42622,7 @@
         <v>40</v>
       </c>
       <c r="C2441">
-        <v>5580</v>
+        <v>5480</v>
       </c>
       <c r="D2441" t="s">
         <v>2443</v>
@@ -42060,7 +42636,7 @@
         <v>41</v>
       </c>
       <c r="C2442">
-        <v>5460</v>
+        <v>5360</v>
       </c>
       <c r="D2442" t="s">
         <v>2444</v>
@@ -42074,7 +42650,7 @@
         <v>42</v>
       </c>
       <c r="C2443">
-        <v>5350</v>
+        <v>5250</v>
       </c>
       <c r="D2443" t="s">
         <v>2445</v>
@@ -42088,7 +42664,7 @@
         <v>43</v>
       </c>
       <c r="C2444">
-        <v>5260</v>
+        <v>5160</v>
       </c>
       <c r="D2444" t="s">
         <v>2446</v>
@@ -42102,7 +42678,7 @@
         <v>44</v>
       </c>
       <c r="C2445">
-        <v>5210</v>
+        <v>5110</v>
       </c>
       <c r="D2445" t="s">
         <v>2447</v>
@@ -42116,7 +42692,7 @@
         <v>45</v>
       </c>
       <c r="C2446">
-        <v>5170</v>
+        <v>5070</v>
       </c>
       <c r="D2446" t="s">
         <v>2448</v>
@@ -42130,7 +42706,7 @@
         <v>46</v>
       </c>
       <c r="C2447">
-        <v>5170</v>
+        <v>5070</v>
       </c>
       <c r="D2447" t="s">
         <v>2449</v>
@@ -42144,7 +42720,7 @@
         <v>47</v>
       </c>
       <c r="C2448">
-        <v>5180</v>
+        <v>5080</v>
       </c>
       <c r="D2448" t="s">
         <v>2450</v>
@@ -42158,7 +42734,7 @@
         <v>48</v>
       </c>
       <c r="C2449">
-        <v>5200</v>
+        <v>5100</v>
       </c>
       <c r="D2449" t="s">
         <v>2451</v>
@@ -42172,7 +42748,7 @@
         <v>49</v>
       </c>
       <c r="C2450">
-        <v>5230</v>
+        <v>5130</v>
       </c>
       <c r="D2450" t="s">
         <v>2452</v>
@@ -42186,7 +42762,7 @@
         <v>50</v>
       </c>
       <c r="C2451">
-        <v>5250</v>
+        <v>5150</v>
       </c>
       <c r="D2451" t="s">
         <v>2453</v>
@@ -42200,7 +42776,7 @@
         <v>51</v>
       </c>
       <c r="C2452">
-        <v>5270</v>
+        <v>5170</v>
       </c>
       <c r="D2452" t="s">
         <v>2454</v>
@@ -42214,7 +42790,7 @@
         <v>52</v>
       </c>
       <c r="C2453">
-        <v>5280</v>
+        <v>5180</v>
       </c>
       <c r="D2453" t="s">
         <v>2455</v>
@@ -42228,7 +42804,7 @@
         <v>53</v>
       </c>
       <c r="C2454">
-        <v>5300</v>
+        <v>5200</v>
       </c>
       <c r="D2454" t="s">
         <v>2456</v>
@@ -42242,7 +42818,7 @@
         <v>54</v>
       </c>
       <c r="C2455">
-        <v>5310</v>
+        <v>5210</v>
       </c>
       <c r="D2455" t="s">
         <v>2457</v>
@@ -42256,7 +42832,7 @@
         <v>55</v>
       </c>
       <c r="C2456">
-        <v>5330</v>
+        <v>5230</v>
       </c>
       <c r="D2456" t="s">
         <v>2458</v>
@@ -42270,7 +42846,7 @@
         <v>56</v>
       </c>
       <c r="C2457">
-        <v>5350</v>
+        <v>5250</v>
       </c>
       <c r="D2457" t="s">
         <v>2459</v>
@@ -42284,7 +42860,7 @@
         <v>57</v>
       </c>
       <c r="C2458">
-        <v>5390</v>
+        <v>5290</v>
       </c>
       <c r="D2458" t="s">
         <v>2460</v>
@@ -42298,7 +42874,7 @@
         <v>58</v>
       </c>
       <c r="C2459">
-        <v>5440</v>
+        <v>5340</v>
       </c>
       <c r="D2459" t="s">
         <v>2461</v>
@@ -42312,7 +42888,7 @@
         <v>59</v>
       </c>
       <c r="C2460">
-        <v>5500</v>
+        <v>5400</v>
       </c>
       <c r="D2460" t="s">
         <v>2462</v>
@@ -42326,7 +42902,7 @@
         <v>60</v>
       </c>
       <c r="C2461">
-        <v>5560</v>
+        <v>5460</v>
       </c>
       <c r="D2461" t="s">
         <v>2463</v>
@@ -42340,7 +42916,7 @@
         <v>61</v>
       </c>
       <c r="C2462">
-        <v>5620</v>
+        <v>5520</v>
       </c>
       <c r="D2462" t="s">
         <v>2464</v>
@@ -42354,7 +42930,7 @@
         <v>62</v>
       </c>
       <c r="C2463">
-        <v>5680</v>
+        <v>5580</v>
       </c>
       <c r="D2463" t="s">
         <v>2465</v>
@@ -42368,7 +42944,7 @@
         <v>63</v>
       </c>
       <c r="C2464">
-        <v>5740</v>
+        <v>5640</v>
       </c>
       <c r="D2464" t="s">
         <v>2466</v>
@@ -42382,7 +42958,7 @@
         <v>64</v>
       </c>
       <c r="C2465">
-        <v>5810</v>
+        <v>5710</v>
       </c>
       <c r="D2465" t="s">
         <v>2467</v>
@@ -42396,7 +42972,7 @@
         <v>65</v>
       </c>
       <c r="C2466">
-        <v>5870</v>
+        <v>5770</v>
       </c>
       <c r="D2466" t="s">
         <v>2468</v>
@@ -42410,7 +42986,7 @@
         <v>66</v>
       </c>
       <c r="C2467">
-        <v>5950</v>
+        <v>5850</v>
       </c>
       <c r="D2467" t="s">
         <v>2469</v>
@@ -42424,7 +43000,7 @@
         <v>67</v>
       </c>
       <c r="C2468">
-        <v>6040</v>
+        <v>5940</v>
       </c>
       <c r="D2468" t="s">
         <v>2470</v>
@@ -42438,7 +43014,7 @@
         <v>68</v>
       </c>
       <c r="C2469">
-        <v>6130</v>
+        <v>6030</v>
       </c>
       <c r="D2469" t="s">
         <v>2471</v>
@@ -42452,7 +43028,7 @@
         <v>69</v>
       </c>
       <c r="C2470">
-        <v>6230</v>
+        <v>6130</v>
       </c>
       <c r="D2470" t="s">
         <v>2472</v>
@@ -42466,7 +43042,7 @@
         <v>70</v>
       </c>
       <c r="C2471">
-        <v>6330</v>
+        <v>6230</v>
       </c>
       <c r="D2471" t="s">
         <v>2473</v>
@@ -42480,7 +43056,7 @@
         <v>71</v>
       </c>
       <c r="C2472">
-        <v>6420</v>
+        <v>6320</v>
       </c>
       <c r="D2472" t="s">
         <v>2474</v>
@@ -42494,7 +43070,7 @@
         <v>72</v>
       </c>
       <c r="C2473">
-        <v>6500</v>
+        <v>6400</v>
       </c>
       <c r="D2473" t="s">
         <v>2475</v>
@@ -42508,7 +43084,7 @@
         <v>73</v>
       </c>
       <c r="C2474">
-        <v>6570</v>
+        <v>6470</v>
       </c>
       <c r="D2474" t="s">
         <v>2476</v>
@@ -42522,7 +43098,7 @@
         <v>74</v>
       </c>
       <c r="C2475">
-        <v>6640</v>
+        <v>6540</v>
       </c>
       <c r="D2475" t="s">
         <v>2477</v>
@@ -42536,7 +43112,7 @@
         <v>75</v>
       </c>
       <c r="C2476">
-        <v>6720</v>
+        <v>6620</v>
       </c>
       <c r="D2476" t="s">
         <v>2478</v>
@@ -42550,7 +43126,7 @@
         <v>76</v>
       </c>
       <c r="C2477">
-        <v>6820</v>
+        <v>6720</v>
       </c>
       <c r="D2477" t="s">
         <v>2479</v>
@@ -42564,7 +43140,7 @@
         <v>77</v>
       </c>
       <c r="C2478">
-        <v>6930</v>
+        <v>6830</v>
       </c>
       <c r="D2478" t="s">
         <v>2480</v>
@@ -42578,7 +43154,7 @@
         <v>78</v>
       </c>
       <c r="C2479">
-        <v>7030</v>
+        <v>6930</v>
       </c>
       <c r="D2479" t="s">
         <v>2481</v>
@@ -42592,7 +43168,7 @@
         <v>79</v>
       </c>
       <c r="C2480">
-        <v>7120</v>
+        <v>7020</v>
       </c>
       <c r="D2480" t="s">
         <v>2482</v>
@@ -42606,7 +43182,7 @@
         <v>80</v>
       </c>
       <c r="C2481">
-        <v>7170</v>
+        <v>7070</v>
       </c>
       <c r="D2481" t="s">
         <v>2483</v>
@@ -42620,7 +43196,7 @@
         <v>81</v>
       </c>
       <c r="C2482">
-        <v>7210</v>
+        <v>7110</v>
       </c>
       <c r="D2482" t="s">
         <v>2484</v>
@@ -42634,7 +43210,7 @@
         <v>82</v>
       </c>
       <c r="C2483">
-        <v>7240</v>
+        <v>7140</v>
       </c>
       <c r="D2483" t="s">
         <v>2485</v>
@@ -42648,7 +43224,7 @@
         <v>83</v>
       </c>
       <c r="C2484">
-        <v>7260</v>
+        <v>7160</v>
       </c>
       <c r="D2484" t="s">
         <v>2486</v>
@@ -42662,7 +43238,7 @@
         <v>84</v>
       </c>
       <c r="C2485">
-        <v>7300</v>
+        <v>7200</v>
       </c>
       <c r="D2485" t="s">
         <v>2487</v>
@@ -42676,7 +43252,7 @@
         <v>85</v>
       </c>
       <c r="C2486">
-        <v>7290</v>
+        <v>7190</v>
       </c>
       <c r="D2486" t="s">
         <v>2488</v>
@@ -42690,7 +43266,7 @@
         <v>86</v>
       </c>
       <c r="C2487">
-        <v>7240</v>
+        <v>7140</v>
       </c>
       <c r="D2487" t="s">
         <v>2489</v>
@@ -42704,7 +43280,7 @@
         <v>87</v>
       </c>
       <c r="C2488">
-        <v>7180</v>
+        <v>7080</v>
       </c>
       <c r="D2488" t="s">
         <v>2490</v>
@@ -42718,7 +43294,7 @@
         <v>88</v>
       </c>
       <c r="C2489">
-        <v>7050</v>
+        <v>6950</v>
       </c>
       <c r="D2489" t="s">
         <v>2491</v>
@@ -42732,7 +43308,7 @@
         <v>89</v>
       </c>
       <c r="C2490">
-        <v>6850</v>
+        <v>6750</v>
       </c>
       <c r="D2490" t="s">
         <v>2492</v>
@@ -42746,7 +43322,7 @@
         <v>90</v>
       </c>
       <c r="C2491">
-        <v>6720</v>
+        <v>6620</v>
       </c>
       <c r="D2491" t="s">
         <v>2493</v>
@@ -42760,7 +43336,7 @@
         <v>91</v>
       </c>
       <c r="C2492">
-        <v>6580</v>
+        <v>6480</v>
       </c>
       <c r="D2492" t="s">
         <v>2494</v>
@@ -42774,7 +43350,7 @@
         <v>92</v>
       </c>
       <c r="C2493">
-        <v>6420</v>
+        <v>6320</v>
       </c>
       <c r="D2493" t="s">
         <v>2495</v>
@@ -42788,7 +43364,7 @@
         <v>93</v>
       </c>
       <c r="C2494">
-        <v>6190</v>
+        <v>6090</v>
       </c>
       <c r="D2494" t="s">
         <v>2496</v>
@@ -42802,7 +43378,7 @@
         <v>94</v>
       </c>
       <c r="C2495">
-        <v>6020</v>
+        <v>5920</v>
       </c>
       <c r="D2495" t="s">
         <v>2497</v>
@@ -42816,7 +43392,7 @@
         <v>95</v>
       </c>
       <c r="C2496">
-        <v>5930</v>
+        <v>5830</v>
       </c>
       <c r="D2496" t="s">
         <v>2498</v>
@@ -42830,10 +43406,2698 @@
         <v>96</v>
       </c>
       <c r="C2497">
-        <v>5820</v>
+        <v>5720</v>
       </c>
       <c r="D2497" t="s">
         <v>2499</v>
+      </c>
+    </row>
+    <row r="2498" spans="1:4">
+      <c r="A2498" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2498">
+        <v>1</v>
+      </c>
+      <c r="C2498">
+        <v>5600</v>
+      </c>
+      <c r="D2498" t="s">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="2499" spans="1:4">
+      <c r="A2499" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2499">
+        <v>2</v>
+      </c>
+      <c r="C2499">
+        <v>5540</v>
+      </c>
+      <c r="D2499" t="s">
+        <v>2501</v>
+      </c>
+    </row>
+    <row r="2500" spans="1:4">
+      <c r="A2500" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2500">
+        <v>3</v>
+      </c>
+      <c r="C2500">
+        <v>5490</v>
+      </c>
+      <c r="D2500" t="s">
+        <v>2502</v>
+      </c>
+    </row>
+    <row r="2501" spans="1:4">
+      <c r="A2501" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2501">
+        <v>4</v>
+      </c>
+      <c r="C2501">
+        <v>5420</v>
+      </c>
+      <c r="D2501" t="s">
+        <v>2503</v>
+      </c>
+    </row>
+    <row r="2502" spans="1:4">
+      <c r="A2502" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2502">
+        <v>5</v>
+      </c>
+      <c r="C2502">
+        <v>5350</v>
+      </c>
+      <c r="D2502" t="s">
+        <v>2504</v>
+      </c>
+    </row>
+    <row r="2503" spans="1:4">
+      <c r="A2503" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2503">
+        <v>6</v>
+      </c>
+      <c r="C2503">
+        <v>5290</v>
+      </c>
+      <c r="D2503" t="s">
+        <v>2505</v>
+      </c>
+    </row>
+    <row r="2504" spans="1:4">
+      <c r="A2504" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2504">
+        <v>7</v>
+      </c>
+      <c r="C2504">
+        <v>5230</v>
+      </c>
+      <c r="D2504" t="s">
+        <v>2506</v>
+      </c>
+    </row>
+    <row r="2505" spans="1:4">
+      <c r="A2505" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2505">
+        <v>8</v>
+      </c>
+      <c r="C2505">
+        <v>5190</v>
+      </c>
+      <c r="D2505" t="s">
+        <v>2507</v>
+      </c>
+    </row>
+    <row r="2506" spans="1:4">
+      <c r="A2506" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2506">
+        <v>9</v>
+      </c>
+      <c r="C2506">
+        <v>5160</v>
+      </c>
+      <c r="D2506" t="s">
+        <v>2508</v>
+      </c>
+    </row>
+    <row r="2507" spans="1:4">
+      <c r="A2507" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2507">
+        <v>10</v>
+      </c>
+      <c r="C2507">
+        <v>5140</v>
+      </c>
+      <c r="D2507" t="s">
+        <v>2509</v>
+      </c>
+    </row>
+    <row r="2508" spans="1:4">
+      <c r="A2508" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2508">
+        <v>11</v>
+      </c>
+      <c r="C2508">
+        <v>5120</v>
+      </c>
+      <c r="D2508" t="s">
+        <v>2510</v>
+      </c>
+    </row>
+    <row r="2509" spans="1:4">
+      <c r="A2509" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2509">
+        <v>12</v>
+      </c>
+      <c r="C2509">
+        <v>5110</v>
+      </c>
+      <c r="D2509" t="s">
+        <v>2511</v>
+      </c>
+    </row>
+    <row r="2510" spans="1:4">
+      <c r="A2510" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2510">
+        <v>13</v>
+      </c>
+      <c r="C2510">
+        <v>5110</v>
+      </c>
+      <c r="D2510" t="s">
+        <v>2512</v>
+      </c>
+    </row>
+    <row r="2511" spans="1:4">
+      <c r="A2511" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2511">
+        <v>14</v>
+      </c>
+      <c r="C2511">
+        <v>5110</v>
+      </c>
+      <c r="D2511" t="s">
+        <v>2513</v>
+      </c>
+    </row>
+    <row r="2512" spans="1:4">
+      <c r="A2512" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2512">
+        <v>15</v>
+      </c>
+      <c r="C2512">
+        <v>5110</v>
+      </c>
+      <c r="D2512" t="s">
+        <v>2514</v>
+      </c>
+    </row>
+    <row r="2513" spans="1:4">
+      <c r="A2513" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2513">
+        <v>16</v>
+      </c>
+      <c r="C2513">
+        <v>5110</v>
+      </c>
+      <c r="D2513" t="s">
+        <v>2515</v>
+      </c>
+    </row>
+    <row r="2514" spans="1:4">
+      <c r="A2514" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2514">
+        <v>17</v>
+      </c>
+      <c r="C2514">
+        <v>5120</v>
+      </c>
+      <c r="D2514" t="s">
+        <v>2516</v>
+      </c>
+    </row>
+    <row r="2515" spans="1:4">
+      <c r="A2515" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2515">
+        <v>18</v>
+      </c>
+      <c r="C2515">
+        <v>5120</v>
+      </c>
+      <c r="D2515" t="s">
+        <v>2517</v>
+      </c>
+    </row>
+    <row r="2516" spans="1:4">
+      <c r="A2516" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2516">
+        <v>19</v>
+      </c>
+      <c r="C2516">
+        <v>5140</v>
+      </c>
+      <c r="D2516" t="s">
+        <v>2518</v>
+      </c>
+    </row>
+    <row r="2517" spans="1:4">
+      <c r="A2517" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2517">
+        <v>20</v>
+      </c>
+      <c r="C2517">
+        <v>5160</v>
+      </c>
+      <c r="D2517" t="s">
+        <v>2519</v>
+      </c>
+    </row>
+    <row r="2518" spans="1:4">
+      <c r="A2518" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2518">
+        <v>21</v>
+      </c>
+      <c r="C2518">
+        <v>5190</v>
+      </c>
+      <c r="D2518" t="s">
+        <v>2520</v>
+      </c>
+    </row>
+    <row r="2519" spans="1:4">
+      <c r="A2519" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2519">
+        <v>22</v>
+      </c>
+      <c r="C2519">
+        <v>5230</v>
+      </c>
+      <c r="D2519" t="s">
+        <v>2521</v>
+      </c>
+    </row>
+    <row r="2520" spans="1:4">
+      <c r="A2520" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2520">
+        <v>23</v>
+      </c>
+      <c r="C2520">
+        <v>5280</v>
+      </c>
+      <c r="D2520" t="s">
+        <v>2522</v>
+      </c>
+    </row>
+    <row r="2521" spans="1:4">
+      <c r="A2521" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2521">
+        <v>24</v>
+      </c>
+      <c r="C2521">
+        <v>5340</v>
+      </c>
+      <c r="D2521" t="s">
+        <v>2523</v>
+      </c>
+    </row>
+    <row r="2522" spans="1:4">
+      <c r="A2522" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2522">
+        <v>25</v>
+      </c>
+      <c r="C2522">
+        <v>5410</v>
+      </c>
+      <c r="D2522" t="s">
+        <v>2524</v>
+      </c>
+    </row>
+    <row r="2523" spans="1:4">
+      <c r="A2523" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2523">
+        <v>26</v>
+      </c>
+      <c r="C2523">
+        <v>5480</v>
+      </c>
+      <c r="D2523" t="s">
+        <v>2525</v>
+      </c>
+    </row>
+    <row r="2524" spans="1:4">
+      <c r="A2524" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2524">
+        <v>27</v>
+      </c>
+      <c r="C2524">
+        <v>5570</v>
+      </c>
+      <c r="D2524" t="s">
+        <v>2526</v>
+      </c>
+    </row>
+    <row r="2525" spans="1:4">
+      <c r="A2525" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2525">
+        <v>28</v>
+      </c>
+      <c r="C2525">
+        <v>5660</v>
+      </c>
+      <c r="D2525" t="s">
+        <v>2527</v>
+      </c>
+    </row>
+    <row r="2526" spans="1:4">
+      <c r="A2526" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2526">
+        <v>29</v>
+      </c>
+      <c r="C2526">
+        <v>5750</v>
+      </c>
+      <c r="D2526" t="s">
+        <v>2528</v>
+      </c>
+    </row>
+    <row r="2527" spans="1:4">
+      <c r="A2527" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2527">
+        <v>30</v>
+      </c>
+      <c r="C2527">
+        <v>5840</v>
+      </c>
+      <c r="D2527" t="s">
+        <v>2529</v>
+      </c>
+    </row>
+    <row r="2528" spans="1:4">
+      <c r="A2528" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2528">
+        <v>31</v>
+      </c>
+      <c r="C2528">
+        <v>5920</v>
+      </c>
+      <c r="D2528" t="s">
+        <v>2530</v>
+      </c>
+    </row>
+    <row r="2529" spans="1:4">
+      <c r="A2529" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2529">
+        <v>32</v>
+      </c>
+      <c r="C2529">
+        <v>5990</v>
+      </c>
+      <c r="D2529" t="s">
+        <v>2531</v>
+      </c>
+    </row>
+    <row r="2530" spans="1:4">
+      <c r="A2530" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2530">
+        <v>33</v>
+      </c>
+      <c r="C2530">
+        <v>6030</v>
+      </c>
+      <c r="D2530" t="s">
+        <v>2532</v>
+      </c>
+    </row>
+    <row r="2531" spans="1:4">
+      <c r="A2531" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2531">
+        <v>34</v>
+      </c>
+      <c r="C2531">
+        <v>6040</v>
+      </c>
+      <c r="D2531" t="s">
+        <v>2533</v>
+      </c>
+    </row>
+    <row r="2532" spans="1:4">
+      <c r="A2532" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2532">
+        <v>35</v>
+      </c>
+      <c r="C2532">
+        <v>6020</v>
+      </c>
+      <c r="D2532" t="s">
+        <v>2534</v>
+      </c>
+    </row>
+    <row r="2533" spans="1:4">
+      <c r="A2533" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2533">
+        <v>36</v>
+      </c>
+      <c r="C2533">
+        <v>5960</v>
+      </c>
+      <c r="D2533" t="s">
+        <v>2535</v>
+      </c>
+    </row>
+    <row r="2534" spans="1:4">
+      <c r="A2534" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2534">
+        <v>37</v>
+      </c>
+      <c r="C2534">
+        <v>5880</v>
+      </c>
+      <c r="D2534" t="s">
+        <v>2536</v>
+      </c>
+    </row>
+    <row r="2535" spans="1:4">
+      <c r="A2535" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2535">
+        <v>38</v>
+      </c>
+      <c r="C2535">
+        <v>5780</v>
+      </c>
+      <c r="D2535" t="s">
+        <v>2537</v>
+      </c>
+    </row>
+    <row r="2536" spans="1:4">
+      <c r="A2536" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2536">
+        <v>39</v>
+      </c>
+      <c r="C2536">
+        <v>5650</v>
+      </c>
+      <c r="D2536" t="s">
+        <v>2538</v>
+      </c>
+    </row>
+    <row r="2537" spans="1:4">
+      <c r="A2537" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2537">
+        <v>40</v>
+      </c>
+      <c r="C2537">
+        <v>5530</v>
+      </c>
+      <c r="D2537" t="s">
+        <v>2539</v>
+      </c>
+    </row>
+    <row r="2538" spans="1:4">
+      <c r="A2538" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2538">
+        <v>41</v>
+      </c>
+      <c r="C2538">
+        <v>5410</v>
+      </c>
+      <c r="D2538" t="s">
+        <v>2540</v>
+      </c>
+    </row>
+    <row r="2539" spans="1:4">
+      <c r="A2539" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2539">
+        <v>42</v>
+      </c>
+      <c r="C2539">
+        <v>5300</v>
+      </c>
+      <c r="D2539" t="s">
+        <v>2541</v>
+      </c>
+    </row>
+    <row r="2540" spans="1:4">
+      <c r="A2540" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2540">
+        <v>43</v>
+      </c>
+      <c r="C2540">
+        <v>5210</v>
+      </c>
+      <c r="D2540" t="s">
+        <v>2542</v>
+      </c>
+    </row>
+    <row r="2541" spans="1:4">
+      <c r="A2541" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2541">
+        <v>44</v>
+      </c>
+      <c r="C2541">
+        <v>5160</v>
+      </c>
+      <c r="D2541" t="s">
+        <v>2543</v>
+      </c>
+    </row>
+    <row r="2542" spans="1:4">
+      <c r="A2542" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2542">
+        <v>45</v>
+      </c>
+      <c r="C2542">
+        <v>5120</v>
+      </c>
+      <c r="D2542" t="s">
+        <v>2544</v>
+      </c>
+    </row>
+    <row r="2543" spans="1:4">
+      <c r="A2543" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2543">
+        <v>46</v>
+      </c>
+      <c r="C2543">
+        <v>5120</v>
+      </c>
+      <c r="D2543" t="s">
+        <v>2545</v>
+      </c>
+    </row>
+    <row r="2544" spans="1:4">
+      <c r="A2544" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2544">
+        <v>47</v>
+      </c>
+      <c r="C2544">
+        <v>5130</v>
+      </c>
+      <c r="D2544" t="s">
+        <v>2546</v>
+      </c>
+    </row>
+    <row r="2545" spans="1:4">
+      <c r="A2545" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2545">
+        <v>48</v>
+      </c>
+      <c r="C2545">
+        <v>5150</v>
+      </c>
+      <c r="D2545" t="s">
+        <v>2547</v>
+      </c>
+    </row>
+    <row r="2546" spans="1:4">
+      <c r="A2546" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2546">
+        <v>49</v>
+      </c>
+      <c r="C2546">
+        <v>5180</v>
+      </c>
+      <c r="D2546" t="s">
+        <v>2548</v>
+      </c>
+    </row>
+    <row r="2547" spans="1:4">
+      <c r="A2547" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2547">
+        <v>50</v>
+      </c>
+      <c r="C2547">
+        <v>5200</v>
+      </c>
+      <c r="D2547" t="s">
+        <v>2549</v>
+      </c>
+    </row>
+    <row r="2548" spans="1:4">
+      <c r="A2548" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2548">
+        <v>51</v>
+      </c>
+      <c r="C2548">
+        <v>5220</v>
+      </c>
+      <c r="D2548" t="s">
+        <v>2550</v>
+      </c>
+    </row>
+    <row r="2549" spans="1:4">
+      <c r="A2549" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2549">
+        <v>52</v>
+      </c>
+      <c r="C2549">
+        <v>5230</v>
+      </c>
+      <c r="D2549" t="s">
+        <v>2551</v>
+      </c>
+    </row>
+    <row r="2550" spans="1:4">
+      <c r="A2550" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2550">
+        <v>53</v>
+      </c>
+      <c r="C2550">
+        <v>5250</v>
+      </c>
+      <c r="D2550" t="s">
+        <v>2552</v>
+      </c>
+    </row>
+    <row r="2551" spans="1:4">
+      <c r="A2551" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2551">
+        <v>54</v>
+      </c>
+      <c r="C2551">
+        <v>5260</v>
+      </c>
+      <c r="D2551" t="s">
+        <v>2553</v>
+      </c>
+    </row>
+    <row r="2552" spans="1:4">
+      <c r="A2552" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2552">
+        <v>55</v>
+      </c>
+      <c r="C2552">
+        <v>5280</v>
+      </c>
+      <c r="D2552" t="s">
+        <v>2554</v>
+      </c>
+    </row>
+    <row r="2553" spans="1:4">
+      <c r="A2553" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2553">
+        <v>56</v>
+      </c>
+      <c r="C2553">
+        <v>5300</v>
+      </c>
+      <c r="D2553" t="s">
+        <v>2555</v>
+      </c>
+    </row>
+    <row r="2554" spans="1:4">
+      <c r="A2554" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2554">
+        <v>57</v>
+      </c>
+      <c r="C2554">
+        <v>5340</v>
+      </c>
+      <c r="D2554" t="s">
+        <v>2556</v>
+      </c>
+    </row>
+    <row r="2555" spans="1:4">
+      <c r="A2555" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2555">
+        <v>58</v>
+      </c>
+      <c r="C2555">
+        <v>5390</v>
+      </c>
+      <c r="D2555" t="s">
+        <v>2557</v>
+      </c>
+    </row>
+    <row r="2556" spans="1:4">
+      <c r="A2556" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2556">
+        <v>59</v>
+      </c>
+      <c r="C2556">
+        <v>5450</v>
+      </c>
+      <c r="D2556" t="s">
+        <v>2558</v>
+      </c>
+    </row>
+    <row r="2557" spans="1:4">
+      <c r="A2557" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2557">
+        <v>60</v>
+      </c>
+      <c r="C2557">
+        <v>5510</v>
+      </c>
+      <c r="D2557" t="s">
+        <v>2559</v>
+      </c>
+    </row>
+    <row r="2558" spans="1:4">
+      <c r="A2558" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2558">
+        <v>61</v>
+      </c>
+      <c r="C2558">
+        <v>5570</v>
+      </c>
+      <c r="D2558" t="s">
+        <v>2560</v>
+      </c>
+    </row>
+    <row r="2559" spans="1:4">
+      <c r="A2559" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2559">
+        <v>62</v>
+      </c>
+      <c r="C2559">
+        <v>5630</v>
+      </c>
+      <c r="D2559" t="s">
+        <v>2561</v>
+      </c>
+    </row>
+    <row r="2560" spans="1:4">
+      <c r="A2560" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2560">
+        <v>63</v>
+      </c>
+      <c r="C2560">
+        <v>5690</v>
+      </c>
+      <c r="D2560" t="s">
+        <v>2562</v>
+      </c>
+    </row>
+    <row r="2561" spans="1:4">
+      <c r="A2561" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2561">
+        <v>64</v>
+      </c>
+      <c r="C2561">
+        <v>5760</v>
+      </c>
+      <c r="D2561" t="s">
+        <v>2563</v>
+      </c>
+    </row>
+    <row r="2562" spans="1:4">
+      <c r="A2562" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2562">
+        <v>65</v>
+      </c>
+      <c r="C2562">
+        <v>5820</v>
+      </c>
+      <c r="D2562" t="s">
+        <v>2564</v>
+      </c>
+    </row>
+    <row r="2563" spans="1:4">
+      <c r="A2563" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2563">
+        <v>66</v>
+      </c>
+      <c r="C2563">
+        <v>5900</v>
+      </c>
+      <c r="D2563" t="s">
+        <v>2565</v>
+      </c>
+    </row>
+    <row r="2564" spans="1:4">
+      <c r="A2564" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2564">
+        <v>67</v>
+      </c>
+      <c r="C2564">
+        <v>5990</v>
+      </c>
+      <c r="D2564" t="s">
+        <v>2566</v>
+      </c>
+    </row>
+    <row r="2565" spans="1:4">
+      <c r="A2565" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2565">
+        <v>68</v>
+      </c>
+      <c r="C2565">
+        <v>6080</v>
+      </c>
+      <c r="D2565" t="s">
+        <v>2567</v>
+      </c>
+    </row>
+    <row r="2566" spans="1:4">
+      <c r="A2566" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2566">
+        <v>69</v>
+      </c>
+      <c r="C2566">
+        <v>6180</v>
+      </c>
+      <c r="D2566" t="s">
+        <v>2568</v>
+      </c>
+    </row>
+    <row r="2567" spans="1:4">
+      <c r="A2567" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2567">
+        <v>70</v>
+      </c>
+      <c r="C2567">
+        <v>6280</v>
+      </c>
+      <c r="D2567" t="s">
+        <v>2569</v>
+      </c>
+    </row>
+    <row r="2568" spans="1:4">
+      <c r="A2568" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2568">
+        <v>71</v>
+      </c>
+      <c r="C2568">
+        <v>6370</v>
+      </c>
+      <c r="D2568" t="s">
+        <v>2570</v>
+      </c>
+    </row>
+    <row r="2569" spans="1:4">
+      <c r="A2569" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2569">
+        <v>72</v>
+      </c>
+      <c r="C2569">
+        <v>6450</v>
+      </c>
+      <c r="D2569" t="s">
+        <v>2571</v>
+      </c>
+    </row>
+    <row r="2570" spans="1:4">
+      <c r="A2570" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2570">
+        <v>73</v>
+      </c>
+      <c r="C2570">
+        <v>6520</v>
+      </c>
+      <c r="D2570" t="s">
+        <v>2572</v>
+      </c>
+    </row>
+    <row r="2571" spans="1:4">
+      <c r="A2571" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2571">
+        <v>74</v>
+      </c>
+      <c r="C2571">
+        <v>6590</v>
+      </c>
+      <c r="D2571" t="s">
+        <v>2573</v>
+      </c>
+    </row>
+    <row r="2572" spans="1:4">
+      <c r="A2572" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2572">
+        <v>75</v>
+      </c>
+      <c r="C2572">
+        <v>6670</v>
+      </c>
+      <c r="D2572" t="s">
+        <v>2574</v>
+      </c>
+    </row>
+    <row r="2573" spans="1:4">
+      <c r="A2573" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2573">
+        <v>76</v>
+      </c>
+      <c r="C2573">
+        <v>6770</v>
+      </c>
+      <c r="D2573" t="s">
+        <v>2575</v>
+      </c>
+    </row>
+    <row r="2574" spans="1:4">
+      <c r="A2574" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2574">
+        <v>77</v>
+      </c>
+      <c r="C2574">
+        <v>6880</v>
+      </c>
+      <c r="D2574" t="s">
+        <v>2576</v>
+      </c>
+    </row>
+    <row r="2575" spans="1:4">
+      <c r="A2575" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2575">
+        <v>78</v>
+      </c>
+      <c r="C2575">
+        <v>6980</v>
+      </c>
+      <c r="D2575" t="s">
+        <v>2577</v>
+      </c>
+    </row>
+    <row r="2576" spans="1:4">
+      <c r="A2576" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2576">
+        <v>79</v>
+      </c>
+      <c r="C2576">
+        <v>7070</v>
+      </c>
+      <c r="D2576" t="s">
+        <v>2578</v>
+      </c>
+    </row>
+    <row r="2577" spans="1:4">
+      <c r="A2577" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2577">
+        <v>80</v>
+      </c>
+      <c r="C2577">
+        <v>7120</v>
+      </c>
+      <c r="D2577" t="s">
+        <v>2579</v>
+      </c>
+    </row>
+    <row r="2578" spans="1:4">
+      <c r="A2578" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2578">
+        <v>81</v>
+      </c>
+      <c r="C2578">
+        <v>7160</v>
+      </c>
+      <c r="D2578" t="s">
+        <v>2580</v>
+      </c>
+    </row>
+    <row r="2579" spans="1:4">
+      <c r="A2579" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2579">
+        <v>82</v>
+      </c>
+      <c r="C2579">
+        <v>7190</v>
+      </c>
+      <c r="D2579" t="s">
+        <v>2581</v>
+      </c>
+    </row>
+    <row r="2580" spans="1:4">
+      <c r="A2580" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2580">
+        <v>83</v>
+      </c>
+      <c r="C2580">
+        <v>7210</v>
+      </c>
+      <c r="D2580" t="s">
+        <v>2582</v>
+      </c>
+    </row>
+    <row r="2581" spans="1:4">
+      <c r="A2581" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2581">
+        <v>84</v>
+      </c>
+      <c r="C2581">
+        <v>7250</v>
+      </c>
+      <c r="D2581" t="s">
+        <v>2583</v>
+      </c>
+    </row>
+    <row r="2582" spans="1:4">
+      <c r="A2582" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2582">
+        <v>85</v>
+      </c>
+      <c r="C2582">
+        <v>7240</v>
+      </c>
+      <c r="D2582" t="s">
+        <v>2584</v>
+      </c>
+    </row>
+    <row r="2583" spans="1:4">
+      <c r="A2583" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2583">
+        <v>86</v>
+      </c>
+      <c r="C2583">
+        <v>7190</v>
+      </c>
+      <c r="D2583" t="s">
+        <v>2585</v>
+      </c>
+    </row>
+    <row r="2584" spans="1:4">
+      <c r="A2584" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2584">
+        <v>87</v>
+      </c>
+      <c r="C2584">
+        <v>7130</v>
+      </c>
+      <c r="D2584" t="s">
+        <v>2586</v>
+      </c>
+    </row>
+    <row r="2585" spans="1:4">
+      <c r="A2585" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2585">
+        <v>88</v>
+      </c>
+      <c r="C2585">
+        <v>7000</v>
+      </c>
+      <c r="D2585" t="s">
+        <v>2587</v>
+      </c>
+    </row>
+    <row r="2586" spans="1:4">
+      <c r="A2586" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2586">
+        <v>89</v>
+      </c>
+      <c r="C2586">
+        <v>6800</v>
+      </c>
+      <c r="D2586" t="s">
+        <v>2588</v>
+      </c>
+    </row>
+    <row r="2587" spans="1:4">
+      <c r="A2587" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2587">
+        <v>90</v>
+      </c>
+      <c r="C2587">
+        <v>6670</v>
+      </c>
+      <c r="D2587" t="s">
+        <v>2589</v>
+      </c>
+    </row>
+    <row r="2588" spans="1:4">
+      <c r="A2588" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2588">
+        <v>91</v>
+      </c>
+      <c r="C2588">
+        <v>6530</v>
+      </c>
+      <c r="D2588" t="s">
+        <v>2590</v>
+      </c>
+    </row>
+    <row r="2589" spans="1:4">
+      <c r="A2589" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2589">
+        <v>92</v>
+      </c>
+      <c r="C2589">
+        <v>6370</v>
+      </c>
+      <c r="D2589" t="s">
+        <v>2591</v>
+      </c>
+    </row>
+    <row r="2590" spans="1:4">
+      <c r="A2590" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2590">
+        <v>93</v>
+      </c>
+      <c r="C2590">
+        <v>6140</v>
+      </c>
+      <c r="D2590" t="s">
+        <v>2592</v>
+      </c>
+    </row>
+    <row r="2591" spans="1:4">
+      <c r="A2591" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2591">
+        <v>94</v>
+      </c>
+      <c r="C2591">
+        <v>5970</v>
+      </c>
+      <c r="D2591" t="s">
+        <v>2593</v>
+      </c>
+    </row>
+    <row r="2592" spans="1:4">
+      <c r="A2592" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2592">
+        <v>95</v>
+      </c>
+      <c r="C2592">
+        <v>5880</v>
+      </c>
+      <c r="D2592" t="s">
+        <v>2594</v>
+      </c>
+    </row>
+    <row r="2593" spans="1:4">
+      <c r="A2593" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B2593">
+        <v>96</v>
+      </c>
+      <c r="C2593">
+        <v>5770</v>
+      </c>
+      <c r="D2593" t="s">
+        <v>2595</v>
+      </c>
+    </row>
+    <row r="2594" spans="1:4">
+      <c r="A2594" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2594">
+        <v>1</v>
+      </c>
+      <c r="C2594">
+        <v>5520</v>
+      </c>
+      <c r="D2594" t="s">
+        <v>2596</v>
+      </c>
+    </row>
+    <row r="2595" spans="1:4">
+      <c r="A2595" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2595">
+        <v>2</v>
+      </c>
+      <c r="C2595">
+        <v>5460</v>
+      </c>
+      <c r="D2595" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="2596" spans="1:4">
+      <c r="A2596" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2596">
+        <v>3</v>
+      </c>
+      <c r="C2596">
+        <v>5410</v>
+      </c>
+      <c r="D2596" t="s">
+        <v>2598</v>
+      </c>
+    </row>
+    <row r="2597" spans="1:4">
+      <c r="A2597" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2597">
+        <v>4</v>
+      </c>
+      <c r="C2597">
+        <v>5340</v>
+      </c>
+      <c r="D2597" t="s">
+        <v>2599</v>
+      </c>
+    </row>
+    <row r="2598" spans="1:4">
+      <c r="A2598" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2598">
+        <v>5</v>
+      </c>
+      <c r="C2598">
+        <v>5270</v>
+      </c>
+      <c r="D2598" t="s">
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="2599" spans="1:4">
+      <c r="A2599" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2599">
+        <v>6</v>
+      </c>
+      <c r="C2599">
+        <v>5210</v>
+      </c>
+      <c r="D2599" t="s">
+        <v>2601</v>
+      </c>
+    </row>
+    <row r="2600" spans="1:4">
+      <c r="A2600" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2600">
+        <v>7</v>
+      </c>
+      <c r="C2600">
+        <v>5150</v>
+      </c>
+      <c r="D2600" t="s">
+        <v>2602</v>
+      </c>
+    </row>
+    <row r="2601" spans="1:4">
+      <c r="A2601" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2601">
+        <v>8</v>
+      </c>
+      <c r="C2601">
+        <v>5110</v>
+      </c>
+      <c r="D2601" t="s">
+        <v>2603</v>
+      </c>
+    </row>
+    <row r="2602" spans="1:4">
+      <c r="A2602" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2602">
+        <v>9</v>
+      </c>
+      <c r="C2602">
+        <v>5080</v>
+      </c>
+      <c r="D2602" t="s">
+        <v>2604</v>
+      </c>
+    </row>
+    <row r="2603" spans="1:4">
+      <c r="A2603" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2603">
+        <v>10</v>
+      </c>
+      <c r="C2603">
+        <v>5060</v>
+      </c>
+      <c r="D2603" t="s">
+        <v>2605</v>
+      </c>
+    </row>
+    <row r="2604" spans="1:4">
+      <c r="A2604" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2604">
+        <v>11</v>
+      </c>
+      <c r="C2604">
+        <v>5040</v>
+      </c>
+      <c r="D2604" t="s">
+        <v>2606</v>
+      </c>
+    </row>
+    <row r="2605" spans="1:4">
+      <c r="A2605" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2605">
+        <v>12</v>
+      </c>
+      <c r="C2605">
+        <v>5030</v>
+      </c>
+      <c r="D2605" t="s">
+        <v>2607</v>
+      </c>
+    </row>
+    <row r="2606" spans="1:4">
+      <c r="A2606" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2606">
+        <v>13</v>
+      </c>
+      <c r="C2606">
+        <v>5030</v>
+      </c>
+      <c r="D2606" t="s">
+        <v>2608</v>
+      </c>
+    </row>
+    <row r="2607" spans="1:4">
+      <c r="A2607" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2607">
+        <v>14</v>
+      </c>
+      <c r="C2607">
+        <v>5030</v>
+      </c>
+      <c r="D2607" t="s">
+        <v>2609</v>
+      </c>
+    </row>
+    <row r="2608" spans="1:4">
+      <c r="A2608" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2608">
+        <v>15</v>
+      </c>
+      <c r="C2608">
+        <v>5030</v>
+      </c>
+      <c r="D2608" t="s">
+        <v>2610</v>
+      </c>
+    </row>
+    <row r="2609" spans="1:4">
+      <c r="A2609" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2609">
+        <v>16</v>
+      </c>
+      <c r="C2609">
+        <v>5030</v>
+      </c>
+      <c r="D2609" t="s">
+        <v>2611</v>
+      </c>
+    </row>
+    <row r="2610" spans="1:4">
+      <c r="A2610" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2610">
+        <v>17</v>
+      </c>
+      <c r="C2610">
+        <v>5040</v>
+      </c>
+      <c r="D2610" t="s">
+        <v>2612</v>
+      </c>
+    </row>
+    <row r="2611" spans="1:4">
+      <c r="A2611" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2611">
+        <v>18</v>
+      </c>
+      <c r="C2611">
+        <v>5040</v>
+      </c>
+      <c r="D2611" t="s">
+        <v>2613</v>
+      </c>
+    </row>
+    <row r="2612" spans="1:4">
+      <c r="A2612" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2612">
+        <v>19</v>
+      </c>
+      <c r="C2612">
+        <v>5060</v>
+      </c>
+      <c r="D2612" t="s">
+        <v>2614</v>
+      </c>
+    </row>
+    <row r="2613" spans="1:4">
+      <c r="A2613" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2613">
+        <v>20</v>
+      </c>
+      <c r="C2613">
+        <v>5080</v>
+      </c>
+      <c r="D2613" t="s">
+        <v>2615</v>
+      </c>
+    </row>
+    <row r="2614" spans="1:4">
+      <c r="A2614" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2614">
+        <v>21</v>
+      </c>
+      <c r="C2614">
+        <v>5110</v>
+      </c>
+      <c r="D2614" t="s">
+        <v>2616</v>
+      </c>
+    </row>
+    <row r="2615" spans="1:4">
+      <c r="A2615" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2615">
+        <v>22</v>
+      </c>
+      <c r="C2615">
+        <v>5150</v>
+      </c>
+      <c r="D2615" t="s">
+        <v>2617</v>
+      </c>
+    </row>
+    <row r="2616" spans="1:4">
+      <c r="A2616" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2616">
+        <v>23</v>
+      </c>
+      <c r="C2616">
+        <v>5200</v>
+      </c>
+      <c r="D2616" t="s">
+        <v>2618</v>
+      </c>
+    </row>
+    <row r="2617" spans="1:4">
+      <c r="A2617" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2617">
+        <v>24</v>
+      </c>
+      <c r="C2617">
+        <v>5260</v>
+      </c>
+      <c r="D2617" t="s">
+        <v>2619</v>
+      </c>
+    </row>
+    <row r="2618" spans="1:4">
+      <c r="A2618" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2618">
+        <v>25</v>
+      </c>
+      <c r="C2618">
+        <v>5330</v>
+      </c>
+      <c r="D2618" t="s">
+        <v>2620</v>
+      </c>
+    </row>
+    <row r="2619" spans="1:4">
+      <c r="A2619" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2619">
+        <v>26</v>
+      </c>
+      <c r="C2619">
+        <v>5400</v>
+      </c>
+      <c r="D2619" t="s">
+        <v>2621</v>
+      </c>
+    </row>
+    <row r="2620" spans="1:4">
+      <c r="A2620" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2620">
+        <v>27</v>
+      </c>
+      <c r="C2620">
+        <v>5490</v>
+      </c>
+      <c r="D2620" t="s">
+        <v>2622</v>
+      </c>
+    </row>
+    <row r="2621" spans="1:4">
+      <c r="A2621" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2621">
+        <v>28</v>
+      </c>
+      <c r="C2621">
+        <v>5580</v>
+      </c>
+      <c r="D2621" t="s">
+        <v>2623</v>
+      </c>
+    </row>
+    <row r="2622" spans="1:4">
+      <c r="A2622" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2622">
+        <v>29</v>
+      </c>
+      <c r="C2622">
+        <v>5670</v>
+      </c>
+      <c r="D2622" t="s">
+        <v>2624</v>
+      </c>
+    </row>
+    <row r="2623" spans="1:4">
+      <c r="A2623" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2623">
+        <v>30</v>
+      </c>
+      <c r="C2623">
+        <v>5760</v>
+      </c>
+      <c r="D2623" t="s">
+        <v>2625</v>
+      </c>
+    </row>
+    <row r="2624" spans="1:4">
+      <c r="A2624" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2624">
+        <v>31</v>
+      </c>
+      <c r="C2624">
+        <v>5840</v>
+      </c>
+      <c r="D2624" t="s">
+        <v>2626</v>
+      </c>
+    </row>
+    <row r="2625" spans="1:4">
+      <c r="A2625" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2625">
+        <v>32</v>
+      </c>
+      <c r="C2625">
+        <v>5910</v>
+      </c>
+      <c r="D2625" t="s">
+        <v>2627</v>
+      </c>
+    </row>
+    <row r="2626" spans="1:4">
+      <c r="A2626" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2626">
+        <v>33</v>
+      </c>
+      <c r="C2626">
+        <v>5950</v>
+      </c>
+      <c r="D2626" t="s">
+        <v>2628</v>
+      </c>
+    </row>
+    <row r="2627" spans="1:4">
+      <c r="A2627" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2627">
+        <v>34</v>
+      </c>
+      <c r="C2627">
+        <v>5960</v>
+      </c>
+      <c r="D2627" t="s">
+        <v>2629</v>
+      </c>
+    </row>
+    <row r="2628" spans="1:4">
+      <c r="A2628" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2628">
+        <v>35</v>
+      </c>
+      <c r="C2628">
+        <v>5940</v>
+      </c>
+      <c r="D2628" t="s">
+        <v>2630</v>
+      </c>
+    </row>
+    <row r="2629" spans="1:4">
+      <c r="A2629" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2629">
+        <v>36</v>
+      </c>
+      <c r="C2629">
+        <v>5880</v>
+      </c>
+      <c r="D2629" t="s">
+        <v>2631</v>
+      </c>
+    </row>
+    <row r="2630" spans="1:4">
+      <c r="A2630" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2630">
+        <v>37</v>
+      </c>
+      <c r="C2630">
+        <v>5800</v>
+      </c>
+      <c r="D2630" t="s">
+        <v>2632</v>
+      </c>
+    </row>
+    <row r="2631" spans="1:4">
+      <c r="A2631" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2631">
+        <v>38</v>
+      </c>
+      <c r="C2631">
+        <v>5700</v>
+      </c>
+      <c r="D2631" t="s">
+        <v>2633</v>
+      </c>
+    </row>
+    <row r="2632" spans="1:4">
+      <c r="A2632" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2632">
+        <v>39</v>
+      </c>
+      <c r="C2632">
+        <v>5570</v>
+      </c>
+      <c r="D2632" t="s">
+        <v>2634</v>
+      </c>
+    </row>
+    <row r="2633" spans="1:4">
+      <c r="A2633" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2633">
+        <v>40</v>
+      </c>
+      <c r="C2633">
+        <v>5450</v>
+      </c>
+      <c r="D2633" t="s">
+        <v>2635</v>
+      </c>
+    </row>
+    <row r="2634" spans="1:4">
+      <c r="A2634" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2634">
+        <v>41</v>
+      </c>
+      <c r="C2634">
+        <v>5330</v>
+      </c>
+      <c r="D2634" t="s">
+        <v>2636</v>
+      </c>
+    </row>
+    <row r="2635" spans="1:4">
+      <c r="A2635" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2635">
+        <v>42</v>
+      </c>
+      <c r="C2635">
+        <v>5220</v>
+      </c>
+      <c r="D2635" t="s">
+        <v>2637</v>
+      </c>
+    </row>
+    <row r="2636" spans="1:4">
+      <c r="A2636" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2636">
+        <v>43</v>
+      </c>
+      <c r="C2636">
+        <v>5130</v>
+      </c>
+      <c r="D2636" t="s">
+        <v>2638</v>
+      </c>
+    </row>
+    <row r="2637" spans="1:4">
+      <c r="A2637" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2637">
+        <v>44</v>
+      </c>
+      <c r="C2637">
+        <v>5080</v>
+      </c>
+      <c r="D2637" t="s">
+        <v>2639</v>
+      </c>
+    </row>
+    <row r="2638" spans="1:4">
+      <c r="A2638" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2638">
+        <v>45</v>
+      </c>
+      <c r="C2638">
+        <v>5040</v>
+      </c>
+      <c r="D2638" t="s">
+        <v>2640</v>
+      </c>
+    </row>
+    <row r="2639" spans="1:4">
+      <c r="A2639" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2639">
+        <v>46</v>
+      </c>
+      <c r="C2639">
+        <v>5040</v>
+      </c>
+      <c r="D2639" t="s">
+        <v>2641</v>
+      </c>
+    </row>
+    <row r="2640" spans="1:4">
+      <c r="A2640" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2640">
+        <v>47</v>
+      </c>
+      <c r="C2640">
+        <v>5050</v>
+      </c>
+      <c r="D2640" t="s">
+        <v>2642</v>
+      </c>
+    </row>
+    <row r="2641" spans="1:4">
+      <c r="A2641" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2641">
+        <v>48</v>
+      </c>
+      <c r="C2641">
+        <v>5070</v>
+      </c>
+      <c r="D2641" t="s">
+        <v>2643</v>
+      </c>
+    </row>
+    <row r="2642" spans="1:4">
+      <c r="A2642" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2642">
+        <v>49</v>
+      </c>
+      <c r="C2642">
+        <v>5100</v>
+      </c>
+      <c r="D2642" t="s">
+        <v>2644</v>
+      </c>
+    </row>
+    <row r="2643" spans="1:4">
+      <c r="A2643" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2643">
+        <v>50</v>
+      </c>
+      <c r="C2643">
+        <v>5120</v>
+      </c>
+      <c r="D2643" t="s">
+        <v>2645</v>
+      </c>
+    </row>
+    <row r="2644" spans="1:4">
+      <c r="A2644" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2644">
+        <v>51</v>
+      </c>
+      <c r="C2644">
+        <v>5140</v>
+      </c>
+      <c r="D2644" t="s">
+        <v>2646</v>
+      </c>
+    </row>
+    <row r="2645" spans="1:4">
+      <c r="A2645" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2645">
+        <v>52</v>
+      </c>
+      <c r="C2645">
+        <v>5150</v>
+      </c>
+      <c r="D2645" t="s">
+        <v>2647</v>
+      </c>
+    </row>
+    <row r="2646" spans="1:4">
+      <c r="A2646" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2646">
+        <v>53</v>
+      </c>
+      <c r="C2646">
+        <v>5170</v>
+      </c>
+      <c r="D2646" t="s">
+        <v>2648</v>
+      </c>
+    </row>
+    <row r="2647" spans="1:4">
+      <c r="A2647" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2647">
+        <v>54</v>
+      </c>
+      <c r="C2647">
+        <v>5180</v>
+      </c>
+      <c r="D2647" t="s">
+        <v>2649</v>
+      </c>
+    </row>
+    <row r="2648" spans="1:4">
+      <c r="A2648" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2648">
+        <v>55</v>
+      </c>
+      <c r="C2648">
+        <v>5200</v>
+      </c>
+      <c r="D2648" t="s">
+        <v>2650</v>
+      </c>
+    </row>
+    <row r="2649" spans="1:4">
+      <c r="A2649" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2649">
+        <v>56</v>
+      </c>
+      <c r="C2649">
+        <v>5220</v>
+      </c>
+      <c r="D2649" t="s">
+        <v>2651</v>
+      </c>
+    </row>
+    <row r="2650" spans="1:4">
+      <c r="A2650" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2650">
+        <v>57</v>
+      </c>
+      <c r="C2650">
+        <v>5260</v>
+      </c>
+      <c r="D2650" t="s">
+        <v>2652</v>
+      </c>
+    </row>
+    <row r="2651" spans="1:4">
+      <c r="A2651" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2651">
+        <v>58</v>
+      </c>
+      <c r="C2651">
+        <v>5310</v>
+      </c>
+      <c r="D2651" t="s">
+        <v>2653</v>
+      </c>
+    </row>
+    <row r="2652" spans="1:4">
+      <c r="A2652" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2652">
+        <v>59</v>
+      </c>
+      <c r="C2652">
+        <v>5370</v>
+      </c>
+      <c r="D2652" t="s">
+        <v>2654</v>
+      </c>
+    </row>
+    <row r="2653" spans="1:4">
+      <c r="A2653" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2653">
+        <v>60</v>
+      </c>
+      <c r="C2653">
+        <v>5430</v>
+      </c>
+      <c r="D2653" t="s">
+        <v>2655</v>
+      </c>
+    </row>
+    <row r="2654" spans="1:4">
+      <c r="A2654" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2654">
+        <v>61</v>
+      </c>
+      <c r="C2654">
+        <v>5490</v>
+      </c>
+      <c r="D2654" t="s">
+        <v>2656</v>
+      </c>
+    </row>
+    <row r="2655" spans="1:4">
+      <c r="A2655" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2655">
+        <v>62</v>
+      </c>
+      <c r="C2655">
+        <v>5550</v>
+      </c>
+      <c r="D2655" t="s">
+        <v>2657</v>
+      </c>
+    </row>
+    <row r="2656" spans="1:4">
+      <c r="A2656" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2656">
+        <v>63</v>
+      </c>
+      <c r="C2656">
+        <v>5610</v>
+      </c>
+      <c r="D2656" t="s">
+        <v>2658</v>
+      </c>
+    </row>
+    <row r="2657" spans="1:4">
+      <c r="A2657" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2657">
+        <v>64</v>
+      </c>
+      <c r="C2657">
+        <v>5680</v>
+      </c>
+      <c r="D2657" t="s">
+        <v>2659</v>
+      </c>
+    </row>
+    <row r="2658" spans="1:4">
+      <c r="A2658" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2658">
+        <v>65</v>
+      </c>
+      <c r="C2658">
+        <v>5740</v>
+      </c>
+      <c r="D2658" t="s">
+        <v>2660</v>
+      </c>
+    </row>
+    <row r="2659" spans="1:4">
+      <c r="A2659" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2659">
+        <v>66</v>
+      </c>
+      <c r="C2659">
+        <v>5820</v>
+      </c>
+      <c r="D2659" t="s">
+        <v>2661</v>
+      </c>
+    </row>
+    <row r="2660" spans="1:4">
+      <c r="A2660" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2660">
+        <v>67</v>
+      </c>
+      <c r="C2660">
+        <v>5910</v>
+      </c>
+      <c r="D2660" t="s">
+        <v>2662</v>
+      </c>
+    </row>
+    <row r="2661" spans="1:4">
+      <c r="A2661" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2661">
+        <v>68</v>
+      </c>
+      <c r="C2661">
+        <v>6000</v>
+      </c>
+      <c r="D2661" t="s">
+        <v>2663</v>
+      </c>
+    </row>
+    <row r="2662" spans="1:4">
+      <c r="A2662" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2662">
+        <v>69</v>
+      </c>
+      <c r="C2662">
+        <v>6100</v>
+      </c>
+      <c r="D2662" t="s">
+        <v>2664</v>
+      </c>
+    </row>
+    <row r="2663" spans="1:4">
+      <c r="A2663" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2663">
+        <v>70</v>
+      </c>
+      <c r="C2663">
+        <v>6200</v>
+      </c>
+      <c r="D2663" t="s">
+        <v>2665</v>
+      </c>
+    </row>
+    <row r="2664" spans="1:4">
+      <c r="A2664" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2664">
+        <v>71</v>
+      </c>
+      <c r="C2664">
+        <v>6290</v>
+      </c>
+      <c r="D2664" t="s">
+        <v>2666</v>
+      </c>
+    </row>
+    <row r="2665" spans="1:4">
+      <c r="A2665" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2665">
+        <v>72</v>
+      </c>
+      <c r="C2665">
+        <v>6370</v>
+      </c>
+      <c r="D2665" t="s">
+        <v>2667</v>
+      </c>
+    </row>
+    <row r="2666" spans="1:4">
+      <c r="A2666" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2666">
+        <v>73</v>
+      </c>
+      <c r="C2666">
+        <v>6440</v>
+      </c>
+      <c r="D2666" t="s">
+        <v>2668</v>
+      </c>
+    </row>
+    <row r="2667" spans="1:4">
+      <c r="A2667" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2667">
+        <v>74</v>
+      </c>
+      <c r="C2667">
+        <v>6510</v>
+      </c>
+      <c r="D2667" t="s">
+        <v>2669</v>
+      </c>
+    </row>
+    <row r="2668" spans="1:4">
+      <c r="A2668" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2668">
+        <v>75</v>
+      </c>
+      <c r="C2668">
+        <v>6590</v>
+      </c>
+      <c r="D2668" t="s">
+        <v>2670</v>
+      </c>
+    </row>
+    <row r="2669" spans="1:4">
+      <c r="A2669" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2669">
+        <v>76</v>
+      </c>
+      <c r="C2669">
+        <v>6690</v>
+      </c>
+      <c r="D2669" t="s">
+        <v>2671</v>
+      </c>
+    </row>
+    <row r="2670" spans="1:4">
+      <c r="A2670" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2670">
+        <v>77</v>
+      </c>
+      <c r="C2670">
+        <v>6800</v>
+      </c>
+      <c r="D2670" t="s">
+        <v>2672</v>
+      </c>
+    </row>
+    <row r="2671" spans="1:4">
+      <c r="A2671" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2671">
+        <v>78</v>
+      </c>
+      <c r="C2671">
+        <v>6900</v>
+      </c>
+      <c r="D2671" t="s">
+        <v>2673</v>
+      </c>
+    </row>
+    <row r="2672" spans="1:4">
+      <c r="A2672" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2672">
+        <v>79</v>
+      </c>
+      <c r="C2672">
+        <v>6990</v>
+      </c>
+      <c r="D2672" t="s">
+        <v>2674</v>
+      </c>
+    </row>
+    <row r="2673" spans="1:4">
+      <c r="A2673" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2673">
+        <v>80</v>
+      </c>
+      <c r="C2673">
+        <v>7040</v>
+      </c>
+      <c r="D2673" t="s">
+        <v>2675</v>
+      </c>
+    </row>
+    <row r="2674" spans="1:4">
+      <c r="A2674" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2674">
+        <v>81</v>
+      </c>
+      <c r="C2674">
+        <v>7080</v>
+      </c>
+      <c r="D2674" t="s">
+        <v>2676</v>
+      </c>
+    </row>
+    <row r="2675" spans="1:4">
+      <c r="A2675" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2675">
+        <v>82</v>
+      </c>
+      <c r="C2675">
+        <v>7110</v>
+      </c>
+      <c r="D2675" t="s">
+        <v>2677</v>
+      </c>
+    </row>
+    <row r="2676" spans="1:4">
+      <c r="A2676" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2676">
+        <v>83</v>
+      </c>
+      <c r="C2676">
+        <v>7130</v>
+      </c>
+      <c r="D2676" t="s">
+        <v>2678</v>
+      </c>
+    </row>
+    <row r="2677" spans="1:4">
+      <c r="A2677" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2677">
+        <v>84</v>
+      </c>
+      <c r="C2677">
+        <v>7170</v>
+      </c>
+      <c r="D2677" t="s">
+        <v>2679</v>
+      </c>
+    </row>
+    <row r="2678" spans="1:4">
+      <c r="A2678" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2678">
+        <v>85</v>
+      </c>
+      <c r="C2678">
+        <v>7160</v>
+      </c>
+      <c r="D2678" t="s">
+        <v>2680</v>
+      </c>
+    </row>
+    <row r="2679" spans="1:4">
+      <c r="A2679" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2679">
+        <v>86</v>
+      </c>
+      <c r="C2679">
+        <v>7110</v>
+      </c>
+      <c r="D2679" t="s">
+        <v>2681</v>
+      </c>
+    </row>
+    <row r="2680" spans="1:4">
+      <c r="A2680" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2680">
+        <v>87</v>
+      </c>
+      <c r="C2680">
+        <v>7050</v>
+      </c>
+      <c r="D2680" t="s">
+        <v>2682</v>
+      </c>
+    </row>
+    <row r="2681" spans="1:4">
+      <c r="A2681" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2681">
+        <v>88</v>
+      </c>
+      <c r="C2681">
+        <v>6920</v>
+      </c>
+      <c r="D2681" t="s">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="2682" spans="1:4">
+      <c r="A2682" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2682">
+        <v>89</v>
+      </c>
+      <c r="C2682">
+        <v>6720</v>
+      </c>
+      <c r="D2682" t="s">
+        <v>2684</v>
+      </c>
+    </row>
+    <row r="2683" spans="1:4">
+      <c r="A2683" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2683">
+        <v>90</v>
+      </c>
+      <c r="C2683">
+        <v>6590</v>
+      </c>
+      <c r="D2683" t="s">
+        <v>2685</v>
+      </c>
+    </row>
+    <row r="2684" spans="1:4">
+      <c r="A2684" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2684">
+        <v>91</v>
+      </c>
+      <c r="C2684">
+        <v>6450</v>
+      </c>
+      <c r="D2684" t="s">
+        <v>2686</v>
+      </c>
+    </row>
+    <row r="2685" spans="1:4">
+      <c r="A2685" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2685">
+        <v>92</v>
+      </c>
+      <c r="C2685">
+        <v>6290</v>
+      </c>
+      <c r="D2685" t="s">
+        <v>2687</v>
+      </c>
+    </row>
+    <row r="2686" spans="1:4">
+      <c r="A2686" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2686">
+        <v>93</v>
+      </c>
+      <c r="C2686">
+        <v>6060</v>
+      </c>
+      <c r="D2686" t="s">
+        <v>2688</v>
+      </c>
+    </row>
+    <row r="2687" spans="1:4">
+      <c r="A2687" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2687">
+        <v>94</v>
+      </c>
+      <c r="C2687">
+        <v>5890</v>
+      </c>
+      <c r="D2687" t="s">
+        <v>2689</v>
+      </c>
+    </row>
+    <row r="2688" spans="1:4">
+      <c r="A2688" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2688">
+        <v>95</v>
+      </c>
+      <c r="C2688">
+        <v>5800</v>
+      </c>
+      <c r="D2688" t="s">
+        <v>2690</v>
+      </c>
+    </row>
+    <row r="2689" spans="1:4">
+      <c r="A2689" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B2689">
+        <v>96</v>
+      </c>
+      <c r="C2689">
+        <v>5690</v>
+      </c>
+      <c r="D2689" t="s">
+        <v>2691</v>
       </c>
     </row>
   </sheetData>
